--- a/NRCS/Output/NRCS_Timetable_Final.xlsx
+++ b/NRCS/Output/NRCS_Timetable_Final.xlsx
@@ -658,13 +658,13 @@
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>U.K.G (EVS)</t>
+          <t>U.K.G (MATH)</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr"/>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (G.K)</t>
+          <t>Class 1 (MATH)</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
@@ -672,12 +672,12 @@
           <t>Class 1 (MATH)</t>
         </is>
       </c>
-      <c r="G5" s="7" t="inlineStr"/>
-      <c r="H5" s="7" t="inlineStr">
+      <c r="G5" s="7" t="inlineStr">
         <is>
           <t>U.K.G (MATH)</t>
         </is>
       </c>
+      <c r="H5" s="7" t="inlineStr"/>
       <c r="I5" s="8" t="inlineStr">
         <is>
           <t>U.K.G</t>
@@ -692,27 +692,31 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>U.K.G (MATH)</t>
+          <t>U.K.G (EVS)</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr"/>
-      <c r="D6" s="7" t="inlineStr"/>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>U.K.G (EVS)</t>
+        </is>
+      </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
+          <t>Class 2 (G.K)</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr"/>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
           <t>Class 1 (MATH)</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (MATH)</t>
-        </is>
-      </c>
-      <c r="G6" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (EVS)</t>
-        </is>
-      </c>
-      <c r="H6" s="7" t="inlineStr"/>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>Class 1 (MATH)</t>
+        </is>
+      </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
           <t>U.K.G</t>
@@ -730,28 +734,20 @@
           <t>U.K.G (MATH)</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (EVS)</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr"/>
+      <c r="C7" s="7" t="inlineStr"/>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>Class 1 (MATH)</t>
+        </is>
+      </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>U.K.G (MATH)</t>
+          <t>Class 1 (MATH)</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr"/>
-      <c r="G7" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (EVS)</t>
-        </is>
-      </c>
-      <c r="H7" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (MATH)</t>
-        </is>
-      </c>
+      <c r="G7" s="7" t="inlineStr"/>
+      <c r="H7" s="7" t="inlineStr"/>
       <c r="I7" s="8" t="inlineStr">
         <is>
           <t>U.K.G</t>
@@ -766,21 +762,25 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
+          <t>U.K.G (EVS)</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr"/>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>Class 1 (MATH)</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>U.K.G (EVS)</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
           <t>U.K.G (MATH)</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (EVS)</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (MATH)</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr"/>
-      <c r="F8" s="7" t="inlineStr"/>
       <c r="G8" s="7" t="inlineStr"/>
       <c r="H8" s="7" t="inlineStr"/>
       <c r="I8" s="8" t="inlineStr">
@@ -800,26 +800,26 @@
           <t>U.K.G (MATH)</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr"/>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (MATH)</t>
-        </is>
-      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>U.K.G (EVS)</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr"/>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>Class 1 (MATH)</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
           <t>U.K.G (MATH)</t>
         </is>
       </c>
-      <c r="G9" s="7" t="inlineStr"/>
+      <c r="F9" s="7" t="inlineStr"/>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>U.K.G (MATH)</t>
+        </is>
+      </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (G.K)</t>
+          <t>U.K.G (MATH)</t>
         </is>
       </c>
       <c r="I9" s="8" t="inlineStr">
@@ -836,31 +836,31 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
+          <t>U.K.G (EVS)</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (G.K)</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr"/>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>U.K.G (EVS)</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
           <t>U.K.G (MATH)</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (EVS)</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (MATH)</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr"/>
-      <c r="F10" s="7" t="inlineStr">
+      <c r="G10" s="7" t="inlineStr">
         <is>
           <t>U.K.G (MATH)</t>
         </is>
       </c>
-      <c r="G10" s="7" t="inlineStr"/>
-      <c r="H10" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (EVS)</t>
-        </is>
-      </c>
+      <c r="H10" s="7" t="inlineStr"/>
       <c r="I10" s="8" t="inlineStr">
         <is>
           <t>U.K.G</t>
@@ -937,7 +937,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Class 9 (CHEM)</t>
+          <t>Class 10 (PHY)</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -945,12 +945,12 @@
           <t>Class 9 (PHY)</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr"/>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (CHEM)</t>
-        </is>
-      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (CHEM)</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr"/>
       <c r="F14" s="7" t="inlineStr"/>
       <c r="G14" s="7" t="inlineStr"/>
       <c r="H14" s="7" t="inlineStr"/>
@@ -964,20 +964,20 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
+          <t>Class 10 (PHY)</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (PHY)</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr"/>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
           <t>Class 10 (CHEM)</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (PHY)</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (CHEM)</t>
-        </is>
-      </c>
-      <c r="E15" s="7" t="inlineStr"/>
       <c r="F15" s="7" t="inlineStr"/>
       <c r="G15" s="7" t="inlineStr"/>
       <c r="H15" s="7" t="inlineStr"/>
@@ -991,19 +991,11 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Class 10 (PHY)</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (PHY)</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (CHEM)</t>
-        </is>
-      </c>
+          <t>Class 10 (CHEM)</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr"/>
+      <c r="D16" s="7" t="inlineStr"/>
       <c r="E16" s="7" t="inlineStr"/>
       <c r="F16" s="7" t="inlineStr"/>
       <c r="G16" s="7" t="inlineStr"/>
@@ -1016,22 +1008,14 @@
           <t>THU</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (CHEM)</t>
-        </is>
-      </c>
+      <c r="B17" s="7" t="inlineStr"/>
       <c r="C17" s="7" t="inlineStr"/>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Class 9 (CHEM)</t>
-        </is>
-      </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (PHY)</t>
-        </is>
-      </c>
+          <t>Class 8 (PHY)</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr"/>
       <c r="F17" s="7" t="inlineStr"/>
       <c r="G17" s="7" t="inlineStr"/>
       <c r="H17" s="7" t="inlineStr"/>
@@ -1043,20 +1027,16 @@
           <t>FRI</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr"/>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (CHEM)</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr"/>
+      <c r="D18" s="7" t="inlineStr"/>
+      <c r="E18" s="7" t="inlineStr">
         <is>
           <t>Class 8 (CHEM)</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (PHY)</t>
-        </is>
-      </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (PHY)</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr"/>
@@ -1070,20 +1050,16 @@
           <t>SAT</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (PHY)</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="inlineStr"/>
-      <c r="D19" s="7" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr"/>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (PHY)</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr"/>
+      <c r="E19" s="7" t="inlineStr">
         <is>
           <t>Class 9 (CHEM)</t>
-        </is>
-      </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (PHY)</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr"/>
@@ -1162,7 +1138,11 @@
       <c r="B23" s="7" t="inlineStr"/>
       <c r="C23" s="7" t="inlineStr"/>
       <c r="D23" s="7" t="inlineStr"/>
-      <c r="E23" s="7" t="inlineStr"/>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (BIO)</t>
+        </is>
+      </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
           <t>Class 10 (BIO)</t>
@@ -1173,11 +1153,7 @@
           <t>Class 9 (BIO)</t>
         </is>
       </c>
-      <c r="H23" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (BIO)</t>
-        </is>
-      </c>
+      <c r="H23" s="7" t="inlineStr"/>
       <c r="I23" s="7" t="inlineStr"/>
     </row>
     <row r="24">
@@ -1194,12 +1170,12 @@
           <t>Class 8 (BIO)</t>
         </is>
       </c>
-      <c r="F24" s="7" t="inlineStr">
+      <c r="F24" s="7" t="inlineStr"/>
+      <c r="G24" s="7" t="inlineStr">
         <is>
           <t>Class 10 (BIO)</t>
         </is>
       </c>
-      <c r="G24" s="7" t="inlineStr"/>
       <c r="H24" s="7" t="inlineStr"/>
       <c r="I24" s="7" t="inlineStr"/>
     </row>
@@ -1212,14 +1188,14 @@
       <c r="B25" s="7" t="inlineStr"/>
       <c r="C25" s="7" t="inlineStr"/>
       <c r="D25" s="7" t="inlineStr"/>
-      <c r="E25" s="7" t="inlineStr"/>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (BIO)</t>
+        </is>
+      </c>
       <c r="F25" s="7" t="inlineStr"/>
       <c r="G25" s="7" t="inlineStr"/>
-      <c r="H25" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (BIO)</t>
-        </is>
-      </c>
+      <c r="H25" s="7" t="inlineStr"/>
       <c r="I25" s="7" t="inlineStr"/>
     </row>
     <row r="26">
@@ -1249,15 +1225,11 @@
       <c r="E27" s="7" t="inlineStr"/>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>Class 10 (BIO)</t>
+          <t>Class 9 (BIO)</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr"/>
-      <c r="H27" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (BIO)</t>
-        </is>
-      </c>
+      <c r="H27" s="7" t="inlineStr"/>
       <c r="I27" s="7" t="inlineStr"/>
     </row>
     <row r="28">
@@ -1351,27 +1323,27 @@
           <t>MON</t>
         </is>
       </c>
-      <c r="B32" s="7" t="inlineStr"/>
-      <c r="C32" s="7" t="inlineStr">
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (TEL)</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr"/>
+      <c r="D32" s="7" t="inlineStr"/>
+      <c r="E32" s="7" t="inlineStr"/>
+      <c r="F32" s="7" t="inlineStr">
         <is>
           <t>Class 7 (TEL)</t>
         </is>
       </c>
-      <c r="D32" s="7" t="inlineStr"/>
-      <c r="E32" s="7" t="inlineStr">
+      <c r="G32" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (TEL)</t>
+        </is>
+      </c>
+      <c r="H32" s="7" t="inlineStr">
         <is>
           <t>Class 8 (TEL)</t>
-        </is>
-      </c>
-      <c r="F32" s="7" t="inlineStr"/>
-      <c r="G32" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (TEL)</t>
-        </is>
-      </c>
-      <c r="H32" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (TEL)</t>
         </is>
       </c>
       <c r="I32" s="8" t="inlineStr">
@@ -1424,24 +1396,24 @@
       <c r="B34" s="7" t="inlineStr"/>
       <c r="C34" s="7" t="inlineStr">
         <is>
+          <t>Class 8 (TEL)</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr"/>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
           <t>Class 7 (TEL)</t>
         </is>
       </c>
-      <c r="D34" s="7" t="inlineStr"/>
-      <c r="E34" s="7" t="inlineStr"/>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (TEL)</t>
-        </is>
-      </c>
-      <c r="G34" s="7" t="inlineStr">
+          <t>Class 10 (TEL)</t>
+        </is>
+      </c>
+      <c r="G34" s="7" t="inlineStr"/>
+      <c r="H34" s="7" t="inlineStr">
         <is>
           <t>Class 9 (TEL)</t>
-        </is>
-      </c>
-      <c r="H34" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (TEL)</t>
         </is>
       </c>
       <c r="I34" s="8" t="inlineStr">
@@ -1457,23 +1429,23 @@
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr"/>
-      <c r="C35" s="7" t="inlineStr"/>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (TEL)</t>
+        </is>
+      </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (TEL)</t>
-        </is>
-      </c>
-      <c r="E35" s="7" t="inlineStr">
+          <t>Class 10 (TEL)</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr"/>
+      <c r="F35" s="7" t="inlineStr">
         <is>
           <t>Class 7 (TEL)</t>
         </is>
       </c>
-      <c r="F35" s="7" t="inlineStr"/>
-      <c r="G35" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (TEL)</t>
-        </is>
-      </c>
+      <c r="G35" s="7" t="inlineStr"/>
       <c r="H35" s="7" t="inlineStr">
         <is>
           <t>Class 9 (TEL)</t>
@@ -1494,26 +1466,26 @@
       <c r="B36" s="7" t="inlineStr"/>
       <c r="C36" s="7" t="inlineStr">
         <is>
+          <t>Class 8 (TEL)</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
           <t>Class 7 (TEL)</t>
-        </is>
-      </c>
-      <c r="D36" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (TEL)</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr"/>
       <c r="F36" s="7" t="inlineStr">
         <is>
+          <t>Class 10 (TEL)</t>
+        </is>
+      </c>
+      <c r="G36" s="7" t="inlineStr"/>
+      <c r="H36" s="7" t="inlineStr">
+        <is>
           <t>Class 9 (TEL)</t>
         </is>
       </c>
-      <c r="G36" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (TEL)</t>
-        </is>
-      </c>
-      <c r="H36" s="7" t="inlineStr"/>
       <c r="I36" s="8" t="inlineStr">
         <is>
           <t>Class 9</t>
@@ -1526,16 +1498,20 @@
           <t>SAT</t>
         </is>
       </c>
-      <c r="B37" s="7" t="inlineStr"/>
-      <c r="C37" s="7" t="inlineStr">
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (TEL)</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr"/>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (TEL)</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
         <is>
           <t>Class 8 (TEL)</t>
-        </is>
-      </c>
-      <c r="D37" s="7" t="inlineStr"/>
-      <c r="E37" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (TEL)</t>
         </is>
       </c>
       <c r="F37" s="7" t="inlineStr"/>
@@ -1544,11 +1520,7 @@
           <t>Class 10 (TEL)</t>
         </is>
       </c>
-      <c r="H37" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (TEL)</t>
-        </is>
-      </c>
+      <c r="H37" s="7" t="inlineStr"/>
       <c r="I37" s="8" t="inlineStr">
         <is>
           <t>Class 9</t>
@@ -1630,21 +1602,17 @@
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (HIN)</t>
+          <t>Class 4 (HIN)</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr"/>
-      <c r="E41" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (HIN)</t>
-        </is>
-      </c>
-      <c r="F41" s="7" t="inlineStr">
+      <c r="E41" s="7" t="inlineStr"/>
+      <c r="F41" s="7" t="inlineStr"/>
+      <c r="G41" s="7" t="inlineStr">
         <is>
           <t>Class 6 (HIN)</t>
         </is>
       </c>
-      <c r="G41" s="7" t="inlineStr"/>
       <c r="H41" s="7" t="inlineStr">
         <is>
           <t>Class 7 (HIN)</t>
@@ -1664,7 +1632,7 @@
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (G.K)</t>
+          <t>Class 8 (HIN)</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
@@ -1675,12 +1643,12 @@
       <c r="D42" s="7" t="inlineStr"/>
       <c r="E42" s="7" t="inlineStr">
         <is>
+          <t>Class 4 (HIN)</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
           <t>Class 6 (HIN)</t>
-        </is>
-      </c>
-      <c r="F42" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (HIN)</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
@@ -1707,23 +1675,23 @@
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr"/>
-      <c r="D43" s="7" t="inlineStr">
+      <c r="D43" s="7" t="inlineStr"/>
+      <c r="E43" s="7" t="inlineStr">
         <is>
           <t>Class 5 (HIN)</t>
         </is>
       </c>
-      <c r="E43" s="7" t="inlineStr">
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (HIN)</t>
+        </is>
+      </c>
+      <c r="G43" s="7" t="inlineStr">
         <is>
           <t>Class 6 (HIN)</t>
         </is>
       </c>
-      <c r="F43" s="7" t="inlineStr"/>
-      <c r="G43" s="7" t="inlineStr"/>
-      <c r="H43" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (HIN)</t>
-        </is>
-      </c>
+      <c r="H43" s="7" t="inlineStr"/>
       <c r="I43" s="8" t="inlineStr">
         <is>
           <t>Class 8</t>
@@ -1738,7 +1706,7 @@
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (HIN)</t>
+          <t>Class 8 (G.K)</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
@@ -1746,21 +1714,17 @@
           <t>Class 6 (HIN)</t>
         </is>
       </c>
-      <c r="D44" s="7" t="inlineStr"/>
-      <c r="E44" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (HIN)</t>
-        </is>
-      </c>
-      <c r="F44" s="7" t="inlineStr">
+      <c r="D44" s="7" t="inlineStr">
         <is>
           <t>Class 5 (HIN)</t>
         </is>
       </c>
+      <c r="E44" s="7" t="inlineStr"/>
+      <c r="F44" s="7" t="inlineStr"/>
       <c r="G44" s="7" t="inlineStr"/>
       <c r="H44" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (HIN)</t>
+          <t>Class 4 (HIN)</t>
         </is>
       </c>
       <c r="I44" s="8" t="inlineStr">
@@ -1780,22 +1744,26 @@
           <t>Class 8 (HIN)</t>
         </is>
       </c>
-      <c r="C45" s="7" t="inlineStr"/>
-      <c r="D45" s="7" t="inlineStr">
+      <c r="C45" s="7" t="inlineStr">
         <is>
           <t>Class 7 (HIN)</t>
         </is>
       </c>
+      <c r="D45" s="7" t="inlineStr"/>
       <c r="E45" s="7" t="inlineStr">
         <is>
           <t>Class 4 (HIN)</t>
         </is>
       </c>
-      <c r="F45" s="7" t="inlineStr"/>
+      <c r="F45" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (G.K)</t>
+        </is>
+      </c>
       <c r="G45" s="7" t="inlineStr"/>
       <c r="H45" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (HIN)</t>
+          <t>Class 5 (HIN)</t>
         </is>
       </c>
       <c r="I45" s="8" t="inlineStr">
@@ -1816,15 +1784,19 @@
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr"/>
-      <c r="D46" s="7" t="inlineStr"/>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (HIN)</t>
+        </is>
+      </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (HIN)</t>
+          <t>Class 4 (HIN)</t>
         </is>
       </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (G.K)</t>
+          <t>Class 6 (HIN)</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr"/>
@@ -1913,11 +1885,7 @@
           <t>Class 10 (MATH)</t>
         </is>
       </c>
-      <c r="D50" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (MATH)</t>
-        </is>
-      </c>
+      <c r="D50" s="7" t="inlineStr"/>
       <c r="E50" s="7" t="inlineStr"/>
       <c r="F50" s="7" t="inlineStr"/>
       <c r="G50" s="7" t="inlineStr"/>
@@ -1931,17 +1899,17 @@
         </is>
       </c>
       <c r="B51" s="7" t="inlineStr"/>
-      <c r="C51" s="7" t="inlineStr"/>
+      <c r="C51" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (MATH)</t>
+        </is>
+      </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>Class 10 (MATH)</t>
-        </is>
-      </c>
-      <c r="E51" s="7" t="inlineStr">
-        <is>
           <t>Class 9 (MATH)</t>
         </is>
       </c>
+      <c r="E51" s="7" t="inlineStr"/>
       <c r="F51" s="7" t="inlineStr"/>
       <c r="G51" s="7" t="inlineStr"/>
       <c r="H51" s="7" t="inlineStr"/>
@@ -1981,15 +1949,15 @@
         </is>
       </c>
       <c r="B53" s="7" t="inlineStr"/>
-      <c r="C53" s="7" t="inlineStr">
+      <c r="C53" s="7" t="inlineStr"/>
+      <c r="D53" s="7" t="inlineStr">
         <is>
           <t>Class 9 (MATH)</t>
         </is>
       </c>
-      <c r="D53" s="7" t="inlineStr"/>
       <c r="E53" s="7" t="inlineStr">
         <is>
-          <t>Class 10 (MATH)</t>
+          <t>Class 9 (MATH)</t>
         </is>
       </c>
       <c r="F53" s="7" t="inlineStr"/>
@@ -2006,15 +1974,19 @@
       <c r="B54" s="7" t="inlineStr"/>
       <c r="C54" s="7" t="inlineStr">
         <is>
+          <t>Class 9 (MATH)</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
           <t>Class 10 (MATH)</t>
         </is>
       </c>
-      <c r="D54" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (MATH)</t>
-        </is>
-      </c>
-      <c r="E54" s="7" t="inlineStr"/>
+      <c r="E54" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (MATH)</t>
+        </is>
+      </c>
       <c r="F54" s="7" t="inlineStr"/>
       <c r="G54" s="7" t="inlineStr"/>
       <c r="H54" s="7" t="inlineStr"/>
@@ -2032,10 +2004,14 @@
           <t>Class 10 (MATH)</t>
         </is>
       </c>
-      <c r="D55" s="7" t="inlineStr"/>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (MATH)</t>
+        </is>
+      </c>
       <c r="E55" s="7" t="inlineStr">
         <is>
-          <t>Class 9 (MATH)</t>
+          <t>Class 10 (MATH)</t>
         </is>
       </c>
       <c r="F55" s="7" t="inlineStr"/>
@@ -2114,23 +2090,23 @@
       <c r="B59" s="7" t="inlineStr"/>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (CHEM)</t>
+          <t>Class 5 (EVS)</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
+          <t>Class 7 (BIO)</t>
+        </is>
+      </c>
+      <c r="E59" s="7" t="inlineStr">
+        <is>
           <t>Class 3 (EVS)</t>
-        </is>
-      </c>
-      <c r="E59" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (BIO)</t>
         </is>
       </c>
       <c r="F59" s="7" t="inlineStr"/>
       <c r="G59" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (EVS)</t>
+          <t>Class 7 (CHEM)</t>
         </is>
       </c>
       <c r="H59" s="7" t="inlineStr">
@@ -2148,12 +2124,12 @@
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (EVS)</t>
+          <t>Class 6 (BIO)</t>
         </is>
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (BIO)</t>
+          <t>Class 6 (PHY)</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
@@ -2164,17 +2140,17 @@
       <c r="E60" s="7" t="inlineStr"/>
       <c r="F60" s="7" t="inlineStr">
         <is>
+          <t>Class 4 (EVS)</t>
+        </is>
+      </c>
+      <c r="G60" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (CHEM)</t>
+        </is>
+      </c>
+      <c r="H60" s="7" t="inlineStr">
+        <is>
           <t>Class 5 (EVS)</t>
-        </is>
-      </c>
-      <c r="G60" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (BIO)</t>
-        </is>
-      </c>
-      <c r="H60" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (CHEM)</t>
         </is>
       </c>
       <c r="I60" s="7" t="inlineStr"/>
@@ -2188,28 +2164,28 @@
       <c r="B61" s="7" t="inlineStr"/>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (EVS)</t>
+          <t>Class 7 (PHY)</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
+          <t>Class 5 (EVS)</t>
+        </is>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
           <t>Class 3 (EVS)</t>
-        </is>
-      </c>
-      <c r="E61" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (EVS)</t>
         </is>
       </c>
       <c r="F61" s="7" t="inlineStr"/>
       <c r="G61" s="7" t="inlineStr">
         <is>
+          <t>Class 4 (EVS)</t>
+        </is>
+      </c>
+      <c r="H61" s="7" t="inlineStr">
+        <is>
           <t>Class 7 (BIO)</t>
-        </is>
-      </c>
-      <c r="H61" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (PHY)</t>
         </is>
       </c>
       <c r="I61" s="7" t="inlineStr"/>
@@ -2222,29 +2198,29 @@
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
+          <t>Class 6 (BIO)</t>
+        </is>
+      </c>
+      <c r="C62" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (EVS)</t>
+        </is>
+      </c>
+      <c r="D62" s="7" t="inlineStr"/>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (EVS)</t>
+        </is>
+      </c>
+      <c r="F62" s="7" t="inlineStr">
+        <is>
           <t>Class 4 (EVS)</t>
-        </is>
-      </c>
-      <c r="C62" s="7" t="inlineStr"/>
-      <c r="D62" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (PHY)</t>
-        </is>
-      </c>
-      <c r="E62" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (EVS)</t>
-        </is>
-      </c>
-      <c r="F62" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (CHEM)</t>
         </is>
       </c>
       <c r="G62" s="7" t="inlineStr"/>
       <c r="H62" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (EVS)</t>
+          <t>Class 7 (BIO)</t>
         </is>
       </c>
       <c r="I62" s="7" t="inlineStr"/>
@@ -2255,35 +2231,31 @@
           <t>FRI</t>
         </is>
       </c>
-      <c r="B63" s="7" t="inlineStr">
+      <c r="B63" s="7" t="inlineStr"/>
+      <c r="C63" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (EVS)</t>
+        </is>
+      </c>
+      <c r="D63" s="7" t="inlineStr">
         <is>
           <t>Class 4 (EVS)</t>
         </is>
       </c>
-      <c r="C63" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (EVS)</t>
-        </is>
-      </c>
-      <c r="D63" s="7" t="inlineStr">
+      <c r="E63" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (PHY)</t>
+        </is>
+      </c>
+      <c r="F63" s="7" t="inlineStr"/>
+      <c r="G63" s="7" t="inlineStr">
         <is>
           <t>Class 3 (EVS)</t>
         </is>
       </c>
-      <c r="E63" s="7" t="inlineStr"/>
-      <c r="F63" s="7" t="inlineStr">
+      <c r="H63" s="7" t="inlineStr">
         <is>
           <t>Class 6 (CHEM)</t>
-        </is>
-      </c>
-      <c r="G63" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (BIO)</t>
-        </is>
-      </c>
-      <c r="H63" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (PHY)</t>
         </is>
       </c>
       <c r="I63" s="7" t="inlineStr"/>
@@ -2294,7 +2266,11 @@
           <t>SAT</t>
         </is>
       </c>
-      <c r="B64" s="7" t="inlineStr"/>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (EVS)</t>
+        </is>
+      </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
           <t>Class 5 (EVS)</t>
@@ -2302,23 +2278,23 @@
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (EVS)</t>
+          <t>Class 6 (BIO)</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr"/>
       <c r="F64" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (BIO)</t>
+          <t>Class 7 (CHEM)</t>
         </is>
       </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
-          <t>Class 3 (EVS)</t>
+          <t>Class 7 (PHY)</t>
         </is>
       </c>
       <c r="H64" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (PHY)</t>
+          <t>Class 4 (EVS)</t>
         </is>
       </c>
       <c r="I64" s="7" t="inlineStr"/>
@@ -2398,7 +2374,7 @@
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>Class 1 (ENG)</t>
+          <t>Class 2 (ENG)</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
@@ -2419,7 +2395,7 @@
       </c>
       <c r="H68" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (ENG)</t>
+          <t>Class 1 (ENG)</t>
         </is>
       </c>
       <c r="I68" s="8" t="inlineStr">
@@ -2446,23 +2422,23 @@
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (ENG)</t>
+          <t>Class 2 (GRAM)</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr"/>
       <c r="F69" s="7" t="inlineStr">
         <is>
+          <t>Class 2 (ENG)</t>
+        </is>
+      </c>
+      <c r="G69" s="7" t="inlineStr">
+        <is>
           <t>Class 3 (ENG)</t>
         </is>
       </c>
-      <c r="G69" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (ENG)</t>
-        </is>
-      </c>
       <c r="H69" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (GRAM)</t>
+          <t>Class 4 (ENG)</t>
         </is>
       </c>
       <c r="I69" s="8" t="inlineStr">
@@ -2489,23 +2465,23 @@
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (ENG)</t>
+          <t>Class 4 (ENG)</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr"/>
       <c r="F70" s="7" t="inlineStr">
         <is>
+          <t>Class 2 (ENG)</t>
+        </is>
+      </c>
+      <c r="G70" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (ENG)</t>
+        </is>
+      </c>
+      <c r="H70" s="7" t="inlineStr">
+        <is>
           <t>Class 1 (ENG)</t>
-        </is>
-      </c>
-      <c r="G70" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (ENG)</t>
-        </is>
-      </c>
-      <c r="H70" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (ENG)</t>
         </is>
       </c>
       <c r="I70" s="8" t="inlineStr">
@@ -2527,13 +2503,13 @@
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (ENG)</t>
+          <t>Class 1 (ENG)</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr"/>
       <c r="E71" s="7" t="inlineStr">
         <is>
-          <t>Class 1 (ENG)</t>
+          <t>Class 4 (ENG)</t>
         </is>
       </c>
       <c r="F71" s="7" t="inlineStr">
@@ -2561,23 +2537,23 @@
       </c>
       <c r="B72" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (GRAM)</t>
+          <t>Class 5 (ENG)</t>
         </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
+          <t>Class 3 (ENG)</t>
+        </is>
+      </c>
+      <c r="D72" s="7" t="inlineStr">
+        <is>
           <t>Class 1 (ENG)</t>
-        </is>
-      </c>
-      <c r="D72" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (ENG)</t>
         </is>
       </c>
       <c r="E72" s="7" t="inlineStr"/>
       <c r="F72" s="7" t="inlineStr">
         <is>
-          <t>Class 3 (ENG)</t>
+          <t>Class 4 (GRAM)</t>
         </is>
       </c>
       <c r="G72" s="7" t="inlineStr">
@@ -2587,7 +2563,7 @@
       </c>
       <c r="H72" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (ENG)</t>
+          <t>Class 2 (ENG)</t>
         </is>
       </c>
       <c r="I72" s="8" t="inlineStr">
@@ -2625,12 +2601,12 @@
       </c>
       <c r="G73" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (GRAM)</t>
+          <t>Class 1 (ENG)</t>
         </is>
       </c>
       <c r="H73" s="7" t="inlineStr">
         <is>
-          <t>Class 1 (ENG)</t>
+          <t>Class 5 (GRAM)</t>
         </is>
       </c>
       <c r="I73" s="8" t="inlineStr">
@@ -2709,10 +2685,14 @@
       </c>
       <c r="B77" s="7" t="inlineStr"/>
       <c r="C77" s="7" t="inlineStr"/>
-      <c r="D77" s="7" t="inlineStr"/>
+      <c r="D77" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (COMP)</t>
+        </is>
+      </c>
       <c r="E77" s="7" t="inlineStr">
         <is>
-          <t>Class 1 (COMP)</t>
+          <t>Class 2 (COMP)</t>
         </is>
       </c>
       <c r="F77" s="7" t="inlineStr"/>
@@ -2729,16 +2709,16 @@
       <c r="B78" s="7" t="inlineStr"/>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>Class 3 (COMP)</t>
+          <t>Class 4 (COMP)</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr"/>
-      <c r="E78" s="7" t="inlineStr"/>
-      <c r="F78" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (COMP)</t>
-        </is>
-      </c>
+      <c r="E78" s="7" t="inlineStr">
+        <is>
+          <t>Class 1 (COMP)</t>
+        </is>
+      </c>
+      <c r="F78" s="7" t="inlineStr"/>
       <c r="G78" s="7" t="inlineStr"/>
       <c r="H78" s="7" t="inlineStr"/>
       <c r="I78" s="7" t="inlineStr"/>
@@ -2752,10 +2732,14 @@
       <c r="B79" s="7" t="inlineStr"/>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>Class 1 (COMP)</t>
-        </is>
-      </c>
-      <c r="D79" s="7" t="inlineStr"/>
+          <t>Class 5 (COMP)</t>
+        </is>
+      </c>
+      <c r="D79" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (COMP)</t>
+        </is>
+      </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
           <t>Class 2 (COMP)</t>
@@ -2775,15 +2759,11 @@
       <c r="B80" s="7" t="inlineStr"/>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (COMP)</t>
+          <t>Class 2 (COMP)</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr"/>
-      <c r="E80" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (COMP)</t>
-        </is>
-      </c>
+      <c r="E80" s="7" t="inlineStr"/>
       <c r="F80" s="7" t="inlineStr"/>
       <c r="G80" s="7" t="inlineStr"/>
       <c r="H80" s="7" t="inlineStr"/>
@@ -2798,14 +2778,14 @@
       <c r="B81" s="7" t="inlineStr"/>
       <c r="C81" s="7" t="inlineStr"/>
       <c r="D81" s="7" t="inlineStr"/>
-      <c r="E81" s="7" t="inlineStr"/>
+      <c r="E81" s="7" t="inlineStr">
+        <is>
+          <t>Class 1 (COMP)</t>
+        </is>
+      </c>
       <c r="F81" s="7" t="inlineStr"/>
       <c r="G81" s="7" t="inlineStr"/>
-      <c r="H81" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (COMP)</t>
-        </is>
-      </c>
+      <c r="H81" s="7" t="inlineStr"/>
       <c r="I81" s="7" t="inlineStr"/>
     </row>
     <row r="82">
@@ -2815,11 +2795,7 @@
         </is>
       </c>
       <c r="B82" s="7" t="inlineStr"/>
-      <c r="C82" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (COMP)</t>
-        </is>
-      </c>
+      <c r="C82" s="7" t="inlineStr"/>
       <c r="D82" s="7" t="inlineStr"/>
       <c r="E82" s="7" t="inlineStr">
         <is>
@@ -2907,20 +2883,20 @@
       <c r="C86" s="7" t="inlineStr"/>
       <c r="D86" s="7" t="inlineStr">
         <is>
+          <t>L.K.G (TEL)</t>
+        </is>
+      </c>
+      <c r="E86" s="7" t="inlineStr">
+        <is>
           <t>U.K.G (TEL)</t>
         </is>
       </c>
-      <c r="E86" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (TEL)</t>
-        </is>
-      </c>
-      <c r="F86" s="7" t="inlineStr">
+      <c r="F86" s="7" t="inlineStr"/>
+      <c r="G86" s="7" t="inlineStr">
         <is>
           <t>Class 2 (TEL)</t>
         </is>
       </c>
-      <c r="G86" s="7" t="inlineStr"/>
       <c r="H86" s="7" t="inlineStr"/>
       <c r="I86" s="8" t="inlineStr">
         <is>
@@ -2940,19 +2916,19 @@
         </is>
       </c>
       <c r="C87" s="7" t="inlineStr"/>
-      <c r="D87" s="7" t="inlineStr">
+      <c r="D87" s="7" t="inlineStr"/>
+      <c r="E87" s="7" t="inlineStr">
         <is>
           <t>U.K.G (TEL)</t>
-        </is>
-      </c>
-      <c r="E87" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (TEL)</t>
         </is>
       </c>
       <c r="F87" s="7" t="inlineStr"/>
       <c r="G87" s="7" t="inlineStr"/>
-      <c r="H87" s="7" t="inlineStr"/>
+      <c r="H87" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (TEL)</t>
+        </is>
+      </c>
       <c r="I87" s="8" t="inlineStr">
         <is>
           <t>Class 1</t>
@@ -2970,24 +2946,28 @@
           <t>Class 1 (TEL)</t>
         </is>
       </c>
-      <c r="C88" s="7" t="inlineStr"/>
+      <c r="C88" s="7" t="inlineStr">
+        <is>
+          <t>Class 1 (G.K)</t>
+        </is>
+      </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
+          <t>L.K.G (TEL)</t>
+        </is>
+      </c>
+      <c r="E88" s="7" t="inlineStr"/>
+      <c r="F88" s="7" t="inlineStr"/>
+      <c r="G88" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (TEL)</t>
+        </is>
+      </c>
+      <c r="H88" s="7" t="inlineStr">
+        <is>
           <t>U.K.G (TEL)</t>
         </is>
       </c>
-      <c r="E88" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (TEL)</t>
-        </is>
-      </c>
-      <c r="F88" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (TEL)</t>
-        </is>
-      </c>
-      <c r="G88" s="7" t="inlineStr"/>
-      <c r="H88" s="7" t="inlineStr"/>
       <c r="I88" s="8" t="inlineStr">
         <is>
           <t>Class 1</t>
@@ -3002,15 +2982,15 @@
       </c>
       <c r="B89" s="7" t="inlineStr">
         <is>
-          <t>Class 1 (G.K)</t>
-        </is>
-      </c>
-      <c r="C89" s="7" t="inlineStr"/>
-      <c r="D89" s="7" t="inlineStr">
+          <t>Class 1 (TEL)</t>
+        </is>
+      </c>
+      <c r="C89" s="7" t="inlineStr">
         <is>
           <t>U.K.G (TEL)</t>
         </is>
       </c>
+      <c r="D89" s="7" t="inlineStr"/>
       <c r="E89" s="7" t="inlineStr">
         <is>
           <t>L.K.G (TEL)</t>
@@ -3022,11 +3002,7 @@
         </is>
       </c>
       <c r="G89" s="7" t="inlineStr"/>
-      <c r="H89" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (TEL)</t>
-        </is>
-      </c>
+      <c r="H89" s="7" t="inlineStr"/>
       <c r="I89" s="8" t="inlineStr">
         <is>
           <t>Class 1</t>
@@ -3041,31 +3017,27 @@
       </c>
       <c r="B90" s="7" t="inlineStr">
         <is>
-          <t>Class 1 (G.K)</t>
-        </is>
-      </c>
-      <c r="C90" s="7" t="inlineStr">
+          <t>Class 1 (TEL)</t>
+        </is>
+      </c>
+      <c r="C90" s="7" t="inlineStr"/>
+      <c r="D90" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (TEL)</t>
+        </is>
+      </c>
+      <c r="E90" s="7" t="inlineStr">
         <is>
           <t>L.K.G (TEL)</t>
         </is>
       </c>
-      <c r="D90" s="7" t="inlineStr"/>
-      <c r="E90" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (TEL)</t>
-        </is>
-      </c>
       <c r="F90" s="7" t="inlineStr">
         <is>
-          <t>Class 1 (TEL)</t>
+          <t>U.K.G (TEL)</t>
         </is>
       </c>
       <c r="G90" s="7" t="inlineStr"/>
-      <c r="H90" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (TEL)</t>
-        </is>
-      </c>
+      <c r="H90" s="7" t="inlineStr"/>
       <c r="I90" s="8" t="inlineStr">
         <is>
           <t>Class 1</t>
@@ -3080,27 +3052,31 @@
       </c>
       <c r="B91" s="7" t="inlineStr">
         <is>
+          <t>Class 1 (G.K)</t>
+        </is>
+      </c>
+      <c r="C91" s="7" t="inlineStr">
+        <is>
           <t>Class 1 (TEL)</t>
         </is>
       </c>
-      <c r="C91" s="7" t="inlineStr"/>
-      <c r="D91" s="7" t="inlineStr">
+      <c r="D91" s="7" t="inlineStr"/>
+      <c r="E91" s="7" t="inlineStr">
         <is>
           <t>L.K.G (TEL)</t>
         </is>
       </c>
-      <c r="E91" s="7" t="inlineStr">
+      <c r="F91" s="7" t="inlineStr">
         <is>
           <t>Class 2 (TEL)</t>
         </is>
       </c>
-      <c r="F91" s="7" t="inlineStr"/>
-      <c r="G91" s="7" t="inlineStr">
+      <c r="G91" s="7" t="inlineStr"/>
+      <c r="H91" s="7" t="inlineStr">
         <is>
           <t>U.K.G (TEL)</t>
         </is>
       </c>
-      <c r="H91" s="7" t="inlineStr"/>
       <c r="I91" s="8" t="inlineStr">
         <is>
           <t>Class 1</t>
@@ -3182,26 +3158,26 @@
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
+          <t>Class 6 (SOC)</t>
+        </is>
+      </c>
+      <c r="D95" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (SOC)</t>
+        </is>
+      </c>
+      <c r="E95" s="7" t="inlineStr"/>
+      <c r="F95" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (SOC)</t>
+        </is>
+      </c>
+      <c r="G95" s="7" t="inlineStr"/>
+      <c r="H95" s="7" t="inlineStr">
+        <is>
           <t>Class 3 (SOC)</t>
         </is>
       </c>
-      <c r="D95" s="7" t="inlineStr"/>
-      <c r="E95" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (SOC)</t>
-        </is>
-      </c>
-      <c r="F95" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (SOC)</t>
-        </is>
-      </c>
-      <c r="G95" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (SOC)</t>
-        </is>
-      </c>
-      <c r="H95" s="7" t="inlineStr"/>
       <c r="I95" s="8" t="inlineStr">
         <is>
           <t>Class 7</t>
@@ -3222,23 +3198,23 @@
       <c r="C96" s="7" t="inlineStr"/>
       <c r="D96" s="7" t="inlineStr">
         <is>
+          <t>Class 4 (SOC)</t>
+        </is>
+      </c>
+      <c r="E96" s="7" t="inlineStr">
+        <is>
           <t>Class 5 (SOC)</t>
         </is>
       </c>
-      <c r="E96" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (SOC)</t>
-        </is>
-      </c>
       <c r="F96" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (SOC)</t>
+          <t>Class 3 (SOC)</t>
         </is>
       </c>
       <c r="G96" s="7" t="inlineStr"/>
       <c r="H96" s="7" t="inlineStr">
         <is>
-          <t>Class 3 (SOC)</t>
+          <t>Class 6 (SOC)</t>
         </is>
       </c>
       <c r="I96" s="8" t="inlineStr">
@@ -3258,20 +3234,20 @@
           <t>Class 7 (SOC)</t>
         </is>
       </c>
-      <c r="C97" s="7" t="inlineStr">
+      <c r="C97" s="7" t="inlineStr"/>
+      <c r="D97" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (SOC)</t>
+        </is>
+      </c>
+      <c r="E97" s="7" t="inlineStr">
         <is>
           <t>Class 6 (SOC)</t>
         </is>
       </c>
-      <c r="D97" s="7" t="inlineStr"/>
-      <c r="E97" s="7" t="inlineStr">
+      <c r="F97" s="7" t="inlineStr">
         <is>
           <t>Class 4 (SOC)</t>
-        </is>
-      </c>
-      <c r="F97" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (SOC)</t>
         </is>
       </c>
       <c r="G97" s="7" t="inlineStr"/>
@@ -3297,20 +3273,20 @@
           <t>Class 7 (SOC)</t>
         </is>
       </c>
-      <c r="C98" s="7" t="inlineStr">
+      <c r="C98" s="7" t="inlineStr"/>
+      <c r="D98" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (SOC)</t>
+        </is>
+      </c>
+      <c r="E98" s="7" t="inlineStr">
         <is>
           <t>Class 3 (SOC)</t>
         </is>
       </c>
-      <c r="D98" s="7" t="inlineStr"/>
-      <c r="E98" s="7" t="inlineStr">
+      <c r="F98" s="7" t="inlineStr">
         <is>
           <t>Class 5 (SOC)</t>
-        </is>
-      </c>
-      <c r="F98" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (SOC)</t>
         </is>
       </c>
       <c r="G98" s="7" t="inlineStr"/>
@@ -3336,28 +3312,28 @@
           <t>Class 7 (SOC)</t>
         </is>
       </c>
-      <c r="C99" s="7" t="inlineStr">
+      <c r="C99" s="7" t="inlineStr"/>
+      <c r="D99" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (SOC)</t>
+        </is>
+      </c>
+      <c r="E99" s="7" t="inlineStr"/>
+      <c r="F99" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (SOC)</t>
+        </is>
+      </c>
+      <c r="G99" s="7" t="inlineStr">
         <is>
           <t>Class 6 (SOC)</t>
         </is>
       </c>
-      <c r="D99" s="7" t="inlineStr"/>
-      <c r="E99" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (SOC)</t>
-        </is>
-      </c>
-      <c r="F99" s="7" t="inlineStr">
+      <c r="H99" s="7" t="inlineStr">
         <is>
           <t>Class 4 (SOC)</t>
         </is>
       </c>
-      <c r="G99" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (SOC)</t>
-        </is>
-      </c>
-      <c r="H99" s="7" t="inlineStr"/>
       <c r="I99" s="8" t="inlineStr">
         <is>
           <t>Class 7</t>
@@ -3375,23 +3351,23 @@
           <t>Class 7 (SOC)</t>
         </is>
       </c>
-      <c r="C100" s="7" t="inlineStr">
+      <c r="C100" s="7" t="inlineStr"/>
+      <c r="D100" s="7" t="inlineStr">
         <is>
           <t>Class 4 (SOC)</t>
         </is>
       </c>
-      <c r="D100" s="7" t="inlineStr">
+      <c r="E100" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (SOC)</t>
+        </is>
+      </c>
+      <c r="F100" s="7" t="inlineStr"/>
+      <c r="G100" s="7" t="inlineStr">
         <is>
           <t>Class 6 (SOC)</t>
         </is>
       </c>
-      <c r="E100" s="7" t="inlineStr"/>
-      <c r="F100" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (SOC)</t>
-        </is>
-      </c>
-      <c r="G100" s="7" t="inlineStr"/>
       <c r="H100" s="7" t="inlineStr">
         <is>
           <t>Class 3 (SOC)</t>
@@ -3472,24 +3448,24 @@
         </is>
       </c>
       <c r="B104" s="7" t="inlineStr"/>
-      <c r="C104" s="7" t="inlineStr"/>
-      <c r="D104" s="7" t="inlineStr">
+      <c r="C104" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (ENG)</t>
+        </is>
+      </c>
+      <c r="D104" s="7" t="inlineStr"/>
+      <c r="E104" s="7" t="inlineStr">
         <is>
           <t>Class 6 (ENG)</t>
         </is>
       </c>
-      <c r="E104" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (GRAM)</t>
-        </is>
-      </c>
-      <c r="F104" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (ENG)</t>
-        </is>
-      </c>
+      <c r="F104" s="7" t="inlineStr"/>
       <c r="G104" s="7" t="inlineStr"/>
-      <c r="H104" s="7" t="inlineStr"/>
+      <c r="H104" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (GRAM)</t>
+        </is>
+      </c>
       <c r="I104" s="7" t="inlineStr"/>
     </row>
     <row r="105">
@@ -3499,28 +3475,24 @@
         </is>
       </c>
       <c r="B105" s="7" t="inlineStr"/>
-      <c r="C105" s="7" t="inlineStr">
+      <c r="C105" s="7" t="inlineStr"/>
+      <c r="D105" s="7" t="inlineStr">
         <is>
           <t>Class 6 (ENG)</t>
-        </is>
-      </c>
-      <c r="D105" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (ENG)</t>
         </is>
       </c>
       <c r="E105" s="7" t="inlineStr"/>
       <c r="F105" s="7" t="inlineStr">
         <is>
+          <t>Class 7 (ENG)</t>
+        </is>
+      </c>
+      <c r="G105" s="7" t="inlineStr"/>
+      <c r="H105" s="7" t="inlineStr">
+        <is>
           <t>Class 9 (GRAM)</t>
         </is>
       </c>
-      <c r="G105" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (GRAM)</t>
-        </is>
-      </c>
-      <c r="H105" s="7" t="inlineStr"/>
       <c r="I105" s="7" t="inlineStr"/>
     </row>
     <row r="106">
@@ -3533,20 +3505,16 @@
       <c r="C106" s="7" t="inlineStr"/>
       <c r="D106" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (GRAM)</t>
-        </is>
-      </c>
-      <c r="E106" s="7" t="inlineStr">
-        <is>
           <t>Class 7 (ENG)</t>
         </is>
       </c>
-      <c r="F106" s="7" t="inlineStr"/>
-      <c r="G106" s="7" t="inlineStr">
+      <c r="E106" s="7" t="inlineStr"/>
+      <c r="F106" s="7" t="inlineStr">
         <is>
           <t>Class 6 (ENG)</t>
         </is>
       </c>
+      <c r="G106" s="7" t="inlineStr"/>
       <c r="H106" s="7" t="inlineStr"/>
       <c r="I106" s="7" t="inlineStr"/>
     </row>
@@ -3564,15 +3532,15 @@
       </c>
       <c r="D107" s="7" t="inlineStr">
         <is>
+          <t>Class 6 (GRAM)</t>
+        </is>
+      </c>
+      <c r="E107" s="7" t="inlineStr">
+        <is>
           <t>Class 6 (ENG)</t>
         </is>
       </c>
-      <c r="E107" s="7" t="inlineStr"/>
-      <c r="F107" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (GRAM)</t>
-        </is>
-      </c>
+      <c r="F107" s="7" t="inlineStr"/>
       <c r="G107" s="7" t="inlineStr"/>
       <c r="H107" s="7" t="inlineStr"/>
       <c r="I107" s="7" t="inlineStr"/>
@@ -3584,19 +3552,23 @@
         </is>
       </c>
       <c r="B108" s="7" t="inlineStr"/>
-      <c r="C108" s="7" t="inlineStr"/>
-      <c r="D108" s="7" t="inlineStr">
+      <c r="C108" s="7" t="inlineStr">
         <is>
           <t>Class 6 (ENG)</t>
         </is>
       </c>
+      <c r="D108" s="7" t="inlineStr"/>
       <c r="E108" s="7" t="inlineStr">
         <is>
+          <t>Class 7 (GRAM)</t>
+        </is>
+      </c>
+      <c r="F108" s="7" t="inlineStr"/>
+      <c r="G108" s="7" t="inlineStr">
+        <is>
           <t>Class 7 (ENG)</t>
         </is>
       </c>
-      <c r="F108" s="7" t="inlineStr"/>
-      <c r="G108" s="7" t="inlineStr"/>
       <c r="H108" s="7" t="inlineStr"/>
       <c r="I108" s="7" t="inlineStr"/>
     </row>
@@ -3607,18 +3579,22 @@
         </is>
       </c>
       <c r="B109" s="7" t="inlineStr"/>
-      <c r="C109" s="7" t="inlineStr"/>
-      <c r="D109" s="7" t="inlineStr">
+      <c r="C109" s="7" t="inlineStr">
         <is>
           <t>Class 7 (ENG)</t>
         </is>
       </c>
+      <c r="D109" s="7" t="inlineStr"/>
       <c r="E109" s="7" t="inlineStr">
         <is>
           <t>Class 6 (ENG)</t>
         </is>
       </c>
-      <c r="F109" s="7" t="inlineStr"/>
+      <c r="F109" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (GRAM)</t>
+        </is>
+      </c>
       <c r="G109" s="7" t="inlineStr"/>
       <c r="H109" s="7" t="inlineStr"/>
       <c r="I109" s="7" t="inlineStr"/>
@@ -3692,7 +3668,11 @@
         </is>
       </c>
       <c r="B113" s="7" t="inlineStr"/>
-      <c r="C113" s="7" t="inlineStr"/>
+      <c r="C113" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (HIN)</t>
+        </is>
+      </c>
       <c r="D113" s="7" t="inlineStr">
         <is>
           <t>Class 10 (HIN)</t>
@@ -3700,7 +3680,7 @@
       </c>
       <c r="E113" s="7" t="inlineStr">
         <is>
-          <t>Class 3 (HIN)</t>
+          <t>Class 9 (HIN)</t>
         </is>
       </c>
       <c r="F113" s="7" t="inlineStr"/>
@@ -3714,12 +3694,12 @@
           <t>TUE</t>
         </is>
       </c>
-      <c r="B114" s="7" t="inlineStr"/>
-      <c r="C114" s="7" t="inlineStr">
+      <c r="B114" s="7" t="inlineStr">
         <is>
           <t>Class 9 (HIN)</t>
         </is>
       </c>
+      <c r="C114" s="7" t="inlineStr"/>
       <c r="D114" s="7" t="inlineStr"/>
       <c r="E114" s="7" t="inlineStr">
         <is>
@@ -3738,17 +3718,17 @@
         </is>
       </c>
       <c r="B115" s="7" t="inlineStr"/>
-      <c r="C115" s="7" t="inlineStr"/>
+      <c r="C115" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (HIN)</t>
+        </is>
+      </c>
       <c r="D115" s="7" t="inlineStr">
         <is>
           <t>Class 9 (HIN)</t>
         </is>
       </c>
-      <c r="E115" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (HIN)</t>
-        </is>
-      </c>
+      <c r="E115" s="7" t="inlineStr"/>
       <c r="F115" s="7" t="inlineStr"/>
       <c r="G115" s="7" t="inlineStr"/>
       <c r="H115" s="7" t="inlineStr"/>
@@ -3763,20 +3743,20 @@
       <c r="B116" s="7" t="inlineStr"/>
       <c r="C116" s="7" t="inlineStr">
         <is>
+          <t>Class 9 (HIN)</t>
+        </is>
+      </c>
+      <c r="D116" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (HIN)</t>
+        </is>
+      </c>
+      <c r="E116" s="7" t="inlineStr">
+        <is>
           <t>Class 10 (HIN)</t>
         </is>
       </c>
-      <c r="D116" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (HIN)</t>
-        </is>
-      </c>
-      <c r="E116" s="7" t="inlineStr"/>
-      <c r="F116" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (HIN)</t>
-        </is>
-      </c>
+      <c r="F116" s="7" t="inlineStr"/>
       <c r="G116" s="7" t="inlineStr"/>
       <c r="H116" s="7" t="inlineStr"/>
       <c r="I116" s="7" t="inlineStr"/>
@@ -3789,18 +3769,18 @@
       </c>
       <c r="B117" s="7" t="inlineStr">
         <is>
+          <t>Class 10 (HIN)</t>
+        </is>
+      </c>
+      <c r="C117" s="7" t="inlineStr"/>
+      <c r="D117" s="7" t="inlineStr">
+        <is>
           <t>Class 9 (HIN)</t>
         </is>
       </c>
-      <c r="C117" s="7" t="inlineStr">
+      <c r="E117" s="7" t="inlineStr">
         <is>
           <t>Class 3 (HIN)</t>
-        </is>
-      </c>
-      <c r="D117" s="7" t="inlineStr"/>
-      <c r="E117" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (HIN)</t>
         </is>
       </c>
       <c r="F117" s="7" t="inlineStr"/>
@@ -3815,11 +3795,7 @@
         </is>
       </c>
       <c r="B118" s="7" t="inlineStr"/>
-      <c r="C118" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (HIN)</t>
-        </is>
-      </c>
+      <c r="C118" s="7" t="inlineStr"/>
       <c r="D118" s="7" t="inlineStr">
         <is>
           <t>Class 10 (HIN)</t>
@@ -3905,12 +3881,12 @@
       </c>
       <c r="B122" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (EVS)</t>
+          <t>Class 2 (HIN)</t>
         </is>
       </c>
       <c r="C122" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (EVS)</t>
+          <t>Class 1 (EVS)</t>
         </is>
       </c>
       <c r="D122" s="7" t="inlineStr">
@@ -3921,17 +3897,17 @@
       <c r="E122" s="7" t="inlineStr"/>
       <c r="F122" s="7" t="inlineStr">
         <is>
+          <t>Class 2 (EVS)</t>
+        </is>
+      </c>
+      <c r="G122" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (G.K)</t>
+        </is>
+      </c>
+      <c r="H122" s="7" t="inlineStr">
+        <is>
           <t>U.K.G (ENG)</t>
-        </is>
-      </c>
-      <c r="G122" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (ENG)</t>
-        </is>
-      </c>
-      <c r="H122" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (EVS)</t>
         </is>
       </c>
       <c r="I122" s="8" t="inlineStr">
@@ -3953,28 +3929,28 @@
       </c>
       <c r="C123" s="7" t="inlineStr">
         <is>
-          <t>U.K.G (ENG)</t>
+          <t>Class 2 (EVS)</t>
         </is>
       </c>
       <c r="D123" s="7" t="inlineStr">
         <is>
-          <t>Class 1 (EVS)</t>
+          <t>Class 1 (HIN)</t>
         </is>
       </c>
       <c r="E123" s="7" t="inlineStr"/>
       <c r="F123" s="7" t="inlineStr">
         <is>
-          <t>Class 1 (HIN)</t>
+          <t>U.K.G (ENG)</t>
         </is>
       </c>
       <c r="G123" s="7" t="inlineStr">
         <is>
-          <t>Class 3 (G.K)</t>
+          <t>U.K.G (ENG)</t>
         </is>
       </c>
       <c r="H123" s="7" t="inlineStr">
         <is>
-          <t>Class 1 (EVS)</t>
+          <t>U.K.G (ENG)</t>
         </is>
       </c>
       <c r="I123" s="8" t="inlineStr">
@@ -3994,23 +3970,27 @@
           <t>Class 2 (HIN)</t>
         </is>
       </c>
-      <c r="C124" s="7" t="inlineStr"/>
+      <c r="C124" s="7" t="inlineStr">
+        <is>
+          <t>U.K.G (ENG)</t>
+        </is>
+      </c>
       <c r="D124" s="7" t="inlineStr">
         <is>
+          <t>U.K.G (ENG)</t>
+        </is>
+      </c>
+      <c r="E124" s="7" t="inlineStr"/>
+      <c r="F124" s="7" t="inlineStr">
+        <is>
           <t>Class 1 (EVS)</t>
         </is>
       </c>
-      <c r="E124" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (EVS)</t>
-        </is>
-      </c>
-      <c r="F124" s="7" t="inlineStr">
+      <c r="G124" s="7" t="inlineStr">
         <is>
           <t>U.K.G (ENG)</t>
         </is>
       </c>
-      <c r="G124" s="7" t="inlineStr"/>
       <c r="H124" s="7" t="inlineStr">
         <is>
           <t>Class 2 (EVS)</t>
@@ -4033,30 +4013,26 @@
           <t>Class 2 (EVS)</t>
         </is>
       </c>
-      <c r="C125" s="7" t="inlineStr">
+      <c r="C125" s="7" t="inlineStr"/>
+      <c r="D125" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (EVS)</t>
+        </is>
+      </c>
+      <c r="E125" s="7" t="inlineStr">
+        <is>
+          <t>Class 1 (EVS)</t>
+        </is>
+      </c>
+      <c r="F125" s="7" t="inlineStr"/>
+      <c r="G125" s="7" t="inlineStr">
+        <is>
+          <t>U.K.G (ENG)</t>
+        </is>
+      </c>
+      <c r="H125" s="7" t="inlineStr">
         <is>
           <t>Class 1 (HIN)</t>
-        </is>
-      </c>
-      <c r="D125" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (HIN)</t>
-        </is>
-      </c>
-      <c r="E125" s="7" t="inlineStr"/>
-      <c r="F125" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (ENG)</t>
-        </is>
-      </c>
-      <c r="G125" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (ENG)</t>
-        </is>
-      </c>
-      <c r="H125" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (ENG)</t>
         </is>
       </c>
       <c r="I125" s="8" t="inlineStr">
@@ -4073,12 +4049,12 @@
       </c>
       <c r="B126" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (EVS)</t>
+          <t>Class 2 (HIN)</t>
         </is>
       </c>
       <c r="C126" s="7" t="inlineStr">
         <is>
-          <t>U.K.G (ENG)</t>
+          <t>Class 1 (HIN)</t>
         </is>
       </c>
       <c r="D126" s="7" t="inlineStr">
@@ -4089,12 +4065,12 @@
       <c r="E126" s="7" t="inlineStr"/>
       <c r="F126" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (HIN)</t>
+          <t>Class 1 (EVS)</t>
         </is>
       </c>
       <c r="G126" s="7" t="inlineStr">
         <is>
-          <t>Class 1 (HIN)</t>
+          <t>Class 2 (EVS)</t>
         </is>
       </c>
       <c r="H126" s="7" t="inlineStr">
@@ -4116,33 +4092,33 @@
       </c>
       <c r="B127" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (EVS)</t>
+          <t>Class 2 (HIN)</t>
         </is>
       </c>
       <c r="C127" s="7" t="inlineStr">
         <is>
+          <t>U.K.G (ENG)</t>
+        </is>
+      </c>
+      <c r="D127" s="7" t="inlineStr">
+        <is>
           <t>Class 1 (EVS)</t>
-        </is>
-      </c>
-      <c r="D127" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (ENG)</t>
         </is>
       </c>
       <c r="E127" s="7" t="inlineStr"/>
       <c r="F127" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (HIN)</t>
+          <t>Class 1 (HIN)</t>
         </is>
       </c>
       <c r="G127" s="7" t="inlineStr">
         <is>
-          <t>Class 1 (HIN)</t>
+          <t>Class 2 (EVS)</t>
         </is>
       </c>
       <c r="H127" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (EVS)</t>
+          <t>Class 1 (EVS)</t>
         </is>
       </c>
       <c r="I127" s="8" t="inlineStr">
@@ -4224,27 +4200,23 @@
           <t>Class 6 (MATH)</t>
         </is>
       </c>
-      <c r="C131" s="7" t="inlineStr">
+      <c r="C131" s="7" t="inlineStr"/>
+      <c r="D131" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (MATH)</t>
+        </is>
+      </c>
+      <c r="E131" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (COMP)</t>
+        </is>
+      </c>
+      <c r="F131" s="7" t="inlineStr">
         <is>
           <t>Class 8 (MATH)</t>
         </is>
       </c>
-      <c r="D131" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (MATH)</t>
-        </is>
-      </c>
-      <c r="E131" s="7" t="inlineStr"/>
-      <c r="F131" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (MATH)</t>
-        </is>
-      </c>
-      <c r="G131" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (MATH)</t>
-        </is>
-      </c>
+      <c r="G131" s="7" t="inlineStr"/>
       <c r="H131" s="7" t="inlineStr"/>
       <c r="I131" s="8" t="inlineStr">
         <is>
@@ -4258,27 +4230,31 @@
           <t>TUE</t>
         </is>
       </c>
-      <c r="B132" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (MATH)</t>
-        </is>
-      </c>
-      <c r="C132" s="7" t="inlineStr"/>
+      <c r="B132" s="7" t="inlineStr"/>
+      <c r="C132" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (MATH)</t>
+        </is>
+      </c>
       <c r="D132" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (MATH)</t>
+          <t>Class 7 (MATH)</t>
         </is>
       </c>
       <c r="E132" s="7" t="inlineStr"/>
       <c r="F132" s="7" t="inlineStr">
         <is>
+          <t>Class 8 (MATH)</t>
+        </is>
+      </c>
+      <c r="G132" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (MATH)</t>
+        </is>
+      </c>
+      <c r="H132" s="7" t="inlineStr">
+        <is>
           <t>Class 7 (MATH)</t>
-        </is>
-      </c>
-      <c r="G132" s="7" t="inlineStr"/>
-      <c r="H132" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (COMP)</t>
         </is>
       </c>
       <c r="I132" s="8" t="inlineStr">
@@ -4298,24 +4274,28 @@
           <t>Class 6 (MATH)</t>
         </is>
       </c>
-      <c r="C133" s="7" t="inlineStr"/>
-      <c r="D133" s="7" t="inlineStr">
+      <c r="C133" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (MATH)</t>
+        </is>
+      </c>
+      <c r="D133" s="7" t="inlineStr"/>
+      <c r="E133" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (G.K)</t>
+        </is>
+      </c>
+      <c r="F133" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (COMP)</t>
+        </is>
+      </c>
+      <c r="G133" s="7" t="inlineStr">
         <is>
           <t>Class 7 (MATH)</t>
         </is>
       </c>
-      <c r="E133" s="7" t="inlineStr"/>
-      <c r="F133" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (MATH)</t>
-        </is>
-      </c>
-      <c r="G133" s="7" t="inlineStr"/>
-      <c r="H133" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (MATH)</t>
-        </is>
-      </c>
+      <c r="H133" s="7" t="inlineStr"/>
       <c r="I133" s="8" t="inlineStr">
         <is>
           <t>Class 6</t>
@@ -4328,25 +4308,25 @@
           <t>THU</t>
         </is>
       </c>
-      <c r="B134" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (G.K)</t>
-        </is>
-      </c>
-      <c r="C134" s="7" t="inlineStr">
+      <c r="B134" s="7" t="inlineStr"/>
+      <c r="C134" s="7" t="inlineStr"/>
+      <c r="D134" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (MATH)</t>
+        </is>
+      </c>
+      <c r="E134" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (MATH)</t>
+        </is>
+      </c>
+      <c r="F134" s="7" t="inlineStr">
         <is>
           <t>Class 8 (MATH)</t>
         </is>
       </c>
-      <c r="D134" s="7" t="inlineStr"/>
-      <c r="E134" s="7" t="inlineStr"/>
-      <c r="F134" s="7" t="inlineStr"/>
       <c r="G134" s="7" t="inlineStr"/>
-      <c r="H134" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (MATH)</t>
-        </is>
-      </c>
+      <c r="H134" s="7" t="inlineStr"/>
       <c r="I134" s="8" t="inlineStr">
         <is>
           <t>Class 6</t>
@@ -4361,18 +4341,18 @@
       </c>
       <c r="B135" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (MATH)</t>
+          <t>Class 6 (G.K)</t>
         </is>
       </c>
       <c r="C135" s="7" t="inlineStr"/>
       <c r="D135" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (G.K)</t>
+          <t>Class 6 (MATH)</t>
         </is>
       </c>
       <c r="E135" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (MATH)</t>
+          <t>Class 5 (G.K)</t>
         </is>
       </c>
       <c r="F135" s="7" t="inlineStr"/>
@@ -4405,26 +4385,22 @@
       </c>
       <c r="C136" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (COMP)</t>
-        </is>
-      </c>
-      <c r="D136" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (G.K)</t>
-        </is>
-      </c>
-      <c r="E136" s="7" t="inlineStr"/>
-      <c r="F136" s="7" t="inlineStr">
+          <t>Class 6 (MATH)</t>
+        </is>
+      </c>
+      <c r="D136" s="7" t="inlineStr"/>
+      <c r="E136" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (MATH)</t>
+        </is>
+      </c>
+      <c r="F136" s="7" t="inlineStr"/>
+      <c r="G136" s="7" t="inlineStr"/>
+      <c r="H136" s="7" t="inlineStr">
         <is>
           <t>Class 8 (MATH)</t>
         </is>
       </c>
-      <c r="G136" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (MATH)</t>
-        </is>
-      </c>
-      <c r="H136" s="7" t="inlineStr"/>
       <c r="I136" s="8" t="inlineStr">
         <is>
           <t>Class 6</t>
@@ -4509,25 +4485,21 @@
           <t>L.K.G (EVS)</t>
         </is>
       </c>
-      <c r="D140" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (EVS)</t>
-        </is>
-      </c>
-      <c r="E140" s="7" t="inlineStr"/>
-      <c r="F140" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (EVS)</t>
-        </is>
-      </c>
+      <c r="D140" s="7" t="inlineStr"/>
+      <c r="E140" s="7" t="inlineStr">
+        <is>
+          <t>L.K.G (ENG)</t>
+        </is>
+      </c>
+      <c r="F140" s="7" t="inlineStr"/>
       <c r="G140" s="7" t="inlineStr">
         <is>
-          <t>L.K.G (EVS)</t>
+          <t>L.K.G (MATH)</t>
         </is>
       </c>
       <c r="H140" s="7" t="inlineStr">
         <is>
-          <t>L.K.G (EVS)</t>
+          <t>L.K.G (MATH)</t>
         </is>
       </c>
       <c r="I140" s="8" t="inlineStr">
@@ -4544,7 +4516,7 @@
       </c>
       <c r="B141" s="7" t="inlineStr">
         <is>
-          <t>L.K.G (ORAL)</t>
+          <t>L.K.G (ENG)</t>
         </is>
       </c>
       <c r="C141" s="7" t="inlineStr">
@@ -4554,18 +4526,18 @@
       </c>
       <c r="D141" s="7" t="inlineStr">
         <is>
-          <t>L.K.G (EVS)</t>
+          <t>L.K.G (ENG)</t>
         </is>
       </c>
       <c r="E141" s="7" t="inlineStr">
         <is>
-          <t>L.K.G (MATH)</t>
+          <t>L.K.G (ENG)</t>
         </is>
       </c>
       <c r="F141" s="7" t="inlineStr"/>
       <c r="G141" s="7" t="inlineStr">
         <is>
-          <t>L.K.G (ENG)</t>
+          <t>L.K.G (MATH)</t>
         </is>
       </c>
       <c r="H141" s="7" t="inlineStr">
@@ -4592,28 +4564,24 @@
       </c>
       <c r="C142" s="7" t="inlineStr">
         <is>
+          <t>L.K.G (EVS)</t>
+        </is>
+      </c>
+      <c r="D142" s="7" t="inlineStr"/>
+      <c r="E142" s="7" t="inlineStr">
+        <is>
+          <t>L.K.G (ENG)</t>
+        </is>
+      </c>
+      <c r="F142" s="7" t="inlineStr"/>
+      <c r="G142" s="7" t="inlineStr">
+        <is>
           <t>L.K.G (MATH)</t>
         </is>
       </c>
-      <c r="D142" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (MATH)</t>
-        </is>
-      </c>
-      <c r="E142" s="7" t="inlineStr"/>
-      <c r="F142" s="7" t="inlineStr">
+      <c r="H142" s="7" t="inlineStr">
         <is>
           <t>L.K.G (ENG)</t>
-        </is>
-      </c>
-      <c r="G142" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (MATH)</t>
-        </is>
-      </c>
-      <c r="H142" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (MATH)</t>
         </is>
       </c>
       <c r="I142" s="8" t="inlineStr">
@@ -4630,28 +4598,28 @@
       </c>
       <c r="B143" s="7" t="inlineStr">
         <is>
-          <t>L.K.G (ENG)</t>
+          <t>L.K.G (ORAL)</t>
         </is>
       </c>
       <c r="C143" s="7" t="inlineStr">
         <is>
-          <t>L.K.G (ENG)</t>
+          <t>L.K.G (EVS)</t>
         </is>
       </c>
       <c r="D143" s="7" t="inlineStr">
         <is>
-          <t>L.K.G (EVS)</t>
+          <t>L.K.G (MATH)</t>
         </is>
       </c>
       <c r="E143" s="7" t="inlineStr"/>
       <c r="F143" s="7" t="inlineStr">
         <is>
+          <t>L.K.G (ENG)</t>
+        </is>
+      </c>
+      <c r="G143" s="7" t="inlineStr">
+        <is>
           <t>L.K.G (EVS)</t>
-        </is>
-      </c>
-      <c r="G143" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (ENG)</t>
         </is>
       </c>
       <c r="H143" s="7" t="inlineStr">
@@ -4673,29 +4641,33 @@
       </c>
       <c r="B144" s="7" t="inlineStr">
         <is>
+          <t>L.K.G (ORAL)</t>
+        </is>
+      </c>
+      <c r="C144" s="7" t="inlineStr">
+        <is>
+          <t>L.K.G (EVS)</t>
+        </is>
+      </c>
+      <c r="D144" s="7" t="inlineStr">
+        <is>
           <t>L.K.G (MATH)</t>
         </is>
       </c>
-      <c r="C144" s="7" t="inlineStr"/>
-      <c r="D144" s="7" t="inlineStr">
+      <c r="E144" s="7" t="inlineStr"/>
+      <c r="F144" s="7" t="inlineStr">
+        <is>
+          <t>L.K.G (EVS)</t>
+        </is>
+      </c>
+      <c r="G144" s="7" t="inlineStr">
         <is>
           <t>L.K.G (MATH)</t>
         </is>
       </c>
-      <c r="E144" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (MATH)</t>
-        </is>
-      </c>
-      <c r="F144" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (MATH)</t>
-        </is>
-      </c>
-      <c r="G144" s="7" t="inlineStr"/>
       <c r="H144" s="7" t="inlineStr">
         <is>
-          <t>L.K.G (ENG)</t>
+          <t>L.K.G (EVS)</t>
         </is>
       </c>
       <c r="I144" s="8" t="inlineStr">
@@ -4712,29 +4684,33 @@
       </c>
       <c r="B145" s="7" t="inlineStr">
         <is>
-          <t>L.K.G (ORAL)</t>
+          <t>L.K.G (EVS)</t>
         </is>
       </c>
       <c r="C145" s="7" t="inlineStr">
         <is>
+          <t>L.K.G (ENG)</t>
+        </is>
+      </c>
+      <c r="D145" s="7" t="inlineStr">
+        <is>
+          <t>L.K.G (ENG)</t>
+        </is>
+      </c>
+      <c r="E145" s="7" t="inlineStr"/>
+      <c r="F145" s="7" t="inlineStr">
+        <is>
           <t>L.K.G (EVS)</t>
         </is>
       </c>
-      <c r="D145" s="7" t="inlineStr"/>
-      <c r="E145" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (ENG)</t>
-        </is>
-      </c>
-      <c r="F145" s="7" t="inlineStr"/>
       <c r="G145" s="7" t="inlineStr">
         <is>
-          <t>L.K.G (ENG)</t>
+          <t>L.K.G (MATH)</t>
         </is>
       </c>
       <c r="H145" s="7" t="inlineStr">
         <is>
-          <t>L.K.G (ENG)</t>
+          <t>L.K.G (MATH)</t>
         </is>
       </c>
       <c r="I145" s="8" t="inlineStr">
@@ -4815,17 +4791,17 @@
       <c r="C149" s="7" t="inlineStr"/>
       <c r="D149" s="7" t="inlineStr"/>
       <c r="E149" s="7" t="inlineStr"/>
-      <c r="F149" s="7" t="inlineStr">
+      <c r="F149" s="7" t="inlineStr"/>
+      <c r="G149" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (ENG)</t>
+        </is>
+      </c>
+      <c r="H149" s="7" t="inlineStr">
         <is>
           <t>Class 9 (ENG)</t>
         </is>
       </c>
-      <c r="G149" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (ENG)</t>
-        </is>
-      </c>
-      <c r="H149" s="7" t="inlineStr"/>
       <c r="I149" s="8" t="inlineStr">
         <is>
           <t>Class 10 (ENG)</t>
@@ -4844,20 +4820,20 @@
       <c r="E150" s="7" t="inlineStr"/>
       <c r="F150" s="7" t="inlineStr">
         <is>
+          <t>Class 9 (ENG)</t>
+        </is>
+      </c>
+      <c r="G150" s="7" t="inlineStr"/>
+      <c r="H150" s="7" t="inlineStr">
+        <is>
           <t>Class 8 (ENG)</t>
         </is>
       </c>
-      <c r="G150" s="7" t="inlineStr">
+      <c r="I150" s="8" t="inlineStr">
         <is>
           <t>Class 10 (ENG)</t>
         </is>
       </c>
-      <c r="H150" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (ENG)</t>
-        </is>
-      </c>
-      <c r="I150" s="7" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="6" t="inlineStr">
@@ -4869,17 +4845,17 @@
       <c r="C151" s="7" t="inlineStr"/>
       <c r="D151" s="7" t="inlineStr"/>
       <c r="E151" s="7" t="inlineStr"/>
-      <c r="F151" s="7" t="inlineStr"/>
+      <c r="F151" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (ENG)</t>
+        </is>
+      </c>
       <c r="G151" s="7" t="inlineStr">
         <is>
           <t>Class 8 (ENG)</t>
         </is>
       </c>
-      <c r="H151" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (ENG)</t>
-        </is>
-      </c>
+      <c r="H151" s="7" t="inlineStr"/>
       <c r="I151" s="8" t="inlineStr">
         <is>
           <t>Class 10 (ENG)</t>
@@ -4898,15 +4874,15 @@
       <c r="E152" s="7" t="inlineStr"/>
       <c r="F152" s="7" t="inlineStr">
         <is>
+          <t>Class 9 (ENG)</t>
+        </is>
+      </c>
+      <c r="G152" s="7" t="inlineStr"/>
+      <c r="H152" s="7" t="inlineStr">
+        <is>
           <t>Class 8 (ENG)</t>
         </is>
       </c>
-      <c r="G152" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (ENG)</t>
-        </is>
-      </c>
-      <c r="H152" s="7" t="inlineStr"/>
       <c r="I152" s="8" t="inlineStr">
         <is>
           <t>Class 10 (ENG)</t>
@@ -4953,12 +4929,12 @@
       <c r="F154" s="7" t="inlineStr"/>
       <c r="G154" s="7" t="inlineStr">
         <is>
+          <t>Class 8 (ENG)</t>
+        </is>
+      </c>
+      <c r="H154" s="7" t="inlineStr">
+        <is>
           <t>Class 9 (ENG)</t>
-        </is>
-      </c>
-      <c r="H154" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (ENG)</t>
         </is>
       </c>
       <c r="I154" s="8" t="inlineStr">
@@ -5035,20 +5011,20 @@
           <t>MON</t>
         </is>
       </c>
-      <c r="B158" s="7" t="inlineStr">
+      <c r="B158" s="7" t="inlineStr"/>
+      <c r="C158" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (SOC)</t>
+        </is>
+      </c>
+      <c r="D158" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (SOC)</t>
+        </is>
+      </c>
+      <c r="E158" s="7" t="inlineStr">
         <is>
           <t>Class 10 (SOC)</t>
-        </is>
-      </c>
-      <c r="C158" s="7" t="inlineStr"/>
-      <c r="D158" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (SOC)</t>
-        </is>
-      </c>
-      <c r="E158" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (SOC)</t>
         </is>
       </c>
       <c r="F158" s="7" t="inlineStr"/>
@@ -5062,20 +5038,20 @@
           <t>TUE</t>
         </is>
       </c>
-      <c r="B159" s="7" t="inlineStr">
+      <c r="B159" s="7" t="inlineStr"/>
+      <c r="C159" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (SOC)</t>
+        </is>
+      </c>
+      <c r="D159" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (SOC)</t>
+        </is>
+      </c>
+      <c r="E159" s="7" t="inlineStr">
         <is>
           <t>Class 9 (SOC)</t>
-        </is>
-      </c>
-      <c r="C159" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (SOC)</t>
-        </is>
-      </c>
-      <c r="D159" s="7" t="inlineStr"/>
-      <c r="E159" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (SOC)</t>
         </is>
       </c>
       <c r="F159" s="7" t="inlineStr"/>
@@ -5094,15 +5070,15 @@
           <t>Class 9 (SOC)</t>
         </is>
       </c>
-      <c r="C160" s="7" t="inlineStr">
+      <c r="C160" s="7" t="inlineStr"/>
+      <c r="D160" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (SOC)</t>
+        </is>
+      </c>
+      <c r="E160" s="7" t="inlineStr">
         <is>
           <t>Class 10 (SOC)</t>
-        </is>
-      </c>
-      <c r="D160" s="7" t="inlineStr"/>
-      <c r="E160" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (SOC)</t>
         </is>
       </c>
       <c r="F160" s="7" t="inlineStr"/>
@@ -5121,12 +5097,12 @@
           <t>Class 9 (SOC)</t>
         </is>
       </c>
-      <c r="C161" s="7" t="inlineStr"/>
-      <c r="D161" s="7" t="inlineStr">
+      <c r="C161" s="7" t="inlineStr">
         <is>
           <t>Class 10 (SOC)</t>
         </is>
       </c>
+      <c r="D161" s="7" t="inlineStr"/>
       <c r="E161" s="7" t="inlineStr">
         <is>
           <t>Class 8 (SOC)</t>
@@ -5143,20 +5119,20 @@
           <t>FRI</t>
         </is>
       </c>
-      <c r="B162" s="7" t="inlineStr">
+      <c r="B162" s="7" t="inlineStr"/>
+      <c r="C162" s="7" t="inlineStr">
         <is>
           <t>Class 10 (SOC)</t>
         </is>
       </c>
-      <c r="C162" s="7" t="inlineStr">
+      <c r="D162" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (SOC)</t>
+        </is>
+      </c>
+      <c r="E162" s="7" t="inlineStr">
         <is>
           <t>Class 9 (SOC)</t>
-        </is>
-      </c>
-      <c r="D162" s="7" t="inlineStr"/>
-      <c r="E162" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (SOC)</t>
         </is>
       </c>
       <c r="F162" s="7" t="inlineStr"/>
@@ -5172,20 +5148,20 @@
       </c>
       <c r="B163" s="7" t="inlineStr">
         <is>
+          <t>Class 10 (SOC)</t>
+        </is>
+      </c>
+      <c r="C163" s="7" t="inlineStr">
+        <is>
           <t>Class 9 (SOC)</t>
         </is>
       </c>
-      <c r="C163" s="7" t="inlineStr"/>
       <c r="D163" s="7" t="inlineStr">
         <is>
           <t>Class 8 (SOC)</t>
         </is>
       </c>
-      <c r="E163" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (SOC)</t>
-        </is>
-      </c>
+      <c r="E163" s="7" t="inlineStr"/>
       <c r="F163" s="7" t="inlineStr"/>
       <c r="G163" s="7" t="inlineStr"/>
       <c r="H163" s="7" t="inlineStr"/>
@@ -5267,18 +5243,18 @@
       <c r="C167" s="7" t="inlineStr"/>
       <c r="D167" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (TEL)</t>
+          <t>U.K.G (HIN)</t>
         </is>
       </c>
       <c r="E167" s="7" t="inlineStr">
         <is>
-          <t>U.K.G (HIN)</t>
+          <t>Class 4 (TEL)</t>
         </is>
       </c>
       <c r="F167" s="7" t="inlineStr"/>
       <c r="G167" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (TEL)</t>
+          <t>Class 5 (TEL)</t>
         </is>
       </c>
       <c r="H167" s="7" t="inlineStr">
@@ -5305,26 +5281,26 @@
       </c>
       <c r="C168" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (TEL)</t>
+          <t>U.K.G (HIN)</t>
         </is>
       </c>
       <c r="D168" s="7" t="inlineStr"/>
       <c r="E168" s="7" t="inlineStr">
         <is>
-          <t>U.K.G (HIN)</t>
-        </is>
-      </c>
-      <c r="F168" s="7" t="inlineStr"/>
+          <t>Class 6 (TEL)</t>
+        </is>
+      </c>
+      <c r="F168" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (TEL)</t>
+        </is>
+      </c>
       <c r="G168" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (TEL)</t>
-        </is>
-      </c>
-      <c r="H168" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (TEL)</t>
-        </is>
-      </c>
+          <t>Class 4 (TEL)</t>
+        </is>
+      </c>
+      <c r="H168" s="7" t="inlineStr"/>
       <c r="I168" s="8" t="inlineStr">
         <is>
           <t>Class 3</t>
@@ -5344,22 +5320,26 @@
       </c>
       <c r="C169" s="7" t="inlineStr">
         <is>
+          <t>Class 4 (TEL)</t>
+        </is>
+      </c>
+      <c r="D169" s="7" t="inlineStr"/>
+      <c r="E169" s="7" t="inlineStr">
+        <is>
+          <t>U.K.G (HIN)</t>
+        </is>
+      </c>
+      <c r="F169" s="7" t="inlineStr">
+        <is>
           <t>Class 5 (TEL)</t>
         </is>
       </c>
-      <c r="D169" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (TEL)</t>
-        </is>
-      </c>
-      <c r="E169" s="7" t="inlineStr"/>
-      <c r="F169" s="7" t="inlineStr">
+      <c r="G169" s="7" t="inlineStr"/>
+      <c r="H169" s="7" t="inlineStr">
         <is>
           <t>Class 6 (TEL)</t>
         </is>
       </c>
-      <c r="G169" s="7" t="inlineStr"/>
-      <c r="H169" s="7" t="inlineStr"/>
       <c r="I169" s="8" t="inlineStr">
         <is>
           <t>Class 3</t>
@@ -5377,17 +5357,17 @@
           <t>Class 3 (TEL)</t>
         </is>
       </c>
-      <c r="C170" s="7" t="inlineStr"/>
+      <c r="C170" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (TEL)</t>
+        </is>
+      </c>
       <c r="D170" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (TEL)</t>
-        </is>
-      </c>
-      <c r="E170" s="7" t="inlineStr">
-        <is>
           <t>U.K.G (HIN)</t>
         </is>
       </c>
+      <c r="E170" s="7" t="inlineStr"/>
       <c r="F170" s="7" t="inlineStr">
         <is>
           <t>Class 6 (TEL)</t>
@@ -5396,7 +5376,7 @@
       <c r="G170" s="7" t="inlineStr"/>
       <c r="H170" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (TEL)</t>
+          <t>Class 5 (TEL)</t>
         </is>
       </c>
       <c r="I170" s="8" t="inlineStr">
@@ -5421,22 +5401,18 @@
           <t>Class 4 (TEL)</t>
         </is>
       </c>
-      <c r="D171" s="7" t="inlineStr"/>
-      <c r="E171" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (HIN)</t>
-        </is>
-      </c>
+      <c r="D171" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (TEL)</t>
+        </is>
+      </c>
+      <c r="E171" s="7" t="inlineStr"/>
       <c r="F171" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (TEL)</t>
-        </is>
-      </c>
-      <c r="G171" s="7" t="inlineStr">
-        <is>
           <t>Class 6 (TEL)</t>
         </is>
       </c>
+      <c r="G171" s="7" t="inlineStr"/>
       <c r="H171" s="7" t="inlineStr"/>
       <c r="I171" s="8" t="inlineStr">
         <is>
@@ -5450,31 +5426,31 @@
           <t>SAT</t>
         </is>
       </c>
-      <c r="B172" s="7" t="inlineStr">
+      <c r="B172" s="7" t="inlineStr"/>
+      <c r="C172" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (TEL)</t>
+        </is>
+      </c>
+      <c r="D172" s="7" t="inlineStr">
+        <is>
+          <t>U.K.G (HIN)</t>
+        </is>
+      </c>
+      <c r="E172" s="7" t="inlineStr"/>
+      <c r="F172" s="7" t="inlineStr">
         <is>
           <t>Class 3 (TEL)</t>
         </is>
       </c>
-      <c r="C172" s="7" t="inlineStr">
+      <c r="G172" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (TEL)</t>
+        </is>
+      </c>
+      <c r="H172" s="7" t="inlineStr">
         <is>
           <t>Class 6 (TEL)</t>
-        </is>
-      </c>
-      <c r="D172" s="7" t="inlineStr"/>
-      <c r="E172" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (HIN)</t>
-        </is>
-      </c>
-      <c r="F172" s="7" t="inlineStr"/>
-      <c r="G172" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (TEL)</t>
-        </is>
-      </c>
-      <c r="H172" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (TEL)</t>
         </is>
       </c>
       <c r="I172" s="8" t="inlineStr">
@@ -5556,30 +5532,26 @@
           <t>Class 4 (MATH)</t>
         </is>
       </c>
-      <c r="C176" s="7" t="inlineStr">
+      <c r="C176" s="7" t="inlineStr"/>
+      <c r="D176" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (MATH)</t>
+        </is>
+      </c>
+      <c r="E176" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (MATH)</t>
+        </is>
+      </c>
+      <c r="F176" s="7" t="inlineStr"/>
+      <c r="G176" s="7" t="inlineStr">
         <is>
           <t>Class 4 (MATH)</t>
         </is>
       </c>
-      <c r="D176" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (MATH)</t>
-        </is>
-      </c>
-      <c r="E176" s="7" t="inlineStr"/>
-      <c r="F176" s="7" t="inlineStr">
+      <c r="H176" s="7" t="inlineStr">
         <is>
           <t>Class 5 (MATH)</t>
-        </is>
-      </c>
-      <c r="G176" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (MATH)</t>
-        </is>
-      </c>
-      <c r="H176" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (MATH)</t>
         </is>
       </c>
       <c r="I176" s="8" t="inlineStr">
@@ -5594,29 +5566,33 @@
           <t>TUE</t>
         </is>
       </c>
-      <c r="B177" s="7" t="inlineStr"/>
+      <c r="B177" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (MATH)</t>
+        </is>
+      </c>
       <c r="C177" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (MATH)</t>
+          <t>Class 3 (MATH)</t>
         </is>
       </c>
       <c r="D177" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (MATH)</t>
-        </is>
-      </c>
-      <c r="E177" s="7" t="inlineStr">
-        <is>
           <t>Class 5 (MATH)</t>
         </is>
       </c>
+      <c r="E177" s="7" t="inlineStr"/>
       <c r="F177" s="7" t="inlineStr"/>
       <c r="G177" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (MATH)</t>
-        </is>
-      </c>
-      <c r="H177" s="7" t="inlineStr"/>
+          <t>Class 5 (MATH)</t>
+        </is>
+      </c>
+      <c r="H177" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (MATH)</t>
+        </is>
+      </c>
       <c r="I177" s="8" t="inlineStr">
         <is>
           <t>Class 4</t>
@@ -5639,23 +5615,23 @@
           <t>Class 2 (MATH)</t>
         </is>
       </c>
-      <c r="D178" s="7" t="inlineStr"/>
-      <c r="E178" s="7" t="inlineStr">
+      <c r="D178" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (MATH)</t>
+        </is>
+      </c>
+      <c r="E178" s="7" t="inlineStr"/>
+      <c r="F178" s="7" t="inlineStr"/>
+      <c r="G178" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (MATH)</t>
+        </is>
+      </c>
+      <c r="H178" s="7" t="inlineStr">
         <is>
           <t>Class 3 (MATH)</t>
         </is>
       </c>
-      <c r="F178" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (MATH)</t>
-        </is>
-      </c>
-      <c r="G178" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (MATH)</t>
-        </is>
-      </c>
-      <c r="H178" s="7" t="inlineStr"/>
       <c r="I178" s="8" t="inlineStr">
         <is>
           <t>Class 4</t>
@@ -5668,17 +5644,17 @@
           <t>THU</t>
         </is>
       </c>
-      <c r="B179" s="7" t="inlineStr"/>
+      <c r="B179" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (MATH)</t>
+        </is>
+      </c>
       <c r="C179" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (MATH)</t>
-        </is>
-      </c>
-      <c r="D179" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (MATH)</t>
-        </is>
-      </c>
+          <t>Class 5 (MATH)</t>
+        </is>
+      </c>
+      <c r="D179" s="7" t="inlineStr"/>
       <c r="E179" s="7" t="inlineStr">
         <is>
           <t>Class 2 (MATH)</t>
@@ -5703,28 +5679,28 @@
           <t>FRI</t>
         </is>
       </c>
-      <c r="B180" s="7" t="inlineStr"/>
+      <c r="B180" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (MATH)</t>
+        </is>
+      </c>
       <c r="C180" s="7" t="inlineStr">
         <is>
           <t>Class 2 (MATH)</t>
         </is>
       </c>
-      <c r="D180" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (MATH)</t>
-        </is>
-      </c>
+      <c r="D180" s="7" t="inlineStr"/>
       <c r="E180" s="7" t="inlineStr">
         <is>
+          <t>Class 2 (MATH)</t>
+        </is>
+      </c>
+      <c r="F180" s="7" t="inlineStr">
+        <is>
           <t>Class 3 (MATH)</t>
         </is>
       </c>
-      <c r="F180" s="7" t="inlineStr"/>
-      <c r="G180" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (MATH)</t>
-        </is>
-      </c>
+      <c r="G180" s="7" t="inlineStr"/>
       <c r="H180" s="7" t="inlineStr">
         <is>
           <t>Class 3 (MATH)</t>
@@ -5755,16 +5731,16 @@
       </c>
       <c r="E181" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (MATH)</t>
-        </is>
-      </c>
-      <c r="F181" s="7" t="inlineStr"/>
+          <t>Class 2 (MATH)</t>
+        </is>
+      </c>
+      <c r="F181" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (MATH)</t>
+        </is>
+      </c>
       <c r="G181" s="7" t="inlineStr"/>
-      <c r="H181" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (MATH)</t>
-        </is>
-      </c>
+      <c r="H181" s="7" t="inlineStr"/>
       <c r="I181" s="8" t="inlineStr">
         <is>
           <t>Class 4</t>
@@ -5843,15 +5819,15 @@
       <c r="C185" s="7" t="inlineStr"/>
       <c r="D185" s="7" t="inlineStr"/>
       <c r="E185" s="7" t="inlineStr"/>
-      <c r="F185" s="7" t="inlineStr"/>
-      <c r="G185" s="7" t="inlineStr">
+      <c r="F185" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (P.E.T)</t>
+        </is>
+      </c>
+      <c r="G185" s="7" t="inlineStr"/>
+      <c r="H185" s="7" t="inlineStr">
         <is>
           <t>Class 2 (P.E.T)</t>
-        </is>
-      </c>
-      <c r="H185" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (P.E.T)</t>
         </is>
       </c>
       <c r="I185" s="7" t="inlineStr"/>
@@ -5868,19 +5844,15 @@
       <c r="E186" s="7" t="inlineStr"/>
       <c r="F186" s="7" t="inlineStr">
         <is>
-          <t>L.K.G (P.E.T)</t>
+          <t>Class 1 (P.E.T)</t>
         </is>
       </c>
       <c r="G186" s="7" t="inlineStr">
         <is>
-          <t>Class 1 (P.E.T)</t>
-        </is>
-      </c>
-      <c r="H186" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (P.E.T)</t>
-        </is>
-      </c>
+          <t>Class 2 (P.E.T)</t>
+        </is>
+      </c>
+      <c r="H186" s="7" t="inlineStr"/>
       <c r="I186" s="7" t="inlineStr"/>
     </row>
     <row r="187">
@@ -5895,17 +5867,17 @@
       <c r="E187" s="7" t="inlineStr"/>
       <c r="F187" s="7" t="inlineStr">
         <is>
-          <t>Class 9 (P.E.T)</t>
+          <t>Class 3 (P.E.T)</t>
         </is>
       </c>
       <c r="G187" s="7" t="inlineStr">
         <is>
-          <t>Class 3 (P.E.T)</t>
+          <t>Class 1 (P.E.T)</t>
         </is>
       </c>
       <c r="H187" s="7" t="inlineStr">
         <is>
-          <t>U.K.G (P.E.T)</t>
+          <t>Class 8 (P.E.T)</t>
         </is>
       </c>
       <c r="I187" s="7" t="inlineStr"/>
@@ -5945,15 +5917,19 @@
       <c r="E189" s="7" t="inlineStr"/>
       <c r="F189" s="7" t="inlineStr">
         <is>
+          <t>Class 2 (P.E.T)</t>
+        </is>
+      </c>
+      <c r="G189" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (P.E.T)</t>
+        </is>
+      </c>
+      <c r="H189" s="7" t="inlineStr">
+        <is>
           <t>Class 7 (P.E.T)</t>
         </is>
       </c>
-      <c r="G189" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (P.E.T)</t>
-        </is>
-      </c>
-      <c r="H189" s="7" t="inlineStr"/>
       <c r="I189" s="7" t="inlineStr"/>
     </row>
     <row r="190">
@@ -5966,17 +5942,17 @@
       <c r="C190" s="7" t="inlineStr"/>
       <c r="D190" s="7" t="inlineStr"/>
       <c r="E190" s="7" t="inlineStr"/>
-      <c r="F190" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (P.E.T)</t>
-        </is>
-      </c>
+      <c r="F190" s="7" t="inlineStr"/>
       <c r="G190" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (P.E.T)</t>
-        </is>
-      </c>
-      <c r="H190" s="7" t="inlineStr"/>
+          <t>Class 4 (P.E.T)</t>
+        </is>
+      </c>
+      <c r="H190" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (P.E.T)</t>
+        </is>
+      </c>
       <c r="I190" s="7" t="inlineStr"/>
     </row>
     <row r="192">
@@ -6099,7 +6075,7 @@
       <c r="F197" s="7" t="inlineStr"/>
       <c r="G197" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (KAR)</t>
+          <t>Class 10 (KAR)</t>
         </is>
       </c>
       <c r="H197" s="7" t="inlineStr"/>
@@ -6292,7 +6268,7 @@
       <c r="F2" s="7" t="inlineStr">
         <is>
           <t>Sai Lakshmi
-(EVS)</t>
+(HIN)</t>
         </is>
       </c>
       <c r="G2" s="7" t="inlineStr">
@@ -6333,14 +6309,14 @@
       </c>
       <c r="M2" s="7" t="inlineStr">
         <is>
+          <t>D.V.Rao
+(TEL)</t>
+        </is>
+      </c>
+      <c r="N2" s="7" t="inlineStr">
+        <is>
           <t>Bheema
-(CHEM)</t>
-        </is>
-      </c>
-      <c r="N2" s="7" t="inlineStr">
-        <is>
-          <t>Sunitha
-(SOC)</t>
+(PHY)</t>
         </is>
       </c>
     </row>
@@ -6358,55 +6334,55 @@
       <c r="D3" s="7" t="inlineStr">
         <is>
           <t>Bhavani
+(MATH)</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>Sai Lakshmi
 (EVS)</t>
         </is>
       </c>
-      <c r="E3" s="7" t="inlineStr">
+      <c r="F3" s="7" t="inlineStr">
         <is>
           <t>Maha
 (ENG)</t>
         </is>
       </c>
-      <c r="F3" s="7" t="inlineStr">
-        <is>
-          <t>Sai Lakshmi
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>Riya
+(HIN)</t>
+        </is>
+      </c>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>Fathima
+(HIN)</t>
+        </is>
+      </c>
+      <c r="I3" s="7" t="inlineStr">
+        <is>
+          <t>Lalitha
 (EVS)</t>
         </is>
       </c>
-      <c r="G3" s="7" t="inlineStr">
+      <c r="J3" s="7" t="inlineStr">
         <is>
           <t>Pallavi
 (SOC)</t>
         </is>
       </c>
-      <c r="H3" s="7" t="inlineStr">
-        <is>
-          <t>Tulasi
-(MATH)</t>
-        </is>
-      </c>
-      <c r="I3" s="7" t="inlineStr">
-        <is>
-          <t>Fathima
-(HIN)</t>
-        </is>
-      </c>
-      <c r="J3" s="7" t="inlineStr">
-        <is>
-          <t>Lalitha
-(CHEM)</t>
-        </is>
-      </c>
       <c r="K3" s="7" t="inlineStr">
         <is>
-          <t>D.V.Rao
-(TEL)</t>
+          <t>Ravi
+(ENG)</t>
         </is>
       </c>
       <c r="L3" s="7" t="inlineStr">
         <is>
-          <t>Sangeetha
-(MATH)</t>
+          <t>Sunitha
+(SOC)</t>
         </is>
       </c>
       <c r="M3" s="7" t="inlineStr">
@@ -6429,16 +6405,16 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>Sitha
-(EVS)</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
           <t>Naga mani
 (TEL)</t>
         </is>
       </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>Swathi
+(HIN)</t>
+        </is>
+      </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
           <t>Sai Lakshmi
@@ -6453,8 +6429,8 @@
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
-          <t>Lalitha
-(EVS)</t>
+          <t>Maheswari
+(COMP)</t>
         </is>
       </c>
       <c r="H4" s="7" t="inlineStr">
@@ -6465,32 +6441,32 @@
       </c>
       <c r="I4" s="7" t="inlineStr">
         <is>
-          <t>Swathi
-(TEL)</t>
+          <t>Pallavi
+(SOC)</t>
         </is>
       </c>
       <c r="J4" s="7" t="inlineStr">
-        <is>
-          <t>Ravi
-(ENG)</t>
-        </is>
-      </c>
-      <c r="K4" s="7" t="inlineStr">
         <is>
           <t>Sangeetha
 (MATH)</t>
         </is>
       </c>
+      <c r="K4" s="7" t="inlineStr">
+        <is>
+          <t>Lalitha
+(BIO)</t>
+        </is>
+      </c>
       <c r="L4" s="7" t="inlineStr">
+        <is>
+          <t>Bheema
+(CHEM)</t>
+        </is>
+      </c>
+      <c r="M4" s="7" t="inlineStr">
         <is>
           <t>Sunitha
 (SOC)</t>
-        </is>
-      </c>
-      <c r="M4" s="7" t="inlineStr">
-        <is>
-          <t>Gowtham
-(MATH)</t>
         </is>
       </c>
       <c r="N4" s="7" t="inlineStr">
@@ -6507,74 +6483,74 @@
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
+          <t>Sitha
+(ENG)</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
           <t>Naga mani
 (TEL)</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>Swathi
-(HIN)</t>
-        </is>
-      </c>
       <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>Bhavani
+(MATH)</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>Maheswari
 (COMP)</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
-        <is>
-          <t>Bhavani
-(G.K)</t>
-        </is>
-      </c>
       <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>Lalitha
+(EVS)</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>Swathi
+(TEL)</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>Tulasi
+(MATH)</t>
+        </is>
+      </c>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>Ravi
+(ENG)</t>
+        </is>
+      </c>
+      <c r="K5" s="7" t="inlineStr">
+        <is>
+          <t>Sangeetha
+(COMP)</t>
+        </is>
+      </c>
+      <c r="L5" s="7" t="inlineStr">
+        <is>
+          <t>Chalapathi
+(BIO)</t>
+        </is>
+      </c>
+      <c r="M5" s="7" t="inlineStr">
         <is>
           <t>Riya
 (HIN)</t>
         </is>
       </c>
-      <c r="H5" s="7" t="inlineStr">
-        <is>
-          <t>Fathima
-(HIN)</t>
-        </is>
-      </c>
-      <c r="I5" s="7" t="inlineStr">
-        <is>
-          <t>Pallavi
-(SOC)</t>
-        </is>
-      </c>
-      <c r="J5" s="7" t="inlineStr">
-        <is>
-          <t>Lalitha
-(BIO)</t>
-        </is>
-      </c>
-      <c r="K5" s="7" t="inlineStr">
-        <is>
-          <t>Ravi
-(GRAM)</t>
-        </is>
-      </c>
-      <c r="L5" s="7" t="inlineStr">
-        <is>
-          <t>D.V.Rao
-(TEL)</t>
-        </is>
-      </c>
-      <c r="M5" s="7" t="inlineStr">
+      <c r="N5" s="7" t="inlineStr">
         <is>
           <t>Sunitha
 (SOC)</t>
-        </is>
-      </c>
-      <c r="N5" s="7" t="inlineStr">
-        <is>
-          <t>Bheema
-(CHEM)</t>
         </is>
       </c>
     </row>
@@ -6585,14 +6561,14 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>Sitha
-(EVS)</t>
+          <t>P.E
+(P.E.T)</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>Sai Lakshmi
-(ENG)</t>
+          <t>P.E
+(P.E.T)</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
@@ -6603,8 +6579,8 @@
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>Naga mani
-(TEL)</t>
+          <t>Sai Lakshmi
+(EVS)</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
@@ -6621,20 +6597,20 @@
       </c>
       <c r="I6" s="7" t="inlineStr">
         <is>
-          <t>Tulasi
-(MATH)</t>
+          <t>P.E
+(P.E.T)</t>
         </is>
       </c>
       <c r="J6" s="7" t="inlineStr">
         <is>
-          <t>Fathima
-(HIN)</t>
+          <t>P.E
+(P.E.T)</t>
         </is>
       </c>
       <c r="K6" s="7" t="inlineStr">
         <is>
-          <t>Ravi
-(ENG)</t>
+          <t>D.V.Rao
+(TEL)</t>
         </is>
       </c>
       <c r="L6" s="7" t="inlineStr">
@@ -6645,8 +6621,8 @@
       </c>
       <c r="M6" s="7" t="inlineStr">
         <is>
-          <t>Sonu
-(ENG)</t>
+          <t>P.E
+(P.E.T)</t>
         </is>
       </c>
       <c r="N6" s="7" t="inlineStr">
@@ -6664,13 +6640,13 @@
       <c r="C7" s="7" t="inlineStr">
         <is>
           <t>Sitha
-(EVS)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Sai Lakshmi
-(ENG)</t>
+          <t>Bhavani
+(MATH)</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
@@ -6681,38 +6657,38 @@
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
+          <t>Naga mani
+(TEL)</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>Sai Lakshmi
+(G.K)</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
         <is>
           <t>Tulasi
 (MATH)</t>
         </is>
       </c>
-      <c r="H7" s="7" t="inlineStr">
+      <c r="I7" s="7" t="inlineStr">
         <is>
           <t>Swathi
 (TEL)</t>
         </is>
       </c>
-      <c r="I7" s="7" t="inlineStr">
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>Fathima
+(HIN)</t>
+        </is>
+      </c>
+      <c r="K7" s="7" t="inlineStr">
         <is>
           <t>Lalitha
-(EVS)</t>
-        </is>
-      </c>
-      <c r="J7" s="7" t="inlineStr">
-        <is>
-          <t>Pallavi
-(SOC)</t>
-        </is>
-      </c>
-      <c r="K7" s="7" t="inlineStr">
-        <is>
-          <t>Sangeetha
-(MATH)</t>
+(CHEM)</t>
         </is>
       </c>
       <c r="L7" s="7" t="inlineStr">
@@ -6742,45 +6718,45 @@
       <c r="C8" s="7" t="inlineStr">
         <is>
           <t>Sitha
-(EVS)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>Bhavani
-(MATH)</t>
+          <t>Sai Lakshmi
+(ENG)</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>Sai Lakshmi
-(EVS)</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>Maha
 (ENG)</t>
         </is>
       </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>P.E
+(P.E.T)</t>
+        </is>
+      </c>
       <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>Pallavi
+(SOC)</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>Lalitha
+(EVS)</t>
+        </is>
+      </c>
+      <c r="I8" s="7" t="inlineStr">
         <is>
           <t>Tulasi
 (MATH)</t>
         </is>
       </c>
-      <c r="H8" s="7" t="inlineStr">
-        <is>
-          <t>Lalitha
-(EVS)</t>
-        </is>
-      </c>
-      <c r="I8" s="7" t="inlineStr">
-        <is>
-          <t>P.E
-(P.E.T)</t>
-        </is>
-      </c>
       <c r="J8" s="7" t="inlineStr">
         <is>
           <t>Swathi
@@ -6795,19 +6771,20 @@
       </c>
       <c r="L8" s="7" t="inlineStr">
         <is>
-          <t>Chalapathi
-(BIO)</t>
-        </is>
-      </c>
-      <c r="M8" s="7" t="inlineStr">
-        <is>
           <t>D.V.Rao
 (TEL)</t>
         </is>
       </c>
-      <c r="N8" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
+      <c r="M8" s="7" t="inlineStr">
+        <is>
+          <t>Sonu
+(ENG)</t>
+        </is>
+      </c>
+      <c r="N8" s="7" t="inlineStr">
+        <is>
+          <t>Ravi
+(GRAM)</t>
         </is>
       </c>
     </row>
@@ -6903,13 +6880,13 @@
       <c r="C10" s="7" t="inlineStr">
         <is>
           <t>Sitha
-(ORAL)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
           <t>Bhavani
-(MATH)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
@@ -6932,8 +6909,8 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>Lalitha
-(EVS)</t>
+          <t>Tulasi
+(MATH)</t>
         </is>
       </c>
       <c r="I10" s="7" t="inlineStr">
@@ -6944,8 +6921,8 @@
       </c>
       <c r="J10" s="7" t="inlineStr">
         <is>
-          <t>Sangeetha
-(MATH)</t>
+          <t>Lalitha
+(BIO)</t>
         </is>
       </c>
       <c r="K10" s="7" t="inlineStr">
@@ -6957,19 +6934,19 @@
       <c r="L10" s="7" t="inlineStr">
         <is>
           <t>Fathima
-(G.K)</t>
+(HIN)</t>
         </is>
       </c>
       <c r="M10" s="7" t="inlineStr">
         <is>
-          <t>Sunitha
-(SOC)</t>
+          <t>Riya
+(HIN)</t>
         </is>
       </c>
       <c r="N10" s="7" t="inlineStr">
         <is>
           <t>Bheema
-(CHEM)</t>
+(PHY)</t>
         </is>
       </c>
     </row>
@@ -6986,8 +6963,8 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Sai Lakshmi
-(ENG)</t>
+          <t>Swathi
+(HIN)</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
@@ -6998,22 +6975,22 @@
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
+          <t>Sai Lakshmi
+(EVS)</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
           <t>Tulasi
 (MATH)</t>
         </is>
       </c>
-      <c r="G11" s="7" t="inlineStr">
+      <c r="H11" s="7" t="inlineStr">
         <is>
           <t>Maheswari
 (COMP)</t>
         </is>
       </c>
-      <c r="H11" s="7" t="inlineStr">
-        <is>
-          <t>Swathi
-(TEL)</t>
-        </is>
-      </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
           <t>Fathima
@@ -7022,14 +6999,14 @@
       </c>
       <c r="J11" s="7" t="inlineStr">
         <is>
-          <t>Ravi
-(ENG)</t>
+          <t>Lalitha
+(PHY)</t>
         </is>
       </c>
       <c r="K11" s="7" t="inlineStr">
         <is>
-          <t>Lalitha
-(BIO)</t>
+          <t>Sangeetha
+(MATH)</t>
         </is>
       </c>
       <c r="L11" s="7" t="inlineStr">
@@ -7040,14 +7017,14 @@
       </c>
       <c r="M11" s="7" t="inlineStr">
         <is>
-          <t>Riya
-(HIN)</t>
-        </is>
-      </c>
-      <c r="N11" s="7" t="inlineStr">
-        <is>
           <t>Bheema
 (PHY)</t>
+        </is>
+      </c>
+      <c r="N11" s="7" t="inlineStr">
+        <is>
+          <t>Gowtham
+(MATH)</t>
         </is>
       </c>
     </row>
@@ -7059,57 +7036,57 @@
       <c r="C12" s="7" t="inlineStr">
         <is>
           <t>Sitha
+(ENG)</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>Bhavani
 (EVS)</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>Naga mani
-(TEL)</t>
-        </is>
-      </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
           <t>Sai Lakshmi
+(HIN)</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>Maha
+(GRAM)</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>Lalitha
 (EVS)</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr">
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>Pallavi
+(SOC)</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
         <is>
           <t>Tulasi
 (MATH)</t>
         </is>
       </c>
-      <c r="G12" s="7" t="inlineStr">
-        <is>
-          <t>Lalitha
-(EVS)</t>
-        </is>
-      </c>
-      <c r="H12" s="7" t="inlineStr">
-        <is>
-          <t>Maha
+      <c r="J12" s="7" t="inlineStr">
+        <is>
+          <t>Ravi
 (ENG)</t>
         </is>
       </c>
-      <c r="I12" s="7" t="inlineStr">
-        <is>
-          <t>Pallavi
-(SOC)</t>
-        </is>
-      </c>
-      <c r="J12" s="7" t="inlineStr">
+      <c r="K12" s="7" t="inlineStr">
         <is>
           <t>Sangeetha
 (MATH)</t>
         </is>
       </c>
-      <c r="K12" s="7" t="inlineStr">
-        <is>
-          <t>Ravi
-(ENG)</t>
-        </is>
-      </c>
       <c r="L12" s="7" t="inlineStr">
         <is>
           <t>D.V.Rao
@@ -7118,14 +7095,14 @@
       </c>
       <c r="M12" s="7" t="inlineStr">
         <is>
-          <t>Bheema
-(CHEM)</t>
-        </is>
-      </c>
-      <c r="N12" s="7" t="inlineStr">
-        <is>
           <t>Gowtham
 (MATH)</t>
+        </is>
+      </c>
+      <c r="N12" s="7" t="inlineStr">
+        <is>
+          <t>Sunitha
+(SOC)</t>
         </is>
       </c>
     </row>
@@ -7137,27 +7114,27 @@
       <c r="C13" s="7" t="inlineStr">
         <is>
           <t>Sitha
-(MATH)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>Swathi
-(HIN)</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>Bhavani
-(MATH)</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="inlineStr">
         <is>
           <t>Naga mani
 (TEL)</t>
         </is>
       </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>Maheswari
+(COMP)</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>Bhavani
+(G.K)</t>
+        </is>
+      </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
           <t>Riya
@@ -7166,20 +7143,20 @@
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
+          <t>Fathima
+(HIN)</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
           <t>Pallavi
 (SOC)</t>
         </is>
       </c>
-      <c r="I13" s="7" t="inlineStr">
-        <is>
-          <t>Tulasi
-(MATH)</t>
-        </is>
-      </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
-          <t>Fathima
-(HIN)</t>
+          <t>Swathi
+(TEL)</t>
         </is>
       </c>
       <c r="K13" s="7" t="inlineStr">
@@ -7196,14 +7173,14 @@
       </c>
       <c r="M13" s="7" t="inlineStr">
         <is>
-          <t>Gowtham
-(MATH)</t>
-        </is>
-      </c>
-      <c r="N13" s="7" t="inlineStr">
-        <is>
           <t>Sunitha
 (SOC)</t>
+        </is>
+      </c>
+      <c r="N13" s="7" t="inlineStr">
+        <is>
+          <t>Bheema
+(CHEM)</t>
         </is>
       </c>
     </row>
@@ -7220,68 +7197,67 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>Bhavani
-(MATH)</t>
+          <t>Sai Lakshmi
+(ENG)</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>Sai Lakshmi
-(HIN)</t>
+          <t>P.E
+(P.E.T)</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
-        <is>
-          <t>Maheswari
-(COMP)</t>
-        </is>
-      </c>
-      <c r="G14" s="7" t="inlineStr">
         <is>
           <t>Maha
 (ENG)</t>
         </is>
       </c>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>Pallavi
+(SOC)</t>
+        </is>
+      </c>
       <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>Lalitha
+(EVS)</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>Swathi
+(TEL)</t>
+        </is>
+      </c>
+      <c r="J14" s="7" t="inlineStr">
         <is>
           <t>Fathima
 (HIN)</t>
         </is>
       </c>
-      <c r="I14" s="7" t="inlineStr">
-        <is>
-          <t>Lalitha
-(EVS)</t>
-        </is>
-      </c>
-      <c r="J14" s="7" t="inlineStr">
-        <is>
-          <t>Pallavi
-(SOC)</t>
-        </is>
-      </c>
       <c r="K14" s="7" t="inlineStr">
+        <is>
+          <t>Ravi
+(ENG)</t>
+        </is>
+      </c>
+      <c r="L14" s="7" t="inlineStr">
         <is>
           <t>Sangeetha
 (MATH)</t>
         </is>
       </c>
-      <c r="L14" s="7" t="inlineStr">
+      <c r="M14" s="7" t="inlineStr">
         <is>
           <t>Sonu
 (ENG)</t>
         </is>
       </c>
-      <c r="M14" s="7" t="inlineStr">
-        <is>
-          <t>Ravi
-(GRAM)</t>
-        </is>
-      </c>
-      <c r="N14" s="7" t="inlineStr">
-        <is>
-          <t>Chalapathi
-(BIO)</t>
+      <c r="N14" s="12" t="inlineStr">
+        <is>
+          <t>Recreation</t>
         </is>
       </c>
     </row>
@@ -7293,49 +7269,49 @@
       <c r="C15" s="7" t="inlineStr">
         <is>
           <t>Sitha
+(MATH)</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>Sai Lakshmi
 (ENG)</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr">
+      <c r="E15" s="7" t="inlineStr">
         <is>
           <t>Bhavani
-(EVS)</t>
-        </is>
-      </c>
-      <c r="E15" s="7" t="inlineStr">
+(MATH)</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
         <is>
           <t>P.E
 (P.E.T)</t>
         </is>
       </c>
-      <c r="F15" s="7" t="inlineStr">
+      <c r="G15" s="7" t="inlineStr">
         <is>
           <t>Maha
 (ENG)</t>
         </is>
       </c>
-      <c r="G15" s="7" t="inlineStr">
-        <is>
-          <t>Sai Lakshmi
-(G.K)</t>
-        </is>
-      </c>
       <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>Swathi
+(TEL)</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
         <is>
           <t>Tulasi
 (MATH)</t>
         </is>
       </c>
-      <c r="I15" s="7" t="inlineStr">
-        <is>
-          <t>Swathi
-(TEL)</t>
-        </is>
-      </c>
       <c r="J15" s="7" t="inlineStr">
         <is>
           <t>Lalitha
-(BIO)</t>
+(CHEM)</t>
         </is>
       </c>
       <c r="K15" s="7" t="inlineStr">
@@ -7346,8 +7322,8 @@
       </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
-          <t>Ravi
-(GRAM)</t>
+          <t>Sangeetha
+(MATH)</t>
         </is>
       </c>
       <c r="M15" s="7" t="inlineStr">
@@ -7358,8 +7334,8 @@
       </c>
       <c r="N15" s="7" t="inlineStr">
         <is>
-          <t>Sonu
-(ENG)</t>
+          <t>Chalapathi
+(BIO)</t>
         </is>
       </c>
     </row>
@@ -7376,62 +7352,62 @@
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
+          <t>Sai Lakshmi
+(ENG)</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>Sai Lakshmi
+          <t>Bhavani
+(MATH)</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>Naga mani
+(TEL)</t>
+        </is>
+      </c>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>Tulasi
+(MATH)</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>Maha
+(ENG)</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>Lalitha
 (EVS)</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr">
-        <is>
-          <t>Maha
-(GRAM)</t>
-        </is>
-      </c>
-      <c r="G16" s="7" t="inlineStr">
+      <c r="J16" s="7" t="inlineStr">
         <is>
           <t>Pallavi
 (SOC)</t>
         </is>
       </c>
-      <c r="H16" s="7" t="inlineStr">
-        <is>
-          <t>P.E
-(P.E.T)</t>
-        </is>
-      </c>
-      <c r="I16" s="7" t="inlineStr">
-        <is>
-          <t>P.E
-(P.E.T)</t>
-        </is>
-      </c>
-      <c r="J16" s="7" t="inlineStr">
-        <is>
-          <t>Swathi
-(TEL)</t>
-        </is>
-      </c>
       <c r="K16" s="7" t="inlineStr">
         <is>
-          <t>Lalitha
-(CHEM)</t>
+          <t>Sangeetha
+(MATH)</t>
         </is>
       </c>
       <c r="L16" s="7" t="inlineStr">
-        <is>
-          <t>Sangeetha
-(COMP)</t>
-        </is>
-      </c>
-      <c r="M16" s="7" t="inlineStr">
         <is>
           <t>Sonu
 (ENG)</t>
+        </is>
+      </c>
+      <c r="M16" s="7" t="inlineStr">
+        <is>
+          <t>Ravi
+(GRAM)</t>
         </is>
       </c>
       <c r="N16" s="7" t="inlineStr">
@@ -7514,9 +7490,10 @@
 (CLASS)</t>
         </is>
       </c>
-      <c r="N17" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
+      <c r="N17" s="8" t="inlineStr">
+        <is>
+          <t>Sonu
+(ENG)</t>
         </is>
       </c>
     </row>
@@ -7598,7 +7575,7 @@
       <c r="N18" s="7" t="inlineStr">
         <is>
           <t>Bheema
-(PHY)</t>
+(CHEM)</t>
         </is>
       </c>
     </row>
@@ -7610,63 +7587,63 @@
       <c r="C19" s="7" t="inlineStr">
         <is>
           <t>Sitha
+(EVS)</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>Sai Lakshmi
+(ENG)</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>Naga mani
+(G.K)</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>Tulasi
 (MATH)</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>Bhavani
-(EVS)</t>
-        </is>
-      </c>
-      <c r="E19" s="7" t="inlineStr">
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>Maha
+(GRAM)</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>Swathi
+(TEL)</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
         <is>
           <t>Maheswari
 (COMP)</t>
         </is>
       </c>
-      <c r="F19" s="7" t="inlineStr">
-        <is>
-          <t>Tulasi
+      <c r="J19" s="7" t="inlineStr">
+        <is>
+          <t>Sangeetha
 (MATH)</t>
         </is>
       </c>
-      <c r="G19" s="7" t="inlineStr">
-        <is>
-          <t>Maha
-(GRAM)</t>
-        </is>
-      </c>
-      <c r="H19" s="7" t="inlineStr">
+      <c r="K19" s="7" t="inlineStr">
         <is>
           <t>Lalitha
-(EVS)</t>
-        </is>
-      </c>
-      <c r="I19" s="7" t="inlineStr">
-        <is>
-          <t>Swathi
-(TEL)</t>
-        </is>
-      </c>
-      <c r="J19" s="7" t="inlineStr">
-        <is>
-          <t>Pallavi
-(SOC)</t>
-        </is>
-      </c>
-      <c r="K19" s="7" t="inlineStr">
+(PHY)</t>
+        </is>
+      </c>
+      <c r="L19" s="7" t="inlineStr">
         <is>
           <t>D.V.Rao
 (TEL)</t>
         </is>
       </c>
-      <c r="L19" s="7" t="inlineStr">
-        <is>
-          <t>Bheema
-(PHY)</t>
-        </is>
-      </c>
       <c r="M19" s="7" t="inlineStr">
         <is>
           <t>Gowtham
@@ -7675,8 +7652,8 @@
       </c>
       <c r="N19" s="7" t="inlineStr">
         <is>
-          <t>Sunitha
-(SOC)</t>
+          <t>Riya
+(HIN)</t>
         </is>
       </c>
     </row>
@@ -7687,62 +7664,62 @@
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>Sitha
-(MATH)</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
           <t>Naga mani
 (TEL)</t>
         </is>
       </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>Sai Lakshmi
+(ENG)</t>
+        </is>
+      </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>Sai Lakshmi
-(EVS)</t>
+          <t>Bhavani
+(MATH)</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>Tulasi
+(MATH)</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>Pallavi
+(SOC)</t>
+        </is>
+      </c>
+      <c r="H20" s="7" t="inlineStr">
         <is>
           <t>Maha
 (ENG)</t>
         </is>
       </c>
-      <c r="G20" s="7" t="inlineStr">
+      <c r="I20" s="7" t="inlineStr">
         <is>
           <t>Lalitha
 (EVS)</t>
         </is>
       </c>
-      <c r="H20" s="7" t="inlineStr">
-        <is>
-          <t>Swathi
-(TEL)</t>
-        </is>
-      </c>
-      <c r="I20" s="7" t="inlineStr">
-        <is>
-          <t>Fathima
-(HIN)</t>
-        </is>
-      </c>
       <c r="J20" s="7" t="inlineStr">
         <is>
+          <t>Maheswari
+(COMP)</t>
+        </is>
+      </c>
+      <c r="K20" s="7" t="inlineStr">
+        <is>
           <t>Ravi
-(GRAM)</t>
-        </is>
-      </c>
-      <c r="K20" s="7" t="inlineStr">
-        <is>
-          <t>Sangeetha
-(MATH)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="L20" s="7" t="inlineStr">
         <is>
-          <t>Bheema
-(CHEM)</t>
+          <t>Sunitha
+(SOC)</t>
         </is>
       </c>
       <c r="M20" s="7" t="inlineStr">
@@ -7765,22 +7742,22 @@
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>Naga mani
-(TEL)</t>
+          <t>Sitha
+(ENG)</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>Swathi
+(HIN)</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
         <is>
           <t>Bhavani
 (MATH)</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
-        <is>
-          <t>Sai Lakshmi
-(EVS)</t>
-        </is>
-      </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
           <t>Maheswari
@@ -7789,50 +7766,50 @@
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>Tulasi
-(MATH)</t>
+          <t>Lalitha
+(EVS)</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>Sangeetha
+(G.K)</t>
+        </is>
+      </c>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>Fathima
+(HIN)</t>
+        </is>
+      </c>
+      <c r="J21" s="7" t="inlineStr">
         <is>
           <t>Pallavi
 (SOC)</t>
         </is>
       </c>
-      <c r="I21" s="7" t="inlineStr">
-        <is>
-          <t>Lalitha
-(EVS)</t>
-        </is>
-      </c>
-      <c r="J21" s="7" t="inlineStr">
-        <is>
-          <t>Fathima
-(HIN)</t>
-        </is>
-      </c>
       <c r="K21" s="7" t="inlineStr">
         <is>
-          <t>Ravi
-(ENG)</t>
+          <t>D.V.Rao
+(TEL)</t>
         </is>
       </c>
       <c r="L21" s="7" t="inlineStr">
+        <is>
+          <t>Chalapathi
+(BIO)</t>
+        </is>
+      </c>
+      <c r="M21" s="7" t="inlineStr">
+        <is>
+          <t>Gowtham
+(MATH)</t>
+        </is>
+      </c>
+      <c r="N21" s="7" t="inlineStr">
         <is>
           <t>Sunitha
 (SOC)</t>
-        </is>
-      </c>
-      <c r="M21" s="7" t="inlineStr">
-        <is>
-          <t>Gowtham
-(MATH)</t>
-        </is>
-      </c>
-      <c r="N21" s="7" t="inlineStr">
-        <is>
-          <t>Riya
-(HIN)</t>
         </is>
       </c>
     </row>
@@ -7843,73 +7820,74 @@
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>Sitha
-(ENG)</t>
+          <t>P.E
+(P.E.T)</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
+          <t>P.E
+(P.E.T)</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
           <t>Sai Lakshmi
-(ENG)</t>
-        </is>
-      </c>
-      <c r="E22" s="7" t="inlineStr">
+(EVS)</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
         <is>
           <t>Maha
 (ENG)</t>
         </is>
       </c>
-      <c r="F22" s="7" t="inlineStr">
-        <is>
-          <t>Naga mani
-(TEL)</t>
-        </is>
-      </c>
       <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>P.E
+(P.E.T)</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="inlineStr">
         <is>
           <t>Pallavi
 (SOC)</t>
         </is>
       </c>
-      <c r="H22" s="7" t="inlineStr">
-        <is>
-          <t>P.E
-(P.E.T)</t>
-        </is>
-      </c>
       <c r="I22" s="7" t="inlineStr">
-        <is>
-          <t>Tulasi
-(MATH)</t>
-        </is>
-      </c>
-      <c r="J22" s="7" t="inlineStr">
         <is>
           <t>Swathi
 (TEL)</t>
         </is>
       </c>
+      <c r="J22" s="7" t="inlineStr">
+        <is>
+          <t>Ravi
+(ENG)</t>
+        </is>
+      </c>
       <c r="K22" s="7" t="inlineStr">
         <is>
+          <t>Fathima
+(HIN)</t>
+        </is>
+      </c>
+      <c r="L22" s="7" t="inlineStr">
+        <is>
           <t>Sangeetha
-(MATH)</t>
-        </is>
-      </c>
-      <c r="L22" s="7" t="inlineStr">
+(COMP)</t>
+        </is>
+      </c>
+      <c r="M22" s="7" t="inlineStr">
+        <is>
+          <t>Sonu
+(ENG)</t>
+        </is>
+      </c>
+      <c r="N22" s="7" t="inlineStr">
         <is>
           <t>D.V.Rao
 (TEL)</t>
-        </is>
-      </c>
-      <c r="M22" s="7" t="inlineStr">
-        <is>
-          <t>P.E
-(P.E.T)</t>
-        </is>
-      </c>
-      <c r="N22" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
         </is>
       </c>
     </row>
@@ -7926,8 +7904,8 @@
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>Bhavani
-(EVS)</t>
+          <t>Sai Lakshmi
+(ENG)</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
@@ -7938,22 +7916,22 @@
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
+          <t>Naga mani
+(TEL)</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
-        <is>
-          <t>P.E
-(P.E.T)</t>
-        </is>
-      </c>
-      <c r="H23" s="7" t="inlineStr">
         <is>
           <t>Maha
 (ENG)</t>
         </is>
       </c>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>Lalitha
+(EVS)</t>
+        </is>
+      </c>
       <c r="I23" s="7" t="inlineStr">
         <is>
           <t>Tulasi
@@ -7962,14 +7940,14 @@
       </c>
       <c r="J23" s="7" t="inlineStr">
         <is>
-          <t>Ravi
-(ENG)</t>
+          <t>Fathima
+(HIN)</t>
         </is>
       </c>
       <c r="K23" s="7" t="inlineStr">
         <is>
-          <t>Lalitha
-(BIO)</t>
+          <t>Sangeetha
+(MATH)</t>
         </is>
       </c>
       <c r="L23" s="7" t="inlineStr">
@@ -7978,10 +7956,9 @@
 (ENG)</t>
         </is>
       </c>
-      <c r="M23" s="7" t="inlineStr">
-        <is>
-          <t>D.V.Rao
-(TEL)</t>
+      <c r="M23" s="12" t="inlineStr">
+        <is>
+          <t>Recreation</t>
         </is>
       </c>
       <c r="N23" s="12" t="inlineStr">
@@ -7998,39 +7975,39 @@
       <c r="C24" s="7" t="inlineStr">
         <is>
           <t>Sitha
+(ENG)</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>Naga mani
+(TEL)</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>Maha
+(ENG)</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>Sai Lakshmi
+(EVS)</t>
+        </is>
+      </c>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>Tulasi
 (MATH)</t>
         </is>
       </c>
-      <c r="D24" s="7" t="inlineStr">
+      <c r="H24" s="7" t="inlineStr">
         <is>
           <t>P.E
 (P.E.T)</t>
         </is>
       </c>
-      <c r="E24" s="7" t="inlineStr">
-        <is>
-          <t>Bhavani
-(MATH)</t>
-        </is>
-      </c>
-      <c r="F24" s="7" t="inlineStr">
-        <is>
-          <t>Sai Lakshmi
-(EVS)</t>
-        </is>
-      </c>
-      <c r="G24" s="7" t="inlineStr">
-        <is>
-          <t>Maha
-(ENG)</t>
-        </is>
-      </c>
-      <c r="H24" s="7" t="inlineStr">
-        <is>
-          <t>Fathima
-(HIN)</t>
-        </is>
-      </c>
       <c r="I24" s="7" t="inlineStr">
         <is>
           <t>Pallavi
@@ -8039,32 +8016,31 @@
       </c>
       <c r="J24" s="7" t="inlineStr">
         <is>
+          <t>Swathi
+(TEL)</t>
+        </is>
+      </c>
+      <c r="K24" s="7" t="inlineStr">
+        <is>
           <t>Lalitha
-(PHY)</t>
-        </is>
-      </c>
-      <c r="K24" s="7" t="inlineStr">
-        <is>
-          <t>Sangeetha
-(MATH)</t>
+(BIO)</t>
         </is>
       </c>
       <c r="L24" s="7" t="inlineStr">
         <is>
-          <t>Chalapathi
-(BIO)</t>
+          <t>P.E
+(P.E.T)</t>
         </is>
       </c>
       <c r="M24" s="7" t="inlineStr">
-        <is>
-          <t>Sonu
-(ENG)</t>
-        </is>
-      </c>
-      <c r="N24" s="7" t="inlineStr">
         <is>
           <t>D.V.Rao
 (TEL)</t>
+        </is>
+      </c>
+      <c r="N24" s="12" t="inlineStr">
+        <is>
+          <t>Recreation</t>
         </is>
       </c>
     </row>
@@ -8160,19 +8136,19 @@
       <c r="C26" s="7" t="inlineStr">
         <is>
           <t>Sitha
-(ENG)</t>
+(ORAL)</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
           <t>Bhavani
-(MATH)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
           <t>Naga mani
-(G.K)</t>
+(TEL)</t>
         </is>
       </c>
       <c r="F26" s="7" t="inlineStr">
@@ -8189,8 +8165,8 @@
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>Lalitha
-(EVS)</t>
+          <t>Tulasi
+(MATH)</t>
         </is>
       </c>
       <c r="I26" s="7" t="inlineStr">
@@ -8201,8 +8177,8 @@
       </c>
       <c r="J26" s="7" t="inlineStr">
         <is>
-          <t>Sangeetha
-(G.K)</t>
+          <t>Lalitha
+(BIO)</t>
         </is>
       </c>
       <c r="K26" s="7" t="inlineStr">
@@ -8214,7 +8190,7 @@
       <c r="L26" s="7" t="inlineStr">
         <is>
           <t>Fathima
-(HIN)</t>
+(G.K)</t>
         </is>
       </c>
       <c r="M26" s="7" t="inlineStr">
@@ -8223,10 +8199,9 @@
 (SOC)</t>
         </is>
       </c>
-      <c r="N26" s="7" t="inlineStr">
-        <is>
-          <t>Bheema
-(CHEM)</t>
+      <c r="N26" s="12" t="inlineStr">
+        <is>
+          <t>Recreation</t>
         </is>
       </c>
     </row>
@@ -8238,45 +8213,45 @@
       <c r="C27" s="7" t="inlineStr">
         <is>
           <t>Sitha
+(EVS)</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>Naga mani
+(TEL)</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>Maha
 (ENG)</t>
         </is>
       </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>Bhavani
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>Maheswari
+(COMP)</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>Lalitha
 (EVS)</t>
         </is>
       </c>
-      <c r="E27" s="7" t="inlineStr">
-        <is>
-          <t>Sai Lakshmi
-(HIN)</t>
-        </is>
-      </c>
-      <c r="F27" s="7" t="inlineStr">
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>Swathi
+(TEL)</t>
+        </is>
+      </c>
+      <c r="I27" s="7" t="inlineStr">
         <is>
           <t>Tulasi
 (MATH)</t>
         </is>
       </c>
-      <c r="G27" s="7" t="inlineStr">
-        <is>
-          <t>Pallavi
-(SOC)</t>
-        </is>
-      </c>
-      <c r="H27" s="7" t="inlineStr">
-        <is>
-          <t>Maha
-(ENG)</t>
-        </is>
-      </c>
-      <c r="I27" s="7" t="inlineStr">
-        <is>
-          <t>Maheswari
-(COMP)</t>
-        </is>
-      </c>
       <c r="J27" s="7" t="inlineStr">
         <is>
           <t>Fathima
@@ -8291,20 +8266,20 @@
       </c>
       <c r="L27" s="7" t="inlineStr">
         <is>
-          <t>Sangeetha
-(MATH)</t>
+          <t>D.V.Rao
+(TEL)</t>
         </is>
       </c>
       <c r="M27" s="7" t="inlineStr">
-        <is>
-          <t>Gowtham
-(MATH)</t>
-        </is>
-      </c>
-      <c r="N27" s="7" t="inlineStr">
         <is>
           <t>Riya
 (HIN)</t>
+        </is>
+      </c>
+      <c r="N27" s="7" t="inlineStr">
+        <is>
+          <t>Sunitha
+(SOC)</t>
         </is>
       </c>
     </row>
@@ -8316,13 +8291,13 @@
       <c r="C28" s="7" t="inlineStr">
         <is>
           <t>Sitha
-(EVS)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>Naga mani
-(TEL)</t>
+          <t>Swathi
+(HIN)</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
@@ -8334,7 +8309,7 @@
       <c r="F28" s="7" t="inlineStr">
         <is>
           <t>Sai Lakshmi
-(HIN)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="G28" s="7" t="inlineStr">
@@ -8345,44 +8320,44 @@
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>Tulasi
+          <t>Pallavi
+(SOC)</t>
+        </is>
+      </c>
+      <c r="I28" s="7" t="inlineStr">
+        <is>
+          <t>Fathima
+(HIN)</t>
+        </is>
+      </c>
+      <c r="J28" s="7" t="inlineStr">
+        <is>
+          <t>Ravi
+(GRAM)</t>
+        </is>
+      </c>
+      <c r="K28" s="7" t="inlineStr">
+        <is>
+          <t>Sangeetha
 (MATH)</t>
         </is>
       </c>
-      <c r="I28" s="7" t="inlineStr">
-        <is>
-          <t>Swathi
-(TEL)</t>
-        </is>
-      </c>
-      <c r="J28" s="7" t="inlineStr">
-        <is>
-          <t>Ravi
-(ENG)</t>
-        </is>
-      </c>
-      <c r="K28" s="7" t="inlineStr">
-        <is>
-          <t>Lalitha
+      <c r="L28" s="7" t="inlineStr">
+        <is>
+          <t>Bheema
 (PHY)</t>
         </is>
       </c>
-      <c r="L28" s="7" t="inlineStr">
+      <c r="M28" s="7" t="inlineStr">
+        <is>
+          <t>Gowtham
+(MATH)</t>
+        </is>
+      </c>
+      <c r="N28" s="7" t="inlineStr">
         <is>
           <t>D.V.Rao
 (TEL)</t>
-        </is>
-      </c>
-      <c r="M28" s="7" t="inlineStr">
-        <is>
-          <t>Bheema
-(CHEM)</t>
-        </is>
-      </c>
-      <c r="N28" s="7" t="inlineStr">
-        <is>
-          <t>Sunitha
-(SOC)</t>
         </is>
       </c>
     </row>
@@ -8399,50 +8374,50 @@
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>Swathi
-(HIN)</t>
+          <t>Bhavani
+(EVS)</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>Sai Lakshmi
+(EVS)</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>Tulasi
+(MATH)</t>
+        </is>
+      </c>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>Pallavi
+(SOC)</t>
+        </is>
+      </c>
+      <c r="H29" s="7" t="inlineStr">
         <is>
           <t>Maha
 (ENG)</t>
         </is>
       </c>
-      <c r="F29" s="7" t="inlineStr">
-        <is>
-          <t>Tulasi
-(MATH)</t>
-        </is>
-      </c>
-      <c r="G29" s="7" t="inlineStr">
+      <c r="I29" s="7" t="inlineStr">
         <is>
           <t>Lalitha
 (EVS)</t>
         </is>
       </c>
-      <c r="H29" s="7" t="inlineStr">
-        <is>
-          <t>Fathima
-(HIN)</t>
-        </is>
-      </c>
-      <c r="I29" s="7" t="inlineStr">
-        <is>
-          <t>Pallavi
-(SOC)</t>
-        </is>
-      </c>
       <c r="J29" s="7" t="inlineStr">
         <is>
-          <t>Maheswari
-(COMP)</t>
+          <t>Ravi
+(ENG)</t>
         </is>
       </c>
       <c r="K29" s="7" t="inlineStr">
         <is>
-          <t>D.V.Rao
-(TEL)</t>
+          <t>Sangeetha
+(MATH)</t>
         </is>
       </c>
       <c r="L29" s="7" t="inlineStr">
@@ -8453,14 +8428,14 @@
       </c>
       <c r="M29" s="7" t="inlineStr">
         <is>
-          <t>Bheema
-(PHY)</t>
-        </is>
-      </c>
-      <c r="N29" s="7" t="inlineStr">
-        <is>
           <t>Gowtham
 (MATH)</t>
+        </is>
+      </c>
+      <c r="N29" s="7" t="inlineStr">
+        <is>
+          <t>Riya
+(HIN)</t>
         </is>
       </c>
     </row>
@@ -8472,13 +8447,13 @@
       <c r="C30" s="7" t="inlineStr">
         <is>
           <t>Sitha
-(EVS)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>Sai Lakshmi
-(ENG)</t>
+          <t>Bhavani
+(MATH)</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
@@ -8501,16 +8476,16 @@
       </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
+          <t>Lalitha
+(EVS)</t>
+        </is>
+      </c>
+      <c r="I30" s="7" t="inlineStr">
+        <is>
           <t>Pallavi
 (SOC)</t>
         </is>
       </c>
-      <c r="I30" s="7" t="inlineStr">
-        <is>
-          <t>Fathima
-(HIN)</t>
-        </is>
-      </c>
       <c r="J30" s="7" t="inlineStr">
         <is>
           <t>Swathi
@@ -8519,26 +8494,25 @@
       </c>
       <c r="K30" s="7" t="inlineStr">
         <is>
-          <t>Lalitha
-(CHEM)</t>
+          <t>D.V.Rao
+(TEL)</t>
         </is>
       </c>
       <c r="L30" s="7" t="inlineStr">
+        <is>
+          <t>Sangeetha
+(MATH)</t>
+        </is>
+      </c>
+      <c r="M30" s="7" t="inlineStr">
         <is>
           <t>Sonu
 (ENG)</t>
         </is>
       </c>
-      <c r="M30" s="7" t="inlineStr">
-        <is>
-          <t>Riya
-(HIN)</t>
-        </is>
-      </c>
-      <c r="N30" s="7" t="inlineStr">
-        <is>
-          <t>Ravi
-(GRAM)</t>
+      <c r="N30" s="12" t="inlineStr">
+        <is>
+          <t>Recreation</t>
         </is>
       </c>
     </row>
@@ -8550,7 +8524,7 @@
       <c r="C31" s="7" t="inlineStr">
         <is>
           <t>Sitha
-(ENG)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
@@ -8609,14 +8583,14 @@
       </c>
       <c r="M31" s="7" t="inlineStr">
         <is>
-          <t>Sonu
-(ENG)</t>
+          <t>Martial Arts
+(KAR)</t>
         </is>
       </c>
       <c r="N31" s="7" t="inlineStr">
         <is>
-          <t>D.V.Rao
-(TEL)</t>
+          <t>Martial Arts
+(KAR)</t>
         </is>
       </c>
     </row>
@@ -8633,14 +8607,14 @@
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
+          <t>P.E
+(P.E.T)</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
           <t>Sai Lakshmi
-(ENG)</t>
-        </is>
-      </c>
-      <c r="E32" s="7" t="inlineStr">
-        <is>
-          <t>Naga mani
-(TEL)</t>
+(HIN)</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
@@ -8657,16 +8631,16 @@
       </c>
       <c r="H32" s="7" t="inlineStr">
         <is>
+          <t>Fathima
+(HIN)</t>
+        </is>
+      </c>
+      <c r="I32" s="7" t="inlineStr">
+        <is>
           <t>Swathi
 (TEL)</t>
         </is>
       </c>
-      <c r="I32" s="7" t="inlineStr">
-        <is>
-          <t>Lalitha
-(EVS)</t>
-        </is>
-      </c>
       <c r="J32" s="7" t="inlineStr">
         <is>
           <t>Pallavi
@@ -8675,14 +8649,14 @@
       </c>
       <c r="K32" s="7" t="inlineStr">
         <is>
-          <t>Fathima
-(HIN)</t>
+          <t>Lalitha
+(BIO)</t>
         </is>
       </c>
       <c r="L32" s="7" t="inlineStr">
         <is>
-          <t>Sangeetha
-(MATH)</t>
+          <t>Sonu
+(ENG)</t>
         </is>
       </c>
       <c r="M32" s="7" t="inlineStr">
@@ -8790,7 +8764,7 @@
       <c r="C34" s="7" t="inlineStr">
         <is>
           <t>Sitha
-(MATH)</t>
+(ORAL)</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
@@ -8802,13 +8776,13 @@
       <c r="E34" s="7" t="inlineStr">
         <is>
           <t>Naga mani
-(G.K)</t>
+(TEL)</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
           <t>Sai Lakshmi
-(EVS)</t>
+(HIN)</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
@@ -8819,20 +8793,20 @@
       </c>
       <c r="H34" s="7" t="inlineStr">
         <is>
-          <t>Lalitha
-(EVS)</t>
+          <t>Tulasi
+(MATH)</t>
         </is>
       </c>
       <c r="I34" s="7" t="inlineStr">
         <is>
           <t>Maha
-(GRAM)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="J34" s="7" t="inlineStr">
         <is>
           <t>Sangeetha
-(MATH)</t>
+(G.K)</t>
         </is>
       </c>
       <c r="K34" s="7" t="inlineStr">
@@ -8849,14 +8823,14 @@
       </c>
       <c r="M34" s="7" t="inlineStr">
         <is>
+          <t>Bheema
+(CHEM)</t>
+        </is>
+      </c>
+      <c r="N34" s="7" t="inlineStr">
+        <is>
           <t>Riya
 (HIN)</t>
-        </is>
-      </c>
-      <c r="N34" s="7" t="inlineStr">
-        <is>
-          <t>Sunitha
-(SOC)</t>
         </is>
       </c>
     </row>
@@ -8867,34 +8841,34 @@
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>Naga mani
-(TEL)</t>
+          <t>Sitha
+(EVS)</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
+          <t>Bhavani
+(EVS)</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
           <t>Sai Lakshmi
-(ENG)</t>
-        </is>
-      </c>
-      <c r="E35" s="7" t="inlineStr">
+(HIN)</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>Tulasi
+(MATH)</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="inlineStr">
         <is>
           <t>Maha
 (ENG)</t>
         </is>
       </c>
-      <c r="F35" s="7" t="inlineStr">
-        <is>
-          <t>Tulasi
-(MATH)</t>
-        </is>
-      </c>
-      <c r="G35" s="7" t="inlineStr">
-        <is>
-          <t>Riya
-(HIN)</t>
-        </is>
-      </c>
       <c r="H35" s="7" t="inlineStr">
         <is>
           <t>Swathi
@@ -8909,32 +8883,32 @@
       </c>
       <c r="J35" s="7" t="inlineStr">
         <is>
-          <t>Pallavi
-(SOC)</t>
+          <t>Ravi
+(ENG)</t>
         </is>
       </c>
       <c r="K35" s="7" t="inlineStr">
+        <is>
+          <t>Fathima
+(HIN)</t>
+        </is>
+      </c>
+      <c r="L35" s="7" t="inlineStr">
         <is>
           <t>D.V.Rao
 (TEL)</t>
         </is>
       </c>
-      <c r="L35" s="7" t="inlineStr">
-        <is>
-          <t>Bheema
-(CHEM)</t>
-        </is>
-      </c>
       <c r="M35" s="7" t="inlineStr">
+        <is>
+          <t>Gowtham
+(MATH)</t>
+        </is>
+      </c>
+      <c r="N35" s="7" t="inlineStr">
         <is>
           <t>Sunitha
 (SOC)</t>
-        </is>
-      </c>
-      <c r="N35" s="7" t="inlineStr">
-        <is>
-          <t>Gowtham
-(MATH)</t>
         </is>
       </c>
     </row>
@@ -8957,62 +8931,62 @@
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>Bhavani
-(MATH)</t>
-        </is>
-      </c>
-      <c r="F36" s="7" t="inlineStr">
-        <is>
           <t>Maha
 (ENG)</t>
         </is>
       </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>Naga mani
+(TEL)</t>
+        </is>
+      </c>
       <c r="G36" s="7" t="inlineStr">
+        <is>
+          <t>Pallavi
+(SOC)</t>
+        </is>
+      </c>
+      <c r="H36" s="7" t="inlineStr">
         <is>
           <t>Lalitha
 (EVS)</t>
         </is>
       </c>
-      <c r="H36" s="7" t="inlineStr">
+      <c r="I36" s="7" t="inlineStr">
+        <is>
+          <t>Swathi
+(TEL)</t>
+        </is>
+      </c>
+      <c r="J36" s="7" t="inlineStr">
         <is>
           <t>Sangeetha
-(G.K)</t>
-        </is>
-      </c>
-      <c r="I36" s="7" t="inlineStr">
-        <is>
-          <t>Tulasi
 (MATH)</t>
         </is>
       </c>
-      <c r="J36" s="7" t="inlineStr">
-        <is>
-          <t>Ravi
-(ENG)</t>
-        </is>
-      </c>
       <c r="K36" s="7" t="inlineStr">
-        <is>
-          <t>Fathima
-(HIN)</t>
-        </is>
-      </c>
-      <c r="L36" s="7" t="inlineStr">
         <is>
           <t>D.V.Rao
 (TEL)</t>
         </is>
       </c>
+      <c r="L36" s="7" t="inlineStr">
+        <is>
+          <t>Sunitha
+(SOC)</t>
+        </is>
+      </c>
       <c r="M36" s="7" t="inlineStr">
+        <is>
+          <t>Riya
+(HIN)</t>
+        </is>
+      </c>
+      <c r="N36" s="7" t="inlineStr">
         <is>
           <t>Gowtham
 (MATH)</t>
-        </is>
-      </c>
-      <c r="N36" s="7" t="inlineStr">
-        <is>
-          <t>Bheema
-(PHY)</t>
         </is>
       </c>
     </row>
@@ -9023,34 +8997,34 @@
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>Sitha
-(MATH)</t>
+          <t>Naga mani
+(TEL)</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
-        <is>
-          <t>Swathi
-(HIN)</t>
-        </is>
-      </c>
-      <c r="E37" s="7" t="inlineStr">
         <is>
           <t>Bhavani
 (MATH)</t>
         </is>
       </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>Maheswari
+(COMP)</t>
+        </is>
+      </c>
       <c r="F37" s="7" t="inlineStr">
-        <is>
-          <t>Naga mani
-(TEL)</t>
-        </is>
-      </c>
-      <c r="G37" s="7" t="inlineStr">
         <is>
           <t>Tulasi
 (MATH)</t>
         </is>
       </c>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>Riya
+(HIN)</t>
+        </is>
+      </c>
       <c r="H37" s="7" t="inlineStr">
         <is>
           <t>Fathima
@@ -9059,38 +9033,38 @@
       </c>
       <c r="I37" s="7" t="inlineStr">
         <is>
-          <t>Pallavi
-(SOC)</t>
+          <t>Sangeetha
+(G.K)</t>
         </is>
       </c>
       <c r="J37" s="7" t="inlineStr">
         <is>
-          <t>Sangeetha
-(MATH)</t>
+          <t>Lalitha
+(PHY)</t>
         </is>
       </c>
       <c r="K37" s="7" t="inlineStr">
         <is>
           <t>Ravi
-(ENG)</t>
+(GRAM)</t>
         </is>
       </c>
       <c r="L37" s="7" t="inlineStr">
+        <is>
+          <t>Bheema
+(CHEM)</t>
+        </is>
+      </c>
+      <c r="M37" s="7" t="inlineStr">
         <is>
           <t>Sunitha
 (SOC)</t>
         </is>
       </c>
-      <c r="M37" s="7" t="inlineStr">
-        <is>
-          <t>Bheema
-(PHY)</t>
-        </is>
-      </c>
       <c r="N37" s="7" t="inlineStr">
         <is>
-          <t>Riya
-(HIN)</t>
+          <t>Gowtham
+(MATH)</t>
         </is>
       </c>
     </row>
@@ -9102,55 +9076,55 @@
       <c r="C38" s="7" t="inlineStr">
         <is>
           <t>Sitha
-(MATH)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
-        <is>
-          <t>Bhavani
-(MATH)</t>
-        </is>
-      </c>
-      <c r="E38" s="7" t="inlineStr">
         <is>
           <t>Naga mani
 (TEL)</t>
         </is>
       </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>Sai Lakshmi
+(EVS)</t>
+        </is>
+      </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>Sai Lakshmi
-(HIN)</t>
+          <t>P.E
+(P.E.T)</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
+          <t>Tulasi
+(MATH)</t>
+        </is>
+      </c>
+      <c r="H38" s="7" t="inlineStr">
+        <is>
           <t>Maha
-(ENG)</t>
-        </is>
-      </c>
-      <c r="H38" s="7" t="inlineStr">
+(GRAM)</t>
+        </is>
+      </c>
+      <c r="I38" s="7" t="inlineStr">
         <is>
           <t>Pallavi
 (SOC)</t>
         </is>
       </c>
-      <c r="I38" s="7" t="inlineStr">
+      <c r="J38" s="7" t="inlineStr">
         <is>
           <t>Swathi
 (TEL)</t>
         </is>
       </c>
-      <c r="J38" s="7" t="inlineStr">
-        <is>
-          <t>Lalitha
-(CHEM)</t>
-        </is>
-      </c>
       <c r="K38" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
+          <t>Fathima
+(G.K)</t>
         </is>
       </c>
       <c r="L38" s="7" t="inlineStr">
@@ -9161,14 +9135,14 @@
       </c>
       <c r="M38" s="7" t="inlineStr">
         <is>
+          <t>Chalapathi
+(BIO)</t>
+        </is>
+      </c>
+      <c r="N38" s="7" t="inlineStr">
+        <is>
           <t>D.V.Rao
 (TEL)</t>
-        </is>
-      </c>
-      <c r="N38" s="7" t="inlineStr">
-        <is>
-          <t>Chalapathi
-(BIO)</t>
         </is>
       </c>
     </row>
@@ -9179,56 +9153,56 @@
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
+          <t>Sitha
+(MATH)</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>Bhavani
+(MATH)</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
           <t>P.E
 (P.E.T)</t>
         </is>
       </c>
-      <c r="D39" s="7" t="inlineStr">
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>Sai Lakshmi
+(EVS)</t>
+        </is>
+      </c>
+      <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t>Lalitha
+(EVS)</t>
+        </is>
+      </c>
+      <c r="H39" s="7" t="inlineStr">
+        <is>
+          <t>Maha
+(ENG)</t>
+        </is>
+      </c>
+      <c r="I39" s="7" t="inlineStr">
         <is>
           <t>P.E
 (P.E.T)</t>
         </is>
       </c>
-      <c r="E39" s="7" t="inlineStr">
-        <is>
-          <t>Sai Lakshmi
-(HIN)</t>
-        </is>
-      </c>
-      <c r="F39" s="7" t="inlineStr">
-        <is>
-          <t>P.E
-(P.E.T)</t>
-        </is>
-      </c>
-      <c r="G39" s="7" t="inlineStr">
+      <c r="J39" s="7" t="inlineStr">
         <is>
           <t>Pallavi
 (SOC)</t>
         </is>
       </c>
-      <c r="H39" s="7" t="inlineStr">
-        <is>
-          <t>Maha
+      <c r="K39" s="7" t="inlineStr">
+        <is>
+          <t>Ravi
 (ENG)</t>
-        </is>
-      </c>
-      <c r="I39" s="7" t="inlineStr">
-        <is>
-          <t>Tulasi
-(MATH)</t>
-        </is>
-      </c>
-      <c r="J39" s="7" t="inlineStr">
-        <is>
-          <t>Swathi
-(TEL)</t>
-        </is>
-      </c>
-      <c r="K39" s="7" t="inlineStr">
-        <is>
-          <t>Lalitha
-(BIO)</t>
         </is>
       </c>
       <c r="L39" s="7" t="inlineStr">
@@ -9243,10 +9217,9 @@
 (ENG)</t>
         </is>
       </c>
-      <c r="N39" s="7" t="inlineStr">
-        <is>
-          <t>D.V.Rao
-(TEL)</t>
+      <c r="N39" s="12" t="inlineStr">
+        <is>
+          <t>Recreation</t>
         </is>
       </c>
     </row>
@@ -9258,13 +9231,13 @@
       <c r="C40" s="7" t="inlineStr">
         <is>
           <t>Sitha
-(ENG)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>Naga mani
-(TEL)</t>
+          <t>Bhavani
+(MATH)</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
@@ -9275,8 +9248,8 @@
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
-          <t>Bhavani
-(G.K)</t>
+          <t>Maha
+(ENG)</t>
         </is>
       </c>
       <c r="G40" s="7" t="inlineStr">
@@ -9287,26 +9260,26 @@
       </c>
       <c r="H40" s="7" t="inlineStr">
         <is>
-          <t>Maheswari
-(COMP)</t>
+          <t>Pallavi
+(SOC)</t>
         </is>
       </c>
       <c r="I40" s="7" t="inlineStr">
-        <is>
-          <t>Maha
-(ENG)</t>
-        </is>
-      </c>
-      <c r="J40" s="7" t="inlineStr">
         <is>
           <t>Fathima
 (HIN)</t>
         </is>
       </c>
+      <c r="J40" s="7" t="inlineStr">
+        <is>
+          <t>Lalitha
+(CHEM)</t>
+        </is>
+      </c>
       <c r="K40" s="7" t="inlineStr">
         <is>
-          <t>Lalitha
-(PHY)</t>
+          <t>P.E
+(P.E.T)</t>
         </is>
       </c>
       <c r="L40" s="7" t="inlineStr">
@@ -9317,8 +9290,8 @@
       </c>
       <c r="M40" s="7" t="inlineStr">
         <is>
-          <t>Chalapathi
-(BIO)</t>
+          <t>D.V.Rao
+(TEL)</t>
         </is>
       </c>
       <c r="N40" s="12" t="inlineStr">
@@ -9419,31 +9392,31 @@
       <c r="C42" s="7" t="inlineStr">
         <is>
           <t>Sitha
-(ORAL)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
           <t>Bhavani
-(MATH)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
           <t>Naga mani
-(TEL)</t>
+(G.K)</t>
         </is>
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
           <t>Sai Lakshmi
+(HIN)</t>
+        </is>
+      </c>
+      <c r="G42" s="7" t="inlineStr">
+        <is>
+          <t>Lalitha
 (EVS)</t>
-        </is>
-      </c>
-      <c r="G42" s="7" t="inlineStr">
-        <is>
-          <t>Swathi
-(TEL)</t>
         </is>
       </c>
       <c r="H42" s="7" t="inlineStr">
@@ -9478,14 +9451,14 @@
       </c>
       <c r="M42" s="7" t="inlineStr">
         <is>
+          <t>D.V.Rao
+(TEL)</t>
+        </is>
+      </c>
+      <c r="N42" s="7" t="inlineStr">
+        <is>
           <t>Sunitha
 (SOC)</t>
-        </is>
-      </c>
-      <c r="N42" s="7" t="inlineStr">
-        <is>
-          <t>Bheema
-(PHY)</t>
         </is>
       </c>
     </row>
@@ -9497,25 +9470,25 @@
       <c r="C43" s="7" t="inlineStr">
         <is>
           <t>Sitha
-(EVS)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
+          <t>Sai Lakshmi
+(ENG)</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>Naga mani
+(TEL)</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
           <t>Bhavani
-(EVS)</t>
-        </is>
-      </c>
-      <c r="E43" s="7" t="inlineStr">
-        <is>
-          <t>Sai Lakshmi
-(EVS)</t>
-        </is>
-      </c>
-      <c r="F43" s="7" t="inlineStr">
-        <is>
-          <t>Maheswari
-(COMP)</t>
+(G.K)</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
@@ -9526,8 +9499,8 @@
       </c>
       <c r="H43" s="7" t="inlineStr">
         <is>
-          <t>Pallavi
-(SOC)</t>
+          <t>Swathi
+(TEL)</t>
         </is>
       </c>
       <c r="I43" s="7" t="inlineStr">
@@ -9538,26 +9511,26 @@
       </c>
       <c r="J43" s="7" t="inlineStr">
         <is>
-          <t>Swathi
-(TEL)</t>
+          <t>Sangeetha
+(MATH)</t>
         </is>
       </c>
       <c r="K43" s="7" t="inlineStr">
         <is>
-          <t>Sangeetha
-(COMP)</t>
+          <t>Ravi
+(ENG)</t>
         </is>
       </c>
       <c r="L43" s="7" t="inlineStr">
         <is>
-          <t>D.V.Rao
-(TEL)</t>
+          <t>Bheema
+(PHY)</t>
         </is>
       </c>
       <c r="M43" s="7" t="inlineStr">
         <is>
-          <t>Riya
-(HIN)</t>
+          <t>Sunitha
+(SOC)</t>
         </is>
       </c>
       <c r="N43" s="7" t="inlineStr">
@@ -9574,20 +9547,20 @@
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>Naga mani
-(TEL)</t>
+          <t>Sitha
+(ENG)</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
+          <t>Swathi
+(HIN)</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
           <t>Sai Lakshmi
-(ENG)</t>
-        </is>
-      </c>
-      <c r="E44" s="7" t="inlineStr">
-        <is>
-          <t>Bhavani
-(MATH)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="F44" s="7" t="inlineStr">
@@ -9604,26 +9577,26 @@
       </c>
       <c r="H44" s="7" t="inlineStr">
         <is>
-          <t>Lalitha
-(EVS)</t>
-        </is>
-      </c>
-      <c r="I44" s="7" t="inlineStr">
-        <is>
-          <t>Sangeetha
-(G.K)</t>
-        </is>
-      </c>
-      <c r="J44" s="7" t="inlineStr">
-        <is>
           <t>Pallavi
 (SOC)</t>
         </is>
       </c>
+      <c r="I44" s="7" t="inlineStr">
+        <is>
+          <t>Fathima
+(HIN)</t>
+        </is>
+      </c>
+      <c r="J44" s="7" t="inlineStr">
+        <is>
+          <t>Lalitha
+(BIO)</t>
+        </is>
+      </c>
       <c r="K44" s="7" t="inlineStr">
         <is>
-          <t>Ravi
-(ENG)</t>
+          <t>D.V.Rao
+(TEL)</t>
         </is>
       </c>
       <c r="L44" s="7" t="inlineStr">
@@ -9634,8 +9607,8 @@
       </c>
       <c r="M44" s="7" t="inlineStr">
         <is>
-          <t>Bheema
-(CHEM)</t>
+          <t>Gowtham
+(MATH)</t>
         </is>
       </c>
       <c r="N44" s="7" t="inlineStr">
@@ -9652,14 +9625,14 @@
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>Sitha
-(ENG)</t>
+          <t>Naga mani
+(TEL)</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>Swathi
-(HIN)</t>
+          <t>Bhavani
+(EVS)</t>
         </is>
       </c>
       <c r="E45" s="7" t="inlineStr">
@@ -9670,8 +9643,8 @@
       </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
-          <t>Naga mani
-(TEL)</t>
+          <t>Tulasi
+(MATH)</t>
         </is>
       </c>
       <c r="G45" s="7" t="inlineStr">
@@ -9682,16 +9655,16 @@
       </c>
       <c r="H45" s="7" t="inlineStr">
         <is>
-          <t>Tulasi
-(MATH)</t>
-        </is>
-      </c>
-      <c r="I45" s="7" t="inlineStr">
-        <is>
           <t>Fathima
 (HIN)</t>
         </is>
       </c>
+      <c r="I45" s="7" t="inlineStr">
+        <is>
+          <t>Pallavi
+(SOC)</t>
+        </is>
+      </c>
       <c r="J45" s="7" t="inlineStr">
         <is>
           <t>Ravi
@@ -9700,26 +9673,26 @@
       </c>
       <c r="K45" s="7" t="inlineStr">
         <is>
+          <t>Sangeetha
+(MATH)</t>
+        </is>
+      </c>
+      <c r="L45" s="7" t="inlineStr">
+        <is>
           <t>D.V.Rao
 (TEL)</t>
         </is>
       </c>
-      <c r="L45" s="7" t="inlineStr">
+      <c r="M45" s="7" t="inlineStr">
         <is>
           <t>Bheema
-(PHY)</t>
-        </is>
-      </c>
-      <c r="M45" s="7" t="inlineStr">
+(CHEM)</t>
+        </is>
+      </c>
+      <c r="N45" s="7" t="inlineStr">
         <is>
           <t>Gowtham
 (MATH)</t>
-        </is>
-      </c>
-      <c r="N45" s="7" t="inlineStr">
-        <is>
-          <t>Sunitha
-(SOC)</t>
         </is>
       </c>
     </row>
@@ -9730,8 +9703,8 @@
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
+          <t>Sitha
+(EVS)</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
@@ -9742,20 +9715,20 @@
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
-        </is>
-      </c>
-      <c r="F46" s="7" t="inlineStr">
-        <is>
           <t>Sai Lakshmi
 (HIN)</t>
         </is>
       </c>
+      <c r="F46" s="7" t="inlineStr">
+        <is>
+          <t>Naga mani
+(TEL)</t>
+        </is>
+      </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
+          <t>Swathi
+(TEL)</t>
         </is>
       </c>
       <c r="H46" s="7" t="inlineStr">
@@ -9766,26 +9739,26 @@
       </c>
       <c r="I46" s="7" t="inlineStr">
         <is>
-          <t>Pallavi
-(SOC)</t>
+          <t>Tulasi
+(MATH)</t>
         </is>
       </c>
       <c r="J46" s="7" t="inlineStr">
         <is>
+          <t>Fathima
+(HIN)</t>
+        </is>
+      </c>
+      <c r="K46" s="7" t="inlineStr">
+        <is>
           <t>Lalitha
-(BIO)</t>
-        </is>
-      </c>
-      <c r="K46" s="7" t="inlineStr">
-        <is>
-          <t>Fathima
-(G.K)</t>
+(CHEM)</t>
         </is>
       </c>
       <c r="L46" s="7" t="inlineStr">
         <is>
-          <t>Sangeetha
-(MATH)</t>
+          <t>Ravi
+(GRAM)</t>
         </is>
       </c>
       <c r="M46" s="7" t="inlineStr">
@@ -9808,37 +9781,37 @@
       <c r="C47" s="7" t="inlineStr">
         <is>
           <t>Sitha
+(MATH)</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>Bhavani
+(MATH)</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>Maha
 (ENG)</t>
         </is>
       </c>
-      <c r="D47" s="7" t="inlineStr">
-        <is>
-          <t>Naga mani
-(TEL)</t>
-        </is>
-      </c>
-      <c r="E47" s="7" t="inlineStr">
+      <c r="F47" s="7" t="inlineStr">
         <is>
           <t>Sai Lakshmi
-(HIN)</t>
-        </is>
-      </c>
-      <c r="F47" s="7" t="inlineStr">
+(EVS)</t>
+        </is>
+      </c>
+      <c r="G47" s="7" t="inlineStr">
         <is>
           <t>P.E
 (P.E.T)</t>
         </is>
       </c>
-      <c r="G47" s="7" t="inlineStr">
-        <is>
-          <t>Lalitha
-(EVS)</t>
-        </is>
-      </c>
       <c r="H47" s="7" t="inlineStr">
         <is>
-          <t>Maha
-(GRAM)</t>
+          <t>P.E
+(P.E.T)</t>
         </is>
       </c>
       <c r="I47" s="7" t="inlineStr">
@@ -9849,26 +9822,25 @@
       </c>
       <c r="J47" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
+          <t>Pallavi
+(SOC)</t>
         </is>
       </c>
       <c r="K47" s="7" t="inlineStr">
         <is>
-          <t>Sangeetha
-(MATH)</t>
+          <t>Lalitha
+(PHY)</t>
         </is>
       </c>
       <c r="L47" s="7" t="inlineStr">
-        <is>
-          <t>P.E
-(P.E.T)</t>
-        </is>
-      </c>
-      <c r="M47" s="7" t="inlineStr">
         <is>
           <t>Sonu
 (ENG)</t>
+        </is>
+      </c>
+      <c r="M47" s="12" t="inlineStr">
+        <is>
+          <t>Recreation</t>
         </is>
       </c>
       <c r="N47" s="7" t="inlineStr">
@@ -9886,27 +9858,27 @@
       <c r="C48" s="7" t="inlineStr">
         <is>
           <t>Sitha
-(ENG)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>Bhavani
-(EVS)</t>
+          <t>Naga mani
+(TEL)</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
-        <is>
-          <t>Maha
-(ENG)</t>
-        </is>
-      </c>
-      <c r="F48" s="7" t="inlineStr">
         <is>
           <t>Sai Lakshmi
 (EVS)</t>
         </is>
       </c>
+      <c r="F48" s="7" t="inlineStr">
+        <is>
+          <t>P.E
+(P.E.T)</t>
+        </is>
+      </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
           <t>Pallavi
@@ -9915,22 +9887,22 @@
       </c>
       <c r="H48" s="7" t="inlineStr">
         <is>
+          <t>Lalitha
+(EVS)</t>
+        </is>
+      </c>
+      <c r="I48" s="7" t="inlineStr">
+        <is>
+          <t>Maha
+(GRAM)</t>
+        </is>
+      </c>
+      <c r="J48" s="7" t="inlineStr">
+        <is>
           <t>Swathi
 (TEL)</t>
         </is>
       </c>
-      <c r="I48" s="7" t="inlineStr">
-        <is>
-          <t>Tulasi
-(MATH)</t>
-        </is>
-      </c>
-      <c r="J48" s="7" t="inlineStr">
-        <is>
-          <t>Lalitha
-(PHY)</t>
-        </is>
-      </c>
       <c r="K48" s="7" t="inlineStr">
         <is>
           <t>Fathima
@@ -9939,14 +9911,14 @@
       </c>
       <c r="L48" s="7" t="inlineStr">
         <is>
+          <t>Sangeetha
+(MATH)</t>
+        </is>
+      </c>
+      <c r="M48" s="7" t="inlineStr">
+        <is>
           <t>Sonu
 (ENG)</t>
-        </is>
-      </c>
-      <c r="M48" s="7" t="inlineStr">
-        <is>
-          <t>D.V.Rao
-(TEL)</t>
         </is>
       </c>
       <c r="N48" s="7" t="inlineStr">

--- a/NRCS/Output/NRCS_Timetable_Final.xlsx
+++ b/NRCS/Output/NRCS_Timetable_Final.xlsx
@@ -656,27 +656,23 @@
           <t>U.K.G (EVS)</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr"/>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>Class 1 (MATH)</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
         <is>
           <t>U.K.G (EVS)</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr"/>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (G.K)</t>
-        </is>
-      </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
           <t>U.K.G (EVS)</t>
         </is>
       </c>
-      <c r="G5" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (EVS)</t>
-        </is>
-      </c>
+      <c r="G5" s="7" t="inlineStr"/>
       <c r="H5" s="7" t="inlineStr"/>
       <c r="I5" s="8" t="inlineStr">
         <is>
@@ -692,27 +688,27 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>U.K.G (MATH)</t>
+          <t>U.K.G (EVS)</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr"/>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>U.K.G (MATH)</t>
+          <t>U.K.G (EVS)</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
+          <t>Class 1 (MATH)</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr"/>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
           <t>U.K.G (EVS)</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr"/>
-      <c r="G6" s="7" t="inlineStr"/>
-      <c r="H6" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (MATH)</t>
-        </is>
-      </c>
+      <c r="H6" s="7" t="inlineStr"/>
       <c r="I6" s="8" t="inlineStr">
         <is>
           <t>U.K.G</t>
@@ -732,22 +728,26 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
+          <t>Class 1 (MATH)</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>Class 1 (MATH)</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr"/>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
           <t>U.K.G (EVS)</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr"/>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="G7" s="7" t="inlineStr"/>
+      <c r="H7" s="7" t="inlineStr">
         <is>
           <t>U.K.G (MATH)</t>
         </is>
       </c>
-      <c r="F7" s="7" t="inlineStr"/>
-      <c r="G7" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (EVS)</t>
-        </is>
-      </c>
-      <c r="H7" s="7" t="inlineStr"/>
       <c r="I7" s="8" t="inlineStr">
         <is>
           <t>U.K.G</t>
@@ -765,22 +765,18 @@
           <t>U.K.G (MATH)</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr"/>
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>U.K.G (MATH)</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr"/>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>Class 1 (MATH)</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (MATH)</t>
-        </is>
-      </c>
+          <t>U.K.G (MATH)</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr"/>
       <c r="G8" s="7" t="inlineStr"/>
       <c r="H8" s="7" t="inlineStr">
         <is>
@@ -809,18 +805,18 @@
           <t>Class 2 (G.K)</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D9" s="7" t="inlineStr"/>
+      <c r="E9" s="7" t="inlineStr">
         <is>
           <t>Class 1 (MATH)</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr"/>
-      <c r="F9" s="7" t="inlineStr"/>
-      <c r="G9" s="7" t="inlineStr">
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>U.K.G (MATH)</t>
         </is>
       </c>
+      <c r="G9" s="7" t="inlineStr"/>
       <c r="H9" s="7" t="inlineStr">
         <is>
           <t>Class 1 (MATH)</t>
@@ -843,24 +839,28 @@
           <t>U.K.G (MATH)</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr"/>
-      <c r="D10" s="7" t="inlineStr"/>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (G.K)</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>U.K.G (MATH)</t>
         </is>
       </c>
-      <c r="F10" s="7" t="inlineStr"/>
+      <c r="E10" s="7" t="inlineStr"/>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>U.K.G (MATH)</t>
+        </is>
+      </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>Class 1 (MATH)</t>
-        </is>
-      </c>
-      <c r="H10" s="7" t="inlineStr">
-        <is>
           <t>U.K.G (MATH)</t>
         </is>
       </c>
+      <c r="H10" s="7" t="inlineStr"/>
       <c r="I10" s="8" t="inlineStr">
         <is>
           <t>U.K.G</t>
@@ -938,12 +938,12 @@
       <c r="B14" s="7" t="inlineStr"/>
       <c r="C14" s="7" t="inlineStr">
         <is>
+          <t>Class 9 (PHY)</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
           <t>Class 9 (CHEM)</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (PHY)</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr"/>
@@ -958,15 +958,19 @@
           <t>TUE</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr"/>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (CHEM)</t>
+        </is>
+      </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (PHY)</t>
+          <t>Class 10 (PHY)</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (CHEM)</t>
+          <t>Class 9 (CHEM)</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr"/>
@@ -984,10 +988,14 @@
       <c r="B16" s="7" t="inlineStr"/>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>Class 9 (PHY)</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr"/>
+          <t>Class 8 (CHEM)</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (CHEM)</t>
+        </is>
+      </c>
       <c r="E16" s="7" t="inlineStr"/>
       <c r="F16" s="7" t="inlineStr"/>
       <c r="G16" s="7" t="inlineStr"/>
@@ -1003,12 +1011,12 @@
       <c r="B17" s="7" t="inlineStr"/>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>Class 10 (PHY)</t>
+          <t>Class 8 (PHY)</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Class 10 (CHEM)</t>
+          <t>Class 9 (PHY)</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr"/>
@@ -1023,19 +1031,11 @@
           <t>FRI</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (PHY)</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr"/>
+      <c r="C18" s="7" t="inlineStr"/>
+      <c r="D18" s="7" t="inlineStr">
         <is>
           <t>Class 8 (CHEM)</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (CHEM)</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr"/>
@@ -1050,15 +1050,15 @@
           <t>SAT</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (CHEM)</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="inlineStr"/>
+      <c r="B19" s="7" t="inlineStr"/>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (PHY)</t>
+        </is>
+      </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Class 9 (PHY)</t>
+          <t>Class 10 (PHY)</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr"/>
@@ -1141,19 +1141,11 @@
       <c r="E23" s="7" t="inlineStr"/>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>Class 9 (BIO)</t>
-        </is>
-      </c>
-      <c r="G23" s="7" t="inlineStr">
-        <is>
           <t>Class 10 (BIO)</t>
         </is>
       </c>
-      <c r="H23" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (BIO)</t>
-        </is>
-      </c>
+      <c r="G23" s="7" t="inlineStr"/>
+      <c r="H23" s="7" t="inlineStr"/>
       <c r="I23" s="7" t="inlineStr"/>
     </row>
     <row r="24">
@@ -1167,11 +1159,7 @@
       <c r="D24" s="7" t="inlineStr"/>
       <c r="E24" s="7" t="inlineStr"/>
       <c r="F24" s="7" t="inlineStr"/>
-      <c r="G24" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (BIO)</t>
-        </is>
-      </c>
+      <c r="G24" s="7" t="inlineStr"/>
       <c r="H24" s="7" t="inlineStr">
         <is>
           <t>Class 8 (BIO)</t>
@@ -1195,7 +1183,11 @@
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr"/>
-      <c r="H25" s="7" t="inlineStr"/>
+      <c r="H25" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (BIO)</t>
+        </is>
+      </c>
       <c r="I25" s="7" t="inlineStr"/>
     </row>
     <row r="26">
@@ -1208,12 +1200,12 @@
       <c r="C26" s="7" t="inlineStr"/>
       <c r="D26" s="7" t="inlineStr"/>
       <c r="E26" s="7" t="inlineStr"/>
-      <c r="F26" s="7" t="inlineStr"/>
-      <c r="G26" s="7" t="inlineStr">
+      <c r="F26" s="7" t="inlineStr">
         <is>
           <t>Class 10 (BIO)</t>
         </is>
       </c>
+      <c r="G26" s="7" t="inlineStr"/>
       <c r="H26" s="7" t="inlineStr">
         <is>
           <t>Class 8 (BIO)</t>
@@ -1237,7 +1229,11 @@
           <t>Class 10 (BIO)</t>
         </is>
       </c>
-      <c r="H27" s="7" t="inlineStr"/>
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (BIO)</t>
+        </is>
+      </c>
       <c r="I27" s="7" t="inlineStr"/>
     </row>
     <row r="28">
@@ -1250,13 +1246,17 @@
       <c r="C28" s="7" t="inlineStr"/>
       <c r="D28" s="7" t="inlineStr"/>
       <c r="E28" s="7" t="inlineStr"/>
-      <c r="F28" s="7" t="inlineStr"/>
-      <c r="G28" s="7" t="inlineStr"/>
-      <c r="H28" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (BIO)</t>
-        </is>
-      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (BIO)</t>
+        </is>
+      </c>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (BIO)</t>
+        </is>
+      </c>
+      <c r="H28" s="7" t="inlineStr"/>
       <c r="I28" s="7" t="inlineStr"/>
     </row>
     <row r="30">
@@ -1337,19 +1337,19 @@
           <t>Class 8 (TEL)</t>
         </is>
       </c>
-      <c r="D32" s="7" t="inlineStr"/>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (TEL)</t>
+        </is>
+      </c>
       <c r="E32" s="7" t="inlineStr"/>
-      <c r="F32" s="7" t="inlineStr">
+      <c r="F32" s="7" t="inlineStr"/>
+      <c r="G32" s="7" t="inlineStr">
         <is>
           <t>Class 10 (TEL)</t>
         </is>
       </c>
-      <c r="G32" s="7" t="inlineStr"/>
-      <c r="H32" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (TEL)</t>
-        </is>
-      </c>
+      <c r="H32" s="7" t="inlineStr"/>
       <c r="I32" s="8" t="inlineStr">
         <is>
           <t>Class 9</t>
@@ -1368,23 +1368,23 @@
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr"/>
-      <c r="D33" s="7" t="inlineStr"/>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (TEL)</t>
+        </is>
+      </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
           <t>Class 8 (TEL)</t>
         </is>
       </c>
-      <c r="F33" s="7" t="inlineStr">
+      <c r="F33" s="7" t="inlineStr"/>
+      <c r="G33" s="7" t="inlineStr">
         <is>
           <t>Class 10 (TEL)</t>
         </is>
       </c>
-      <c r="G33" s="7" t="inlineStr"/>
-      <c r="H33" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (TEL)</t>
-        </is>
-      </c>
+      <c r="H33" s="7" t="inlineStr"/>
       <c r="I33" s="8" t="inlineStr">
         <is>
           <t>Class 9</t>
@@ -1402,18 +1402,18 @@
           <t>Class 9 (TEL)</t>
         </is>
       </c>
-      <c r="C34" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (TEL)</t>
-        </is>
-      </c>
+      <c r="C34" s="7" t="inlineStr"/>
       <c r="D34" s="7" t="inlineStr"/>
       <c r="E34" s="7" t="inlineStr">
         <is>
+          <t>Class 7 (TEL)</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
           <t>Class 10 (TEL)</t>
         </is>
       </c>
-      <c r="F34" s="7" t="inlineStr"/>
       <c r="G34" s="7" t="inlineStr">
         <is>
           <t>Class 8 (TEL)</t>
@@ -1440,17 +1440,17 @@
       <c r="C35" s="7" t="inlineStr"/>
       <c r="D35" s="7" t="inlineStr">
         <is>
+          <t>Class 8 (TEL)</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (TEL)</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
           <t>Class 7 (TEL)</t>
-        </is>
-      </c>
-      <c r="E35" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (TEL)</t>
-        </is>
-      </c>
-      <c r="F35" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (TEL)</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr"/>
@@ -1474,20 +1474,20 @@
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (TEL)</t>
+          <t>Class 8 (TEL)</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr"/>
-      <c r="E36" s="7" t="inlineStr">
+      <c r="E36" s="7" t="inlineStr"/>
+      <c r="F36" s="7" t="inlineStr">
         <is>
           <t>Class 10 (TEL)</t>
         </is>
       </c>
-      <c r="F36" s="7" t="inlineStr"/>
       <c r="G36" s="7" t="inlineStr"/>
       <c r="H36" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (TEL)</t>
+          <t>Class 7 (TEL)</t>
         </is>
       </c>
       <c r="I36" s="8" t="inlineStr">
@@ -1508,23 +1508,23 @@
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr"/>
-      <c r="D37" s="7" t="inlineStr"/>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (TEL)</t>
+        </is>
+      </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
           <t>Class 10 (TEL)</t>
         </is>
       </c>
-      <c r="F37" s="7" t="inlineStr"/>
-      <c r="G37" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (TEL)</t>
-        </is>
-      </c>
-      <c r="H37" s="7" t="inlineStr">
+      <c r="F37" s="7" t="inlineStr">
         <is>
           <t>Class 7 (TEL)</t>
         </is>
       </c>
+      <c r="G37" s="7" t="inlineStr"/>
+      <c r="H37" s="7" t="inlineStr"/>
       <c r="I37" s="8" t="inlineStr">
         <is>
           <t>Class 9</t>
@@ -1601,27 +1601,27 @@
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (HIN)</t>
-        </is>
-      </c>
-      <c r="C41" s="7" t="inlineStr">
+          <t>Class 8 (G.K)</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr"/>
+      <c r="D41" s="7" t="inlineStr"/>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (HIN)</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
         <is>
           <t>Class 6 (HIN)</t>
         </is>
       </c>
-      <c r="D41" s="7" t="inlineStr"/>
-      <c r="E41" s="7" t="inlineStr"/>
-      <c r="F41" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (HIN)</t>
-        </is>
-      </c>
-      <c r="G41" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (HIN)</t>
-        </is>
-      </c>
-      <c r="H41" s="7" t="inlineStr"/>
+      <c r="G41" s="7" t="inlineStr"/>
+      <c r="H41" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (HIN)</t>
+        </is>
+      </c>
       <c r="I41" s="8" t="inlineStr">
         <is>
           <t>Class 8</t>
@@ -1641,20 +1641,24 @@
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
+          <t>Class 6 (HIN)</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
           <t>Class 4 (HIN)</t>
-        </is>
-      </c>
-      <c r="D42" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (HIN)</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr"/>
       <c r="F42" s="7" t="inlineStr"/>
-      <c r="G42" s="7" t="inlineStr"/>
+      <c r="G42" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (G.K)</t>
+        </is>
+      </c>
       <c r="H42" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (HIN)</t>
+          <t>Class 7 (HIN)</t>
         </is>
       </c>
       <c r="I42" s="8" t="inlineStr">
@@ -1674,10 +1678,14 @@
           <t>Class 8 (HIN)</t>
         </is>
       </c>
-      <c r="C43" s="7" t="inlineStr"/>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (HIN)</t>
+        </is>
+      </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (HIN)</t>
+          <t>Class 4 (HIN)</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr"/>
@@ -1686,11 +1694,7 @@
           <t>Class 6 (HIN)</t>
         </is>
       </c>
-      <c r="G43" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (HIN)</t>
-        </is>
-      </c>
+      <c r="G43" s="7" t="inlineStr"/>
       <c r="H43" s="7" t="inlineStr"/>
       <c r="I43" s="8" t="inlineStr">
         <is>
@@ -1720,17 +1724,17 @@
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr"/>
-      <c r="F44" s="7" t="inlineStr"/>
+      <c r="F44" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (HIN)</t>
+        </is>
+      </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
           <t>Class 7 (HIN)</t>
         </is>
       </c>
-      <c r="H44" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (HIN)</t>
-        </is>
-      </c>
+      <c r="H44" s="7" t="inlineStr"/>
       <c r="I44" s="8" t="inlineStr">
         <is>
           <t>Class 8</t>
@@ -1750,24 +1754,24 @@
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
+          <t>Class 4 (HIN)</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (HIN)</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr"/>
+      <c r="F45" s="7" t="inlineStr"/>
+      <c r="G45" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (HIN)</t>
+        </is>
+      </c>
+      <c r="H45" s="7" t="inlineStr">
+        <is>
           <t>Class 5 (HIN)</t>
-        </is>
-      </c>
-      <c r="D45" s="7" t="inlineStr"/>
-      <c r="E45" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (G.K)</t>
-        </is>
-      </c>
-      <c r="F45" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (HIN)</t>
-        </is>
-      </c>
-      <c r="G45" s="7" t="inlineStr"/>
-      <c r="H45" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (HIN)</t>
         </is>
       </c>
       <c r="I45" s="8" t="inlineStr">
@@ -1784,7 +1788,7 @@
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (G.K)</t>
+          <t>Class 8 (HIN)</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
@@ -1795,20 +1799,16 @@
       <c r="D46" s="7" t="inlineStr"/>
       <c r="E46" s="7" t="inlineStr">
         <is>
+          <t>Class 5 (HIN)</t>
+        </is>
+      </c>
+      <c r="F46" s="7" t="inlineStr"/>
+      <c r="G46" s="7" t="inlineStr"/>
+      <c r="H46" s="7" t="inlineStr">
+        <is>
           <t>Class 7 (HIN)</t>
         </is>
       </c>
-      <c r="F46" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (HIN)</t>
-        </is>
-      </c>
-      <c r="G46" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (HIN)</t>
-        </is>
-      </c>
-      <c r="H46" s="7" t="inlineStr"/>
       <c r="I46" s="8" t="inlineStr">
         <is>
           <t>Class 8</t>
@@ -1889,11 +1889,7 @@
         </is>
       </c>
       <c r="C50" s="7" t="inlineStr"/>
-      <c r="D50" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (MATH)</t>
-        </is>
-      </c>
+      <c r="D50" s="7" t="inlineStr"/>
       <c r="E50" s="7" t="inlineStr"/>
       <c r="F50" s="7" t="inlineStr"/>
       <c r="G50" s="7" t="inlineStr"/>
@@ -1909,12 +1905,12 @@
       <c r="B51" s="7" t="inlineStr"/>
       <c r="C51" s="7" t="inlineStr">
         <is>
+          <t>Class 9 (MATH)</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
           <t>Class 10 (MATH)</t>
-        </is>
-      </c>
-      <c r="D51" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (MATH)</t>
         </is>
       </c>
       <c r="E51" s="7" t="inlineStr"/>
@@ -1952,19 +1948,15 @@
           <t>THU</t>
         </is>
       </c>
-      <c r="B53" s="7" t="inlineStr">
+      <c r="B53" s="7" t="inlineStr"/>
+      <c r="C53" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (MATH)</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
         <is>
           <t>Class 10 (MATH)</t>
-        </is>
-      </c>
-      <c r="C53" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (MATH)</t>
-        </is>
-      </c>
-      <c r="D53" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (MATH)</t>
         </is>
       </c>
       <c r="E53" s="7" t="inlineStr"/>
@@ -1979,7 +1971,11 @@
           <t>FRI</t>
         </is>
       </c>
-      <c r="B54" s="7" t="inlineStr"/>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (MATH)</t>
+        </is>
+      </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
           <t>Class 9 (MATH)</t>
@@ -1987,7 +1983,7 @@
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>Class 10 (MATH)</t>
+          <t>Class 9 (MATH)</t>
         </is>
       </c>
       <c r="E54" s="7" t="inlineStr"/>
@@ -2002,7 +1998,11 @@
           <t>SAT</t>
         </is>
       </c>
-      <c r="B55" s="7" t="inlineStr"/>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (MATH)</t>
+        </is>
+      </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
           <t>Class 9 (MATH)</t>
@@ -2010,7 +2010,7 @@
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>Class 10 (MATH)</t>
+          <t>Class 9 (MATH)</t>
         </is>
       </c>
       <c r="E55" s="7" t="inlineStr"/>
@@ -2095,25 +2095,25 @@
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (BIO)</t>
+          <t>Class 4 (EVS)</t>
         </is>
       </c>
       <c r="E59" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (PHY)</t>
+          <t>Class 5 (EVS)</t>
         </is>
       </c>
       <c r="F59" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (EVS)</t>
-        </is>
-      </c>
-      <c r="G59" s="7" t="inlineStr"/>
-      <c r="H59" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (EVS)</t>
-        </is>
-      </c>
+          <t>Class 7 (CHEM)</t>
+        </is>
+      </c>
+      <c r="G59" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (BIO)</t>
+        </is>
+      </c>
+      <c r="H59" s="7" t="inlineStr"/>
       <c r="I59" s="7" t="inlineStr"/>
     </row>
     <row r="60">
@@ -2125,17 +2125,17 @@
       <c r="B60" s="7" t="inlineStr"/>
       <c r="C60" s="7" t="inlineStr">
         <is>
+          <t>Class 4 (EVS)</t>
+        </is>
+      </c>
+      <c r="D60" s="7" t="inlineStr">
+        <is>
           <t>Class 5 (EVS)</t>
         </is>
       </c>
-      <c r="D60" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (PHY)</t>
-        </is>
-      </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (EVS)</t>
+          <t>Class 6 (BIO)</t>
         </is>
       </c>
       <c r="F60" s="7" t="inlineStr">
@@ -2145,14 +2145,10 @@
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (CHEM)</t>
-        </is>
-      </c>
-      <c r="H60" s="7" t="inlineStr">
-        <is>
           <t>Class 6 (CHEM)</t>
         </is>
       </c>
+      <c r="H60" s="7" t="inlineStr"/>
       <c r="I60" s="7" t="inlineStr"/>
     </row>
     <row r="61">
@@ -2162,7 +2158,11 @@
         </is>
       </c>
       <c r="B61" s="7" t="inlineStr"/>
-      <c r="C61" s="7" t="inlineStr"/>
+      <c r="C61" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (PHY)</t>
+        </is>
+      </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
           <t>Class 5 (EVS)</t>
@@ -2170,22 +2170,18 @@
       </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (CHEM)</t>
+          <t>Class 3 (EVS)</t>
         </is>
       </c>
       <c r="F61" s="7" t="inlineStr">
         <is>
+          <t>Class 4 (EVS)</t>
+        </is>
+      </c>
+      <c r="G61" s="7" t="inlineStr"/>
+      <c r="H61" s="7" t="inlineStr">
+        <is>
           <t>Class 7 (BIO)</t>
-        </is>
-      </c>
-      <c r="G61" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (EVS)</t>
-        </is>
-      </c>
-      <c r="H61" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (EVS)</t>
         </is>
       </c>
       <c r="I61" s="7" t="inlineStr"/>
@@ -2199,32 +2195,32 @@
       <c r="B62" s="7" t="inlineStr"/>
       <c r="C62" s="7" t="inlineStr">
         <is>
+          <t>Class 4 (EVS)</t>
+        </is>
+      </c>
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (EVS)</t>
+        </is>
+      </c>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (PHY)</t>
+        </is>
+      </c>
+      <c r="F62" s="7" t="inlineStr">
+        <is>
           <t>Class 3 (EVS)</t>
         </is>
       </c>
-      <c r="D62" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (BIO)</t>
-        </is>
-      </c>
-      <c r="E62" s="7" t="inlineStr">
+      <c r="G62" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (PHY)</t>
+        </is>
+      </c>
+      <c r="H62" s="7" t="inlineStr">
         <is>
           <t>Class 7 (BIO)</t>
-        </is>
-      </c>
-      <c r="F62" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (PHY)</t>
-        </is>
-      </c>
-      <c r="G62" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (EVS)</t>
-        </is>
-      </c>
-      <c r="H62" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (EVS)</t>
         </is>
       </c>
       <c r="I62" s="7" t="inlineStr"/>
@@ -2238,28 +2234,32 @@
       <c r="B63" s="7" t="inlineStr"/>
       <c r="C63" s="7" t="inlineStr">
         <is>
+          <t>Class 6 (CHEM)</t>
+        </is>
+      </c>
+      <c r="D63" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (EVS)</t>
+        </is>
+      </c>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (CHEM)</t>
+        </is>
+      </c>
+      <c r="F63" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (EVS)</t>
+        </is>
+      </c>
+      <c r="G63" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (BIO)</t>
+        </is>
+      </c>
+      <c r="H63" s="7" t="inlineStr">
+        <is>
           <t>Class 4 (EVS)</t>
-        </is>
-      </c>
-      <c r="D63" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (BIO)</t>
-        </is>
-      </c>
-      <c r="E63" s="7" t="inlineStr"/>
-      <c r="F63" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (EVS)</t>
-        </is>
-      </c>
-      <c r="G63" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (EVS)</t>
-        </is>
-      </c>
-      <c r="H63" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (BIO)</t>
         </is>
       </c>
       <c r="I63" s="7" t="inlineStr"/>
@@ -2273,7 +2273,7 @@
       <c r="B64" s="7" t="inlineStr"/>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (PHY)</t>
+          <t>Class 6 (BIO)</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
@@ -2281,20 +2281,20 @@
           <t>Class 5 (EVS)</t>
         </is>
       </c>
-      <c r="E64" s="7" t="inlineStr">
+      <c r="E64" s="7" t="inlineStr"/>
+      <c r="F64" s="7" t="inlineStr">
         <is>
           <t>Class 3 (EVS)</t>
         </is>
       </c>
-      <c r="F64" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (CHEM)</t>
-        </is>
-      </c>
-      <c r="G64" s="7" t="inlineStr"/>
+      <c r="G64" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (EVS)</t>
+        </is>
+      </c>
       <c r="H64" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (EVS)</t>
+          <t>Class 6 (PHY)</t>
         </is>
       </c>
       <c r="I64" s="7" t="inlineStr"/>
@@ -2372,30 +2372,30 @@
           <t>Class 5 (GRAM)</t>
         </is>
       </c>
-      <c r="C68" s="7" t="inlineStr"/>
+      <c r="C68" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (ENG)</t>
+        </is>
+      </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
           <t>Class 3 (ENG)</t>
         </is>
       </c>
-      <c r="E68" s="7" t="inlineStr">
+      <c r="E68" s="7" t="inlineStr"/>
+      <c r="F68" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (ENG)</t>
+        </is>
+      </c>
+      <c r="G68" s="7" t="inlineStr">
         <is>
           <t>Class 5 (ENG)</t>
         </is>
       </c>
-      <c r="F68" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (ENG)</t>
-        </is>
-      </c>
-      <c r="G68" s="7" t="inlineStr">
+      <c r="H68" s="7" t="inlineStr">
         <is>
           <t>Class 1 (ENG)</t>
-        </is>
-      </c>
-      <c r="H68" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (ENG)</t>
         </is>
       </c>
       <c r="I68" s="7" t="inlineStr"/>
@@ -2411,17 +2411,17 @@
           <t>Class 5 (ENG)</t>
         </is>
       </c>
-      <c r="C69" s="7" t="inlineStr"/>
-      <c r="D69" s="7" t="inlineStr">
+      <c r="C69" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (ENG)</t>
+        </is>
+      </c>
+      <c r="D69" s="7" t="inlineStr"/>
+      <c r="E69" s="7" t="inlineStr">
         <is>
           <t>Class 2 (ENG)</t>
         </is>
       </c>
-      <c r="E69" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (GRAM)</t>
-        </is>
-      </c>
       <c r="F69" s="7" t="inlineStr">
         <is>
           <t>Class 1 (ENG)</t>
@@ -2432,11 +2432,7 @@
           <t>Class 4 (ENG)</t>
         </is>
       </c>
-      <c r="H69" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (ENG)</t>
-        </is>
-      </c>
+      <c r="H69" s="7" t="inlineStr"/>
       <c r="I69" s="7" t="inlineStr"/>
     </row>
     <row r="70">
@@ -2450,30 +2446,30 @@
           <t>Class 5 (ENG)</t>
         </is>
       </c>
-      <c r="C70" s="7" t="inlineStr"/>
-      <c r="D70" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (GRAM)</t>
-        </is>
-      </c>
+      <c r="C70" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (ENG)</t>
+        </is>
+      </c>
+      <c r="D70" s="7" t="inlineStr"/>
       <c r="E70" s="7" t="inlineStr">
         <is>
+          <t>Class 2 (ENG)</t>
+        </is>
+      </c>
+      <c r="F70" s="7" t="inlineStr">
+        <is>
+          <t>Class 1 (ENG)</t>
+        </is>
+      </c>
+      <c r="G70" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (GRAM)</t>
+        </is>
+      </c>
+      <c r="H70" s="7" t="inlineStr">
+        <is>
           <t>Class 3 (ENG)</t>
-        </is>
-      </c>
-      <c r="F70" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (ENG)</t>
-        </is>
-      </c>
-      <c r="G70" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (ENG)</t>
-        </is>
-      </c>
-      <c r="H70" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (ENG)</t>
         </is>
       </c>
       <c r="I70" s="7" t="inlineStr"/>
@@ -2489,30 +2485,30 @@
           <t>Class 5 (ENG)</t>
         </is>
       </c>
-      <c r="C71" s="7" t="inlineStr">
+      <c r="C71" s="7" t="inlineStr"/>
+      <c r="D71" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (ENG)</t>
+        </is>
+      </c>
+      <c r="E71" s="7" t="inlineStr">
+        <is>
+          <t>Class 1 (ENG)</t>
+        </is>
+      </c>
+      <c r="F71" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (ENG)</t>
+        </is>
+      </c>
+      <c r="G71" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (GRAM)</t>
+        </is>
+      </c>
+      <c r="H71" s="7" t="inlineStr">
         <is>
           <t>Class 4 (ENG)</t>
-        </is>
-      </c>
-      <c r="D71" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (ENG)</t>
-        </is>
-      </c>
-      <c r="E71" s="7" t="inlineStr"/>
-      <c r="F71" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (GRAM)</t>
-        </is>
-      </c>
-      <c r="G71" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (ENG)</t>
-        </is>
-      </c>
-      <c r="H71" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (ENG)</t>
         </is>
       </c>
       <c r="I71" s="7" t="inlineStr"/>
@@ -2528,15 +2524,15 @@
           <t>Class 5 (ENG)</t>
         </is>
       </c>
-      <c r="C72" s="7" t="inlineStr">
+      <c r="C72" s="7" t="inlineStr"/>
+      <c r="D72" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (ENG)</t>
+        </is>
+      </c>
+      <c r="E72" s="7" t="inlineStr">
         <is>
           <t>Class 3 (ENG)</t>
-        </is>
-      </c>
-      <c r="D72" s="7" t="inlineStr"/>
-      <c r="E72" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (ENG)</t>
         </is>
       </c>
       <c r="F72" s="7" t="inlineStr">
@@ -2567,26 +2563,30 @@
           <t>Class 5 (ENG)</t>
         </is>
       </c>
-      <c r="C73" s="7" t="inlineStr">
+      <c r="C73" s="7" t="inlineStr"/>
+      <c r="D73" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (GRAM)</t>
+        </is>
+      </c>
+      <c r="E73" s="7" t="inlineStr">
         <is>
           <t>Class 1 (ENG)</t>
         </is>
       </c>
-      <c r="D73" s="7" t="inlineStr">
+      <c r="F73" s="7" t="inlineStr">
         <is>
           <t>Class 4 (ENG)</t>
         </is>
       </c>
-      <c r="E73" s="7" t="inlineStr"/>
-      <c r="F73" s="7" t="inlineStr"/>
       <c r="G73" s="7" t="inlineStr">
         <is>
+          <t>Class 2 (ENG)</t>
+        </is>
+      </c>
+      <c r="H73" s="7" t="inlineStr">
+        <is>
           <t>Class 3 (ENG)</t>
-        </is>
-      </c>
-      <c r="H73" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (ENG)</t>
         </is>
       </c>
       <c r="I73" s="7" t="inlineStr"/>
@@ -2660,17 +2660,17 @@
         </is>
       </c>
       <c r="B77" s="7" t="inlineStr"/>
-      <c r="C77" s="7" t="inlineStr">
+      <c r="C77" s="7" t="inlineStr"/>
+      <c r="D77" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (COMP)</t>
+        </is>
+      </c>
+      <c r="E77" s="7" t="inlineStr">
         <is>
           <t>Class 2 (COMP)</t>
         </is>
       </c>
-      <c r="D77" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (COMP)</t>
-        </is>
-      </c>
-      <c r="E77" s="7" t="inlineStr"/>
       <c r="F77" s="7" t="inlineStr"/>
       <c r="G77" s="7" t="inlineStr"/>
       <c r="H77" s="7" t="inlineStr"/>
@@ -2684,18 +2684,14 @@
       </c>
       <c r="B78" s="7" t="inlineStr"/>
       <c r="C78" s="7" t="inlineStr"/>
-      <c r="D78" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (COMP)</t>
-        </is>
-      </c>
-      <c r="E78" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (COMP)</t>
-        </is>
-      </c>
+      <c r="D78" s="7" t="inlineStr"/>
+      <c r="E78" s="7" t="inlineStr"/>
       <c r="F78" s="7" t="inlineStr"/>
-      <c r="G78" s="7" t="inlineStr"/>
+      <c r="G78" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (COMP)</t>
+        </is>
+      </c>
       <c r="H78" s="7" t="inlineStr"/>
       <c r="I78" s="7" t="inlineStr"/>
     </row>
@@ -2706,23 +2702,15 @@
         </is>
       </c>
       <c r="B79" s="7" t="inlineStr"/>
-      <c r="C79" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (COMP)</t>
-        </is>
-      </c>
+      <c r="C79" s="7" t="inlineStr"/>
       <c r="D79" s="7" t="inlineStr"/>
       <c r="E79" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (COMP)</t>
+          <t>Class 1 (COMP)</t>
         </is>
       </c>
       <c r="F79" s="7" t="inlineStr"/>
-      <c r="G79" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (COMP)</t>
-        </is>
-      </c>
+      <c r="G79" s="7" t="inlineStr"/>
       <c r="H79" s="7" t="inlineStr"/>
       <c r="I79" s="7" t="inlineStr"/>
     </row>
@@ -2737,7 +2725,7 @@
       <c r="D80" s="7" t="inlineStr"/>
       <c r="E80" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (COMP)</t>
+          <t>Class 3 (COMP)</t>
         </is>
       </c>
       <c r="F80" s="7" t="inlineStr"/>
@@ -2752,7 +2740,11 @@
         </is>
       </c>
       <c r="B81" s="7" t="inlineStr"/>
-      <c r="C81" s="7" t="inlineStr"/>
+      <c r="C81" s="7" t="inlineStr">
+        <is>
+          <t>Class 1 (COMP)</t>
+        </is>
+      </c>
       <c r="D81" s="7" t="inlineStr"/>
       <c r="E81" s="7" t="inlineStr">
         <is>
@@ -2772,14 +2764,22 @@
       </c>
       <c r="B82" s="7" t="inlineStr"/>
       <c r="C82" s="7" t="inlineStr"/>
-      <c r="D82" s="7" t="inlineStr">
+      <c r="D82" s="7" t="inlineStr"/>
+      <c r="E82" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (COMP)</t>
+        </is>
+      </c>
+      <c r="F82" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (COMP)</t>
+        </is>
+      </c>
+      <c r="G82" s="7" t="inlineStr">
         <is>
           <t>Class 1 (COMP)</t>
         </is>
       </c>
-      <c r="E82" s="7" t="inlineStr"/>
-      <c r="F82" s="7" t="inlineStr"/>
-      <c r="G82" s="7" t="inlineStr"/>
       <c r="H82" s="7" t="inlineStr"/>
       <c r="I82" s="7" t="inlineStr"/>
     </row>
@@ -2856,22 +2856,22 @@
           <t>Class 1 (TEL)</t>
         </is>
       </c>
-      <c r="C86" s="7" t="inlineStr"/>
-      <c r="D86" s="7" t="inlineStr">
+      <c r="C86" s="7" t="inlineStr">
         <is>
           <t>U.K.G (TEL)</t>
         </is>
       </c>
-      <c r="E86" s="7" t="inlineStr"/>
+      <c r="D86" s="7" t="inlineStr"/>
+      <c r="E86" s="7" t="inlineStr">
+        <is>
+          <t>L.K.G (TEL)</t>
+        </is>
+      </c>
       <c r="F86" s="7" t="inlineStr"/>
-      <c r="G86" s="7" t="inlineStr">
+      <c r="G86" s="7" t="inlineStr"/>
+      <c r="H86" s="7" t="inlineStr">
         <is>
           <t>Class 2 (TEL)</t>
-        </is>
-      </c>
-      <c r="H86" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (TEL)</t>
         </is>
       </c>
       <c r="I86" s="8" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>Class 1 (G.K)</t>
+          <t>Class 2 (TEL)</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr"/>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="F87" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (TEL)</t>
+          <t>U.K.G (TEL)</t>
         </is>
       </c>
       <c r="G87" s="7" t="inlineStr">
         <is>
-          <t>U.K.G (TEL)</t>
+          <t>Class 1 (G.K)</t>
         </is>
       </c>
       <c r="H87" s="7" t="inlineStr"/>
@@ -2927,25 +2927,29 @@
       </c>
       <c r="B88" s="7" t="inlineStr">
         <is>
-          <t>Class 1 (TEL)</t>
+          <t>Class 1 (G.K)</t>
         </is>
       </c>
       <c r="C88" s="7" t="inlineStr"/>
-      <c r="D88" s="7" t="inlineStr"/>
+      <c r="D88" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (TEL)</t>
+        </is>
+      </c>
       <c r="E88" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (TEL)</t>
+          <t>L.K.G (TEL)</t>
         </is>
       </c>
       <c r="F88" s="7" t="inlineStr"/>
       <c r="G88" s="7" t="inlineStr">
         <is>
-          <t>Class 1 (G.K)</t>
+          <t>U.K.G (TEL)</t>
         </is>
       </c>
       <c r="H88" s="7" t="inlineStr">
         <is>
-          <t>U.K.G (TEL)</t>
+          <t>Class 1 (TEL)</t>
         </is>
       </c>
       <c r="I88" s="8" t="inlineStr">
@@ -2966,21 +2970,17 @@
         </is>
       </c>
       <c r="C89" s="7" t="inlineStr"/>
-      <c r="D89" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (TEL)</t>
-        </is>
-      </c>
-      <c r="E89" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (TEL)</t>
-        </is>
-      </c>
-      <c r="F89" s="7" t="inlineStr"/>
+      <c r="D89" s="7" t="inlineStr"/>
+      <c r="E89" s="7" t="inlineStr"/>
+      <c r="F89" s="7" t="inlineStr">
+        <is>
+          <t>U.K.G (TEL)</t>
+        </is>
+      </c>
       <c r="G89" s="7" t="inlineStr"/>
       <c r="H89" s="7" t="inlineStr">
         <is>
-          <t>U.K.G (TEL)</t>
+          <t>Class 2 (TEL)</t>
         </is>
       </c>
       <c r="I89" s="8" t="inlineStr">
@@ -3035,24 +3035,24 @@
           <t>Class 1 (TEL)</t>
         </is>
       </c>
-      <c r="C91" s="7" t="inlineStr"/>
-      <c r="D91" s="7" t="inlineStr">
+      <c r="C91" s="7" t="inlineStr">
+        <is>
+          <t>U.K.G (TEL)</t>
+        </is>
+      </c>
+      <c r="D91" s="7" t="inlineStr"/>
+      <c r="E91" s="7" t="inlineStr">
+        <is>
+          <t>L.K.G (TEL)</t>
+        </is>
+      </c>
+      <c r="F91" s="7" t="inlineStr"/>
+      <c r="G91" s="7" t="inlineStr"/>
+      <c r="H91" s="7" t="inlineStr">
         <is>
           <t>Class 2 (TEL)</t>
         </is>
       </c>
-      <c r="E91" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (TEL)</t>
-        </is>
-      </c>
-      <c r="F91" s="7" t="inlineStr"/>
-      <c r="G91" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (TEL)</t>
-        </is>
-      </c>
-      <c r="H91" s="7" t="inlineStr"/>
       <c r="I91" s="8" t="inlineStr">
         <is>
           <t>Class 1</t>
@@ -3137,12 +3137,12 @@
           <t>Class 5 (SOC)</t>
         </is>
       </c>
-      <c r="D95" s="7" t="inlineStr">
+      <c r="D95" s="7" t="inlineStr"/>
+      <c r="E95" s="7" t="inlineStr">
         <is>
           <t>Class 4 (SOC)</t>
         </is>
       </c>
-      <c r="E95" s="7" t="inlineStr"/>
       <c r="F95" s="7" t="inlineStr"/>
       <c r="G95" s="7" t="inlineStr">
         <is>
@@ -3171,28 +3171,28 @@
           <t>Class 7 (SOC)</t>
         </is>
       </c>
-      <c r="C96" s="7" t="inlineStr"/>
+      <c r="C96" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (SOC)</t>
+        </is>
+      </c>
       <c r="D96" s="7" t="inlineStr">
         <is>
           <t>Class 3 (SOC)</t>
         </is>
       </c>
-      <c r="E96" s="7" t="inlineStr">
+      <c r="E96" s="7" t="inlineStr"/>
+      <c r="F96" s="7" t="inlineStr">
         <is>
           <t>Class 6 (SOC)</t>
         </is>
       </c>
-      <c r="F96" s="7" t="inlineStr">
+      <c r="G96" s="7" t="inlineStr"/>
+      <c r="H96" s="7" t="inlineStr">
         <is>
           <t>Class 4 (SOC)</t>
         </is>
       </c>
-      <c r="G96" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (SOC)</t>
-        </is>
-      </c>
-      <c r="H96" s="7" t="inlineStr"/>
       <c r="I96" s="8" t="inlineStr">
         <is>
           <t>Class 7</t>
@@ -3213,25 +3213,25 @@
       <c r="C97" s="7" t="inlineStr"/>
       <c r="D97" s="7" t="inlineStr">
         <is>
+          <t>Class 6 (SOC)</t>
+        </is>
+      </c>
+      <c r="E97" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (SOC)</t>
+        </is>
+      </c>
+      <c r="F97" s="7" t="inlineStr">
+        <is>
           <t>Class 3 (SOC)</t>
         </is>
       </c>
-      <c r="E97" s="7" t="inlineStr">
+      <c r="G97" s="7" t="inlineStr"/>
+      <c r="H97" s="7" t="inlineStr">
         <is>
           <t>Class 4 (SOC)</t>
         </is>
       </c>
-      <c r="F97" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (SOC)</t>
-        </is>
-      </c>
-      <c r="G97" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (SOC)</t>
-        </is>
-      </c>
-      <c r="H97" s="7" t="inlineStr"/>
       <c r="I97" s="8" t="inlineStr">
         <is>
           <t>Class 7</t>
@@ -3262,13 +3262,13 @@
       </c>
       <c r="F98" s="7" t="inlineStr">
         <is>
-          <t>Class 3 (SOC)</t>
+          <t>Class 5 (SOC)</t>
         </is>
       </c>
       <c r="G98" s="7" t="inlineStr"/>
       <c r="H98" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (SOC)</t>
+          <t>Class 3 (SOC)</t>
         </is>
       </c>
       <c r="I98" s="8" t="inlineStr">
@@ -3291,25 +3291,25 @@
       <c r="C99" s="7" t="inlineStr"/>
       <c r="D99" s="7" t="inlineStr">
         <is>
+          <t>Class 5 (SOC)</t>
+        </is>
+      </c>
+      <c r="E99" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (SOC)</t>
+        </is>
+      </c>
+      <c r="F99" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (SOC)</t>
+        </is>
+      </c>
+      <c r="G99" s="7" t="inlineStr"/>
+      <c r="H99" s="7" t="inlineStr">
+        <is>
           <t>Class 3 (SOC)</t>
         </is>
       </c>
-      <c r="E99" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (SOC)</t>
-        </is>
-      </c>
-      <c r="F99" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (SOC)</t>
-        </is>
-      </c>
-      <c r="G99" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (SOC)</t>
-        </is>
-      </c>
-      <c r="H99" s="7" t="inlineStr"/>
       <c r="I99" s="8" t="inlineStr">
         <is>
           <t>Class 7</t>
@@ -3332,23 +3332,23 @@
           <t>Class 5 (SOC)</t>
         </is>
       </c>
-      <c r="D100" s="7" t="inlineStr"/>
-      <c r="E100" s="7" t="inlineStr">
+      <c r="D100" s="7" t="inlineStr">
         <is>
           <t>Class 6 (SOC)</t>
         </is>
       </c>
-      <c r="F100" s="7" t="inlineStr">
+      <c r="E100" s="7" t="inlineStr"/>
+      <c r="F100" s="7" t="inlineStr"/>
+      <c r="G100" s="7" t="inlineStr">
         <is>
           <t>Class 3 (SOC)</t>
         </is>
       </c>
-      <c r="G100" s="7" t="inlineStr">
+      <c r="H100" s="7" t="inlineStr">
         <is>
           <t>Class 4 (SOC)</t>
         </is>
       </c>
-      <c r="H100" s="7" t="inlineStr"/>
       <c r="I100" s="8" t="inlineStr">
         <is>
           <t>Class 7</t>
@@ -3436,16 +3436,12 @@
       </c>
       <c r="E104" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (GRAM)</t>
+          <t>Class 6 (ENG)</t>
         </is>
       </c>
       <c r="F104" s="7" t="inlineStr"/>
       <c r="G104" s="7" t="inlineStr"/>
-      <c r="H104" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (ENG)</t>
-        </is>
-      </c>
+      <c r="H104" s="7" t="inlineStr"/>
       <c r="I104" s="7" t="inlineStr"/>
     </row>
     <row r="105">
@@ -3455,18 +3451,22 @@
         </is>
       </c>
       <c r="B105" s="7" t="inlineStr"/>
-      <c r="C105" s="7" t="inlineStr"/>
-      <c r="D105" s="7" t="inlineStr"/>
+      <c r="C105" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (GRAM)</t>
+        </is>
+      </c>
+      <c r="D105" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (ENG)</t>
+        </is>
+      </c>
       <c r="E105" s="7" t="inlineStr">
         <is>
           <t>Class 7 (ENG)</t>
         </is>
       </c>
-      <c r="F105" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (ENG)</t>
-        </is>
-      </c>
+      <c r="F105" s="7" t="inlineStr"/>
       <c r="G105" s="7" t="inlineStr"/>
       <c r="H105" s="7" t="inlineStr"/>
       <c r="I105" s="7" t="inlineStr"/>
@@ -3478,19 +3478,27 @@
         </is>
       </c>
       <c r="B106" s="7" t="inlineStr"/>
-      <c r="C106" s="7" t="inlineStr"/>
+      <c r="C106" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (ENG)</t>
+        </is>
+      </c>
       <c r="D106" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (ENG)</t>
-        </is>
-      </c>
-      <c r="E106" s="7" t="inlineStr"/>
-      <c r="F106" s="7" t="inlineStr"/>
-      <c r="G106" s="7" t="inlineStr">
-        <is>
           <t>Class 7 (ENG)</t>
         </is>
       </c>
+      <c r="E106" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (GRAM)</t>
+        </is>
+      </c>
+      <c r="F106" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (GRAM)</t>
+        </is>
+      </c>
+      <c r="G106" s="7" t="inlineStr"/>
       <c r="H106" s="7" t="inlineStr"/>
       <c r="I106" s="7" t="inlineStr"/>
     </row>
@@ -3501,22 +3509,22 @@
         </is>
       </c>
       <c r="B107" s="7" t="inlineStr"/>
-      <c r="C107" s="7" t="inlineStr">
+      <c r="C107" s="7" t="inlineStr"/>
+      <c r="D107" s="7" t="inlineStr">
         <is>
           <t>Class 7 (ENG)</t>
         </is>
       </c>
-      <c r="D107" s="7" t="inlineStr"/>
-      <c r="E107" s="7" t="inlineStr"/>
+      <c r="E107" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (ENG)</t>
+        </is>
+      </c>
       <c r="F107" s="7" t="inlineStr"/>
-      <c r="G107" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (ENG)</t>
-        </is>
-      </c>
+      <c r="G107" s="7" t="inlineStr"/>
       <c r="H107" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (GRAM)</t>
+          <t>Class 9 (GRAM)</t>
         </is>
       </c>
       <c r="I107" s="7" t="inlineStr"/>
@@ -3529,23 +3537,19 @@
       </c>
       <c r="B108" s="7" t="inlineStr"/>
       <c r="C108" s="7" t="inlineStr"/>
-      <c r="D108" s="7" t="inlineStr">
+      <c r="D108" s="7" t="inlineStr"/>
+      <c r="E108" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (ENG)</t>
+        </is>
+      </c>
+      <c r="F108" s="7" t="inlineStr">
         <is>
           <t>Class 7 (ENG)</t>
         </is>
       </c>
-      <c r="E108" s="7" t="inlineStr"/>
-      <c r="F108" s="7" t="inlineStr"/>
-      <c r="G108" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (GRAM)</t>
-        </is>
-      </c>
-      <c r="H108" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (ENG)</t>
-        </is>
-      </c>
+      <c r="G108" s="7" t="inlineStr"/>
+      <c r="H108" s="7" t="inlineStr"/>
       <c r="I108" s="7" t="inlineStr"/>
     </row>
     <row r="109">
@@ -3556,20 +3560,16 @@
       </c>
       <c r="B109" s="7" t="inlineStr"/>
       <c r="C109" s="7" t="inlineStr"/>
-      <c r="D109" s="7" t="inlineStr">
+      <c r="D109" s="7" t="inlineStr"/>
+      <c r="E109" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (ENG)</t>
+        </is>
+      </c>
+      <c r="F109" s="7" t="inlineStr"/>
+      <c r="G109" s="7" t="inlineStr">
         <is>
           <t>Class 6 (ENG)</t>
-        </is>
-      </c>
-      <c r="E109" s="7" t="inlineStr"/>
-      <c r="F109" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (GRAM)</t>
-        </is>
-      </c>
-      <c r="G109" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (ENG)</t>
         </is>
       </c>
       <c r="H109" s="7" t="inlineStr"/>
@@ -3644,21 +3644,21 @@
         </is>
       </c>
       <c r="B113" s="7" t="inlineStr"/>
-      <c r="C113" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (HIN)</t>
-        </is>
-      </c>
+      <c r="C113" s="7" t="inlineStr"/>
       <c r="D113" s="7" t="inlineStr"/>
       <c r="E113" s="7" t="inlineStr">
         <is>
+          <t>Class 10 (HIN)</t>
+        </is>
+      </c>
+      <c r="F113" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (HIN)</t>
+        </is>
+      </c>
+      <c r="G113" s="7" t="inlineStr">
+        <is>
           <t>Class 9 (HIN)</t>
-        </is>
-      </c>
-      <c r="F113" s="7" t="inlineStr"/>
-      <c r="G113" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (HIN)</t>
         </is>
       </c>
       <c r="H113" s="7" t="inlineStr"/>
@@ -3670,25 +3670,25 @@
           <t>TUE</t>
         </is>
       </c>
-      <c r="B114" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (HIN)</t>
-        </is>
-      </c>
+      <c r="B114" s="7" t="inlineStr"/>
       <c r="C114" s="7" t="inlineStr"/>
       <c r="D114" s="7" t="inlineStr"/>
-      <c r="E114" s="7" t="inlineStr"/>
+      <c r="E114" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (HIN)</t>
+        </is>
+      </c>
       <c r="F114" s="7" t="inlineStr">
         <is>
+          <t>Class 10 (HIN)</t>
+        </is>
+      </c>
+      <c r="G114" s="7" t="inlineStr"/>
+      <c r="H114" s="7" t="inlineStr">
+        <is>
           <t>Class 9 (HIN)</t>
         </is>
       </c>
-      <c r="G114" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (HIN)</t>
-        </is>
-      </c>
-      <c r="H114" s="7" t="inlineStr"/>
       <c r="I114" s="7" t="inlineStr"/>
     </row>
     <row r="115">
@@ -3697,21 +3697,17 @@
           <t>WED</t>
         </is>
       </c>
-      <c r="B115" s="7" t="inlineStr"/>
+      <c r="B115" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (HIN)</t>
+        </is>
+      </c>
       <c r="C115" s="7" t="inlineStr"/>
       <c r="D115" s="7" t="inlineStr"/>
       <c r="E115" s="7" t="inlineStr"/>
-      <c r="F115" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (HIN)</t>
-        </is>
-      </c>
+      <c r="F115" s="7" t="inlineStr"/>
       <c r="G115" s="7" t="inlineStr"/>
-      <c r="H115" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (HIN)</t>
-        </is>
-      </c>
+      <c r="H115" s="7" t="inlineStr"/>
       <c r="I115" s="7" t="inlineStr"/>
     </row>
     <row r="116">
@@ -3721,20 +3717,24 @@
         </is>
       </c>
       <c r="B116" s="7" t="inlineStr"/>
-      <c r="C116" s="7" t="inlineStr"/>
+      <c r="C116" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (HIN)</t>
+        </is>
+      </c>
       <c r="D116" s="7" t="inlineStr"/>
       <c r="E116" s="7" t="inlineStr">
         <is>
-          <t>Class 3 (HIN)</t>
+          <t>Class 9 (HIN)</t>
         </is>
       </c>
       <c r="F116" s="7" t="inlineStr"/>
-      <c r="G116" s="7" t="inlineStr"/>
-      <c r="H116" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (HIN)</t>
-        </is>
-      </c>
+      <c r="G116" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (HIN)</t>
+        </is>
+      </c>
+      <c r="H116" s="7" t="inlineStr"/>
       <c r="I116" s="7" t="inlineStr"/>
     </row>
     <row r="117">
@@ -3750,14 +3750,18 @@
         </is>
       </c>
       <c r="D117" s="7" t="inlineStr"/>
-      <c r="E117" s="7" t="inlineStr"/>
+      <c r="E117" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (HIN)</t>
+        </is>
+      </c>
       <c r="F117" s="7" t="inlineStr"/>
-      <c r="G117" s="7" t="inlineStr"/>
-      <c r="H117" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (HIN)</t>
-        </is>
-      </c>
+      <c r="G117" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (HIN)</t>
+        </is>
+      </c>
+      <c r="H117" s="7" t="inlineStr"/>
       <c r="I117" s="7" t="inlineStr"/>
     </row>
     <row r="118">
@@ -3769,7 +3773,7 @@
       <c r="B118" s="7" t="inlineStr"/>
       <c r="C118" s="7" t="inlineStr">
         <is>
-          <t>Class 10 (HIN)</t>
+          <t>Class 3 (HIN)</t>
         </is>
       </c>
       <c r="D118" s="7" t="inlineStr"/>
@@ -3780,11 +3784,7 @@
       </c>
       <c r="F118" s="7" t="inlineStr"/>
       <c r="G118" s="7" t="inlineStr"/>
-      <c r="H118" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (HIN)</t>
-        </is>
-      </c>
+      <c r="H118" s="7" t="inlineStr"/>
       <c r="I118" s="7" t="inlineStr"/>
     </row>
     <row r="120">
@@ -3867,17 +3867,17 @@
       </c>
       <c r="D122" s="7" t="inlineStr">
         <is>
+          <t>U.K.G (ENG)</t>
+        </is>
+      </c>
+      <c r="E122" s="7" t="inlineStr">
+        <is>
+          <t>Class 1 (HIN)</t>
+        </is>
+      </c>
+      <c r="F122" s="7" t="inlineStr">
+        <is>
           <t>Class 1 (EVS)</t>
-        </is>
-      </c>
-      <c r="E122" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (EVS)</t>
-        </is>
-      </c>
-      <c r="F122" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (HIN)</t>
         </is>
       </c>
       <c r="G122" s="7" t="inlineStr"/>
@@ -3905,30 +3905,30 @@
       </c>
       <c r="C123" s="7" t="inlineStr">
         <is>
+          <t>Class 1 (EVS)</t>
+        </is>
+      </c>
+      <c r="D123" s="7" t="inlineStr">
+        <is>
+          <t>Class 1 (HIN)</t>
+        </is>
+      </c>
+      <c r="E123" s="7" t="inlineStr">
+        <is>
+          <t>U.K.G (ENG)</t>
+        </is>
+      </c>
+      <c r="F123" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (EVS)</t>
+        </is>
+      </c>
+      <c r="G123" s="7" t="inlineStr">
+        <is>
           <t>Class 2 (HIN)</t>
         </is>
       </c>
-      <c r="D123" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (HIN)</t>
-        </is>
-      </c>
-      <c r="E123" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (EVS)</t>
-        </is>
-      </c>
-      <c r="F123" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (ENG)</t>
-        </is>
-      </c>
-      <c r="G123" s="7" t="inlineStr"/>
-      <c r="H123" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (ENG)</t>
-        </is>
-      </c>
+      <c r="H123" s="7" t="inlineStr"/>
       <c r="I123" s="8" t="inlineStr">
         <is>
           <t>Class 2</t>
@@ -3948,28 +3948,28 @@
       </c>
       <c r="C124" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (HIN)</t>
+          <t>Class 2 (EVS)</t>
         </is>
       </c>
       <c r="D124" s="7" t="inlineStr">
         <is>
-          <t>Class 1 (EVS)</t>
+          <t>U.K.G (ENG)</t>
         </is>
       </c>
       <c r="E124" s="7" t="inlineStr">
         <is>
-          <t>Class 1 (HIN)</t>
+          <t>U.K.G (ENG)</t>
         </is>
       </c>
       <c r="F124" s="7" t="inlineStr">
         <is>
-          <t>U.K.G (ENG)</t>
+          <t>Class 2 (EVS)</t>
         </is>
       </c>
       <c r="G124" s="7" t="inlineStr"/>
       <c r="H124" s="7" t="inlineStr">
         <is>
-          <t>Class 1 (EVS)</t>
+          <t>Class 2 (HIN)</t>
         </is>
       </c>
       <c r="I124" s="8" t="inlineStr">
@@ -3991,26 +3991,30 @@
       </c>
       <c r="C125" s="7" t="inlineStr">
         <is>
+          <t>Class 1 (EVS)</t>
+        </is>
+      </c>
+      <c r="D125" s="7" t="inlineStr">
+        <is>
           <t>Class 1 (HIN)</t>
         </is>
       </c>
-      <c r="D125" s="7" t="inlineStr"/>
       <c r="E125" s="7" t="inlineStr">
         <is>
+          <t>Class 2 (HIN)</t>
+        </is>
+      </c>
+      <c r="F125" s="7" t="inlineStr">
+        <is>
+          <t>Class 1 (EVS)</t>
+        </is>
+      </c>
+      <c r="G125" s="7" t="inlineStr"/>
+      <c r="H125" s="7" t="inlineStr">
+        <is>
           <t>U.K.G (ENG)</t>
         </is>
       </c>
-      <c r="F125" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (ENG)</t>
-        </is>
-      </c>
-      <c r="G125" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (G.K)</t>
-        </is>
-      </c>
-      <c r="H125" s="7" t="inlineStr"/>
       <c r="I125" s="8" t="inlineStr">
         <is>
           <t>Class 2</t>
@@ -4025,30 +4029,26 @@
       </c>
       <c r="B126" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (EVS)</t>
+          <t>Class 2 (HIN)</t>
         </is>
       </c>
       <c r="C126" s="7" t="inlineStr">
         <is>
-          <t>Class 1 (EVS)</t>
+          <t>U.K.G (ENG)</t>
         </is>
       </c>
       <c r="D126" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (HIN)</t>
-        </is>
-      </c>
-      <c r="E126" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (EVS)</t>
-        </is>
-      </c>
-      <c r="F126" s="7" t="inlineStr">
+          <t>Class 1 (HIN)</t>
+        </is>
+      </c>
+      <c r="E126" s="7" t="inlineStr"/>
+      <c r="F126" s="7" t="inlineStr"/>
+      <c r="G126" s="7" t="inlineStr">
         <is>
           <t>U.K.G (ENG)</t>
         </is>
       </c>
-      <c r="G126" s="7" t="inlineStr"/>
       <c r="H126" s="7" t="inlineStr">
         <is>
           <t>U.K.G (ENG)</t>
@@ -4073,28 +4073,28 @@
       </c>
       <c r="C127" s="7" t="inlineStr">
         <is>
+          <t>Class 1 (HIN)</t>
+        </is>
+      </c>
+      <c r="D127" s="7" t="inlineStr">
+        <is>
+          <t>Class 1 (EVS)</t>
+        </is>
+      </c>
+      <c r="E127" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (G.K)</t>
+        </is>
+      </c>
+      <c r="F127" s="7" t="inlineStr">
+        <is>
+          <t>Class 1 (EVS)</t>
+        </is>
+      </c>
+      <c r="G127" s="7" t="inlineStr"/>
+      <c r="H127" s="7" t="inlineStr">
+        <is>
           <t>U.K.G (ENG)</t>
-        </is>
-      </c>
-      <c r="D127" s="7" t="inlineStr"/>
-      <c r="E127" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (EVS)</t>
-        </is>
-      </c>
-      <c r="F127" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (ENG)</t>
-        </is>
-      </c>
-      <c r="G127" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (HIN)</t>
-        </is>
-      </c>
-      <c r="H127" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (HIN)</t>
         </is>
       </c>
       <c r="I127" s="8" t="inlineStr">
@@ -4173,22 +4173,22 @@
       </c>
       <c r="B131" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (G.K)</t>
+          <t>Class 6 (MATH)</t>
         </is>
       </c>
       <c r="C131" s="7" t="inlineStr"/>
-      <c r="D131" s="7" t="inlineStr"/>
+      <c r="D131" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (MATH)</t>
+        </is>
+      </c>
       <c r="E131" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (MATH)</t>
+          <t>Class 8 (MATH)</t>
         </is>
       </c>
       <c r="F131" s="7" t="inlineStr"/>
-      <c r="G131" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (MATH)</t>
-        </is>
-      </c>
+      <c r="G131" s="7" t="inlineStr"/>
       <c r="H131" s="7" t="inlineStr"/>
       <c r="I131" s="8" t="inlineStr">
         <is>
@@ -4204,7 +4204,7 @@
       </c>
       <c r="B132" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (MATH)</t>
+          <t>Class 6 (G.K)</t>
         </is>
       </c>
       <c r="C132" s="7" t="inlineStr">
@@ -4212,15 +4212,15 @@
           <t>Class 7 (MATH)</t>
         </is>
       </c>
-      <c r="D132" s="7" t="inlineStr"/>
-      <c r="E132" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (G.K)</t>
-        </is>
-      </c>
+      <c r="D132" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (MATH)</t>
+        </is>
+      </c>
+      <c r="E132" s="7" t="inlineStr"/>
       <c r="F132" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (COMP)</t>
+          <t>Class 7 (MATH)</t>
         </is>
       </c>
       <c r="G132" s="7" t="inlineStr"/>
@@ -4242,23 +4242,23 @@
           <t>Class 6 (MATH)</t>
         </is>
       </c>
-      <c r="C133" s="7" t="inlineStr">
+      <c r="C133" s="7" t="inlineStr"/>
+      <c r="D133" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (MATH)</t>
+        </is>
+      </c>
+      <c r="E133" s="7" t="inlineStr">
         <is>
           <t>Class 8 (COMP)</t>
         </is>
       </c>
-      <c r="D133" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (MATH)</t>
-        </is>
-      </c>
-      <c r="E133" s="7" t="inlineStr"/>
-      <c r="F133" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (MATH)</t>
-        </is>
-      </c>
-      <c r="G133" s="7" t="inlineStr"/>
+      <c r="F133" s="7" t="inlineStr"/>
+      <c r="G133" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (COMP)</t>
+        </is>
+      </c>
       <c r="H133" s="7" t="inlineStr">
         <is>
           <t>Class 6 (MATH)</t>
@@ -4281,23 +4281,23 @@
           <t>Class 6 (MATH)</t>
         </is>
       </c>
-      <c r="C134" s="7" t="inlineStr"/>
+      <c r="C134" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (MATH)</t>
+        </is>
+      </c>
       <c r="D134" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (MATH)</t>
+          <t>Class 6 (MATH)</t>
         </is>
       </c>
       <c r="E134" s="7" t="inlineStr"/>
       <c r="F134" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (MATH)</t>
-        </is>
-      </c>
-      <c r="G134" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (G.K)</t>
-        </is>
-      </c>
+          <t>Class 8 (MATH)</t>
+        </is>
+      </c>
+      <c r="G134" s="7" t="inlineStr"/>
       <c r="H134" s="7" t="inlineStr"/>
       <c r="I134" s="8" t="inlineStr">
         <is>
@@ -4318,26 +4318,26 @@
       </c>
       <c r="C135" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (MATH)</t>
+          <t>Class 7 (MATH)</t>
         </is>
       </c>
       <c r="D135" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (MATH)</t>
+          <t>Class 7 (MATH)</t>
         </is>
       </c>
       <c r="E135" s="7" t="inlineStr"/>
       <c r="F135" s="7" t="inlineStr">
         <is>
+          <t>Class 4 (G.K)</t>
+        </is>
+      </c>
+      <c r="G135" s="7" t="inlineStr"/>
+      <c r="H135" s="7" t="inlineStr">
+        <is>
           <t>Class 8 (MATH)</t>
         </is>
       </c>
-      <c r="G135" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (MATH)</t>
-        </is>
-      </c>
-      <c r="H135" s="7" t="inlineStr"/>
       <c r="I135" s="8" t="inlineStr">
         <is>
           <t>Class 6</t>
@@ -4355,28 +4355,28 @@
           <t>Class 6 (MATH)</t>
         </is>
       </c>
-      <c r="C136" s="7" t="inlineStr"/>
+      <c r="C136" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (MATH)</t>
+        </is>
+      </c>
       <c r="D136" s="7" t="inlineStr">
         <is>
           <t>Class 7 (MATH)</t>
         </is>
       </c>
-      <c r="E136" s="7" t="inlineStr">
+      <c r="E136" s="7" t="inlineStr"/>
+      <c r="F136" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (G.K)</t>
+        </is>
+      </c>
+      <c r="G136" s="7" t="inlineStr">
         <is>
           <t>Class 8 (MATH)</t>
         </is>
       </c>
-      <c r="F136" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (MATH)</t>
-        </is>
-      </c>
-      <c r="G136" s="7" t="inlineStr"/>
-      <c r="H136" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (MATH)</t>
-        </is>
-      </c>
+      <c r="H136" s="7" t="inlineStr"/>
       <c r="I136" s="8" t="inlineStr">
         <is>
           <t>Class 6</t>
@@ -4466,22 +4466,18 @@
           <t>L.K.G (EVS)</t>
         </is>
       </c>
-      <c r="E140" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (ORAL)</t>
-        </is>
-      </c>
+      <c r="E140" s="7" t="inlineStr"/>
       <c r="F140" s="7" t="inlineStr">
         <is>
           <t>L.K.G (EVS)</t>
         </is>
       </c>
-      <c r="G140" s="7" t="inlineStr">
+      <c r="G140" s="7" t="inlineStr"/>
+      <c r="H140" s="7" t="inlineStr">
         <is>
           <t>L.K.G (EVS)</t>
         </is>
       </c>
-      <c r="H140" s="7" t="inlineStr"/>
       <c r="I140" s="8" t="inlineStr">
         <is>
           <t>L.K.G</t>
@@ -4496,31 +4492,31 @@
       </c>
       <c r="B141" s="7" t="inlineStr">
         <is>
+          <t>L.K.G (MATH)</t>
+        </is>
+      </c>
+      <c r="C141" s="7" t="inlineStr">
+        <is>
           <t>L.K.G (ENG)</t>
         </is>
       </c>
-      <c r="C141" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (EVS)</t>
-        </is>
-      </c>
       <c r="D141" s="7" t="inlineStr">
         <is>
+          <t>L.K.G (MATH)</t>
+        </is>
+      </c>
+      <c r="E141" s="7" t="inlineStr"/>
+      <c r="F141" s="7" t="inlineStr">
+        <is>
           <t>L.K.G (ENG)</t>
         </is>
       </c>
-      <c r="E141" s="7" t="inlineStr"/>
-      <c r="F141" s="7" t="inlineStr"/>
       <c r="G141" s="7" t="inlineStr">
         <is>
-          <t>L.K.G (ENG)</t>
-        </is>
-      </c>
-      <c r="H141" s="7" t="inlineStr">
-        <is>
           <t>L.K.G (ORAL)</t>
         </is>
       </c>
+      <c r="H141" s="7" t="inlineStr"/>
       <c r="I141" s="8" t="inlineStr">
         <is>
           <t>L.K.G</t>
@@ -4540,28 +4536,24 @@
       </c>
       <c r="C142" s="7" t="inlineStr">
         <is>
-          <t>L.K.G (ENG)</t>
+          <t>L.K.G (EVS)</t>
         </is>
       </c>
       <c r="D142" s="7" t="inlineStr">
         <is>
-          <t>L.K.G (EVS)</t>
+          <t>L.K.G (ORAL)</t>
         </is>
       </c>
       <c r="E142" s="7" t="inlineStr"/>
       <c r="F142" s="7" t="inlineStr">
         <is>
-          <t>L.K.G (ENG)</t>
-        </is>
-      </c>
-      <c r="G142" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (ORAL)</t>
-        </is>
-      </c>
+          <t>L.K.G (EVS)</t>
+        </is>
+      </c>
+      <c r="G142" s="7" t="inlineStr"/>
       <c r="H142" s="7" t="inlineStr">
         <is>
-          <t>L.K.G (ENG)</t>
+          <t>L.K.G (EVS)</t>
         </is>
       </c>
       <c r="I142" s="8" t="inlineStr">
@@ -4578,33 +4570,37 @@
       </c>
       <c r="B143" s="7" t="inlineStr">
         <is>
+          <t>L.K.G (MATH)</t>
+        </is>
+      </c>
+      <c r="C143" s="7" t="inlineStr">
+        <is>
           <t>L.K.G (ENG)</t>
         </is>
       </c>
-      <c r="C143" s="7" t="inlineStr">
+      <c r="D143" s="7" t="inlineStr">
+        <is>
+          <t>L.K.G (ENG)</t>
+        </is>
+      </c>
+      <c r="E143" s="7" t="inlineStr">
         <is>
           <t>L.K.G (MATH)</t>
         </is>
       </c>
-      <c r="D143" s="7" t="inlineStr">
+      <c r="F143" s="7" t="inlineStr">
         <is>
           <t>L.K.G (EVS)</t>
         </is>
       </c>
-      <c r="E143" s="7" t="inlineStr"/>
-      <c r="F143" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (MATH)</t>
-        </is>
-      </c>
       <c r="G143" s="7" t="inlineStr">
         <is>
-          <t>L.K.G (MATH)</t>
+          <t>L.K.G (EVS)</t>
         </is>
       </c>
       <c r="H143" s="7" t="inlineStr">
         <is>
-          <t>L.K.G (EVS)</t>
+          <t>L.K.G (ENG)</t>
         </is>
       </c>
       <c r="I143" s="8" t="inlineStr">
@@ -4621,33 +4617,33 @@
       </c>
       <c r="B144" s="7" t="inlineStr">
         <is>
-          <t>L.K.G (EVS)</t>
+          <t>L.K.G (ENG)</t>
         </is>
       </c>
       <c r="C144" s="7" t="inlineStr">
         <is>
-          <t>L.K.G (ORAL)</t>
+          <t>L.K.G (MATH)</t>
         </is>
       </c>
       <c r="D144" s="7" t="inlineStr"/>
       <c r="E144" s="7" t="inlineStr">
         <is>
+          <t>L.K.G (ENG)</t>
+        </is>
+      </c>
+      <c r="F144" s="7" t="inlineStr">
+        <is>
+          <t>L.K.G (ORAL)</t>
+        </is>
+      </c>
+      <c r="G144" s="7" t="inlineStr">
+        <is>
+          <t>L.K.G (ENG)</t>
+        </is>
+      </c>
+      <c r="H144" s="7" t="inlineStr">
+        <is>
           <t>L.K.G (MATH)</t>
-        </is>
-      </c>
-      <c r="F144" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (MATH)</t>
-        </is>
-      </c>
-      <c r="G144" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (MATH)</t>
-        </is>
-      </c>
-      <c r="H144" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (ENG)</t>
         </is>
       </c>
       <c r="I144" s="8" t="inlineStr">
@@ -4664,31 +4660,35 @@
       </c>
       <c r="B145" s="7" t="inlineStr">
         <is>
+          <t>L.K.G (ENG)</t>
+        </is>
+      </c>
+      <c r="C145" s="7" t="inlineStr">
+        <is>
           <t>L.K.G (MATH)</t>
         </is>
       </c>
-      <c r="C145" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (EVS)</t>
-        </is>
-      </c>
       <c r="D145" s="7" t="inlineStr">
         <is>
-          <t>L.K.G (ENG)</t>
+          <t>L.K.G (ORAL)</t>
         </is>
       </c>
       <c r="E145" s="7" t="inlineStr"/>
       <c r="F145" s="7" t="inlineStr">
         <is>
+          <t>L.K.G (MATH)</t>
+        </is>
+      </c>
+      <c r="G145" s="7" t="inlineStr">
+        <is>
           <t>L.K.G (ENG)</t>
         </is>
       </c>
-      <c r="G145" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (MATH)</t>
-        </is>
-      </c>
-      <c r="H145" s="7" t="inlineStr"/>
+      <c r="H145" s="7" t="inlineStr">
+        <is>
+          <t>L.K.G (EVS)</t>
+        </is>
+      </c>
       <c r="I145" s="8" t="inlineStr">
         <is>
           <t>L.K.G</t>
@@ -4769,20 +4769,20 @@
       <c r="E149" s="7" t="inlineStr"/>
       <c r="F149" s="7" t="inlineStr">
         <is>
+          <t>Class 9 (ENG)</t>
+        </is>
+      </c>
+      <c r="G149" s="7" t="inlineStr">
+        <is>
           <t>Class 8 (ENG)</t>
         </is>
       </c>
-      <c r="G149" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (ENG)</t>
-        </is>
-      </c>
-      <c r="H149" s="7" t="inlineStr">
+      <c r="H149" s="7" t="inlineStr"/>
+      <c r="I149" s="8" t="inlineStr">
         <is>
           <t>Class 10 (ENG)</t>
         </is>
       </c>
-      <c r="I149" s="7" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="6" t="inlineStr">
@@ -4796,17 +4796,17 @@
       <c r="E150" s="7" t="inlineStr"/>
       <c r="F150" s="7" t="inlineStr">
         <is>
+          <t>Class 9 (ENG)</t>
+        </is>
+      </c>
+      <c r="G150" s="7" t="inlineStr">
+        <is>
           <t>Class 8 (ENG)</t>
         </is>
       </c>
-      <c r="G150" s="7" t="inlineStr">
+      <c r="H150" s="7" t="inlineStr">
         <is>
           <t>Class 10 (ENG)</t>
-        </is>
-      </c>
-      <c r="H150" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (ENG)</t>
         </is>
       </c>
       <c r="I150" s="7" t="inlineStr"/>
@@ -4823,17 +4823,17 @@
       <c r="E151" s="7" t="inlineStr"/>
       <c r="F151" s="7" t="inlineStr">
         <is>
+          <t>Class 8 (ENG)</t>
+        </is>
+      </c>
+      <c r="G151" s="7" t="inlineStr">
+        <is>
           <t>Class 10 (ENG)</t>
         </is>
       </c>
-      <c r="G151" s="7" t="inlineStr">
+      <c r="H151" s="7" t="inlineStr">
         <is>
           <t>Class 9 (ENG)</t>
-        </is>
-      </c>
-      <c r="H151" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (ENG)</t>
         </is>
       </c>
       <c r="I151" s="7" t="inlineStr"/>
@@ -4904,17 +4904,17 @@
       <c r="E154" s="7" t="inlineStr"/>
       <c r="F154" s="7" t="inlineStr">
         <is>
+          <t>Class 9 (ENG)</t>
+        </is>
+      </c>
+      <c r="G154" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (ENG)</t>
+        </is>
+      </c>
+      <c r="H154" s="7" t="inlineStr">
+        <is>
           <t>Class 8 (ENG)</t>
-        </is>
-      </c>
-      <c r="G154" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (ENG)</t>
-        </is>
-      </c>
-      <c r="H154" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (ENG)</t>
         </is>
       </c>
       <c r="I154" s="7" t="inlineStr"/>
@@ -4988,24 +4988,24 @@
         </is>
       </c>
       <c r="B158" s="7" t="inlineStr"/>
-      <c r="C158" s="7" t="inlineStr"/>
+      <c r="C158" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (SOC)</t>
+        </is>
+      </c>
       <c r="D158" s="7" t="inlineStr"/>
       <c r="E158" s="7" t="inlineStr">
         <is>
-          <t>Class 10 (SOC)</t>
-        </is>
-      </c>
-      <c r="F158" s="7" t="inlineStr"/>
-      <c r="G158" s="7" t="inlineStr">
+          <t>Class 9 (SOC)</t>
+        </is>
+      </c>
+      <c r="F158" s="7" t="inlineStr">
         <is>
           <t>Class 8 (SOC)</t>
         </is>
       </c>
-      <c r="H158" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (SOC)</t>
-        </is>
-      </c>
+      <c r="G158" s="7" t="inlineStr"/>
+      <c r="H158" s="7" t="inlineStr"/>
       <c r="I158" s="7" t="inlineStr"/>
     </row>
     <row r="159">
@@ -5019,20 +5019,20 @@
       <c r="D159" s="7" t="inlineStr"/>
       <c r="E159" s="7" t="inlineStr">
         <is>
+          <t>Class 10 (SOC)</t>
+        </is>
+      </c>
+      <c r="F159" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (SOC)</t>
+        </is>
+      </c>
+      <c r="G159" s="7" t="inlineStr">
+        <is>
           <t>Class 9 (SOC)</t>
         </is>
       </c>
-      <c r="F159" s="7" t="inlineStr"/>
-      <c r="G159" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (SOC)</t>
-        </is>
-      </c>
-      <c r="H159" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (SOC)</t>
-        </is>
-      </c>
+      <c r="H159" s="7" t="inlineStr"/>
       <c r="I159" s="7" t="inlineStr"/>
     </row>
     <row r="160">
@@ -5046,18 +5046,18 @@
       <c r="D160" s="7" t="inlineStr"/>
       <c r="E160" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (SOC)</t>
+          <t>Class 10 (SOC)</t>
         </is>
       </c>
       <c r="F160" s="7" t="inlineStr"/>
       <c r="G160" s="7" t="inlineStr">
         <is>
-          <t>Class 10 (SOC)</t>
+          <t>Class 9 (SOC)</t>
         </is>
       </c>
       <c r="H160" s="7" t="inlineStr">
         <is>
-          <t>Class 9 (SOC)</t>
+          <t>Class 8 (SOC)</t>
         </is>
       </c>
       <c r="I160" s="7" t="inlineStr"/>
@@ -5068,24 +5068,24 @@
           <t>THU</t>
         </is>
       </c>
-      <c r="B161" s="7" t="inlineStr"/>
-      <c r="C161" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (SOC)</t>
-        </is>
-      </c>
+      <c r="B161" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (SOC)</t>
+        </is>
+      </c>
+      <c r="C161" s="7" t="inlineStr"/>
       <c r="D161" s="7" t="inlineStr"/>
       <c r="E161" s="7" t="inlineStr">
         <is>
+          <t>Class 8 (SOC)</t>
+        </is>
+      </c>
+      <c r="F161" s="7" t="inlineStr"/>
+      <c r="G161" s="7" t="inlineStr">
+        <is>
           <t>Class 9 (SOC)</t>
         </is>
       </c>
-      <c r="F161" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (SOC)</t>
-        </is>
-      </c>
-      <c r="G161" s="7" t="inlineStr"/>
       <c r="H161" s="7" t="inlineStr"/>
       <c r="I161" s="7" t="inlineStr"/>
     </row>
@@ -5100,12 +5100,12 @@
       <c r="D162" s="7" t="inlineStr"/>
       <c r="E162" s="7" t="inlineStr">
         <is>
+          <t>Class 10 (SOC)</t>
+        </is>
+      </c>
+      <c r="F162" s="7" t="inlineStr">
+        <is>
           <t>Class 8 (SOC)</t>
-        </is>
-      </c>
-      <c r="F162" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (SOC)</t>
         </is>
       </c>
       <c r="G162" s="7" t="inlineStr">
@@ -5123,24 +5123,24 @@
         </is>
       </c>
       <c r="B163" s="7" t="inlineStr"/>
-      <c r="C163" s="7" t="inlineStr">
+      <c r="C163" s="7" t="inlineStr"/>
+      <c r="D163" s="7" t="inlineStr"/>
+      <c r="E163" s="7" t="inlineStr">
         <is>
           <t>Class 8 (SOC)</t>
         </is>
       </c>
-      <c r="D163" s="7" t="inlineStr"/>
-      <c r="E163" s="7" t="inlineStr"/>
       <c r="F163" s="7" t="inlineStr">
         <is>
           <t>Class 10 (SOC)</t>
         </is>
       </c>
-      <c r="G163" s="7" t="inlineStr">
+      <c r="G163" s="7" t="inlineStr"/>
+      <c r="H163" s="7" t="inlineStr">
         <is>
           <t>Class 9 (SOC)</t>
         </is>
       </c>
-      <c r="H163" s="7" t="inlineStr"/>
       <c r="I163" s="7" t="inlineStr"/>
     </row>
     <row r="165">
@@ -5218,25 +5218,21 @@
       </c>
       <c r="C167" s="7" t="inlineStr">
         <is>
+          <t>Class 6 (TEL)</t>
+        </is>
+      </c>
+      <c r="D167" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (TEL)</t>
+        </is>
+      </c>
+      <c r="E167" s="7" t="inlineStr"/>
+      <c r="F167" s="7" t="inlineStr">
+        <is>
           <t>Class 4 (TEL)</t>
         </is>
       </c>
-      <c r="D167" s="7" t="inlineStr"/>
-      <c r="E167" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (HIN)</t>
-        </is>
-      </c>
-      <c r="F167" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (TEL)</t>
-        </is>
-      </c>
-      <c r="G167" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (TEL)</t>
-        </is>
-      </c>
+      <c r="G167" s="7" t="inlineStr"/>
       <c r="H167" s="7" t="inlineStr"/>
       <c r="I167" s="8" t="inlineStr">
         <is>
@@ -5260,21 +5256,21 @@
           <t>U.K.G (HIN)</t>
         </is>
       </c>
-      <c r="D168" s="7" t="inlineStr">
+      <c r="D168" s="7" t="inlineStr"/>
+      <c r="E168" s="7" t="inlineStr">
         <is>
           <t>Class 5 (TEL)</t>
         </is>
       </c>
-      <c r="E168" s="7" t="inlineStr"/>
-      <c r="F168" s="7" t="inlineStr"/>
-      <c r="G168" s="7" t="inlineStr">
+      <c r="F168" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (TEL)</t>
+        </is>
+      </c>
+      <c r="G168" s="7" t="inlineStr"/>
+      <c r="H168" s="7" t="inlineStr">
         <is>
           <t>Class 6 (TEL)</t>
-        </is>
-      </c>
-      <c r="H168" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (TEL)</t>
         </is>
       </c>
       <c r="I168" s="8" t="inlineStr">
@@ -5296,21 +5292,21 @@
       </c>
       <c r="C169" s="7" t="inlineStr">
         <is>
+          <t>U.K.G (HIN)</t>
+        </is>
+      </c>
+      <c r="D169" s="7" t="inlineStr"/>
+      <c r="E169" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (TEL)</t>
+        </is>
+      </c>
+      <c r="F169" s="7" t="inlineStr"/>
+      <c r="G169" s="7" t="inlineStr">
+        <is>
           <t>Class 6 (TEL)</t>
         </is>
       </c>
-      <c r="D169" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (HIN)</t>
-        </is>
-      </c>
-      <c r="E169" s="7" t="inlineStr"/>
-      <c r="F169" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (TEL)</t>
-        </is>
-      </c>
-      <c r="G169" s="7" t="inlineStr"/>
       <c r="H169" s="7" t="inlineStr">
         <is>
           <t>Class 5 (TEL)</t>
@@ -5333,28 +5329,28 @@
           <t>Class 3 (TEL)</t>
         </is>
       </c>
-      <c r="C170" s="7" t="inlineStr"/>
-      <c r="D170" s="7" t="inlineStr">
+      <c r="C170" s="7" t="inlineStr">
+        <is>
+          <t>U.K.G (HIN)</t>
+        </is>
+      </c>
+      <c r="D170" s="7" t="inlineStr"/>
+      <c r="E170" s="7" t="inlineStr">
         <is>
           <t>Class 5 (TEL)</t>
         </is>
       </c>
-      <c r="E170" s="7" t="inlineStr">
+      <c r="F170" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (TEL)</t>
+        </is>
+      </c>
+      <c r="G170" s="7" t="inlineStr"/>
+      <c r="H170" s="7" t="inlineStr">
         <is>
           <t>Class 6 (TEL)</t>
         </is>
       </c>
-      <c r="F170" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (TEL)</t>
-        </is>
-      </c>
-      <c r="G170" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (HIN)</t>
-        </is>
-      </c>
-      <c r="H170" s="7" t="inlineStr"/>
       <c r="I170" s="8" t="inlineStr">
         <is>
           <t>Class 3</t>
@@ -5374,24 +5370,24 @@
       </c>
       <c r="C171" s="7" t="inlineStr">
         <is>
+          <t>Class 5 (TEL)</t>
+        </is>
+      </c>
+      <c r="D171" s="7" t="inlineStr">
+        <is>
           <t>U.K.G (HIN)</t>
         </is>
       </c>
-      <c r="D171" s="7" t="inlineStr">
+      <c r="E171" s="7" t="inlineStr"/>
+      <c r="F171" s="7" t="inlineStr"/>
+      <c r="G171" s="7" t="inlineStr">
         <is>
           <t>Class 4 (TEL)</t>
         </is>
       </c>
-      <c r="E171" s="7" t="inlineStr"/>
-      <c r="F171" s="7" t="inlineStr">
+      <c r="H171" s="7" t="inlineStr">
         <is>
           <t>Class 6 (TEL)</t>
-        </is>
-      </c>
-      <c r="G171" s="7" t="inlineStr"/>
-      <c r="H171" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (TEL)</t>
         </is>
       </c>
       <c r="I171" s="8" t="inlineStr">
@@ -5411,24 +5407,28 @@
           <t>Class 3 (TEL)</t>
         </is>
       </c>
-      <c r="C172" s="7" t="inlineStr">
+      <c r="C172" s="7" t="inlineStr"/>
+      <c r="D172" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (TEL)</t>
+        </is>
+      </c>
+      <c r="E172" s="7" t="inlineStr">
+        <is>
+          <t>U.K.G (HIN)</t>
+        </is>
+      </c>
+      <c r="F172" s="7" t="inlineStr">
         <is>
           <t>Class 6 (TEL)</t>
         </is>
       </c>
-      <c r="D172" s="7" t="inlineStr"/>
-      <c r="E172" s="7" t="inlineStr"/>
-      <c r="F172" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (TEL)</t>
-        </is>
-      </c>
-      <c r="G172" s="7" t="inlineStr">
+      <c r="G172" s="7" t="inlineStr"/>
+      <c r="H172" s="7" t="inlineStr">
         <is>
           <t>Class 5 (TEL)</t>
         </is>
       </c>
-      <c r="H172" s="7" t="inlineStr"/>
       <c r="I172" s="8" t="inlineStr">
         <is>
           <t>Class 3</t>
@@ -5508,28 +5508,28 @@
           <t>Class 4 (MATH)</t>
         </is>
       </c>
-      <c r="C176" s="7" t="inlineStr"/>
+      <c r="C176" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (MATH)</t>
+        </is>
+      </c>
       <c r="D176" s="7" t="inlineStr">
         <is>
           <t>Class 2 (MATH)</t>
         </is>
       </c>
-      <c r="E176" s="7" t="inlineStr">
+      <c r="E176" s="7" t="inlineStr"/>
+      <c r="F176" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (MATH)</t>
+        </is>
+      </c>
+      <c r="G176" s="7" t="inlineStr">
         <is>
           <t>Class 3 (MATH)</t>
         </is>
       </c>
-      <c r="F176" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (MATH)</t>
-        </is>
-      </c>
-      <c r="G176" s="7" t="inlineStr"/>
-      <c r="H176" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (MATH)</t>
-        </is>
-      </c>
+      <c r="H176" s="7" t="inlineStr"/>
       <c r="I176" s="8" t="inlineStr">
         <is>
           <t>Class 4</t>
@@ -5547,24 +5547,28 @@
           <t>Class 4 (MATH)</t>
         </is>
       </c>
-      <c r="C177" s="7" t="inlineStr">
+      <c r="C177" s="7" t="inlineStr"/>
+      <c r="D177" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (MATH)</t>
+        </is>
+      </c>
+      <c r="E177" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (MATH)</t>
+        </is>
+      </c>
+      <c r="F177" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (MATH)</t>
+        </is>
+      </c>
+      <c r="G177" s="7" t="inlineStr">
         <is>
           <t>Class 3 (MATH)</t>
         </is>
       </c>
-      <c r="D177" s="7" t="inlineStr"/>
-      <c r="E177" s="7" t="inlineStr"/>
-      <c r="F177" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (MATH)</t>
-        </is>
-      </c>
-      <c r="G177" s="7" t="inlineStr"/>
-      <c r="H177" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (MATH)</t>
-        </is>
-      </c>
+      <c r="H177" s="7" t="inlineStr"/>
       <c r="I177" s="8" t="inlineStr">
         <is>
           <t>Class 4</t>
@@ -5582,28 +5586,28 @@
           <t>Class 4 (MATH)</t>
         </is>
       </c>
-      <c r="C178" s="7" t="inlineStr"/>
+      <c r="C178" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (MATH)</t>
+        </is>
+      </c>
       <c r="D178" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (MATH)</t>
-        </is>
-      </c>
-      <c r="E178" s="7" t="inlineStr">
+          <t>Class 3 (MATH)</t>
+        </is>
+      </c>
+      <c r="E178" s="7" t="inlineStr"/>
+      <c r="F178" s="7" t="inlineStr">
         <is>
           <t>Class 5 (MATH)</t>
         </is>
       </c>
-      <c r="F178" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (MATH)</t>
-        </is>
-      </c>
-      <c r="G178" s="7" t="inlineStr"/>
-      <c r="H178" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (MATH)</t>
-        </is>
-      </c>
+      <c r="G178" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (MATH)</t>
+        </is>
+      </c>
+      <c r="H178" s="7" t="inlineStr"/>
       <c r="I178" s="8" t="inlineStr">
         <is>
           <t>Class 4</t>
@@ -5621,24 +5625,24 @@
           <t>Class 4 (MATH)</t>
         </is>
       </c>
-      <c r="C179" s="7" t="inlineStr"/>
+      <c r="C179" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (MATH)</t>
+        </is>
+      </c>
       <c r="D179" s="7" t="inlineStr">
         <is>
-          <t>Class 3 (MATH)</t>
-        </is>
-      </c>
-      <c r="E179" s="7" t="inlineStr">
+          <t>Class 2 (MATH)</t>
+        </is>
+      </c>
+      <c r="E179" s="7" t="inlineStr"/>
+      <c r="F179" s="7" t="inlineStr"/>
+      <c r="G179" s="7" t="inlineStr"/>
+      <c r="H179" s="7" t="inlineStr">
         <is>
           <t>Class 5 (MATH)</t>
         </is>
       </c>
-      <c r="F179" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (MATH)</t>
-        </is>
-      </c>
-      <c r="G179" s="7" t="inlineStr"/>
-      <c r="H179" s="7" t="inlineStr"/>
       <c r="I179" s="8" t="inlineStr">
         <is>
           <t>Class 4</t>
@@ -5656,28 +5660,28 @@
           <t>Class 4 (MATH)</t>
         </is>
       </c>
-      <c r="C180" s="7" t="inlineStr"/>
+      <c r="C180" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (MATH)</t>
+        </is>
+      </c>
       <c r="D180" s="7" t="inlineStr">
         <is>
+          <t>Class 2 (MATH)</t>
+        </is>
+      </c>
+      <c r="E180" s="7" t="inlineStr"/>
+      <c r="F180" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (MATH)</t>
+        </is>
+      </c>
+      <c r="G180" s="7" t="inlineStr">
+        <is>
           <t>Class 5 (MATH)</t>
         </is>
       </c>
-      <c r="E180" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (MATH)</t>
-        </is>
-      </c>
-      <c r="F180" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (MATH)</t>
-        </is>
-      </c>
-      <c r="G180" s="7" t="inlineStr"/>
-      <c r="H180" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (MATH)</t>
-        </is>
-      </c>
+      <c r="H180" s="7" t="inlineStr"/>
       <c r="I180" s="8" t="inlineStr">
         <is>
           <t>Class 4</t>
@@ -5703,20 +5707,16 @@
       </c>
       <c r="E181" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (MATH)</t>
-        </is>
-      </c>
-      <c r="F181" s="7" t="inlineStr">
-        <is>
           <t>Class 2 (MATH)</t>
         </is>
       </c>
-      <c r="G181" s="7" t="inlineStr"/>
-      <c r="H181" s="7" t="inlineStr">
+      <c r="F181" s="7" t="inlineStr"/>
+      <c r="G181" s="7" t="inlineStr">
         <is>
           <t>Class 5 (MATH)</t>
         </is>
       </c>
+      <c r="H181" s="7" t="inlineStr"/>
       <c r="I181" s="8" t="inlineStr">
         <is>
           <t>Class 4</t>
@@ -5796,12 +5796,16 @@
       <c r="D185" s="7" t="inlineStr"/>
       <c r="E185" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (KAR)</t>
+          <t>Class 3 (KAR)</t>
         </is>
       </c>
       <c r="F185" s="7" t="inlineStr"/>
       <c r="G185" s="7" t="inlineStr"/>
-      <c r="H185" s="7" t="inlineStr"/>
+      <c r="H185" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (KAR)</t>
+        </is>
+      </c>
       <c r="I185" s="7" t="inlineStr"/>
     </row>
     <row r="186">
@@ -5811,17 +5815,9 @@
         </is>
       </c>
       <c r="B186" s="7" t="inlineStr"/>
-      <c r="C186" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (KAR)</t>
-        </is>
-      </c>
+      <c r="C186" s="7" t="inlineStr"/>
       <c r="D186" s="7" t="inlineStr"/>
-      <c r="E186" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (KAR)</t>
-        </is>
-      </c>
+      <c r="E186" s="7" t="inlineStr"/>
       <c r="F186" s="7" t="inlineStr"/>
       <c r="G186" s="7" t="inlineStr"/>
       <c r="H186" s="7" t="inlineStr"/>
@@ -5836,18 +5832,14 @@
       <c r="B187" s="7" t="inlineStr"/>
       <c r="C187" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (KAR)</t>
+          <t>Class 9 (KAR)</t>
         </is>
       </c>
       <c r="D187" s="7" t="inlineStr"/>
       <c r="E187" s="7" t="inlineStr"/>
       <c r="F187" s="7" t="inlineStr"/>
       <c r="G187" s="7" t="inlineStr"/>
-      <c r="H187" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (KAR)</t>
-        </is>
-      </c>
+      <c r="H187" s="7" t="inlineStr"/>
       <c r="I187" s="7" t="inlineStr"/>
     </row>
     <row r="188">
@@ -5857,20 +5849,16 @@
         </is>
       </c>
       <c r="B188" s="7" t="inlineStr"/>
-      <c r="C188" s="7" t="inlineStr"/>
+      <c r="C188" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (KAR)</t>
+        </is>
+      </c>
       <c r="D188" s="7" t="inlineStr"/>
-      <c r="E188" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (KAR)</t>
-        </is>
-      </c>
+      <c r="E188" s="7" t="inlineStr"/>
       <c r="F188" s="7" t="inlineStr"/>
       <c r="G188" s="7" t="inlineStr"/>
-      <c r="H188" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (KAR)</t>
-        </is>
-      </c>
+      <c r="H188" s="7" t="inlineStr"/>
       <c r="I188" s="7" t="inlineStr"/>
     </row>
     <row r="189">
@@ -5882,9 +5870,17 @@
       <c r="B189" s="7" t="inlineStr"/>
       <c r="C189" s="7" t="inlineStr"/>
       <c r="D189" s="7" t="inlineStr"/>
-      <c r="E189" s="7" t="inlineStr"/>
+      <c r="E189" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (KAR)</t>
+        </is>
+      </c>
       <c r="F189" s="7" t="inlineStr"/>
-      <c r="G189" s="7" t="inlineStr"/>
+      <c r="G189" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (KAR)</t>
+        </is>
+      </c>
       <c r="H189" s="7" t="inlineStr"/>
       <c r="I189" s="7" t="inlineStr"/>
     </row>
@@ -5895,20 +5891,24 @@
         </is>
       </c>
       <c r="B190" s="7" t="inlineStr"/>
-      <c r="C190" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (KAR)</t>
-        </is>
-      </c>
+      <c r="C190" s="7" t="inlineStr"/>
       <c r="D190" s="7" t="inlineStr"/>
-      <c r="E190" s="7" t="inlineStr"/>
-      <c r="F190" s="7" t="inlineStr">
+      <c r="E190" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (KAR)</t>
+        </is>
+      </c>
+      <c r="F190" s="7" t="inlineStr"/>
+      <c r="G190" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (KAR)</t>
+        </is>
+      </c>
+      <c r="H190" s="7" t="inlineStr">
         <is>
           <t>Class 1 (KAR)</t>
         </is>
       </c>
-      <c r="G190" s="7" t="inlineStr"/>
-      <c r="H190" s="7" t="inlineStr"/>
       <c r="I190" s="7" t="inlineStr"/>
     </row>
     <row r="192">
@@ -5981,21 +5981,17 @@
       </c>
       <c r="B194" s="7" t="inlineStr"/>
       <c r="C194" s="7" t="inlineStr"/>
-      <c r="D194" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (P.E.T)</t>
-        </is>
-      </c>
+      <c r="D194" s="7" t="inlineStr"/>
       <c r="E194" s="7" t="inlineStr"/>
-      <c r="F194" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (P.E.T)</t>
-        </is>
-      </c>
-      <c r="G194" s="7" t="inlineStr"/>
+      <c r="F194" s="7" t="inlineStr"/>
+      <c r="G194" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (P.E.T)</t>
+        </is>
+      </c>
       <c r="H194" s="7" t="inlineStr">
         <is>
-          <t>Class 1 (P.E.T)</t>
+          <t>Class 10 (P.E.T)</t>
         </is>
       </c>
       <c r="I194" s="7" t="inlineStr"/>
@@ -6008,23 +6004,15 @@
       </c>
       <c r="B195" s="7" t="inlineStr"/>
       <c r="C195" s="7" t="inlineStr"/>
-      <c r="D195" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (P.E.T)</t>
-        </is>
-      </c>
+      <c r="D195" s="7" t="inlineStr"/>
       <c r="E195" s="7" t="inlineStr"/>
-      <c r="F195" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (P.E.T)</t>
-        </is>
-      </c>
-      <c r="G195" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (P.E.T)</t>
-        </is>
-      </c>
-      <c r="H195" s="7" t="inlineStr"/>
+      <c r="F195" s="7" t="inlineStr"/>
+      <c r="G195" s="7" t="inlineStr"/>
+      <c r="H195" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (P.E.T)</t>
+        </is>
+      </c>
       <c r="I195" s="7" t="inlineStr"/>
     </row>
     <row r="196">
@@ -6034,19 +6022,15 @@
         </is>
       </c>
       <c r="B196" s="7" t="inlineStr"/>
-      <c r="C196" s="7" t="inlineStr">
+      <c r="C196" s="7" t="inlineStr"/>
+      <c r="D196" s="7" t="inlineStr"/>
+      <c r="E196" s="7" t="inlineStr"/>
+      <c r="F196" s="7" t="inlineStr"/>
+      <c r="G196" s="7" t="inlineStr">
         <is>
           <t>Class 4 (P.E.T)</t>
         </is>
       </c>
-      <c r="D196" s="7" t="inlineStr"/>
-      <c r="E196" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (P.E.T)</t>
-        </is>
-      </c>
-      <c r="F196" s="7" t="inlineStr"/>
-      <c r="G196" s="7" t="inlineStr"/>
       <c r="H196" s="7" t="inlineStr"/>
       <c r="I196" s="7" t="inlineStr"/>
     </row>
@@ -6057,21 +6041,13 @@
         </is>
       </c>
       <c r="B197" s="7" t="inlineStr"/>
-      <c r="C197" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (P.E.T)</t>
-        </is>
-      </c>
-      <c r="D197" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (P.E.T)</t>
-        </is>
-      </c>
+      <c r="C197" s="7" t="inlineStr"/>
+      <c r="D197" s="7" t="inlineStr"/>
       <c r="E197" s="7" t="inlineStr"/>
       <c r="F197" s="7" t="inlineStr"/>
       <c r="G197" s="7" t="inlineStr">
         <is>
-          <t>Class 1 (P.E.T)</t>
+          <t>Class 5 (P.E.T)</t>
         </is>
       </c>
       <c r="H197" s="7" t="inlineStr"/>
@@ -6085,22 +6061,10 @@
       </c>
       <c r="B198" s="7" t="inlineStr"/>
       <c r="C198" s="7" t="inlineStr"/>
-      <c r="D198" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (P.E.T)</t>
-        </is>
-      </c>
-      <c r="E198" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (P.E.T)</t>
-        </is>
-      </c>
+      <c r="D198" s="7" t="inlineStr"/>
+      <c r="E198" s="7" t="inlineStr"/>
       <c r="F198" s="7" t="inlineStr"/>
-      <c r="G198" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (P.E.T)</t>
-        </is>
-      </c>
+      <c r="G198" s="7" t="inlineStr"/>
       <c r="H198" s="7" t="inlineStr"/>
       <c r="I198" s="7" t="inlineStr"/>
     </row>
@@ -6111,28 +6075,12 @@
         </is>
       </c>
       <c r="B199" s="7" t="inlineStr"/>
-      <c r="C199" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (P.E.T)</t>
-        </is>
-      </c>
-      <c r="D199" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (P.E.T)</t>
-        </is>
-      </c>
-      <c r="E199" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (P.E.T)</t>
-        </is>
-      </c>
+      <c r="C199" s="7" t="inlineStr"/>
+      <c r="D199" s="7" t="inlineStr"/>
+      <c r="E199" s="7" t="inlineStr"/>
       <c r="F199" s="7" t="inlineStr"/>
       <c r="G199" s="7" t="inlineStr"/>
-      <c r="H199" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (P.E.T)</t>
-        </is>
-      </c>
+      <c r="H199" s="7" t="inlineStr"/>
       <c r="I199" s="7" t="inlineStr"/>
     </row>
   </sheetData>
@@ -6316,7 +6264,7 @@
       <c r="J2" s="7" t="inlineStr">
         <is>
           <t>SANGEETHA
-(G.K)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="K2" s="7" t="inlineStr">
@@ -6328,7 +6276,7 @@
       <c r="L2" s="7" t="inlineStr">
         <is>
           <t>FATHIMA
-(HIN)</t>
+(G.K)</t>
         </is>
       </c>
       <c r="M2" s="7" t="inlineStr">
@@ -6357,8 +6305,8 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>BHAVANI
-(EVS)</t>
+          <t>NAGAMANI
+(TEL)</t>
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr">
@@ -6369,8 +6317,8 @@
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
-          <t>MAHESWARI
-(COMP)</t>
+          <t>TULASI
+(MATH)</t>
         </is>
       </c>
       <c r="G3" s="7" t="inlineStr">
@@ -6381,22 +6329,22 @@
       </c>
       <c r="H3" s="7" t="inlineStr">
         <is>
+          <t>MAHA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="I3" s="7" t="inlineStr">
+        <is>
+          <t>PALLAVI
+(SOC)</t>
+        </is>
+      </c>
+      <c r="J3" s="7" t="inlineStr">
+        <is>
           <t>SWATHI
 (TEL)</t>
         </is>
       </c>
-      <c r="I3" s="7" t="inlineStr">
-        <is>
-          <t>PALLAVI
-(SOC)</t>
-        </is>
-      </c>
-      <c r="J3" s="7" t="inlineStr">
-        <is>
-          <t>FATHIMA
-(HIN)</t>
-        </is>
-      </c>
       <c r="K3" s="7" t="inlineStr">
         <is>
           <t>RAVI
@@ -6412,13 +6360,13 @@
       <c r="M3" s="7" t="inlineStr">
         <is>
           <t>BHEEMA
-(CHEM)</t>
+(PHY)</t>
         </is>
       </c>
       <c r="N3" s="7" t="inlineStr">
         <is>
-          <t>RIYA
-(HIN)</t>
+          <t>SUNITHA
+(SOC)</t>
         </is>
       </c>
     </row>
@@ -6435,14 +6383,14 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>NAGAMANI
-(TEL)</t>
+          <t>SAI LAKSHMI
+(ENG)</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>SAI LAKSHMI
-(EVS)</t>
+          <t>BHAVANI
+(MATH)</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
@@ -6459,38 +6407,38 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>PALLAVI
-(SOC)</t>
+          <t>LALITHA
+(EVS)</t>
         </is>
       </c>
       <c r="I4" s="7" t="inlineStr">
+        <is>
+          <t>SWATHI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="J4" s="7" t="inlineStr">
         <is>
           <t>MAHESWARI
 (COMP)</t>
         </is>
       </c>
-      <c r="J4" s="7" t="inlineStr">
-        <is>
-          <t>LALITHA
-(BIO)</t>
-        </is>
-      </c>
       <c r="K4" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
+          <t>D.V.RAO
+(TEL)</t>
         </is>
       </c>
       <c r="L4" s="7" t="inlineStr">
         <is>
+          <t>SANGEETHA
+(MATH)</t>
+        </is>
+      </c>
+      <c r="M4" s="7" t="inlineStr">
+        <is>
           <t>BHEEMA
-(PHY)</t>
-        </is>
-      </c>
-      <c r="M4" s="7" t="inlineStr">
-        <is>
-          <t>GOWTHAM
-(MATH)</t>
+(CHEM)</t>
         </is>
       </c>
       <c r="N4" s="7" t="inlineStr">
@@ -6507,74 +6455,74 @@
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>SITHA
-(ORAL)</t>
+          <t>NAGAMANI
+(TEL)</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>SWATHI
+          <t>BHAVANI
+(EVS)</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>SAI LAKSHMI
 (HIN)</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>SAI LAKSHMI
-(EVS)</t>
-        </is>
-      </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>BHAVANI
-(G.K)</t>
+          <t>MAHESWARI
+(COMP)</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
-        <is>
-          <t>TULASI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="H5" s="7" t="inlineStr">
         <is>
           <t>MARTIAL ARTS
 (KAR)</t>
         </is>
       </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>PALLAVI
+(SOC)</t>
+        </is>
+      </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
-          <t>MAHA
+          <t>LALITHA
+(EVS)</t>
+        </is>
+      </c>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>RAVI
 (ENG)</t>
         </is>
       </c>
-      <c r="J5" s="7" t="inlineStr">
-        <is>
-          <t>LALITHA
-(PHY)</t>
-        </is>
-      </c>
       <c r="K5" s="7" t="inlineStr">
+        <is>
+          <t>FATHIMA
+(HIN)</t>
+        </is>
+      </c>
+      <c r="L5" s="7" t="inlineStr">
         <is>
           <t>SANGEETHA
 (MATH)</t>
         </is>
       </c>
-      <c r="L5" s="7" t="inlineStr">
-        <is>
-          <t>RAVI
-(GRAM)</t>
-        </is>
-      </c>
       <c r="M5" s="7" t="inlineStr">
+        <is>
+          <t>SUNITHA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="N5" s="7" t="inlineStr">
         <is>
           <t>RIYA
 (HIN)</t>
-        </is>
-      </c>
-      <c r="N5" s="7" t="inlineStr">
-        <is>
-          <t>SUNITHA
-(SOC)</t>
         </is>
       </c>
     </row>
@@ -6598,7 +6546,7 @@
       <c r="E6" s="7" t="inlineStr">
         <is>
           <t>SAI LAKSHMI
-(HIN)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
@@ -6609,14 +6557,14 @@
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
+          <t>RIYA
+(HIN)</t>
         </is>
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>LALITHA
-(EVS)</t>
+          <t>SWATHI
+(TEL)</t>
         </is>
       </c>
       <c r="I6" s="7" t="inlineStr">
@@ -6627,32 +6575,32 @@
       </c>
       <c r="J6" s="7" t="inlineStr">
         <is>
-          <t>SWATHI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="K6" s="7" t="inlineStr">
-        <is>
           <t>FATHIMA
 (HIN)</t>
         </is>
       </c>
+      <c r="K6" s="7" t="inlineStr">
+        <is>
+          <t>LALITHA
+(CHEM)</t>
+        </is>
+      </c>
       <c r="L6" s="7" t="inlineStr">
+        <is>
+          <t>SUNITHA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="M6" s="7" t="inlineStr">
         <is>
           <t>SONU
 (ENG)</t>
         </is>
       </c>
-      <c r="M6" s="7" t="inlineStr">
+      <c r="N6" s="7" t="inlineStr">
         <is>
           <t>CHALAPATHI
 (BIO)</t>
-        </is>
-      </c>
-      <c r="N6" s="7" t="inlineStr">
-        <is>
-          <t>D.V.RAO
-(TEL)</t>
         </is>
       </c>
     </row>
@@ -6663,74 +6611,74 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>SITHA
-(EVS)</t>
+          <t>P.E
+(P.E.T)</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>BHAVANI
-(EVS)</t>
+          <t>P.E
+(P.E.T)</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>P.E
+(P.E.T)</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>P.E
+(P.E.T)</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>TULASI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>P.E
+(P.E.T)</t>
+        </is>
+      </c>
+      <c r="I7" s="7" t="inlineStr">
         <is>
           <t>MAHA
 (ENG)</t>
         </is>
       </c>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>NAGAMANI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="G7" s="7" t="inlineStr">
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>PALLAVI
+(SOC)</t>
+        </is>
+      </c>
+      <c r="K7" s="7" t="inlineStr">
+        <is>
+          <t>LALITHA
+(BIO)</t>
+        </is>
+      </c>
+      <c r="L7" s="7" t="inlineStr">
+        <is>
+          <t>SONU
+(ENG)</t>
+        </is>
+      </c>
+      <c r="M7" s="7" t="inlineStr">
         <is>
           <t>RIYA
 (HIN)</t>
         </is>
       </c>
-      <c r="H7" s="7" t="inlineStr">
-        <is>
-          <t>FATHIMA
-(HIN)</t>
-        </is>
-      </c>
-      <c r="I7" s="7" t="inlineStr">
-        <is>
-          <t>SWATHI
+      <c r="N7" s="7" t="inlineStr">
+        <is>
+          <t>D.V.RAO
 (TEL)</t>
-        </is>
-      </c>
-      <c r="J7" s="7" t="inlineStr">
-        <is>
-          <t>PALLAVI
-(SOC)</t>
-        </is>
-      </c>
-      <c r="K7" s="7" t="inlineStr">
-        <is>
-          <t>SANGEETHA
-(MATH)</t>
-        </is>
-      </c>
-      <c r="L7" s="7" t="inlineStr">
-        <is>
-          <t>SUNITHA
-(SOC)</t>
-        </is>
-      </c>
-      <c r="M7" s="7" t="inlineStr">
-        <is>
-          <t>SONU
-(ENG)</t>
-        </is>
-      </c>
-      <c r="N7" s="7" t="inlineStr">
-        <is>
-          <t>CHALAPATHI
-(BIO)</t>
         </is>
       </c>
     </row>
@@ -6741,74 +6689,74 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
+          <t>SITHA
+(EVS)</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>SAI LAKSHMI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>MAHA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
           <t>NAGAMANI
 (TEL)</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>SAI LAKSHMI
-(ENG)</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>PALLAVI
+(SOC)</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>MARTIAL ARTS
+(KAR)</t>
+        </is>
+      </c>
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>FATHIMA
+(HIN)</t>
+        </is>
+      </c>
+      <c r="J8" s="7" t="inlineStr">
         <is>
           <t>P.E
 (P.E.T)</t>
         </is>
       </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>TULASI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="G8" s="7" t="inlineStr">
-        <is>
-          <t>PALLAVI
-(SOC)</t>
-        </is>
-      </c>
-      <c r="H8" s="7" t="inlineStr">
-        <is>
-          <t>MAHA
-(ENG)</t>
-        </is>
-      </c>
-      <c r="I8" s="7" t="inlineStr">
-        <is>
-          <t>LALITHA
-(EVS)</t>
-        </is>
-      </c>
-      <c r="J8" s="7" t="inlineStr">
-        <is>
-          <t>RAVI
-(ENG)</t>
-        </is>
-      </c>
       <c r="K8" s="7" t="inlineStr">
         <is>
-          <t>D.V.RAO
-(TEL)</t>
+          <t>P.E
+(P.E.T)</t>
         </is>
       </c>
       <c r="L8" s="7" t="inlineStr">
         <is>
-          <t>CHALAPATHI
-(BIO)</t>
+          <t>P.E
+(P.E.T)</t>
         </is>
       </c>
       <c r="M8" s="7" t="inlineStr">
         <is>
-          <t>SUNITHA
-(SOC)</t>
+          <t>P.E
+(P.E.T)</t>
         </is>
       </c>
       <c r="N8" s="7" t="inlineStr">
         <is>
-          <t>SONU
-(ENG)</t>
+          <t>P.E
+(P.E.T)</t>
         </is>
       </c>
     </row>
@@ -6884,9 +6832,10 @@
 (CLASS)</t>
         </is>
       </c>
-      <c r="N9" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
+      <c r="N9" s="8" t="inlineStr">
+        <is>
+          <t>SONU
+(ENG)</t>
         </is>
       </c>
     </row>
@@ -6902,13 +6851,13 @@
       <c r="C10" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(ENG)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
           <t>BHAVANI
-(MATH)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
@@ -6944,7 +6893,7 @@
       <c r="J10" s="7" t="inlineStr">
         <is>
           <t>SANGEETHA
-(MATH)</t>
+(G.K)</t>
         </is>
       </c>
       <c r="K10" s="7" t="inlineStr">
@@ -6967,8 +6916,8 @@
       </c>
       <c r="N10" s="7" t="inlineStr">
         <is>
-          <t>RIYA
-(HIN)</t>
+          <t>BHEEMA
+(CHEM)</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6929,7 @@
       <c r="C11" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(EVS)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
@@ -6991,40 +6940,40 @@
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
+          <t>SAI LAKSHMI
+(EVS)</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
           <t>NAGAMANI
-(G.K)</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>SAI LAKSHMI
-(HIN)</t>
+(TEL)</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>TULASI
-(MATH)</t>
+          <t>MAHA
+(ENG)</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>LALITHA
+(EVS)</t>
+        </is>
+      </c>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>PALLAVI
+(SOC)</t>
+        </is>
+      </c>
+      <c r="J11" s="7" t="inlineStr">
         <is>
           <t>FATHIMA
 (HIN)</t>
         </is>
       </c>
-      <c r="I11" s="7" t="inlineStr">
-        <is>
-          <t>LALITHA
-(EVS)</t>
-        </is>
-      </c>
-      <c r="J11" s="7" t="inlineStr">
-        <is>
-          <t>MARTIAL ARTS
-(KAR)</t>
-        </is>
-      </c>
       <c r="K11" s="7" t="inlineStr">
         <is>
           <t>SANGEETHA
@@ -7033,20 +6982,20 @@
       </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
+          <t>RAVI
+(GRAM)</t>
+        </is>
+      </c>
+      <c r="M11" s="7" t="inlineStr">
+        <is>
+          <t>GOWTHAM
+(MATH)</t>
+        </is>
+      </c>
+      <c r="N11" s="7" t="inlineStr">
+        <is>
           <t>BHEEMA
 (PHY)</t>
-        </is>
-      </c>
-      <c r="M11" s="7" t="inlineStr">
-        <is>
-          <t>MARTIAL ARTS
-(KAR)</t>
-        </is>
-      </c>
-      <c r="N11" s="7" t="inlineStr">
-        <is>
-          <t>GOWTHAM
-(MATH)</t>
         </is>
       </c>
     </row>
@@ -7058,13 +7007,13 @@
       <c r="C12" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(ENG)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
           <t>BHAVANI
-(MATH)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
@@ -7075,8 +7024,8 @@
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>MAHA
-(ENG)</t>
+          <t>TULASI
+(MATH)</t>
         </is>
       </c>
       <c r="G12" s="7" t="inlineStr">
@@ -7087,44 +7036,44 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>MAHESWARI
-(COMP)</t>
-        </is>
-      </c>
-      <c r="I12" s="7" t="inlineStr">
-        <is>
-          <t>SWATHI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="J12" s="7" t="inlineStr">
-        <is>
           <t>FATHIMA
 (HIN)</t>
         </is>
       </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>LALITHA
+(EVS)</t>
+        </is>
+      </c>
+      <c r="J12" s="7" t="inlineStr">
+        <is>
+          <t>RAVI
+(ENG)</t>
+        </is>
+      </c>
       <c r="K12" s="7" t="inlineStr">
         <is>
-          <t>LALITHA
-(PHY)</t>
+          <t>D.V.RAO
+(TEL)</t>
         </is>
       </c>
       <c r="L12" s="7" t="inlineStr">
+        <is>
+          <t>SANGEETHA
+(MATH)</t>
+        </is>
+      </c>
+      <c r="M12" s="7" t="inlineStr">
         <is>
           <t>BHEEMA
 (CHEM)</t>
         </is>
       </c>
-      <c r="M12" s="7" t="inlineStr">
+      <c r="N12" s="7" t="inlineStr">
         <is>
           <t>GOWTHAM
 (MATH)</t>
-        </is>
-      </c>
-      <c r="N12" s="7" t="inlineStr">
-        <is>
-          <t>P.E
-(P.E.T)</t>
         </is>
       </c>
     </row>
@@ -7141,44 +7090,44 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
+          <t>SAI LAKSHMI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
           <t>BHAVANI
-(EVS)</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>MAHESWARI
-(COMP)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>SAI LAKSHMI
-(EVS)</t>
+          <t>MAHA
+(ENG)</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>MAHA
-(GRAM)</t>
+          <t>RIYA
+(HIN)</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
+          <t>TULASI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>SWATHI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
           <t>LALITHA
-(EVS)</t>
-        </is>
-      </c>
-      <c r="I13" s="7" t="inlineStr">
-        <is>
-          <t>SANGEETHA
-(G.K)</t>
-        </is>
-      </c>
-      <c r="J13" s="7" t="inlineStr">
-        <is>
-          <t>PALLAVI
-(SOC)</t>
+(BIO)</t>
         </is>
       </c>
       <c r="K13" s="7" t="inlineStr">
@@ -7193,16 +7142,15 @@
 (TEL)</t>
         </is>
       </c>
-      <c r="M13" s="7" t="inlineStr">
+      <c r="M13" s="12" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+      <c r="N13" s="7" t="inlineStr">
         <is>
           <t>SUNITHA
 (SOC)</t>
-        </is>
-      </c>
-      <c r="N13" s="7" t="inlineStr">
-        <is>
-          <t>MARTIAL ARTS
-(KAR)</t>
         </is>
       </c>
     </row>
@@ -7213,14 +7161,14 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
+          <t>SITHA
+(ENG)</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>SAI LAKSHMI
-(ENG)</t>
+          <t>NAGAMANI
+(TEL)</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
@@ -7231,8 +7179,8 @@
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>NAGAMANI
-(TEL)</t>
+          <t>SAI LAKSHMI
+(EVS)</t>
         </is>
       </c>
       <c r="G14" s="7" t="inlineStr">
@@ -7243,44 +7191,44 @@
       </c>
       <c r="H14" s="7" t="inlineStr">
         <is>
+          <t>SWATHI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>TULASI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="J14" s="7" t="inlineStr">
+        <is>
           <t>PALLAVI
 (SOC)</t>
         </is>
       </c>
-      <c r="I14" s="7" t="inlineStr">
-        <is>
-          <t>TULASI
+      <c r="K14" s="7" t="inlineStr">
+        <is>
+          <t>SANGEETHA
 (MATH)</t>
         </is>
       </c>
-      <c r="J14" s="7" t="inlineStr">
-        <is>
-          <t>RAVI
-(ENG)</t>
-        </is>
-      </c>
-      <c r="K14" s="7" t="inlineStr">
-        <is>
-          <t>SANGEETHA
-(COMP)</t>
-        </is>
-      </c>
       <c r="L14" s="7" t="inlineStr">
+        <is>
+          <t>SUNITHA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="M14" s="7" t="inlineStr">
         <is>
           <t>SONU
 (ENG)</t>
         </is>
       </c>
-      <c r="M14" s="7" t="inlineStr">
+      <c r="N14" s="7" t="inlineStr">
         <is>
           <t>RIYA
 (HIN)</t>
-        </is>
-      </c>
-      <c r="N14" s="7" t="inlineStr">
-        <is>
-          <t>D.V.RAO
-(TEL)</t>
         </is>
       </c>
     </row>
@@ -7292,31 +7240,31 @@
       <c r="C15" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(ENG)</t>
+(ORAL)</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
+          <t>BHAVANI
+(EVS)</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
           <t>NAGAMANI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>P.E
-(P.E.T)</t>
+(G.K)</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
+          <t>SAI LAKSHMI
+(HIN)</t>
         </is>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>RIYA
-(HIN)</t>
+          <t>TULASI
+(MATH)</t>
         </is>
       </c>
       <c r="H15" s="7" t="inlineStr">
@@ -7327,38 +7275,38 @@
       </c>
       <c r="I15" s="7" t="inlineStr">
         <is>
-          <t>PALLAVI
-(SOC)</t>
+          <t>MAHESWARI
+(COMP)</t>
         </is>
       </c>
       <c r="J15" s="7" t="inlineStr">
-        <is>
-          <t>SWATHI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="K15" s="7" t="inlineStr">
         <is>
           <t>LALITHA
 (CHEM)</t>
         </is>
       </c>
+      <c r="K15" s="7" t="inlineStr">
+        <is>
+          <t>FATHIMA
+(G.K)</t>
+        </is>
+      </c>
       <c r="L15" s="7" t="inlineStr">
+        <is>
+          <t>SONU
+(ENG)</t>
+        </is>
+      </c>
+      <c r="M15" s="7" t="inlineStr">
         <is>
           <t>SUNITHA
 (SOC)</t>
         </is>
       </c>
-      <c r="M15" s="7" t="inlineStr">
-        <is>
-          <t>CHALAPATHI
-(BIO)</t>
-        </is>
-      </c>
       <c r="N15" s="7" t="inlineStr">
         <is>
-          <t>SONU
-(ENG)</t>
+          <t>D.V.RAO
+(TEL)</t>
         </is>
       </c>
     </row>
@@ -7369,58 +7317,58 @@
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>SITHA
-(ORAL)</t>
+          <t>P.E
+(P.E.T)</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>SAI LAKSHMI
-(ENG)</t>
+          <t>P.E
+(P.E.T)</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>BHAVANI
-(MATH)</t>
+          <t>P.E
+(P.E.T)</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>TULASI
-(MATH)</t>
+          <t>P.E
+(P.E.T)</t>
         </is>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>MAHA
-(ENG)</t>
+          <t>P.E
+(P.E.T)</t>
         </is>
       </c>
       <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>PALLAVI
+(SOC)</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>P.E
+(P.E.T)</t>
+        </is>
+      </c>
+      <c r="J16" s="7" t="inlineStr">
         <is>
           <t>SWATHI
 (TEL)</t>
         </is>
       </c>
-      <c r="I16" s="7" t="inlineStr">
+      <c r="K16" s="7" t="inlineStr">
         <is>
           <t>FATHIMA
 (HIN)</t>
         </is>
       </c>
-      <c r="J16" s="7" t="inlineStr">
-        <is>
-          <t>LALITHA
-(CHEM)</t>
-        </is>
-      </c>
-      <c r="K16" s="7" t="inlineStr">
-        <is>
-          <t>D.V.RAO
-(TEL)</t>
-        </is>
-      </c>
       <c r="L16" s="7" t="inlineStr">
         <is>
           <t>CHALAPATHI
@@ -7429,14 +7377,14 @@
       </c>
       <c r="M16" s="7" t="inlineStr">
         <is>
+          <t>RIYA
+(HIN)</t>
+        </is>
+      </c>
+      <c r="N16" s="7" t="inlineStr">
+        <is>
           <t>SONU
 (ENG)</t>
-        </is>
-      </c>
-      <c r="N16" s="7" t="inlineStr">
-        <is>
-          <t>SUNITHA
-(SOC)</t>
         </is>
       </c>
     </row>
@@ -7542,7 +7490,7 @@
       <c r="E18" s="7" t="inlineStr">
         <is>
           <t>NAGAMANI
-(TEL)</t>
+(G.K)</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
@@ -7593,9 +7541,10 @@
 (TEL)</t>
         </is>
       </c>
-      <c r="N18" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
+      <c r="N18" s="7" t="inlineStr">
+        <is>
+          <t>RIYA
+(HIN)</t>
         </is>
       </c>
     </row>
@@ -7607,67 +7556,67 @@
       <c r="C19" s="7" t="inlineStr">
         <is>
           <t>SITHA
+(EVS)</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>SWATHI
+(HIN)</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>BHAVANI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>SAI LAKSHMI
+(EVS)</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>TULASI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>MAHA
 (ENG)</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>BHAVANI
-(EVS)</t>
-        </is>
-      </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>MAHESWARI
-(COMP)</t>
-        </is>
-      </c>
-      <c r="F19" s="7" t="inlineStr">
-        <is>
-          <t>SAI LAKSHMI
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>FATHIMA
 (HIN)</t>
         </is>
       </c>
-      <c r="G19" s="7" t="inlineStr">
-        <is>
-          <t>P.E
-(P.E.T)</t>
-        </is>
-      </c>
-      <c r="H19" s="7" t="inlineStr">
-        <is>
-          <t>P.E
-(P.E.T)</t>
-        </is>
-      </c>
-      <c r="I19" s="7" t="inlineStr">
+      <c r="J19" s="7" t="inlineStr">
+        <is>
+          <t>RAVI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="K19" s="7" t="inlineStr">
+        <is>
+          <t>LALITHA
+(PHY)</t>
+        </is>
+      </c>
+      <c r="L19" s="7" t="inlineStr">
+        <is>
+          <t>BHEEMA
+(CHEM)</t>
+        </is>
+      </c>
+      <c r="M19" s="7" t="inlineStr">
         <is>
           <t>MARTIAL ARTS
 (KAR)</t>
-        </is>
-      </c>
-      <c r="J19" s="7" t="inlineStr">
-        <is>
-          <t>SWATHI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="K19" s="7" t="inlineStr">
-        <is>
-          <t>D.V.RAO
-(TEL)</t>
-        </is>
-      </c>
-      <c r="L19" s="7" t="inlineStr">
-        <is>
-          <t>SANGEETHA
-(COMP)</t>
-        </is>
-      </c>
-      <c r="M19" s="7" t="inlineStr">
-        <is>
-          <t>BHEEMA
-(PHY)</t>
         </is>
       </c>
       <c r="N19" s="7" t="inlineStr">
@@ -7685,57 +7634,57 @@
       <c r="C20" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(EVS)</t>
+(ORAL)</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>SWATHI
-(HIN)</t>
+          <t>SAI LAKSHMI
+(ENG)</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>SAI LAKSHMI
-(EVS)</t>
+          <t>BHAVANI
+(MATH)</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>NAGAMANI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
         <is>
           <t>TULASI
 (MATH)</t>
         </is>
       </c>
-      <c r="G20" s="7" t="inlineStr">
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>FATHIMA
+(HIN)</t>
+        </is>
+      </c>
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>LALITHA
+(EVS)</t>
+        </is>
+      </c>
+      <c r="J20" s="7" t="inlineStr">
         <is>
           <t>PALLAVI
 (SOC)</t>
         </is>
       </c>
-      <c r="H20" s="7" t="inlineStr">
-        <is>
-          <t>MAHA
-(GRAM)</t>
-        </is>
-      </c>
-      <c r="I20" s="7" t="inlineStr">
-        <is>
-          <t>LALITHA
-(EVS)</t>
-        </is>
-      </c>
-      <c r="J20" s="7" t="inlineStr">
+      <c r="K20" s="7" t="inlineStr">
         <is>
           <t>RAVI
 (ENG)</t>
         </is>
       </c>
-      <c r="K20" s="7" t="inlineStr">
-        <is>
-          <t>FATHIMA
-(HIN)</t>
-        </is>
-      </c>
       <c r="L20" s="7" t="inlineStr">
         <is>
           <t>SANGEETHA
@@ -7748,9 +7697,10 @@
 (MATH)</t>
         </is>
       </c>
-      <c r="N20" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
+      <c r="N20" s="7" t="inlineStr">
+        <is>
+          <t>BHEEMA
+(CHEM)</t>
         </is>
       </c>
     </row>
@@ -7761,74 +7711,73 @@
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>BHAVANI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="E21" s="7" t="inlineStr">
-        <is>
-          <t>SAI LAKSHMI
-(HIN)</t>
-        </is>
-      </c>
-      <c r="F21" s="7" t="inlineStr">
-        <is>
           <t>NAGAMANI
 (TEL)</t>
         </is>
       </c>
-      <c r="G21" s="7" t="inlineStr">
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>SAI LAKSHMI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>MAHESWARI
+(COMP)</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
         <is>
           <t>MAHA
 (ENG)</t>
         </is>
       </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>LALITHA
+(EVS)</t>
+        </is>
+      </c>
       <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>SWATHI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="I21" s="7" t="inlineStr">
         <is>
           <t>PALLAVI
 (SOC)</t>
         </is>
       </c>
-      <c r="I21" s="7" t="inlineStr">
-        <is>
-          <t>TULASI
-(MATH)</t>
-        </is>
-      </c>
       <c r="J21" s="7" t="inlineStr">
         <is>
-          <t>MAHESWARI
+          <t>RAVI
+(GRAM)</t>
+        </is>
+      </c>
+      <c r="K21" s="7" t="inlineStr">
+        <is>
+          <t>D.V.RAO
+(TEL)</t>
+        </is>
+      </c>
+      <c r="L21" s="7" t="inlineStr">
+        <is>
+          <t>SANGEETHA
 (COMP)</t>
         </is>
       </c>
-      <c r="K21" s="7" t="inlineStr">
-        <is>
-          <t>LALITHA
-(CHEM)</t>
-        </is>
-      </c>
-      <c r="L21" s="7" t="inlineStr">
+      <c r="M21" s="12" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+      <c r="N21" s="7" t="inlineStr">
         <is>
           <t>SUNITHA
 (SOC)</t>
-        </is>
-      </c>
-      <c r="M21" s="7" t="inlineStr">
-        <is>
-          <t>P.E
-(P.E.T)</t>
-        </is>
-      </c>
-      <c r="N21" s="7" t="inlineStr">
-        <is>
-          <t>D.V.RAO
-(TEL)</t>
         </is>
       </c>
     </row>
@@ -7840,13 +7789,13 @@
       <c r="C22" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(ENG)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>SAI LAKSHMI
-(ENG)</t>
+          <t>BHAVANI
+(EVS)</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
@@ -7857,28 +7806,28 @@
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
+          <t>SAI LAKSHMI
+(EVS)</t>
+        </is>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>PALLAVI
+(SOC)</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>LALITHA
+(EVS)</t>
+        </is>
+      </c>
+      <c r="I22" s="7" t="inlineStr">
+        <is>
           <t>TULASI
 (MATH)</t>
         </is>
       </c>
-      <c r="G22" s="7" t="inlineStr">
-        <is>
-          <t>RIYA
-(HIN)</t>
-        </is>
-      </c>
-      <c r="H22" s="7" t="inlineStr">
-        <is>
-          <t>SWATHI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="I22" s="7" t="inlineStr">
-        <is>
-          <t>PALLAVI
-(SOC)</t>
-        </is>
-      </c>
       <c r="J22" s="7" t="inlineStr">
         <is>
           <t>FATHIMA
@@ -7887,14 +7836,14 @@
       </c>
       <c r="K22" s="7" t="inlineStr">
         <is>
-          <t>LALITHA
-(BIO)</t>
+          <t>RAVI
+(GRAM)</t>
         </is>
       </c>
       <c r="L22" s="7" t="inlineStr">
         <is>
-          <t>SANGEETHA
-(MATH)</t>
+          <t>SONU
+(ENG)</t>
         </is>
       </c>
       <c r="M22" s="7" t="inlineStr">
@@ -7905,8 +7854,8 @@
       </c>
       <c r="N22" s="7" t="inlineStr">
         <is>
-          <t>SONU
-(ENG)</t>
+          <t>D.V.RAO
+(TEL)</t>
         </is>
       </c>
     </row>
@@ -7917,56 +7866,56 @@
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>SITHA
-(ORAL)</t>
+          <t>P.E
+(P.E.T)</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>BHAVANI
-(EVS)</t>
+          <t>NAGAMANI
+(TEL)</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>NAGAMANI
-(G.K)</t>
+          <t>P.E
+(P.E.T)</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
+          <t>P.E
+(P.E.T)</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
           <t>MAHA
-(ENG)</t>
-        </is>
-      </c>
-      <c r="G23" s="7" t="inlineStr">
-        <is>
-          <t>MAHESWARI
+(GRAM)</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>P.E
+(P.E.T)</t>
+        </is>
+      </c>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>TULASI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="J23" s="7" t="inlineStr">
+        <is>
+          <t>SWATHI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="K23" s="7" t="inlineStr">
+        <is>
+          <t>SANGEETHA
 (COMP)</t>
-        </is>
-      </c>
-      <c r="H23" s="7" t="inlineStr">
-        <is>
-          <t>LALITHA
-(EVS)</t>
-        </is>
-      </c>
-      <c r="I23" s="7" t="inlineStr">
-        <is>
-          <t>FATHIMA
-(HIN)</t>
-        </is>
-      </c>
-      <c r="J23" s="7" t="inlineStr">
-        <is>
-          <t>PALLAVI
-(SOC)</t>
-        </is>
-      </c>
-      <c r="K23" s="7" t="inlineStr">
-        <is>
-          <t>RAVI
-(ENG)</t>
         </is>
       </c>
       <c r="L23" s="7" t="inlineStr">
@@ -7977,14 +7926,14 @@
       </c>
       <c r="M23" s="7" t="inlineStr">
         <is>
+          <t>SUNITHA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="N23" s="7" t="inlineStr">
+        <is>
           <t>SONU
 (ENG)</t>
-        </is>
-      </c>
-      <c r="N23" s="7" t="inlineStr">
-        <is>
-          <t>SUNITHA
-(SOC)</t>
         </is>
       </c>
     </row>
@@ -7996,39 +7945,39 @@
       <c r="C24" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(ENG)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>BHAVANI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
         <is>
           <t>NAGAMANI
 (TEL)</t>
         </is>
       </c>
-      <c r="E24" s="7" t="inlineStr">
+      <c r="F24" s="7" t="inlineStr">
         <is>
           <t>SAI LAKSHMI
-(EVS)</t>
-        </is>
-      </c>
-      <c r="F24" s="7" t="inlineStr">
-        <is>
-          <t>TULASI
-(MATH)</t>
+(HIN)</t>
         </is>
       </c>
       <c r="G24" s="7" t="inlineStr">
-        <is>
-          <t>LALITHA
-(EVS)</t>
-        </is>
-      </c>
-      <c r="H24" s="7" t="inlineStr">
         <is>
           <t>MAHA
 (ENG)</t>
         </is>
       </c>
+      <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>PALLAVI
+(SOC)</t>
+        </is>
+      </c>
       <c r="I24" s="7" t="inlineStr">
         <is>
           <t>SWATHI
@@ -8043,26 +7992,26 @@
       </c>
       <c r="K24" s="7" t="inlineStr">
         <is>
-          <t>MARTIAL ARTS
-(KAR)</t>
+          <t>LALITHA
+(BIO)</t>
         </is>
       </c>
       <c r="L24" s="7" t="inlineStr">
+        <is>
+          <t>SUNITHA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="M24" s="7" t="inlineStr">
         <is>
           <t>SONU
 (ENG)</t>
         </is>
       </c>
-      <c r="M24" s="7" t="inlineStr">
-        <is>
-          <t>SUNITHA
-(SOC)</t>
-        </is>
-      </c>
       <c r="N24" s="7" t="inlineStr">
         <is>
-          <t>RIYA
-(HIN)</t>
+          <t>CHALAPATHI
+(BIO)</t>
         </is>
       </c>
     </row>
@@ -8156,7 +8105,7 @@
       <c r="C26" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(ENG)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
@@ -8221,8 +8170,8 @@
       </c>
       <c r="N26" s="7" t="inlineStr">
         <is>
-          <t>GOWTHAM
-(MATH)</t>
+          <t>SUNITHA
+(SOC)</t>
         </is>
       </c>
     </row>
@@ -8234,39 +8183,39 @@
       <c r="C27" s="7" t="inlineStr">
         <is>
           <t>SITHA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>SWATHI
+(HIN)</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>SAI LAKSHMI
+(EVS)</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>TULASI
 (MATH)</t>
         </is>
       </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>BHAVANI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="E27" s="7" t="inlineStr">
-        <is>
-          <t>SAI LAKSHMI
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>RIYA
 (HIN)</t>
         </is>
       </c>
-      <c r="F27" s="7" t="inlineStr">
-        <is>
-          <t>P.E
-(P.E.T)</t>
-        </is>
-      </c>
-      <c r="G27" s="7" t="inlineStr">
+      <c r="H27" s="7" t="inlineStr">
         <is>
           <t>LALITHA
 (EVS)</t>
         </is>
       </c>
-      <c r="H27" s="7" t="inlineStr">
-        <is>
-          <t>MAHA
-(ENG)</t>
-        </is>
-      </c>
       <c r="I27" s="7" t="inlineStr">
         <is>
           <t>FATHIMA
@@ -8281,14 +8230,14 @@
       </c>
       <c r="K27" s="7" t="inlineStr">
         <is>
-          <t>RAVI
-(ENG)</t>
+          <t>SANGEETHA
+(MATH)</t>
         </is>
       </c>
       <c r="L27" s="7" t="inlineStr">
         <is>
-          <t>SUNITHA
-(SOC)</t>
+          <t>BHEEMA
+(PHY)</t>
         </is>
       </c>
       <c r="M27" s="7" t="inlineStr">
@@ -8299,8 +8248,8 @@
       </c>
       <c r="N27" s="7" t="inlineStr">
         <is>
-          <t>BHEEMA
-(PHY)</t>
+          <t>MARTIAL ARTS
+(KAR)</t>
         </is>
       </c>
     </row>
@@ -8312,33 +8261,33 @@
       <c r="C28" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(EVS)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
+          <t>BHAVANI
+(MATH)</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>SAI LAKSHMI
+(HIN)</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>TULASI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="G28" s="7" t="inlineStr">
         <is>
           <t>MAHA
 (ENG)</t>
         </is>
       </c>
-      <c r="F28" s="7" t="inlineStr">
-        <is>
-          <t>NAGAMANI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="G28" s="7" t="inlineStr">
-        <is>
-          <t>TULASI
-(MATH)</t>
-        </is>
-      </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
           <t>FATHIMA
@@ -8347,38 +8296,38 @@
       </c>
       <c r="I28" s="7" t="inlineStr">
         <is>
-          <t>SWATHI
-(TEL)</t>
+          <t>LALITHA
+(EVS)</t>
         </is>
       </c>
       <c r="J28" s="7" t="inlineStr">
         <is>
-          <t>LALITHA
-(BIO)</t>
+          <t>SANGEETHA
+(MATH)</t>
         </is>
       </c>
       <c r="K28" s="7" t="inlineStr">
+        <is>
+          <t>RAVI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="L28" s="7" t="inlineStr">
         <is>
           <t>D.V.RAO
 (TEL)</t>
         </is>
       </c>
-      <c r="L28" s="7" t="inlineStr">
-        <is>
-          <t>SANGEETHA
-(MATH)</t>
-        </is>
-      </c>
       <c r="M28" s="7" t="inlineStr">
+        <is>
+          <t>BHEEMA
+(PHY)</t>
+        </is>
+      </c>
+      <c r="N28" s="7" t="inlineStr">
         <is>
           <t>GOWTHAM
 (MATH)</t>
-        </is>
-      </c>
-      <c r="N28" s="7" t="inlineStr">
-        <is>
-          <t>BHEEMA
-(CHEM)</t>
         </is>
       </c>
     </row>
@@ -8389,68 +8338,68 @@
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>NAGAMANI
-(TEL)</t>
+          <t>SITHA
+(MATH)</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
-        <is>
-          <t>SAI LAKSHMI
-(ENG)</t>
-        </is>
-      </c>
-      <c r="E29" s="7" t="inlineStr">
         <is>
           <t>BHAVANI
 (MATH)</t>
         </is>
       </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>MAHA
+(ENG)</t>
+        </is>
+      </c>
       <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>SAI LAKSHMI
+(HIN)</t>
+        </is>
+      </c>
+      <c r="G29" s="7" t="inlineStr">
         <is>
           <t>MAHESWARI
 (COMP)</t>
         </is>
       </c>
-      <c r="G29" s="7" t="inlineStr">
+      <c r="H29" s="7" t="inlineStr">
+        <is>
+          <t>PALLAVI
+(SOC)</t>
+        </is>
+      </c>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>SWATHI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="J29" s="7" t="inlineStr">
+        <is>
+          <t>RAVI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="K29" s="7" t="inlineStr">
+        <is>
+          <t>LALITHA
+(PHY)</t>
+        </is>
+      </c>
+      <c r="L29" s="7" t="inlineStr">
+        <is>
+          <t>SUNITHA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="M29" s="7" t="inlineStr">
         <is>
           <t>RIYA
 (HIN)</t>
-        </is>
-      </c>
-      <c r="H29" s="7" t="inlineStr">
-        <is>
-          <t>PALLAVI
-(SOC)</t>
-        </is>
-      </c>
-      <c r="I29" s="7" t="inlineStr">
-        <is>
-          <t>TULASI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="J29" s="7" t="inlineStr">
-        <is>
-          <t>SWATHI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="K29" s="7" t="inlineStr">
-        <is>
-          <t>LALITHA
-(BIO)</t>
-        </is>
-      </c>
-      <c r="L29" s="7" t="inlineStr">
-        <is>
-          <t>MARTIAL ARTS
-(KAR)</t>
-        </is>
-      </c>
-      <c r="M29" s="7" t="inlineStr">
-        <is>
-          <t>SUNITHA
-(SOC)</t>
         </is>
       </c>
       <c r="N29" s="7" t="inlineStr">
@@ -8468,63 +8417,63 @@
       <c r="C30" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(MATH)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
+          <t>NAGAMANI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
           <t>SAI LAKSHMI
+(EVS)</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>MAHA
 (ENG)</t>
         </is>
       </c>
-      <c r="E30" s="7" t="inlineStr">
-        <is>
-          <t>BHAVANI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="F30" s="7" t="inlineStr">
-        <is>
-          <t>MAHA
-(GRAM)</t>
-        </is>
-      </c>
       <c r="G30" s="7" t="inlineStr">
+        <is>
+          <t>LALITHA
+(EVS)</t>
+        </is>
+      </c>
+      <c r="H30" s="7" t="inlineStr">
+        <is>
+          <t>SWATHI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="I30" s="7" t="inlineStr">
         <is>
           <t>PALLAVI
 (SOC)</t>
         </is>
       </c>
-      <c r="H30" s="7" t="inlineStr">
-        <is>
-          <t>SWATHI
+      <c r="J30" s="7" t="inlineStr">
+        <is>
+          <t>FATHIMA
+(HIN)</t>
+        </is>
+      </c>
+      <c r="K30" s="7" t="inlineStr">
+        <is>
+          <t>D.V.RAO
 (TEL)</t>
         </is>
       </c>
-      <c r="I30" s="7" t="inlineStr">
-        <is>
-          <t>TULASI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="J30" s="7" t="inlineStr">
-        <is>
-          <t>LALITHA
-(PHY)</t>
-        </is>
-      </c>
-      <c r="K30" s="7" t="inlineStr">
+      <c r="L30" s="7" t="inlineStr">
         <is>
           <t>SANGEETHA
 (MATH)</t>
         </is>
       </c>
-      <c r="L30" s="7" t="inlineStr">
-        <is>
-          <t>D.V.RAO
-(TEL)</t>
-        </is>
-      </c>
       <c r="M30" s="7" t="inlineStr">
         <is>
           <t>SONU
@@ -8533,8 +8482,8 @@
       </c>
       <c r="N30" s="7" t="inlineStr">
         <is>
-          <t>SUNITHA
-(SOC)</t>
+          <t>CHALAPATHI
+(BIO)</t>
         </is>
       </c>
     </row>
@@ -8546,49 +8495,49 @@
       <c r="C31" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(MATH)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
-        <is>
-          <t>SWATHI
-(HIN)</t>
-        </is>
-      </c>
-      <c r="E31" s="7" t="inlineStr">
         <is>
           <t>P.E
 (P.E.T)</t>
         </is>
       </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>P.E
+(P.E.T)</t>
+        </is>
+      </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
+          <t>P.E
+(P.E.T)</t>
+        </is>
+      </c>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>P.E
+(P.E.T)</t>
+        </is>
+      </c>
+      <c r="H31" s="7" t="inlineStr">
+        <is>
           <t>MAHA
-(ENG)</t>
-        </is>
-      </c>
-      <c r="G31" s="7" t="inlineStr">
-        <is>
-          <t>SAI LAKSHMI
-(G.K)</t>
-        </is>
-      </c>
-      <c r="H31" s="7" t="inlineStr">
-        <is>
-          <t>SANGEETHA
-(G.K)</t>
+(GRAM)</t>
         </is>
       </c>
       <c r="I31" s="7" t="inlineStr">
         <is>
+          <t>P.E
+(P.E.T)</t>
+        </is>
+      </c>
+      <c r="J31" s="7" t="inlineStr">
+        <is>
           <t>LALITHA
-(EVS)</t>
-        </is>
-      </c>
-      <c r="J31" s="7" t="inlineStr">
-        <is>
-          <t>RAVI
-(ENG)</t>
+(PHY)</t>
         </is>
       </c>
       <c r="K31" s="7" t="inlineStr">
@@ -8603,15 +8552,16 @@
 (ENG)</t>
         </is>
       </c>
-      <c r="M31" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
+      <c r="M31" s="7" t="inlineStr">
+        <is>
+          <t>SUNITHA
+(SOC)</t>
         </is>
       </c>
       <c r="N31" s="7" t="inlineStr">
         <is>
-          <t>CHALAPATHI
-(BIO)</t>
+          <t>RIYA
+(HIN)</t>
         </is>
       </c>
     </row>
@@ -8623,67 +8573,67 @@
       <c r="C32" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(EVS)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>SAI LAKSHMI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>BHAVANI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
         <is>
           <t>NAGAMANI
 (TEL)</t>
         </is>
       </c>
-      <c r="E32" s="7" t="inlineStr">
-        <is>
-          <t>BHAVANI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="F32" s="7" t="inlineStr">
-        <is>
-          <t>MARTIAL ARTS
-(KAR)</t>
-        </is>
-      </c>
       <c r="G32" s="7" t="inlineStr">
+        <is>
+          <t>PALLAVI
+(SOC)</t>
+        </is>
+      </c>
+      <c r="H32" s="7" t="inlineStr">
         <is>
           <t>MAHA
 (ENG)</t>
         </is>
       </c>
-      <c r="H32" s="7" t="inlineStr">
+      <c r="I32" s="7" t="inlineStr">
+        <is>
+          <t>TULASI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="J32" s="7" t="inlineStr">
+        <is>
+          <t>SWATHI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="K32" s="7" t="inlineStr">
         <is>
           <t>LALITHA
-(EVS)</t>
-        </is>
-      </c>
-      <c r="I32" s="7" t="inlineStr">
-        <is>
-          <t>PALLAVI
-(SOC)</t>
-        </is>
-      </c>
-      <c r="J32" s="7" t="inlineStr">
-        <is>
-          <t>FATHIMA
-(HIN)</t>
-        </is>
-      </c>
-      <c r="K32" s="7" t="inlineStr">
+(BIO)</t>
+        </is>
+      </c>
+      <c r="L32" s="7" t="inlineStr">
+        <is>
+          <t>CHALAPATHI
+(BIO)</t>
+        </is>
+      </c>
+      <c r="M32" s="7" t="inlineStr">
         <is>
           <t>RAVI
 (GRAM)</t>
-        </is>
-      </c>
-      <c r="L32" s="7" t="inlineStr">
-        <is>
-          <t>CHALAPATHI
-(BIO)</t>
-        </is>
-      </c>
-      <c r="M32" s="7" t="inlineStr">
-        <is>
-          <t>RIYA
-(HIN)</t>
         </is>
       </c>
       <c r="N32" s="7" t="inlineStr">
@@ -8783,7 +8733,7 @@
       <c r="C34" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(EVS)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
@@ -8801,7 +8751,7 @@
       <c r="F34" s="7" t="inlineStr">
         <is>
           <t>SAI LAKSHMI
-(EVS)</t>
+(HIN)</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
@@ -8848,8 +8798,8 @@
       </c>
       <c r="N34" s="7" t="inlineStr">
         <is>
-          <t>BHEEMA
-(PHY)</t>
+          <t>GOWTHAM
+(MATH)</t>
         </is>
       </c>
     </row>
@@ -8861,19 +8811,19 @@
       <c r="C35" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(ORAL)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>SWATHI
-(HIN)</t>
+          <t>SAI LAKSHMI
+(ENG)</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>SAI LAKSHMI
-(EVS)</t>
+          <t>MAHESWARI
+(COMP)</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr">
@@ -8884,38 +8834,38 @@
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>MAHA
-(ENG)</t>
+          <t>TULASI
+(MATH)</t>
         </is>
       </c>
       <c r="H35" s="7" t="inlineStr">
-        <is>
-          <t>LALITHA
-(EVS)</t>
-        </is>
-      </c>
-      <c r="I35" s="7" t="inlineStr">
         <is>
           <t>FATHIMA
 (HIN)</t>
         </is>
       </c>
+      <c r="I35" s="7" t="inlineStr">
+        <is>
+          <t>SWATHI
+(TEL)</t>
+        </is>
+      </c>
       <c r="J35" s="7" t="inlineStr">
+        <is>
+          <t>LALITHA
+(CHEM)</t>
+        </is>
+      </c>
+      <c r="K35" s="7" t="inlineStr">
         <is>
           <t>SANGEETHA
 (MATH)</t>
         </is>
       </c>
-      <c r="K35" s="7" t="inlineStr">
+      <c r="L35" s="7" t="inlineStr">
         <is>
           <t>D.V.RAO
 (TEL)</t>
-        </is>
-      </c>
-      <c r="L35" s="7" t="inlineStr">
-        <is>
-          <t>BHEEMA
-(CHEM)</t>
         </is>
       </c>
       <c r="M35" s="7" t="inlineStr">
@@ -8944,68 +8894,67 @@
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
+          <t>SWATHI
+(HIN)</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
-        <is>
-          <t>BHAVANI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="F36" s="7" t="inlineStr">
         <is>
           <t>SAI LAKSHMI
 (HIN)</t>
         </is>
       </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>TULASI
+(MATH)</t>
+        </is>
+      </c>
       <c r="G36" s="7" t="inlineStr">
+        <is>
+          <t>LALITHA
+(EVS)</t>
+        </is>
+      </c>
+      <c r="H36" s="7" t="inlineStr">
+        <is>
+          <t>MAHA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="I36" s="7" t="inlineStr">
         <is>
           <t>PALLAVI
 (SOC)</t>
         </is>
       </c>
-      <c r="H36" s="7" t="inlineStr">
-        <is>
-          <t>SWATHI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="I36" s="7" t="inlineStr">
-        <is>
-          <t>TULASI
-(MATH)</t>
-        </is>
-      </c>
       <c r="J36" s="7" t="inlineStr">
         <is>
-          <t>LALITHA
-(BIO)</t>
+          <t>FATHIMA
+(HIN)</t>
         </is>
       </c>
       <c r="K36" s="7" t="inlineStr">
-        <is>
-          <t>RAVI
-(ENG)</t>
-        </is>
-      </c>
-      <c r="L36" s="7" t="inlineStr">
         <is>
           <t>SANGEETHA
 (MATH)</t>
         </is>
       </c>
-      <c r="M36" s="7" t="inlineStr">
+      <c r="L36" s="7" t="inlineStr">
         <is>
           <t>BHEEMA
 (CHEM)</t>
         </is>
       </c>
-      <c r="N36" s="7" t="inlineStr">
+      <c r="M36" s="7" t="inlineStr">
         <is>
           <t>GOWTHAM
 (MATH)</t>
+        </is>
+      </c>
+      <c r="N36" s="12" t="inlineStr">
+        <is>
+          <t>Recreation</t>
         </is>
       </c>
     </row>
@@ -9017,7 +8966,7 @@
       <c r="C37" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(MATH)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
@@ -9028,8 +8977,8 @@
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>SAI LAKSHMI
-(EVS)</t>
+          <t>BHAVANI
+(MATH)</t>
         </is>
       </c>
       <c r="F37" s="7" t="inlineStr">
@@ -9040,49 +8989,50 @@
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>TULASI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="H37" s="7" t="inlineStr">
-        <is>
           <t>MAHA
 (ENG)</t>
         </is>
       </c>
-      <c r="I37" s="7" t="inlineStr">
-        <is>
-          <t>P.E
-(P.E.T)</t>
-        </is>
-      </c>
-      <c r="J37" s="7" t="inlineStr">
+      <c r="H37" s="7" t="inlineStr">
         <is>
           <t>PALLAVI
 (SOC)</t>
         </is>
       </c>
+      <c r="I37" s="7" t="inlineStr">
+        <is>
+          <t>MARTIAL ARTS
+(KAR)</t>
+        </is>
+      </c>
+      <c r="J37" s="7" t="inlineStr">
+        <is>
+          <t>RAVI
+(ENG)</t>
+        </is>
+      </c>
       <c r="K37" s="7" t="inlineStr">
         <is>
-          <t>FATHIMA
-(G.K)</t>
+          <t>LALITHA
+(CHEM)</t>
         </is>
       </c>
       <c r="L37" s="7" t="inlineStr">
+        <is>
+          <t>MARTIAL ARTS
+(KAR)</t>
+        </is>
+      </c>
+      <c r="M37" s="7" t="inlineStr">
+        <is>
+          <t>RIYA
+(HIN)</t>
+        </is>
+      </c>
+      <c r="N37" s="7" t="inlineStr">
         <is>
           <t>SUNITHA
 (SOC)</t>
-        </is>
-      </c>
-      <c r="M37" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
-        </is>
-      </c>
-      <c r="N37" s="7" t="inlineStr">
-        <is>
-          <t>D.V.RAO
-(TEL)</t>
         </is>
       </c>
     </row>
@@ -9094,13 +9044,13 @@
       <c r="C38" s="7" t="inlineStr">
         <is>
           <t>SITHA
+(ORAL)</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>BHAVANI
 (MATH)</t>
-        </is>
-      </c>
-      <c r="D38" s="7" t="inlineStr">
-        <is>
-          <t>SAI LAKSHMI
-(ENG)</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
@@ -9123,32 +9073,32 @@
       </c>
       <c r="H38" s="7" t="inlineStr">
         <is>
+          <t>SANGEETHA
+(G.K)</t>
+        </is>
+      </c>
+      <c r="I38" s="7" t="inlineStr">
+        <is>
+          <t>LALITHA
+(EVS)</t>
+        </is>
+      </c>
+      <c r="J38" s="7" t="inlineStr">
+        <is>
           <t>PALLAVI
 (SOC)</t>
         </is>
       </c>
-      <c r="I38" s="7" t="inlineStr">
-        <is>
-          <t>LALITHA
-(EVS)</t>
-        </is>
-      </c>
-      <c r="J38" s="7" t="inlineStr">
-        <is>
-          <t>SWATHI
-(TEL)</t>
-        </is>
-      </c>
       <c r="K38" s="7" t="inlineStr">
         <is>
-          <t>FATHIMA
-(HIN)</t>
+          <t>RAVI
+(ENG)</t>
         </is>
       </c>
       <c r="L38" s="7" t="inlineStr">
         <is>
-          <t>SANGEETHA
-(MATH)</t>
+          <t>SUNITHA
+(SOC)</t>
         </is>
       </c>
       <c r="M38" s="7" t="inlineStr">
@@ -9159,8 +9109,8 @@
       </c>
       <c r="N38" s="7" t="inlineStr">
         <is>
-          <t>SUNITHA
-(SOC)</t>
+          <t>D.V.RAO
+(TEL)</t>
         </is>
       </c>
     </row>
@@ -9172,13 +9122,13 @@
       <c r="C39" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(MATH)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>BHAVANI
-(MATH)</t>
+          <t>SAI LAKSHMI
+(ENG)</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
@@ -9189,38 +9139,38 @@
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
+          <t>MARTIAL ARTS
+(KAR)</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
+          <t>RIYA
+(HIN)</t>
+        </is>
+      </c>
+      <c r="H39" s="7" t="inlineStr">
+        <is>
+          <t>SWATHI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="I39" s="7" t="inlineStr">
+        <is>
+          <t>TULASI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="J39" s="7" t="inlineStr">
+        <is>
           <t>LALITHA
-(EVS)</t>
-        </is>
-      </c>
-      <c r="H39" s="7" t="inlineStr">
-        <is>
-          <t>P.E
-(P.E.T)</t>
-        </is>
-      </c>
-      <c r="I39" s="7" t="inlineStr">
-        <is>
-          <t>PALLAVI
-(SOC)</t>
-        </is>
-      </c>
-      <c r="J39" s="7" t="inlineStr">
-        <is>
-          <t>RAVI
-(GRAM)</t>
+(BIO)</t>
         </is>
       </c>
       <c r="K39" s="7" t="inlineStr">
         <is>
-          <t>SANGEETHA
-(MATH)</t>
+          <t>FATHIMA
+(HIN)</t>
         </is>
       </c>
       <c r="L39" s="7" t="inlineStr">
@@ -9250,7 +9200,7 @@
       <c r="C40" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(ENG)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
@@ -9273,44 +9223,44 @@
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>TULASI
-(MATH)</t>
+          <t>PALLAVI
+(SOC)</t>
         </is>
       </c>
       <c r="H40" s="7" t="inlineStr">
+        <is>
+          <t>LALITHA
+(EVS)</t>
+        </is>
+      </c>
+      <c r="I40" s="7" t="inlineStr">
         <is>
           <t>FATHIMA
 (HIN)</t>
         </is>
       </c>
-      <c r="I40" s="7" t="inlineStr">
+      <c r="J40" s="7" t="inlineStr">
         <is>
           <t>SWATHI
 (TEL)</t>
         </is>
       </c>
-      <c r="J40" s="7" t="inlineStr">
-        <is>
-          <t>RAVI
-(ENG)</t>
-        </is>
-      </c>
       <c r="K40" s="7" t="inlineStr">
-        <is>
-          <t>LALITHA
-(BIO)</t>
-        </is>
-      </c>
-      <c r="L40" s="7" t="inlineStr">
         <is>
           <t>D.V.RAO
 (TEL)</t>
         </is>
       </c>
+      <c r="L40" s="7" t="inlineStr">
+        <is>
+          <t>SANGEETHA
+(MATH)</t>
+        </is>
+      </c>
       <c r="M40" s="7" t="inlineStr">
         <is>
-          <t>RIYA
-(HIN)</t>
+          <t>CHALAPATHI
+(BIO)</t>
         </is>
       </c>
       <c r="N40" s="7" t="inlineStr">
@@ -9410,7 +9360,7 @@
       <c r="C42" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(MATH)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
@@ -9464,7 +9414,7 @@
       <c r="L42" s="7" t="inlineStr">
         <is>
           <t>FATHIMA
-(G.K)</t>
+(HIN)</t>
         </is>
       </c>
       <c r="M42" s="7" t="inlineStr">
@@ -9475,8 +9425,8 @@
       </c>
       <c r="N42" s="7" t="inlineStr">
         <is>
-          <t>BHEEMA
-(CHEM)</t>
+          <t>GOWTHAM
+(MATH)</t>
         </is>
       </c>
     </row>
@@ -9488,31 +9438,31 @@
       <c r="C43" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(EVS)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
+          <t>NAGAMANI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
           <t>SAI LAKSHMI
-(ENG)</t>
-        </is>
-      </c>
-      <c r="E43" s="7" t="inlineStr">
-        <is>
-          <t>MAHA
-(ENG)</t>
+(HIN)</t>
         </is>
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
+          <t>BHAVANI
+(G.K)</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>MARTIAL ARTS
-(KAR)</t>
+          <t>RIYA
+(HIN)</t>
         </is>
       </c>
       <c r="H43" s="7" t="inlineStr">
@@ -9529,20 +9479,20 @@
       </c>
       <c r="J43" s="7" t="inlineStr">
         <is>
-          <t>SWATHI
-(TEL)</t>
+          <t>LALITHA
+(BIO)</t>
         </is>
       </c>
       <c r="K43" s="7" t="inlineStr">
         <is>
-          <t>LALITHA
+          <t>SANGEETHA
+(MATH)</t>
+        </is>
+      </c>
+      <c r="L43" s="7" t="inlineStr">
+        <is>
+          <t>BHEEMA
 (PHY)</t>
-        </is>
-      </c>
-      <c r="L43" s="7" t="inlineStr">
-        <is>
-          <t>SUNITHA
-(SOC)</t>
         </is>
       </c>
       <c r="M43" s="7" t="inlineStr">
@@ -9551,10 +9501,9 @@
 (MATH)</t>
         </is>
       </c>
-      <c r="N43" s="7" t="inlineStr">
-        <is>
-          <t>RIYA
-(HIN)</t>
+      <c r="N43" s="12" t="inlineStr">
+        <is>
+          <t>Recreation</t>
         </is>
       </c>
     </row>
@@ -9566,25 +9515,25 @@
       <c r="C44" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(ENG)</t>
+(ORAL)</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
+          <t>BHAVANI
+(MATH)</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>MAHESWARI
-(COMP)</t>
+          <t>SAI LAKSHMI
+(EVS)</t>
         </is>
       </c>
       <c r="F44" s="7" t="inlineStr">
         <is>
-          <t>NAGAMANI
-(TEL)</t>
+          <t>MAHA
+(GRAM)</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr">
@@ -9595,8 +9544,8 @@
       </c>
       <c r="H44" s="7" t="inlineStr">
         <is>
-          <t>MAHA
-(ENG)</t>
+          <t>SWATHI
+(TEL)</t>
         </is>
       </c>
       <c r="I44" s="7" t="inlineStr">
@@ -9607,8 +9556,8 @@
       </c>
       <c r="J44" s="7" t="inlineStr">
         <is>
-          <t>RAVI
-(ENG)</t>
+          <t>PALLAVI
+(SOC)</t>
         </is>
       </c>
       <c r="K44" s="7" t="inlineStr">
@@ -9619,20 +9568,20 @@
       </c>
       <c r="L44" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
+          <t>D.V.RAO
+(TEL)</t>
         </is>
       </c>
       <c r="M44" s="7" t="inlineStr">
+        <is>
+          <t>GOWTHAM
+(MATH)</t>
+        </is>
+      </c>
+      <c r="N44" s="7" t="inlineStr">
         <is>
           <t>BHEEMA
 (PHY)</t>
-        </is>
-      </c>
-      <c r="N44" s="7" t="inlineStr">
-        <is>
-          <t>GOWTHAM
-(MATH)</t>
         </is>
       </c>
     </row>
@@ -9649,56 +9598,56 @@
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>BHAVANI
-(MATH)</t>
+          <t>SWATHI
+(HIN)</t>
         </is>
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
+          <t>MAHA
+(ENG)</t>
         </is>
       </c>
       <c r="F45" s="7" t="inlineStr">
-        <is>
-          <t>SAI LAKSHMI
-(EVS)</t>
-        </is>
-      </c>
-      <c r="G45" s="7" t="inlineStr">
-        <is>
-          <t>LALITHA
-(EVS)</t>
-        </is>
-      </c>
-      <c r="H45" s="7" t="inlineStr">
         <is>
           <t>TULASI
 (MATH)</t>
         </is>
       </c>
+      <c r="G45" s="7" t="inlineStr">
+        <is>
+          <t>SAI LAKSHMI
+(G.K)</t>
+        </is>
+      </c>
+      <c r="H45" s="7" t="inlineStr">
+        <is>
+          <t>MAHESWARI
+(COMP)</t>
+        </is>
+      </c>
       <c r="I45" s="7" t="inlineStr">
-        <is>
-          <t>P.E
-(P.E.T)</t>
-        </is>
-      </c>
-      <c r="J45" s="7" t="inlineStr">
-        <is>
-          <t>PALLAVI
-(SOC)</t>
-        </is>
-      </c>
-      <c r="K45" s="7" t="inlineStr">
         <is>
           <t>FATHIMA
 (HIN)</t>
         </is>
       </c>
+      <c r="J45" s="7" t="inlineStr">
+        <is>
+          <t>MARTIAL ARTS
+(KAR)</t>
+        </is>
+      </c>
+      <c r="K45" s="7" t="inlineStr">
+        <is>
+          <t>RAVI
+(ENG)</t>
+        </is>
+      </c>
       <c r="L45" s="7" t="inlineStr">
         <is>
-          <t>SANGEETHA
-(MATH)</t>
+          <t>SUNITHA
+(SOC)</t>
         </is>
       </c>
       <c r="M45" s="7" t="inlineStr">
@@ -9722,67 +9671,67 @@
       <c r="C46" s="7" t="inlineStr">
         <is>
           <t>SITHA
+(MATH)</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>BHAVANI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>SAI LAKSHMI
+(EVS)</t>
+        </is>
+      </c>
+      <c r="F46" s="7" t="inlineStr">
+        <is>
+          <t>MAHESWARI
+(COMP)</t>
+        </is>
+      </c>
+      <c r="G46" s="7" t="inlineStr">
+        <is>
+          <t>LALITHA
+(EVS)</t>
+        </is>
+      </c>
+      <c r="H46" s="7" t="inlineStr">
+        <is>
+          <t>MAHA
 (ENG)</t>
         </is>
       </c>
-      <c r="D46" s="7" t="inlineStr">
-        <is>
-          <t>SAI LAKSHMI
-(ENG)</t>
-        </is>
-      </c>
-      <c r="E46" s="7" t="inlineStr">
-        <is>
-          <t>MARTIAL ARTS
-(KAR)</t>
-        </is>
-      </c>
-      <c r="F46" s="7" t="inlineStr">
-        <is>
-          <t>TULASI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="G46" s="7" t="inlineStr">
-        <is>
-          <t>PALLAVI
-(SOC)</t>
-        </is>
-      </c>
-      <c r="H46" s="7" t="inlineStr">
+      <c r="I46" s="7" t="inlineStr">
+        <is>
+          <t>SANGEETHA
+(G.K)</t>
+        </is>
+      </c>
+      <c r="J46" s="7" t="inlineStr">
         <is>
           <t>SWATHI
 (TEL)</t>
         </is>
       </c>
-      <c r="I46" s="7" t="inlineStr">
-        <is>
-          <t>FATHIMA
-(HIN)</t>
-        </is>
-      </c>
-      <c r="J46" s="7" t="inlineStr">
-        <is>
-          <t>LALITHA
-(CHEM)</t>
-        </is>
-      </c>
       <c r="K46" s="7" t="inlineStr">
         <is>
-          <t>SANGEETHA
-(MATH)</t>
+          <t>D.V.RAO
+(TEL)</t>
         </is>
       </c>
       <c r="L46" s="7" t="inlineStr">
+        <is>
+          <t>CHALAPATHI
+(BIO)</t>
+        </is>
+      </c>
+      <c r="M46" s="7" t="inlineStr">
         <is>
           <t>SONU
 (ENG)</t>
-        </is>
-      </c>
-      <c r="M46" s="7" t="inlineStr">
-        <is>
-          <t>RAVI
-(GRAM)</t>
         </is>
       </c>
       <c r="N46" s="7" t="inlineStr">
@@ -9800,67 +9749,67 @@
       <c r="C47" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(MATH)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
-        <is>
-          <t>NAGAMANI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="E47" s="7" t="inlineStr">
         <is>
           <t>BHAVANI
 (MATH)</t>
         </is>
       </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>MAHESWARI
+(COMP)</t>
+        </is>
+      </c>
       <c r="F47" s="7" t="inlineStr">
-        <is>
-          <t>SAI LAKSHMI
-(HIN)</t>
-        </is>
-      </c>
-      <c r="G47" s="7" t="inlineStr">
         <is>
           <t>MAHA
 (ENG)</t>
         </is>
       </c>
-      <c r="H47" s="7" t="inlineStr">
+      <c r="G47" s="7" t="inlineStr">
         <is>
           <t>PALLAVI
 (SOC)</t>
         </is>
       </c>
+      <c r="H47" s="7" t="inlineStr">
+        <is>
+          <t>LALITHA
+(EVS)</t>
+        </is>
+      </c>
       <c r="I47" s="7" t="inlineStr">
         <is>
-          <t>SWATHI
-(TEL)</t>
+          <t>TULASI
+(MATH)</t>
         </is>
       </c>
       <c r="J47" s="7" t="inlineStr">
-        <is>
-          <t>FATHIMA
-(HIN)</t>
-        </is>
-      </c>
-      <c r="K47" s="7" t="inlineStr">
         <is>
           <t>RAVI
 (ENG)</t>
         </is>
       </c>
+      <c r="K47" s="7" t="inlineStr">
+        <is>
+          <t>MARTIAL ARTS
+(KAR)</t>
+        </is>
+      </c>
       <c r="L47" s="7" t="inlineStr">
         <is>
-          <t>D.V.RAO
-(TEL)</t>
+          <t>SANGEETHA
+(MATH)</t>
         </is>
       </c>
       <c r="M47" s="7" t="inlineStr">
         <is>
-          <t>SUNITHA
-(SOC)</t>
+          <t>CHALAPATHI
+(BIO)</t>
         </is>
       </c>
       <c r="N47" s="7" t="inlineStr">
@@ -9877,74 +9826,73 @@
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
+          <t>SITHA
+(EVS)</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>BHAVANI
-(MATH)</t>
+          <t>SAI LAKSHMI
+(ENG)</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>SAI LAKSHMI
-(HIN)</t>
+          <t>MARTIAL ARTS
+(KAR)</t>
         </is>
       </c>
       <c r="F48" s="7" t="inlineStr">
+        <is>
+          <t>NAGAMANI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="G48" s="7" t="inlineStr">
         <is>
           <t>MAHA
 (ENG)</t>
         </is>
       </c>
-      <c r="G48" s="7" t="inlineStr">
-        <is>
-          <t>RIYA
+      <c r="H48" s="7" t="inlineStr">
+        <is>
+          <t>PALLAVI
+(SOC)</t>
+        </is>
+      </c>
+      <c r="I48" s="7" t="inlineStr">
+        <is>
+          <t>SWATHI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="J48" s="7" t="inlineStr">
+        <is>
+          <t>LALITHA
+(PHY)</t>
+        </is>
+      </c>
+      <c r="K48" s="7" t="inlineStr">
+        <is>
+          <t>FATHIMA
 (HIN)</t>
         </is>
       </c>
-      <c r="H48" s="7" t="inlineStr">
-        <is>
-          <t>LALITHA
-(EVS)</t>
-        </is>
-      </c>
-      <c r="I48" s="7" t="inlineStr">
-        <is>
-          <t>TULASI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="J48" s="7" t="inlineStr">
-        <is>
-          <t>P.E
-(P.E.T)</t>
-        </is>
-      </c>
-      <c r="K48" s="7" t="inlineStr">
-        <is>
-          <t>D.V.RAO
-(TEL)</t>
-        </is>
-      </c>
       <c r="L48" s="7" t="inlineStr">
-        <is>
-          <t>SANGEETHA
-(MATH)</t>
-        </is>
-      </c>
-      <c r="M48" s="7" t="inlineStr">
         <is>
           <t>SONU
 (ENG)</t>
         </is>
       </c>
-      <c r="N48" s="7" t="inlineStr">
-        <is>
-          <t>CHALAPATHI
-(BIO)</t>
+      <c r="M48" s="7" t="inlineStr">
+        <is>
+          <t>SUNITHA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="N48" s="12" t="inlineStr">
+        <is>
+          <t>Recreation</t>
         </is>
       </c>
     </row>

--- a/NRCS/Output/NRCS_Timetable_Final.xlsx
+++ b/NRCS/Output/NRCS_Timetable_Final.xlsx
@@ -659,25 +659,21 @@
       <c r="C5" s="7" t="inlineStr"/>
       <c r="D5" s="7" t="inlineStr">
         <is>
+          <t>U.K.G (MATH)</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
           <t>Class 1 (MATH)</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (EVS)</t>
-        </is>
-      </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>U.K.G (EVS)</t>
+          <t>Class 1 (MATH)</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr"/>
-      <c r="H5" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (MATH)</t>
-        </is>
-      </c>
+      <c r="H5" s="7" t="inlineStr"/>
       <c r="I5" s="8" t="inlineStr">
         <is>
           <t>U.K.G</t>
@@ -692,29 +688,29 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>U.K.G (EVS)</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
+          <t>U.K.G (MATH)</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr"/>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>U.K.G (MATH)</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>U.K.G (MATH)</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>Class 2 (G.K)</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr"/>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (EVS)</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (EVS)</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr"/>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>U.K.G (EVS)</t>
+          <t>U.K.G (MATH)</t>
         </is>
       </c>
       <c r="I6" s="8" t="inlineStr">
@@ -736,18 +732,26 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
+          <t>U.K.G (MATH)</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>U.K.G (MATH)</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr"/>
+      <c r="F7" s="7" t="inlineStr"/>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
           <t>Class 1 (MATH)</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr"/>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (MATH)</t>
-        </is>
-      </c>
-      <c r="F7" s="7" t="inlineStr"/>
-      <c r="G7" s="7" t="inlineStr"/>
-      <c r="H7" s="7" t="inlineStr"/>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>U.K.G (EVS)</t>
+        </is>
+      </c>
       <c r="I7" s="8" t="inlineStr">
         <is>
           <t>U.K.G</t>
@@ -762,15 +766,15 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
+          <t>U.K.G (EVS)</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr"/>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
           <t>U.K.G (MATH)</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (MATH)</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr"/>
       <c r="E8" s="7" t="inlineStr">
         <is>
           <t>Class 1 (MATH)</t>
@@ -778,11 +782,15 @@
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>U.K.G (MATH)</t>
+          <t>Class 1 (MATH)</t>
         </is>
       </c>
       <c r="G8" s="7" t="inlineStr"/>
-      <c r="H8" s="7" t="inlineStr"/>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>Class 1 (MATH)</t>
+        </is>
+      </c>
       <c r="I8" s="8" t="inlineStr">
         <is>
           <t>U.K.G</t>
@@ -797,13 +805,13 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>U.K.G (MATH)</t>
+          <t>U.K.G (EVS)</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr"/>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Class 1 (MATH)</t>
+          <t>Class 2 (G.K)</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
@@ -811,17 +819,9 @@
           <t>U.K.G (MATH)</t>
         </is>
       </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (MATH)</t>
-        </is>
-      </c>
+      <c r="F9" s="7" t="inlineStr"/>
       <c r="G9" s="7" t="inlineStr"/>
-      <c r="H9" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (MATH)</t>
-        </is>
-      </c>
+      <c r="H9" s="7" t="inlineStr"/>
       <c r="I9" s="8" t="inlineStr">
         <is>
           <t>U.K.G</t>
@@ -836,28 +836,28 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
+          <t>U.K.G (EVS)</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>Class 1 (MATH)</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr"/>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>U.K.G (EVS)</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
           <t>U.K.G (MATH)</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr"/>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (MATH)</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (G.K)</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (MATH)</t>
-        </is>
-      </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>Class 1 (MATH)</t>
+          <t>U.K.G (EVS)</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr"/>
@@ -935,15 +935,19 @@
           <t>MON</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr"/>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (CHEM)</t>
+        </is>
+      </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (CHEM)</t>
+          <t>Class 9 (CHEM)</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (PHY)</t>
+          <t>Class 9 (PHY)</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr"/>
@@ -961,14 +965,10 @@
       <c r="B15" s="7" t="inlineStr"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>Class 10 (PHY)</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (CHEM)</t>
-        </is>
-      </c>
+          <t>Class 8 (PHY)</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr"/>
       <c r="E15" s="7" t="inlineStr"/>
       <c r="F15" s="7" t="inlineStr"/>
       <c r="G15" s="7" t="inlineStr"/>
@@ -984,12 +984,12 @@
       <c r="B16" s="7" t="inlineStr"/>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>Class 9 (PHY)</t>
+          <t>Class 10 (CHEM)</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>Class 10 (CHEM)</t>
+          <t>Class 8 (CHEM)</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr"/>
@@ -1010,7 +1010,11 @@
           <t>Class 9 (CHEM)</t>
         </is>
       </c>
-      <c r="D17" s="7" t="inlineStr"/>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (PHY)</t>
+        </is>
+      </c>
       <c r="E17" s="7" t="inlineStr"/>
       <c r="F17" s="7" t="inlineStr"/>
       <c r="G17" s="7" t="inlineStr"/>
@@ -1023,19 +1027,15 @@
           <t>FRI</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr"/>
+      <c r="C18" s="7" t="inlineStr">
         <is>
           <t>Class 10 (PHY)</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="D18" s="7" t="inlineStr">
         <is>
           <t>Class 8 (PHY)</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (CHEM)</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr"/>
@@ -1146,10 +1146,14 @@
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
+          <t>Class 9 (BIO)</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
           <t>Class 8 (BIO)</t>
         </is>
       </c>
-      <c r="H23" s="7" t="inlineStr"/>
       <c r="I23" s="7" t="inlineStr"/>
     </row>
     <row r="24">
@@ -1164,15 +1168,11 @@
       <c r="E24" s="7" t="inlineStr"/>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>Class 9 (BIO)</t>
+          <t>Class 8 (BIO)</t>
         </is>
       </c>
       <c r="G24" s="7" t="inlineStr"/>
-      <c r="H24" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (BIO)</t>
-        </is>
-      </c>
+      <c r="H24" s="7" t="inlineStr"/>
       <c r="I24" s="7" t="inlineStr"/>
     </row>
     <row r="25">
@@ -1200,17 +1200,13 @@
       <c r="C26" s="7" t="inlineStr"/>
       <c r="D26" s="7" t="inlineStr"/>
       <c r="E26" s="7" t="inlineStr"/>
-      <c r="F26" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (BIO)</t>
-        </is>
-      </c>
-      <c r="G26" s="7" t="inlineStr"/>
-      <c r="H26" s="7" t="inlineStr">
+      <c r="F26" s="7" t="inlineStr"/>
+      <c r="G26" s="7" t="inlineStr">
         <is>
           <t>Class 10 (BIO)</t>
         </is>
       </c>
+      <c r="H26" s="7" t="inlineStr"/>
       <c r="I26" s="7" t="inlineStr"/>
     </row>
     <row r="27">
@@ -1225,17 +1221,17 @@
       <c r="E27" s="7" t="inlineStr"/>
       <c r="F27" s="7" t="inlineStr">
         <is>
+          <t>Class 10 (BIO)</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
           <t>Class 8 (BIO)</t>
         </is>
       </c>
-      <c r="G27" s="7" t="inlineStr">
+      <c r="H27" s="7" t="inlineStr">
         <is>
           <t>Class 9 (BIO)</t>
-        </is>
-      </c>
-      <c r="H27" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (BIO)</t>
         </is>
       </c>
       <c r="I27" s="7" t="inlineStr"/>
@@ -1253,10 +1249,14 @@
       <c r="F28" s="7" t="inlineStr"/>
       <c r="G28" s="7" t="inlineStr">
         <is>
+          <t>Class 9 (BIO)</t>
+        </is>
+      </c>
+      <c r="H28" s="7" t="inlineStr">
+        <is>
           <t>Class 10 (BIO)</t>
         </is>
       </c>
-      <c r="H28" s="7" t="inlineStr"/>
       <c r="I28" s="7" t="inlineStr"/>
     </row>
     <row r="30">
@@ -1334,20 +1334,20 @@
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (TEL)</t>
-        </is>
-      </c>
-      <c r="D32" s="7" t="inlineStr"/>
-      <c r="E32" s="7" t="inlineStr">
-        <is>
           <t>Class 8 (TEL)</t>
         </is>
       </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (TEL)</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr"/>
       <c r="F32" s="7" t="inlineStr"/>
       <c r="G32" s="7" t="inlineStr"/>
       <c r="H32" s="7" t="inlineStr">
         <is>
-          <t>Class 10 (TEL)</t>
+          <t>Class 7 (TEL)</t>
         </is>
       </c>
       <c r="I32" s="8" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (TEL)</t>
+          <t>Class 7 (TEL)</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (TEL)</t>
+          <t>Class 10 (TEL)</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr"/>
@@ -1382,7 +1382,7 @@
       <c r="G33" s="7" t="inlineStr"/>
       <c r="H33" s="7" t="inlineStr">
         <is>
-          <t>Class 10 (TEL)</t>
+          <t>Class 8 (TEL)</t>
         </is>
       </c>
       <c r="I33" s="8" t="inlineStr">
@@ -1402,24 +1402,24 @@
           <t>Class 9 (TEL)</t>
         </is>
       </c>
-      <c r="C34" s="7" t="inlineStr"/>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (TEL)</t>
+        </is>
+      </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (TEL)</t>
+          <t>Class 10 (TEL)</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr"/>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (TEL)</t>
+          <t>Class 7 (TEL)</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr"/>
-      <c r="H34" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (TEL)</t>
-        </is>
-      </c>
+      <c r="H34" s="7" t="inlineStr"/>
       <c r="I34" s="8" t="inlineStr">
         <is>
           <t>Class 9</t>
@@ -1442,18 +1442,18 @@
           <t>Class 7 (TEL)</t>
         </is>
       </c>
-      <c r="D35" s="7" t="inlineStr">
+      <c r="D35" s="7" t="inlineStr"/>
+      <c r="E35" s="7" t="inlineStr">
         <is>
           <t>Class 10 (TEL)</t>
         </is>
       </c>
-      <c r="E35" s="7" t="inlineStr"/>
-      <c r="F35" s="7" t="inlineStr"/>
-      <c r="G35" s="7" t="inlineStr">
+      <c r="F35" s="7" t="inlineStr">
         <is>
           <t>Class 8 (TEL)</t>
         </is>
       </c>
+      <c r="G35" s="7" t="inlineStr"/>
       <c r="H35" s="7" t="inlineStr"/>
       <c r="I35" s="8" t="inlineStr">
         <is>
@@ -1475,21 +1475,21 @@
       <c r="C36" s="7" t="inlineStr"/>
       <c r="D36" s="7" t="inlineStr">
         <is>
+          <t>Class 10 (TEL)</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
           <t>Class 8 (TEL)</t>
         </is>
       </c>
-      <c r="E36" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (TEL)</t>
-        </is>
-      </c>
-      <c r="F36" s="7" t="inlineStr"/>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (TEL)</t>
+        </is>
+      </c>
       <c r="G36" s="7" t="inlineStr"/>
-      <c r="H36" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (TEL)</t>
-        </is>
-      </c>
+      <c r="H36" s="7" t="inlineStr"/>
       <c r="I36" s="8" t="inlineStr">
         <is>
           <t>Class 9</t>
@@ -1507,24 +1507,24 @@
           <t>Class 9 (TEL)</t>
         </is>
       </c>
-      <c r="C37" s="7" t="inlineStr">
+      <c r="C37" s="7" t="inlineStr"/>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (TEL)</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
         <is>
           <t>Class 10 (TEL)</t>
         </is>
       </c>
-      <c r="D37" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (TEL)</t>
-        </is>
-      </c>
-      <c r="E37" s="7" t="inlineStr"/>
       <c r="F37" s="7" t="inlineStr"/>
-      <c r="G37" s="7" t="inlineStr"/>
-      <c r="H37" s="7" t="inlineStr">
+      <c r="G37" s="7" t="inlineStr">
         <is>
           <t>Class 7 (TEL)</t>
         </is>
       </c>
+      <c r="H37" s="7" t="inlineStr"/>
       <c r="I37" s="8" t="inlineStr">
         <is>
           <t>Class 9</t>
@@ -1606,21 +1606,25 @@
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
+          <t>Class 4 (HIN)</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr"/>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (HIN)</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (HIN)</t>
+        </is>
+      </c>
+      <c r="G41" s="7" t="inlineStr">
+        <is>
           <t>Class 6 (HIN)</t>
         </is>
       </c>
-      <c r="D41" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (HIN)</t>
-        </is>
-      </c>
-      <c r="E41" s="7" t="inlineStr"/>
-      <c r="F41" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (HIN)</t>
-        </is>
-      </c>
-      <c r="G41" s="7" t="inlineStr"/>
       <c r="H41" s="7" t="inlineStr"/>
       <c r="I41" s="8" t="inlineStr">
         <is>
@@ -1639,15 +1643,11 @@
           <t>Class 8 (HIN)</t>
         </is>
       </c>
-      <c r="C42" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (HIN)</t>
-        </is>
-      </c>
+      <c r="C42" s="7" t="inlineStr"/>
       <c r="D42" s="7" t="inlineStr"/>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (HIN)</t>
+          <t>Class 4 (HIN)</t>
         </is>
       </c>
       <c r="F42" s="7" t="inlineStr">
@@ -1656,7 +1656,11 @@
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr"/>
-      <c r="H42" s="7" t="inlineStr"/>
+      <c r="H42" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (HIN)</t>
+        </is>
+      </c>
       <c r="I42" s="8" t="inlineStr">
         <is>
           <t>Class 8</t>
@@ -1676,22 +1680,26 @@
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
+          <t>Class 7 (HIN)</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr"/>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
           <t>Class 5 (HIN)</t>
         </is>
       </c>
-      <c r="D43" s="7" t="inlineStr"/>
-      <c r="E43" s="7" t="inlineStr"/>
-      <c r="F43" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (HIN)</t>
-        </is>
-      </c>
+      <c r="F43" s="7" t="inlineStr"/>
       <c r="G43" s="7" t="inlineStr">
         <is>
+          <t>Class 7 (G.K)</t>
+        </is>
+      </c>
+      <c r="H43" s="7" t="inlineStr">
+        <is>
           <t>Class 4 (HIN)</t>
         </is>
       </c>
-      <c r="H43" s="7" t="inlineStr"/>
       <c r="I43" s="8" t="inlineStr">
         <is>
           <t>Class 8</t>
@@ -1709,20 +1717,16 @@
           <t>Class 8 (HIN)</t>
         </is>
       </c>
-      <c r="C44" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (HIN)</t>
-        </is>
-      </c>
-      <c r="D44" s="7" t="inlineStr">
+      <c r="C44" s="7" t="inlineStr"/>
+      <c r="D44" s="7" t="inlineStr"/>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (HIN)</t>
+        </is>
+      </c>
+      <c r="F44" s="7" t="inlineStr">
         <is>
           <t>Class 6 (HIN)</t>
-        </is>
-      </c>
-      <c r="E44" s="7" t="inlineStr"/>
-      <c r="F44" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (HIN)</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr">
@@ -1748,28 +1752,24 @@
           <t>Class 8 (HIN)</t>
         </is>
       </c>
-      <c r="C45" s="7" t="inlineStr">
+      <c r="C45" s="7" t="inlineStr"/>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (HIN)</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (HIN)</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="inlineStr">
         <is>
           <t>Class 5 (HIN)</t>
         </is>
       </c>
-      <c r="D45" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (HIN)</t>
-        </is>
-      </c>
-      <c r="E45" s="7" t="inlineStr"/>
-      <c r="F45" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (G.K)</t>
-        </is>
-      </c>
       <c r="G45" s="7" t="inlineStr"/>
-      <c r="H45" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (HIN)</t>
-        </is>
-      </c>
+      <c r="H45" s="7" t="inlineStr"/>
       <c r="I45" s="8" t="inlineStr">
         <is>
           <t>Class 8</t>
@@ -1790,23 +1790,23 @@
       <c r="C46" s="7" t="inlineStr"/>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (HIN)</t>
+          <t>Class 6 (HIN)</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (HIN)</t>
+          <t>Class 4 (HIN)</t>
         </is>
       </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (HIN)</t>
+          <t>Class 5 (HIN)</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr"/>
       <c r="H46" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (HIN)</t>
+          <t>Class 7 (HIN)</t>
         </is>
       </c>
       <c r="I46" s="8" t="inlineStr">
@@ -1883,21 +1883,13 @@
           <t>MON</t>
         </is>
       </c>
-      <c r="B50" s="7" t="inlineStr">
+      <c r="B50" s="7" t="inlineStr"/>
+      <c r="C50" s="7" t="inlineStr">
         <is>
           <t>Class 10 (MATH)</t>
         </is>
       </c>
-      <c r="C50" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (MATH)</t>
-        </is>
-      </c>
-      <c r="D50" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (MATH)</t>
-        </is>
-      </c>
+      <c r="D50" s="7" t="inlineStr"/>
       <c r="E50" s="7" t="inlineStr"/>
       <c r="F50" s="7" t="inlineStr"/>
       <c r="G50" s="7" t="inlineStr"/>
@@ -1937,10 +1929,14 @@
           <t>WED</t>
         </is>
       </c>
-      <c r="B52" s="7" t="inlineStr"/>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (MATH)</t>
+        </is>
+      </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>Class 10 (MATH)</t>
+          <t>Class 9 (MATH)</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
@@ -1966,11 +1962,7 @@
           <t>Class 10 (MATH)</t>
         </is>
       </c>
-      <c r="D53" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (MATH)</t>
-        </is>
-      </c>
+      <c r="D53" s="7" t="inlineStr"/>
       <c r="E53" s="7" t="inlineStr"/>
       <c r="F53" s="7" t="inlineStr"/>
       <c r="G53" s="7" t="inlineStr"/>
@@ -1983,11 +1975,19 @@
           <t>FRI</t>
         </is>
       </c>
-      <c r="B54" s="7" t="inlineStr"/>
-      <c r="C54" s="7" t="inlineStr"/>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (MATH)</t>
+        </is>
+      </c>
+      <c r="C54" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (MATH)</t>
+        </is>
+      </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>Class 10 (MATH)</t>
+          <t>Class 9 (MATH)</t>
         </is>
       </c>
       <c r="E54" s="7" t="inlineStr"/>
@@ -2090,30 +2090,34 @@
       <c r="B59" s="7" t="inlineStr"/>
       <c r="C59" s="7" t="inlineStr">
         <is>
+          <t>Class 5 (EVS)</t>
+        </is>
+      </c>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
           <t>Class 3 (EVS)</t>
         </is>
       </c>
-      <c r="D59" s="7" t="inlineStr">
+      <c r="E59" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (PHY)</t>
+        </is>
+      </c>
+      <c r="F59" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (BIO)</t>
+        </is>
+      </c>
+      <c r="G59" s="7" t="inlineStr">
         <is>
           <t>Class 4 (EVS)</t>
         </is>
       </c>
-      <c r="E59" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (BIO)</t>
-        </is>
-      </c>
-      <c r="F59" s="7" t="inlineStr">
+      <c r="H59" s="7" t="inlineStr">
         <is>
           <t>Class 6 (BIO)</t>
         </is>
       </c>
-      <c r="G59" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (EVS)</t>
-        </is>
-      </c>
-      <c r="H59" s="7" t="inlineStr"/>
       <c r="I59" s="7" t="inlineStr"/>
     </row>
     <row r="60">
@@ -2125,32 +2129,28 @@
       <c r="B60" s="7" t="inlineStr"/>
       <c r="C60" s="7" t="inlineStr">
         <is>
+          <t>Class 6 (CHEM)</t>
+        </is>
+      </c>
+      <c r="D60" s="7" t="inlineStr">
+        <is>
           <t>Class 7 (PHY)</t>
         </is>
       </c>
-      <c r="D60" s="7" t="inlineStr">
+      <c r="E60" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (EVS)</t>
+        </is>
+      </c>
+      <c r="F60" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (EVS)</t>
+        </is>
+      </c>
+      <c r="G60" s="7" t="inlineStr"/>
+      <c r="H60" s="7" t="inlineStr">
         <is>
           <t>Class 4 (EVS)</t>
-        </is>
-      </c>
-      <c r="E60" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (EVS)</t>
-        </is>
-      </c>
-      <c r="F60" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (BIO)</t>
-        </is>
-      </c>
-      <c r="G60" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (EVS)</t>
-        </is>
-      </c>
-      <c r="H60" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (BIO)</t>
         </is>
       </c>
       <c r="I60" s="7" t="inlineStr"/>
@@ -2164,30 +2164,30 @@
       <c r="B61" s="7" t="inlineStr"/>
       <c r="C61" s="7" t="inlineStr">
         <is>
+          <t>Class 6 (BIO)</t>
+        </is>
+      </c>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (EVS)</t>
+        </is>
+      </c>
+      <c r="E61" s="7" t="inlineStr"/>
+      <c r="F61" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (EVS)</t>
+        </is>
+      </c>
+      <c r="G61" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (EVS)</t>
+        </is>
+      </c>
+      <c r="H61" s="7" t="inlineStr">
+        <is>
           <t>Class 7 (BIO)</t>
         </is>
       </c>
-      <c r="D61" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (EVS)</t>
-        </is>
-      </c>
-      <c r="E61" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (BIO)</t>
-        </is>
-      </c>
-      <c r="F61" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (EVS)</t>
-        </is>
-      </c>
-      <c r="G61" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (EVS)</t>
-        </is>
-      </c>
-      <c r="H61" s="7" t="inlineStr"/>
       <c r="I61" s="7" t="inlineStr"/>
     </row>
     <row r="62">
@@ -2209,22 +2209,18 @@
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
+          <t>Class 6 (BIO)</t>
+        </is>
+      </c>
+      <c r="F62" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (PHY)</t>
+        </is>
+      </c>
+      <c r="G62" s="7" t="inlineStr"/>
+      <c r="H62" s="7" t="inlineStr">
+        <is>
           <t>Class 5 (EVS)</t>
-        </is>
-      </c>
-      <c r="F62" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (CHEM)</t>
-        </is>
-      </c>
-      <c r="G62" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (CHEM)</t>
-        </is>
-      </c>
-      <c r="H62" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (PHY)</t>
         </is>
       </c>
       <c r="I62" s="7" t="inlineStr"/>
@@ -2238,23 +2234,23 @@
       <c r="B63" s="7" t="inlineStr"/>
       <c r="C63" s="7" t="inlineStr">
         <is>
+          <t>Class 6 (PHY)</t>
+        </is>
+      </c>
+      <c r="D63" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (EVS)</t>
+        </is>
+      </c>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
           <t>Class 4 (EVS)</t>
-        </is>
-      </c>
-      <c r="D63" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (CHEM)</t>
-        </is>
-      </c>
-      <c r="E63" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (EVS)</t>
         </is>
       </c>
       <c r="F63" s="7" t="inlineStr"/>
       <c r="G63" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (PHY)</t>
+          <t>Class 7 (CHEM)</t>
         </is>
       </c>
       <c r="H63" s="7" t="inlineStr">
@@ -2273,30 +2269,34 @@
       <c r="B64" s="7" t="inlineStr"/>
       <c r="C64" s="7" t="inlineStr">
         <is>
+          <t>Class 3 (EVS)</t>
+        </is>
+      </c>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (BIO)</t>
+        </is>
+      </c>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
           <t>Class 5 (EVS)</t>
         </is>
       </c>
-      <c r="D64" s="7" t="inlineStr">
+      <c r="F64" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (CHEM)</t>
+        </is>
+      </c>
+      <c r="G64" s="7" t="inlineStr">
         <is>
           <t>Class 4 (EVS)</t>
         </is>
       </c>
-      <c r="E64" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (EVS)</t>
-        </is>
-      </c>
-      <c r="F64" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (PHY)</t>
-        </is>
-      </c>
-      <c r="G64" s="7" t="inlineStr">
+      <c r="H64" s="7" t="inlineStr">
         <is>
           <t>Class 6 (CHEM)</t>
         </is>
       </c>
-      <c r="H64" s="7" t="inlineStr"/>
       <c r="I64" s="7" t="inlineStr"/>
     </row>
     <row r="66">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>Class 3 (ENG)</t>
+          <t>Class 4 (ENG)</t>
         </is>
       </c>
       <c r="E68" s="7" t="inlineStr"/>
@@ -2390,7 +2390,7 @@
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (ENG)</t>
+          <t>Class 3 (ENG)</t>
         </is>
       </c>
       <c r="H68" s="7" t="inlineStr">
@@ -2411,26 +2411,30 @@
           <t>Class 5 (ENG)</t>
         </is>
       </c>
-      <c r="C69" s="7" t="inlineStr"/>
-      <c r="D69" s="7" t="inlineStr">
+      <c r="C69" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (ENG)</t>
+        </is>
+      </c>
+      <c r="D69" s="7" t="inlineStr"/>
+      <c r="E69" s="7" t="inlineStr">
         <is>
           <t>Class 1 (ENG)</t>
         </is>
       </c>
-      <c r="E69" s="7" t="inlineStr">
+      <c r="F69" s="7" t="inlineStr">
         <is>
           <t>Class 4 (ENG)</t>
         </is>
       </c>
-      <c r="F69" s="7" t="inlineStr">
+      <c r="G69" s="7" t="inlineStr">
         <is>
           <t>Class 2 (ENG)</t>
         </is>
       </c>
-      <c r="G69" s="7" t="inlineStr"/>
       <c r="H69" s="7" t="inlineStr">
         <is>
-          <t>Class 3 (ENG)</t>
+          <t>Class 3 (GRAM)</t>
         </is>
       </c>
       <c r="I69" s="7" t="inlineStr"/>
@@ -2454,22 +2458,22 @@
       <c r="D70" s="7" t="inlineStr"/>
       <c r="E70" s="7" t="inlineStr">
         <is>
+          <t>Class 1 (GRAM)</t>
+        </is>
+      </c>
+      <c r="F70" s="7" t="inlineStr">
+        <is>
           <t>Class 1 (ENG)</t>
         </is>
       </c>
-      <c r="F70" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (GRAM)</t>
-        </is>
-      </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
+          <t>Class 4 (ENG)</t>
+        </is>
+      </c>
+      <c r="H70" s="7" t="inlineStr">
+        <is>
           <t>Class 2 (ENG)</t>
-        </is>
-      </c>
-      <c r="H70" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (ENG)</t>
         </is>
       </c>
       <c r="I70" s="7" t="inlineStr"/>
@@ -2485,30 +2489,30 @@
           <t>Class 5 (ENG)</t>
         </is>
       </c>
-      <c r="C71" s="7" t="inlineStr"/>
+      <c r="C71" s="7" t="inlineStr">
+        <is>
+          <t>Class 1 (ENG)</t>
+        </is>
+      </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>Class 1 (ENG)</t>
-        </is>
-      </c>
-      <c r="E71" s="7" t="inlineStr">
-        <is>
           <t>Class 2 (GRAM)</t>
         </is>
       </c>
+      <c r="E71" s="7" t="inlineStr"/>
       <c r="F71" s="7" t="inlineStr">
         <is>
+          <t>Class 3 (ENG)</t>
+        </is>
+      </c>
+      <c r="G71" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (ENG)</t>
+        </is>
+      </c>
+      <c r="H71" s="7" t="inlineStr">
+        <is>
           <t>Class 2 (ENG)</t>
-        </is>
-      </c>
-      <c r="G71" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (ENG)</t>
-        </is>
-      </c>
-      <c r="H71" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (ENG)</t>
         </is>
       </c>
       <c r="I71" s="7" t="inlineStr"/>
@@ -2524,30 +2528,30 @@
           <t>Class 5 (ENG)</t>
         </is>
       </c>
-      <c r="C72" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (GRAM)</t>
-        </is>
-      </c>
+      <c r="C72" s="7" t="inlineStr"/>
       <c r="D72" s="7" t="inlineStr">
         <is>
+          <t>Class 1 (ENG)</t>
+        </is>
+      </c>
+      <c r="E72" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (ENG)</t>
+        </is>
+      </c>
+      <c r="F72" s="7" t="inlineStr">
+        <is>
           <t>Class 2 (ENG)</t>
         </is>
       </c>
-      <c r="E72" s="7" t="inlineStr"/>
-      <c r="F72" s="7" t="inlineStr">
+      <c r="G72" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (GRAM)</t>
+        </is>
+      </c>
+      <c r="H72" s="7" t="inlineStr">
         <is>
           <t>Class 4 (ENG)</t>
-        </is>
-      </c>
-      <c r="G72" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (ENG)</t>
-        </is>
-      </c>
-      <c r="H72" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (ENG)</t>
         </is>
       </c>
       <c r="I72" s="7" t="inlineStr"/>
@@ -2565,30 +2569,26 @@
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
+          <t>Class 4 (ENG)</t>
+        </is>
+      </c>
+      <c r="D73" s="7" t="inlineStr"/>
+      <c r="E73" s="7" t="inlineStr">
+        <is>
+          <t>Class 1 (ENG)</t>
+        </is>
+      </c>
+      <c r="F73" s="7" t="inlineStr">
+        <is>
           <t>Class 2 (ENG)</t>
         </is>
       </c>
-      <c r="D73" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (ENG)</t>
-        </is>
-      </c>
-      <c r="E73" s="7" t="inlineStr"/>
-      <c r="F73" s="7" t="inlineStr">
+      <c r="G73" s="7" t="inlineStr">
         <is>
           <t>Class 3 (ENG)</t>
         </is>
       </c>
-      <c r="G73" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (GRAM)</t>
-        </is>
-      </c>
-      <c r="H73" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (ENG)</t>
-        </is>
-      </c>
+      <c r="H73" s="7" t="inlineStr"/>
       <c r="I73" s="7" t="inlineStr"/>
     </row>
     <row r="75">
@@ -2661,12 +2661,12 @@
       </c>
       <c r="B77" s="7" t="inlineStr"/>
       <c r="C77" s="7" t="inlineStr"/>
-      <c r="D77" s="7" t="inlineStr"/>
-      <c r="E77" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (COMP)</t>
-        </is>
-      </c>
+      <c r="D77" s="7" t="inlineStr">
+        <is>
+          <t>Class 1 (COMP)</t>
+        </is>
+      </c>
+      <c r="E77" s="7" t="inlineStr"/>
       <c r="F77" s="7" t="inlineStr"/>
       <c r="G77" s="7" t="inlineStr"/>
       <c r="H77" s="7" t="inlineStr"/>
@@ -2680,14 +2680,18 @@
       </c>
       <c r="B78" s="7" t="inlineStr"/>
       <c r="C78" s="7" t="inlineStr"/>
-      <c r="D78" s="7" t="inlineStr"/>
-      <c r="E78" s="7" t="inlineStr">
+      <c r="D78" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (COMP)</t>
+        </is>
+      </c>
+      <c r="E78" s="7" t="inlineStr"/>
+      <c r="F78" s="7" t="inlineStr"/>
+      <c r="G78" s="7" t="inlineStr">
         <is>
           <t>Class 1 (COMP)</t>
         </is>
       </c>
-      <c r="F78" s="7" t="inlineStr"/>
-      <c r="G78" s="7" t="inlineStr"/>
       <c r="H78" s="7" t="inlineStr"/>
       <c r="I78" s="7" t="inlineStr"/>
     </row>
@@ -2698,20 +2702,32 @@
         </is>
       </c>
       <c r="B79" s="7" t="inlineStr"/>
-      <c r="C79" s="7" t="inlineStr"/>
+      <c r="C79" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (COMP)</t>
+        </is>
+      </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
+          <t>Class 5 (COMP)</t>
+        </is>
+      </c>
+      <c r="E79" s="7" t="inlineStr">
+        <is>
           <t>Class 2 (COMP)</t>
         </is>
       </c>
-      <c r="E79" s="7" t="inlineStr"/>
-      <c r="F79" s="7" t="inlineStr">
+      <c r="F79" s="7" t="inlineStr"/>
+      <c r="G79" s="7" t="inlineStr">
         <is>
           <t>Class 6 (COMP)</t>
         </is>
       </c>
-      <c r="G79" s="7" t="inlineStr"/>
-      <c r="H79" s="7" t="inlineStr"/>
+      <c r="H79" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (COMP)</t>
+        </is>
+      </c>
       <c r="I79" s="7" t="inlineStr"/>
     </row>
     <row r="80">
@@ -2722,11 +2738,7 @@
       </c>
       <c r="B80" s="7" t="inlineStr"/>
       <c r="C80" s="7" t="inlineStr"/>
-      <c r="D80" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (COMP)</t>
-        </is>
-      </c>
+      <c r="D80" s="7" t="inlineStr"/>
       <c r="E80" s="7" t="inlineStr"/>
       <c r="F80" s="7" t="inlineStr"/>
       <c r="G80" s="7" t="inlineStr"/>
@@ -2740,19 +2752,15 @@
         </is>
       </c>
       <c r="B81" s="7" t="inlineStr"/>
-      <c r="C81" s="7" t="inlineStr"/>
+      <c r="C81" s="7" t="inlineStr">
+        <is>
+          <t>Class 1 (COMP)</t>
+        </is>
+      </c>
       <c r="D81" s="7" t="inlineStr"/>
-      <c r="E81" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (COMP)</t>
-        </is>
-      </c>
+      <c r="E81" s="7" t="inlineStr"/>
       <c r="F81" s="7" t="inlineStr"/>
-      <c r="G81" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (COMP)</t>
-        </is>
-      </c>
+      <c r="G81" s="7" t="inlineStr"/>
       <c r="H81" s="7" t="inlineStr"/>
       <c r="I81" s="7" t="inlineStr"/>
     </row>
@@ -2763,24 +2771,16 @@
         </is>
       </c>
       <c r="B82" s="7" t="inlineStr"/>
-      <c r="C82" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (COMP)</t>
-        </is>
-      </c>
+      <c r="C82" s="7" t="inlineStr"/>
       <c r="D82" s="7" t="inlineStr"/>
-      <c r="E82" s="7" t="inlineStr"/>
+      <c r="E82" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (COMP)</t>
+        </is>
+      </c>
       <c r="F82" s="7" t="inlineStr"/>
-      <c r="G82" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (COMP)</t>
-        </is>
-      </c>
-      <c r="H82" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (COMP)</t>
-        </is>
-      </c>
+      <c r="G82" s="7" t="inlineStr"/>
+      <c r="H82" s="7" t="inlineStr"/>
       <c r="I82" s="7" t="inlineStr"/>
     </row>
     <row r="84">
@@ -2859,21 +2859,21 @@
       <c r="C86" s="7" t="inlineStr"/>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>L.K.G (TEL)</t>
-        </is>
-      </c>
-      <c r="E86" s="7" t="inlineStr"/>
+          <t>Class 2 (TEL)</t>
+        </is>
+      </c>
+      <c r="E86" s="7" t="inlineStr">
+        <is>
+          <t>U.K.G (TEL)</t>
+        </is>
+      </c>
       <c r="F86" s="7" t="inlineStr"/>
       <c r="G86" s="7" t="inlineStr">
         <is>
-          <t>U.K.G (TEL)</t>
-        </is>
-      </c>
-      <c r="H86" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (TEL)</t>
-        </is>
-      </c>
+          <t>Class 1 (G.K)</t>
+        </is>
+      </c>
+      <c r="H86" s="7" t="inlineStr"/>
       <c r="I86" s="8" t="inlineStr">
         <is>
           <t>Class 1</t>
@@ -2896,14 +2896,22 @@
           <t>U.K.G (TEL)</t>
         </is>
       </c>
-      <c r="D87" s="7" t="inlineStr">
+      <c r="D87" s="7" t="inlineStr"/>
+      <c r="E87" s="7" t="inlineStr">
         <is>
           <t>Class 2 (TEL)</t>
         </is>
       </c>
-      <c r="E87" s="7" t="inlineStr"/>
-      <c r="F87" s="7" t="inlineStr"/>
-      <c r="G87" s="7" t="inlineStr"/>
+      <c r="F87" s="7" t="inlineStr">
+        <is>
+          <t>Class 1 (G.K)</t>
+        </is>
+      </c>
+      <c r="G87" s="7" t="inlineStr">
+        <is>
+          <t>L.K.G (TEL)</t>
+        </is>
+      </c>
       <c r="H87" s="7" t="inlineStr"/>
       <c r="I87" s="8" t="inlineStr">
         <is>
@@ -2919,7 +2927,7 @@
       </c>
       <c r="B88" s="7" t="inlineStr">
         <is>
-          <t>Class 1 (G.K)</t>
+          <t>Class 1 (TEL)</t>
         </is>
       </c>
       <c r="C88" s="7" t="inlineStr">
@@ -2927,11 +2935,7 @@
           <t>Class 2 (TEL)</t>
         </is>
       </c>
-      <c r="D88" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (TEL)</t>
-        </is>
-      </c>
+      <c r="D88" s="7" t="inlineStr"/>
       <c r="E88" s="7" t="inlineStr"/>
       <c r="F88" s="7" t="inlineStr">
         <is>
@@ -2961,23 +2965,23 @@
           <t>Class 1 (TEL)</t>
         </is>
       </c>
-      <c r="C89" s="7" t="inlineStr">
+      <c r="C89" s="7" t="inlineStr"/>
+      <c r="D89" s="7" t="inlineStr">
+        <is>
+          <t>L.K.G (TEL)</t>
+        </is>
+      </c>
+      <c r="E89" s="7" t="inlineStr">
         <is>
           <t>Class 2 (TEL)</t>
         </is>
       </c>
-      <c r="D89" s="7" t="inlineStr"/>
-      <c r="E89" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (TEL)</t>
-        </is>
-      </c>
-      <c r="F89" s="7" t="inlineStr"/>
-      <c r="G89" s="7" t="inlineStr">
+      <c r="F89" s="7" t="inlineStr">
         <is>
           <t>U.K.G (TEL)</t>
         </is>
       </c>
+      <c r="G89" s="7" t="inlineStr"/>
       <c r="H89" s="7" t="inlineStr"/>
       <c r="I89" s="8" t="inlineStr">
         <is>
@@ -2996,24 +3000,24 @@
           <t>Class 1 (TEL)</t>
         </is>
       </c>
-      <c r="C90" s="7" t="inlineStr">
+      <c r="C90" s="7" t="inlineStr"/>
+      <c r="D90" s="7" t="inlineStr">
+        <is>
+          <t>L.K.G (TEL)</t>
+        </is>
+      </c>
+      <c r="E90" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (TEL)</t>
+        </is>
+      </c>
+      <c r="F90" s="7" t="inlineStr">
         <is>
           <t>U.K.G (TEL)</t>
         </is>
       </c>
-      <c r="D90" s="7" t="inlineStr"/>
-      <c r="E90" s="7" t="inlineStr"/>
-      <c r="F90" s="7" t="inlineStr"/>
-      <c r="G90" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (TEL)</t>
-        </is>
-      </c>
-      <c r="H90" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (TEL)</t>
-        </is>
-      </c>
+      <c r="G90" s="7" t="inlineStr"/>
+      <c r="H90" s="7" t="inlineStr"/>
       <c r="I90" s="8" t="inlineStr">
         <is>
           <t>Class 1</t>
@@ -3028,31 +3032,27 @@
       </c>
       <c r="B91" s="7" t="inlineStr">
         <is>
-          <t>Class 1 (G.K)</t>
-        </is>
-      </c>
-      <c r="C91" s="7" t="inlineStr"/>
+          <t>Class 1 (TEL)</t>
+        </is>
+      </c>
+      <c r="C91" s="7" t="inlineStr">
+        <is>
+          <t>U.K.G (TEL)</t>
+        </is>
+      </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
           <t>L.K.G (TEL)</t>
         </is>
       </c>
-      <c r="E91" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (TEL)</t>
-        </is>
-      </c>
+      <c r="E91" s="7" t="inlineStr"/>
       <c r="F91" s="7" t="inlineStr"/>
       <c r="G91" s="7" t="inlineStr">
         <is>
-          <t>U.K.G (TEL)</t>
-        </is>
-      </c>
-      <c r="H91" s="7" t="inlineStr">
-        <is>
           <t>Class 2 (TEL)</t>
         </is>
       </c>
+      <c r="H91" s="7" t="inlineStr"/>
       <c r="I91" s="8" t="inlineStr">
         <is>
           <t>Class 1</t>
@@ -3132,23 +3132,23 @@
           <t>Class 7 (SOC)</t>
         </is>
       </c>
-      <c r="C95" s="7" t="inlineStr">
+      <c r="C95" s="7" t="inlineStr"/>
+      <c r="D95" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (SOC)</t>
+        </is>
+      </c>
+      <c r="E95" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (SOC)</t>
+        </is>
+      </c>
+      <c r="F95" s="7" t="inlineStr">
         <is>
           <t>Class 4 (SOC)</t>
         </is>
       </c>
-      <c r="D95" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (SOC)</t>
-        </is>
-      </c>
-      <c r="E95" s="7" t="inlineStr"/>
-      <c r="F95" s="7" t="inlineStr"/>
-      <c r="G95" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (SOC)</t>
-        </is>
-      </c>
+      <c r="G95" s="7" t="inlineStr"/>
       <c r="H95" s="7" t="inlineStr">
         <is>
           <t>Class 3 (SOC)</t>
@@ -3173,24 +3173,24 @@
       </c>
       <c r="C96" s="7" t="inlineStr">
         <is>
+          <t>Class 5 (SOC)</t>
+        </is>
+      </c>
+      <c r="D96" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (SOC)</t>
+        </is>
+      </c>
+      <c r="E96" s="7" t="inlineStr"/>
+      <c r="F96" s="7" t="inlineStr"/>
+      <c r="G96" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (SOC)</t>
+        </is>
+      </c>
+      <c r="H96" s="7" t="inlineStr">
+        <is>
           <t>Class 6 (SOC)</t>
-        </is>
-      </c>
-      <c r="D96" s="7" t="inlineStr"/>
-      <c r="E96" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (SOC)</t>
-        </is>
-      </c>
-      <c r="F96" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (SOC)</t>
-        </is>
-      </c>
-      <c r="G96" s="7" t="inlineStr"/>
-      <c r="H96" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (SOC)</t>
         </is>
       </c>
       <c r="I96" s="8" t="inlineStr">
@@ -3212,26 +3212,26 @@
       </c>
       <c r="C97" s="7" t="inlineStr">
         <is>
+          <t>Class 5 (SOC)</t>
+        </is>
+      </c>
+      <c r="D97" s="7" t="inlineStr"/>
+      <c r="E97" s="7" t="inlineStr">
+        <is>
           <t>Class 4 (SOC)</t>
         </is>
       </c>
-      <c r="D97" s="7" t="inlineStr">
+      <c r="F97" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (SOC)</t>
+        </is>
+      </c>
+      <c r="G97" s="7" t="inlineStr">
         <is>
           <t>Class 3 (SOC)</t>
         </is>
       </c>
-      <c r="E97" s="7" t="inlineStr"/>
-      <c r="F97" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (SOC)</t>
-        </is>
-      </c>
-      <c r="G97" s="7" t="inlineStr"/>
-      <c r="H97" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (SOC)</t>
-        </is>
-      </c>
+      <c r="H97" s="7" t="inlineStr"/>
       <c r="I97" s="8" t="inlineStr">
         <is>
           <t>Class 7</t>
@@ -3254,21 +3254,21 @@
           <t>Class 3 (SOC)</t>
         </is>
       </c>
-      <c r="D98" s="7" t="inlineStr"/>
-      <c r="E98" s="7" t="inlineStr">
+      <c r="D98" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (SOC)</t>
+        </is>
+      </c>
+      <c r="E98" s="7" t="inlineStr"/>
+      <c r="F98" s="7" t="inlineStr"/>
+      <c r="G98" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (SOC)</t>
+        </is>
+      </c>
+      <c r="H98" s="7" t="inlineStr">
         <is>
           <t>Class 4 (SOC)</t>
-        </is>
-      </c>
-      <c r="F98" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (SOC)</t>
-        </is>
-      </c>
-      <c r="G98" s="7" t="inlineStr"/>
-      <c r="H98" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (SOC)</t>
         </is>
       </c>
       <c r="I98" s="8" t="inlineStr">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (SOC)</t>
+          <t>Class 5 (SOC)</t>
         </is>
       </c>
       <c r="D99" s="7" t="inlineStr">
@@ -3301,15 +3301,15 @@
       <c r="E99" s="7" t="inlineStr"/>
       <c r="F99" s="7" t="inlineStr">
         <is>
+          <t>Class 6 (SOC)</t>
+        </is>
+      </c>
+      <c r="G99" s="7" t="inlineStr"/>
+      <c r="H99" s="7" t="inlineStr">
+        <is>
           <t>Class 3 (SOC)</t>
         </is>
       </c>
-      <c r="G99" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (SOC)</t>
-        </is>
-      </c>
-      <c r="H99" s="7" t="inlineStr"/>
       <c r="I99" s="8" t="inlineStr">
         <is>
           <t>Class 7</t>
@@ -3327,26 +3327,26 @@
           <t>Class 7 (SOC)</t>
         </is>
       </c>
-      <c r="C100" s="7" t="inlineStr">
+      <c r="C100" s="7" t="inlineStr"/>
+      <c r="D100" s="7" t="inlineStr">
         <is>
           <t>Class 4 (SOC)</t>
         </is>
       </c>
-      <c r="D100" s="7" t="inlineStr">
+      <c r="E100" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (SOC)</t>
+        </is>
+      </c>
+      <c r="F100" s="7" t="inlineStr">
         <is>
           <t>Class 3 (SOC)</t>
-        </is>
-      </c>
-      <c r="E100" s="7" t="inlineStr"/>
-      <c r="F100" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (SOC)</t>
         </is>
       </c>
       <c r="G100" s="7" t="inlineStr"/>
       <c r="H100" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (SOC)</t>
+          <t>Class 5 (SOC)</t>
         </is>
       </c>
       <c r="I100" s="8" t="inlineStr">
@@ -3424,24 +3424,28 @@
         </is>
       </c>
       <c r="B104" s="7" t="inlineStr"/>
-      <c r="C104" s="7" t="inlineStr"/>
+      <c r="C104" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (ENG)</t>
+        </is>
+      </c>
       <c r="D104" s="7" t="inlineStr">
         <is>
-          <t>Class 10 (GRAM)</t>
+          <t>Class 7 (ENG)</t>
         </is>
       </c>
       <c r="E104" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (ENG)</t>
+          <t>Class 9 (GRAM)</t>
         </is>
       </c>
       <c r="F104" s="7" t="inlineStr"/>
-      <c r="G104" s="7" t="inlineStr"/>
-      <c r="H104" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (ENG)</t>
-        </is>
-      </c>
+      <c r="G104" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (GRAM)</t>
+        </is>
+      </c>
+      <c r="H104" s="7" t="inlineStr"/>
       <c r="I104" s="7" t="inlineStr"/>
     </row>
     <row r="105">
@@ -3451,24 +3455,24 @@
         </is>
       </c>
       <c r="B105" s="7" t="inlineStr"/>
-      <c r="C105" s="7" t="inlineStr"/>
-      <c r="D105" s="7" t="inlineStr">
+      <c r="C105" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (GRAM)</t>
+        </is>
+      </c>
+      <c r="D105" s="7" t="inlineStr"/>
+      <c r="E105" s="7" t="inlineStr">
         <is>
           <t>Class 6 (ENG)</t>
         </is>
       </c>
-      <c r="E105" s="7" t="inlineStr"/>
-      <c r="F105" s="7" t="inlineStr"/>
-      <c r="G105" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (GRAM)</t>
-        </is>
-      </c>
-      <c r="H105" s="7" t="inlineStr">
+      <c r="F105" s="7" t="inlineStr">
         <is>
           <t>Class 7 (ENG)</t>
         </is>
       </c>
+      <c r="G105" s="7" t="inlineStr"/>
+      <c r="H105" s="7" t="inlineStr"/>
       <c r="I105" s="7" t="inlineStr"/>
     </row>
     <row r="106">
@@ -3481,17 +3485,17 @@
       <c r="C106" s="7" t="inlineStr"/>
       <c r="D106" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (ENG)</t>
-        </is>
-      </c>
-      <c r="E106" s="7" t="inlineStr">
-        <is>
           <t>Class 7 (ENG)</t>
         </is>
       </c>
+      <c r="E106" s="7" t="inlineStr"/>
       <c r="F106" s="7" t="inlineStr"/>
       <c r="G106" s="7" t="inlineStr"/>
-      <c r="H106" s="7" t="inlineStr"/>
+      <c r="H106" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (ENG)</t>
+        </is>
+      </c>
       <c r="I106" s="7" t="inlineStr"/>
     </row>
     <row r="107">
@@ -3501,22 +3505,18 @@
         </is>
       </c>
       <c r="B107" s="7" t="inlineStr"/>
-      <c r="C107" s="7" t="inlineStr"/>
+      <c r="C107" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (ENG)</t>
+        </is>
+      </c>
       <c r="D107" s="7" t="inlineStr">
         <is>
           <t>Class 7 (ENG)</t>
         </is>
       </c>
-      <c r="E107" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (ENG)</t>
-        </is>
-      </c>
-      <c r="F107" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (GRAM)</t>
-        </is>
-      </c>
+      <c r="E107" s="7" t="inlineStr"/>
+      <c r="F107" s="7" t="inlineStr"/>
       <c r="G107" s="7" t="inlineStr"/>
       <c r="H107" s="7" t="inlineStr"/>
       <c r="I107" s="7" t="inlineStr"/>
@@ -3528,22 +3528,22 @@
         </is>
       </c>
       <c r="B108" s="7" t="inlineStr"/>
-      <c r="C108" s="7" t="inlineStr"/>
-      <c r="D108" s="7" t="inlineStr"/>
-      <c r="E108" s="7" t="inlineStr">
+      <c r="C108" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (GRAM)</t>
+        </is>
+      </c>
+      <c r="D108" s="7" t="inlineStr">
         <is>
           <t>Class 6 (ENG)</t>
         </is>
       </c>
+      <c r="E108" s="7" t="inlineStr"/>
       <c r="F108" s="7" t="inlineStr"/>
-      <c r="G108" s="7" t="inlineStr">
+      <c r="G108" s="7" t="inlineStr"/>
+      <c r="H108" s="7" t="inlineStr">
         <is>
           <t>Class 7 (ENG)</t>
-        </is>
-      </c>
-      <c r="H108" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (GRAM)</t>
         </is>
       </c>
       <c r="I108" s="7" t="inlineStr"/>
@@ -3563,12 +3563,12 @@
       <c r="D109" s="7" t="inlineStr"/>
       <c r="E109" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (GRAM)</t>
+          <t>Class 7 (ENG)</t>
         </is>
       </c>
       <c r="F109" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (ENG)</t>
+          <t>Class 6 (GRAM)</t>
         </is>
       </c>
       <c r="G109" s="7" t="inlineStr"/>
@@ -3646,13 +3646,13 @@
       <c r="B113" s="7" t="inlineStr"/>
       <c r="C113" s="7" t="inlineStr">
         <is>
-          <t>Class 10 (HIN)</t>
+          <t>Class 3 (HIN)</t>
         </is>
       </c>
       <c r="D113" s="7" t="inlineStr"/>
       <c r="E113" s="7" t="inlineStr">
         <is>
-          <t>Class 3 (HIN)</t>
+          <t>Class 10 (HIN)</t>
         </is>
       </c>
       <c r="F113" s="7" t="inlineStr"/>
@@ -3667,15 +3667,11 @@
         </is>
       </c>
       <c r="B114" s="7" t="inlineStr"/>
-      <c r="C114" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (HIN)</t>
-        </is>
-      </c>
+      <c r="C114" s="7" t="inlineStr"/>
       <c r="D114" s="7" t="inlineStr"/>
       <c r="E114" s="7" t="inlineStr">
         <is>
-          <t>Class 10 (HIN)</t>
+          <t>Class 3 (HIN)</t>
         </is>
       </c>
       <c r="F114" s="7" t="inlineStr"/>
@@ -3706,12 +3702,12 @@
           <t>Class 10 (HIN)</t>
         </is>
       </c>
-      <c r="G115" s="7" t="inlineStr"/>
-      <c r="H115" s="7" t="inlineStr">
+      <c r="G115" s="7" t="inlineStr">
         <is>
           <t>Class 9 (HIN)</t>
         </is>
       </c>
+      <c r="H115" s="7" t="inlineStr"/>
       <c r="I115" s="7" t="inlineStr"/>
     </row>
     <row r="116">
@@ -3720,25 +3716,25 @@
           <t>THU</t>
         </is>
       </c>
-      <c r="B116" s="7" t="inlineStr"/>
+      <c r="B116" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (HIN)</t>
+        </is>
+      </c>
       <c r="C116" s="7" t="inlineStr"/>
       <c r="D116" s="7" t="inlineStr"/>
       <c r="E116" s="7" t="inlineStr">
         <is>
-          <t>Class 10 (HIN)</t>
+          <t>Class 3 (HIN)</t>
         </is>
       </c>
       <c r="F116" s="7" t="inlineStr"/>
       <c r="G116" s="7" t="inlineStr">
         <is>
-          <t>Class 3 (HIN)</t>
-        </is>
-      </c>
-      <c r="H116" s="7" t="inlineStr">
-        <is>
           <t>Class 9 (HIN)</t>
         </is>
       </c>
+      <c r="H116" s="7" t="inlineStr"/>
       <c r="I116" s="7" t="inlineStr"/>
     </row>
     <row r="117">
@@ -3750,21 +3746,21 @@
       <c r="B117" s="7" t="inlineStr"/>
       <c r="C117" s="7" t="inlineStr">
         <is>
-          <t>Class 10 (HIN)</t>
+          <t>Class 3 (HIN)</t>
         </is>
       </c>
       <c r="D117" s="7" t="inlineStr"/>
       <c r="E117" s="7" t="inlineStr">
         <is>
+          <t>Class 10 (HIN)</t>
+        </is>
+      </c>
+      <c r="F117" s="7" t="inlineStr">
+        <is>
           <t>Class 9 (HIN)</t>
         </is>
       </c>
-      <c r="F117" s="7" t="inlineStr"/>
-      <c r="G117" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (HIN)</t>
-        </is>
-      </c>
+      <c r="G117" s="7" t="inlineStr"/>
       <c r="H117" s="7" t="inlineStr"/>
       <c r="I117" s="7" t="inlineStr"/>
     </row>
@@ -3774,7 +3770,11 @@
           <t>SAT</t>
         </is>
       </c>
-      <c r="B118" s="7" t="inlineStr"/>
+      <c r="B118" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (HIN)</t>
+        </is>
+      </c>
       <c r="C118" s="7" t="inlineStr"/>
       <c r="D118" s="7" t="inlineStr"/>
       <c r="E118" s="7" t="inlineStr">
@@ -3857,30 +3857,30 @@
       </c>
       <c r="B122" s="7" t="inlineStr">
         <is>
+          <t>Class 2 (EVS)</t>
+        </is>
+      </c>
+      <c r="C122" s="7" t="inlineStr">
+        <is>
           <t>Class 2 (HIN)</t>
         </is>
       </c>
-      <c r="C122" s="7" t="inlineStr">
+      <c r="D122" s="7" t="inlineStr"/>
+      <c r="E122" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (EVS)</t>
+        </is>
+      </c>
+      <c r="F122" s="7" t="inlineStr">
         <is>
           <t>U.K.G (ENG)</t>
         </is>
       </c>
-      <c r="D122" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (EVS)</t>
-        </is>
-      </c>
-      <c r="E122" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (EVS)</t>
-        </is>
-      </c>
-      <c r="F122" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (EVS)</t>
-        </is>
-      </c>
-      <c r="G122" s="7" t="inlineStr"/>
+      <c r="G122" s="7" t="inlineStr">
+        <is>
+          <t>U.K.G (ENG)</t>
+        </is>
+      </c>
       <c r="H122" s="7" t="inlineStr">
         <is>
           <t>U.K.G (ENG)</t>
@@ -3905,28 +3905,28 @@
       </c>
       <c r="C123" s="7" t="inlineStr">
         <is>
+          <t>Class 1 (HIN)</t>
+        </is>
+      </c>
+      <c r="D123" s="7" t="inlineStr">
+        <is>
           <t>Class 1 (EVS)</t>
         </is>
       </c>
-      <c r="D123" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (G.K)</t>
-        </is>
-      </c>
-      <c r="E123" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (EVS)</t>
-        </is>
-      </c>
+      <c r="E123" s="7" t="inlineStr"/>
       <c r="F123" s="7" t="inlineStr">
         <is>
-          <t>Class 1 (HIN)</t>
-        </is>
-      </c>
-      <c r="G123" s="7" t="inlineStr"/>
+          <t>U.K.G (ENG)</t>
+        </is>
+      </c>
+      <c r="G123" s="7" t="inlineStr">
+        <is>
+          <t>U.K.G (ENG)</t>
+        </is>
+      </c>
       <c r="H123" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (EVS)</t>
+          <t>Class 2 (HIN)</t>
         </is>
       </c>
       <c r="I123" s="8" t="inlineStr">
@@ -3948,30 +3948,30 @@
       </c>
       <c r="C124" s="7" t="inlineStr">
         <is>
+          <t>Class 1 (EVS)</t>
+        </is>
+      </c>
+      <c r="D124" s="7" t="inlineStr">
+        <is>
+          <t>Class 1 (HIN)</t>
+        </is>
+      </c>
+      <c r="E124" s="7" t="inlineStr">
+        <is>
           <t>U.K.G (ENG)</t>
         </is>
       </c>
-      <c r="D124" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (ENG)</t>
-        </is>
-      </c>
-      <c r="E124" s="7" t="inlineStr">
+      <c r="F124" s="7" t="inlineStr"/>
+      <c r="G124" s="7" t="inlineStr">
         <is>
           <t>Class 2 (HIN)</t>
         </is>
       </c>
-      <c r="F124" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (EVS)</t>
-        </is>
-      </c>
-      <c r="G124" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (HIN)</t>
-        </is>
-      </c>
-      <c r="H124" s="7" t="inlineStr"/>
+      <c r="H124" s="7" t="inlineStr">
+        <is>
+          <t>Class 1 (EVS)</t>
+        </is>
+      </c>
       <c r="I124" s="8" t="inlineStr">
         <is>
           <t>Class 2</t>
@@ -3991,27 +3991,27 @@
       </c>
       <c r="C125" s="7" t="inlineStr">
         <is>
-          <t>Class 1 (EVS)</t>
+          <t>U.K.G (ENG)</t>
         </is>
       </c>
       <c r="D125" s="7" t="inlineStr">
         <is>
+          <t>Class 1 (HIN)</t>
+        </is>
+      </c>
+      <c r="E125" s="7" t="inlineStr">
+        <is>
           <t>U.K.G (ENG)</t>
         </is>
       </c>
-      <c r="E125" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (ENG)</t>
-        </is>
-      </c>
       <c r="F125" s="7" t="inlineStr">
         <is>
-          <t>Class 1 (EVS)</t>
+          <t>Class 2 (EVS)</t>
         </is>
       </c>
       <c r="G125" s="7" t="inlineStr">
         <is>
-          <t>Class 1 (HIN)</t>
+          <t>Class 3 (G.K)</t>
         </is>
       </c>
       <c r="H125" s="7" t="inlineStr"/>
@@ -4029,20 +4029,24 @@
       </c>
       <c r="B126" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (HIN)</t>
+          <t>Class 2 (EVS)</t>
         </is>
       </c>
       <c r="C126" s="7" t="inlineStr">
         <is>
+          <t>U.K.G (ENG)</t>
+        </is>
+      </c>
+      <c r="D126" s="7" t="inlineStr">
+        <is>
+          <t>U.K.G (ENG)</t>
+        </is>
+      </c>
+      <c r="E126" s="7" t="inlineStr">
+        <is>
           <t>Class 1 (EVS)</t>
         </is>
       </c>
-      <c r="D126" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (ENG)</t>
-        </is>
-      </c>
-      <c r="E126" s="7" t="inlineStr"/>
       <c r="F126" s="7" t="inlineStr">
         <is>
           <t>Class 1 (EVS)</t>
@@ -4068,35 +4072,31 @@
       </c>
       <c r="B127" s="7" t="inlineStr">
         <is>
+          <t>Class 2 (HIN)</t>
+        </is>
+      </c>
+      <c r="C127" s="7" t="inlineStr">
+        <is>
           <t>Class 2 (EVS)</t>
         </is>
       </c>
-      <c r="C127" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (ENG)</t>
-        </is>
-      </c>
       <c r="D127" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (HIN)</t>
-        </is>
-      </c>
-      <c r="E127" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (ENG)</t>
-        </is>
-      </c>
+          <t>Class 1 (EVS)</t>
+        </is>
+      </c>
+      <c r="E127" s="7" t="inlineStr"/>
       <c r="F127" s="7" t="inlineStr">
         <is>
-          <t>U.K.G (ENG)</t>
-        </is>
-      </c>
-      <c r="G127" s="7" t="inlineStr"/>
-      <c r="H127" s="7" t="inlineStr">
+          <t>Class 1 (EVS)</t>
+        </is>
+      </c>
+      <c r="G127" s="7" t="inlineStr">
         <is>
           <t>Class 1 (HIN)</t>
         </is>
       </c>
+      <c r="H127" s="7" t="inlineStr"/>
       <c r="I127" s="8" t="inlineStr">
         <is>
           <t>Class 2</t>
@@ -4176,25 +4176,21 @@
           <t>Class 6 (MATH)</t>
         </is>
       </c>
-      <c r="C131" s="7" t="inlineStr"/>
+      <c r="C131" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (MATH)</t>
+        </is>
+      </c>
       <c r="D131" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (MATH)</t>
-        </is>
-      </c>
-      <c r="E131" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (G.K)</t>
-        </is>
-      </c>
-      <c r="F131" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (COMP)</t>
-        </is>
-      </c>
+          <t>Class 8 (MATH)</t>
+        </is>
+      </c>
+      <c r="E131" s="7" t="inlineStr"/>
+      <c r="F131" s="7" t="inlineStr"/>
       <c r="G131" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (MATH)</t>
+          <t>Class 8 (MATH)</t>
         </is>
       </c>
       <c r="H131" s="7" t="inlineStr"/>
@@ -4212,7 +4208,7 @@
       </c>
       <c r="B132" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (G.K)</t>
+          <t>Class 6 (MATH)</t>
         </is>
       </c>
       <c r="C132" s="7" t="inlineStr"/>
@@ -4223,7 +4219,7 @@
       </c>
       <c r="E132" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (MATH)</t>
+          <t>Class 7 (COMP)</t>
         </is>
       </c>
       <c r="F132" s="7" t="inlineStr"/>
@@ -4253,19 +4249,23 @@
       <c r="C133" s="7" t="inlineStr"/>
       <c r="D133" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (MATH)</t>
+          <t>Class 6 (G.K)</t>
         </is>
       </c>
       <c r="E133" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (MATH)</t>
-        </is>
-      </c>
-      <c r="F133" s="7" t="inlineStr"/>
+          <t>Class 7 (MATH)</t>
+        </is>
+      </c>
+      <c r="F133" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (COMP)</t>
+        </is>
+      </c>
       <c r="G133" s="7" t="inlineStr"/>
       <c r="H133" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (MATH)</t>
+          <t>Class 8 (MATH)</t>
         </is>
       </c>
       <c r="I133" s="8" t="inlineStr">
@@ -4327,12 +4327,12 @@
           <t>Class 7 (MATH)</t>
         </is>
       </c>
-      <c r="F135" s="7" t="inlineStr"/>
-      <c r="G135" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (MATH)</t>
-        </is>
-      </c>
+      <c r="F135" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (G.K)</t>
+        </is>
+      </c>
+      <c r="G135" s="7" t="inlineStr"/>
       <c r="H135" s="7" t="inlineStr">
         <is>
           <t>Class 6 (MATH)</t>
@@ -4355,26 +4355,26 @@
           <t>Class 6 (MATH)</t>
         </is>
       </c>
-      <c r="C136" s="7" t="inlineStr"/>
+      <c r="C136" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (MATH)</t>
+        </is>
+      </c>
       <c r="D136" s="7" t="inlineStr">
         <is>
           <t>Class 5 (G.K)</t>
         </is>
       </c>
-      <c r="E136" s="7" t="inlineStr">
+      <c r="E136" s="7" t="inlineStr"/>
+      <c r="F136" s="7" t="inlineStr">
         <is>
           <t>Class 8 (MATH)</t>
         </is>
       </c>
-      <c r="F136" s="7" t="inlineStr"/>
-      <c r="G136" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (MATH)</t>
-        </is>
-      </c>
+      <c r="G136" s="7" t="inlineStr"/>
       <c r="H136" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (COMP)</t>
+          <t>Class 8 (MATH)</t>
         </is>
       </c>
       <c r="I136" s="8" t="inlineStr">
@@ -4458,24 +4458,32 @@
       </c>
       <c r="C140" s="7" t="inlineStr">
         <is>
+          <t>L.K.G (MATH)</t>
+        </is>
+      </c>
+      <c r="D140" s="7" t="inlineStr">
+        <is>
+          <t>L.K.G (MATH)</t>
+        </is>
+      </c>
+      <c r="E140" s="7" t="inlineStr">
+        <is>
           <t>L.K.G (ORAL)</t>
         </is>
       </c>
-      <c r="D140" s="7" t="inlineStr"/>
-      <c r="E140" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (MATH)</t>
-        </is>
-      </c>
       <c r="F140" s="7" t="inlineStr">
         <is>
           <t>L.K.G (EVS)</t>
         </is>
       </c>
-      <c r="G140" s="7" t="inlineStr"/>
+      <c r="G140" s="7" t="inlineStr">
+        <is>
+          <t>L.K.G (ENG)</t>
+        </is>
+      </c>
       <c r="H140" s="7" t="inlineStr">
         <is>
-          <t>L.K.G (EVS)</t>
+          <t>L.K.G (ENG)</t>
         </is>
       </c>
       <c r="I140" s="8" t="inlineStr">
@@ -4492,7 +4500,7 @@
       </c>
       <c r="B141" s="7" t="inlineStr">
         <is>
-          <t>L.K.G (ORAL)</t>
+          <t>L.K.G (MATH)</t>
         </is>
       </c>
       <c r="C141" s="7" t="inlineStr">
@@ -4512,13 +4520,13 @@
       </c>
       <c r="F141" s="7" t="inlineStr">
         <is>
-          <t>L.K.G (EVS)</t>
+          <t>L.K.G (MATH)</t>
         </is>
       </c>
       <c r="G141" s="7" t="inlineStr"/>
       <c r="H141" s="7" t="inlineStr">
         <is>
-          <t>L.K.G (EVS)</t>
+          <t>L.K.G (MATH)</t>
         </is>
       </c>
       <c r="I141" s="8" t="inlineStr">
@@ -4535,32 +4543,32 @@
       </c>
       <c r="B142" s="7" t="inlineStr">
         <is>
+          <t>L.K.G (ENG)</t>
+        </is>
+      </c>
+      <c r="C142" s="7" t="inlineStr">
+        <is>
+          <t>L.K.G (MATH)</t>
+        </is>
+      </c>
+      <c r="D142" s="7" t="inlineStr">
+        <is>
+          <t>L.K.G (ENG)</t>
+        </is>
+      </c>
+      <c r="E142" s="7" t="inlineStr">
+        <is>
+          <t>L.K.G (EVS)</t>
+        </is>
+      </c>
+      <c r="F142" s="7" t="inlineStr">
+        <is>
+          <t>L.K.G (EVS)</t>
+        </is>
+      </c>
+      <c r="G142" s="7" t="inlineStr">
+        <is>
           <t>L.K.G (ORAL)</t>
-        </is>
-      </c>
-      <c r="C142" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (EVS)</t>
-        </is>
-      </c>
-      <c r="D142" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (EVS)</t>
-        </is>
-      </c>
-      <c r="E142" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (MATH)</t>
-        </is>
-      </c>
-      <c r="F142" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (MATH)</t>
-        </is>
-      </c>
-      <c r="G142" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (ENG)</t>
         </is>
       </c>
       <c r="H142" s="7" t="inlineStr"/>
@@ -4578,31 +4586,31 @@
       </c>
       <c r="B143" s="7" t="inlineStr">
         <is>
+          <t>L.K.G (ORAL)</t>
+        </is>
+      </c>
+      <c r="C143" s="7" t="inlineStr">
+        <is>
           <t>L.K.G (ENG)</t>
         </is>
       </c>
-      <c r="C143" s="7" t="inlineStr">
+      <c r="D143" s="7" t="inlineStr"/>
+      <c r="E143" s="7" t="inlineStr">
+        <is>
+          <t>L.K.G (MATH)</t>
+        </is>
+      </c>
+      <c r="F143" s="7" t="inlineStr">
+        <is>
+          <t>L.K.G (MATH)</t>
+        </is>
+      </c>
+      <c r="G143" s="7" t="inlineStr"/>
+      <c r="H143" s="7" t="inlineStr">
         <is>
           <t>L.K.G (ENG)</t>
         </is>
       </c>
-      <c r="D143" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (ENG)</t>
-        </is>
-      </c>
-      <c r="E143" s="7" t="inlineStr"/>
-      <c r="F143" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (ENG)</t>
-        </is>
-      </c>
-      <c r="G143" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (MATH)</t>
-        </is>
-      </c>
-      <c r="H143" s="7" t="inlineStr"/>
       <c r="I143" s="8" t="inlineStr">
         <is>
           <t>L.K.G</t>
@@ -4622,17 +4630,13 @@
       </c>
       <c r="C144" s="7" t="inlineStr">
         <is>
-          <t>L.K.G (MATH)</t>
-        </is>
-      </c>
-      <c r="D144" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (MATH)</t>
-        </is>
-      </c>
+          <t>L.K.G (ENG)</t>
+        </is>
+      </c>
+      <c r="D144" s="7" t="inlineStr"/>
       <c r="E144" s="7" t="inlineStr">
         <is>
-          <t>L.K.G (MATH)</t>
+          <t>L.K.G (EVS)</t>
         </is>
       </c>
       <c r="F144" s="7" t="inlineStr">
@@ -4643,7 +4647,7 @@
       <c r="G144" s="7" t="inlineStr"/>
       <c r="H144" s="7" t="inlineStr">
         <is>
-          <t>L.K.G (MATH)</t>
+          <t>L.K.G (ENG)</t>
         </is>
       </c>
       <c r="I144" s="8" t="inlineStr">
@@ -4660,35 +4664,31 @@
       </c>
       <c r="B145" s="7" t="inlineStr">
         <is>
-          <t>L.K.G (ENG)</t>
+          <t>L.K.G (EVS)</t>
         </is>
       </c>
       <c r="C145" s="7" t="inlineStr">
         <is>
-          <t>L.K.G (MATH)</t>
+          <t>L.K.G (EVS)</t>
         </is>
       </c>
       <c r="D145" s="7" t="inlineStr"/>
       <c r="E145" s="7" t="inlineStr">
         <is>
+          <t>L.K.G (ENG)</t>
+        </is>
+      </c>
+      <c r="F145" s="7" t="inlineStr">
+        <is>
+          <t>L.K.G (MATH)</t>
+        </is>
+      </c>
+      <c r="G145" s="7" t="inlineStr">
+        <is>
           <t>L.K.G (ORAL)</t>
         </is>
       </c>
-      <c r="F145" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (ENG)</t>
-        </is>
-      </c>
-      <c r="G145" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (ENG)</t>
-        </is>
-      </c>
-      <c r="H145" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (ENG)</t>
-        </is>
-      </c>
+      <c r="H145" s="7" t="inlineStr"/>
       <c r="I145" s="8" t="inlineStr">
         <is>
           <t>L.K.G</t>
@@ -4796,12 +4796,12 @@
       <c r="E150" s="7" t="inlineStr"/>
       <c r="F150" s="7" t="inlineStr">
         <is>
+          <t>Class 10 (ENG)</t>
+        </is>
+      </c>
+      <c r="G150" s="7" t="inlineStr">
+        <is>
           <t>Class 8 (ENG)</t>
-        </is>
-      </c>
-      <c r="G150" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (ENG)</t>
         </is>
       </c>
       <c r="H150" s="7" t="inlineStr">
@@ -4826,17 +4826,17 @@
           <t>Class 9 (ENG)</t>
         </is>
       </c>
-      <c r="G151" s="7" t="inlineStr"/>
+      <c r="G151" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (ENG)</t>
+        </is>
+      </c>
       <c r="H151" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (ENG)</t>
-        </is>
-      </c>
-      <c r="I151" s="8" t="inlineStr">
-        <is>
           <t>Class 10 (ENG)</t>
         </is>
       </c>
+      <c r="I151" s="7" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="6" t="inlineStr">
@@ -4850,20 +4850,20 @@
       <c r="E152" s="7" t="inlineStr"/>
       <c r="F152" s="7" t="inlineStr">
         <is>
+          <t>Class 9 (ENG)</t>
+        </is>
+      </c>
+      <c r="G152" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (ENG)</t>
+        </is>
+      </c>
+      <c r="H152" s="7" t="inlineStr"/>
+      <c r="I152" s="8" t="inlineStr">
+        <is>
           <t>Class 10 (ENG)</t>
         </is>
       </c>
-      <c r="G152" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (ENG)</t>
-        </is>
-      </c>
-      <c r="H152" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (ENG)</t>
-        </is>
-      </c>
-      <c r="I152" s="7" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="6" t="inlineStr">
@@ -4877,17 +4877,17 @@
       <c r="E153" s="7" t="inlineStr"/>
       <c r="F153" s="7" t="inlineStr">
         <is>
+          <t>Class 8 (ENG)</t>
+        </is>
+      </c>
+      <c r="G153" s="7" t="inlineStr">
+        <is>
           <t>Class 9 (ENG)</t>
         </is>
       </c>
-      <c r="G153" s="7" t="inlineStr">
+      <c r="H153" s="7" t="inlineStr">
         <is>
           <t>Class 10 (ENG)</t>
-        </is>
-      </c>
-      <c r="H153" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (ENG)</t>
         </is>
       </c>
       <c r="I153" s="7" t="inlineStr"/>
@@ -4904,17 +4904,17 @@
       <c r="E154" s="7" t="inlineStr"/>
       <c r="F154" s="7" t="inlineStr">
         <is>
+          <t>Class 10 (ENG)</t>
+        </is>
+      </c>
+      <c r="G154" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (ENG)</t>
+        </is>
+      </c>
+      <c r="H154" s="7" t="inlineStr">
+        <is>
           <t>Class 9 (ENG)</t>
-        </is>
-      </c>
-      <c r="G154" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (ENG)</t>
-        </is>
-      </c>
-      <c r="H154" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (ENG)</t>
         </is>
       </c>
       <c r="I154" s="7" t="inlineStr"/>
@@ -4992,7 +4992,7 @@
       <c r="D158" s="7" t="inlineStr"/>
       <c r="E158" s="7" t="inlineStr">
         <is>
-          <t>Class 10 (SOC)</t>
+          <t>Class 8 (SOC)</t>
         </is>
       </c>
       <c r="F158" s="7" t="inlineStr">
@@ -5003,7 +5003,7 @@
       <c r="G158" s="7" t="inlineStr"/>
       <c r="H158" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (SOC)</t>
+          <t>Class 10 (SOC)</t>
         </is>
       </c>
       <c r="I158" s="7" t="inlineStr"/>
@@ -5019,20 +5019,20 @@
       <c r="D159" s="7" t="inlineStr"/>
       <c r="E159" s="7" t="inlineStr">
         <is>
+          <t>Class 8 (SOC)</t>
+        </is>
+      </c>
+      <c r="F159" s="7" t="inlineStr">
+        <is>
           <t>Class 9 (SOC)</t>
         </is>
       </c>
-      <c r="F159" s="7" t="inlineStr">
+      <c r="G159" s="7" t="inlineStr"/>
+      <c r="H159" s="7" t="inlineStr">
         <is>
           <t>Class 10 (SOC)</t>
         </is>
       </c>
-      <c r="G159" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (SOC)</t>
-        </is>
-      </c>
-      <c r="H159" s="7" t="inlineStr"/>
       <c r="I159" s="7" t="inlineStr"/>
     </row>
     <row r="160">
@@ -5041,25 +5041,25 @@
           <t>WED</t>
         </is>
       </c>
-      <c r="B160" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (SOC)</t>
-        </is>
-      </c>
-      <c r="C160" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (SOC)</t>
-        </is>
-      </c>
+      <c r="B160" s="7" t="inlineStr"/>
+      <c r="C160" s="7" t="inlineStr"/>
       <c r="D160" s="7" t="inlineStr"/>
       <c r="E160" s="7" t="inlineStr">
         <is>
+          <t>Class 8 (SOC)</t>
+        </is>
+      </c>
+      <c r="F160" s="7" t="inlineStr"/>
+      <c r="G160" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (SOC)</t>
+        </is>
+      </c>
+      <c r="H160" s="7" t="inlineStr">
+        <is>
           <t>Class 9 (SOC)</t>
         </is>
       </c>
-      <c r="F160" s="7" t="inlineStr"/>
-      <c r="G160" s="7" t="inlineStr"/>
-      <c r="H160" s="7" t="inlineStr"/>
       <c r="I160" s="7" t="inlineStr"/>
     </row>
     <row r="161">
@@ -5068,11 +5068,7 @@
           <t>THU</t>
         </is>
       </c>
-      <c r="B161" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (SOC)</t>
-        </is>
-      </c>
+      <c r="B161" s="7" t="inlineStr"/>
       <c r="C161" s="7" t="inlineStr">
         <is>
           <t>Class 8 (SOC)</t>
@@ -5084,7 +5080,11 @@
           <t>Class 9 (SOC)</t>
         </is>
       </c>
-      <c r="F161" s="7" t="inlineStr"/>
+      <c r="F161" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (SOC)</t>
+        </is>
+      </c>
       <c r="G161" s="7" t="inlineStr"/>
       <c r="H161" s="7" t="inlineStr"/>
       <c r="I161" s="7" t="inlineStr"/>
@@ -5096,24 +5096,24 @@
         </is>
       </c>
       <c r="B162" s="7" t="inlineStr"/>
-      <c r="C162" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (SOC)</t>
-        </is>
-      </c>
+      <c r="C162" s="7" t="inlineStr"/>
       <c r="D162" s="7" t="inlineStr"/>
       <c r="E162" s="7" t="inlineStr">
         <is>
+          <t>Class 9 (SOC)</t>
+        </is>
+      </c>
+      <c r="F162" s="7" t="inlineStr"/>
+      <c r="G162" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (SOC)</t>
+        </is>
+      </c>
+      <c r="H162" s="7" t="inlineStr">
+        <is>
           <t>Class 8 (SOC)</t>
         </is>
       </c>
-      <c r="F162" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (SOC)</t>
-        </is>
-      </c>
-      <c r="G162" s="7" t="inlineStr"/>
-      <c r="H162" s="7" t="inlineStr"/>
       <c r="I162" s="7" t="inlineStr"/>
     </row>
     <row r="163">
@@ -5122,25 +5122,25 @@
           <t>SAT</t>
         </is>
       </c>
-      <c r="B163" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (SOC)</t>
-        </is>
-      </c>
+      <c r="B163" s="7" t="inlineStr"/>
       <c r="C163" s="7" t="inlineStr"/>
       <c r="D163" s="7" t="inlineStr"/>
-      <c r="E163" s="7" t="inlineStr"/>
+      <c r="E163" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (SOC)</t>
+        </is>
+      </c>
       <c r="F163" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (SOC)</t>
-        </is>
-      </c>
-      <c r="G163" s="7" t="inlineStr"/>
-      <c r="H163" s="7" t="inlineStr">
-        <is>
           <t>Class 9 (SOC)</t>
         </is>
       </c>
+      <c r="G163" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (SOC)</t>
+        </is>
+      </c>
+      <c r="H163" s="7" t="inlineStr"/>
       <c r="I163" s="7" t="inlineStr"/>
     </row>
     <row r="165">
@@ -5218,26 +5218,26 @@
       </c>
       <c r="C167" s="7" t="inlineStr">
         <is>
+          <t>U.K.G (HIN)</t>
+        </is>
+      </c>
+      <c r="D167" s="7" t="inlineStr"/>
+      <c r="E167" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (TEL)</t>
+        </is>
+      </c>
+      <c r="F167" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (TEL)</t>
+        </is>
+      </c>
+      <c r="G167" s="7" t="inlineStr">
+        <is>
           <t>Class 5 (TEL)</t>
         </is>
       </c>
-      <c r="D167" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (HIN)</t>
-        </is>
-      </c>
-      <c r="E167" s="7" t="inlineStr"/>
-      <c r="F167" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (TEL)</t>
-        </is>
-      </c>
-      <c r="G167" s="7" t="inlineStr"/>
-      <c r="H167" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (TEL)</t>
-        </is>
-      </c>
+      <c r="H167" s="7" t="inlineStr"/>
       <c r="I167" s="8" t="inlineStr">
         <is>
           <t>Class 3</t>
@@ -5255,28 +5255,24 @@
           <t>Class 3 (TEL)</t>
         </is>
       </c>
-      <c r="C168" s="7" t="inlineStr"/>
+      <c r="C168" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (TEL)</t>
+        </is>
+      </c>
       <c r="D168" s="7" t="inlineStr">
         <is>
-          <t>U.K.G (HIN)</t>
-        </is>
-      </c>
-      <c r="E168" s="7" t="inlineStr">
+          <t>Class 5 (TEL)</t>
+        </is>
+      </c>
+      <c r="E168" s="7" t="inlineStr"/>
+      <c r="F168" s="7" t="inlineStr"/>
+      <c r="G168" s="7" t="inlineStr">
         <is>
           <t>Class 6 (TEL)</t>
         </is>
       </c>
-      <c r="F168" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (TEL)</t>
-        </is>
-      </c>
-      <c r="G168" s="7" t="inlineStr"/>
-      <c r="H168" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (TEL)</t>
-        </is>
-      </c>
+      <c r="H168" s="7" t="inlineStr"/>
       <c r="I168" s="8" t="inlineStr">
         <is>
           <t>Class 3</t>
@@ -5294,20 +5290,20 @@
           <t>Class 3 (TEL)</t>
         </is>
       </c>
-      <c r="C169" s="7" t="inlineStr">
+      <c r="C169" s="7" t="inlineStr"/>
+      <c r="D169" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (TEL)</t>
+        </is>
+      </c>
+      <c r="E169" s="7" t="inlineStr">
         <is>
           <t>Class 6 (TEL)</t>
         </is>
       </c>
-      <c r="D169" s="7" t="inlineStr"/>
-      <c r="E169" s="7" t="inlineStr">
+      <c r="F169" s="7" t="inlineStr">
         <is>
           <t>Class 5 (TEL)</t>
-        </is>
-      </c>
-      <c r="F169" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (TEL)</t>
         </is>
       </c>
       <c r="G169" s="7" t="inlineStr">
@@ -5333,24 +5329,28 @@
           <t>Class 3 (TEL)</t>
         </is>
       </c>
-      <c r="C170" s="7" t="inlineStr"/>
+      <c r="C170" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (TEL)</t>
+        </is>
+      </c>
       <c r="D170" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (TEL)</t>
+          <t>Class 6 (TEL)</t>
         </is>
       </c>
       <c r="E170" s="7" t="inlineStr"/>
       <c r="F170" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (TEL)</t>
-        </is>
-      </c>
-      <c r="G170" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (TEL)</t>
-        </is>
-      </c>
-      <c r="H170" s="7" t="inlineStr"/>
+          <t>Class 4 (TEL)</t>
+        </is>
+      </c>
+      <c r="G170" s="7" t="inlineStr"/>
+      <c r="H170" s="7" t="inlineStr">
+        <is>
+          <t>U.K.G (HIN)</t>
+        </is>
+      </c>
       <c r="I170" s="8" t="inlineStr">
         <is>
           <t>Class 3</t>
@@ -5368,28 +5368,28 @@
           <t>Class 3 (TEL)</t>
         </is>
       </c>
-      <c r="C171" s="7" t="inlineStr"/>
+      <c r="C171" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (TEL)</t>
+        </is>
+      </c>
       <c r="D171" s="7" t="inlineStr">
         <is>
           <t>Class 5 (TEL)</t>
         </is>
       </c>
-      <c r="E171" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (TEL)</t>
-        </is>
-      </c>
-      <c r="F171" s="7" t="inlineStr">
+      <c r="E171" s="7" t="inlineStr"/>
+      <c r="F171" s="7" t="inlineStr"/>
+      <c r="G171" s="7" t="inlineStr">
         <is>
           <t>Class 6 (TEL)</t>
         </is>
       </c>
-      <c r="G171" s="7" t="inlineStr">
+      <c r="H171" s="7" t="inlineStr">
         <is>
           <t>U.K.G (HIN)</t>
         </is>
       </c>
-      <c r="H171" s="7" t="inlineStr"/>
       <c r="I171" s="8" t="inlineStr">
         <is>
           <t>Class 3</t>
@@ -5407,28 +5407,28 @@
           <t>Class 3 (TEL)</t>
         </is>
       </c>
-      <c r="C172" s="7" t="inlineStr"/>
+      <c r="C172" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (TEL)</t>
+        </is>
+      </c>
       <c r="D172" s="7" t="inlineStr">
         <is>
+          <t>U.K.G (HIN)</t>
+        </is>
+      </c>
+      <c r="E172" s="7" t="inlineStr"/>
+      <c r="F172" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (TEL)</t>
+        </is>
+      </c>
+      <c r="G172" s="7" t="inlineStr">
+        <is>
           <t>Class 6 (TEL)</t>
         </is>
       </c>
-      <c r="E172" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (TEL)</t>
-        </is>
-      </c>
-      <c r="F172" s="7" t="inlineStr"/>
-      <c r="G172" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (TEL)</t>
-        </is>
-      </c>
-      <c r="H172" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (HIN)</t>
-        </is>
-      </c>
+      <c r="H172" s="7" t="inlineStr"/>
       <c r="I172" s="8" t="inlineStr">
         <is>
           <t>Class 3</t>
@@ -5508,23 +5508,27 @@
           <t>Class 4 (MATH)</t>
         </is>
       </c>
-      <c r="C176" s="7" t="inlineStr">
+      <c r="C176" s="7" t="inlineStr"/>
+      <c r="D176" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (MATH)</t>
+        </is>
+      </c>
+      <c r="E176" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (MATH)</t>
+        </is>
+      </c>
+      <c r="F176" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (MATH)</t>
+        </is>
+      </c>
+      <c r="G176" s="7" t="inlineStr">
         <is>
           <t>Class 2 (MATH)</t>
         </is>
       </c>
-      <c r="D176" s="7" t="inlineStr"/>
-      <c r="E176" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (MATH)</t>
-        </is>
-      </c>
-      <c r="F176" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (MATH)</t>
-        </is>
-      </c>
-      <c r="G176" s="7" t="inlineStr"/>
       <c r="H176" s="7" t="inlineStr"/>
       <c r="I176" s="8" t="inlineStr">
         <is>
@@ -5545,21 +5549,25 @@
       </c>
       <c r="C177" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (MATH)</t>
+          <t>Class 2 (MATH)</t>
         </is>
       </c>
       <c r="D177" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (MATH)</t>
+          <t>Class 3 (MATH)</t>
         </is>
       </c>
       <c r="E177" s="7" t="inlineStr"/>
       <c r="F177" s="7" t="inlineStr">
         <is>
-          <t>Class 3 (MATH)</t>
-        </is>
-      </c>
-      <c r="G177" s="7" t="inlineStr"/>
+          <t>Class 5 (MATH)</t>
+        </is>
+      </c>
+      <c r="G177" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (MATH)</t>
+        </is>
+      </c>
       <c r="H177" s="7" t="inlineStr"/>
       <c r="I177" s="8" t="inlineStr">
         <is>
@@ -5581,20 +5589,16 @@
       <c r="C178" s="7" t="inlineStr"/>
       <c r="D178" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (MATH)</t>
-        </is>
-      </c>
-      <c r="E178" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (MATH)</t>
-        </is>
-      </c>
-      <c r="F178" s="7" t="inlineStr"/>
-      <c r="G178" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (MATH)</t>
-        </is>
-      </c>
+          <t>Class 2 (MATH)</t>
+        </is>
+      </c>
+      <c r="E178" s="7" t="inlineStr"/>
+      <c r="F178" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (MATH)</t>
+        </is>
+      </c>
+      <c r="G178" s="7" t="inlineStr"/>
       <c r="H178" s="7" t="inlineStr">
         <is>
           <t>Class 5 (MATH)</t>
@@ -5617,28 +5621,28 @@
           <t>Class 4 (MATH)</t>
         </is>
       </c>
-      <c r="C179" s="7" t="inlineStr"/>
+      <c r="C179" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (MATH)</t>
+        </is>
+      </c>
       <c r="D179" s="7" t="inlineStr">
         <is>
+          <t>Class 4 (MATH)</t>
+        </is>
+      </c>
+      <c r="E179" s="7" t="inlineStr"/>
+      <c r="F179" s="7" t="inlineStr">
+        <is>
           <t>Class 5 (MATH)</t>
         </is>
       </c>
-      <c r="E179" s="7" t="inlineStr">
+      <c r="G179" s="7" t="inlineStr"/>
+      <c r="H179" s="7" t="inlineStr">
         <is>
           <t>Class 3 (MATH)</t>
         </is>
       </c>
-      <c r="F179" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (MATH)</t>
-        </is>
-      </c>
-      <c r="G179" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (MATH)</t>
-        </is>
-      </c>
-      <c r="H179" s="7" t="inlineStr"/>
       <c r="I179" s="8" t="inlineStr">
         <is>
           <t>Class 4</t>
@@ -5664,20 +5668,20 @@
       <c r="D180" s="7" t="inlineStr"/>
       <c r="E180" s="7" t="inlineStr">
         <is>
+          <t>Class 5 (MATH)</t>
+        </is>
+      </c>
+      <c r="F180" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (MATH)</t>
+        </is>
+      </c>
+      <c r="G180" s="7" t="inlineStr"/>
+      <c r="H180" s="7" t="inlineStr">
+        <is>
           <t>Class 2 (MATH)</t>
         </is>
       </c>
-      <c r="F180" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (MATH)</t>
-        </is>
-      </c>
-      <c r="G180" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (MATH)</t>
-        </is>
-      </c>
-      <c r="H180" s="7" t="inlineStr"/>
       <c r="I180" s="8" t="inlineStr">
         <is>
           <t>Class 4</t>
@@ -5695,25 +5699,21 @@
           <t>Class 4 (MATH)</t>
         </is>
       </c>
-      <c r="C181" s="7" t="inlineStr">
+      <c r="C181" s="7" t="inlineStr"/>
+      <c r="D181" s="7" t="inlineStr">
         <is>
           <t>Class 3 (MATH)</t>
         </is>
       </c>
-      <c r="D181" s="7" t="inlineStr"/>
       <c r="E181" s="7" t="inlineStr">
         <is>
+          <t>Class 3 (MATH)</t>
+        </is>
+      </c>
+      <c r="F181" s="7" t="inlineStr"/>
+      <c r="G181" s="7" t="inlineStr">
+        <is>
           <t>Class 5 (MATH)</t>
-        </is>
-      </c>
-      <c r="F181" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (MATH)</t>
-        </is>
-      </c>
-      <c r="G181" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (MATH)</t>
         </is>
       </c>
       <c r="H181" s="7" t="inlineStr"/>
@@ -5794,18 +5794,10 @@
       <c r="B185" s="7" t="inlineStr"/>
       <c r="C185" s="7" t="inlineStr"/>
       <c r="D185" s="7" t="inlineStr"/>
-      <c r="E185" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (KAR)</t>
-        </is>
-      </c>
+      <c r="E185" s="7" t="inlineStr"/>
       <c r="F185" s="7" t="inlineStr"/>
       <c r="G185" s="7" t="inlineStr"/>
-      <c r="H185" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (KAR)</t>
-        </is>
-      </c>
+      <c r="H185" s="7" t="inlineStr"/>
       <c r="I185" s="7" t="inlineStr"/>
     </row>
     <row r="186">
@@ -5816,13 +5808,21 @@
       </c>
       <c r="B186" s="7" t="inlineStr"/>
       <c r="C186" s="7" t="inlineStr"/>
-      <c r="D186" s="7" t="inlineStr"/>
+      <c r="D186" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (KAR)</t>
+        </is>
+      </c>
       <c r="E186" s="7" t="inlineStr"/>
       <c r="F186" s="7" t="inlineStr"/>
-      <c r="G186" s="7" t="inlineStr"/>
+      <c r="G186" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (KAR)</t>
+        </is>
+      </c>
       <c r="H186" s="7" t="inlineStr">
         <is>
-          <t>Class 1 (KAR)</t>
+          <t>Class 7 (KAR)</t>
         </is>
       </c>
       <c r="I186" s="7" t="inlineStr"/>
@@ -5841,7 +5841,11 @@
           <t>Class 10 (KAR)</t>
         </is>
       </c>
-      <c r="F187" s="7" t="inlineStr"/>
+      <c r="F187" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (KAR)</t>
+        </is>
+      </c>
       <c r="G187" s="7" t="inlineStr"/>
       <c r="H187" s="7" t="inlineStr"/>
       <c r="I187" s="7" t="inlineStr"/>
@@ -5853,12 +5857,12 @@
         </is>
       </c>
       <c r="B188" s="7" t="inlineStr"/>
-      <c r="C188" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (KAR)</t>
-        </is>
-      </c>
-      <c r="D188" s="7" t="inlineStr"/>
+      <c r="C188" s="7" t="inlineStr"/>
+      <c r="D188" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (KAR)</t>
+        </is>
+      </c>
       <c r="E188" s="7" t="inlineStr">
         <is>
           <t>Class 8 (KAR)</t>
@@ -5877,21 +5881,9 @@
       </c>
       <c r="B189" s="7" t="inlineStr"/>
       <c r="C189" s="7" t="inlineStr"/>
-      <c r="D189" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (KAR)</t>
-        </is>
-      </c>
-      <c r="E189" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (KAR)</t>
-        </is>
-      </c>
-      <c r="F189" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (KAR)</t>
-        </is>
-      </c>
+      <c r="D189" s="7" t="inlineStr"/>
+      <c r="E189" s="7" t="inlineStr"/>
+      <c r="F189" s="7" t="inlineStr"/>
       <c r="G189" s="7" t="inlineStr"/>
       <c r="H189" s="7" t="inlineStr"/>
       <c r="I189" s="7" t="inlineStr"/>
@@ -5903,12 +5895,12 @@
         </is>
       </c>
       <c r="B190" s="7" t="inlineStr"/>
-      <c r="C190" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (KAR)</t>
-        </is>
-      </c>
-      <c r="D190" s="7" t="inlineStr"/>
+      <c r="C190" s="7" t="inlineStr"/>
+      <c r="D190" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (KAR)</t>
+        </is>
+      </c>
       <c r="E190" s="7" t="inlineStr"/>
       <c r="F190" s="7" t="inlineStr"/>
       <c r="G190" s="7" t="inlineStr"/>
@@ -5988,12 +5980,12 @@
       <c r="D194" s="7" t="inlineStr"/>
       <c r="E194" s="7" t="inlineStr"/>
       <c r="F194" s="7" t="inlineStr"/>
-      <c r="G194" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (P.E.T)</t>
-        </is>
-      </c>
-      <c r="H194" s="7" t="inlineStr"/>
+      <c r="G194" s="7" t="inlineStr"/>
+      <c r="H194" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (P.E.T)</t>
+        </is>
+      </c>
       <c r="I194" s="7" t="inlineStr"/>
     </row>
     <row r="195">
@@ -6007,11 +5999,7 @@
       <c r="D195" s="7" t="inlineStr"/>
       <c r="E195" s="7" t="inlineStr"/>
       <c r="F195" s="7" t="inlineStr"/>
-      <c r="G195" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (P.E.T)</t>
-        </is>
-      </c>
+      <c r="G195" s="7" t="inlineStr"/>
       <c r="H195" s="7" t="inlineStr"/>
       <c r="I195" s="7" t="inlineStr"/>
     </row>
@@ -6026,16 +6014,8 @@
       <c r="D196" s="7" t="inlineStr"/>
       <c r="E196" s="7" t="inlineStr"/>
       <c r="F196" s="7" t="inlineStr"/>
-      <c r="G196" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (P.E.T)</t>
-        </is>
-      </c>
-      <c r="H196" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (P.E.T)</t>
-        </is>
-      </c>
+      <c r="G196" s="7" t="inlineStr"/>
+      <c r="H196" s="7" t="inlineStr"/>
       <c r="I196" s="7" t="inlineStr"/>
     </row>
     <row r="197">
@@ -6049,10 +6029,14 @@
       <c r="D197" s="7" t="inlineStr"/>
       <c r="E197" s="7" t="inlineStr"/>
       <c r="F197" s="7" t="inlineStr"/>
-      <c r="G197" s="7" t="inlineStr"/>
+      <c r="G197" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (P.E.T)</t>
+        </is>
+      </c>
       <c r="H197" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (P.E.T)</t>
+          <t>Class 10 (P.E.T)</t>
         </is>
       </c>
       <c r="I197" s="7" t="inlineStr"/>
@@ -6068,7 +6052,11 @@
       <c r="D198" s="7" t="inlineStr"/>
       <c r="E198" s="7" t="inlineStr"/>
       <c r="F198" s="7" t="inlineStr"/>
-      <c r="G198" s="7" t="inlineStr"/>
+      <c r="G198" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (P.E.T)</t>
+        </is>
+      </c>
       <c r="H198" s="7" t="inlineStr"/>
       <c r="I198" s="7" t="inlineStr"/>
     </row>
@@ -6084,7 +6072,11 @@
       <c r="E199" s="7" t="inlineStr"/>
       <c r="F199" s="7" t="inlineStr"/>
       <c r="G199" s="7" t="inlineStr"/>
-      <c r="H199" s="7" t="inlineStr"/>
+      <c r="H199" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (P.E.T)</t>
+        </is>
+      </c>
       <c r="I199" s="7" t="inlineStr"/>
     </row>
   </sheetData>
@@ -6244,7 +6236,7 @@
       <c r="F2" s="7" t="inlineStr">
         <is>
           <t>SAI LAKSHMI
-(HIN)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="G2" s="7" t="inlineStr">
@@ -6291,8 +6283,8 @@
       </c>
       <c r="N2" s="7" t="inlineStr">
         <is>
-          <t>GOWTHAM
-(MATH)</t>
+          <t>BHEEMA
+(CHEM)</t>
         </is>
       </c>
     </row>
@@ -6304,13 +6296,13 @@
       <c r="C3" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(ORAL)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>SAI LAKSHMI
-(ENG)</t>
+          <t>SWATHI
+(HIN)</t>
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr">
@@ -6321,56 +6313,56 @@
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
-          <t>TULASI
-(MATH)</t>
+          <t>SAI LAKSHMI
+(HIN)</t>
         </is>
       </c>
       <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>RIYA
+(HIN)</t>
+        </is>
+      </c>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>FATHIMA
+(HIN)</t>
+        </is>
+      </c>
+      <c r="I3" s="7" t="inlineStr">
         <is>
           <t>LALITHA
 (EVS)</t>
         </is>
       </c>
-      <c r="H3" s="7" t="inlineStr">
-        <is>
-          <t>PALLAVI
-(SOC)</t>
-        </is>
-      </c>
-      <c r="I3" s="7" t="inlineStr">
-        <is>
-          <t>SWATHI
-(TEL)</t>
-        </is>
-      </c>
       <c r="J3" s="7" t="inlineStr">
         <is>
-          <t>FATHIMA
-(HIN)</t>
+          <t>RAVI
+(ENG)</t>
         </is>
       </c>
       <c r="K3" s="7" t="inlineStr">
+        <is>
+          <t>SANGEETHA
+(MATH)</t>
+        </is>
+      </c>
+      <c r="L3" s="7" t="inlineStr">
         <is>
           <t>D.V.RAO
 (TEL)</t>
         </is>
       </c>
-      <c r="L3" s="7" t="inlineStr">
+      <c r="M3" s="7" t="inlineStr">
         <is>
           <t>BHEEMA
 (CHEM)</t>
         </is>
       </c>
-      <c r="M3" s="7" t="inlineStr">
+      <c r="N3" s="7" t="inlineStr">
         <is>
           <t>GOWTHAM
 (MATH)</t>
-        </is>
-      </c>
-      <c r="N3" s="7" t="inlineStr">
-        <is>
-          <t>RIYA
-(HIN)</t>
         </is>
       </c>
     </row>
@@ -6381,74 +6373,74 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
+          <t>SITHA
+(MATH)</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>BHAVANI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>MAHESWARI
+(COMP)</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
           <t>NAGAMANI
 (TEL)</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>SWATHI
-(HIN)</t>
-        </is>
-      </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>BHAVANI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>SAI LAKSHMI
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>LALITHA
 (EVS)</t>
         </is>
       </c>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>MAHA
 (ENG)</t>
         </is>
       </c>
-      <c r="H4" s="7" t="inlineStr">
-        <is>
-          <t>LALITHA
-(EVS)</t>
-        </is>
-      </c>
       <c r="I4" s="7" t="inlineStr">
+        <is>
+          <t>TULASI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="J4" s="7" t="inlineStr">
         <is>
           <t>PALLAVI
 (SOC)</t>
         </is>
       </c>
-      <c r="J4" s="7" t="inlineStr">
+      <c r="K4" s="7" t="inlineStr">
+        <is>
+          <t>RAVI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="L4" s="7" t="inlineStr">
         <is>
           <t>SANGEETHA
 (MATH)</t>
         </is>
       </c>
-      <c r="K4" s="7" t="inlineStr">
-        <is>
-          <t>FATHIMA
-(HIN)</t>
-        </is>
-      </c>
-      <c r="L4" s="7" t="inlineStr">
+      <c r="M4" s="7" t="inlineStr">
         <is>
           <t>BHEEMA
 (PHY)</t>
         </is>
       </c>
-      <c r="M4" s="7" t="inlineStr">
-        <is>
-          <t>GOWTHAM
-(MATH)</t>
-        </is>
-      </c>
       <c r="N4" s="7" t="inlineStr">
         <is>
-          <t>RAVI
-(GRAM)</t>
+          <t>D.V.RAO
+(TEL)</t>
         </is>
       </c>
     </row>
@@ -6460,73 +6452,73 @@
       <c r="C5" s="7" t="inlineStr">
         <is>
           <t>SITHA
+(ORAL)</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>NAGAMANI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>BHAVANI
 (MATH)</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>BHAVANI
-(EVS)</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>SAI LAKSHMI
 (EVS)</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="G5" s="7" t="inlineStr">
         <is>
           <t>TULASI
 (MATH)</t>
         </is>
       </c>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>SWATHI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>PALLAVI
+(SOC)</t>
+        </is>
+      </c>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>LALITHA
+(PHY)</t>
+        </is>
+      </c>
+      <c r="K5" s="7" t="inlineStr">
+        <is>
+          <t>FATHIMA
+(HIN)</t>
+        </is>
+      </c>
+      <c r="L5" s="7" t="inlineStr">
+        <is>
+          <t>SUNITHA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="M5" s="7" t="inlineStr">
+        <is>
+          <t>RAVI
+(GRAM)</t>
+        </is>
+      </c>
+      <c r="N5" s="7" t="inlineStr">
         <is>
           <t>RIYA
 (HIN)</t>
-        </is>
-      </c>
-      <c r="H5" s="7" t="inlineStr">
-        <is>
-          <t>SANGEETHA
-(G.K)</t>
-        </is>
-      </c>
-      <c r="I5" s="7" t="inlineStr">
-        <is>
-          <t>MAHESWARI
-(COMP)</t>
-        </is>
-      </c>
-      <c r="J5" s="7" t="inlineStr">
-        <is>
-          <t>RAVI
-(ENG)</t>
-        </is>
-      </c>
-      <c r="K5" s="7" t="inlineStr">
-        <is>
-          <t>LALITHA
-(BIO)</t>
-        </is>
-      </c>
-      <c r="L5" s="7" t="inlineStr">
-        <is>
-          <t>D.V.RAO
-(TEL)</t>
-        </is>
-      </c>
-      <c r="M5" s="7" t="inlineStr">
-        <is>
-          <t>MARTIAL ARTS
-(KAR)</t>
-        </is>
-      </c>
-      <c r="N5" s="7" t="inlineStr">
-        <is>
-          <t>SUNITHA
-(SOC)</t>
         </is>
       </c>
     </row>
@@ -6543,14 +6535,14 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>SAI LAKSHMI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
           <t>BHAVANI
-(EVS)</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>SAI LAKSHMI
-(EVS)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
@@ -6567,26 +6559,26 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
+          <t>PALLAVI
+(SOC)</t>
+        </is>
+      </c>
+      <c r="I6" s="7" t="inlineStr">
+        <is>
+          <t>FATHIMA
+(HIN)</t>
+        </is>
+      </c>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
           <t>SWATHI
 (TEL)</t>
         </is>
       </c>
-      <c r="I6" s="7" t="inlineStr">
-        <is>
-          <t>FATHIMA
-(HIN)</t>
-        </is>
-      </c>
-      <c r="J6" s="7" t="inlineStr">
+      <c r="K6" s="7" t="inlineStr">
         <is>
           <t>LALITHA
 (BIO)</t>
-        </is>
-      </c>
-      <c r="K6" s="7" t="inlineStr">
-        <is>
-          <t>SANGEETHA
-(COMP)</t>
         </is>
       </c>
       <c r="L6" s="7" t="inlineStr">
@@ -6615,67 +6607,68 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
+          <t>SITHA
+(ENG)</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
+          <t>SAI LAKSHMI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
           <t>NAGAMANI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>P.E
-(P.E.T)</t>
+(G.K)</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
+          <t>TULASI
+(MATH)</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
-        <is>
-          <t>P.E
-(P.E.T)</t>
-        </is>
-      </c>
-      <c r="H7" s="7" t="inlineStr">
         <is>
           <t>MAHA
 (ENG)</t>
         </is>
       </c>
-      <c r="I7" s="7" t="inlineStr">
+      <c r="H7" s="7" t="inlineStr">
         <is>
           <t>LALITHA
 (EVS)</t>
         </is>
       </c>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>SWATHI
+(TEL)</t>
+        </is>
+      </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>PALLAVI
-(SOC)</t>
+          <t>FATHIMA
+(HIN)</t>
         </is>
       </c>
       <c r="K7" s="7" t="inlineStr">
+        <is>
+          <t>RAVI
+(GRAM)</t>
+        </is>
+      </c>
+      <c r="L7" s="7" t="inlineStr">
         <is>
           <t>SANGEETHA
 (MATH)</t>
         </is>
       </c>
-      <c r="L7" s="7" t="inlineStr">
+      <c r="M7" s="7" t="inlineStr">
         <is>
           <t>CHALAPATHI
 (BIO)</t>
-        </is>
-      </c>
-      <c r="M7" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
         </is>
       </c>
       <c r="N7" s="7" t="inlineStr">
@@ -6693,7 +6686,7 @@
       <c r="C8" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(EVS)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
@@ -6704,14 +6697,14 @@
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>BHAVANI
-(MATH)</t>
+          <t>P.E
+(P.E.T)</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>NAGAMANI
-(TEL)</t>
+          <t>P.E
+(P.E.T)</t>
         </is>
       </c>
       <c r="G8" s="7" t="inlineStr">
@@ -6722,8 +6715,8 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>MARTIAL ARTS
-(KAR)</t>
+          <t>P.E
+(P.E.T)</t>
         </is>
       </c>
       <c r="I8" s="7" t="inlineStr">
@@ -6734,32 +6727,32 @@
       </c>
       <c r="J8" s="7" t="inlineStr">
         <is>
-          <t>SWATHI
+          <t>LALITHA
+(BIO)</t>
+        </is>
+      </c>
+      <c r="K8" s="7" t="inlineStr">
+        <is>
+          <t>D.V.RAO
 (TEL)</t>
         </is>
       </c>
-      <c r="K8" s="7" t="inlineStr">
-        <is>
-          <t>RAVI
+      <c r="L8" s="7" t="inlineStr">
+        <is>
+          <t>CHALAPATHI
+(BIO)</t>
+        </is>
+      </c>
+      <c r="M8" s="7" t="inlineStr">
+        <is>
+          <t>SONU
 (ENG)</t>
         </is>
       </c>
-      <c r="L8" s="7" t="inlineStr">
+      <c r="N8" s="7" t="inlineStr">
         <is>
           <t>SUNITHA
 (SOC)</t>
-        </is>
-      </c>
-      <c r="M8" s="7" t="inlineStr">
-        <is>
-          <t>SONU
-(ENG)</t>
-        </is>
-      </c>
-      <c r="N8" s="7" t="inlineStr">
-        <is>
-          <t>D.V.RAO
-(TEL)</t>
         </is>
       </c>
     </row>
@@ -6853,13 +6846,13 @@
       <c r="C10" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(ORAL)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
           <t>BHAVANI
-(EVS)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
@@ -6895,7 +6888,7 @@
       <c r="J10" s="7" t="inlineStr">
         <is>
           <t>SANGEETHA
-(G.K)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="K10" s="7" t="inlineStr">
@@ -6943,51 +6936,51 @@
       <c r="E11" s="7" t="inlineStr">
         <is>
           <t>SAI LAKSHMI
-(EVS)</t>
+(HIN)</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>BHAVANI
-(G.K)</t>
-        </is>
-      </c>
-      <c r="G11" s="7" t="inlineStr">
-        <is>
-          <t>RIYA
-(HIN)</t>
-        </is>
-      </c>
-      <c r="H11" s="7" t="inlineStr">
-        <is>
-          <t>FATHIMA
-(HIN)</t>
-        </is>
-      </c>
-      <c r="I11" s="7" t="inlineStr">
         <is>
           <t>TULASI
 (MATH)</t>
         </is>
       </c>
-      <c r="J11" s="7" t="inlineStr">
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>MAHA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>SWATHI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="I11" s="7" t="inlineStr">
         <is>
           <t>PALLAVI
 (SOC)</t>
         </is>
       </c>
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>LALITHA
+(CHEM)</t>
+        </is>
+      </c>
       <c r="K11" s="7" t="inlineStr">
-        <is>
-          <t>LALITHA
-(PHY)</t>
-        </is>
-      </c>
-      <c r="L11" s="7" t="inlineStr">
         <is>
           <t>D.V.RAO
 (TEL)</t>
         </is>
       </c>
+      <c r="L11" s="7" t="inlineStr">
+        <is>
+          <t>BHEEMA
+(PHY)</t>
+        </is>
+      </c>
       <c r="M11" s="7" t="inlineStr">
         <is>
           <t>GOWTHAM
@@ -6996,8 +6989,8 @@
       </c>
       <c r="N11" s="7" t="inlineStr">
         <is>
-          <t>BHEEMA
-(PHY)</t>
+          <t>RAVI
+(GRAM)</t>
         </is>
       </c>
     </row>
@@ -7014,68 +7007,68 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>SWATHI
-(HIN)</t>
+          <t>BHAVANI
+(MATH)</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>MAHA
-(ENG)</t>
+          <t>SAI LAKSHMI
+(EVS)</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>NAGAMANI
-(TEL)</t>
+          <t>MAHESWARI
+(COMP)</t>
         </is>
       </c>
       <c r="G12" s="7" t="inlineStr">
-        <is>
-          <t>SAI LAKSHMI
-(G.K)</t>
-        </is>
-      </c>
-      <c r="H12" s="7" t="inlineStr">
-        <is>
-          <t>LALITHA
-(EVS)</t>
-        </is>
-      </c>
-      <c r="I12" s="7" t="inlineStr">
         <is>
           <t>TULASI
 (MATH)</t>
         </is>
       </c>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>PALLAVI
+(SOC)</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>SWATHI
+(TEL)</t>
+        </is>
+      </c>
       <c r="J12" s="7" t="inlineStr">
         <is>
-          <t>RAVI
-(ENG)</t>
+          <t>MARTIAL ARTS
+(KAR)</t>
         </is>
       </c>
       <c r="K12" s="7" t="inlineStr">
+        <is>
+          <t>LALITHA
+(PHY)</t>
+        </is>
+      </c>
+      <c r="L12" s="7" t="inlineStr">
+        <is>
+          <t>SANGEETHA
+(MATH)</t>
+        </is>
+      </c>
+      <c r="M12" s="7" t="inlineStr">
+        <is>
+          <t>GOWTHAM
+(MATH)</t>
+        </is>
+      </c>
+      <c r="N12" s="7" t="inlineStr">
         <is>
           <t>D.V.RAO
 (TEL)</t>
-        </is>
-      </c>
-      <c r="L12" s="7" t="inlineStr">
-        <is>
-          <t>SANGEETHA
-(MATH)</t>
-        </is>
-      </c>
-      <c r="M12" s="7" t="inlineStr">
-        <is>
-          <t>GOWTHAM
-(MATH)</t>
-        </is>
-      </c>
-      <c r="N12" s="7" t="inlineStr">
-        <is>
-          <t>BHEEMA
-(CHEM)</t>
         </is>
       </c>
     </row>
@@ -7093,33 +7086,33 @@
       <c r="D13" s="7" t="inlineStr">
         <is>
           <t>BHAVANI
-(EVS)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>MAHESWARI
-(COMP)</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t>SAI LAKSHMI
-(EVS)</t>
-        </is>
-      </c>
-      <c r="G13" s="7" t="inlineStr">
-        <is>
-          <t>PALLAVI
-(SOC)</t>
-        </is>
-      </c>
-      <c r="H13" s="7" t="inlineStr">
         <is>
           <t>MAHA
 (ENG)</t>
         </is>
       </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>NAGAMANI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>RIYA
+(HIN)</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>FATHIMA
+(HIN)</t>
+        </is>
+      </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
           <t>LALITHA
@@ -7128,32 +7121,30 @@
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
-          <t>SWATHI
-(TEL)</t>
+          <t>RAVI
+(ENG)</t>
         </is>
       </c>
       <c r="K13" s="7" t="inlineStr">
         <is>
-          <t>FATHIMA
-(HIN)</t>
+          <t>SANGEETHA
+(COMP)</t>
         </is>
       </c>
       <c r="L13" s="7" t="inlineStr">
-        <is>
-          <t>SANGEETHA
-(MATH)</t>
-        </is>
-      </c>
-      <c r="M13" s="7" t="inlineStr">
         <is>
           <t>SUNITHA
 (SOC)</t>
         </is>
       </c>
-      <c r="N13" s="7" t="inlineStr">
-        <is>
-          <t>RIYA
-(HIN)</t>
+      <c r="M13" s="12" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+      <c r="N13" s="12" t="inlineStr">
+        <is>
+          <t>Recreation</t>
         </is>
       </c>
     </row>
@@ -7165,45 +7156,45 @@
       <c r="C14" s="7" t="inlineStr">
         <is>
           <t>SITHA
+(MATH)</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>SAI LAKSHMI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>NAGAMANI
+(G.K)</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>BHAVANI
+(G.K)</t>
+        </is>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>LALITHA
 (EVS)</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>BHAVANI
-(EVS)</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>SAI LAKSHMI
-(HIN)</t>
-        </is>
-      </c>
-      <c r="F14" s="7" t="inlineStr">
+      <c r="H14" s="7" t="inlineStr">
         <is>
           <t>MAHA
 (ENG)</t>
         </is>
       </c>
-      <c r="G14" s="7" t="inlineStr">
+      <c r="I14" s="7" t="inlineStr">
         <is>
           <t>TULASI
 (MATH)</t>
         </is>
       </c>
-      <c r="H14" s="7" t="inlineStr">
-        <is>
-          <t>PALLAVI
-(SOC)</t>
-        </is>
-      </c>
-      <c r="I14" s="7" t="inlineStr">
-        <is>
-          <t>SWATHI
-(TEL)</t>
-        </is>
-      </c>
       <c r="J14" s="7" t="inlineStr">
         <is>
           <t>FATHIMA
@@ -7212,26 +7203,26 @@
       </c>
       <c r="K14" s="7" t="inlineStr">
         <is>
-          <t>LALITHA
+          <t>RAVI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="L14" s="7" t="inlineStr">
+        <is>
+          <t>CHALAPATHI
 (BIO)</t>
         </is>
       </c>
-      <c r="L14" s="7" t="inlineStr">
+      <c r="M14" s="7" t="inlineStr">
+        <is>
+          <t>SUNITHA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="N14" s="7" t="inlineStr">
         <is>
           <t>SONU
 (ENG)</t>
-        </is>
-      </c>
-      <c r="M14" s="7" t="inlineStr">
-        <is>
-          <t>CHALAPATHI
-(BIO)</t>
-        </is>
-      </c>
-      <c r="N14" s="7" t="inlineStr">
-        <is>
-          <t>SUNITHA
-(SOC)</t>
         </is>
       </c>
     </row>
@@ -7242,50 +7233,50 @@
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
+          <t>NAGAMANI
+(TEL)</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
+          <t>SAI LAKSHMI
+(ENG)</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
+          <t>MAHESWARI
+(COMP)</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
+          <t>MAHA
+(ENG)</t>
         </is>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>LALITHA
-(EVS)</t>
+          <t>PALLAVI
+(SOC)</t>
         </is>
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
+          <t>MARTIAL ARTS
+(KAR)</t>
         </is>
       </c>
       <c r="I15" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
+          <t>TULASI
+(MATH)</t>
         </is>
       </c>
       <c r="J15" s="7" t="inlineStr">
         <is>
-          <t>RAVI
-(GRAM)</t>
+          <t>SWATHI
+(TEL)</t>
         </is>
       </c>
       <c r="K15" s="7" t="inlineStr">
@@ -7296,8 +7287,8 @@
       </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
-          <t>SUNITHA
-(SOC)</t>
+          <t>SONU
+(ENG)</t>
         </is>
       </c>
       <c r="M15" s="7" t="inlineStr">
@@ -7306,10 +7297,9 @@
 (HIN)</t>
         </is>
       </c>
-      <c r="N15" s="7" t="inlineStr">
-        <is>
-          <t>SONU
-(ENG)</t>
+      <c r="N15" s="12" t="inlineStr">
+        <is>
+          <t>Recreation</t>
         </is>
       </c>
     </row>
@@ -7321,13 +7311,13 @@
       <c r="C16" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(EVS)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
           <t>BHAVANI
-(EVS)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
@@ -7339,43 +7329,43 @@
       <c r="F16" s="7" t="inlineStr">
         <is>
           <t>SAI LAKSHMI
+(HIN)</t>
+        </is>
+      </c>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>MAHA
+(GRAM)</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>LALITHA
 (EVS)</t>
         </is>
       </c>
-      <c r="G16" s="7" t="inlineStr">
-        <is>
-          <t>MAHA
-(ENG)</t>
-        </is>
-      </c>
-      <c r="H16" s="7" t="inlineStr">
-        <is>
-          <t>SWATHI
-(TEL)</t>
-        </is>
-      </c>
       <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>FATHIMA
+(HIN)</t>
+        </is>
+      </c>
+      <c r="J16" s="7" t="inlineStr">
         <is>
           <t>PALLAVI
 (SOC)</t>
         </is>
       </c>
-      <c r="J16" s="7" t="inlineStr">
-        <is>
-          <t>LALITHA
-(BIO)</t>
-        </is>
-      </c>
       <c r="K16" s="7" t="inlineStr">
         <is>
-          <t>RAVI
-(ENG)</t>
+          <t>MARTIAL ARTS
+(KAR)</t>
         </is>
       </c>
       <c r="L16" s="7" t="inlineStr">
         <is>
-          <t>CHALAPATHI
-(BIO)</t>
+          <t>D.V.RAO
+(TEL)</t>
         </is>
       </c>
       <c r="M16" s="7" t="inlineStr">
@@ -7386,8 +7376,8 @@
       </c>
       <c r="N16" s="7" t="inlineStr">
         <is>
-          <t>D.V.RAO
-(TEL)</t>
+          <t>SUNITHA
+(SOC)</t>
         </is>
       </c>
     </row>
@@ -7481,7 +7471,7 @@
       <c r="C18" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(ORAL)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
@@ -7493,7 +7483,7 @@
       <c r="E18" s="7" t="inlineStr">
         <is>
           <t>NAGAMANI
-(G.K)</t>
+(TEL)</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
@@ -7546,8 +7536,8 @@
       </c>
       <c r="N18" s="7" t="inlineStr">
         <is>
-          <t>SUNITHA
-(SOC)</t>
+          <t>GOWTHAM
+(MATH)</t>
         </is>
       </c>
     </row>
@@ -7559,21 +7549,21 @@
       <c r="C19" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(EVS)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>SAI LAKSHMI
-(ENG)</t>
-        </is>
-      </c>
-      <c r="E19" s="7" t="inlineStr">
         <is>
           <t>BHAVANI
 (MATH)</t>
         </is>
       </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>SAI LAKSHMI
+(EVS)</t>
+        </is>
+      </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
           <t>NAGAMANI
@@ -7588,44 +7578,44 @@
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
+          <t>MAHESWARI
+(COMP)</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
           <t>PALLAVI
 (SOC)</t>
         </is>
       </c>
-      <c r="I19" s="7" t="inlineStr">
+      <c r="J19" s="7" t="inlineStr">
+        <is>
+          <t>LALITHA
+(BIO)</t>
+        </is>
+      </c>
+      <c r="K19" s="7" t="inlineStr">
         <is>
           <t>FATHIMA
 (HIN)</t>
         </is>
       </c>
-      <c r="J19" s="7" t="inlineStr">
-        <is>
-          <t>SWATHI
+      <c r="L19" s="7" t="inlineStr">
+        <is>
+          <t>D.V.RAO
 (TEL)</t>
         </is>
       </c>
-      <c r="K19" s="7" t="inlineStr">
-        <is>
-          <t>LALITHA
-(BIO)</t>
-        </is>
-      </c>
-      <c r="L19" s="7" t="inlineStr">
-        <is>
-          <t>SUNITHA
-(SOC)</t>
-        </is>
-      </c>
       <c r="M19" s="7" t="inlineStr">
-        <is>
-          <t>BHEEMA
-(PHY)</t>
-        </is>
-      </c>
-      <c r="N19" s="7" t="inlineStr">
         <is>
           <t>GOWTHAM
 (MATH)</t>
+        </is>
+      </c>
+      <c r="N19" s="7" t="inlineStr">
+        <is>
+          <t>BHEEMA
+(CHEM)</t>
         </is>
       </c>
     </row>
@@ -7637,73 +7627,73 @@
       <c r="C20" s="7" t="inlineStr">
         <is>
           <t>SITHA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>BHAVANI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>SAI LAKSHMI
+(HIN)</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>TULASI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>LALITHA
 (EVS)</t>
         </is>
       </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>SAI LAKSHMI
-(ENG)</t>
-        </is>
-      </c>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t>NAGAMANI
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>SWATHI
 (TEL)</t>
         </is>
       </c>
-      <c r="F20" s="7" t="inlineStr">
+      <c r="I20" s="7" t="inlineStr">
         <is>
           <t>MAHESWARI
 (COMP)</t>
         </is>
       </c>
-      <c r="G20" s="7" t="inlineStr">
-        <is>
-          <t>PALLAVI
-(SOC)</t>
-        </is>
-      </c>
-      <c r="H20" s="7" t="inlineStr">
-        <is>
-          <t>LALITHA
-(EVS)</t>
-        </is>
-      </c>
-      <c r="I20" s="7" t="inlineStr">
-        <is>
-          <t>TULASI
-(MATH)</t>
-        </is>
-      </c>
       <c r="J20" s="7" t="inlineStr">
+        <is>
+          <t>SANGEETHA
+(G.K)</t>
+        </is>
+      </c>
+      <c r="K20" s="7" t="inlineStr">
         <is>
           <t>RAVI
 (ENG)</t>
         </is>
       </c>
-      <c r="K20" s="7" t="inlineStr">
+      <c r="L20" s="7" t="inlineStr">
+        <is>
+          <t>BHEEMA
+(CHEM)</t>
+        </is>
+      </c>
+      <c r="M20" s="7" t="inlineStr">
+        <is>
+          <t>GOWTHAM
+(MATH)</t>
+        </is>
+      </c>
+      <c r="N20" s="7" t="inlineStr">
         <is>
           <t>D.V.RAO
 (TEL)</t>
-        </is>
-      </c>
-      <c r="L20" s="7" t="inlineStr">
-        <is>
-          <t>SANGEETHA
-(MATH)</t>
-        </is>
-      </c>
-      <c r="M20" s="7" t="inlineStr">
-        <is>
-          <t>GOWTHAM
-(MATH)</t>
-        </is>
-      </c>
-      <c r="N20" s="7" t="inlineStr">
-        <is>
-          <t>BHEEMA
-(CHEM)</t>
         </is>
       </c>
     </row>
@@ -7715,25 +7705,25 @@
       <c r="C21" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(MATH)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>BHAVANI
-(MATH)</t>
+          <t>SAI LAKSHMI
+(ENG)</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
           <t>MAHA
-(ENG)</t>
+(GRAM)</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>SAI LAKSHMI
-(HIN)</t>
+          <t>MAHESWARI
+(COMP)</t>
         </is>
       </c>
       <c r="G21" s="7" t="inlineStr">
@@ -7744,38 +7734,37 @@
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>TULASI
-(MATH)</t>
+          <t>PALLAVI
+(SOC)</t>
         </is>
       </c>
       <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>FATHIMA
+(HIN)</t>
+        </is>
+      </c>
+      <c r="J21" s="7" t="inlineStr">
         <is>
           <t>SWATHI
 (TEL)</t>
         </is>
       </c>
-      <c r="J21" s="7" t="inlineStr">
-        <is>
-          <t>LALITHA
-(BIO)</t>
-        </is>
-      </c>
       <c r="K21" s="7" t="inlineStr">
-        <is>
-          <t>RAVI
-(ENG)</t>
-        </is>
-      </c>
-      <c r="L21" s="7" t="inlineStr">
         <is>
           <t>SANGEETHA
 (MATH)</t>
         </is>
       </c>
-      <c r="M21" s="7" t="inlineStr">
+      <c r="L21" s="7" t="inlineStr">
         <is>
           <t>SUNITHA
 (SOC)</t>
+        </is>
+      </c>
+      <c r="M21" s="12" t="inlineStr">
+        <is>
+          <t>Recreation</t>
         </is>
       </c>
       <c r="N21" s="7" t="inlineStr">
@@ -7793,7 +7782,7 @@
       <c r="C22" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(MATH)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
@@ -7805,49 +7794,49 @@
       <c r="E22" s="7" t="inlineStr">
         <is>
           <t>MAHA
-(GRAM)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>SAI LAKSHMI
-(EVS)</t>
+          <t>TULASI
+(MATH)</t>
         </is>
       </c>
       <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>MARTIAL ARTS
+(KAR)</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="inlineStr">
         <is>
           <t>LALITHA
 (EVS)</t>
         </is>
       </c>
-      <c r="H22" s="7" t="inlineStr">
+      <c r="I22" s="7" t="inlineStr">
         <is>
           <t>SWATHI
 (TEL)</t>
         </is>
       </c>
-      <c r="I22" s="7" t="inlineStr">
+      <c r="J22" s="7" t="inlineStr">
         <is>
           <t>PALLAVI
 (SOC)</t>
         </is>
       </c>
-      <c r="J22" s="7" t="inlineStr">
-        <is>
-          <t>MAHESWARI
-(COMP)</t>
-        </is>
-      </c>
       <c r="K22" s="7" t="inlineStr">
-        <is>
-          <t>FATHIMA
-(HIN)</t>
-        </is>
-      </c>
-      <c r="L22" s="7" t="inlineStr">
         <is>
           <t>D.V.RAO
 (TEL)</t>
+        </is>
+      </c>
+      <c r="L22" s="7" t="inlineStr">
+        <is>
+          <t>SANGEETHA
+(COMP)</t>
         </is>
       </c>
       <c r="M22" s="7" t="inlineStr">
@@ -7871,7 +7860,7 @@
       <c r="C23" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(ENG)</t>
+(ORAL)</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
@@ -7882,28 +7871,28 @@
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
+          <t>BHAVANI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
           <t>SAI LAKSHMI
 (HIN)</t>
         </is>
       </c>
-      <c r="F23" s="7" t="inlineStr">
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>PALLAVI
+(SOC)</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
         <is>
           <t>MAHA
 (ENG)</t>
         </is>
       </c>
-      <c r="G23" s="7" t="inlineStr">
-        <is>
-          <t>TULASI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="H23" s="7" t="inlineStr">
-        <is>
-          <t>FATHIMA
-(HIN)</t>
-        </is>
-      </c>
       <c r="I23" s="7" t="inlineStr">
         <is>
           <t>LALITHA
@@ -7912,32 +7901,32 @@
       </c>
       <c r="J23" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
+          <t>MAHESWARI
+(COMP)</t>
         </is>
       </c>
       <c r="K23" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
+          <t>FATHIMA
+(G.K)</t>
         </is>
       </c>
       <c r="L23" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
+          <t>SONU
+(ENG)</t>
         </is>
       </c>
       <c r="M23" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
+          <t>RIYA
+(HIN)</t>
         </is>
       </c>
       <c r="N23" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
+          <t>SUNITHA
+(SOC)</t>
         </is>
       </c>
     </row>
@@ -7954,34 +7943,34 @@
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
+          <t>BHAVANI
+(EVS)</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
+          <t>SAI LAKSHMI
+(EVS)</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
-        <is>
-          <t>P.E
-(P.E.T)</t>
-        </is>
-      </c>
-      <c r="G24" s="7" t="inlineStr">
-        <is>
-          <t>P.E
-(P.E.T)</t>
-        </is>
-      </c>
-      <c r="H24" s="7" t="inlineStr">
         <is>
           <t>MAHA
 (ENG)</t>
         </is>
       </c>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>MAHESWARI
+(COMP)</t>
+        </is>
+      </c>
+      <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>FATHIMA
+(HIN)</t>
+        </is>
+      </c>
       <c r="I24" s="7" t="inlineStr">
         <is>
           <t>TULASI
@@ -7990,32 +7979,32 @@
       </c>
       <c r="J24" s="7" t="inlineStr">
         <is>
-          <t>PALLAVI
-(SOC)</t>
+          <t>RAVI
+(ENG)</t>
         </is>
       </c>
       <c r="K24" s="7" t="inlineStr">
+        <is>
+          <t>LALITHA
+(BIO)</t>
+        </is>
+      </c>
+      <c r="L24" s="7" t="inlineStr">
         <is>
           <t>SANGEETHA
 (MATH)</t>
         </is>
       </c>
-      <c r="L24" s="7" t="inlineStr">
+      <c r="M24" s="7" t="inlineStr">
+        <is>
+          <t>SUNITHA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="N24" s="7" t="inlineStr">
         <is>
           <t>SONU
 (ENG)</t>
-        </is>
-      </c>
-      <c r="M24" s="7" t="inlineStr">
-        <is>
-          <t>RIYA
-(HIN)</t>
-        </is>
-      </c>
-      <c r="N24" s="7" t="inlineStr">
-        <is>
-          <t>D.V.RAO
-(TEL)</t>
         </is>
       </c>
     </row>
@@ -8091,10 +8080,9 @@
 (CLASS)</t>
         </is>
       </c>
-      <c r="N25" s="8" t="inlineStr">
-        <is>
-          <t>SONU
-(ENG)</t>
+      <c r="N25" s="12" t="inlineStr">
+        <is>
+          <t>Recreation</t>
         </is>
       </c>
     </row>
@@ -8110,13 +8098,13 @@
       <c r="C26" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(ENG)</t>
+(ORAL)</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
           <t>BHAVANI
-(MATH)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
@@ -8175,8 +8163,8 @@
       </c>
       <c r="N26" s="7" t="inlineStr">
         <is>
-          <t>SUNITHA
-(SOC)</t>
+          <t>RIYA
+(HIN)</t>
         </is>
       </c>
     </row>
@@ -8193,20 +8181,20 @@
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>BHAVANI
+          <t>SAI LAKSHMI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>MAHA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>TULASI
 (MATH)</t>
-        </is>
-      </c>
-      <c r="E27" s="7" t="inlineStr">
-        <is>
-          <t>SAI LAKSHMI
-(EVS)</t>
-        </is>
-      </c>
-      <c r="F27" s="7" t="inlineStr">
-        <is>
-          <t>NAGAMANI
-(TEL)</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr">
@@ -8223,14 +8211,14 @@
       </c>
       <c r="I27" s="7" t="inlineStr">
         <is>
-          <t>FATHIMA
-(HIN)</t>
+          <t>SWATHI
+(TEL)</t>
         </is>
       </c>
       <c r="J27" s="7" t="inlineStr">
         <is>
-          <t>MARTIAL ARTS
-(KAR)</t>
+          <t>RAVI
+(ENG)</t>
         </is>
       </c>
       <c r="K27" s="7" t="inlineStr">
@@ -8265,26 +8253,26 @@
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>SITHA
-(ENG)</t>
+          <t>NAGAMANI
+(TEL)</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
+          <t>BHAVANI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
           <t>SAI LAKSHMI
-(ENG)</t>
-        </is>
-      </c>
-      <c r="E28" s="7" t="inlineStr">
+(HIN)</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
         <is>
           <t>MAHA
-(ENG)</t>
-        </is>
-      </c>
-      <c r="F28" s="7" t="inlineStr">
-        <is>
-          <t>MAHESWARI
-(COMP)</t>
+(GRAM)</t>
         </is>
       </c>
       <c r="G28" s="7" t="inlineStr">
@@ -8295,22 +8283,22 @@
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
+          <t>TULASI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="I28" s="7" t="inlineStr">
+        <is>
+          <t>PALLAVI
+(SOC)</t>
+        </is>
+      </c>
+      <c r="J28" s="7" t="inlineStr">
+        <is>
           <t>SWATHI
 (TEL)</t>
         </is>
       </c>
-      <c r="I28" s="7" t="inlineStr">
-        <is>
-          <t>TULASI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="J28" s="7" t="inlineStr">
-        <is>
-          <t>FATHIMA
-(HIN)</t>
-        </is>
-      </c>
       <c r="K28" s="7" t="inlineStr">
         <is>
           <t>RAVI
@@ -8325,14 +8313,14 @@
       </c>
       <c r="M28" s="7" t="inlineStr">
         <is>
-          <t>GOWTHAM
-(MATH)</t>
+          <t>MARTIAL ARTS
+(KAR)</t>
         </is>
       </c>
       <c r="N28" s="7" t="inlineStr">
         <is>
-          <t>D.V.RAO
-(TEL)</t>
+          <t>BHEEMA
+(PHY)</t>
         </is>
       </c>
     </row>
@@ -8343,50 +8331,50 @@
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
+          <t>SITHA
+(MATH)</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>SAI LAKSHMI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>BHAVANI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
           <t>NAGAMANI
 (TEL)</t>
         </is>
       </c>
-      <c r="D29" s="7" t="inlineStr">
-        <is>
-          <t>SAI LAKSHMI
-(ENG)</t>
-        </is>
-      </c>
-      <c r="E29" s="7" t="inlineStr">
-        <is>
-          <t>BHAVANI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="F29" s="7" t="inlineStr">
-        <is>
-          <t>MAHA
-(GRAM)</t>
-        </is>
-      </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>TULASI
-(MATH)</t>
+          <t>RIYA
+(HIN)</t>
         </is>
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
-          <t>PALLAVI
-(SOC)</t>
+          <t>FATHIMA
+(HIN)</t>
         </is>
       </c>
       <c r="I29" s="7" t="inlineStr">
         <is>
+          <t>MARTIAL ARTS
+(KAR)</t>
+        </is>
+      </c>
+      <c r="J29" s="7" t="inlineStr">
+        <is>
           <t>LALITHA
-(EVS)</t>
-        </is>
-      </c>
-      <c r="J29" s="7" t="inlineStr">
-        <is>
-          <t>RAVI
-(ENG)</t>
+(BIO)</t>
         </is>
       </c>
       <c r="K29" s="7" t="inlineStr">
@@ -8409,8 +8397,8 @@
       </c>
       <c r="N29" s="7" t="inlineStr">
         <is>
-          <t>RIYA
-(HIN)</t>
+          <t>D.V.RAO
+(TEL)</t>
         </is>
       </c>
     </row>
@@ -8422,73 +8410,73 @@
       <c r="C30" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(ENG)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>NAGAMANI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
         <is>
           <t>BHAVANI
 (MATH)</t>
         </is>
       </c>
-      <c r="E30" s="7" t="inlineStr">
+      <c r="F30" s="7" t="inlineStr">
         <is>
           <t>SAI LAKSHMI
 (EVS)</t>
         </is>
       </c>
-      <c r="F30" s="7" t="inlineStr">
+      <c r="G30" s="7" t="inlineStr">
         <is>
           <t>MAHA
 (ENG)</t>
         </is>
       </c>
-      <c r="G30" s="7" t="inlineStr">
+      <c r="H30" s="7" t="inlineStr">
+        <is>
+          <t>SWATHI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="I30" s="7" t="inlineStr">
         <is>
           <t>TULASI
 (MATH)</t>
         </is>
       </c>
-      <c r="H30" s="7" t="inlineStr">
+      <c r="J30" s="7" t="inlineStr">
         <is>
           <t>FATHIMA
 (HIN)</t>
         </is>
       </c>
-      <c r="I30" s="7" t="inlineStr">
-        <is>
-          <t>PALLAVI
-(SOC)</t>
-        </is>
-      </c>
-      <c r="J30" s="7" t="inlineStr">
-        <is>
-          <t>SWATHI
+      <c r="K30" s="7" t="inlineStr">
+        <is>
+          <t>LALITHA
+(PHY)</t>
+        </is>
+      </c>
+      <c r="L30" s="7" t="inlineStr">
+        <is>
+          <t>D.V.RAO
 (TEL)</t>
         </is>
       </c>
-      <c r="K30" s="7" t="inlineStr">
-        <is>
-          <t>LALITHA
-(CHEM)</t>
-        </is>
-      </c>
-      <c r="L30" s="7" t="inlineStr">
-        <is>
-          <t>RAVI
-(GRAM)</t>
-        </is>
-      </c>
       <c r="M30" s="7" t="inlineStr">
-        <is>
-          <t>CHALAPATHI
-(BIO)</t>
-        </is>
-      </c>
-      <c r="N30" s="7" t="inlineStr">
         <is>
           <t>SONU
 (ENG)</t>
+        </is>
+      </c>
+      <c r="N30" s="7" t="inlineStr">
+        <is>
+          <t>SUNITHA
+(SOC)</t>
         </is>
       </c>
     </row>
@@ -8499,73 +8487,74 @@
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>SITHA
-(MATH)</t>
+          <t>P.E
+(P.E.T)</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>NAGAMANI
-(TEL)</t>
+          <t>P.E
+(P.E.T)</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
+          <t>P.E
+(P.E.T)</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>P.E
+(P.E.T)</t>
+        </is>
+      </c>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
           <t>SAI LAKSHMI
+(G.K)</t>
+        </is>
+      </c>
+      <c r="H31" s="7" t="inlineStr">
+        <is>
+          <t>MAHA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t>P.E
+(P.E.T)</t>
+        </is>
+      </c>
+      <c r="J31" s="7" t="inlineStr">
+        <is>
+          <t>PALLAVI
+(SOC)</t>
+        </is>
+      </c>
+      <c r="K31" s="7" t="inlineStr">
+        <is>
+          <t>FATHIMA
 (HIN)</t>
         </is>
       </c>
-      <c r="F31" s="7" t="inlineStr">
-        <is>
-          <t>TULASI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="G31" s="7" t="inlineStr">
+      <c r="L31" s="7" t="inlineStr">
+        <is>
+          <t>SONU
+(ENG)</t>
+        </is>
+      </c>
+      <c r="M31" s="7" t="inlineStr">
         <is>
           <t>RIYA
 (HIN)</t>
         </is>
       </c>
-      <c r="H31" s="7" t="inlineStr">
-        <is>
-          <t>MAHA
-(ENG)</t>
-        </is>
-      </c>
-      <c r="I31" s="7" t="inlineStr">
-        <is>
-          <t>SWATHI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="J31" s="7" t="inlineStr">
-        <is>
-          <t>LALITHA
-(CHEM)</t>
-        </is>
-      </c>
-      <c r="K31" s="7" t="inlineStr">
-        <is>
-          <t>FATHIMA
-(HIN)</t>
-        </is>
-      </c>
-      <c r="L31" s="7" t="inlineStr">
-        <is>
-          <t>D.V.RAO
-(TEL)</t>
-        </is>
-      </c>
-      <c r="M31" s="7" t="inlineStr">
-        <is>
-          <t>SONU
-(ENG)</t>
-        </is>
-      </c>
-      <c r="N31" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
+      <c r="N31" s="7" t="inlineStr">
+        <is>
+          <t>CHALAPATHI
+(BIO)</t>
         </is>
       </c>
     </row>
@@ -8576,74 +8565,74 @@
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
+          <t>SITHA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>SWATHI
+(HIN)</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>BHAVANI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>MAHA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="G32" s="7" t="inlineStr">
+        <is>
+          <t>TULASI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="H32" s="7" t="inlineStr">
+        <is>
+          <t>PALLAVI
+(SOC)</t>
+        </is>
+      </c>
+      <c r="I32" s="7" t="inlineStr">
+        <is>
+          <t>LALITHA
+(EVS)</t>
+        </is>
+      </c>
+      <c r="J32" s="7" t="inlineStr">
+        <is>
           <t>P.E
 (P.E.T)</t>
         </is>
       </c>
-      <c r="D32" s="7" t="inlineStr">
+      <c r="K32" s="7" t="inlineStr">
         <is>
           <t>P.E
 (P.E.T)</t>
         </is>
       </c>
-      <c r="E32" s="7" t="inlineStr">
+      <c r="L32" s="7" t="inlineStr">
         <is>
           <t>P.E
 (P.E.T)</t>
         </is>
       </c>
-      <c r="F32" s="7" t="inlineStr">
+      <c r="M32" s="7" t="inlineStr">
         <is>
           <t>P.E
 (P.E.T)</t>
         </is>
       </c>
-      <c r="G32" s="7" t="inlineStr">
-        <is>
-          <t>MAHA
-(ENG)</t>
-        </is>
-      </c>
-      <c r="H32" s="7" t="inlineStr">
+      <c r="N32" s="7" t="inlineStr">
         <is>
           <t>P.E
 (P.E.T)</t>
-        </is>
-      </c>
-      <c r="I32" s="7" t="inlineStr">
-        <is>
-          <t>P.E
-(P.E.T)</t>
-        </is>
-      </c>
-      <c r="J32" s="7" t="inlineStr">
-        <is>
-          <t>PALLAVI
-(SOC)</t>
-        </is>
-      </c>
-      <c r="K32" s="7" t="inlineStr">
-        <is>
-          <t>LALITHA
-(PHY)</t>
-        </is>
-      </c>
-      <c r="L32" s="7" t="inlineStr">
-        <is>
-          <t>SONU
-(ENG)</t>
-        </is>
-      </c>
-      <c r="M32" s="7" t="inlineStr">
-        <is>
-          <t>RIYA
-(HIN)</t>
-        </is>
-      </c>
-      <c r="N32" s="7" t="inlineStr">
-        <is>
-          <t>CHALAPATHI
-(BIO)</t>
         </is>
       </c>
     </row>
@@ -8719,9 +8708,10 @@
 (CLASS)</t>
         </is>
       </c>
-      <c r="N33" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
+      <c r="N33" s="8" t="inlineStr">
+        <is>
+          <t>SONU
+(ENG)</t>
         </is>
       </c>
     </row>
@@ -8743,7 +8733,7 @@
       <c r="D34" s="7" t="inlineStr">
         <is>
           <t>BHAVANI
-(MATH)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
@@ -8755,7 +8745,7 @@
       <c r="F34" s="7" t="inlineStr">
         <is>
           <t>SAI LAKSHMI
-(HIN)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
@@ -8802,8 +8792,8 @@
       </c>
       <c r="N34" s="7" t="inlineStr">
         <is>
-          <t>BHEEMA
-(PHY)</t>
+          <t>GOWTHAM
+(MATH)</t>
         </is>
       </c>
     </row>
@@ -8815,19 +8805,19 @@
       <c r="C35" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(MATH)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>NAGAMANI
-(TEL)</t>
+          <t>SAI LAKSHMI
+(ENG)</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>SAI LAKSHMI
-(EVS)</t>
+          <t>MAHESWARI
+(COMP)</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr">
@@ -8838,28 +8828,28 @@
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>MAHA
-(GRAM)</t>
+          <t>RIYA
+(HIN)</t>
         </is>
       </c>
       <c r="H35" s="7" t="inlineStr">
         <is>
-          <t>LALITHA
-(EVS)</t>
+          <t>SWATHI
+(TEL)</t>
         </is>
       </c>
       <c r="I35" s="7" t="inlineStr">
-        <is>
-          <t>FATHIMA
-(HIN)</t>
-        </is>
-      </c>
-      <c r="J35" s="7" t="inlineStr">
         <is>
           <t>PALLAVI
 (SOC)</t>
         </is>
       </c>
+      <c r="J35" s="7" t="inlineStr">
+        <is>
+          <t>LALITHA
+(PHY)</t>
+        </is>
+      </c>
       <c r="K35" s="7" t="inlineStr">
         <is>
           <t>SANGEETHA
@@ -8868,20 +8858,20 @@
       </c>
       <c r="L35" s="7" t="inlineStr">
         <is>
+          <t>RAVI
+(GRAM)</t>
+        </is>
+      </c>
+      <c r="M35" s="7" t="inlineStr">
+        <is>
+          <t>GOWTHAM
+(MATH)</t>
+        </is>
+      </c>
+      <c r="N35" s="7" t="inlineStr">
+        <is>
           <t>BHEEMA
 (PHY)</t>
-        </is>
-      </c>
-      <c r="M35" s="7" t="inlineStr">
-        <is>
-          <t>SUNITHA
-(SOC)</t>
-        </is>
-      </c>
-      <c r="N35" s="7" t="inlineStr">
-        <is>
-          <t>RIYA
-(HIN)</t>
         </is>
       </c>
     </row>
@@ -8892,8 +8882,8 @@
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>SITHA
-(MATH)</t>
+          <t>NAGAMANI
+(TEL)</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
@@ -8904,20 +8894,20 @@
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>BHAVANI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="F36" s="7" t="inlineStr">
-        <is>
           <t>MAHA
 (ENG)</t>
         </is>
       </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>BHAVANI
+(G.K)</t>
+        </is>
+      </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>MARTIAL ARTS
-(KAR)</t>
+          <t>LALITHA
+(EVS)</t>
         </is>
       </c>
       <c r="H36" s="7" t="inlineStr">
@@ -8934,32 +8924,32 @@
       </c>
       <c r="J36" s="7" t="inlineStr">
         <is>
+          <t>RAVI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="K36" s="7" t="inlineStr">
+        <is>
           <t>FATHIMA
 (HIN)</t>
         </is>
       </c>
-      <c r="K36" s="7" t="inlineStr">
-        <is>
-          <t>LALITHA
-(CHEM)</t>
-        </is>
-      </c>
       <c r="L36" s="7" t="inlineStr">
+        <is>
+          <t>BHEEMA
+(PHY)</t>
+        </is>
+      </c>
+      <c r="M36" s="7" t="inlineStr">
+        <is>
+          <t>GOWTHAM
+(MATH)</t>
+        </is>
+      </c>
+      <c r="N36" s="7" t="inlineStr">
         <is>
           <t>D.V.RAO
 (TEL)</t>
-        </is>
-      </c>
-      <c r="M36" s="7" t="inlineStr">
-        <is>
-          <t>BHEEMA
-(CHEM)</t>
-        </is>
-      </c>
-      <c r="N36" s="7" t="inlineStr">
-        <is>
-          <t>GOWTHAM
-(MATH)</t>
         </is>
       </c>
     </row>
@@ -8971,7 +8961,7 @@
       <c r="C37" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(MATH)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
@@ -8982,38 +8972,38 @@
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>MAHESWARI
-(COMP)</t>
+          <t>SAI LAKSHMI
+(EVS)</t>
         </is>
       </c>
       <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>NAGAMANI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>MAHA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="H37" s="7" t="inlineStr">
+        <is>
+          <t>LALITHA
+(EVS)</t>
+        </is>
+      </c>
+      <c r="I37" s="7" t="inlineStr">
         <is>
           <t>TULASI
 (MATH)</t>
         </is>
       </c>
-      <c r="G37" s="7" t="inlineStr">
-        <is>
-          <t>LALITHA
-(EVS)</t>
-        </is>
-      </c>
-      <c r="H37" s="7" t="inlineStr">
-        <is>
-          <t>SWATHI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="I37" s="7" t="inlineStr">
-        <is>
-          <t>MARTIAL ARTS
-(KAR)</t>
-        </is>
-      </c>
       <c r="J37" s="7" t="inlineStr">
         <is>
-          <t>RAVI
-(ENG)</t>
+          <t>FATHIMA
+(HIN)</t>
         </is>
       </c>
       <c r="K37" s="7" t="inlineStr">
@@ -9024,20 +9014,20 @@
       </c>
       <c r="L37" s="7" t="inlineStr">
         <is>
+          <t>D.V.RAO
+(TEL)</t>
+        </is>
+      </c>
+      <c r="M37" s="7" t="inlineStr">
+        <is>
           <t>SUNITHA
 (SOC)</t>
         </is>
       </c>
-      <c r="M37" s="7" t="inlineStr">
+      <c r="N37" s="7" t="inlineStr">
         <is>
           <t>RIYA
 (HIN)</t>
-        </is>
-      </c>
-      <c r="N37" s="7" t="inlineStr">
-        <is>
-          <t>D.V.RAO
-(TEL)</t>
         </is>
       </c>
     </row>
@@ -9054,8 +9044,8 @@
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>BHAVANI
-(MATH)</t>
+          <t>NAGAMANI
+(TEL)</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
@@ -9066,56 +9056,56 @@
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>MARTIAL ARTS
-(KAR)</t>
+          <t>MAHA
+(ENG)</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr">
+        <is>
+          <t>TULASI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="H38" s="7" t="inlineStr">
+        <is>
+          <t>SANGEETHA
+(G.K)</t>
+        </is>
+      </c>
+      <c r="I38" s="7" t="inlineStr">
+        <is>
+          <t>FATHIMA
+(HIN)</t>
+        </is>
+      </c>
+      <c r="J38" s="7" t="inlineStr">
         <is>
           <t>PALLAVI
 (SOC)</t>
         </is>
       </c>
-      <c r="H38" s="7" t="inlineStr">
-        <is>
-          <t>MAHA
+      <c r="K38" s="7" t="inlineStr">
+        <is>
+          <t>D.V.RAO
+(TEL)</t>
+        </is>
+      </c>
+      <c r="L38" s="7" t="inlineStr">
+        <is>
+          <t>SONU
 (ENG)</t>
         </is>
       </c>
-      <c r="I38" s="7" t="inlineStr">
-        <is>
-          <t>TULASI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="J38" s="7" t="inlineStr">
-        <is>
-          <t>SWATHI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="K38" s="7" t="inlineStr">
-        <is>
-          <t>FATHIMA
-(G.K)</t>
-        </is>
-      </c>
-      <c r="L38" s="7" t="inlineStr">
+      <c r="M38" s="7" t="inlineStr">
+        <is>
+          <t>RIYA
+(HIN)</t>
+        </is>
+      </c>
+      <c r="N38" s="7" t="inlineStr">
         <is>
           <t>CHALAPATHI
 (BIO)</t>
-        </is>
-      </c>
-      <c r="M38" s="7" t="inlineStr">
-        <is>
-          <t>SONU
-(ENG)</t>
-        </is>
-      </c>
-      <c r="N38" s="7" t="inlineStr">
-        <is>
-          <t>SUNITHA
-(SOC)</t>
         </is>
       </c>
     </row>
@@ -9126,74 +9116,74 @@
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>NAGAMANI
+          <t>P.E
+(P.E.T)</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>P.E
+(P.E.T)</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>P.E
+(P.E.T)</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>P.E
+(P.E.T)</t>
+        </is>
+      </c>
+      <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t>P.E
+(P.E.T)</t>
+        </is>
+      </c>
+      <c r="H39" s="7" t="inlineStr">
+        <is>
+          <t>MAHA
+(GRAM)</t>
+        </is>
+      </c>
+      <c r="I39" s="7" t="inlineStr">
+        <is>
+          <t>P.E
+(P.E.T)</t>
+        </is>
+      </c>
+      <c r="J39" s="7" t="inlineStr">
+        <is>
+          <t>SWATHI
 (TEL)</t>
         </is>
       </c>
-      <c r="D39" s="7" t="inlineStr">
-        <is>
-          <t>SWATHI
-(HIN)</t>
-        </is>
-      </c>
-      <c r="E39" s="7" t="inlineStr">
-        <is>
-          <t>MAHA
-(ENG)</t>
-        </is>
-      </c>
-      <c r="F39" s="7" t="inlineStr">
-        <is>
-          <t>TULASI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="G39" s="7" t="inlineStr">
-        <is>
-          <t>RIYA
-(HIN)</t>
-        </is>
-      </c>
-      <c r="H39" s="7" t="inlineStr">
-        <is>
-          <t>MAHESWARI
-(COMP)</t>
-        </is>
-      </c>
-      <c r="I39" s="7" t="inlineStr">
-        <is>
-          <t>PALLAVI
-(SOC)</t>
-        </is>
-      </c>
-      <c r="J39" s="7" t="inlineStr">
+      <c r="K39" s="7" t="inlineStr">
         <is>
           <t>LALITHA
-(PHY)</t>
-        </is>
-      </c>
-      <c r="K39" s="7" t="inlineStr">
-        <is>
-          <t>RAVI
-(ENG)</t>
+(CHEM)</t>
         </is>
       </c>
       <c r="L39" s="7" t="inlineStr">
-        <is>
-          <t>SANGEETHA
-(MATH)</t>
-        </is>
-      </c>
-      <c r="M39" s="7" t="inlineStr">
         <is>
           <t>CHALAPATHI
 (BIO)</t>
         </is>
       </c>
-      <c r="N39" s="7" t="inlineStr">
+      <c r="M39" s="7" t="inlineStr">
         <is>
           <t>SONU
 (ENG)</t>
+        </is>
+      </c>
+      <c r="N39" s="7" t="inlineStr">
+        <is>
+          <t>SUNITHA
+(SOC)</t>
         </is>
       </c>
     </row>
@@ -9205,13 +9195,13 @@
       <c r="C40" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(MATH)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>BHAVANI
-(MATH)</t>
+          <t>SWATHI
+(HIN)</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
@@ -9222,22 +9212,22 @@
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
-          <t>NAGAMANI
-(TEL)</t>
+          <t>TULASI
+(MATH)</t>
         </is>
       </c>
       <c r="G40" s="7" t="inlineStr">
+        <is>
+          <t>PALLAVI
+(SOC)</t>
+        </is>
+      </c>
+      <c r="H40" s="7" t="inlineStr">
         <is>
           <t>MAHA
 (ENG)</t>
         </is>
       </c>
-      <c r="H40" s="7" t="inlineStr">
-        <is>
-          <t>FATHIMA
-(HIN)</t>
-        </is>
-      </c>
       <c r="I40" s="7" t="inlineStr">
         <is>
           <t>LALITHA
@@ -9252,26 +9242,26 @@
       </c>
       <c r="K40" s="7" t="inlineStr">
         <is>
-          <t>D.V.RAO
-(TEL)</t>
+          <t>RAVI
+(ENG)</t>
         </is>
       </c>
       <c r="L40" s="7" t="inlineStr">
+        <is>
+          <t>SUNITHA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="M40" s="7" t="inlineStr">
+        <is>
+          <t>CHALAPATHI
+(BIO)</t>
+        </is>
+      </c>
+      <c r="N40" s="7" t="inlineStr">
         <is>
           <t>SONU
 (ENG)</t>
-        </is>
-      </c>
-      <c r="M40" s="7" t="inlineStr">
-        <is>
-          <t>RAVI
-(GRAM)</t>
-        </is>
-      </c>
-      <c r="N40" s="7" t="inlineStr">
-        <is>
-          <t>CHALAPATHI
-(BIO)</t>
         </is>
       </c>
     </row>
@@ -9365,25 +9355,25 @@
       <c r="C42" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(ENG)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
           <t>BHAVANI
-(MATH)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
           <t>NAGAMANI
-(G.K)</t>
+(TEL)</t>
         </is>
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
           <t>SAI LAKSHMI
-(EVS)</t>
+(HIN)</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
@@ -9430,8 +9420,8 @@
       </c>
       <c r="N42" s="7" t="inlineStr">
         <is>
-          <t>SUNITHA
-(SOC)</t>
+          <t>RIYA
+(HIN)</t>
         </is>
       </c>
     </row>
@@ -9443,43 +9433,43 @@
       <c r="C43" s="7" t="inlineStr">
         <is>
           <t>SITHA
+(EVS)</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>NAGAMANI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>BHAVANI
 (MATH)</t>
         </is>
       </c>
-      <c r="D43" s="7" t="inlineStr">
+      <c r="F43" s="7" t="inlineStr">
         <is>
           <t>SAI LAKSHMI
-(ENG)</t>
-        </is>
-      </c>
-      <c r="E43" s="7" t="inlineStr">
-        <is>
-          <t>MAHESWARI
-(COMP)</t>
-        </is>
-      </c>
-      <c r="F43" s="7" t="inlineStr">
+(EVS)</t>
+        </is>
+      </c>
+      <c r="G43" s="7" t="inlineStr">
+        <is>
+          <t>LALITHA
+(EVS)</t>
+        </is>
+      </c>
+      <c r="H43" s="7" t="inlineStr">
         <is>
           <t>MAHA
 (ENG)</t>
         </is>
       </c>
-      <c r="G43" s="7" t="inlineStr">
-        <is>
-          <t>TULASI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="H43" s="7" t="inlineStr">
-        <is>
-          <t>PALLAVI
-(SOC)</t>
-        </is>
-      </c>
       <c r="I43" s="7" t="inlineStr">
         <is>
-          <t>LALITHA
-(EVS)</t>
+          <t>SWATHI
+(TEL)</t>
         </is>
       </c>
       <c r="J43" s="7" t="inlineStr">
@@ -9490,8 +9480,8 @@
       </c>
       <c r="K43" s="7" t="inlineStr">
         <is>
-          <t>MARTIAL ARTS
-(KAR)</t>
+          <t>SANGEETHA
+(MATH)</t>
         </is>
       </c>
       <c r="L43" s="7" t="inlineStr">
@@ -9506,10 +9496,9 @@
 (MATH)</t>
         </is>
       </c>
-      <c r="N43" s="7" t="inlineStr">
-        <is>
-          <t>D.V.RAO
-(TEL)</t>
+      <c r="N43" s="12" t="inlineStr">
+        <is>
+          <t>Recreation</t>
         </is>
       </c>
     </row>
@@ -9526,34 +9515,34 @@
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>BHAVANI
+          <t>SWATHI
+(HIN)</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>SAI LAKSHMI
+(EVS)</t>
+        </is>
+      </c>
+      <c r="F44" s="7" t="inlineStr">
+        <is>
+          <t>MARTIAL ARTS
+(KAR)</t>
+        </is>
+      </c>
+      <c r="G44" s="7" t="inlineStr">
+        <is>
+          <t>TULASI
 (MATH)</t>
         </is>
       </c>
-      <c r="E44" s="7" t="inlineStr">
-        <is>
-          <t>MAHA
-(ENG)</t>
-        </is>
-      </c>
-      <c r="F44" s="7" t="inlineStr">
-        <is>
-          <t>SAI LAKSHMI
-(HIN)</t>
-        </is>
-      </c>
-      <c r="G44" s="7" t="inlineStr">
+      <c r="H44" s="7" t="inlineStr">
         <is>
           <t>PALLAVI
 (SOC)</t>
         </is>
       </c>
-      <c r="H44" s="7" t="inlineStr">
-        <is>
-          <t>LALITHA
-(EVS)</t>
-        </is>
-      </c>
       <c r="I44" s="7" t="inlineStr">
         <is>
           <t>SANGEETHA
@@ -9562,14 +9551,14 @@
       </c>
       <c r="J44" s="7" t="inlineStr">
         <is>
-          <t>SWATHI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="K44" s="7" t="inlineStr">
-        <is>
           <t>FATHIMA
 (HIN)</t>
+        </is>
+      </c>
+      <c r="K44" s="7" t="inlineStr">
+        <is>
+          <t>LALITHA
+(BIO)</t>
         </is>
       </c>
       <c r="L44" s="7" t="inlineStr">
@@ -9599,61 +9588,61 @@
       <c r="C45" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(ORAL)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>SAI LAKSHMI
+          <t>BHAVANI
+(EVS)</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>MAHA
 (ENG)</t>
         </is>
       </c>
-      <c r="E45" s="7" t="inlineStr">
-        <is>
-          <t>NAGAMANI
-(TEL)</t>
-        </is>
-      </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
-          <t>BHAVANI
-(G.K)</t>
+          <t>MAHESWARI
+(COMP)</t>
         </is>
       </c>
       <c r="G45" s="7" t="inlineStr">
+        <is>
+          <t>TULASI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="H45" s="7" t="inlineStr">
+        <is>
+          <t>FATHIMA
+(HIN)</t>
+        </is>
+      </c>
+      <c r="I45" s="7" t="inlineStr">
         <is>
           <t>LALITHA
 (EVS)</t>
         </is>
       </c>
-      <c r="H45" s="7" t="inlineStr">
-        <is>
-          <t>SWATHI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="I45" s="7" t="inlineStr">
-        <is>
-          <t>TULASI
-(MATH)</t>
-        </is>
-      </c>
       <c r="J45" s="7" t="inlineStr">
         <is>
-          <t>FATHIMA
-(HIN)</t>
+          <t>PALLAVI
+(SOC)</t>
         </is>
       </c>
       <c r="K45" s="7" t="inlineStr">
         <is>
           <t>RAVI
-(GRAM)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="L45" s="7" t="inlineStr">
         <is>
-          <t>SANGEETHA
-(MATH)</t>
+          <t>SUNITHA
+(SOC)</t>
         </is>
       </c>
       <c r="M45" s="7" t="inlineStr">
@@ -9662,9 +9651,10 @@
 (HIN)</t>
         </is>
       </c>
-      <c r="N45" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
+      <c r="N45" s="7" t="inlineStr">
+        <is>
+          <t>D.V.RAO
+(TEL)</t>
         </is>
       </c>
     </row>
@@ -9676,72 +9666,73 @@
       <c r="C46" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(ENG)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
-        <is>
-          <t>SAI LAKSHMI
-(ENG)</t>
-        </is>
-      </c>
-      <c r="E46" s="7" t="inlineStr">
         <is>
           <t>BHAVANI
 (MATH)</t>
         </is>
       </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>SAI LAKSHMI
+(EVS)</t>
+        </is>
+      </c>
       <c r="F46" s="7" t="inlineStr">
-        <is>
-          <t>TULASI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="G46" s="7" t="inlineStr">
         <is>
           <t>MAHA
 (ENG)</t>
         </is>
       </c>
+      <c r="G46" s="7" t="inlineStr">
+        <is>
+          <t>PALLAVI
+(SOC)</t>
+        </is>
+      </c>
       <c r="H46" s="7" t="inlineStr">
+        <is>
+          <t>SWATHI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="I46" s="7" t="inlineStr">
         <is>
           <t>FATHIMA
 (HIN)</t>
         </is>
       </c>
-      <c r="I46" s="7" t="inlineStr">
-        <is>
-          <t>PALLAVI
-(SOC)</t>
-        </is>
-      </c>
       <c r="J46" s="7" t="inlineStr">
         <is>
+          <t>RAVI
+(GRAM)</t>
+        </is>
+      </c>
+      <c r="K46" s="7" t="inlineStr">
+        <is>
           <t>LALITHA
-(PHY)</t>
-        </is>
-      </c>
-      <c r="K46" s="7" t="inlineStr">
-        <is>
-          <t>RAVI
-(ENG)</t>
+(CHEM)</t>
         </is>
       </c>
       <c r="L46" s="7" t="inlineStr">
+        <is>
+          <t>SANGEETHA
+(MATH)</t>
+        </is>
+      </c>
+      <c r="M46" s="7" t="inlineStr">
         <is>
           <t>SUNITHA
 (SOC)</t>
         </is>
       </c>
-      <c r="M46" s="7" t="inlineStr">
+      <c r="N46" s="7" t="inlineStr">
         <is>
           <t>SONU
 (ENG)</t>
-        </is>
-      </c>
-      <c r="N46" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
         </is>
       </c>
     </row>
@@ -9753,55 +9744,55 @@
       <c r="C47" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(ENG)</t>
+(ORAL)</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>BHAVANI
+(EVS)</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>SAI LAKSHMI
+(HIN)</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="inlineStr">
         <is>
           <t>NAGAMANI
 (TEL)</t>
         </is>
       </c>
-      <c r="E47" s="7" t="inlineStr">
-        <is>
-          <t>BHAVANI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="F47" s="7" t="inlineStr">
-        <is>
-          <t>MAHESWARI
-(COMP)</t>
-        </is>
-      </c>
       <c r="G47" s="7" t="inlineStr">
+        <is>
+          <t>MAHA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="H47" s="7" t="inlineStr">
+        <is>
+          <t>LALITHA
+(EVS)</t>
+        </is>
+      </c>
+      <c r="I47" s="7" t="inlineStr">
         <is>
           <t>TULASI
 (MATH)</t>
         </is>
       </c>
-      <c r="H47" s="7" t="inlineStr">
-        <is>
-          <t>MAHA
-(GRAM)</t>
-        </is>
-      </c>
-      <c r="I47" s="7" t="inlineStr">
+      <c r="J47" s="7" t="inlineStr">
         <is>
           <t>SWATHI
 (TEL)</t>
         </is>
       </c>
-      <c r="J47" s="7" t="inlineStr">
-        <is>
-          <t>LALITHA
-(CHEM)</t>
-        </is>
-      </c>
       <c r="K47" s="7" t="inlineStr">
         <is>
-          <t>SANGEETHA
-(MATH)</t>
+          <t>D.V.RAO
+(TEL)</t>
         </is>
       </c>
       <c r="L47" s="7" t="inlineStr">
@@ -9810,15 +9801,16 @@
 (ENG)</t>
         </is>
       </c>
-      <c r="M47" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
-        </is>
-      </c>
-      <c r="N47" s="7" t="inlineStr">
+      <c r="M47" s="7" t="inlineStr">
         <is>
           <t>CHALAPATHI
 (BIO)</t>
+        </is>
+      </c>
+      <c r="N47" s="7" t="inlineStr">
+        <is>
+          <t>SUNITHA
+(SOC)</t>
         </is>
       </c>
     </row>
@@ -9829,74 +9821,74 @@
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>SITHA
-(ENG)</t>
+          <t>P.E
+(P.E.T)</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>SWATHI
-(HIN)</t>
+          <t>P.E
+(P.E.T)</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>SAI LAKSHMI
-(HIN)</t>
+          <t>P.E
+(P.E.T)</t>
         </is>
       </c>
       <c r="F48" s="7" t="inlineStr">
         <is>
-          <t>NAGAMANI
-(TEL)</t>
+          <t>P.E
+(P.E.T)</t>
         </is>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
-          <t>MAHESWARI
-(COMP)</t>
+          <t>P.E
+(P.E.T)</t>
         </is>
       </c>
       <c r="H48" s="7" t="inlineStr">
         <is>
-          <t>MAHA
-(ENG)</t>
+          <t>P.E
+(P.E.T)</t>
         </is>
       </c>
       <c r="I48" s="7" t="inlineStr">
+        <is>
+          <t>PALLAVI
+(SOC)</t>
+        </is>
+      </c>
+      <c r="J48" s="7" t="inlineStr">
+        <is>
+          <t>LALITHA
+(CHEM)</t>
+        </is>
+      </c>
+      <c r="K48" s="7" t="inlineStr">
         <is>
           <t>FATHIMA
 (HIN)</t>
         </is>
       </c>
-      <c r="J48" s="7" t="inlineStr">
-        <is>
-          <t>PALLAVI
-(SOC)</t>
-        </is>
-      </c>
-      <c r="K48" s="7" t="inlineStr">
-        <is>
-          <t>D.V.RAO
-(TEL)</t>
-        </is>
-      </c>
       <c r="L48" s="7" t="inlineStr">
         <is>
           <t>SANGEETHA
-(COMP)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="M48" s="7" t="inlineStr">
-        <is>
-          <t>SUNITHA
-(SOC)</t>
-        </is>
-      </c>
-      <c r="N48" s="7" t="inlineStr">
         <is>
           <t>SONU
 (ENG)</t>
+        </is>
+      </c>
+      <c r="N48" s="7" t="inlineStr">
+        <is>
+          <t>CHALAPATHI
+(BIO)</t>
         </is>
       </c>
     </row>

--- a/NRCS/Output/NRCS_Timetable_Final.xlsx
+++ b/NRCS/Output/NRCS_Timetable_Final.xlsx
@@ -659,20 +659,20 @@
       <c r="C5" s="7" t="inlineStr"/>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>U.K.G (MATH)</t>
+          <t>Class 1 (MATH)</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>Class 1 (MATH)</t>
-        </is>
-      </c>
-      <c r="F5" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (MATH)</t>
-        </is>
-      </c>
-      <c r="G5" s="7" t="inlineStr"/>
+          <t>U.K.G (EVS)</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr"/>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>U.K.G (EVS)</t>
+        </is>
+      </c>
       <c r="H5" s="7" t="inlineStr"/>
       <c r="I5" s="8" t="inlineStr">
         <is>
@@ -688,29 +688,29 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
+          <t>U.K.G (EVS)</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>Class 1 (MATH)</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr"/>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
           <t>U.K.G (MATH)</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr"/>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>U.K.G (MATH)</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (MATH)</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (G.K)</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr"/>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>U.K.G (MATH)</t>
+          <t>Class 1 (MATH)</t>
         </is>
       </c>
       <c r="I6" s="8" t="inlineStr">
@@ -727,26 +727,26 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
+          <t>U.K.G (MATH)</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
           <t>U.K.G (EVS)</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (MATH)</t>
-        </is>
-      </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>U.K.G (MATH)</t>
+          <t>Class 1 (MATH)</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr"/>
-      <c r="F7" s="7" t="inlineStr"/>
-      <c r="G7" s="7" t="inlineStr">
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>Class 1 (MATH)</t>
         </is>
       </c>
+      <c r="G7" s="7" t="inlineStr"/>
       <c r="H7" s="7" t="inlineStr">
         <is>
           <t>U.K.G (EVS)</t>
@@ -766,7 +766,7 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>U.K.G (EVS)</t>
+          <t>U.K.G (MATH)</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr"/>
@@ -777,20 +777,16 @@
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>Class 1 (MATH)</t>
+          <t>Class 2 (G.K)</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>Class 1 (MATH)</t>
+          <t>U.K.G (EVS)</t>
         </is>
       </c>
       <c r="G8" s="7" t="inlineStr"/>
-      <c r="H8" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (MATH)</t>
-        </is>
-      </c>
+      <c r="H8" s="7" t="inlineStr"/>
       <c r="I8" s="8" t="inlineStr">
         <is>
           <t>U.K.G</t>
@@ -805,21 +801,25 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>U.K.G (EVS)</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr"/>
+          <t>U.K.G (MATH)</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>U.K.G (MATH)</t>
+        </is>
+      </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (G.K)</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
           <t>U.K.G (MATH)</t>
         </is>
       </c>
-      <c r="F9" s="7" t="inlineStr"/>
+      <c r="E9" s="7" t="inlineStr"/>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>U.K.G (MATH)</t>
+        </is>
+      </c>
       <c r="G9" s="7" t="inlineStr"/>
       <c r="H9" s="7" t="inlineStr"/>
       <c r="I9" s="8" t="inlineStr">
@@ -836,12 +836,12 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>U.K.G (EVS)</t>
+          <t>U.K.G (MATH)</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>Class 1 (MATH)</t>
+          <t>Class 2 (G.K)</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr"/>
@@ -852,15 +852,15 @@
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>U.K.G (MATH)</t>
-        </is>
-      </c>
-      <c r="G10" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (EVS)</t>
-        </is>
-      </c>
-      <c r="H10" s="7" t="inlineStr"/>
+          <t>Class 1 (MATH)</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="inlineStr"/>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>Class 1 (MATH)</t>
+        </is>
+      </c>
       <c r="I10" s="8" t="inlineStr">
         <is>
           <t>U.K.G</t>
@@ -935,19 +935,15 @@
           <t>MON</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (CHEM)</t>
-        </is>
-      </c>
+      <c r="B14" s="7" t="inlineStr"/>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>Class 9 (CHEM)</t>
+          <t>Class 10 (PHY)</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>Class 9 (PHY)</t>
+          <t>Class 8 (CHEM)</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr"/>
@@ -965,10 +961,14 @@
       <c r="B15" s="7" t="inlineStr"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (PHY)</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr"/>
+          <t>Class 9 (PHY)</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (PHY)</t>
+        </is>
+      </c>
       <c r="E15" s="7" t="inlineStr"/>
       <c r="F15" s="7" t="inlineStr"/>
       <c r="G15" s="7" t="inlineStr"/>
@@ -981,15 +981,19 @@
           <t>WED</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr"/>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (CHEM)</t>
+        </is>
+      </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>Class 10 (CHEM)</t>
+          <t>Class 8 (CHEM)</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (CHEM)</t>
+          <t>Class 9 (CHEM)</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr"/>
@@ -1010,11 +1014,7 @@
           <t>Class 9 (CHEM)</t>
         </is>
       </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (PHY)</t>
-        </is>
-      </c>
+      <c r="D17" s="7" t="inlineStr"/>
       <c r="E17" s="7" t="inlineStr"/>
       <c r="F17" s="7" t="inlineStr"/>
       <c r="G17" s="7" t="inlineStr"/>
@@ -1030,12 +1030,12 @@
       <c r="B18" s="7" t="inlineStr"/>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>Class 10 (PHY)</t>
+          <t>Class 8 (PHY)</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (PHY)</t>
+          <t>Class 10 (CHEM)</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr"/>
@@ -1053,7 +1053,7 @@
       <c r="B19" s="7" t="inlineStr"/>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (CHEM)</t>
+          <t>Class 8 (PHY)</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
@@ -1139,21 +1139,13 @@
       <c r="C23" s="7" t="inlineStr"/>
       <c r="D23" s="7" t="inlineStr"/>
       <c r="E23" s="7" t="inlineStr"/>
-      <c r="F23" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (BIO)</t>
-        </is>
-      </c>
+      <c r="F23" s="7" t="inlineStr"/>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>Class 9 (BIO)</t>
-        </is>
-      </c>
-      <c r="H23" s="7" t="inlineStr">
-        <is>
           <t>Class 8 (BIO)</t>
         </is>
       </c>
+      <c r="H23" s="7" t="inlineStr"/>
       <c r="I23" s="7" t="inlineStr"/>
     </row>
     <row r="24">
@@ -1166,12 +1158,12 @@
       <c r="C24" s="7" t="inlineStr"/>
       <c r="D24" s="7" t="inlineStr"/>
       <c r="E24" s="7" t="inlineStr"/>
-      <c r="F24" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (BIO)</t>
-        </is>
-      </c>
-      <c r="G24" s="7" t="inlineStr"/>
+      <c r="F24" s="7" t="inlineStr"/>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (BIO)</t>
+        </is>
+      </c>
       <c r="H24" s="7" t="inlineStr"/>
       <c r="I24" s="7" t="inlineStr"/>
     </row>
@@ -1185,9 +1177,17 @@
       <c r="C25" s="7" t="inlineStr"/>
       <c r="D25" s="7" t="inlineStr"/>
       <c r="E25" s="7" t="inlineStr"/>
-      <c r="F25" s="7" t="inlineStr"/>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (BIO)</t>
+        </is>
+      </c>
       <c r="G25" s="7" t="inlineStr"/>
-      <c r="H25" s="7" t="inlineStr"/>
+      <c r="H25" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (BIO)</t>
+        </is>
+      </c>
       <c r="I25" s="7" t="inlineStr"/>
     </row>
     <row r="26">
@@ -1219,19 +1219,15 @@
       <c r="C27" s="7" t="inlineStr"/>
       <c r="D27" s="7" t="inlineStr"/>
       <c r="E27" s="7" t="inlineStr"/>
-      <c r="F27" s="7" t="inlineStr">
+      <c r="F27" s="7" t="inlineStr"/>
+      <c r="G27" s="7" t="inlineStr">
         <is>
           <t>Class 10 (BIO)</t>
         </is>
       </c>
-      <c r="G27" s="7" t="inlineStr">
+      <c r="H27" s="7" t="inlineStr">
         <is>
           <t>Class 8 (BIO)</t>
-        </is>
-      </c>
-      <c r="H27" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (BIO)</t>
         </is>
       </c>
       <c r="I27" s="7" t="inlineStr"/>
@@ -1246,15 +1242,19 @@
       <c r="C28" s="7" t="inlineStr"/>
       <c r="D28" s="7" t="inlineStr"/>
       <c r="E28" s="7" t="inlineStr"/>
-      <c r="F28" s="7" t="inlineStr"/>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (BIO)</t>
+        </is>
+      </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>Class 9 (BIO)</t>
+          <t>Class 10 (BIO)</t>
         </is>
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>Class 10 (BIO)</t>
+          <t>Class 8 (BIO)</t>
         </is>
       </c>
       <c r="I28" s="7" t="inlineStr"/>
@@ -1334,20 +1334,20 @@
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
+          <t>Class 7 (TEL)</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr"/>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
           <t>Class 8 (TEL)</t>
         </is>
       </c>
-      <c r="D32" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (TEL)</t>
-        </is>
-      </c>
-      <c r="E32" s="7" t="inlineStr"/>
       <c r="F32" s="7" t="inlineStr"/>
       <c r="G32" s="7" t="inlineStr"/>
       <c r="H32" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (TEL)</t>
+          <t>Class 10 (TEL)</t>
         </is>
       </c>
       <c r="I32" s="8" t="inlineStr">
@@ -1367,22 +1367,22 @@
           <t>Class 9 (TEL)</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr">
+      <c r="C33" s="7" t="inlineStr"/>
+      <c r="D33" s="7" t="inlineStr">
         <is>
           <t>Class 7 (TEL)</t>
         </is>
       </c>
-      <c r="D33" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (TEL)</t>
-        </is>
-      </c>
-      <c r="E33" s="7" t="inlineStr"/>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (TEL)</t>
+        </is>
+      </c>
       <c r="F33" s="7" t="inlineStr"/>
       <c r="G33" s="7" t="inlineStr"/>
       <c r="H33" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (TEL)</t>
+          <t>Class 10 (TEL)</t>
         </is>
       </c>
       <c r="I33" s="8" t="inlineStr">
@@ -1402,14 +1402,10 @@
           <t>Class 9 (TEL)</t>
         </is>
       </c>
-      <c r="C34" s="7" t="inlineStr">
+      <c r="C34" s="7" t="inlineStr"/>
+      <c r="D34" s="7" t="inlineStr">
         <is>
           <t>Class 8 (TEL)</t>
-        </is>
-      </c>
-      <c r="D34" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (TEL)</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr"/>
@@ -1418,7 +1414,11 @@
           <t>Class 7 (TEL)</t>
         </is>
       </c>
-      <c r="G34" s="7" t="inlineStr"/>
+      <c r="G34" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (TEL)</t>
+        </is>
+      </c>
       <c r="H34" s="7" t="inlineStr"/>
       <c r="I34" s="8" t="inlineStr">
         <is>
@@ -1437,20 +1437,20 @@
           <t>Class 9 (TEL)</t>
         </is>
       </c>
-      <c r="C35" s="7" t="inlineStr">
+      <c r="C35" s="7" t="inlineStr"/>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (TEL)</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (TEL)</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
         <is>
           <t>Class 7 (TEL)</t>
-        </is>
-      </c>
-      <c r="D35" s="7" t="inlineStr"/>
-      <c r="E35" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (TEL)</t>
-        </is>
-      </c>
-      <c r="F35" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (TEL)</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr"/>
@@ -1472,24 +1472,24 @@
           <t>Class 9 (TEL)</t>
         </is>
       </c>
-      <c r="C36" s="7" t="inlineStr"/>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (TEL)</t>
+        </is>
+      </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>Class 10 (TEL)</t>
-        </is>
-      </c>
-      <c r="E36" s="7" t="inlineStr">
-        <is>
           <t>Class 8 (TEL)</t>
         </is>
       </c>
-      <c r="F36" s="7" t="inlineStr">
+      <c r="E36" s="7" t="inlineStr"/>
+      <c r="F36" s="7" t="inlineStr"/>
+      <c r="G36" s="7" t="inlineStr"/>
+      <c r="H36" s="7" t="inlineStr">
         <is>
           <t>Class 7 (TEL)</t>
         </is>
       </c>
-      <c r="G36" s="7" t="inlineStr"/>
-      <c r="H36" s="7" t="inlineStr"/>
       <c r="I36" s="8" t="inlineStr">
         <is>
           <t>Class 9</t>
@@ -1507,24 +1507,24 @@
           <t>Class 9 (TEL)</t>
         </is>
       </c>
-      <c r="C37" s="7" t="inlineStr"/>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (TEL)</t>
+        </is>
+      </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
           <t>Class 8 (TEL)</t>
         </is>
       </c>
-      <c r="E37" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (TEL)</t>
-        </is>
-      </c>
+      <c r="E37" s="7" t="inlineStr"/>
       <c r="F37" s="7" t="inlineStr"/>
-      <c r="G37" s="7" t="inlineStr">
+      <c r="G37" s="7" t="inlineStr"/>
+      <c r="H37" s="7" t="inlineStr">
         <is>
           <t>Class 7 (TEL)</t>
         </is>
       </c>
-      <c r="H37" s="7" t="inlineStr"/>
       <c r="I37" s="8" t="inlineStr">
         <is>
           <t>Class 9</t>
@@ -1601,31 +1601,31 @@
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (G.K)</t>
+          <t>Class 8 (HIN)</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (HIN)</t>
+          <t>Class 5 (HIN)</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr"/>
       <c r="E41" s="7" t="inlineStr">
         <is>
+          <t>Class 4 (HIN)</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
           <t>Class 7 (HIN)</t>
         </is>
       </c>
-      <c r="F41" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (HIN)</t>
-        </is>
-      </c>
-      <c r="G41" s="7" t="inlineStr">
+      <c r="G41" s="7" t="inlineStr"/>
+      <c r="H41" s="7" t="inlineStr">
         <is>
           <t>Class 6 (HIN)</t>
         </is>
       </c>
-      <c r="H41" s="7" t="inlineStr"/>
       <c r="I41" s="8" t="inlineStr">
         <is>
           <t>Class 8</t>
@@ -1643,24 +1643,28 @@
           <t>Class 8 (HIN)</t>
         </is>
       </c>
-      <c r="C42" s="7" t="inlineStr"/>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (HIN)</t>
+        </is>
+      </c>
       <c r="D42" s="7" t="inlineStr"/>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (HIN)</t>
+          <t>Class 7 (HIN)</t>
         </is>
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (HIN)</t>
-        </is>
-      </c>
-      <c r="G42" s="7" t="inlineStr"/>
-      <c r="H42" s="7" t="inlineStr">
-        <is>
           <t>Class 5 (HIN)</t>
         </is>
       </c>
+      <c r="G42" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (G.K)</t>
+        </is>
+      </c>
+      <c r="H42" s="7" t="inlineStr"/>
       <c r="I42" s="8" t="inlineStr">
         <is>
           <t>Class 8</t>
@@ -1680,7 +1684,7 @@
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (HIN)</t>
+          <t>Class 4 (HIN)</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr"/>
@@ -1692,12 +1696,12 @@
       <c r="F43" s="7" t="inlineStr"/>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (G.K)</t>
+          <t>Class 6 (HIN)</t>
         </is>
       </c>
       <c r="H43" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (HIN)</t>
+          <t>Class 7 (HIN)</t>
         </is>
       </c>
       <c r="I43" s="8" t="inlineStr">
@@ -1717,21 +1721,17 @@
           <t>Class 8 (HIN)</t>
         </is>
       </c>
-      <c r="C44" s="7" t="inlineStr"/>
+      <c r="C44" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (HIN)</t>
+        </is>
+      </c>
       <c r="D44" s="7" t="inlineStr"/>
-      <c r="E44" s="7" t="inlineStr">
+      <c r="E44" s="7" t="inlineStr"/>
+      <c r="F44" s="7" t="inlineStr"/>
+      <c r="G44" s="7" t="inlineStr">
         <is>
           <t>Class 4 (HIN)</t>
-        </is>
-      </c>
-      <c r="F44" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (HIN)</t>
-        </is>
-      </c>
-      <c r="G44" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (HIN)</t>
         </is>
       </c>
       <c r="H44" s="7" t="inlineStr"/>
@@ -1755,21 +1755,21 @@
       <c r="C45" s="7" t="inlineStr"/>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (HIN)</t>
+          <t>Class 6 (HIN)</t>
         </is>
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (HIN)</t>
-        </is>
-      </c>
-      <c r="F45" s="7" t="inlineStr">
-        <is>
           <t>Class 5 (HIN)</t>
         </is>
       </c>
+      <c r="F45" s="7" t="inlineStr"/>
       <c r="G45" s="7" t="inlineStr"/>
-      <c r="H45" s="7" t="inlineStr"/>
+      <c r="H45" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (HIN)</t>
+        </is>
+      </c>
       <c r="I45" s="8" t="inlineStr">
         <is>
           <t>Class 8</t>
@@ -1784,29 +1784,29 @@
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (HIN)</t>
+          <t>Class 8 (G.K)</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr"/>
       <c r="D46" s="7" t="inlineStr">
         <is>
+          <t>Class 7 (HIN)</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
           <t>Class 6 (HIN)</t>
         </is>
       </c>
-      <c r="E46" s="7" t="inlineStr">
+      <c r="F46" s="7" t="inlineStr">
         <is>
           <t>Class 4 (HIN)</t>
-        </is>
-      </c>
-      <c r="F46" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (HIN)</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr"/>
       <c r="H46" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (HIN)</t>
+          <t>Class 5 (HIN)</t>
         </is>
       </c>
       <c r="I46" s="8" t="inlineStr">
@@ -1883,13 +1883,21 @@
           <t>MON</t>
         </is>
       </c>
-      <c r="B50" s="7" t="inlineStr"/>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (MATH)</t>
+        </is>
+      </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>Class 10 (MATH)</t>
-        </is>
-      </c>
-      <c r="D50" s="7" t="inlineStr"/>
+          <t>Class 9 (MATH)</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (MATH)</t>
+        </is>
+      </c>
       <c r="E50" s="7" t="inlineStr"/>
       <c r="F50" s="7" t="inlineStr"/>
       <c r="G50" s="7" t="inlineStr"/>
@@ -1907,11 +1915,7 @@
           <t>Class 10 (MATH)</t>
         </is>
       </c>
-      <c r="C51" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (MATH)</t>
-        </is>
-      </c>
+      <c r="C51" s="7" t="inlineStr"/>
       <c r="D51" s="7" t="inlineStr">
         <is>
           <t>Class 9 (MATH)</t>
@@ -1929,19 +1933,15 @@
           <t>WED</t>
         </is>
       </c>
-      <c r="B52" s="7" t="inlineStr">
+      <c r="B52" s="7" t="inlineStr"/>
+      <c r="C52" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (MATH)</t>
+        </is>
+      </c>
+      <c r="D52" s="7" t="inlineStr">
         <is>
           <t>Class 10 (MATH)</t>
-        </is>
-      </c>
-      <c r="C52" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (MATH)</t>
-        </is>
-      </c>
-      <c r="D52" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (MATH)</t>
         </is>
       </c>
       <c r="E52" s="7" t="inlineStr"/>
@@ -1962,7 +1962,11 @@
           <t>Class 10 (MATH)</t>
         </is>
       </c>
-      <c r="D53" s="7" t="inlineStr"/>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (MATH)</t>
+        </is>
+      </c>
       <c r="E53" s="7" t="inlineStr"/>
       <c r="F53" s="7" t="inlineStr"/>
       <c r="G53" s="7" t="inlineStr"/>
@@ -2002,17 +2006,13 @@
           <t>SAT</t>
         </is>
       </c>
-      <c r="B55" s="7" t="inlineStr"/>
-      <c r="C55" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (MATH)</t>
-        </is>
-      </c>
-      <c r="D55" s="7" t="inlineStr">
+      <c r="B55" s="7" t="inlineStr">
         <is>
           <t>Class 10 (MATH)</t>
         </is>
       </c>
+      <c r="C55" s="7" t="inlineStr"/>
+      <c r="D55" s="7" t="inlineStr"/>
       <c r="E55" s="7" t="inlineStr"/>
       <c r="F55" s="7" t="inlineStr"/>
       <c r="G55" s="7" t="inlineStr"/>
@@ -2088,34 +2088,22 @@
         </is>
       </c>
       <c r="B59" s="7" t="inlineStr"/>
-      <c r="C59" s="7" t="inlineStr">
+      <c r="C59" s="7" t="inlineStr"/>
+      <c r="D59" s="7" t="inlineStr"/>
+      <c r="E59" s="7" t="inlineStr"/>
+      <c r="F59" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (EVS)</t>
+        </is>
+      </c>
+      <c r="G59" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (EVS)</t>
+        </is>
+      </c>
+      <c r="H59" s="7" t="inlineStr">
         <is>
           <t>Class 5 (EVS)</t>
-        </is>
-      </c>
-      <c r="D59" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (EVS)</t>
-        </is>
-      </c>
-      <c r="E59" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (PHY)</t>
-        </is>
-      </c>
-      <c r="F59" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (BIO)</t>
-        </is>
-      </c>
-      <c r="G59" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (EVS)</t>
-        </is>
-      </c>
-      <c r="H59" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (BIO)</t>
         </is>
       </c>
       <c r="I59" s="7" t="inlineStr"/>
@@ -2129,12 +2117,12 @@
       <c r="B60" s="7" t="inlineStr"/>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (CHEM)</t>
+          <t>Class 7 (CHEM)</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (PHY)</t>
+          <t>Class 4 (EVS)</t>
         </is>
       </c>
       <c r="E60" s="7" t="inlineStr">
@@ -2144,13 +2132,17 @@
       </c>
       <c r="F60" s="7" t="inlineStr">
         <is>
+          <t>Class 7 (BIO)</t>
+        </is>
+      </c>
+      <c r="G60" s="7" t="inlineStr">
+        <is>
           <t>Class 3 (EVS)</t>
         </is>
       </c>
-      <c r="G60" s="7" t="inlineStr"/>
       <c r="H60" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (EVS)</t>
+          <t>Class 6 (BIO)</t>
         </is>
       </c>
       <c r="I60" s="7" t="inlineStr"/>
@@ -2164,28 +2156,32 @@
       <c r="B61" s="7" t="inlineStr"/>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (BIO)</t>
+          <t>Class 5 (EVS)</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
+          <t>Class 4 (EVS)</t>
+        </is>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (CHEM)</t>
+        </is>
+      </c>
+      <c r="F61" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (PHY)</t>
+        </is>
+      </c>
+      <c r="G61" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (BIO)</t>
+        </is>
+      </c>
+      <c r="H61" s="7" t="inlineStr">
+        <is>
           <t>Class 3 (EVS)</t>
-        </is>
-      </c>
-      <c r="E61" s="7" t="inlineStr"/>
-      <c r="F61" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (EVS)</t>
-        </is>
-      </c>
-      <c r="G61" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (EVS)</t>
-        </is>
-      </c>
-      <c r="H61" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (BIO)</t>
         </is>
       </c>
       <c r="I61" s="7" t="inlineStr"/>
@@ -2199,30 +2195,30 @@
       <c r="B62" s="7" t="inlineStr"/>
       <c r="C62" s="7" t="inlineStr">
         <is>
+          <t>Class 6 (BIO)</t>
+        </is>
+      </c>
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (EVS)</t>
+        </is>
+      </c>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (EVS)</t>
+        </is>
+      </c>
+      <c r="F62" s="7" t="inlineStr">
+        <is>
           <t>Class 4 (EVS)</t>
         </is>
       </c>
-      <c r="D62" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (EVS)</t>
-        </is>
-      </c>
-      <c r="E62" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (BIO)</t>
-        </is>
-      </c>
-      <c r="F62" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (PHY)</t>
-        </is>
-      </c>
-      <c r="G62" s="7" t="inlineStr"/>
-      <c r="H62" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (EVS)</t>
-        </is>
-      </c>
+      <c r="G62" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (CHEM)</t>
+        </is>
+      </c>
+      <c r="H62" s="7" t="inlineStr"/>
       <c r="I62" s="7" t="inlineStr"/>
     </row>
     <row r="63">
@@ -2234,28 +2230,32 @@
       <c r="B63" s="7" t="inlineStr"/>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (PHY)</t>
+          <t>Class 4 (EVS)</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
+          <t>Class 7 (PHY)</t>
+        </is>
+      </c>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
           <t>Class 3 (EVS)</t>
         </is>
       </c>
-      <c r="E63" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (EVS)</t>
-        </is>
-      </c>
-      <c r="F63" s="7" t="inlineStr"/>
+      <c r="F63" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (EVS)</t>
+        </is>
+      </c>
       <c r="G63" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (CHEM)</t>
+          <t>Class 6 (BIO)</t>
         </is>
       </c>
       <c r="H63" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (EVS)</t>
+          <t>Class 6 (CHEM)</t>
         </is>
       </c>
       <c r="I63" s="7" t="inlineStr"/>
@@ -2269,22 +2269,22 @@
       <c r="B64" s="7" t="inlineStr"/>
       <c r="C64" s="7" t="inlineStr">
         <is>
+          <t>Class 7 (BIO)</t>
+        </is>
+      </c>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (EVS)</t>
+        </is>
+      </c>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
           <t>Class 3 (EVS)</t>
         </is>
       </c>
-      <c r="D64" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (BIO)</t>
-        </is>
-      </c>
-      <c r="E64" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (EVS)</t>
-        </is>
-      </c>
       <c r="F64" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (CHEM)</t>
+          <t>Class 7 (PHY)</t>
         </is>
       </c>
       <c r="G64" s="7" t="inlineStr">
@@ -2294,7 +2294,7 @@
       </c>
       <c r="H64" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (CHEM)</t>
+          <t>Class 6 (PHY)</t>
         </is>
       </c>
       <c r="I64" s="7" t="inlineStr"/>
@@ -2369,12 +2369,12 @@
       </c>
       <c r="B68" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (GRAM)</t>
+          <t>Class 5 (ENG)</t>
         </is>
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>Class 1 (ENG)</t>
+          <t>Class 2 (ENG)</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
@@ -2385,17 +2385,17 @@
       <c r="E68" s="7" t="inlineStr"/>
       <c r="F68" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (ENG)</t>
+          <t>Class 1 (ENG)</t>
         </is>
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
+          <t>Class 5 (GRAM)</t>
+        </is>
+      </c>
+      <c r="H68" s="7" t="inlineStr">
+        <is>
           <t>Class 3 (ENG)</t>
-        </is>
-      </c>
-      <c r="H68" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (ENG)</t>
         </is>
       </c>
       <c r="I68" s="7" t="inlineStr"/>
@@ -2413,28 +2413,28 @@
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
+          <t>Class 4 (GRAM)</t>
+        </is>
+      </c>
+      <c r="D69" s="7" t="inlineStr">
+        <is>
+          <t>Class 1 (ENG)</t>
+        </is>
+      </c>
+      <c r="E69" s="7" t="inlineStr"/>
+      <c r="F69" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (ENG)</t>
+        </is>
+      </c>
+      <c r="G69" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (ENG)</t>
+        </is>
+      </c>
+      <c r="H69" s="7" t="inlineStr">
+        <is>
           <t>Class 3 (ENG)</t>
-        </is>
-      </c>
-      <c r="D69" s="7" t="inlineStr"/>
-      <c r="E69" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (ENG)</t>
-        </is>
-      </c>
-      <c r="F69" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (ENG)</t>
-        </is>
-      </c>
-      <c r="G69" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (ENG)</t>
-        </is>
-      </c>
-      <c r="H69" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (GRAM)</t>
         </is>
       </c>
       <c r="I69" s="7" t="inlineStr"/>
@@ -2452,28 +2452,24 @@
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>Class 3 (ENG)</t>
+          <t>Class 1 (ENG)</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr"/>
       <c r="E70" s="7" t="inlineStr">
         <is>
-          <t>Class 1 (GRAM)</t>
+          <t>Class 2 (ENG)</t>
         </is>
       </c>
       <c r="F70" s="7" t="inlineStr">
         <is>
-          <t>Class 1 (ENG)</t>
-        </is>
-      </c>
-      <c r="G70" s="7" t="inlineStr">
+          <t>Class 3 (ENG)</t>
+        </is>
+      </c>
+      <c r="G70" s="7" t="inlineStr"/>
+      <c r="H70" s="7" t="inlineStr">
         <is>
           <t>Class 4 (ENG)</t>
-        </is>
-      </c>
-      <c r="H70" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (ENG)</t>
         </is>
       </c>
       <c r="I70" s="7" t="inlineStr"/>
@@ -2489,30 +2485,30 @@
           <t>Class 5 (ENG)</t>
         </is>
       </c>
-      <c r="C71" s="7" t="inlineStr">
+      <c r="C71" s="7" t="inlineStr"/>
+      <c r="D71" s="7" t="inlineStr">
         <is>
           <t>Class 1 (ENG)</t>
         </is>
       </c>
-      <c r="D71" s="7" t="inlineStr">
+      <c r="E71" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (ENG)</t>
+        </is>
+      </c>
+      <c r="F71" s="7" t="inlineStr">
         <is>
           <t>Class 2 (GRAM)</t>
         </is>
       </c>
-      <c r="E71" s="7" t="inlineStr"/>
-      <c r="F71" s="7" t="inlineStr">
+      <c r="G71" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (ENG)</t>
+        </is>
+      </c>
+      <c r="H71" s="7" t="inlineStr">
         <is>
           <t>Class 3 (ENG)</t>
-        </is>
-      </c>
-      <c r="G71" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (ENG)</t>
-        </is>
-      </c>
-      <c r="H71" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (ENG)</t>
         </is>
       </c>
       <c r="I71" s="7" t="inlineStr"/>
@@ -2531,27 +2527,27 @@
       <c r="C72" s="7" t="inlineStr"/>
       <c r="D72" s="7" t="inlineStr">
         <is>
+          <t>Class 3 (ENG)</t>
+        </is>
+      </c>
+      <c r="E72" s="7" t="inlineStr">
+        <is>
           <t>Class 1 (ENG)</t>
         </is>
       </c>
-      <c r="E72" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (ENG)</t>
-        </is>
-      </c>
       <c r="F72" s="7" t="inlineStr">
         <is>
+          <t>Class 4 (ENG)</t>
+        </is>
+      </c>
+      <c r="G72" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (GRAM)</t>
+        </is>
+      </c>
+      <c r="H72" s="7" t="inlineStr">
+        <is>
           <t>Class 2 (ENG)</t>
-        </is>
-      </c>
-      <c r="G72" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (GRAM)</t>
-        </is>
-      </c>
-      <c r="H72" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (ENG)</t>
         </is>
       </c>
       <c r="I72" s="7" t="inlineStr"/>
@@ -2569,26 +2565,30 @@
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (ENG)</t>
+          <t>Class 1 (GRAM)</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr"/>
       <c r="E73" s="7" t="inlineStr">
         <is>
+          <t>Class 4 (ENG)</t>
+        </is>
+      </c>
+      <c r="F73" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (ENG)</t>
+        </is>
+      </c>
+      <c r="G73" s="7" t="inlineStr">
+        <is>
           <t>Class 1 (ENG)</t>
         </is>
       </c>
-      <c r="F73" s="7" t="inlineStr">
+      <c r="H73" s="7" t="inlineStr">
         <is>
           <t>Class 2 (ENG)</t>
         </is>
       </c>
-      <c r="G73" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (ENG)</t>
-        </is>
-      </c>
-      <c r="H73" s="7" t="inlineStr"/>
       <c r="I73" s="7" t="inlineStr"/>
     </row>
     <row r="75">
@@ -2660,12 +2660,12 @@
         </is>
       </c>
       <c r="B77" s="7" t="inlineStr"/>
-      <c r="C77" s="7" t="inlineStr"/>
-      <c r="D77" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (COMP)</t>
-        </is>
-      </c>
+      <c r="C77" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (COMP)</t>
+        </is>
+      </c>
+      <c r="D77" s="7" t="inlineStr"/>
       <c r="E77" s="7" t="inlineStr"/>
       <c r="F77" s="7" t="inlineStr"/>
       <c r="G77" s="7" t="inlineStr"/>
@@ -2682,16 +2682,16 @@
       <c r="C78" s="7" t="inlineStr"/>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (COMP)</t>
-        </is>
-      </c>
-      <c r="E78" s="7" t="inlineStr"/>
+          <t>Class 5 (COMP)</t>
+        </is>
+      </c>
+      <c r="E78" s="7" t="inlineStr">
+        <is>
+          <t>Class 1 (COMP)</t>
+        </is>
+      </c>
       <c r="F78" s="7" t="inlineStr"/>
-      <c r="G78" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (COMP)</t>
-        </is>
-      </c>
+      <c r="G78" s="7" t="inlineStr"/>
       <c r="H78" s="7" t="inlineStr"/>
       <c r="I78" s="7" t="inlineStr"/>
     </row>
@@ -2702,32 +2702,16 @@
         </is>
       </c>
       <c r="B79" s="7" t="inlineStr"/>
-      <c r="C79" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (COMP)</t>
-        </is>
-      </c>
+      <c r="C79" s="7" t="inlineStr"/>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (COMP)</t>
-        </is>
-      </c>
-      <c r="E79" s="7" t="inlineStr">
-        <is>
           <t>Class 2 (COMP)</t>
         </is>
       </c>
+      <c r="E79" s="7" t="inlineStr"/>
       <c r="F79" s="7" t="inlineStr"/>
-      <c r="G79" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (COMP)</t>
-        </is>
-      </c>
-      <c r="H79" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (COMP)</t>
-        </is>
-      </c>
+      <c r="G79" s="7" t="inlineStr"/>
+      <c r="H79" s="7" t="inlineStr"/>
       <c r="I79" s="7" t="inlineStr"/>
     </row>
     <row r="80">
@@ -2739,7 +2723,11 @@
       <c r="B80" s="7" t="inlineStr"/>
       <c r="C80" s="7" t="inlineStr"/>
       <c r="D80" s="7" t="inlineStr"/>
-      <c r="E80" s="7" t="inlineStr"/>
+      <c r="E80" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (COMP)</t>
+        </is>
+      </c>
       <c r="F80" s="7" t="inlineStr"/>
       <c r="G80" s="7" t="inlineStr"/>
       <c r="H80" s="7" t="inlineStr"/>
@@ -2754,14 +2742,22 @@
       <c r="B81" s="7" t="inlineStr"/>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>Class 1 (COMP)</t>
+          <t>Class 2 (COMP)</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr"/>
       <c r="E81" s="7" t="inlineStr"/>
       <c r="F81" s="7" t="inlineStr"/>
-      <c r="G81" s="7" t="inlineStr"/>
-      <c r="H81" s="7" t="inlineStr"/>
+      <c r="G81" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (COMP)</t>
+        </is>
+      </c>
+      <c r="H81" s="7" t="inlineStr">
+        <is>
+          <t>Class 1 (COMP)</t>
+        </is>
+      </c>
       <c r="I81" s="7" t="inlineStr"/>
     </row>
     <row r="82">
@@ -2775,10 +2771,14 @@
       <c r="D82" s="7" t="inlineStr"/>
       <c r="E82" s="7" t="inlineStr">
         <is>
+          <t>Class 1 (COMP)</t>
+        </is>
+      </c>
+      <c r="F82" s="7" t="inlineStr">
+        <is>
           <t>Class 2 (COMP)</t>
         </is>
       </c>
-      <c r="F82" s="7" t="inlineStr"/>
       <c r="G82" s="7" t="inlineStr"/>
       <c r="H82" s="7" t="inlineStr"/>
       <c r="I82" s="7" t="inlineStr"/>
@@ -2856,24 +2856,28 @@
           <t>Class 1 (TEL)</t>
         </is>
       </c>
-      <c r="C86" s="7" t="inlineStr"/>
-      <c r="D86" s="7" t="inlineStr">
+      <c r="C86" s="7" t="inlineStr">
+        <is>
+          <t>Class 1 (G.K)</t>
+        </is>
+      </c>
+      <c r="D86" s="7" t="inlineStr"/>
+      <c r="E86" s="7" t="inlineStr">
+        <is>
+          <t>L.K.G (TEL)</t>
+        </is>
+      </c>
+      <c r="F86" s="7" t="inlineStr">
         <is>
           <t>Class 2 (TEL)</t>
         </is>
       </c>
-      <c r="E86" s="7" t="inlineStr">
+      <c r="G86" s="7" t="inlineStr"/>
+      <c r="H86" s="7" t="inlineStr">
         <is>
           <t>U.K.G (TEL)</t>
         </is>
       </c>
-      <c r="F86" s="7" t="inlineStr"/>
-      <c r="G86" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (G.K)</t>
-        </is>
-      </c>
-      <c r="H86" s="7" t="inlineStr"/>
       <c r="I86" s="8" t="inlineStr">
         <is>
           <t>Class 1</t>
@@ -2893,26 +2897,22 @@
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
+          <t>Class 2 (TEL)</t>
+        </is>
+      </c>
+      <c r="D87" s="7" t="inlineStr">
+        <is>
+          <t>L.K.G (TEL)</t>
+        </is>
+      </c>
+      <c r="E87" s="7" t="inlineStr"/>
+      <c r="F87" s="7" t="inlineStr"/>
+      <c r="G87" s="7" t="inlineStr"/>
+      <c r="H87" s="7" t="inlineStr">
+        <is>
           <t>U.K.G (TEL)</t>
         </is>
       </c>
-      <c r="D87" s="7" t="inlineStr"/>
-      <c r="E87" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (TEL)</t>
-        </is>
-      </c>
-      <c r="F87" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (G.K)</t>
-        </is>
-      </c>
-      <c r="G87" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (TEL)</t>
-        </is>
-      </c>
-      <c r="H87" s="7" t="inlineStr"/>
       <c r="I87" s="8" t="inlineStr">
         <is>
           <t>Class 1</t>
@@ -2932,20 +2932,20 @@
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (TEL)</t>
+          <t>L.K.G (TEL)</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr"/>
-      <c r="E88" s="7" t="inlineStr"/>
-      <c r="F88" s="7" t="inlineStr">
+      <c r="E88" s="7" t="inlineStr">
         <is>
           <t>U.K.G (TEL)</t>
         </is>
       </c>
+      <c r="F88" s="7" t="inlineStr"/>
       <c r="G88" s="7" t="inlineStr"/>
       <c r="H88" s="7" t="inlineStr">
         <is>
-          <t>L.K.G (TEL)</t>
+          <t>Class 2 (TEL)</t>
         </is>
       </c>
       <c r="I88" s="8" t="inlineStr">
@@ -2965,23 +2965,23 @@
           <t>Class 1 (TEL)</t>
         </is>
       </c>
-      <c r="C89" s="7" t="inlineStr"/>
-      <c r="D89" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (TEL)</t>
-        </is>
-      </c>
+      <c r="C89" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (TEL)</t>
+        </is>
+      </c>
+      <c r="D89" s="7" t="inlineStr"/>
       <c r="E89" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (TEL)</t>
-        </is>
-      </c>
-      <c r="F89" s="7" t="inlineStr">
+          <t>Class 1 (G.K)</t>
+        </is>
+      </c>
+      <c r="F89" s="7" t="inlineStr"/>
+      <c r="G89" s="7" t="inlineStr">
         <is>
           <t>U.K.G (TEL)</t>
         </is>
       </c>
-      <c r="G89" s="7" t="inlineStr"/>
       <c r="H89" s="7" t="inlineStr"/>
       <c r="I89" s="8" t="inlineStr">
         <is>
@@ -3003,17 +3003,17 @@
       <c r="C90" s="7" t="inlineStr"/>
       <c r="D90" s="7" t="inlineStr">
         <is>
+          <t>Class 2 (TEL)</t>
+        </is>
+      </c>
+      <c r="E90" s="7" t="inlineStr">
+        <is>
+          <t>U.K.G (TEL)</t>
+        </is>
+      </c>
+      <c r="F90" s="7" t="inlineStr">
+        <is>
           <t>L.K.G (TEL)</t>
-        </is>
-      </c>
-      <c r="E90" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (TEL)</t>
-        </is>
-      </c>
-      <c r="F90" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (TEL)</t>
         </is>
       </c>
       <c r="G90" s="7" t="inlineStr"/>
@@ -3035,21 +3035,21 @@
           <t>Class 1 (TEL)</t>
         </is>
       </c>
-      <c r="C91" s="7" t="inlineStr">
+      <c r="C91" s="7" t="inlineStr"/>
+      <c r="D91" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (TEL)</t>
+        </is>
+      </c>
+      <c r="E91" s="7" t="inlineStr"/>
+      <c r="F91" s="7" t="inlineStr">
+        <is>
+          <t>L.K.G (TEL)</t>
+        </is>
+      </c>
+      <c r="G91" s="7" t="inlineStr">
         <is>
           <t>U.K.G (TEL)</t>
-        </is>
-      </c>
-      <c r="D91" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (TEL)</t>
-        </is>
-      </c>
-      <c r="E91" s="7" t="inlineStr"/>
-      <c r="F91" s="7" t="inlineStr"/>
-      <c r="G91" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (TEL)</t>
         </is>
       </c>
       <c r="H91" s="7" t="inlineStr"/>
@@ -3132,26 +3132,26 @@
           <t>Class 7 (SOC)</t>
         </is>
       </c>
-      <c r="C95" s="7" t="inlineStr"/>
+      <c r="C95" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (SOC)</t>
+        </is>
+      </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
+          <t>Class 5 (SOC)</t>
+        </is>
+      </c>
+      <c r="E95" s="7" t="inlineStr"/>
+      <c r="F95" s="7" t="inlineStr">
+        <is>
           <t>Class 6 (SOC)</t>
-        </is>
-      </c>
-      <c r="E95" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (SOC)</t>
-        </is>
-      </c>
-      <c r="F95" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (SOC)</t>
         </is>
       </c>
       <c r="G95" s="7" t="inlineStr"/>
       <c r="H95" s="7" t="inlineStr">
         <is>
-          <t>Class 3 (SOC)</t>
+          <t>Class 4 (SOC)</t>
         </is>
       </c>
       <c r="I95" s="8" t="inlineStr">
@@ -3171,26 +3171,26 @@
           <t>Class 7 (SOC)</t>
         </is>
       </c>
-      <c r="C96" s="7" t="inlineStr">
+      <c r="C96" s="7" t="inlineStr"/>
+      <c r="D96" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (SOC)</t>
+        </is>
+      </c>
+      <c r="E96" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (SOC)</t>
+        </is>
+      </c>
+      <c r="F96" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (SOC)</t>
+        </is>
+      </c>
+      <c r="G96" s="7" t="inlineStr"/>
+      <c r="H96" s="7" t="inlineStr">
         <is>
           <t>Class 5 (SOC)</t>
-        </is>
-      </c>
-      <c r="D96" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (SOC)</t>
-        </is>
-      </c>
-      <c r="E96" s="7" t="inlineStr"/>
-      <c r="F96" s="7" t="inlineStr"/>
-      <c r="G96" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (SOC)</t>
-        </is>
-      </c>
-      <c r="H96" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (SOC)</t>
         </is>
       </c>
       <c r="I96" s="8" t="inlineStr">
@@ -3212,23 +3212,23 @@
       </c>
       <c r="C97" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (SOC)</t>
+          <t>Class 6 (SOC)</t>
         </is>
       </c>
       <c r="D97" s="7" t="inlineStr"/>
       <c r="E97" s="7" t="inlineStr">
         <is>
+          <t>Class 3 (SOC)</t>
+        </is>
+      </c>
+      <c r="F97" s="7" t="inlineStr">
+        <is>
           <t>Class 4 (SOC)</t>
         </is>
       </c>
-      <c r="F97" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (SOC)</t>
-        </is>
-      </c>
       <c r="G97" s="7" t="inlineStr">
         <is>
-          <t>Class 3 (SOC)</t>
+          <t>Class 5 (SOC)</t>
         </is>
       </c>
       <c r="H97" s="7" t="inlineStr"/>
@@ -3251,26 +3251,26 @@
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
+          <t>Class 4 (SOC)</t>
+        </is>
+      </c>
+      <c r="D98" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (SOC)</t>
+        </is>
+      </c>
+      <c r="E98" s="7" t="inlineStr"/>
+      <c r="F98" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (SOC)</t>
+        </is>
+      </c>
+      <c r="G98" s="7" t="inlineStr">
+        <is>
           <t>Class 3 (SOC)</t>
         </is>
       </c>
-      <c r="D98" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (SOC)</t>
-        </is>
-      </c>
-      <c r="E98" s="7" t="inlineStr"/>
-      <c r="F98" s="7" t="inlineStr"/>
-      <c r="G98" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (SOC)</t>
-        </is>
-      </c>
-      <c r="H98" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (SOC)</t>
-        </is>
-      </c>
+      <c r="H98" s="7" t="inlineStr"/>
       <c r="I98" s="8" t="inlineStr">
         <is>
           <t>Class 7</t>
@@ -3290,26 +3290,26 @@
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
+          <t>Class 6 (SOC)</t>
+        </is>
+      </c>
+      <c r="D99" s="7" t="inlineStr"/>
+      <c r="E99" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (SOC)</t>
+        </is>
+      </c>
+      <c r="F99" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (SOC)</t>
+        </is>
+      </c>
+      <c r="G99" s="7" t="inlineStr">
+        <is>
           <t>Class 5 (SOC)</t>
         </is>
       </c>
-      <c r="D99" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (SOC)</t>
-        </is>
-      </c>
-      <c r="E99" s="7" t="inlineStr"/>
-      <c r="F99" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (SOC)</t>
-        </is>
-      </c>
-      <c r="G99" s="7" t="inlineStr"/>
-      <c r="H99" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (SOC)</t>
-        </is>
-      </c>
+      <c r="H99" s="7" t="inlineStr"/>
       <c r="I99" s="8" t="inlineStr">
         <is>
           <t>Class 7</t>
@@ -3327,26 +3327,26 @@
           <t>Class 7 (SOC)</t>
         </is>
       </c>
-      <c r="C100" s="7" t="inlineStr"/>
+      <c r="C100" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (SOC)</t>
+        </is>
+      </c>
       <c r="D100" s="7" t="inlineStr">
         <is>
           <t>Class 4 (SOC)</t>
         </is>
       </c>
-      <c r="E100" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (SOC)</t>
-        </is>
-      </c>
-      <c r="F100" s="7" t="inlineStr">
+      <c r="E100" s="7" t="inlineStr"/>
+      <c r="F100" s="7" t="inlineStr"/>
+      <c r="G100" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (SOC)</t>
+        </is>
+      </c>
+      <c r="H100" s="7" t="inlineStr">
         <is>
           <t>Class 3 (SOC)</t>
-        </is>
-      </c>
-      <c r="G100" s="7" t="inlineStr"/>
-      <c r="H100" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (SOC)</t>
         </is>
       </c>
       <c r="I100" s="8" t="inlineStr">
@@ -3424,25 +3424,21 @@
         </is>
       </c>
       <c r="B104" s="7" t="inlineStr"/>
-      <c r="C104" s="7" t="inlineStr">
+      <c r="C104" s="7" t="inlineStr"/>
+      <c r="D104" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (GRAM)</t>
+        </is>
+      </c>
+      <c r="E104" s="7" t="inlineStr">
         <is>
           <t>Class 6 (ENG)</t>
-        </is>
-      </c>
-      <c r="D104" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (ENG)</t>
-        </is>
-      </c>
-      <c r="E104" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (GRAM)</t>
         </is>
       </c>
       <c r="F104" s="7" t="inlineStr"/>
       <c r="G104" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (GRAM)</t>
+          <t>Class 7 (ENG)</t>
         </is>
       </c>
       <c r="H104" s="7" t="inlineStr"/>
@@ -3460,19 +3456,23 @@
           <t>Class 10 (GRAM)</t>
         </is>
       </c>
-      <c r="D105" s="7" t="inlineStr"/>
-      <c r="E105" s="7" t="inlineStr">
+      <c r="D105" s="7" t="inlineStr">
         <is>
           <t>Class 6 (ENG)</t>
         </is>
       </c>
+      <c r="E105" s="7" t="inlineStr"/>
       <c r="F105" s="7" t="inlineStr">
         <is>
+          <t>Class 9 (GRAM)</t>
+        </is>
+      </c>
+      <c r="G105" s="7" t="inlineStr"/>
+      <c r="H105" s="7" t="inlineStr">
+        <is>
           <t>Class 7 (ENG)</t>
         </is>
       </c>
-      <c r="G105" s="7" t="inlineStr"/>
-      <c r="H105" s="7" t="inlineStr"/>
       <c r="I105" s="7" t="inlineStr"/>
     </row>
     <row r="106">
@@ -3488,14 +3488,14 @@
           <t>Class 7 (ENG)</t>
         </is>
       </c>
-      <c r="E106" s="7" t="inlineStr"/>
+      <c r="E106" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (ENG)</t>
+        </is>
+      </c>
       <c r="F106" s="7" t="inlineStr"/>
       <c r="G106" s="7" t="inlineStr"/>
-      <c r="H106" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (ENG)</t>
-        </is>
-      </c>
+      <c r="H106" s="7" t="inlineStr"/>
       <c r="I106" s="7" t="inlineStr"/>
     </row>
     <row r="107">
@@ -3505,19 +3505,23 @@
         </is>
       </c>
       <c r="B107" s="7" t="inlineStr"/>
-      <c r="C107" s="7" t="inlineStr">
+      <c r="C107" s="7" t="inlineStr"/>
+      <c r="D107" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (ENG)</t>
+        </is>
+      </c>
+      <c r="E107" s="7" t="inlineStr">
         <is>
           <t>Class 6 (ENG)</t>
         </is>
       </c>
-      <c r="D107" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (ENG)</t>
-        </is>
-      </c>
-      <c r="E107" s="7" t="inlineStr"/>
       <c r="F107" s="7" t="inlineStr"/>
-      <c r="G107" s="7" t="inlineStr"/>
+      <c r="G107" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (GRAM)</t>
+        </is>
+      </c>
       <c r="H107" s="7" t="inlineStr"/>
       <c r="I107" s="7" t="inlineStr"/>
     </row>
@@ -3528,24 +3532,24 @@
         </is>
       </c>
       <c r="B108" s="7" t="inlineStr"/>
-      <c r="C108" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (GRAM)</t>
-        </is>
-      </c>
-      <c r="D108" s="7" t="inlineStr">
+      <c r="C108" s="7" t="inlineStr"/>
+      <c r="D108" s="7" t="inlineStr"/>
+      <c r="E108" s="7" t="inlineStr">
         <is>
           <t>Class 6 (ENG)</t>
         </is>
       </c>
-      <c r="E108" s="7" t="inlineStr"/>
-      <c r="F108" s="7" t="inlineStr"/>
-      <c r="G108" s="7" t="inlineStr"/>
-      <c r="H108" s="7" t="inlineStr">
+      <c r="F108" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (GRAM)</t>
+        </is>
+      </c>
+      <c r="G108" s="7" t="inlineStr">
         <is>
           <t>Class 7 (ENG)</t>
         </is>
       </c>
+      <c r="H108" s="7" t="inlineStr"/>
       <c r="I108" s="7" t="inlineStr"/>
     </row>
     <row r="109">
@@ -3555,11 +3559,7 @@
         </is>
       </c>
       <c r="B109" s="7" t="inlineStr"/>
-      <c r="C109" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (ENG)</t>
-        </is>
-      </c>
+      <c r="C109" s="7" t="inlineStr"/>
       <c r="D109" s="7" t="inlineStr"/>
       <c r="E109" s="7" t="inlineStr">
         <is>
@@ -3568,7 +3568,7 @@
       </c>
       <c r="F109" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (GRAM)</t>
+          <t>Class 6 (ENG)</t>
         </is>
       </c>
       <c r="G109" s="7" t="inlineStr"/>
@@ -3644,19 +3644,23 @@
         </is>
       </c>
       <c r="B113" s="7" t="inlineStr"/>
-      <c r="C113" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (HIN)</t>
-        </is>
-      </c>
+      <c r="C113" s="7" t="inlineStr"/>
       <c r="D113" s="7" t="inlineStr"/>
       <c r="E113" s="7" t="inlineStr">
         <is>
+          <t>Class 3 (HIN)</t>
+        </is>
+      </c>
+      <c r="F113" s="7" t="inlineStr">
+        <is>
           <t>Class 10 (HIN)</t>
         </is>
       </c>
-      <c r="F113" s="7" t="inlineStr"/>
-      <c r="G113" s="7" t="inlineStr"/>
+      <c r="G113" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (HIN)</t>
+        </is>
+      </c>
       <c r="H113" s="7" t="inlineStr"/>
       <c r="I113" s="7" t="inlineStr"/>
     </row>
@@ -3667,19 +3671,19 @@
         </is>
       </c>
       <c r="B114" s="7" t="inlineStr"/>
-      <c r="C114" s="7" t="inlineStr"/>
+      <c r="C114" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (HIN)</t>
+        </is>
+      </c>
       <c r="D114" s="7" t="inlineStr"/>
       <c r="E114" s="7" t="inlineStr">
         <is>
-          <t>Class 3 (HIN)</t>
+          <t>Class 10 (HIN)</t>
         </is>
       </c>
       <c r="F114" s="7" t="inlineStr"/>
-      <c r="G114" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (HIN)</t>
-        </is>
-      </c>
+      <c r="G114" s="7" t="inlineStr"/>
       <c r="H114" s="7" t="inlineStr"/>
       <c r="I114" s="7" t="inlineStr"/>
     </row>
@@ -3690,23 +3694,19 @@
         </is>
       </c>
       <c r="B115" s="7" t="inlineStr"/>
-      <c r="C115" s="7" t="inlineStr"/>
+      <c r="C115" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (HIN)</t>
+        </is>
+      </c>
       <c r="D115" s="7" t="inlineStr"/>
       <c r="E115" s="7" t="inlineStr">
         <is>
-          <t>Class 3 (HIN)</t>
-        </is>
-      </c>
-      <c r="F115" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (HIN)</t>
-        </is>
-      </c>
-      <c r="G115" s="7" t="inlineStr">
-        <is>
           <t>Class 9 (HIN)</t>
         </is>
       </c>
+      <c r="F115" s="7" t="inlineStr"/>
+      <c r="G115" s="7" t="inlineStr"/>
       <c r="H115" s="7" t="inlineStr"/>
       <c r="I115" s="7" t="inlineStr"/>
     </row>
@@ -3716,24 +3716,24 @@
           <t>THU</t>
         </is>
       </c>
-      <c r="B116" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (HIN)</t>
-        </is>
-      </c>
-      <c r="C116" s="7" t="inlineStr"/>
+      <c r="B116" s="7" t="inlineStr"/>
+      <c r="C116" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (HIN)</t>
+        </is>
+      </c>
       <c r="D116" s="7" t="inlineStr"/>
       <c r="E116" s="7" t="inlineStr">
         <is>
-          <t>Class 3 (HIN)</t>
-        </is>
-      </c>
-      <c r="F116" s="7" t="inlineStr"/>
-      <c r="G116" s="7" t="inlineStr">
+          <t>Class 10 (HIN)</t>
+        </is>
+      </c>
+      <c r="F116" s="7" t="inlineStr">
         <is>
           <t>Class 9 (HIN)</t>
         </is>
       </c>
+      <c r="G116" s="7" t="inlineStr"/>
       <c r="H116" s="7" t="inlineStr"/>
       <c r="I116" s="7" t="inlineStr"/>
     </row>
@@ -3752,14 +3752,10 @@
       <c r="D117" s="7" t="inlineStr"/>
       <c r="E117" s="7" t="inlineStr">
         <is>
-          <t>Class 10 (HIN)</t>
-        </is>
-      </c>
-      <c r="F117" s="7" t="inlineStr">
-        <is>
           <t>Class 9 (HIN)</t>
         </is>
       </c>
+      <c r="F117" s="7" t="inlineStr"/>
       <c r="G117" s="7" t="inlineStr"/>
       <c r="H117" s="7" t="inlineStr"/>
       <c r="I117" s="7" t="inlineStr"/>
@@ -3770,11 +3766,7 @@
           <t>SAT</t>
         </is>
       </c>
-      <c r="B118" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (HIN)</t>
-        </is>
-      </c>
+      <c r="B118" s="7" t="inlineStr"/>
       <c r="C118" s="7" t="inlineStr"/>
       <c r="D118" s="7" t="inlineStr"/>
       <c r="E118" s="7" t="inlineStr">
@@ -3783,8 +3775,16 @@
         </is>
       </c>
       <c r="F118" s="7" t="inlineStr"/>
-      <c r="G118" s="7" t="inlineStr"/>
-      <c r="H118" s="7" t="inlineStr"/>
+      <c r="G118" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (HIN)</t>
+        </is>
+      </c>
+      <c r="H118" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (HIN)</t>
+        </is>
+      </c>
       <c r="I118" s="7" t="inlineStr"/>
     </row>
     <row r="120">
@@ -3862,13 +3862,17 @@
       </c>
       <c r="C122" s="7" t="inlineStr">
         <is>
+          <t>U.K.G (ENG)</t>
+        </is>
+      </c>
+      <c r="D122" s="7" t="inlineStr">
+        <is>
           <t>Class 2 (HIN)</t>
         </is>
       </c>
-      <c r="D122" s="7" t="inlineStr"/>
       <c r="E122" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (EVS)</t>
+          <t>Class 1 (EVS)</t>
         </is>
       </c>
       <c r="F122" s="7" t="inlineStr">
@@ -3876,14 +3880,10 @@
           <t>U.K.G (ENG)</t>
         </is>
       </c>
-      <c r="G122" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (ENG)</t>
-        </is>
-      </c>
+      <c r="G122" s="7" t="inlineStr"/>
       <c r="H122" s="7" t="inlineStr">
         <is>
-          <t>U.K.G (ENG)</t>
+          <t>Class 1 (HIN)</t>
         </is>
       </c>
       <c r="I122" s="8" t="inlineStr">
@@ -3905,25 +3905,25 @@
       </c>
       <c r="C123" s="7" t="inlineStr">
         <is>
+          <t>U.K.G (ENG)</t>
+        </is>
+      </c>
+      <c r="D123" s="7" t="inlineStr">
+        <is>
+          <t>U.K.G (ENG)</t>
+        </is>
+      </c>
+      <c r="E123" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (EVS)</t>
+        </is>
+      </c>
+      <c r="F123" s="7" t="inlineStr">
+        <is>
           <t>Class 1 (HIN)</t>
         </is>
       </c>
-      <c r="D123" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (EVS)</t>
-        </is>
-      </c>
-      <c r="E123" s="7" t="inlineStr"/>
-      <c r="F123" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (ENG)</t>
-        </is>
-      </c>
-      <c r="G123" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (ENG)</t>
-        </is>
-      </c>
+      <c r="G123" s="7" t="inlineStr"/>
       <c r="H123" s="7" t="inlineStr">
         <is>
           <t>Class 2 (HIN)</t>
@@ -3948,25 +3948,25 @@
       </c>
       <c r="C124" s="7" t="inlineStr">
         <is>
-          <t>Class 1 (EVS)</t>
+          <t>Class 2 (EVS)</t>
         </is>
       </c>
       <c r="D124" s="7" t="inlineStr">
         <is>
+          <t>Class 3 (G.K)</t>
+        </is>
+      </c>
+      <c r="E124" s="7" t="inlineStr">
+        <is>
           <t>Class 1 (HIN)</t>
         </is>
       </c>
-      <c r="E124" s="7" t="inlineStr">
+      <c r="F124" s="7" t="inlineStr">
         <is>
           <t>U.K.G (ENG)</t>
         </is>
       </c>
-      <c r="F124" s="7" t="inlineStr"/>
-      <c r="G124" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (HIN)</t>
-        </is>
-      </c>
+      <c r="G124" s="7" t="inlineStr"/>
       <c r="H124" s="7" t="inlineStr">
         <is>
           <t>Class 1 (EVS)</t>
@@ -3986,32 +3986,32 @@
       </c>
       <c r="B125" s="7" t="inlineStr">
         <is>
+          <t>Class 2 (EVS)</t>
+        </is>
+      </c>
+      <c r="C125" s="7" t="inlineStr">
+        <is>
+          <t>Class 1 (EVS)</t>
+        </is>
+      </c>
+      <c r="D125" s="7" t="inlineStr">
+        <is>
           <t>Class 2 (HIN)</t>
         </is>
       </c>
-      <c r="C125" s="7" t="inlineStr">
+      <c r="E125" s="7" t="inlineStr">
         <is>
           <t>U.K.G (ENG)</t>
         </is>
       </c>
-      <c r="D125" s="7" t="inlineStr">
+      <c r="F125" s="7" t="inlineStr">
+        <is>
+          <t>Class 1 (EVS)</t>
+        </is>
+      </c>
+      <c r="G125" s="7" t="inlineStr">
         <is>
           <t>Class 1 (HIN)</t>
-        </is>
-      </c>
-      <c r="E125" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (ENG)</t>
-        </is>
-      </c>
-      <c r="F125" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (EVS)</t>
-        </is>
-      </c>
-      <c r="G125" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (G.K)</t>
         </is>
       </c>
       <c r="H125" s="7" t="inlineStr"/>
@@ -4029,33 +4029,29 @@
       </c>
       <c r="B126" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (EVS)</t>
+          <t>Class 2 (HIN)</t>
         </is>
       </c>
       <c r="C126" s="7" t="inlineStr">
         <is>
+          <t>Class 1 (EVS)</t>
+        </is>
+      </c>
+      <c r="D126" s="7" t="inlineStr">
+        <is>
+          <t>Class 1 (EVS)</t>
+        </is>
+      </c>
+      <c r="E126" s="7" t="inlineStr"/>
+      <c r="F126" s="7" t="inlineStr"/>
+      <c r="G126" s="7" t="inlineStr">
+        <is>
+          <t>Class 1 (HIN)</t>
+        </is>
+      </c>
+      <c r="H126" s="7" t="inlineStr">
+        <is>
           <t>U.K.G (ENG)</t>
-        </is>
-      </c>
-      <c r="D126" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (ENG)</t>
-        </is>
-      </c>
-      <c r="E126" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (EVS)</t>
-        </is>
-      </c>
-      <c r="F126" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (EVS)</t>
-        </is>
-      </c>
-      <c r="G126" s="7" t="inlineStr"/>
-      <c r="H126" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (HIN)</t>
         </is>
       </c>
       <c r="I126" s="8" t="inlineStr">
@@ -4072,31 +4068,35 @@
       </c>
       <c r="B127" s="7" t="inlineStr">
         <is>
+          <t>Class 2 (EVS)</t>
+        </is>
+      </c>
+      <c r="C127" s="7" t="inlineStr">
+        <is>
+          <t>U.K.G (ENG)</t>
+        </is>
+      </c>
+      <c r="D127" s="7" t="inlineStr">
+        <is>
+          <t>Class 1 (EVS)</t>
+        </is>
+      </c>
+      <c r="E127" s="7" t="inlineStr">
+        <is>
           <t>Class 2 (HIN)</t>
         </is>
       </c>
-      <c r="C127" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (EVS)</t>
-        </is>
-      </c>
-      <c r="D127" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (EVS)</t>
-        </is>
-      </c>
-      <c r="E127" s="7" t="inlineStr"/>
       <c r="F127" s="7" t="inlineStr">
         <is>
-          <t>Class 1 (EVS)</t>
-        </is>
-      </c>
-      <c r="G127" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (HIN)</t>
-        </is>
-      </c>
-      <c r="H127" s="7" t="inlineStr"/>
+          <t>U.K.G (ENG)</t>
+        </is>
+      </c>
+      <c r="G127" s="7" t="inlineStr"/>
+      <c r="H127" s="7" t="inlineStr">
+        <is>
+          <t>U.K.G (ENG)</t>
+        </is>
+      </c>
       <c r="I127" s="8" t="inlineStr">
         <is>
           <t>Class 2</t>
@@ -4178,22 +4178,22 @@
       </c>
       <c r="C131" s="7" t="inlineStr">
         <is>
+          <t>Class 8 (MATH)</t>
+        </is>
+      </c>
+      <c r="D131" s="7" t="inlineStr"/>
+      <c r="E131" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (COMP)</t>
+        </is>
+      </c>
+      <c r="F131" s="7" t="inlineStr"/>
+      <c r="G131" s="7" t="inlineStr"/>
+      <c r="H131" s="7" t="inlineStr">
+        <is>
           <t>Class 7 (MATH)</t>
         </is>
       </c>
-      <c r="D131" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (MATH)</t>
-        </is>
-      </c>
-      <c r="E131" s="7" t="inlineStr"/>
-      <c r="F131" s="7" t="inlineStr"/>
-      <c r="G131" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (MATH)</t>
-        </is>
-      </c>
-      <c r="H131" s="7" t="inlineStr"/>
       <c r="I131" s="8" t="inlineStr">
         <is>
           <t>Class 6</t>
@@ -4219,16 +4219,16 @@
       </c>
       <c r="E132" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (COMP)</t>
+          <t>Class 6 (G.K)</t>
         </is>
       </c>
       <c r="F132" s="7" t="inlineStr"/>
-      <c r="G132" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (MATH)</t>
-        </is>
-      </c>
-      <c r="H132" s="7" t="inlineStr"/>
+      <c r="G132" s="7" t="inlineStr"/>
+      <c r="H132" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (MATH)</t>
+        </is>
+      </c>
       <c r="I132" s="8" t="inlineStr">
         <is>
           <t>Class 6</t>
@@ -4246,28 +4246,24 @@
           <t>Class 6 (MATH)</t>
         </is>
       </c>
-      <c r="C133" s="7" t="inlineStr"/>
-      <c r="D133" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (G.K)</t>
-        </is>
-      </c>
+      <c r="C133" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (MATH)</t>
+        </is>
+      </c>
+      <c r="D133" s="7" t="inlineStr"/>
       <c r="E133" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (MATH)</t>
-        </is>
-      </c>
-      <c r="F133" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (COMP)</t>
-        </is>
-      </c>
-      <c r="G133" s="7" t="inlineStr"/>
-      <c r="H133" s="7" t="inlineStr">
-        <is>
           <t>Class 8 (MATH)</t>
         </is>
       </c>
+      <c r="F133" s="7" t="inlineStr"/>
+      <c r="G133" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (MATH)</t>
+        </is>
+      </c>
+      <c r="H133" s="7" t="inlineStr"/>
       <c r="I133" s="8" t="inlineStr">
         <is>
           <t>Class 6</t>
@@ -4288,7 +4284,7 @@
       <c r="C134" s="7" t="inlineStr"/>
       <c r="D134" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (MATH)</t>
+          <t>Class 8 (COMP)</t>
         </is>
       </c>
       <c r="E134" s="7" t="inlineStr">
@@ -4297,7 +4293,11 @@
         </is>
       </c>
       <c r="F134" s="7" t="inlineStr"/>
-      <c r="G134" s="7" t="inlineStr"/>
+      <c r="G134" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (MATH)</t>
+        </is>
+      </c>
       <c r="H134" s="7" t="inlineStr"/>
       <c r="I134" s="8" t="inlineStr">
         <is>
@@ -4329,13 +4329,13 @@
       </c>
       <c r="F135" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (G.K)</t>
+          <t>Class 8 (MATH)</t>
         </is>
       </c>
       <c r="G135" s="7" t="inlineStr"/>
       <c r="H135" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (MATH)</t>
+          <t>Class 5 (G.K)</t>
         </is>
       </c>
       <c r="I135" s="8" t="inlineStr">
@@ -4355,26 +4355,26 @@
           <t>Class 6 (MATH)</t>
         </is>
       </c>
-      <c r="C136" s="7" t="inlineStr">
+      <c r="C136" s="7" t="inlineStr"/>
+      <c r="D136" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (MATH)</t>
+        </is>
+      </c>
+      <c r="E136" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (MATH)</t>
+        </is>
+      </c>
+      <c r="F136" s="7" t="inlineStr"/>
+      <c r="G136" s="7" t="inlineStr">
         <is>
           <t>Class 7 (MATH)</t>
         </is>
       </c>
-      <c r="D136" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (G.K)</t>
-        </is>
-      </c>
-      <c r="E136" s="7" t="inlineStr"/>
-      <c r="F136" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (MATH)</t>
-        </is>
-      </c>
-      <c r="G136" s="7" t="inlineStr"/>
       <c r="H136" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (MATH)</t>
+          <t>Class 4 (G.K)</t>
         </is>
       </c>
       <c r="I136" s="8" t="inlineStr">
@@ -4453,37 +4453,29 @@
       </c>
       <c r="B140" s="7" t="inlineStr">
         <is>
+          <t>L.K.G (MATH)</t>
+        </is>
+      </c>
+      <c r="C140" s="7" t="inlineStr">
+        <is>
+          <t>L.K.G (MATH)</t>
+        </is>
+      </c>
+      <c r="D140" s="7" t="inlineStr">
+        <is>
           <t>L.K.G (EVS)</t>
         </is>
       </c>
-      <c r="C140" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (MATH)</t>
-        </is>
-      </c>
-      <c r="D140" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (MATH)</t>
-        </is>
-      </c>
-      <c r="E140" s="7" t="inlineStr">
+      <c r="E140" s="7" t="inlineStr"/>
+      <c r="F140" s="7" t="inlineStr">
         <is>
           <t>L.K.G (ORAL)</t>
         </is>
       </c>
-      <c r="F140" s="7" t="inlineStr">
+      <c r="G140" s="7" t="inlineStr"/>
+      <c r="H140" s="7" t="inlineStr">
         <is>
           <t>L.K.G (EVS)</t>
-        </is>
-      </c>
-      <c r="G140" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (ENG)</t>
-        </is>
-      </c>
-      <c r="H140" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (ENG)</t>
         </is>
       </c>
       <c r="I140" s="8" t="inlineStr">
@@ -4500,22 +4492,18 @@
       </c>
       <c r="B141" s="7" t="inlineStr">
         <is>
+          <t>L.K.G (ORAL)</t>
+        </is>
+      </c>
+      <c r="C141" s="7" t="inlineStr">
+        <is>
           <t>L.K.G (MATH)</t>
         </is>
       </c>
-      <c r="C141" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (EVS)</t>
-        </is>
-      </c>
-      <c r="D141" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (EVS)</t>
-        </is>
-      </c>
+      <c r="D141" s="7" t="inlineStr"/>
       <c r="E141" s="7" t="inlineStr">
         <is>
-          <t>L.K.G (EVS)</t>
+          <t>L.K.G (MATH)</t>
         </is>
       </c>
       <c r="F141" s="7" t="inlineStr">
@@ -4526,7 +4514,7 @@
       <c r="G141" s="7" t="inlineStr"/>
       <c r="H141" s="7" t="inlineStr">
         <is>
-          <t>L.K.G (MATH)</t>
+          <t>L.K.G (ENG)</t>
         </is>
       </c>
       <c r="I141" s="8" t="inlineStr">
@@ -4543,35 +4531,31 @@
       </c>
       <c r="B142" s="7" t="inlineStr">
         <is>
+          <t>L.K.G (ORAL)</t>
+        </is>
+      </c>
+      <c r="C142" s="7" t="inlineStr"/>
+      <c r="D142" s="7" t="inlineStr">
+        <is>
+          <t>L.K.G (EVS)</t>
+        </is>
+      </c>
+      <c r="E142" s="7" t="inlineStr">
+        <is>
+          <t>L.K.G (EVS)</t>
+        </is>
+      </c>
+      <c r="F142" s="7" t="inlineStr">
+        <is>
           <t>L.K.G (ENG)</t>
         </is>
       </c>
-      <c r="C142" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (MATH)</t>
-        </is>
-      </c>
-      <c r="D142" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (ENG)</t>
-        </is>
-      </c>
-      <c r="E142" s="7" t="inlineStr">
+      <c r="G142" s="7" t="inlineStr"/>
+      <c r="H142" s="7" t="inlineStr">
         <is>
           <t>L.K.G (EVS)</t>
         </is>
       </c>
-      <c r="F142" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (EVS)</t>
-        </is>
-      </c>
-      <c r="G142" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (ORAL)</t>
-        </is>
-      </c>
-      <c r="H142" s="7" t="inlineStr"/>
       <c r="I142" s="8" t="inlineStr">
         <is>
           <t>L.K.G</t>
@@ -4586,7 +4570,7 @@
       </c>
       <c r="B143" s="7" t="inlineStr">
         <is>
-          <t>L.K.G (ORAL)</t>
+          <t>L.K.G (ENG)</t>
         </is>
       </c>
       <c r="C143" s="7" t="inlineStr">
@@ -4594,21 +4578,29 @@
           <t>L.K.G (ENG)</t>
         </is>
       </c>
-      <c r="D143" s="7" t="inlineStr"/>
+      <c r="D143" s="7" t="inlineStr">
+        <is>
+          <t>L.K.G (EVS)</t>
+        </is>
+      </c>
       <c r="E143" s="7" t="inlineStr">
         <is>
+          <t>L.K.G (ENG)</t>
+        </is>
+      </c>
+      <c r="F143" s="7" t="inlineStr">
+        <is>
+          <t>L.K.G (ENG)</t>
+        </is>
+      </c>
+      <c r="G143" s="7" t="inlineStr">
+        <is>
+          <t>L.K.G (ENG)</t>
+        </is>
+      </c>
+      <c r="H143" s="7" t="inlineStr">
+        <is>
           <t>L.K.G (MATH)</t>
-        </is>
-      </c>
-      <c r="F143" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (MATH)</t>
-        </is>
-      </c>
-      <c r="G143" s="7" t="inlineStr"/>
-      <c r="H143" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (ENG)</t>
         </is>
       </c>
       <c r="I143" s="8" t="inlineStr">
@@ -4625,26 +4617,30 @@
       </c>
       <c r="B144" s="7" t="inlineStr">
         <is>
+          <t>L.K.G (EVS)</t>
+        </is>
+      </c>
+      <c r="C144" s="7" t="inlineStr">
+        <is>
           <t>L.K.G (ENG)</t>
         </is>
       </c>
-      <c r="C144" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (ENG)</t>
-        </is>
-      </c>
-      <c r="D144" s="7" t="inlineStr"/>
+      <c r="D144" s="7" t="inlineStr">
+        <is>
+          <t>L.K.G (MATH)</t>
+        </is>
+      </c>
       <c r="E144" s="7" t="inlineStr">
         <is>
+          <t>L.K.G (MATH)</t>
+        </is>
+      </c>
+      <c r="F144" s="7" t="inlineStr"/>
+      <c r="G144" s="7" t="inlineStr">
+        <is>
           <t>L.K.G (EVS)</t>
         </is>
       </c>
-      <c r="F144" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (MATH)</t>
-        </is>
-      </c>
-      <c r="G144" s="7" t="inlineStr"/>
       <c r="H144" s="7" t="inlineStr">
         <is>
           <t>L.K.G (ENG)</t>
@@ -4664,31 +4660,35 @@
       </c>
       <c r="B145" s="7" t="inlineStr">
         <is>
+          <t>L.K.G (ORAL)</t>
+        </is>
+      </c>
+      <c r="C145" s="7" t="inlineStr">
+        <is>
+          <t>L.K.G (ENG)</t>
+        </is>
+      </c>
+      <c r="D145" s="7" t="inlineStr">
+        <is>
           <t>L.K.G (EVS)</t>
         </is>
       </c>
-      <c r="C145" s="7" t="inlineStr">
+      <c r="E145" s="7" t="inlineStr">
         <is>
           <t>L.K.G (EVS)</t>
         </is>
       </c>
-      <c r="D145" s="7" t="inlineStr"/>
-      <c r="E145" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (ENG)</t>
-        </is>
-      </c>
-      <c r="F145" s="7" t="inlineStr">
+      <c r="F145" s="7" t="inlineStr"/>
+      <c r="G145" s="7" t="inlineStr">
         <is>
           <t>L.K.G (MATH)</t>
         </is>
       </c>
-      <c r="G145" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (ORAL)</t>
-        </is>
-      </c>
-      <c r="H145" s="7" t="inlineStr"/>
+      <c r="H145" s="7" t="inlineStr">
+        <is>
+          <t>L.K.G (MATH)</t>
+        </is>
+      </c>
       <c r="I145" s="8" t="inlineStr">
         <is>
           <t>L.K.G</t>
@@ -4823,12 +4823,12 @@
       <c r="E151" s="7" t="inlineStr"/>
       <c r="F151" s="7" t="inlineStr">
         <is>
+          <t>Class 8 (ENG)</t>
+        </is>
+      </c>
+      <c r="G151" s="7" t="inlineStr">
+        <is>
           <t>Class 9 (ENG)</t>
-        </is>
-      </c>
-      <c r="G151" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (ENG)</t>
         </is>
       </c>
       <c r="H151" s="7" t="inlineStr">
@@ -4850,12 +4850,12 @@
       <c r="E152" s="7" t="inlineStr"/>
       <c r="F152" s="7" t="inlineStr">
         <is>
+          <t>Class 8 (ENG)</t>
+        </is>
+      </c>
+      <c r="G152" s="7" t="inlineStr">
+        <is>
           <t>Class 9 (ENG)</t>
-        </is>
-      </c>
-      <c r="G152" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (ENG)</t>
         </is>
       </c>
       <c r="H152" s="7" t="inlineStr"/>
@@ -4877,12 +4877,12 @@
       <c r="E153" s="7" t="inlineStr"/>
       <c r="F153" s="7" t="inlineStr">
         <is>
+          <t>Class 9 (ENG)</t>
+        </is>
+      </c>
+      <c r="G153" s="7" t="inlineStr">
+        <is>
           <t>Class 8 (ENG)</t>
-        </is>
-      </c>
-      <c r="G153" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (ENG)</t>
         </is>
       </c>
       <c r="H153" s="7" t="inlineStr">
@@ -4992,7 +4992,7 @@
       <c r="D158" s="7" t="inlineStr"/>
       <c r="E158" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (SOC)</t>
+          <t>Class 10 (SOC)</t>
         </is>
       </c>
       <c r="F158" s="7" t="inlineStr">
@@ -5003,7 +5003,7 @@
       <c r="G158" s="7" t="inlineStr"/>
       <c r="H158" s="7" t="inlineStr">
         <is>
-          <t>Class 10 (SOC)</t>
+          <t>Class 8 (SOC)</t>
         </is>
       </c>
       <c r="I158" s="7" t="inlineStr"/>
@@ -5015,24 +5015,24 @@
         </is>
       </c>
       <c r="B159" s="7" t="inlineStr"/>
-      <c r="C159" s="7" t="inlineStr"/>
+      <c r="C159" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (SOC)</t>
+        </is>
+      </c>
       <c r="D159" s="7" t="inlineStr"/>
       <c r="E159" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (SOC)</t>
-        </is>
-      </c>
-      <c r="F159" s="7" t="inlineStr">
-        <is>
           <t>Class 9 (SOC)</t>
         </is>
       </c>
-      <c r="G159" s="7" t="inlineStr"/>
-      <c r="H159" s="7" t="inlineStr">
+      <c r="F159" s="7" t="inlineStr"/>
+      <c r="G159" s="7" t="inlineStr">
         <is>
           <t>Class 10 (SOC)</t>
         </is>
       </c>
+      <c r="H159" s="7" t="inlineStr"/>
       <c r="I159" s="7" t="inlineStr"/>
     </row>
     <row r="160">
@@ -5046,18 +5046,18 @@
       <c r="D160" s="7" t="inlineStr"/>
       <c r="E160" s="7" t="inlineStr">
         <is>
+          <t>Class 10 (SOC)</t>
+        </is>
+      </c>
+      <c r="F160" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (SOC)</t>
+        </is>
+      </c>
+      <c r="G160" s="7" t="inlineStr"/>
+      <c r="H160" s="7" t="inlineStr">
+        <is>
           <t>Class 8 (SOC)</t>
-        </is>
-      </c>
-      <c r="F160" s="7" t="inlineStr"/>
-      <c r="G160" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (SOC)</t>
-        </is>
-      </c>
-      <c r="H160" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (SOC)</t>
         </is>
       </c>
       <c r="I160" s="7" t="inlineStr"/>
@@ -5100,18 +5100,18 @@
       <c r="D162" s="7" t="inlineStr"/>
       <c r="E162" s="7" t="inlineStr">
         <is>
+          <t>Class 8 (SOC)</t>
+        </is>
+      </c>
+      <c r="F162" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (SOC)</t>
+        </is>
+      </c>
+      <c r="G162" s="7" t="inlineStr"/>
+      <c r="H162" s="7" t="inlineStr">
+        <is>
           <t>Class 9 (SOC)</t>
-        </is>
-      </c>
-      <c r="F162" s="7" t="inlineStr"/>
-      <c r="G162" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (SOC)</t>
-        </is>
-      </c>
-      <c r="H162" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (SOC)</t>
         </is>
       </c>
       <c r="I162" s="7" t="inlineStr"/>
@@ -5123,23 +5123,23 @@
         </is>
       </c>
       <c r="B163" s="7" t="inlineStr"/>
-      <c r="C163" s="7" t="inlineStr"/>
+      <c r="C163" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (SOC)</t>
+        </is>
+      </c>
       <c r="D163" s="7" t="inlineStr"/>
       <c r="E163" s="7" t="inlineStr">
         <is>
+          <t>Class 10 (SOC)</t>
+        </is>
+      </c>
+      <c r="F163" s="7" t="inlineStr">
+        <is>
           <t>Class 8 (SOC)</t>
         </is>
       </c>
-      <c r="F163" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (SOC)</t>
-        </is>
-      </c>
-      <c r="G163" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (SOC)</t>
-        </is>
-      </c>
+      <c r="G163" s="7" t="inlineStr"/>
       <c r="H163" s="7" t="inlineStr"/>
       <c r="I163" s="7" t="inlineStr"/>
     </row>
@@ -5216,25 +5216,25 @@
           <t>Class 3 (TEL)</t>
         </is>
       </c>
-      <c r="C167" s="7" t="inlineStr">
+      <c r="C167" s="7" t="inlineStr"/>
+      <c r="D167" s="7" t="inlineStr">
         <is>
           <t>U.K.G (HIN)</t>
         </is>
       </c>
-      <c r="D167" s="7" t="inlineStr"/>
       <c r="E167" s="7" t="inlineStr">
         <is>
+          <t>Class 5 (TEL)</t>
+        </is>
+      </c>
+      <c r="F167" s="7" t="inlineStr">
+        <is>
           <t>Class 4 (TEL)</t>
         </is>
       </c>
-      <c r="F167" s="7" t="inlineStr">
+      <c r="G167" s="7" t="inlineStr">
         <is>
           <t>Class 6 (TEL)</t>
-        </is>
-      </c>
-      <c r="G167" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (TEL)</t>
         </is>
       </c>
       <c r="H167" s="7" t="inlineStr"/>
@@ -5257,16 +5257,16 @@
       </c>
       <c r="C168" s="7" t="inlineStr">
         <is>
+          <t>Class 5 (TEL)</t>
+        </is>
+      </c>
+      <c r="D168" s="7" t="inlineStr"/>
+      <c r="E168" s="7" t="inlineStr"/>
+      <c r="F168" s="7" t="inlineStr">
+        <is>
           <t>Class 4 (TEL)</t>
         </is>
       </c>
-      <c r="D168" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (TEL)</t>
-        </is>
-      </c>
-      <c r="E168" s="7" t="inlineStr"/>
-      <c r="F168" s="7" t="inlineStr"/>
       <c r="G168" s="7" t="inlineStr">
         <is>
           <t>Class 6 (TEL)</t>
@@ -5293,25 +5293,25 @@
       <c r="C169" s="7" t="inlineStr"/>
       <c r="D169" s="7" t="inlineStr">
         <is>
+          <t>U.K.G (HIN)</t>
+        </is>
+      </c>
+      <c r="E169" s="7" t="inlineStr">
+        <is>
           <t>Class 4 (TEL)</t>
         </is>
       </c>
-      <c r="E169" s="7" t="inlineStr">
+      <c r="F169" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (TEL)</t>
+        </is>
+      </c>
+      <c r="G169" s="7" t="inlineStr"/>
+      <c r="H169" s="7" t="inlineStr">
         <is>
           <t>Class 6 (TEL)</t>
         </is>
       </c>
-      <c r="F169" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (TEL)</t>
-        </is>
-      </c>
-      <c r="G169" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (HIN)</t>
-        </is>
-      </c>
-      <c r="H169" s="7" t="inlineStr"/>
       <c r="I169" s="8" t="inlineStr">
         <is>
           <t>Class 3</t>
@@ -5331,26 +5331,26 @@
       </c>
       <c r="C170" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (TEL)</t>
+          <t>U.K.G (HIN)</t>
         </is>
       </c>
       <c r="D170" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (TEL)</t>
+          <t>Class 4 (TEL)</t>
         </is>
       </c>
       <c r="E170" s="7" t="inlineStr"/>
       <c r="F170" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (TEL)</t>
-        </is>
-      </c>
-      <c r="G170" s="7" t="inlineStr"/>
-      <c r="H170" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (HIN)</t>
-        </is>
-      </c>
+          <t>Class 6 (TEL)</t>
+        </is>
+      </c>
+      <c r="G170" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (TEL)</t>
+        </is>
+      </c>
+      <c r="H170" s="7" t="inlineStr"/>
       <c r="I170" s="8" t="inlineStr">
         <is>
           <t>Class 3</t>
@@ -5370,26 +5370,26 @@
       </c>
       <c r="C171" s="7" t="inlineStr">
         <is>
+          <t>Class 5 (TEL)</t>
+        </is>
+      </c>
+      <c r="D171" s="7" t="inlineStr">
+        <is>
           <t>Class 4 (TEL)</t>
         </is>
       </c>
-      <c r="D171" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (TEL)</t>
-        </is>
-      </c>
       <c r="E171" s="7" t="inlineStr"/>
-      <c r="F171" s="7" t="inlineStr"/>
+      <c r="F171" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (TEL)</t>
+        </is>
+      </c>
       <c r="G171" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (TEL)</t>
-        </is>
-      </c>
-      <c r="H171" s="7" t="inlineStr">
-        <is>
           <t>U.K.G (HIN)</t>
         </is>
       </c>
+      <c r="H171" s="7" t="inlineStr"/>
       <c r="I171" s="8" t="inlineStr">
         <is>
           <t>Class 3</t>
@@ -5409,7 +5409,7 @@
       </c>
       <c r="C172" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (TEL)</t>
+          <t>Class 4 (TEL)</t>
         </is>
       </c>
       <c r="D172" s="7" t="inlineStr">
@@ -5420,7 +5420,7 @@
       <c r="E172" s="7" t="inlineStr"/>
       <c r="F172" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (TEL)</t>
+          <t>Class 5 (TEL)</t>
         </is>
       </c>
       <c r="G172" s="7" t="inlineStr">
@@ -5511,25 +5511,25 @@
       <c r="C176" s="7" t="inlineStr"/>
       <c r="D176" s="7" t="inlineStr">
         <is>
+          <t>Class 3 (MATH)</t>
+        </is>
+      </c>
+      <c r="E176" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (MATH)</t>
+        </is>
+      </c>
+      <c r="F176" s="7" t="inlineStr">
+        <is>
           <t>Class 5 (MATH)</t>
         </is>
       </c>
-      <c r="E176" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (MATH)</t>
-        </is>
-      </c>
-      <c r="F176" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (MATH)</t>
-        </is>
-      </c>
-      <c r="G176" s="7" t="inlineStr">
+      <c r="G176" s="7" t="inlineStr"/>
+      <c r="H176" s="7" t="inlineStr">
         <is>
           <t>Class 2 (MATH)</t>
         </is>
       </c>
-      <c r="H176" s="7" t="inlineStr"/>
       <c r="I176" s="8" t="inlineStr">
         <is>
           <t>Class 4</t>
@@ -5547,28 +5547,28 @@
           <t>Class 4 (MATH)</t>
         </is>
       </c>
-      <c r="C177" s="7" t="inlineStr">
+      <c r="C177" s="7" t="inlineStr"/>
+      <c r="D177" s="7" t="inlineStr">
         <is>
           <t>Class 2 (MATH)</t>
         </is>
       </c>
-      <c r="D177" s="7" t="inlineStr">
+      <c r="E177" s="7" t="inlineStr">
         <is>
           <t>Class 3 (MATH)</t>
         </is>
       </c>
-      <c r="E177" s="7" t="inlineStr"/>
       <c r="F177" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (MATH)</t>
-        </is>
-      </c>
-      <c r="G177" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (MATH)</t>
-        </is>
-      </c>
-      <c r="H177" s="7" t="inlineStr"/>
+          <t>Class 3 (MATH)</t>
+        </is>
+      </c>
+      <c r="G177" s="7" t="inlineStr"/>
+      <c r="H177" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (MATH)</t>
+        </is>
+      </c>
       <c r="I177" s="8" t="inlineStr">
         <is>
           <t>Class 4</t>
@@ -5586,10 +5586,14 @@
           <t>Class 4 (MATH)</t>
         </is>
       </c>
-      <c r="C178" s="7" t="inlineStr"/>
+      <c r="C178" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (MATH)</t>
+        </is>
+      </c>
       <c r="D178" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (MATH)</t>
+          <t>Class 5 (MATH)</t>
         </is>
       </c>
       <c r="E178" s="7" t="inlineStr"/>
@@ -5623,26 +5627,22 @@
       </c>
       <c r="C179" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (MATH)</t>
+          <t>Class 5 (MATH)</t>
         </is>
       </c>
       <c r="D179" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (MATH)</t>
+          <t>Class 5 (MATH)</t>
         </is>
       </c>
       <c r="E179" s="7" t="inlineStr"/>
       <c r="F179" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (MATH)</t>
+          <t>Class 3 (MATH)</t>
         </is>
       </c>
       <c r="G179" s="7" t="inlineStr"/>
-      <c r="H179" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (MATH)</t>
-        </is>
-      </c>
+      <c r="H179" s="7" t="inlineStr"/>
       <c r="I179" s="8" t="inlineStr">
         <is>
           <t>Class 4</t>
@@ -5660,26 +5660,26 @@
           <t>Class 4 (MATH)</t>
         </is>
       </c>
-      <c r="C180" s="7" t="inlineStr">
+      <c r="C180" s="7" t="inlineStr"/>
+      <c r="D180" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (MATH)</t>
+        </is>
+      </c>
+      <c r="E180" s="7" t="inlineStr">
         <is>
           <t>Class 2 (MATH)</t>
         </is>
       </c>
-      <c r="D180" s="7" t="inlineStr"/>
-      <c r="E180" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (MATH)</t>
-        </is>
-      </c>
       <c r="F180" s="7" t="inlineStr">
         <is>
-          <t>Class 3 (MATH)</t>
+          <t>Class 2 (MATH)</t>
         </is>
       </c>
       <c r="G180" s="7" t="inlineStr"/>
       <c r="H180" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (MATH)</t>
+          <t>Class 3 (MATH)</t>
         </is>
       </c>
       <c r="I180" s="8" t="inlineStr">
@@ -5707,13 +5707,13 @@
       </c>
       <c r="E181" s="7" t="inlineStr">
         <is>
-          <t>Class 3 (MATH)</t>
+          <t>Class 5 (MATH)</t>
         </is>
       </c>
       <c r="F181" s="7" t="inlineStr"/>
       <c r="G181" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (MATH)</t>
+          <t>Class 2 (MATH)</t>
         </is>
       </c>
       <c r="H181" s="7" t="inlineStr"/>
@@ -5785,16 +5785,29 @@
         </is>
       </c>
     </row>
-    <row r="185">
+    <row r="185" ht="26" customHeight="1">
       <c r="A185" s="6" t="inlineStr">
         <is>
           <t>MON</t>
         </is>
       </c>
       <c r="B185" s="7" t="inlineStr"/>
-      <c r="C185" s="7" t="inlineStr"/>
-      <c r="D185" s="7" t="inlineStr"/>
-      <c r="E185" s="7" t="inlineStr"/>
+      <c r="C185" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (KAR)</t>
+        </is>
+      </c>
+      <c r="D185" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (KAR)
+Class 10 (KAR)</t>
+        </is>
+      </c>
+      <c r="E185" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (KAR)</t>
+        </is>
+      </c>
       <c r="F185" s="7" t="inlineStr"/>
       <c r="G185" s="7" t="inlineStr"/>
       <c r="H185" s="7" t="inlineStr"/>
@@ -5808,23 +5821,15 @@
       </c>
       <c r="B186" s="7" t="inlineStr"/>
       <c r="C186" s="7" t="inlineStr"/>
-      <c r="D186" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (KAR)</t>
-        </is>
-      </c>
+      <c r="D186" s="7" t="inlineStr"/>
       <c r="E186" s="7" t="inlineStr"/>
-      <c r="F186" s="7" t="inlineStr"/>
-      <c r="G186" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (KAR)</t>
-        </is>
-      </c>
-      <c r="H186" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (KAR)</t>
-        </is>
-      </c>
+      <c r="F186" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (KAR)</t>
+        </is>
+      </c>
+      <c r="G186" s="7" t="inlineStr"/>
+      <c r="H186" s="7" t="inlineStr"/>
       <c r="I186" s="7" t="inlineStr"/>
     </row>
     <row r="187">
@@ -5835,17 +5840,13 @@
       </c>
       <c r="B187" s="7" t="inlineStr"/>
       <c r="C187" s="7" t="inlineStr"/>
-      <c r="D187" s="7" t="inlineStr"/>
-      <c r="E187" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (KAR)</t>
-        </is>
-      </c>
-      <c r="F187" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (KAR)</t>
-        </is>
-      </c>
+      <c r="D187" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (KAR)</t>
+        </is>
+      </c>
+      <c r="E187" s="7" t="inlineStr"/>
+      <c r="F187" s="7" t="inlineStr"/>
       <c r="G187" s="7" t="inlineStr"/>
       <c r="H187" s="7" t="inlineStr"/>
       <c r="I187" s="7" t="inlineStr"/>
@@ -5858,16 +5859,8 @@
       </c>
       <c r="B188" s="7" t="inlineStr"/>
       <c r="C188" s="7" t="inlineStr"/>
-      <c r="D188" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (KAR)</t>
-        </is>
-      </c>
-      <c r="E188" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (KAR)</t>
-        </is>
-      </c>
+      <c r="D188" s="7" t="inlineStr"/>
+      <c r="E188" s="7" t="inlineStr"/>
       <c r="F188" s="7" t="inlineStr"/>
       <c r="G188" s="7" t="inlineStr"/>
       <c r="H188" s="7" t="inlineStr"/>
@@ -5883,24 +5876,33 @@
       <c r="C189" s="7" t="inlineStr"/>
       <c r="D189" s="7" t="inlineStr"/>
       <c r="E189" s="7" t="inlineStr"/>
-      <c r="F189" s="7" t="inlineStr"/>
-      <c r="G189" s="7" t="inlineStr"/>
+      <c r="F189" s="7" t="inlineStr">
+        <is>
+          <t>Class 1 (KAR)</t>
+        </is>
+      </c>
+      <c r="G189" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (KAR)</t>
+        </is>
+      </c>
       <c r="H189" s="7" t="inlineStr"/>
       <c r="I189" s="7" t="inlineStr"/>
     </row>
-    <row r="190">
+    <row r="190" ht="26" customHeight="1">
       <c r="A190" s="6" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
       <c r="B190" s="7" t="inlineStr"/>
-      <c r="C190" s="7" t="inlineStr"/>
-      <c r="D190" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (KAR)</t>
-        </is>
-      </c>
+      <c r="C190" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (KAR)
+Class 5 (KAR)</t>
+        </is>
+      </c>
+      <c r="D190" s="7" t="inlineStr"/>
       <c r="E190" s="7" t="inlineStr"/>
       <c r="F190" s="7" t="inlineStr"/>
       <c r="G190" s="7" t="inlineStr"/>
@@ -5969,7 +5971,7 @@
         </is>
       </c>
     </row>
-    <row r="194">
+    <row r="194" ht="52" customHeight="1">
       <c r="A194" s="6" t="inlineStr">
         <is>
           <t>MON</t>
@@ -5980,15 +5982,18 @@
       <c r="D194" s="7" t="inlineStr"/>
       <c r="E194" s="7" t="inlineStr"/>
       <c r="F194" s="7" t="inlineStr"/>
-      <c r="G194" s="7" t="inlineStr"/>
-      <c r="H194" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (P.E.T)</t>
-        </is>
-      </c>
+      <c r="G194" s="7" t="inlineStr">
+        <is>
+          <t>L.K.G (P.E.T)
+Class 1 (P.E.T)
+Class 2 (P.E.T)
+Class 3 (P.E.T)</t>
+        </is>
+      </c>
+      <c r="H194" s="7" t="inlineStr"/>
       <c r="I194" s="7" t="inlineStr"/>
     </row>
-    <row r="195">
+    <row r="195" ht="65" customHeight="1">
       <c r="A195" s="6" t="inlineStr">
         <is>
           <t>TUE</t>
@@ -5999,11 +6004,19 @@
       <c r="D195" s="7" t="inlineStr"/>
       <c r="E195" s="7" t="inlineStr"/>
       <c r="F195" s="7" t="inlineStr"/>
-      <c r="G195" s="7" t="inlineStr"/>
+      <c r="G195" s="7" t="inlineStr">
+        <is>
+          <t>L.K.G (P.E.T)
+U.K.G (P.E.T)
+Class 1 (P.E.T)
+Class 2 (P.E.T)
+Class 5 (P.E.T)</t>
+        </is>
+      </c>
       <c r="H195" s="7" t="inlineStr"/>
       <c r="I195" s="7" t="inlineStr"/>
     </row>
-    <row r="196">
+    <row r="196" ht="78" customHeight="1">
       <c r="A196" s="6" t="inlineStr">
         <is>
           <t>WED</t>
@@ -6014,11 +6027,20 @@
       <c r="D196" s="7" t="inlineStr"/>
       <c r="E196" s="7" t="inlineStr"/>
       <c r="F196" s="7" t="inlineStr"/>
-      <c r="G196" s="7" t="inlineStr"/>
+      <c r="G196" s="7" t="inlineStr">
+        <is>
+          <t>L.K.G (P.E.T)
+U.K.G (P.E.T)
+Class 1 (P.E.T)
+Class 2 (P.E.T)
+Class 3 (P.E.T)
+Class 4 (P.E.T)</t>
+        </is>
+      </c>
       <c r="H196" s="7" t="inlineStr"/>
       <c r="I196" s="7" t="inlineStr"/>
     </row>
-    <row r="197">
+    <row r="197" ht="130" customHeight="1">
       <c r="A197" s="6" t="inlineStr">
         <is>
           <t>THU</t>
@@ -6029,14 +6051,19 @@
       <c r="D197" s="7" t="inlineStr"/>
       <c r="E197" s="7" t="inlineStr"/>
       <c r="F197" s="7" t="inlineStr"/>
-      <c r="G197" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (P.E.T)</t>
-        </is>
-      </c>
+      <c r="G197" s="7" t="inlineStr"/>
       <c r="H197" s="7" t="inlineStr">
         <is>
-          <t>Class 10 (P.E.T)</t>
+          <t>U.K.G (P.E.T)
+Class 1 (P.E.T)
+Class 2 (P.E.T)
+Class 4 (P.E.T)
+Class 5 (P.E.T)
+Class 6 (P.E.T)
+Class 7 (P.E.T)
+Class 8 (P.E.T)
+Class 9 (P.E.T)
+Class 10 (P.E.T)</t>
         </is>
       </c>
       <c r="I197" s="7" t="inlineStr"/>
@@ -6052,11 +6079,7 @@
       <c r="D198" s="7" t="inlineStr"/>
       <c r="E198" s="7" t="inlineStr"/>
       <c r="F198" s="7" t="inlineStr"/>
-      <c r="G198" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (P.E.T)</t>
-        </is>
-      </c>
+      <c r="G198" s="7" t="inlineStr"/>
       <c r="H198" s="7" t="inlineStr"/>
       <c r="I198" s="7" t="inlineStr"/>
     </row>
@@ -6072,11 +6095,7 @@
       <c r="E199" s="7" t="inlineStr"/>
       <c r="F199" s="7" t="inlineStr"/>
       <c r="G199" s="7" t="inlineStr"/>
-      <c r="H199" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (P.E.T)</t>
-        </is>
-      </c>
+      <c r="H199" s="7" t="inlineStr"/>
       <c r="I199" s="7" t="inlineStr"/>
     </row>
   </sheetData>
@@ -6218,7 +6237,7 @@
       <c r="C2" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(EVS)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="D2" s="7" t="inlineStr">
@@ -6254,7 +6273,7 @@
       <c r="I2" s="7" t="inlineStr">
         <is>
           <t>MAHA
-(GRAM)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="J2" s="7" t="inlineStr">
@@ -6272,7 +6291,7 @@
       <c r="L2" s="7" t="inlineStr">
         <is>
           <t>FATHIMA
-(G.K)</t>
+(HIN)</t>
         </is>
       </c>
       <c r="M2" s="7" t="inlineStr">
@@ -6283,8 +6302,8 @@
       </c>
       <c r="N2" s="7" t="inlineStr">
         <is>
-          <t>BHEEMA
-(CHEM)</t>
+          <t>GOWTHAM
+(MATH)</t>
         </is>
       </c>
     </row>
@@ -6301,68 +6320,68 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>SWATHI
-(HIN)</t>
+          <t>SAI LAKSHMI
+(ENG)</t>
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>NAGAMANI
+(G.K)</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
         <is>
           <t>MAHA
 (ENG)</t>
         </is>
       </c>
-      <c r="F3" s="7" t="inlineStr">
-        <is>
-          <t>SAI LAKSHMI
-(HIN)</t>
-        </is>
-      </c>
       <c r="G3" s="7" t="inlineStr">
         <is>
-          <t>RIYA
-(HIN)</t>
+          <t>PALLAVI
+(SOC)</t>
         </is>
       </c>
       <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>MARTIAL ARTS
+(KAR)</t>
+        </is>
+      </c>
+      <c r="I3" s="7" t="inlineStr">
         <is>
           <t>FATHIMA
 (HIN)</t>
         </is>
       </c>
-      <c r="I3" s="7" t="inlineStr">
-        <is>
-          <t>LALITHA
-(EVS)</t>
-        </is>
-      </c>
       <c r="J3" s="7" t="inlineStr">
         <is>
-          <t>RAVI
-(ENG)</t>
+          <t>MAHESWARI
+(COMP)</t>
         </is>
       </c>
       <c r="K3" s="7" t="inlineStr">
+        <is>
+          <t>D.V.RAO
+(TEL)</t>
+        </is>
+      </c>
+      <c r="L3" s="7" t="inlineStr">
         <is>
           <t>SANGEETHA
 (MATH)</t>
         </is>
       </c>
-      <c r="L3" s="7" t="inlineStr">
-        <is>
-          <t>D.V.RAO
-(TEL)</t>
-        </is>
-      </c>
       <c r="M3" s="7" t="inlineStr">
-        <is>
-          <t>BHEEMA
-(CHEM)</t>
-        </is>
-      </c>
-      <c r="N3" s="7" t="inlineStr">
         <is>
           <t>GOWTHAM
 (MATH)</t>
+        </is>
+      </c>
+      <c r="N3" s="7" t="inlineStr">
+        <is>
+          <t>BHEEMA
+(PHY)</t>
         </is>
       </c>
     </row>
@@ -6374,31 +6393,31 @@
       <c r="C4" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(MATH)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>SWATHI
+(HIN)</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>BHAVANI
 (MATH)</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>MAHESWARI
-(COMP)</t>
-        </is>
-      </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>NAGAMANI
-(TEL)</t>
+          <t>SAI LAKSHMI
+(HIN)</t>
         </is>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
-          <t>LALITHA
-(EVS)</t>
+          <t>TULASI
+(MATH)</t>
         </is>
       </c>
       <c r="H4" s="7" t="inlineStr">
@@ -6409,38 +6428,38 @@
       </c>
       <c r="I4" s="7" t="inlineStr">
         <is>
-          <t>TULASI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="J4" s="7" t="inlineStr">
-        <is>
           <t>PALLAVI
 (SOC)</t>
         </is>
       </c>
+      <c r="J4" s="7" t="inlineStr">
+        <is>
+          <t>RAVI
+(GRAM)</t>
+        </is>
+      </c>
       <c r="K4" s="7" t="inlineStr">
         <is>
-          <t>RAVI
-(ENG)</t>
+          <t>MARTIAL ARTS
+(KAR)</t>
         </is>
       </c>
       <c r="L4" s="7" t="inlineStr">
         <is>
-          <t>SANGEETHA
+          <t>BHEEMA
+(CHEM)</t>
+        </is>
+      </c>
+      <c r="M4" s="7" t="inlineStr">
+        <is>
+          <t>GOWTHAM
 (MATH)</t>
         </is>
       </c>
-      <c r="M4" s="7" t="inlineStr">
-        <is>
-          <t>BHEEMA
-(PHY)</t>
-        </is>
-      </c>
       <c r="N4" s="7" t="inlineStr">
         <is>
-          <t>D.V.RAO
-(TEL)</t>
+          <t>MARTIAL ARTS
+(KAR)</t>
         </is>
       </c>
     </row>
@@ -6451,74 +6470,74 @@
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>SITHA
-(ORAL)</t>
-        </is>
-      </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
           <t>NAGAMANI
 (TEL)</t>
         </is>
       </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>BHAVANI
+(EVS)</t>
+        </is>
+      </c>
       <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>BHAVANI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>SAI LAKSHMI
 (EVS)</t>
         </is>
       </c>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>TULASI
 (MATH)</t>
         </is>
       </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>RIYA
+(HIN)</t>
+        </is>
+      </c>
       <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>FATHIMA
+(HIN)</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
         <is>
           <t>SWATHI
 (TEL)</t>
         </is>
       </c>
-      <c r="I5" s="7" t="inlineStr">
-        <is>
-          <t>PALLAVI
-(SOC)</t>
-        </is>
-      </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
-          <t>LALITHA
-(PHY)</t>
+          <t>RAVI
+(ENG)</t>
         </is>
       </c>
       <c r="K5" s="7" t="inlineStr">
         <is>
-          <t>FATHIMA
-(HIN)</t>
+          <t>SANGEETHA
+(COMP)</t>
         </is>
       </c>
       <c r="L5" s="7" t="inlineStr">
+        <is>
+          <t>D.V.RAO
+(TEL)</t>
+        </is>
+      </c>
+      <c r="M5" s="7" t="inlineStr">
+        <is>
+          <t>MARTIAL ARTS
+(KAR)</t>
+        </is>
+      </c>
+      <c r="N5" s="7" t="inlineStr">
         <is>
           <t>SUNITHA
 (SOC)</t>
-        </is>
-      </c>
-      <c r="M5" s="7" t="inlineStr">
-        <is>
-          <t>RAVI
-(GRAM)</t>
-        </is>
-      </c>
-      <c r="N5" s="7" t="inlineStr">
-        <is>
-          <t>RIYA
-(HIN)</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6549,7 @@
       <c r="C6" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(EVS)</t>
+(ORAL)</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
@@ -6541,46 +6560,46 @@
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>BHAVANI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
           <t>MAHA
 (ENG)</t>
         </is>
       </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>NAGAMANI
+(TEL)</t>
+        </is>
+      </c>
       <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>LALITHA
+(EVS)</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>SWATHI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="I6" s="7" t="inlineStr">
         <is>
           <t>TULASI
 (MATH)</t>
         </is>
       </c>
-      <c r="H6" s="7" t="inlineStr">
+      <c r="J6" s="7" t="inlineStr">
         <is>
           <t>PALLAVI
 (SOC)</t>
         </is>
       </c>
-      <c r="I6" s="7" t="inlineStr">
+      <c r="K6" s="7" t="inlineStr">
         <is>
           <t>FATHIMA
 (HIN)</t>
         </is>
       </c>
-      <c r="J6" s="7" t="inlineStr">
-        <is>
-          <t>SWATHI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="K6" s="7" t="inlineStr">
-        <is>
-          <t>LALITHA
-(BIO)</t>
-        </is>
-      </c>
       <c r="L6" s="7" t="inlineStr">
         <is>
           <t>SONU
@@ -6595,8 +6614,8 @@
       </c>
       <c r="N6" s="7" t="inlineStr">
         <is>
-          <t>CHALAPATHI
-(BIO)</t>
+          <t>RIYA
+(HIN)</t>
         </is>
       </c>
     </row>
@@ -6607,32 +6626,32 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>SITHA
-(ENG)</t>
+          <t>P.E
+(P.E.T)</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>SAI LAKSHMI
-(ENG)</t>
+          <t>BHAVANI
+(EVS)</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>NAGAMANI
-(G.K)</t>
+          <t>P.E
+(P.E.T)</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>TULASI
-(MATH)</t>
+          <t>P.E
+(P.E.T)</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>MAHA
-(ENG)</t>
+          <t>P.E
+(P.E.T)</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
@@ -6643,32 +6662,32 @@
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
+          <t>MAHA
+(GRAM)</t>
+        </is>
+      </c>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
           <t>SWATHI
 (TEL)</t>
         </is>
       </c>
-      <c r="J7" s="7" t="inlineStr">
-        <is>
-          <t>FATHIMA
-(HIN)</t>
-        </is>
-      </c>
       <c r="K7" s="7" t="inlineStr">
         <is>
           <t>RAVI
-(GRAM)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="L7" s="7" t="inlineStr">
-        <is>
-          <t>SANGEETHA
-(MATH)</t>
-        </is>
-      </c>
-      <c r="M7" s="7" t="inlineStr">
         <is>
           <t>CHALAPATHI
 (BIO)</t>
+        </is>
+      </c>
+      <c r="M7" s="7" t="inlineStr">
+        <is>
+          <t>RIYA
+(HIN)</t>
         </is>
       </c>
       <c r="N7" s="7" t="inlineStr">
@@ -6686,73 +6705,73 @@
       <c r="C8" s="7" t="inlineStr">
         <is>
           <t>SITHA
+(EVS)</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>NAGAMANI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>SAI LAKSHMI
+(HIN)</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>TULASI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>MAHA
 (ENG)</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>SAI LAKSHMI
-(ENG)</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>P.E
-(P.E.T)</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>P.E
-(P.E.T)</t>
-        </is>
-      </c>
-      <c r="G8" s="7" t="inlineStr">
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>PALLAVI
 (SOC)</t>
         </is>
       </c>
-      <c r="H8" s="7" t="inlineStr">
-        <is>
-          <t>P.E
-(P.E.T)</t>
-        </is>
-      </c>
       <c r="I8" s="7" t="inlineStr">
         <is>
-          <t>MAHA
+          <t>LALITHA
+(EVS)</t>
+        </is>
+      </c>
+      <c r="J8" s="7" t="inlineStr">
+        <is>
+          <t>FATHIMA
+(HIN)</t>
+        </is>
+      </c>
+      <c r="K8" s="7" t="inlineStr">
+        <is>
+          <t>SANGEETHA
+(MATH)</t>
+        </is>
+      </c>
+      <c r="L8" s="7" t="inlineStr">
+        <is>
+          <t>SUNITHA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="M8" s="7" t="inlineStr">
+        <is>
+          <t>SONU
 (ENG)</t>
         </is>
       </c>
-      <c r="J8" s="7" t="inlineStr">
-        <is>
-          <t>LALITHA
-(BIO)</t>
-        </is>
-      </c>
-      <c r="K8" s="7" t="inlineStr">
+      <c r="N8" s="7" t="inlineStr">
         <is>
           <t>D.V.RAO
 (TEL)</t>
-        </is>
-      </c>
-      <c r="L8" s="7" t="inlineStr">
-        <is>
-          <t>CHALAPATHI
-(BIO)</t>
-        </is>
-      </c>
-      <c r="M8" s="7" t="inlineStr">
-        <is>
-          <t>SONU
-(ENG)</t>
-        </is>
-      </c>
-      <c r="N8" s="7" t="inlineStr">
-        <is>
-          <t>SUNITHA
-(SOC)</t>
         </is>
       </c>
     </row>
@@ -6846,13 +6865,13 @@
       <c r="C10" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(MATH)</t>
+(ORAL)</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
           <t>BHAVANI
-(MATH)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
@@ -6924,67 +6943,67 @@
       <c r="C11" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(EVS)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>SAI LAKSHMI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>BHAVANI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
         <is>
           <t>NAGAMANI
 (TEL)</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>SAI LAKSHMI
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>RIYA
 (HIN)</t>
         </is>
       </c>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>TULASI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="G11" s="7" t="inlineStr">
+      <c r="H11" s="7" t="inlineStr">
         <is>
           <t>MAHA
-(ENG)</t>
-        </is>
-      </c>
-      <c r="H11" s="7" t="inlineStr">
+(GRAM)</t>
+        </is>
+      </c>
+      <c r="I11" s="7" t="inlineStr">
         <is>
           <t>SWATHI
 (TEL)</t>
         </is>
       </c>
-      <c r="I11" s="7" t="inlineStr">
-        <is>
-          <t>PALLAVI
-(SOC)</t>
-        </is>
-      </c>
       <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>FATHIMA
+(HIN)</t>
+        </is>
+      </c>
+      <c r="K11" s="7" t="inlineStr">
         <is>
           <t>LALITHA
 (CHEM)</t>
         </is>
       </c>
-      <c r="K11" s="7" t="inlineStr">
-        <is>
-          <t>D.V.RAO
-(TEL)</t>
-        </is>
-      </c>
       <c r="L11" s="7" t="inlineStr">
+        <is>
+          <t>SUNITHA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="M11" s="7" t="inlineStr">
         <is>
           <t>BHEEMA
 (PHY)</t>
-        </is>
-      </c>
-      <c r="M11" s="7" t="inlineStr">
-        <is>
-          <t>GOWTHAM
-(MATH)</t>
         </is>
       </c>
       <c r="N11" s="7" t="inlineStr">
@@ -7001,56 +7020,56 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>SITHA
+          <t>NAGAMANI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>SAI LAKSHMI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>MAHA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>TULASI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>PALLAVI
+(SOC)</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>LALITHA
 (EVS)</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>BHAVANI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>SAI LAKSHMI
-(EVS)</t>
-        </is>
-      </c>
-      <c r="F12" s="7" t="inlineStr">
+      <c r="I12" s="7" t="inlineStr">
         <is>
           <t>MAHESWARI
 (COMP)</t>
         </is>
       </c>
-      <c r="G12" s="7" t="inlineStr">
-        <is>
-          <t>TULASI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="H12" s="7" t="inlineStr">
-        <is>
-          <t>PALLAVI
-(SOC)</t>
-        </is>
-      </c>
-      <c r="I12" s="7" t="inlineStr">
-        <is>
-          <t>SWATHI
+      <c r="J12" s="7" t="inlineStr">
+        <is>
+          <t>RAVI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="K12" s="7" t="inlineStr">
+        <is>
+          <t>D.V.RAO
 (TEL)</t>
-        </is>
-      </c>
-      <c r="J12" s="7" t="inlineStr">
-        <is>
-          <t>MARTIAL ARTS
-(KAR)</t>
-        </is>
-      </c>
-      <c r="K12" s="7" t="inlineStr">
-        <is>
-          <t>LALITHA
-(PHY)</t>
         </is>
       </c>
       <c r="L12" s="7" t="inlineStr">
@@ -7067,8 +7086,8 @@
       </c>
       <c r="N12" s="7" t="inlineStr">
         <is>
-          <t>D.V.RAO
-(TEL)</t>
+          <t>BHEEMA
+(PHY)</t>
         </is>
       </c>
     </row>
@@ -7080,7 +7099,7 @@
       <c r="C13" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(EVS)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
@@ -7091,60 +7110,62 @@
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>MAHA
-(ENG)</t>
+          <t>MAHESWARI
+(COMP)</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>NAGAMANI
+          <t>SAI LAKSHMI
+(EVS)</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>TULASI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>PALLAVI
+(SOC)</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>LALITHA
+(EVS)</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>SANGEETHA
+(G.K)</t>
+        </is>
+      </c>
+      <c r="K13" s="7" t="inlineStr">
+        <is>
+          <t>FATHIMA
+(HIN)</t>
+        </is>
+      </c>
+      <c r="L13" s="7" t="inlineStr">
+        <is>
+          <t>D.V.RAO
 (TEL)</t>
         </is>
       </c>
-      <c r="G13" s="7" t="inlineStr">
+      <c r="M13" s="7" t="inlineStr">
+        <is>
+          <t>SUNITHA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="N13" s="7" t="inlineStr">
         <is>
           <t>RIYA
 (HIN)</t>
-        </is>
-      </c>
-      <c r="H13" s="7" t="inlineStr">
-        <is>
-          <t>FATHIMA
-(HIN)</t>
-        </is>
-      </c>
-      <c r="I13" s="7" t="inlineStr">
-        <is>
-          <t>LALITHA
-(EVS)</t>
-        </is>
-      </c>
-      <c r="J13" s="7" t="inlineStr">
-        <is>
-          <t>RAVI
-(ENG)</t>
-        </is>
-      </c>
-      <c r="K13" s="7" t="inlineStr">
-        <is>
-          <t>SANGEETHA
-(COMP)</t>
-        </is>
-      </c>
-      <c r="L13" s="7" t="inlineStr">
-        <is>
-          <t>SUNITHA
-(SOC)</t>
-        </is>
-      </c>
-      <c r="M13" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
-        </is>
-      </c>
-      <c r="N13" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
         </is>
       </c>
     </row>
@@ -7161,62 +7182,62 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
+          <t>BHAVANI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
           <t>SAI LAKSHMI
-(ENG)</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>NAGAMANI
-(G.K)</t>
+(HIN)</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
-        <is>
-          <t>BHAVANI
-(G.K)</t>
-        </is>
-      </c>
-      <c r="G14" s="7" t="inlineStr">
-        <is>
-          <t>LALITHA
-(EVS)</t>
-        </is>
-      </c>
-      <c r="H14" s="7" t="inlineStr">
         <is>
           <t>MAHA
 (ENG)</t>
         </is>
       </c>
-      <c r="I14" s="7" t="inlineStr">
+      <c r="G14" s="7" t="inlineStr">
         <is>
           <t>TULASI
 (MATH)</t>
         </is>
       </c>
-      <c r="J14" s="7" t="inlineStr">
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>SWATHI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="inlineStr">
         <is>
           <t>FATHIMA
 (HIN)</t>
         </is>
       </c>
+      <c r="J14" s="7" t="inlineStr">
+        <is>
+          <t>PALLAVI
+(SOC)</t>
+        </is>
+      </c>
       <c r="K14" s="7" t="inlineStr">
         <is>
+          <t>LALITHA
+(BIO)</t>
+        </is>
+      </c>
+      <c r="L14" s="7" t="inlineStr">
+        <is>
+          <t>MARTIAL ARTS
+(KAR)</t>
+        </is>
+      </c>
+      <c r="M14" s="7" t="inlineStr">
+        <is>
           <t>RAVI
-(ENG)</t>
-        </is>
-      </c>
-      <c r="L14" s="7" t="inlineStr">
-        <is>
-          <t>CHALAPATHI
-(BIO)</t>
-        </is>
-      </c>
-      <c r="M14" s="7" t="inlineStr">
-        <is>
-          <t>SUNITHA
-(SOC)</t>
+(GRAM)</t>
         </is>
       </c>
       <c r="N14" s="7" t="inlineStr">
@@ -7233,44 +7254,44 @@
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>NAGAMANI
-(TEL)</t>
+          <t>P.E
+(P.E.T)</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>SAI LAKSHMI
-(ENG)</t>
+          <t>P.E
+(P.E.T)</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>MAHESWARI
-(COMP)</t>
+          <t>P.E
+(P.E.T)</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>P.E
+(P.E.T)</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>LALITHA
+(EVS)</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
         <is>
           <t>MAHA
 (ENG)</t>
         </is>
       </c>
-      <c r="G15" s="7" t="inlineStr">
-        <is>
-          <t>PALLAVI
-(SOC)</t>
-        </is>
-      </c>
-      <c r="H15" s="7" t="inlineStr">
-        <is>
-          <t>MARTIAL ARTS
-(KAR)</t>
-        </is>
-      </c>
       <c r="I15" s="7" t="inlineStr">
         <is>
-          <t>TULASI
-(MATH)</t>
+          <t>P.E
+(P.E.T)</t>
         </is>
       </c>
       <c r="J15" s="7" t="inlineStr">
@@ -7281,8 +7302,8 @@
       </c>
       <c r="K15" s="7" t="inlineStr">
         <is>
-          <t>SANGEETHA
-(MATH)</t>
+          <t>FATHIMA
+(G.K)</t>
         </is>
       </c>
       <c r="L15" s="7" t="inlineStr">
@@ -7293,13 +7314,14 @@
       </c>
       <c r="M15" s="7" t="inlineStr">
         <is>
-          <t>RIYA
-(HIN)</t>
-        </is>
-      </c>
-      <c r="N15" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
+          <t>CHALAPATHI
+(BIO)</t>
+        </is>
+      </c>
+      <c r="N15" s="7" t="inlineStr">
+        <is>
+          <t>SUNITHA
+(SOC)</t>
         </is>
       </c>
     </row>
@@ -7311,21 +7333,21 @@
       <c r="C16" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(MATH)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>NAGAMANI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
         <is>
           <t>BHAVANI
 (MATH)</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>MARTIAL ARTS
-(KAR)</t>
-        </is>
-      </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
           <t>SAI LAKSHMI
@@ -7335,49 +7357,49 @@
       <c r="G16" s="7" t="inlineStr">
         <is>
           <t>MAHA
-(GRAM)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="H16" s="7" t="inlineStr">
         <is>
-          <t>LALITHA
-(EVS)</t>
+          <t>TULASI
+(MATH)</t>
         </is>
       </c>
       <c r="I16" s="7" t="inlineStr">
-        <is>
-          <t>FATHIMA
-(HIN)</t>
-        </is>
-      </c>
-      <c r="J16" s="7" t="inlineStr">
         <is>
           <t>PALLAVI
 (SOC)</t>
         </is>
       </c>
+      <c r="J16" s="7" t="inlineStr">
+        <is>
+          <t>LALITHA
+(BIO)</t>
+        </is>
+      </c>
       <c r="K16" s="7" t="inlineStr">
         <is>
-          <t>MARTIAL ARTS
-(KAR)</t>
+          <t>RAVI
+(ENG)</t>
         </is>
       </c>
       <c r="L16" s="7" t="inlineStr">
+        <is>
+          <t>SANGEETHA
+(MATH)</t>
+        </is>
+      </c>
+      <c r="M16" s="7" t="inlineStr">
+        <is>
+          <t>SONU
+(ENG)</t>
+        </is>
+      </c>
+      <c r="N16" s="7" t="inlineStr">
         <is>
           <t>D.V.RAO
 (TEL)</t>
-        </is>
-      </c>
-      <c r="M16" s="7" t="inlineStr">
-        <is>
-          <t>SONU
-(ENG)</t>
-        </is>
-      </c>
-      <c r="N16" s="7" t="inlineStr">
-        <is>
-          <t>SUNITHA
-(SOC)</t>
         </is>
       </c>
     </row>
@@ -7471,13 +7493,13 @@
       <c r="C18" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(ENG)</t>
+(ORAL)</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
           <t>BHAVANI
-(EVS)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
@@ -7536,8 +7558,8 @@
       </c>
       <c r="N18" s="7" t="inlineStr">
         <is>
-          <t>GOWTHAM
-(MATH)</t>
+          <t>BHEEMA
+(CHEM)</t>
         </is>
       </c>
     </row>
@@ -7548,62 +7570,62 @@
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>SITHA
-(MATH)</t>
+          <t>NAGAMANI
+(TEL)</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
           <t>BHAVANI
-(MATH)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>MAHA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
         <is>
           <t>SAI LAKSHMI
 (EVS)</t>
         </is>
       </c>
-      <c r="F19" s="7" t="inlineStr">
-        <is>
-          <t>NAGAMANI
-(TEL)</t>
-        </is>
-      </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>MAHA
-(ENG)</t>
+          <t>TULASI
+(MATH)</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>MAHESWARI
-(COMP)</t>
+          <t>FATHIMA
+(HIN)</t>
         </is>
       </c>
       <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>LALITHA
+(EVS)</t>
+        </is>
+      </c>
+      <c r="J19" s="7" t="inlineStr">
         <is>
           <t>PALLAVI
 (SOC)</t>
         </is>
       </c>
-      <c r="J19" s="7" t="inlineStr">
-        <is>
-          <t>LALITHA
-(BIO)</t>
-        </is>
-      </c>
       <c r="K19" s="7" t="inlineStr">
         <is>
-          <t>FATHIMA
-(HIN)</t>
+          <t>SANGEETHA
+(MATH)</t>
         </is>
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
-          <t>D.V.RAO
-(TEL)</t>
+          <t>BHEEMA
+(CHEM)</t>
         </is>
       </c>
       <c r="M19" s="7" t="inlineStr">
@@ -7614,8 +7636,8 @@
       </c>
       <c r="N19" s="7" t="inlineStr">
         <is>
-          <t>BHEEMA
-(CHEM)</t>
+          <t>RIYA
+(HIN)</t>
         </is>
       </c>
     </row>
@@ -7627,49 +7649,49 @@
       <c r="C20" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(ENG)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>SWATHI
+(HIN)</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
         <is>
           <t>BHAVANI
 (MATH)</t>
         </is>
       </c>
-      <c r="E20" s="7" t="inlineStr">
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>MAHESWARI
+(COMP)</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
         <is>
           <t>SAI LAKSHMI
-(HIN)</t>
-        </is>
-      </c>
-      <c r="F20" s="7" t="inlineStr">
+(G.K)</t>
+        </is>
+      </c>
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>LALITHA
+(EVS)</t>
+        </is>
+      </c>
+      <c r="I20" s="7" t="inlineStr">
         <is>
           <t>TULASI
 (MATH)</t>
         </is>
       </c>
-      <c r="G20" s="7" t="inlineStr">
-        <is>
-          <t>LALITHA
-(EVS)</t>
-        </is>
-      </c>
-      <c r="H20" s="7" t="inlineStr">
-        <is>
-          <t>SWATHI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="I20" s="7" t="inlineStr">
-        <is>
-          <t>MAHESWARI
-(COMP)</t>
-        </is>
-      </c>
       <c r="J20" s="7" t="inlineStr">
         <is>
-          <t>SANGEETHA
-(G.K)</t>
+          <t>MARTIAL ARTS
+(KAR)</t>
         </is>
       </c>
       <c r="K20" s="7" t="inlineStr">
@@ -7680,20 +7702,20 @@
       </c>
       <c r="L20" s="7" t="inlineStr">
         <is>
+          <t>D.V.RAO
+(TEL)</t>
+        </is>
+      </c>
+      <c r="M20" s="7" t="inlineStr">
+        <is>
           <t>BHEEMA
 (CHEM)</t>
         </is>
       </c>
-      <c r="M20" s="7" t="inlineStr">
+      <c r="N20" s="7" t="inlineStr">
         <is>
           <t>GOWTHAM
 (MATH)</t>
-        </is>
-      </c>
-      <c r="N20" s="7" t="inlineStr">
-        <is>
-          <t>D.V.RAO
-(TEL)</t>
         </is>
       </c>
     </row>
@@ -7710,67 +7732,68 @@
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
+          <t>NAGAMANI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
           <t>SAI LAKSHMI
+(HIN)</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>MAHA
 (ENG)</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
-        <is>
-          <t>MAHA
-(GRAM)</t>
-        </is>
-      </c>
-      <c r="F21" s="7" t="inlineStr">
-        <is>
-          <t>MAHESWARI
-(COMP)</t>
-        </is>
-      </c>
       <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>PALLAVI
+(SOC)</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>SWATHI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>FATHIMA
+(HIN)</t>
+        </is>
+      </c>
+      <c r="J21" s="7" t="inlineStr">
+        <is>
+          <t>RAVI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="K21" s="7" t="inlineStr">
+        <is>
+          <t>LALITHA
+(CHEM)</t>
+        </is>
+      </c>
+      <c r="L21" s="7" t="inlineStr">
+        <is>
+          <t>SANGEETHA
+(MATH)</t>
+        </is>
+      </c>
+      <c r="M21" s="7" t="inlineStr">
         <is>
           <t>RIYA
 (HIN)</t>
         </is>
       </c>
-      <c r="H21" s="7" t="inlineStr">
-        <is>
-          <t>PALLAVI
-(SOC)</t>
-        </is>
-      </c>
-      <c r="I21" s="7" t="inlineStr">
-        <is>
-          <t>FATHIMA
-(HIN)</t>
-        </is>
-      </c>
-      <c r="J21" s="7" t="inlineStr">
-        <is>
-          <t>SWATHI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="K21" s="7" t="inlineStr">
-        <is>
-          <t>SANGEETHA
-(MATH)</t>
-        </is>
-      </c>
-      <c r="L21" s="7" t="inlineStr">
+      <c r="N21" s="7" t="inlineStr">
         <is>
           <t>SUNITHA
 (SOC)</t>
-        </is>
-      </c>
-      <c r="M21" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
-        </is>
-      </c>
-      <c r="N21" s="7" t="inlineStr">
-        <is>
-          <t>MARTIAL ARTS
-(KAR)</t>
         </is>
       </c>
     </row>
@@ -7782,37 +7805,37 @@
       <c r="C22" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(EVS)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>NAGAMANI
-(TEL)</t>
+          <t>SAI LAKSHMI
+(ENG)</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>BHAVANI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>TULASI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
         <is>
           <t>MAHA
 (ENG)</t>
         </is>
       </c>
-      <c r="F22" s="7" t="inlineStr">
-        <is>
-          <t>TULASI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="G22" s="7" t="inlineStr">
-        <is>
-          <t>MARTIAL ARTS
-(KAR)</t>
-        </is>
-      </c>
       <c r="H22" s="7" t="inlineStr">
         <is>
-          <t>LALITHA
-(EVS)</t>
+          <t>PALLAVI
+(SOC)</t>
         </is>
       </c>
       <c r="I22" s="7" t="inlineStr">
@@ -7823,8 +7846,8 @@
       </c>
       <c r="J22" s="7" t="inlineStr">
         <is>
-          <t>PALLAVI
-(SOC)</t>
+          <t>LALITHA
+(PHY)</t>
         </is>
       </c>
       <c r="K22" s="7" t="inlineStr">
@@ -7835,20 +7858,20 @@
       </c>
       <c r="L22" s="7" t="inlineStr">
         <is>
-          <t>SANGEETHA
-(COMP)</t>
-        </is>
-      </c>
-      <c r="M22" s="7" t="inlineStr">
-        <is>
           <t>SONU
 (ENG)</t>
         </is>
       </c>
+      <c r="M22" s="7" t="inlineStr">
+        <is>
+          <t>SUNITHA
+(SOC)</t>
+        </is>
+      </c>
       <c r="N22" s="7" t="inlineStr">
         <is>
-          <t>RIYA
-(HIN)</t>
+          <t>CHALAPATHI
+(BIO)</t>
         </is>
       </c>
     </row>
@@ -7859,74 +7882,74 @@
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>SITHA
-(ORAL)</t>
+          <t>P.E
+(P.E.T)</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>SWATHI
-(HIN)</t>
+          <t>P.E
+(P.E.T)</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>BHAVANI
-(MATH)</t>
+          <t>P.E
+(P.E.T)</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>SAI LAKSHMI
-(HIN)</t>
+          <t>P.E
+(P.E.T)</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>P.E
+(P.E.T)</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>P.E
+(P.E.T)</t>
+        </is>
+      </c>
+      <c r="I23" s="7" t="inlineStr">
         <is>
           <t>PALLAVI
 (SOC)</t>
         </is>
       </c>
-      <c r="H23" s="7" t="inlineStr">
-        <is>
-          <t>MAHA
-(ENG)</t>
-        </is>
-      </c>
-      <c r="I23" s="7" t="inlineStr">
+      <c r="J23" s="7" t="inlineStr">
+        <is>
+          <t>FATHIMA
+(HIN)</t>
+        </is>
+      </c>
+      <c r="K23" s="7" t="inlineStr">
         <is>
           <t>LALITHA
-(EVS)</t>
-        </is>
-      </c>
-      <c r="J23" s="7" t="inlineStr">
-        <is>
-          <t>MAHESWARI
-(COMP)</t>
-        </is>
-      </c>
-      <c r="K23" s="7" t="inlineStr">
-        <is>
-          <t>FATHIMA
-(G.K)</t>
+(BIO)</t>
         </is>
       </c>
       <c r="L23" s="7" t="inlineStr">
+        <is>
+          <t>SANGEETHA
+(MATH)</t>
+        </is>
+      </c>
+      <c r="M23" s="7" t="inlineStr">
         <is>
           <t>SONU
 (ENG)</t>
         </is>
       </c>
-      <c r="M23" s="7" t="inlineStr">
-        <is>
-          <t>RIYA
-(HIN)</t>
-        </is>
-      </c>
       <c r="N23" s="7" t="inlineStr">
         <is>
-          <t>SUNITHA
-(SOC)</t>
+          <t>D.V.RAO
+(TEL)</t>
         </is>
       </c>
     </row>
@@ -7937,68 +7960,68 @@
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
+          <t>SITHA
+(EVS)</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>BHAVANI
+(EVS)</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>SAI LAKSHMI
+(EVS)</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
           <t>NAGAMANI
 (TEL)</t>
         </is>
       </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>BHAVANI
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>LALITHA
 (EVS)</t>
         </is>
       </c>
-      <c r="E24" s="7" t="inlineStr">
-        <is>
-          <t>SAI LAKSHMI
-(EVS)</t>
-        </is>
-      </c>
-      <c r="F24" s="7" t="inlineStr">
+      <c r="H24" s="7" t="inlineStr">
         <is>
           <t>MAHA
 (ENG)</t>
         </is>
       </c>
-      <c r="G24" s="7" t="inlineStr">
-        <is>
-          <t>MAHESWARI
-(COMP)</t>
-        </is>
-      </c>
-      <c r="H24" s="7" t="inlineStr">
+      <c r="I24" s="7" t="inlineStr">
+        <is>
+          <t>TULASI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="J24" s="7" t="inlineStr">
+        <is>
+          <t>SWATHI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="K24" s="7" t="inlineStr">
         <is>
           <t>FATHIMA
 (HIN)</t>
         </is>
       </c>
-      <c r="I24" s="7" t="inlineStr">
-        <is>
-          <t>TULASI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="J24" s="7" t="inlineStr">
-        <is>
-          <t>RAVI
-(ENG)</t>
-        </is>
-      </c>
-      <c r="K24" s="7" t="inlineStr">
-        <is>
-          <t>LALITHA
-(BIO)</t>
-        </is>
-      </c>
       <c r="L24" s="7" t="inlineStr">
-        <is>
-          <t>SANGEETHA
-(MATH)</t>
-        </is>
-      </c>
-      <c r="M24" s="7" t="inlineStr">
         <is>
           <t>SUNITHA
 (SOC)</t>
+        </is>
+      </c>
+      <c r="M24" s="7" t="inlineStr">
+        <is>
+          <t>CHALAPATHI
+(BIO)</t>
         </is>
       </c>
       <c r="N24" s="7" t="inlineStr">
@@ -8098,13 +8121,13 @@
       <c r="C26" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(ORAL)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
           <t>BHAVANI
-(EVS)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
@@ -8116,7 +8139,7 @@
       <c r="F26" s="7" t="inlineStr">
         <is>
           <t>SAI LAKSHMI
-(HIN)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">
@@ -8161,10 +8184,9 @@
 (TEL)</t>
         </is>
       </c>
-      <c r="N26" s="7" t="inlineStr">
-        <is>
-          <t>RIYA
-(HIN)</t>
+      <c r="N26" s="12" t="inlineStr">
+        <is>
+          <t>Recreation</t>
         </is>
       </c>
     </row>
@@ -8181,50 +8203,50 @@
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
+          <t>SWATHI
+(HIN)</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
           <t>SAI LAKSHMI
-(ENG)</t>
-        </is>
-      </c>
-      <c r="E27" s="7" t="inlineStr">
-        <is>
-          <t>MAHA
-(ENG)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>NAGAMANI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>RIYA
+(HIN)</t>
+        </is>
+      </c>
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>PALLAVI
+(SOC)</t>
+        </is>
+      </c>
+      <c r="I27" s="7" t="inlineStr">
         <is>
           <t>TULASI
 (MATH)</t>
         </is>
       </c>
-      <c r="G27" s="7" t="inlineStr">
-        <is>
-          <t>PALLAVI
-(SOC)</t>
-        </is>
-      </c>
-      <c r="H27" s="7" t="inlineStr">
+      <c r="J27" s="7" t="inlineStr">
         <is>
           <t>LALITHA
-(EVS)</t>
-        </is>
-      </c>
-      <c r="I27" s="7" t="inlineStr">
-        <is>
-          <t>SWATHI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="J27" s="7" t="inlineStr">
-        <is>
-          <t>RAVI
-(ENG)</t>
+(BIO)</t>
         </is>
       </c>
       <c r="K27" s="7" t="inlineStr">
         <is>
-          <t>D.V.RAO
-(TEL)</t>
+          <t>FATHIMA
+(HIN)</t>
         </is>
       </c>
       <c r="L27" s="7" t="inlineStr">
@@ -8253,8 +8275,8 @@
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>NAGAMANI
-(TEL)</t>
+          <t>SITHA
+(EVS)</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
@@ -8265,16 +8287,16 @@
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
+          <t>MAHA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
           <t>SAI LAKSHMI
 (HIN)</t>
         </is>
       </c>
-      <c r="F28" s="7" t="inlineStr">
-        <is>
-          <t>MAHA
-(GRAM)</t>
-        </is>
-      </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
           <t>LALITHA
@@ -8283,22 +8305,22 @@
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
+          <t>SWATHI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="I28" s="7" t="inlineStr">
+        <is>
           <t>TULASI
 (MATH)</t>
         </is>
       </c>
-      <c r="I28" s="7" t="inlineStr">
+      <c r="J28" s="7" t="inlineStr">
         <is>
           <t>PALLAVI
 (SOC)</t>
         </is>
       </c>
-      <c r="J28" s="7" t="inlineStr">
-        <is>
-          <t>SWATHI
-(TEL)</t>
-        </is>
-      </c>
       <c r="K28" s="7" t="inlineStr">
         <is>
           <t>RAVI
@@ -8308,19 +8330,19 @@
       <c r="L28" s="7" t="inlineStr">
         <is>
           <t>SANGEETHA
+(COMP)</t>
+        </is>
+      </c>
+      <c r="M28" s="7" t="inlineStr">
+        <is>
+          <t>GOWTHAM
 (MATH)</t>
         </is>
       </c>
-      <c r="M28" s="7" t="inlineStr">
-        <is>
-          <t>MARTIAL ARTS
-(KAR)</t>
-        </is>
-      </c>
       <c r="N28" s="7" t="inlineStr">
         <is>
-          <t>BHEEMA
-(PHY)</t>
+          <t>D.V.RAO
+(TEL)</t>
         </is>
       </c>
     </row>
@@ -8332,7 +8354,7 @@
       <c r="C29" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(MATH)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
@@ -8343,62 +8365,62 @@
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
+          <t>NAGAMANI
+(G.K)</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
           <t>BHAVANI
+(G.K)</t>
+        </is>
+      </c>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>MAHESWARI
+(COMP)</t>
+        </is>
+      </c>
+      <c r="H29" s="7" t="inlineStr">
+        <is>
+          <t>MAHA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>LALITHA
+(EVS)</t>
+        </is>
+      </c>
+      <c r="J29" s="7" t="inlineStr">
+        <is>
+          <t>RAVI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="K29" s="7" t="inlineStr">
+        <is>
+          <t>SANGEETHA
 (MATH)</t>
         </is>
       </c>
-      <c r="F29" s="7" t="inlineStr">
-        <is>
-          <t>NAGAMANI
+      <c r="L29" s="7" t="inlineStr">
+        <is>
+          <t>D.V.RAO
 (TEL)</t>
         </is>
       </c>
-      <c r="G29" s="7" t="inlineStr">
+      <c r="M29" s="7" t="inlineStr">
+        <is>
+          <t>SUNITHA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="N29" s="7" t="inlineStr">
         <is>
           <t>RIYA
 (HIN)</t>
-        </is>
-      </c>
-      <c r="H29" s="7" t="inlineStr">
-        <is>
-          <t>FATHIMA
-(HIN)</t>
-        </is>
-      </c>
-      <c r="I29" s="7" t="inlineStr">
-        <is>
-          <t>MARTIAL ARTS
-(KAR)</t>
-        </is>
-      </c>
-      <c r="J29" s="7" t="inlineStr">
-        <is>
-          <t>LALITHA
-(BIO)</t>
-        </is>
-      </c>
-      <c r="K29" s="7" t="inlineStr">
-        <is>
-          <t>SANGEETHA
-(MATH)</t>
-        </is>
-      </c>
-      <c r="L29" s="7" t="inlineStr">
-        <is>
-          <t>MARTIAL ARTS
-(KAR)</t>
-        </is>
-      </c>
-      <c r="M29" s="7" t="inlineStr">
-        <is>
-          <t>SUNITHA
-(SOC)</t>
-        </is>
-      </c>
-      <c r="N29" s="7" t="inlineStr">
-        <is>
-          <t>D.V.RAO
-(TEL)</t>
         </is>
       </c>
     </row>
@@ -8410,67 +8432,67 @@
       <c r="C30" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(MATH)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>NAGAMANI
-(TEL)</t>
+          <t>BHAVANI
+(EVS)</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
-        <is>
-          <t>BHAVANI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="F30" s="7" t="inlineStr">
         <is>
           <t>SAI LAKSHMI
 (EVS)</t>
         </is>
       </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>MAHA
+(GRAM)</t>
+        </is>
+      </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>MAHA
-(ENG)</t>
+          <t>TULASI
+(MATH)</t>
         </is>
       </c>
       <c r="H30" s="7" t="inlineStr">
+        <is>
+          <t>LALITHA
+(EVS)</t>
+        </is>
+      </c>
+      <c r="I30" s="7" t="inlineStr">
+        <is>
+          <t>PALLAVI
+(SOC)</t>
+        </is>
+      </c>
+      <c r="J30" s="7" t="inlineStr">
         <is>
           <t>SWATHI
 (TEL)</t>
         </is>
       </c>
-      <c r="I30" s="7" t="inlineStr">
-        <is>
-          <t>TULASI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="J30" s="7" t="inlineStr">
-        <is>
-          <t>FATHIMA
-(HIN)</t>
-        </is>
-      </c>
       <c r="K30" s="7" t="inlineStr">
-        <is>
-          <t>LALITHA
-(PHY)</t>
-        </is>
-      </c>
-      <c r="L30" s="7" t="inlineStr">
         <is>
           <t>D.V.RAO
 (TEL)</t>
         </is>
       </c>
-      <c r="M30" s="7" t="inlineStr">
+      <c r="L30" s="7" t="inlineStr">
         <is>
           <t>SONU
 (ENG)</t>
+        </is>
+      </c>
+      <c r="M30" s="7" t="inlineStr">
+        <is>
+          <t>RIYA
+(HIN)</t>
         </is>
       </c>
       <c r="N30" s="7" t="inlineStr">
@@ -8487,68 +8509,68 @@
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
+          <t>SITHA
+(ENG)</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
+          <t>NAGAMANI
+(TEL)</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
+          <t>SAI LAKSHMI
+(HIN)</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
-        <is>
-          <t>P.E
-(P.E.T)</t>
-        </is>
-      </c>
-      <c r="G31" s="7" t="inlineStr">
-        <is>
-          <t>SAI LAKSHMI
-(G.K)</t>
-        </is>
-      </c>
-      <c r="H31" s="7" t="inlineStr">
         <is>
           <t>MAHA
 (ENG)</t>
         </is>
       </c>
-      <c r="I31" s="7" t="inlineStr">
-        <is>
-          <t>P.E
-(P.E.T)</t>
-        </is>
-      </c>
-      <c r="J31" s="7" t="inlineStr">
+      <c r="G31" s="7" t="inlineStr">
         <is>
           <t>PALLAVI
 (SOC)</t>
         </is>
       </c>
-      <c r="K31" s="7" t="inlineStr">
+      <c r="H31" s="7" t="inlineStr">
         <is>
           <t>FATHIMA
 (HIN)</t>
         </is>
       </c>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t>SWATHI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="J31" s="7" t="inlineStr">
+        <is>
+          <t>LALITHA
+(CHEM)</t>
+        </is>
+      </c>
+      <c r="K31" s="7" t="inlineStr">
+        <is>
+          <t>SANGEETHA
+(MATH)</t>
+        </is>
+      </c>
       <c r="L31" s="7" t="inlineStr">
+        <is>
+          <t>RAVI
+(GRAM)</t>
+        </is>
+      </c>
+      <c r="M31" s="7" t="inlineStr">
         <is>
           <t>SONU
 (ENG)</t>
-        </is>
-      </c>
-      <c r="M31" s="7" t="inlineStr">
-        <is>
-          <t>RIYA
-(HIN)</t>
         </is>
       </c>
       <c r="N31" s="7" t="inlineStr">
@@ -8566,43 +8588,43 @@
       <c r="C32" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(ENG)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>SWATHI
-(HIN)</t>
+          <t>P.E
+(P.E.T)</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>BHAVANI
-(MATH)</t>
+          <t>P.E
+(P.E.T)</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>P.E
+(P.E.T)</t>
+        </is>
+      </c>
+      <c r="G32" s="7" t="inlineStr">
         <is>
           <t>MAHA
 (ENG)</t>
         </is>
       </c>
-      <c r="G32" s="7" t="inlineStr">
-        <is>
-          <t>TULASI
-(MATH)</t>
-        </is>
-      </c>
       <c r="H32" s="7" t="inlineStr">
         <is>
-          <t>PALLAVI
-(SOC)</t>
+          <t>P.E
+(P.E.T)</t>
         </is>
       </c>
       <c r="I32" s="7" t="inlineStr">
         <is>
-          <t>LALITHA
-(EVS)</t>
+          <t>P.E
+(P.E.T)</t>
         </is>
       </c>
       <c r="J32" s="7" t="inlineStr">
@@ -8727,13 +8749,13 @@
       <c r="C34" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(ENG)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
           <t>BHAVANI
-(EVS)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
@@ -8745,7 +8767,7 @@
       <c r="F34" s="7" t="inlineStr">
         <is>
           <t>SAI LAKSHMI
-(EVS)</t>
+(HIN)</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
@@ -8810,22 +8832,22 @@
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
+          <t>BHAVANI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
           <t>SAI LAKSHMI
-(ENG)</t>
-        </is>
-      </c>
-      <c r="E35" s="7" t="inlineStr">
+(EVS)</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
         <is>
           <t>MAHESWARI
 (COMP)</t>
         </is>
       </c>
-      <c r="F35" s="7" t="inlineStr">
-        <is>
-          <t>TULASI
-(MATH)</t>
-        </is>
-      </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
           <t>RIYA
@@ -8834,22 +8856,22 @@
       </c>
       <c r="H35" s="7" t="inlineStr">
         <is>
+          <t>LALITHA
+(EVS)</t>
+        </is>
+      </c>
+      <c r="I35" s="7" t="inlineStr">
+        <is>
           <t>SWATHI
 (TEL)</t>
         </is>
       </c>
-      <c r="I35" s="7" t="inlineStr">
+      <c r="J35" s="7" t="inlineStr">
         <is>
           <t>PALLAVI
 (SOC)</t>
         </is>
       </c>
-      <c r="J35" s="7" t="inlineStr">
-        <is>
-          <t>LALITHA
-(PHY)</t>
-        </is>
-      </c>
       <c r="K35" s="7" t="inlineStr">
         <is>
           <t>SANGEETHA
@@ -8858,8 +8880,8 @@
       </c>
       <c r="L35" s="7" t="inlineStr">
         <is>
-          <t>RAVI
-(GRAM)</t>
+          <t>BHEEMA
+(PHY)</t>
         </is>
       </c>
       <c r="M35" s="7" t="inlineStr">
@@ -8870,8 +8892,8 @@
       </c>
       <c r="N35" s="7" t="inlineStr">
         <is>
-          <t>BHEEMA
-(PHY)</t>
+          <t>D.V.RAO
+(TEL)</t>
         </is>
       </c>
     </row>
@@ -8882,62 +8904,62 @@
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
+          <t>SITHA
+(MATH)</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>BHAVANI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>SAI LAKSHMI
+(EVS)</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
           <t>NAGAMANI
 (TEL)</t>
         </is>
       </c>
-      <c r="D36" s="7" t="inlineStr">
-        <is>
-          <t>SAI LAKSHMI
-(ENG)</t>
-        </is>
-      </c>
-      <c r="E36" s="7" t="inlineStr">
+      <c r="G36" s="7" t="inlineStr">
         <is>
           <t>MAHA
 (ENG)</t>
         </is>
       </c>
-      <c r="F36" s="7" t="inlineStr">
-        <is>
-          <t>BHAVANI
-(G.K)</t>
-        </is>
-      </c>
-      <c r="G36" s="7" t="inlineStr">
-        <is>
-          <t>LALITHA
-(EVS)</t>
-        </is>
-      </c>
       <c r="H36" s="7" t="inlineStr">
-        <is>
-          <t>PALLAVI
-(SOC)</t>
-        </is>
-      </c>
-      <c r="I36" s="7" t="inlineStr">
         <is>
           <t>SWATHI
 (TEL)</t>
         </is>
       </c>
+      <c r="I36" s="7" t="inlineStr">
+        <is>
+          <t>TULASI
+(MATH)</t>
+        </is>
+      </c>
       <c r="J36" s="7" t="inlineStr">
-        <is>
-          <t>RAVI
-(ENG)</t>
-        </is>
-      </c>
-      <c r="K36" s="7" t="inlineStr">
         <is>
           <t>FATHIMA
 (HIN)</t>
         </is>
       </c>
+      <c r="K36" s="7" t="inlineStr">
+        <is>
+          <t>LALITHA
+(PHY)</t>
+        </is>
+      </c>
       <c r="L36" s="7" t="inlineStr">
         <is>
-          <t>BHEEMA
-(PHY)</t>
+          <t>D.V.RAO
+(TEL)</t>
         </is>
       </c>
       <c r="M36" s="7" t="inlineStr">
@@ -8948,8 +8970,8 @@
       </c>
       <c r="N36" s="7" t="inlineStr">
         <is>
-          <t>D.V.RAO
-(TEL)</t>
+          <t>BHEEMA
+(CHEM)</t>
         </is>
       </c>
     </row>
@@ -8961,51 +8983,51 @@
       <c r="C37" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(EVS)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
-        <is>
-          <t>BHAVANI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="E37" s="7" t="inlineStr">
-        <is>
-          <t>SAI LAKSHMI
-(EVS)</t>
-        </is>
-      </c>
-      <c r="F37" s="7" t="inlineStr">
         <is>
           <t>NAGAMANI
 (TEL)</t>
         </is>
       </c>
-      <c r="G37" s="7" t="inlineStr">
+      <c r="E37" s="7" t="inlineStr">
         <is>
           <t>MAHA
 (ENG)</t>
         </is>
       </c>
-      <c r="H37" s="7" t="inlineStr">
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>TULASI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="G37" s="7" t="inlineStr">
         <is>
           <t>LALITHA
 (EVS)</t>
         </is>
       </c>
+      <c r="H37" s="7" t="inlineStr">
+        <is>
+          <t>PALLAVI
+(SOC)</t>
+        </is>
+      </c>
       <c r="I37" s="7" t="inlineStr">
-        <is>
-          <t>TULASI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="J37" s="7" t="inlineStr">
         <is>
           <t>FATHIMA
 (HIN)</t>
         </is>
       </c>
+      <c r="J37" s="7" t="inlineStr">
+        <is>
+          <t>RAVI
+(ENG)</t>
+        </is>
+      </c>
       <c r="K37" s="7" t="inlineStr">
         <is>
           <t>SANGEETHA
@@ -9014,20 +9036,19 @@
       </c>
       <c r="L37" s="7" t="inlineStr">
         <is>
-          <t>D.V.RAO
-(TEL)</t>
-        </is>
-      </c>
-      <c r="M37" s="7" t="inlineStr">
-        <is>
           <t>SUNITHA
 (SOC)</t>
         </is>
       </c>
-      <c r="N37" s="7" t="inlineStr">
+      <c r="M37" s="7" t="inlineStr">
         <is>
           <t>RIYA
 (HIN)</t>
+        </is>
+      </c>
+      <c r="N37" s="12" t="inlineStr">
+        <is>
+          <t>Recreation</t>
         </is>
       </c>
     </row>
@@ -9038,74 +9059,74 @@
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>SITHA
-(MATH)</t>
-        </is>
-      </c>
-      <c r="D38" s="7" t="inlineStr">
-        <is>
           <t>NAGAMANI
 (TEL)</t>
         </is>
       </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>BHAVANI
+(MATH)</t>
+        </is>
+      </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>SAI LAKSHMI
-(EVS)</t>
+          <t>MARTIAL ARTS
+(KAR)</t>
         </is>
       </c>
       <c r="F38" s="7" t="inlineStr">
+        <is>
+          <t>TULASI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="G38" s="7" t="inlineStr">
+        <is>
+          <t>PALLAVI
+(SOC)</t>
+        </is>
+      </c>
+      <c r="H38" s="7" t="inlineStr">
         <is>
           <t>MAHA
 (ENG)</t>
         </is>
       </c>
-      <c r="G38" s="7" t="inlineStr">
-        <is>
-          <t>TULASI
+      <c r="I38" s="7" t="inlineStr">
+        <is>
+          <t>LALITHA
+(EVS)</t>
+        </is>
+      </c>
+      <c r="J38" s="7" t="inlineStr">
+        <is>
+          <t>SWATHI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="K38" s="7" t="inlineStr">
+        <is>
+          <t>RAVI
+(GRAM)</t>
+        </is>
+      </c>
+      <c r="L38" s="7" t="inlineStr">
+        <is>
+          <t>SANGEETHA
 (MATH)</t>
         </is>
       </c>
-      <c r="H38" s="7" t="inlineStr">
-        <is>
-          <t>SANGEETHA
-(G.K)</t>
-        </is>
-      </c>
-      <c r="I38" s="7" t="inlineStr">
-        <is>
-          <t>FATHIMA
-(HIN)</t>
-        </is>
-      </c>
-      <c r="J38" s="7" t="inlineStr">
-        <is>
-          <t>PALLAVI
-(SOC)</t>
-        </is>
-      </c>
-      <c r="K38" s="7" t="inlineStr">
-        <is>
-          <t>D.V.RAO
-(TEL)</t>
-        </is>
-      </c>
-      <c r="L38" s="7" t="inlineStr">
+      <c r="M38" s="7" t="inlineStr">
         <is>
           <t>SONU
 (ENG)</t>
         </is>
       </c>
-      <c r="M38" s="7" t="inlineStr">
-        <is>
-          <t>RIYA
-(HIN)</t>
-        </is>
-      </c>
       <c r="N38" s="7" t="inlineStr">
         <is>
-          <t>CHALAPATHI
-(BIO)</t>
+          <t>SUNITHA
+(SOC)</t>
         </is>
       </c>
     </row>
@@ -9116,74 +9137,73 @@
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
+          <t>SITHA
+(EVS)</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
+          <t>SWATHI
+(HIN)</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
+          <t>SAI LAKSHMI
+(HIN)</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
+          <t>MARTIAL ARTS
+(KAR)</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
-        <is>
-          <t>P.E
-(P.E.T)</t>
-        </is>
-      </c>
-      <c r="H39" s="7" t="inlineStr">
         <is>
           <t>MAHA
 (GRAM)</t>
         </is>
       </c>
+      <c r="H39" s="7" t="inlineStr">
+        <is>
+          <t>MAHESWARI
+(COMP)</t>
+        </is>
+      </c>
       <c r="I39" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
+          <t>PALLAVI
+(SOC)</t>
         </is>
       </c>
       <c r="J39" s="7" t="inlineStr">
         <is>
-          <t>SWATHI
-(TEL)</t>
+          <t>LALITHA
+(BIO)</t>
         </is>
       </c>
       <c r="K39" s="7" t="inlineStr">
         <is>
-          <t>LALITHA
-(CHEM)</t>
+          <t>RAVI
+(ENG)</t>
         </is>
       </c>
       <c r="L39" s="7" t="inlineStr">
+        <is>
+          <t>SONU
+(ENG)</t>
+        </is>
+      </c>
+      <c r="M39" s="12" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+      <c r="N39" s="7" t="inlineStr">
         <is>
           <t>CHALAPATHI
 (BIO)</t>
-        </is>
-      </c>
-      <c r="M39" s="7" t="inlineStr">
-        <is>
-          <t>SONU
-(ENG)</t>
-        </is>
-      </c>
-      <c r="N39" s="7" t="inlineStr">
-        <is>
-          <t>SUNITHA
-(SOC)</t>
         </is>
       </c>
     </row>
@@ -9200,62 +9220,62 @@
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>SWATHI
-(HIN)</t>
+          <t>SAI LAKSHMI
+(ENG)</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>SAI LAKSHMI
-(HIN)</t>
+          <t>MAHESWARI
+(COMP)</t>
         </is>
       </c>
       <c r="F40" s="7" t="inlineStr">
+        <is>
+          <t>MAHA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="G40" s="7" t="inlineStr">
         <is>
           <t>TULASI
 (MATH)</t>
         </is>
       </c>
-      <c r="G40" s="7" t="inlineStr">
-        <is>
-          <t>PALLAVI
-(SOC)</t>
-        </is>
-      </c>
       <c r="H40" s="7" t="inlineStr">
         <is>
-          <t>MAHA
-(ENG)</t>
+          <t>FATHIMA
+(HIN)</t>
         </is>
       </c>
       <c r="I40" s="7" t="inlineStr">
         <is>
+          <t>SANGEETHA
+(G.K)</t>
+        </is>
+      </c>
+      <c r="J40" s="7" t="inlineStr">
+        <is>
           <t>LALITHA
-(EVS)</t>
-        </is>
-      </c>
-      <c r="J40" s="7" t="inlineStr">
-        <is>
-          <t>SANGEETHA
-(MATH)</t>
+(CHEM)</t>
         </is>
       </c>
       <c r="K40" s="7" t="inlineStr">
         <is>
-          <t>RAVI
-(ENG)</t>
+          <t>D.V.RAO
+(TEL)</t>
         </is>
       </c>
       <c r="L40" s="7" t="inlineStr">
+        <is>
+          <t>CHALAPATHI
+(BIO)</t>
+        </is>
+      </c>
+      <c r="M40" s="7" t="inlineStr">
         <is>
           <t>SUNITHA
 (SOC)</t>
-        </is>
-      </c>
-      <c r="M40" s="7" t="inlineStr">
-        <is>
-          <t>CHALAPATHI
-(BIO)</t>
         </is>
       </c>
       <c r="N40" s="7" t="inlineStr">
@@ -9355,13 +9375,13 @@
       <c r="C42" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(EVS)</t>
+(ORAL)</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
           <t>BHAVANI
-(EVS)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
@@ -9373,7 +9393,7 @@
       <c r="F42" s="7" t="inlineStr">
         <is>
           <t>SAI LAKSHMI
-(HIN)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
@@ -9409,7 +9429,7 @@
       <c r="L42" s="7" t="inlineStr">
         <is>
           <t>FATHIMA
-(HIN)</t>
+(G.K)</t>
         </is>
       </c>
       <c r="M42" s="7" t="inlineStr">
@@ -9420,8 +9440,8 @@
       </c>
       <c r="N42" s="7" t="inlineStr">
         <is>
-          <t>RIYA
-(HIN)</t>
+          <t>GOWTHAM
+(MATH)</t>
         </is>
       </c>
     </row>
@@ -9433,72 +9453,73 @@
       <c r="C43" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(EVS)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>NAGAMANI
-(TEL)</t>
+          <t>SAI LAKSHMI
+(ENG)</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
+          <t>MAHA
+(GRAM)</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
           <t>BHAVANI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="F43" s="7" t="inlineStr">
-        <is>
-          <t>SAI LAKSHMI
-(EVS)</t>
+(G.K)</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>LALITHA
-(EVS)</t>
+          <t>MARTIAL ARTS
+(KAR)</t>
         </is>
       </c>
       <c r="H43" s="7" t="inlineStr">
-        <is>
-          <t>MAHA
-(ENG)</t>
-        </is>
-      </c>
-      <c r="I43" s="7" t="inlineStr">
         <is>
           <t>SWATHI
 (TEL)</t>
         </is>
       </c>
+      <c r="I43" s="7" t="inlineStr">
+        <is>
+          <t>MARTIAL ARTS
+(KAR)</t>
+        </is>
+      </c>
       <c r="J43" s="7" t="inlineStr">
         <is>
-          <t>RAVI
-(ENG)</t>
+          <t>PALLAVI
+(SOC)</t>
         </is>
       </c>
       <c r="K43" s="7" t="inlineStr">
         <is>
-          <t>SANGEETHA
-(MATH)</t>
+          <t>LALITHA
+(BIO)</t>
         </is>
       </c>
       <c r="L43" s="7" t="inlineStr">
         <is>
           <t>BHEEMA
-(CHEM)</t>
+(PHY)</t>
         </is>
       </c>
       <c r="M43" s="7" t="inlineStr">
         <is>
-          <t>GOWTHAM
-(MATH)</t>
-        </is>
-      </c>
-      <c r="N43" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
+          <t>SUNITHA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="N43" s="7" t="inlineStr">
+        <is>
+          <t>D.V.RAO
+(TEL)</t>
         </is>
       </c>
     </row>
@@ -9509,28 +9530,28 @@
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
+          <t>SITHA
+(EVS)</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>SWATHI
+(HIN)</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>SAI LAKSHMI
+(EVS)</t>
+        </is>
+      </c>
+      <c r="F44" s="7" t="inlineStr">
+        <is>
           <t>NAGAMANI
 (TEL)</t>
         </is>
       </c>
-      <c r="D44" s="7" t="inlineStr">
-        <is>
-          <t>SWATHI
-(HIN)</t>
-        </is>
-      </c>
-      <c r="E44" s="7" t="inlineStr">
-        <is>
-          <t>SAI LAKSHMI
-(EVS)</t>
-        </is>
-      </c>
-      <c r="F44" s="7" t="inlineStr">
-        <is>
-          <t>MARTIAL ARTS
-(KAR)</t>
-        </is>
-      </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
           <t>TULASI
@@ -9545,22 +9566,22 @@
       </c>
       <c r="I44" s="7" t="inlineStr">
         <is>
+          <t>LALITHA
+(EVS)</t>
+        </is>
+      </c>
+      <c r="J44" s="7" t="inlineStr">
+        <is>
           <t>SANGEETHA
-(G.K)</t>
-        </is>
-      </c>
-      <c r="J44" s="7" t="inlineStr">
+(MATH)</t>
+        </is>
+      </c>
+      <c r="K44" s="7" t="inlineStr">
         <is>
           <t>FATHIMA
 (HIN)</t>
         </is>
       </c>
-      <c r="K44" s="7" t="inlineStr">
-        <is>
-          <t>LALITHA
-(BIO)</t>
-        </is>
-      </c>
       <c r="L44" s="7" t="inlineStr">
         <is>
           <t>D.V.RAO
@@ -9573,10 +9594,9 @@
 (PHY)</t>
         </is>
       </c>
-      <c r="N44" s="7" t="inlineStr">
-        <is>
-          <t>GOWTHAM
-(MATH)</t>
+      <c r="N44" s="12" t="inlineStr">
+        <is>
+          <t>Recreation</t>
         </is>
       </c>
     </row>
@@ -9588,7 +9608,7 @@
       <c r="C45" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(ENG)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
@@ -9599,40 +9619,40 @@
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
+          <t>MAHESWARI
+(COMP)</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="inlineStr">
+        <is>
+          <t>SAI LAKSHMI
+(HIN)</t>
+        </is>
+      </c>
+      <c r="G45" s="7" t="inlineStr">
+        <is>
+          <t>LALITHA
+(EVS)</t>
+        </is>
+      </c>
+      <c r="H45" s="7" t="inlineStr">
+        <is>
           <t>MAHA
 (ENG)</t>
         </is>
       </c>
-      <c r="F45" s="7" t="inlineStr">
-        <is>
-          <t>MAHESWARI
-(COMP)</t>
-        </is>
-      </c>
-      <c r="G45" s="7" t="inlineStr">
+      <c r="I45" s="7" t="inlineStr">
         <is>
           <t>TULASI
 (MATH)</t>
         </is>
       </c>
-      <c r="H45" s="7" t="inlineStr">
+      <c r="J45" s="7" t="inlineStr">
         <is>
           <t>FATHIMA
 (HIN)</t>
         </is>
       </c>
-      <c r="I45" s="7" t="inlineStr">
-        <is>
-          <t>LALITHA
-(EVS)</t>
-        </is>
-      </c>
-      <c r="J45" s="7" t="inlineStr">
-        <is>
-          <t>PALLAVI
-(SOC)</t>
-        </is>
-      </c>
       <c r="K45" s="7" t="inlineStr">
         <is>
           <t>RAVI
@@ -9641,20 +9661,20 @@
       </c>
       <c r="L45" s="7" t="inlineStr">
         <is>
+          <t>SANGEETHA
+(MATH)</t>
+        </is>
+      </c>
+      <c r="M45" s="7" t="inlineStr">
+        <is>
+          <t>RIYA
+(HIN)</t>
+        </is>
+      </c>
+      <c r="N45" s="7" t="inlineStr">
+        <is>
           <t>SUNITHA
 (SOC)</t>
-        </is>
-      </c>
-      <c r="M45" s="7" t="inlineStr">
-        <is>
-          <t>RIYA
-(HIN)</t>
-        </is>
-      </c>
-      <c r="N45" s="7" t="inlineStr">
-        <is>
-          <t>D.V.RAO
-(TEL)</t>
         </is>
       </c>
     </row>
@@ -9665,68 +9685,68 @@
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>SITHA
-(MATH)</t>
+          <t>NAGAMANI
+(TEL)</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>SAI LAKSHMI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
         <is>
           <t>BHAVANI
 (MATH)</t>
         </is>
       </c>
-      <c r="E46" s="7" t="inlineStr">
-        <is>
-          <t>SAI LAKSHMI
-(EVS)</t>
-        </is>
-      </c>
       <c r="F46" s="7" t="inlineStr">
+        <is>
+          <t>MAHESWARI
+(COMP)</t>
+        </is>
+      </c>
+      <c r="G46" s="7" t="inlineStr">
         <is>
           <t>MAHA
 (ENG)</t>
         </is>
       </c>
-      <c r="G46" s="7" t="inlineStr">
-        <is>
-          <t>PALLAVI
-(SOC)</t>
-        </is>
-      </c>
       <c r="H46" s="7" t="inlineStr">
+        <is>
+          <t>FATHIMA
+(HIN)</t>
+        </is>
+      </c>
+      <c r="I46" s="7" t="inlineStr">
         <is>
           <t>SWATHI
 (TEL)</t>
         </is>
       </c>
-      <c r="I46" s="7" t="inlineStr">
-        <is>
-          <t>FATHIMA
-(HIN)</t>
-        </is>
-      </c>
       <c r="J46" s="7" t="inlineStr">
         <is>
           <t>RAVI
-(GRAM)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="K46" s="7" t="inlineStr">
         <is>
           <t>LALITHA
-(CHEM)</t>
+(PHY)</t>
         </is>
       </c>
       <c r="L46" s="7" t="inlineStr">
-        <is>
-          <t>SANGEETHA
-(MATH)</t>
-        </is>
-      </c>
-      <c r="M46" s="7" t="inlineStr">
         <is>
           <t>SUNITHA
 (SOC)</t>
+        </is>
+      </c>
+      <c r="M46" s="7" t="inlineStr">
+        <is>
+          <t>CHALAPATHI
+(BIO)</t>
         </is>
       </c>
       <c r="N46" s="7" t="inlineStr">
@@ -9744,33 +9764,33 @@
       <c r="C47" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(ORAL)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
-        <is>
-          <t>BHAVANI
-(EVS)</t>
-        </is>
-      </c>
-      <c r="E47" s="7" t="inlineStr">
-        <is>
-          <t>SAI LAKSHMI
-(HIN)</t>
-        </is>
-      </c>
-      <c r="F47" s="7" t="inlineStr">
         <is>
           <t>NAGAMANI
 (TEL)</t>
         </is>
       </c>
-      <c r="G47" s="7" t="inlineStr">
+      <c r="E47" s="7" t="inlineStr">
         <is>
           <t>MAHA
 (ENG)</t>
         </is>
       </c>
+      <c r="F47" s="7" t="inlineStr">
+        <is>
+          <t>TULASI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="G47" s="7" t="inlineStr">
+        <is>
+          <t>RIYA
+(HIN)</t>
+        </is>
+      </c>
       <c r="H47" s="7" t="inlineStr">
         <is>
           <t>LALITHA
@@ -9779,8 +9799,8 @@
       </c>
       <c r="I47" s="7" t="inlineStr">
         <is>
-          <t>TULASI
-(MATH)</t>
+          <t>PALLAVI
+(SOC)</t>
         </is>
       </c>
       <c r="J47" s="7" t="inlineStr">
@@ -9791,8 +9811,8 @@
       </c>
       <c r="K47" s="7" t="inlineStr">
         <is>
-          <t>D.V.RAO
-(TEL)</t>
+          <t>SANGEETHA
+(MATH)</t>
         </is>
       </c>
       <c r="L47" s="7" t="inlineStr">
@@ -9801,16 +9821,15 @@
 (ENG)</t>
         </is>
       </c>
-      <c r="M47" s="7" t="inlineStr">
+      <c r="M47" s="12" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+      <c r="N47" s="7" t="inlineStr">
         <is>
           <t>CHALAPATHI
 (BIO)</t>
-        </is>
-      </c>
-      <c r="N47" s="7" t="inlineStr">
-        <is>
-          <t>SUNITHA
-(SOC)</t>
         </is>
       </c>
     </row>
@@ -9821,62 +9840,62 @@
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
+          <t>SITHA
+(MATH)</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
+          <t>SAI LAKSHMI
+(ENG)</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
+          <t>BHAVANI
+(MATH)</t>
         </is>
       </c>
       <c r="F48" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
+          <t>MAHA
+(ENG)</t>
         </is>
       </c>
       <c r="G48" s="7" t="inlineStr">
-        <is>
-          <t>P.E
-(P.E.T)</t>
-        </is>
-      </c>
-      <c r="H48" s="7" t="inlineStr">
-        <is>
-          <t>P.E
-(P.E.T)</t>
-        </is>
-      </c>
-      <c r="I48" s="7" t="inlineStr">
         <is>
           <t>PALLAVI
 (SOC)</t>
         </is>
       </c>
-      <c r="J48" s="7" t="inlineStr">
-        <is>
-          <t>LALITHA
-(CHEM)</t>
-        </is>
-      </c>
-      <c r="K48" s="7" t="inlineStr">
+      <c r="H48" s="7" t="inlineStr">
+        <is>
+          <t>SANGEETHA
+(G.K)</t>
+        </is>
+      </c>
+      <c r="I48" s="7" t="inlineStr">
         <is>
           <t>FATHIMA
 (HIN)</t>
         </is>
       </c>
+      <c r="J48" s="7" t="inlineStr">
+        <is>
+          <t>LALITHA
+(PHY)</t>
+        </is>
+      </c>
+      <c r="K48" s="7" t="inlineStr">
+        <is>
+          <t>D.V.RAO
+(TEL)</t>
+        </is>
+      </c>
       <c r="L48" s="7" t="inlineStr">
         <is>
-          <t>SANGEETHA
-(MATH)</t>
+          <t>CHALAPATHI
+(BIO)</t>
         </is>
       </c>
       <c r="M48" s="7" t="inlineStr">
@@ -9887,8 +9906,8 @@
       </c>
       <c r="N48" s="7" t="inlineStr">
         <is>
-          <t>CHALAPATHI
-(BIO)</t>
+          <t>RIYA
+(HIN)</t>
         </is>
       </c>
     </row>

--- a/NRCS/Output/NRCS_Timetable_Final.xlsx
+++ b/NRCS/Output/NRCS_Timetable_Final.xlsx
@@ -659,18 +659,22 @@
       <c r="C5" s="7" t="inlineStr"/>
       <c r="D5" s="7" t="inlineStr">
         <is>
+          <t>U.K.G (MATH)</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>U.K.G (MATH)</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (G.K)</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
           <t>Class 1 (MATH)</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (EVS)</t>
-        </is>
-      </c>
-      <c r="F5" s="7" t="inlineStr"/>
-      <c r="G5" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (EVS)</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr"/>
@@ -688,7 +692,7 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>U.K.G (EVS)</t>
+          <t>U.K.G (MATH)</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
@@ -696,23 +700,19 @@
           <t>Class 1 (MATH)</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr"/>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (G.K)</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr"/>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>U.K.G (MATH)</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (MATH)</t>
-        </is>
-      </c>
       <c r="G6" s="7" t="inlineStr"/>
-      <c r="H6" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (MATH)</t>
-        </is>
-      </c>
+      <c r="H6" s="7" t="inlineStr"/>
       <c r="I6" s="8" t="inlineStr">
         <is>
           <t>U.K.G</t>
@@ -727,31 +727,31 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
+          <t>U.K.G (EVS)</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Class 1 (MATH)</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
           <t>U.K.G (MATH)</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (EVS)</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (MATH)</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr"/>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>Class 1 (MATH)</t>
-        </is>
-      </c>
-      <c r="G7" s="7" t="inlineStr"/>
-      <c r="H7" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (EVS)</t>
-        </is>
-      </c>
+          <t>U.K.G (MATH)</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>U.K.G (MATH)</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr"/>
       <c r="I7" s="8" t="inlineStr">
         <is>
           <t>U.K.G</t>
@@ -766,25 +766,21 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>U.K.G (MATH)</t>
+          <t>U.K.G (EVS)</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr"/>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>U.K.G (MATH)</t>
+          <t>Class 1 (MATH)</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (G.K)</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
           <t>U.K.G (EVS)</t>
         </is>
       </c>
+      <c r="F8" s="7" t="inlineStr"/>
       <c r="G8" s="7" t="inlineStr"/>
       <c r="H8" s="7" t="inlineStr"/>
       <c r="I8" s="8" t="inlineStr">
@@ -801,27 +797,31 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>U.K.G (MATH)</t>
+          <t>U.K.G (EVS)</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>U.K.G (MATH)</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (MATH)</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="inlineStr"/>
+          <t>Class 1 (MATH)</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr"/>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>U.K.G (EVS)</t>
+        </is>
+      </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>U.K.G (MATH)</t>
+          <t>Class 1 (MATH)</t>
         </is>
       </c>
       <c r="G9" s="7" t="inlineStr"/>
-      <c r="H9" s="7" t="inlineStr"/>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>U.K.G (EVS)</t>
+        </is>
+      </c>
       <c r="I9" s="8" t="inlineStr">
         <is>
           <t>U.K.G</t>
@@ -836,18 +836,18 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
+          <t>U.K.G (EVS)</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr"/>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
           <t>U.K.G (MATH)</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (G.K)</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr"/>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>U.K.G (EVS)</t>
+          <t>U.K.G (MATH)</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
@@ -855,12 +855,12 @@
           <t>Class 1 (MATH)</t>
         </is>
       </c>
-      <c r="G10" s="7" t="inlineStr"/>
-      <c r="H10" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (MATH)</t>
-        </is>
-      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>U.K.G (MATH)</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr"/>
       <c r="I10" s="8" t="inlineStr">
         <is>
           <t>U.K.G</t>
@@ -936,14 +936,10 @@
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr"/>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (PHY)</t>
-        </is>
-      </c>
+      <c r="C14" s="7" t="inlineStr"/>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (CHEM)</t>
+          <t>Class 9 (CHEM)</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr"/>
@@ -966,7 +962,7 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Class 10 (PHY)</t>
+          <t>Class 10 (CHEM)</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr"/>
@@ -983,17 +979,17 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Class 10 (CHEM)</t>
+          <t>Class 10 (PHY)</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (CHEM)</t>
+          <t>Class 8 (PHY)</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>Class 9 (CHEM)</t>
+          <t>Class 9 (PHY)</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr"/>
@@ -1014,7 +1010,11 @@
           <t>Class 9 (CHEM)</t>
         </is>
       </c>
-      <c r="D17" s="7" t="inlineStr"/>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (CHEM)</t>
+        </is>
+      </c>
       <c r="E17" s="7" t="inlineStr"/>
       <c r="F17" s="7" t="inlineStr"/>
       <c r="G17" s="7" t="inlineStr"/>
@@ -1027,15 +1027,19 @@
           <t>FRI</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr"/>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (PHY)</t>
+        </is>
+      </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
+          <t>Class 8 (CHEM)</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
           <t>Class 8 (PHY)</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (CHEM)</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr"/>
@@ -1051,14 +1055,10 @@
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr"/>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (PHY)</t>
-        </is>
-      </c>
+      <c r="C19" s="7" t="inlineStr"/>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Class 9 (PHY)</t>
+          <t>Class 10 (CHEM)</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr"/>
@@ -1139,13 +1139,21 @@
       <c r="C23" s="7" t="inlineStr"/>
       <c r="D23" s="7" t="inlineStr"/>
       <c r="E23" s="7" t="inlineStr"/>
-      <c r="F23" s="7" t="inlineStr"/>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (BIO)</t>
+        </is>
+      </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
+          <t>Class 10 (BIO)</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
           <t>Class 8 (BIO)</t>
         </is>
       </c>
-      <c r="H23" s="7" t="inlineStr"/>
       <c r="I23" s="7" t="inlineStr"/>
     </row>
     <row r="24">
@@ -1158,13 +1166,17 @@
       <c r="C24" s="7" t="inlineStr"/>
       <c r="D24" s="7" t="inlineStr"/>
       <c r="E24" s="7" t="inlineStr"/>
-      <c r="F24" s="7" t="inlineStr"/>
-      <c r="G24" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (BIO)</t>
-        </is>
-      </c>
-      <c r="H24" s="7" t="inlineStr"/>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (BIO)</t>
+        </is>
+      </c>
+      <c r="G24" s="7" t="inlineStr"/>
+      <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (BIO)</t>
+        </is>
+      </c>
       <c r="I24" s="7" t="inlineStr"/>
     </row>
     <row r="25">
@@ -1179,15 +1191,11 @@
       <c r="E25" s="7" t="inlineStr"/>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>Class 10 (BIO)</t>
+          <t>Class 8 (BIO)</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr"/>
-      <c r="H25" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (BIO)</t>
-        </is>
-      </c>
+      <c r="H25" s="7" t="inlineStr"/>
       <c r="I25" s="7" t="inlineStr"/>
     </row>
     <row r="26">
@@ -1200,13 +1208,17 @@
       <c r="C26" s="7" t="inlineStr"/>
       <c r="D26" s="7" t="inlineStr"/>
       <c r="E26" s="7" t="inlineStr"/>
-      <c r="F26" s="7" t="inlineStr"/>
-      <c r="G26" s="7" t="inlineStr">
+      <c r="F26" s="7" t="inlineStr">
         <is>
           <t>Class 10 (BIO)</t>
         </is>
       </c>
-      <c r="H26" s="7" t="inlineStr"/>
+      <c r="G26" s="7" t="inlineStr"/>
+      <c r="H26" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (BIO)</t>
+        </is>
+      </c>
       <c r="I26" s="7" t="inlineStr"/>
     </row>
     <row r="27">
@@ -1220,14 +1232,10 @@
       <c r="D27" s="7" t="inlineStr"/>
       <c r="E27" s="7" t="inlineStr"/>
       <c r="F27" s="7" t="inlineStr"/>
-      <c r="G27" s="7" t="inlineStr">
+      <c r="G27" s="7" t="inlineStr"/>
+      <c r="H27" s="7" t="inlineStr">
         <is>
           <t>Class 10 (BIO)</t>
-        </is>
-      </c>
-      <c r="H27" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (BIO)</t>
         </is>
       </c>
       <c r="I27" s="7" t="inlineStr"/>
@@ -1242,21 +1250,13 @@
       <c r="C28" s="7" t="inlineStr"/>
       <c r="D28" s="7" t="inlineStr"/>
       <c r="E28" s="7" t="inlineStr"/>
-      <c r="F28" s="7" t="inlineStr">
+      <c r="F28" s="7" t="inlineStr"/>
+      <c r="G28" s="7" t="inlineStr">
         <is>
           <t>Class 9 (BIO)</t>
         </is>
       </c>
-      <c r="G28" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (BIO)</t>
-        </is>
-      </c>
-      <c r="H28" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (BIO)</t>
-        </is>
-      </c>
+      <c r="H28" s="7" t="inlineStr"/>
       <c r="I28" s="7" t="inlineStr"/>
     </row>
     <row r="30">
@@ -1332,24 +1332,24 @@
           <t>Class 9 (TEL)</t>
         </is>
       </c>
-      <c r="C32" s="7" t="inlineStr">
+      <c r="C32" s="7" t="inlineStr"/>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (TEL)</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (TEL)</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr"/>
+      <c r="G32" s="7" t="inlineStr">
         <is>
           <t>Class 7 (TEL)</t>
         </is>
       </c>
-      <c r="D32" s="7" t="inlineStr"/>
-      <c r="E32" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (TEL)</t>
-        </is>
-      </c>
-      <c r="F32" s="7" t="inlineStr"/>
-      <c r="G32" s="7" t="inlineStr"/>
-      <c r="H32" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (TEL)</t>
-        </is>
-      </c>
+      <c r="H32" s="7" t="inlineStr"/>
       <c r="I32" s="8" t="inlineStr">
         <is>
           <t>Class 9</t>
@@ -1368,21 +1368,21 @@
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr"/>
-      <c r="D33" s="7" t="inlineStr">
+      <c r="D33" s="7" t="inlineStr"/>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (TEL)</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr"/>
+      <c r="G33" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (TEL)</t>
+        </is>
+      </c>
+      <c r="H33" s="7" t="inlineStr">
         <is>
           <t>Class 7 (TEL)</t>
-        </is>
-      </c>
-      <c r="E33" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (TEL)</t>
-        </is>
-      </c>
-      <c r="F33" s="7" t="inlineStr"/>
-      <c r="G33" s="7" t="inlineStr"/>
-      <c r="H33" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (TEL)</t>
         </is>
       </c>
       <c r="I33" s="8" t="inlineStr">
@@ -1437,23 +1437,23 @@
           <t>Class 9 (TEL)</t>
         </is>
       </c>
-      <c r="C35" s="7" t="inlineStr"/>
-      <c r="D35" s="7" t="inlineStr">
+      <c r="C35" s="7" t="inlineStr">
         <is>
           <t>Class 10 (TEL)</t>
         </is>
       </c>
+      <c r="D35" s="7" t="inlineStr"/>
       <c r="E35" s="7" t="inlineStr">
         <is>
           <t>Class 8 (TEL)</t>
         </is>
       </c>
-      <c r="F35" s="7" t="inlineStr">
+      <c r="F35" s="7" t="inlineStr"/>
+      <c r="G35" s="7" t="inlineStr">
         <is>
           <t>Class 7 (TEL)</t>
         </is>
       </c>
-      <c r="G35" s="7" t="inlineStr"/>
       <c r="H35" s="7" t="inlineStr"/>
       <c r="I35" s="8" t="inlineStr">
         <is>
@@ -1479,17 +1479,17 @@
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
+          <t>Class 7 (TEL)</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr"/>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
           <t>Class 8 (TEL)</t>
         </is>
       </c>
-      <c r="E36" s="7" t="inlineStr"/>
-      <c r="F36" s="7" t="inlineStr"/>
       <c r="G36" s="7" t="inlineStr"/>
-      <c r="H36" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (TEL)</t>
-        </is>
-      </c>
+      <c r="H36" s="7" t="inlineStr"/>
       <c r="I36" s="8" t="inlineStr">
         <is>
           <t>Class 9</t>
@@ -1509,22 +1509,22 @@
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
+          <t>Class 7 (TEL)</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr"/>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (TEL)</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
           <t>Class 10 (TEL)</t>
         </is>
       </c>
-      <c r="D37" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (TEL)</t>
-        </is>
-      </c>
-      <c r="E37" s="7" t="inlineStr"/>
-      <c r="F37" s="7" t="inlineStr"/>
       <c r="G37" s="7" t="inlineStr"/>
-      <c r="H37" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (TEL)</t>
-        </is>
-      </c>
+      <c r="H37" s="7" t="inlineStr"/>
       <c r="I37" s="8" t="inlineStr">
         <is>
           <t>Class 9</t>
@@ -1604,28 +1604,20 @@
           <t>Class 8 (HIN)</t>
         </is>
       </c>
-      <c r="C41" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (HIN)</t>
-        </is>
-      </c>
-      <c r="D41" s="7" t="inlineStr"/>
-      <c r="E41" s="7" t="inlineStr">
+      <c r="C41" s="7" t="inlineStr"/>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (G.K)</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr"/>
+      <c r="F41" s="7" t="inlineStr"/>
+      <c r="G41" s="7" t="inlineStr">
         <is>
           <t>Class 4 (HIN)</t>
         </is>
       </c>
-      <c r="F41" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (HIN)</t>
-        </is>
-      </c>
-      <c r="G41" s="7" t="inlineStr"/>
-      <c r="H41" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (HIN)</t>
-        </is>
-      </c>
+      <c r="H41" s="7" t="inlineStr"/>
       <c r="I41" s="8" t="inlineStr">
         <is>
           <t>Class 8</t>
@@ -1640,31 +1632,31 @@
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (HIN)</t>
-        </is>
-      </c>
-      <c r="C42" s="7" t="inlineStr">
+          <t>Class 8 (G.K)</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr"/>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (HIN)</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (HIN)</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (HIN)</t>
+        </is>
+      </c>
+      <c r="G42" s="7" t="inlineStr"/>
+      <c r="H42" s="7" t="inlineStr">
         <is>
           <t>Class 6 (HIN)</t>
         </is>
       </c>
-      <c r="D42" s="7" t="inlineStr"/>
-      <c r="E42" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (HIN)</t>
-        </is>
-      </c>
-      <c r="F42" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (HIN)</t>
-        </is>
-      </c>
-      <c r="G42" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (G.K)</t>
-        </is>
-      </c>
-      <c r="H42" s="7" t="inlineStr"/>
       <c r="I42" s="8" t="inlineStr">
         <is>
           <t>Class 8</t>
@@ -1687,21 +1679,21 @@
           <t>Class 4 (HIN)</t>
         </is>
       </c>
-      <c r="D43" s="7" t="inlineStr"/>
-      <c r="E43" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (HIN)</t>
-        </is>
-      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (HIN)</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr"/>
       <c r="F43" s="7" t="inlineStr"/>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (HIN)</t>
+          <t>Class 7 (HIN)</t>
         </is>
       </c>
       <c r="H43" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (HIN)</t>
+          <t>Class 5 (HIN)</t>
         </is>
       </c>
       <c r="I43" s="8" t="inlineStr">
@@ -1723,18 +1715,26 @@
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
+          <t>Class 5 (HIN)</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr"/>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (HIN)</t>
+        </is>
+      </c>
+      <c r="F44" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (HIN)</t>
+        </is>
+      </c>
+      <c r="G44" s="7" t="inlineStr"/>
+      <c r="H44" s="7" t="inlineStr">
+        <is>
           <t>Class 7 (HIN)</t>
         </is>
       </c>
-      <c r="D44" s="7" t="inlineStr"/>
-      <c r="E44" s="7" t="inlineStr"/>
-      <c r="F44" s="7" t="inlineStr"/>
-      <c r="G44" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (HIN)</t>
-        </is>
-      </c>
-      <c r="H44" s="7" t="inlineStr"/>
       <c r="I44" s="8" t="inlineStr">
         <is>
           <t>Class 8</t>
@@ -1752,24 +1752,24 @@
           <t>Class 8 (HIN)</t>
         </is>
       </c>
-      <c r="C45" s="7" t="inlineStr"/>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (HIN)</t>
+        </is>
+      </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
+          <t>Class 5 (HIN)</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr"/>
+      <c r="F45" s="7" t="inlineStr">
+        <is>
           <t>Class 6 (HIN)</t>
         </is>
       </c>
-      <c r="E45" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (HIN)</t>
-        </is>
-      </c>
-      <c r="F45" s="7" t="inlineStr"/>
       <c r="G45" s="7" t="inlineStr"/>
-      <c r="H45" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (HIN)</t>
-        </is>
-      </c>
+      <c r="H45" s="7" t="inlineStr"/>
       <c r="I45" s="8" t="inlineStr">
         <is>
           <t>Class 8</t>
@@ -1784,29 +1784,29 @@
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (G.K)</t>
+          <t>Class 8 (HIN)</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr"/>
       <c r="D46" s="7" t="inlineStr">
         <is>
+          <t>Class 6 (HIN)</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
           <t>Class 7 (HIN)</t>
         </is>
       </c>
-      <c r="E46" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (HIN)</t>
-        </is>
-      </c>
-      <c r="F46" s="7" t="inlineStr">
+      <c r="F46" s="7" t="inlineStr"/>
+      <c r="G46" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (HIN)</t>
+        </is>
+      </c>
+      <c r="H46" s="7" t="inlineStr">
         <is>
           <t>Class 4 (HIN)</t>
-        </is>
-      </c>
-      <c r="G46" s="7" t="inlineStr"/>
-      <c r="H46" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (HIN)</t>
         </is>
       </c>
       <c r="I46" s="8" t="inlineStr">
@@ -1883,19 +1883,15 @@
           <t>MON</t>
         </is>
       </c>
-      <c r="B50" s="7" t="inlineStr">
+      <c r="B50" s="7" t="inlineStr"/>
+      <c r="C50" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (MATH)</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="inlineStr">
         <is>
           <t>Class 10 (MATH)</t>
-        </is>
-      </c>
-      <c r="C50" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (MATH)</t>
-        </is>
-      </c>
-      <c r="D50" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (MATH)</t>
         </is>
       </c>
       <c r="E50" s="7" t="inlineStr"/>
@@ -1956,12 +1952,12 @@
           <t>THU</t>
         </is>
       </c>
-      <c r="B53" s="7" t="inlineStr"/>
-      <c r="C53" s="7" t="inlineStr">
+      <c r="B53" s="7" t="inlineStr">
         <is>
           <t>Class 10 (MATH)</t>
         </is>
       </c>
+      <c r="C53" s="7" t="inlineStr"/>
       <c r="D53" s="7" t="inlineStr">
         <is>
           <t>Class 9 (MATH)</t>
@@ -1979,19 +1975,15 @@
           <t>FRI</t>
         </is>
       </c>
-      <c r="B54" s="7" t="inlineStr">
+      <c r="B54" s="7" t="inlineStr"/>
+      <c r="C54" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (MATH)</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="inlineStr">
         <is>
           <t>Class 10 (MATH)</t>
-        </is>
-      </c>
-      <c r="C54" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (MATH)</t>
-        </is>
-      </c>
-      <c r="D54" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (MATH)</t>
         </is>
       </c>
       <c r="E54" s="7" t="inlineStr"/>
@@ -2011,8 +2003,16 @@
           <t>Class 10 (MATH)</t>
         </is>
       </c>
-      <c r="C55" s="7" t="inlineStr"/>
-      <c r="D55" s="7" t="inlineStr"/>
+      <c r="C55" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (MATH)</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (MATH)</t>
+        </is>
+      </c>
       <c r="E55" s="7" t="inlineStr"/>
       <c r="F55" s="7" t="inlineStr"/>
       <c r="G55" s="7" t="inlineStr"/>
@@ -2088,17 +2088,29 @@
         </is>
       </c>
       <c r="B59" s="7" t="inlineStr"/>
-      <c r="C59" s="7" t="inlineStr"/>
-      <c r="D59" s="7" t="inlineStr"/>
-      <c r="E59" s="7" t="inlineStr"/>
+      <c r="C59" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (BIO)</t>
+        </is>
+      </c>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (EVS)</t>
+        </is>
+      </c>
+      <c r="E59" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (PHY)</t>
+        </is>
+      </c>
       <c r="F59" s="7" t="inlineStr">
         <is>
-          <t>Class 3 (EVS)</t>
+          <t>Class 4 (EVS)</t>
         </is>
       </c>
       <c r="G59" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (EVS)</t>
+          <t>Class 6 (CHEM)</t>
         </is>
       </c>
       <c r="H59" s="7" t="inlineStr">
@@ -2115,34 +2127,26 @@
         </is>
       </c>
       <c r="B60" s="7" t="inlineStr"/>
-      <c r="C60" s="7" t="inlineStr">
+      <c r="C60" s="7" t="inlineStr"/>
+      <c r="D60" s="7" t="inlineStr">
         <is>
           <t>Class 7 (CHEM)</t>
         </is>
       </c>
-      <c r="D60" s="7" t="inlineStr">
+      <c r="E60" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (EVS)</t>
+        </is>
+      </c>
+      <c r="F60" s="7" t="inlineStr">
         <is>
           <t>Class 4 (EVS)</t>
         </is>
       </c>
-      <c r="E60" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (EVS)</t>
-        </is>
-      </c>
-      <c r="F60" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (BIO)</t>
-        </is>
-      </c>
-      <c r="G60" s="7" t="inlineStr">
+      <c r="G60" s="7" t="inlineStr"/>
+      <c r="H60" s="7" t="inlineStr">
         <is>
           <t>Class 3 (EVS)</t>
-        </is>
-      </c>
-      <c r="H60" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (BIO)</t>
         </is>
       </c>
       <c r="I60" s="7" t="inlineStr"/>
@@ -2156,32 +2160,32 @@
       <c r="B61" s="7" t="inlineStr"/>
       <c r="C61" s="7" t="inlineStr">
         <is>
+          <t>Class 7 (PHY)</t>
+        </is>
+      </c>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (EVS)</t>
+        </is>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
           <t>Class 5 (EVS)</t>
         </is>
       </c>
-      <c r="D61" s="7" t="inlineStr">
+      <c r="F61" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (PHY)</t>
+        </is>
+      </c>
+      <c r="G61" s="7" t="inlineStr">
         <is>
           <t>Class 4 (EVS)</t>
         </is>
       </c>
-      <c r="E61" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (CHEM)</t>
-        </is>
-      </c>
-      <c r="F61" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (PHY)</t>
-        </is>
-      </c>
-      <c r="G61" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (BIO)</t>
-        </is>
-      </c>
       <c r="H61" s="7" t="inlineStr">
         <is>
-          <t>Class 3 (EVS)</t>
+          <t>Class 6 (BIO)</t>
         </is>
       </c>
       <c r="I61" s="7" t="inlineStr"/>
@@ -2195,30 +2199,34 @@
       <c r="B62" s="7" t="inlineStr"/>
       <c r="C62" s="7" t="inlineStr">
         <is>
+          <t>Class 7 (CHEM)</t>
+        </is>
+      </c>
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (EVS)</t>
+        </is>
+      </c>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (EVS)</t>
+        </is>
+      </c>
+      <c r="F62" s="7" t="inlineStr">
+        <is>
           <t>Class 6 (BIO)</t>
         </is>
       </c>
-      <c r="D62" s="7" t="inlineStr">
+      <c r="G62" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (PHY)</t>
+        </is>
+      </c>
+      <c r="H62" s="7" t="inlineStr">
         <is>
           <t>Class 3 (EVS)</t>
         </is>
       </c>
-      <c r="E62" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (EVS)</t>
-        </is>
-      </c>
-      <c r="F62" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (EVS)</t>
-        </is>
-      </c>
-      <c r="G62" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (CHEM)</t>
-        </is>
-      </c>
-      <c r="H62" s="7" t="inlineStr"/>
       <c r="I62" s="7" t="inlineStr"/>
     </row>
     <row r="63">
@@ -2230,32 +2238,28 @@
       <c r="B63" s="7" t="inlineStr"/>
       <c r="C63" s="7" t="inlineStr">
         <is>
+          <t>Class 5 (EVS)</t>
+        </is>
+      </c>
+      <c r="D63" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (EVS)</t>
+        </is>
+      </c>
+      <c r="E63" s="7" t="inlineStr"/>
+      <c r="F63" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (BIO)</t>
+        </is>
+      </c>
+      <c r="G63" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (BIO)</t>
+        </is>
+      </c>
+      <c r="H63" s="7" t="inlineStr">
+        <is>
           <t>Class 4 (EVS)</t>
-        </is>
-      </c>
-      <c r="D63" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (PHY)</t>
-        </is>
-      </c>
-      <c r="E63" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (EVS)</t>
-        </is>
-      </c>
-      <c r="F63" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (EVS)</t>
-        </is>
-      </c>
-      <c r="G63" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (BIO)</t>
-        </is>
-      </c>
-      <c r="H63" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (CHEM)</t>
         </is>
       </c>
       <c r="I63" s="7" t="inlineStr"/>
@@ -2269,32 +2273,28 @@
       <c r="B64" s="7" t="inlineStr"/>
       <c r="C64" s="7" t="inlineStr">
         <is>
+          <t>Class 6 (CHEM)</t>
+        </is>
+      </c>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
           <t>Class 7 (BIO)</t>
         </is>
       </c>
-      <c r="D64" s="7" t="inlineStr">
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (EVS)</t>
+        </is>
+      </c>
+      <c r="F64" s="7" t="inlineStr"/>
+      <c r="G64" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (EVS)</t>
+        </is>
+      </c>
+      <c r="H64" s="7" t="inlineStr">
         <is>
           <t>Class 5 (EVS)</t>
-        </is>
-      </c>
-      <c r="E64" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (EVS)</t>
-        </is>
-      </c>
-      <c r="F64" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (PHY)</t>
-        </is>
-      </c>
-      <c r="G64" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (EVS)</t>
-        </is>
-      </c>
-      <c r="H64" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (PHY)</t>
         </is>
       </c>
       <c r="I64" s="7" t="inlineStr"/>
@@ -2369,33 +2369,33 @@
       </c>
       <c r="B68" s="7" t="inlineStr">
         <is>
+          <t>Class 5 (GRAM)</t>
+        </is>
+      </c>
+      <c r="C68" s="7" t="inlineStr"/>
+      <c r="D68" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (ENG)</t>
+        </is>
+      </c>
+      <c r="E68" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (ENG)</t>
+        </is>
+      </c>
+      <c r="F68" s="7" t="inlineStr">
+        <is>
+          <t>Class 1 (ENG)</t>
+        </is>
+      </c>
+      <c r="G68" s="7" t="inlineStr">
+        <is>
           <t>Class 5 (ENG)</t>
         </is>
       </c>
-      <c r="C68" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (ENG)</t>
-        </is>
-      </c>
-      <c r="D68" s="7" t="inlineStr">
+      <c r="H68" s="7" t="inlineStr">
         <is>
           <t>Class 4 (ENG)</t>
-        </is>
-      </c>
-      <c r="E68" s="7" t="inlineStr"/>
-      <c r="F68" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (ENG)</t>
-        </is>
-      </c>
-      <c r="G68" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (GRAM)</t>
-        </is>
-      </c>
-      <c r="H68" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (ENG)</t>
         </is>
       </c>
       <c r="I68" s="7" t="inlineStr"/>
@@ -2413,28 +2413,24 @@
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (GRAM)</t>
-        </is>
-      </c>
-      <c r="D69" s="7" t="inlineStr">
+          <t>Class 2 (ENG)</t>
+        </is>
+      </c>
+      <c r="D69" s="7" t="inlineStr"/>
+      <c r="E69" s="7" t="inlineStr">
         <is>
           <t>Class 1 (ENG)</t>
         </is>
       </c>
-      <c r="E69" s="7" t="inlineStr"/>
       <c r="F69" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (ENG)</t>
-        </is>
-      </c>
-      <c r="G69" s="7" t="inlineStr">
+          <t>Class 3 (ENG)</t>
+        </is>
+      </c>
+      <c r="G69" s="7" t="inlineStr"/>
+      <c r="H69" s="7" t="inlineStr">
         <is>
           <t>Class 4 (ENG)</t>
-        </is>
-      </c>
-      <c r="H69" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (ENG)</t>
         </is>
       </c>
       <c r="I69" s="7" t="inlineStr"/>
@@ -2450,23 +2446,27 @@
           <t>Class 5 (ENG)</t>
         </is>
       </c>
-      <c r="C70" s="7" t="inlineStr">
+      <c r="C70" s="7" t="inlineStr"/>
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (ENG)</t>
+        </is>
+      </c>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (ENG)</t>
+        </is>
+      </c>
+      <c r="F70" s="7" t="inlineStr">
         <is>
           <t>Class 1 (ENG)</t>
         </is>
       </c>
-      <c r="D70" s="7" t="inlineStr"/>
-      <c r="E70" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (ENG)</t>
-        </is>
-      </c>
-      <c r="F70" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (ENG)</t>
-        </is>
-      </c>
-      <c r="G70" s="7" t="inlineStr"/>
+      <c r="G70" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (GRAM)</t>
+        </is>
+      </c>
       <c r="H70" s="7" t="inlineStr">
         <is>
           <t>Class 4 (ENG)</t>
@@ -2485,30 +2485,30 @@
           <t>Class 5 (ENG)</t>
         </is>
       </c>
-      <c r="C71" s="7" t="inlineStr"/>
-      <c r="D71" s="7" t="inlineStr">
+      <c r="C71" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (ENG)</t>
+        </is>
+      </c>
+      <c r="D71" s="7" t="inlineStr"/>
+      <c r="E71" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (ENG)</t>
+        </is>
+      </c>
+      <c r="F71" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (ENG)</t>
+        </is>
+      </c>
+      <c r="G71" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (GRAM)</t>
+        </is>
+      </c>
+      <c r="H71" s="7" t="inlineStr">
         <is>
           <t>Class 1 (ENG)</t>
-        </is>
-      </c>
-      <c r="E71" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (ENG)</t>
-        </is>
-      </c>
-      <c r="F71" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (GRAM)</t>
-        </is>
-      </c>
-      <c r="G71" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (ENG)</t>
-        </is>
-      </c>
-      <c r="H71" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (ENG)</t>
         </is>
       </c>
       <c r="I71" s="7" t="inlineStr"/>
@@ -2527,27 +2527,27 @@
       <c r="C72" s="7" t="inlineStr"/>
       <c r="D72" s="7" t="inlineStr">
         <is>
+          <t>Class 2 (ENG)</t>
+        </is>
+      </c>
+      <c r="E72" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (ENG)</t>
+        </is>
+      </c>
+      <c r="F72" s="7" t="inlineStr">
+        <is>
           <t>Class 3 (ENG)</t>
         </is>
       </c>
-      <c r="E72" s="7" t="inlineStr">
+      <c r="G72" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (GRAM)</t>
+        </is>
+      </c>
+      <c r="H72" s="7" t="inlineStr">
         <is>
           <t>Class 1 (ENG)</t>
-        </is>
-      </c>
-      <c r="F72" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (ENG)</t>
-        </is>
-      </c>
-      <c r="G72" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (GRAM)</t>
-        </is>
-      </c>
-      <c r="H72" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (ENG)</t>
         </is>
       </c>
       <c r="I72" s="7" t="inlineStr"/>
@@ -2563,17 +2563,17 @@
           <t>Class 5 (ENG)</t>
         </is>
       </c>
-      <c r="C73" s="7" t="inlineStr">
+      <c r="C73" s="7" t="inlineStr"/>
+      <c r="D73" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (ENG)</t>
+        </is>
+      </c>
+      <c r="E73" s="7" t="inlineStr">
         <is>
           <t>Class 1 (GRAM)</t>
         </is>
       </c>
-      <c r="D73" s="7" t="inlineStr"/>
-      <c r="E73" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (ENG)</t>
-        </is>
-      </c>
       <c r="F73" s="7" t="inlineStr">
         <is>
           <t>Class 3 (ENG)</t>
@@ -2581,12 +2581,12 @@
       </c>
       <c r="G73" s="7" t="inlineStr">
         <is>
+          <t>Class 2 (ENG)</t>
+        </is>
+      </c>
+      <c r="H73" s="7" t="inlineStr">
+        <is>
           <t>Class 1 (ENG)</t>
-        </is>
-      </c>
-      <c r="H73" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (ENG)</t>
         </is>
       </c>
       <c r="I73" s="7" t="inlineStr"/>
@@ -2662,10 +2662,14 @@
       <c r="B77" s="7" t="inlineStr"/>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (COMP)</t>
-        </is>
-      </c>
-      <c r="D77" s="7" t="inlineStr"/>
+          <t>Class 1 (COMP)</t>
+        </is>
+      </c>
+      <c r="D77" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (COMP)</t>
+        </is>
+      </c>
       <c r="E77" s="7" t="inlineStr"/>
       <c r="F77" s="7" t="inlineStr"/>
       <c r="G77" s="7" t="inlineStr"/>
@@ -2680,19 +2684,15 @@
       </c>
       <c r="B78" s="7" t="inlineStr"/>
       <c r="C78" s="7" t="inlineStr"/>
-      <c r="D78" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (COMP)</t>
-        </is>
-      </c>
-      <c r="E78" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (COMP)</t>
-        </is>
-      </c>
+      <c r="D78" s="7" t="inlineStr"/>
+      <c r="E78" s="7" t="inlineStr"/>
       <c r="F78" s="7" t="inlineStr"/>
       <c r="G78" s="7" t="inlineStr"/>
-      <c r="H78" s="7" t="inlineStr"/>
+      <c r="H78" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (COMP)</t>
+        </is>
+      </c>
       <c r="I78" s="7" t="inlineStr"/>
     </row>
     <row r="79">
@@ -2703,14 +2703,14 @@
       </c>
       <c r="B79" s="7" t="inlineStr"/>
       <c r="C79" s="7" t="inlineStr"/>
-      <c r="D79" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (COMP)</t>
-        </is>
-      </c>
+      <c r="D79" s="7" t="inlineStr"/>
       <c r="E79" s="7" t="inlineStr"/>
       <c r="F79" s="7" t="inlineStr"/>
-      <c r="G79" s="7" t="inlineStr"/>
+      <c r="G79" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (COMP)</t>
+        </is>
+      </c>
       <c r="H79" s="7" t="inlineStr"/>
       <c r="I79" s="7" t="inlineStr"/>
     </row>
@@ -2722,10 +2722,14 @@
       </c>
       <c r="B80" s="7" t="inlineStr"/>
       <c r="C80" s="7" t="inlineStr"/>
-      <c r="D80" s="7" t="inlineStr"/>
+      <c r="D80" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (COMP)</t>
+        </is>
+      </c>
       <c r="E80" s="7" t="inlineStr">
         <is>
-          <t>Class 3 (COMP)</t>
+          <t>Class 1 (COMP)</t>
         </is>
       </c>
       <c r="F80" s="7" t="inlineStr"/>
@@ -2740,24 +2744,20 @@
         </is>
       </c>
       <c r="B81" s="7" t="inlineStr"/>
-      <c r="C81" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (COMP)</t>
-        </is>
-      </c>
-      <c r="D81" s="7" t="inlineStr"/>
-      <c r="E81" s="7" t="inlineStr"/>
+      <c r="C81" s="7" t="inlineStr"/>
+      <c r="D81" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (COMP)</t>
+        </is>
+      </c>
+      <c r="E81" s="7" t="inlineStr">
+        <is>
+          <t>Class 1 (COMP)</t>
+        </is>
+      </c>
       <c r="F81" s="7" t="inlineStr"/>
-      <c r="G81" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (COMP)</t>
-        </is>
-      </c>
-      <c r="H81" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (COMP)</t>
-        </is>
-      </c>
+      <c r="G81" s="7" t="inlineStr"/>
+      <c r="H81" s="7" t="inlineStr"/>
       <c r="I81" s="7" t="inlineStr"/>
     </row>
     <row r="82">
@@ -2771,12 +2771,12 @@
       <c r="D82" s="7" t="inlineStr"/>
       <c r="E82" s="7" t="inlineStr">
         <is>
-          <t>Class 1 (COMP)</t>
+          <t>Class 2 (COMP)</t>
         </is>
       </c>
       <c r="F82" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (COMP)</t>
+          <t>Class 4 (COMP)</t>
         </is>
       </c>
       <c r="G82" s="7" t="inlineStr"/>
@@ -2858,26 +2858,18 @@
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
-          <t>Class 1 (G.K)</t>
+          <t>Class 2 (TEL)</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr"/>
-      <c r="E86" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (TEL)</t>
-        </is>
-      </c>
-      <c r="F86" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (TEL)</t>
-        </is>
-      </c>
-      <c r="G86" s="7" t="inlineStr"/>
-      <c r="H86" s="7" t="inlineStr">
+      <c r="E86" s="7" t="inlineStr"/>
+      <c r="F86" s="7" t="inlineStr"/>
+      <c r="G86" s="7" t="inlineStr">
         <is>
           <t>U.K.G (TEL)</t>
         </is>
       </c>
+      <c r="H86" s="7" t="inlineStr"/>
       <c r="I86" s="8" t="inlineStr">
         <is>
           <t>Class 1</t>
@@ -2892,25 +2884,29 @@
       </c>
       <c r="B87" s="7" t="inlineStr">
         <is>
+          <t>Class 1 (G.K)</t>
+        </is>
+      </c>
+      <c r="C87" s="7" t="inlineStr"/>
+      <c r="D87" s="7" t="inlineStr">
+        <is>
+          <t>U.K.G (TEL)</t>
+        </is>
+      </c>
+      <c r="E87" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (TEL)</t>
+        </is>
+      </c>
+      <c r="F87" s="7" t="inlineStr">
+        <is>
           <t>Class 1 (TEL)</t>
         </is>
       </c>
-      <c r="C87" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (TEL)</t>
-        </is>
-      </c>
-      <c r="D87" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (TEL)</t>
-        </is>
-      </c>
-      <c r="E87" s="7" t="inlineStr"/>
-      <c r="F87" s="7" t="inlineStr"/>
       <c r="G87" s="7" t="inlineStr"/>
       <c r="H87" s="7" t="inlineStr">
         <is>
-          <t>U.K.G (TEL)</t>
+          <t>L.K.G (TEL)</t>
         </is>
       </c>
       <c r="I87" s="8" t="inlineStr">
@@ -2932,7 +2928,7 @@
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
-          <t>L.K.G (TEL)</t>
+          <t>Class 2 (TEL)</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr"/>
@@ -2942,10 +2938,14 @@
         </is>
       </c>
       <c r="F88" s="7" t="inlineStr"/>
-      <c r="G88" s="7" t="inlineStr"/>
+      <c r="G88" s="7" t="inlineStr">
+        <is>
+          <t>L.K.G (TEL)</t>
+        </is>
+      </c>
       <c r="H88" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (TEL)</t>
+          <t>Class 1 (G.K)</t>
         </is>
       </c>
       <c r="I88" s="8" t="inlineStr">
@@ -2967,22 +2967,22 @@
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (TEL)</t>
+          <t>U.K.G (TEL)</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr"/>
       <c r="E89" s="7" t="inlineStr">
         <is>
-          <t>Class 1 (G.K)</t>
+          <t>L.K.G (TEL)</t>
         </is>
       </c>
       <c r="F89" s="7" t="inlineStr"/>
-      <c r="G89" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (TEL)</t>
-        </is>
-      </c>
-      <c r="H89" s="7" t="inlineStr"/>
+      <c r="G89" s="7" t="inlineStr"/>
+      <c r="H89" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (TEL)</t>
+        </is>
+      </c>
       <c r="I89" s="8" t="inlineStr">
         <is>
           <t>Class 1</t>
@@ -3003,21 +3003,21 @@
       <c r="C90" s="7" t="inlineStr"/>
       <c r="D90" s="7" t="inlineStr">
         <is>
+          <t>U.K.G (TEL)</t>
+        </is>
+      </c>
+      <c r="E90" s="7" t="inlineStr">
+        <is>
+          <t>L.K.G (TEL)</t>
+        </is>
+      </c>
+      <c r="F90" s="7" t="inlineStr"/>
+      <c r="G90" s="7" t="inlineStr"/>
+      <c r="H90" s="7" t="inlineStr">
+        <is>
           <t>Class 2 (TEL)</t>
         </is>
       </c>
-      <c r="E90" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (TEL)</t>
-        </is>
-      </c>
-      <c r="F90" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (TEL)</t>
-        </is>
-      </c>
-      <c r="G90" s="7" t="inlineStr"/>
-      <c r="H90" s="7" t="inlineStr"/>
       <c r="I90" s="8" t="inlineStr">
         <is>
           <t>Class 1</t>
@@ -3035,24 +3035,24 @@
           <t>Class 1 (TEL)</t>
         </is>
       </c>
-      <c r="C91" s="7" t="inlineStr"/>
+      <c r="C91" s="7" t="inlineStr">
+        <is>
+          <t>U.K.G (TEL)</t>
+        </is>
+      </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
           <t>Class 2 (TEL)</t>
         </is>
       </c>
       <c r="E91" s="7" t="inlineStr"/>
-      <c r="F91" s="7" t="inlineStr">
+      <c r="F91" s="7" t="inlineStr"/>
+      <c r="G91" s="7" t="inlineStr"/>
+      <c r="H91" s="7" t="inlineStr">
         <is>
           <t>L.K.G (TEL)</t>
         </is>
       </c>
-      <c r="G91" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (TEL)</t>
-        </is>
-      </c>
-      <c r="H91" s="7" t="inlineStr"/>
       <c r="I91" s="8" t="inlineStr">
         <is>
           <t>Class 1</t>
@@ -3134,26 +3134,26 @@
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
+          <t>Class 4 (SOC)</t>
+        </is>
+      </c>
+      <c r="D95" s="7" t="inlineStr"/>
+      <c r="E95" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (SOC)</t>
+        </is>
+      </c>
+      <c r="F95" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (SOC)</t>
+        </is>
+      </c>
+      <c r="G95" s="7" t="inlineStr">
+        <is>
           <t>Class 3 (SOC)</t>
         </is>
       </c>
-      <c r="D95" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (SOC)</t>
-        </is>
-      </c>
-      <c r="E95" s="7" t="inlineStr"/>
-      <c r="F95" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (SOC)</t>
-        </is>
-      </c>
-      <c r="G95" s="7" t="inlineStr"/>
-      <c r="H95" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (SOC)</t>
-        </is>
-      </c>
+      <c r="H95" s="7" t="inlineStr"/>
       <c r="I95" s="8" t="inlineStr">
         <is>
           <t>Class 7</t>
@@ -3171,12 +3171,12 @@
           <t>Class 7 (SOC)</t>
         </is>
       </c>
-      <c r="C96" s="7" t="inlineStr"/>
-      <c r="D96" s="7" t="inlineStr">
+      <c r="C96" s="7" t="inlineStr">
         <is>
           <t>Class 3 (SOC)</t>
         </is>
       </c>
+      <c r="D96" s="7" t="inlineStr"/>
       <c r="E96" s="7" t="inlineStr">
         <is>
           <t>Class 4 (SOC)</t>
@@ -3187,12 +3187,12 @@
           <t>Class 6 (SOC)</t>
         </is>
       </c>
-      <c r="G96" s="7" t="inlineStr"/>
-      <c r="H96" s="7" t="inlineStr">
+      <c r="G96" s="7" t="inlineStr">
         <is>
           <t>Class 5 (SOC)</t>
         </is>
       </c>
+      <c r="H96" s="7" t="inlineStr"/>
       <c r="I96" s="8" t="inlineStr">
         <is>
           <t>Class 7</t>
@@ -3210,28 +3210,28 @@
           <t>Class 7 (SOC)</t>
         </is>
       </c>
-      <c r="C97" s="7" t="inlineStr">
+      <c r="C97" s="7" t="inlineStr"/>
+      <c r="D97" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (SOC)</t>
+        </is>
+      </c>
+      <c r="E97" s="7" t="inlineStr">
         <is>
           <t>Class 6 (SOC)</t>
         </is>
       </c>
-      <c r="D97" s="7" t="inlineStr"/>
-      <c r="E97" s="7" t="inlineStr">
+      <c r="F97" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (SOC)</t>
+        </is>
+      </c>
+      <c r="G97" s="7" t="inlineStr"/>
+      <c r="H97" s="7" t="inlineStr">
         <is>
           <t>Class 3 (SOC)</t>
         </is>
       </c>
-      <c r="F97" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (SOC)</t>
-        </is>
-      </c>
-      <c r="G97" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (SOC)</t>
-        </is>
-      </c>
-      <c r="H97" s="7" t="inlineStr"/>
       <c r="I97" s="8" t="inlineStr">
         <is>
           <t>Class 7</t>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (SOC)</t>
+          <t>Class 6 (SOC)</t>
         </is>
       </c>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (SOC)</t>
+          <t>Class 3 (SOC)</t>
         </is>
       </c>
       <c r="E98" s="7" t="inlineStr"/>
@@ -3265,12 +3265,12 @@
           <t>Class 5 (SOC)</t>
         </is>
       </c>
-      <c r="G98" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (SOC)</t>
-        </is>
-      </c>
-      <c r="H98" s="7" t="inlineStr"/>
+      <c r="G98" s="7" t="inlineStr"/>
+      <c r="H98" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (SOC)</t>
+        </is>
+      </c>
       <c r="I98" s="8" t="inlineStr">
         <is>
           <t>Class 7</t>
@@ -3296,20 +3296,20 @@
       <c r="D99" s="7" t="inlineStr"/>
       <c r="E99" s="7" t="inlineStr">
         <is>
+          <t>Class 5 (SOC)</t>
+        </is>
+      </c>
+      <c r="F99" s="7" t="inlineStr">
+        <is>
           <t>Class 4 (SOC)</t>
         </is>
       </c>
-      <c r="F99" s="7" t="inlineStr">
+      <c r="G99" s="7" t="inlineStr"/>
+      <c r="H99" s="7" t="inlineStr">
         <is>
           <t>Class 3 (SOC)</t>
         </is>
       </c>
-      <c r="G99" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (SOC)</t>
-        </is>
-      </c>
-      <c r="H99" s="7" t="inlineStr"/>
       <c r="I99" s="8" t="inlineStr">
         <is>
           <t>Class 7</t>
@@ -3329,19 +3329,19 @@
       </c>
       <c r="C100" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (SOC)</t>
-        </is>
-      </c>
-      <c r="D100" s="7" t="inlineStr">
+          <t>Class 5 (SOC)</t>
+        </is>
+      </c>
+      <c r="D100" s="7" t="inlineStr"/>
+      <c r="E100" s="7" t="inlineStr">
         <is>
           <t>Class 4 (SOC)</t>
         </is>
       </c>
-      <c r="E100" s="7" t="inlineStr"/>
       <c r="F100" s="7" t="inlineStr"/>
       <c r="G100" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (SOC)</t>
+          <t>Class 6 (SOC)</t>
         </is>
       </c>
       <c r="H100" s="7" t="inlineStr">
@@ -3423,25 +3423,33 @@
           <t>MON</t>
         </is>
       </c>
-      <c r="B104" s="7" t="inlineStr"/>
-      <c r="C104" s="7" t="inlineStr"/>
-      <c r="D104" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (GRAM)</t>
-        </is>
-      </c>
+      <c r="B104" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (GRAM)</t>
+        </is>
+      </c>
+      <c r="C104" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (ENG)</t>
+        </is>
+      </c>
+      <c r="D104" s="7" t="inlineStr"/>
       <c r="E104" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (ENG)</t>
-        </is>
-      </c>
-      <c r="F104" s="7" t="inlineStr"/>
-      <c r="G104" s="7" t="inlineStr">
+          <t>Class 8 (GRAM)</t>
+        </is>
+      </c>
+      <c r="F104" s="7" t="inlineStr">
         <is>
           <t>Class 7 (ENG)</t>
         </is>
       </c>
-      <c r="H104" s="7" t="inlineStr"/>
+      <c r="G104" s="7" t="inlineStr"/>
+      <c r="H104" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (GRAM)</t>
+        </is>
+      </c>
       <c r="I104" s="7" t="inlineStr"/>
     </row>
     <row r="105">
@@ -3451,28 +3459,24 @@
         </is>
       </c>
       <c r="B105" s="7" t="inlineStr"/>
-      <c r="C105" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (GRAM)</t>
-        </is>
-      </c>
+      <c r="C105" s="7" t="inlineStr"/>
       <c r="D105" s="7" t="inlineStr">
         <is>
+          <t>Class 6 (GRAM)</t>
+        </is>
+      </c>
+      <c r="E105" s="7" t="inlineStr">
+        <is>
           <t>Class 6 (ENG)</t>
         </is>
       </c>
-      <c r="E105" s="7" t="inlineStr"/>
       <c r="F105" s="7" t="inlineStr">
         <is>
-          <t>Class 9 (GRAM)</t>
+          <t>Class 7 (ENG)</t>
         </is>
       </c>
       <c r="G105" s="7" t="inlineStr"/>
-      <c r="H105" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (ENG)</t>
-        </is>
-      </c>
+      <c r="H105" s="7" t="inlineStr"/>
       <c r="I105" s="7" t="inlineStr"/>
     </row>
     <row r="106">
@@ -3482,20 +3486,20 @@
         </is>
       </c>
       <c r="B106" s="7" t="inlineStr"/>
-      <c r="C106" s="7" t="inlineStr"/>
-      <c r="D106" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (ENG)</t>
-        </is>
-      </c>
-      <c r="E106" s="7" t="inlineStr">
+      <c r="C106" s="7" t="inlineStr">
         <is>
           <t>Class 6 (ENG)</t>
         </is>
       </c>
+      <c r="D106" s="7" t="inlineStr"/>
+      <c r="E106" s="7" t="inlineStr"/>
       <c r="F106" s="7" t="inlineStr"/>
       <c r="G106" s="7" t="inlineStr"/>
-      <c r="H106" s="7" t="inlineStr"/>
+      <c r="H106" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (ENG)</t>
+        </is>
+      </c>
       <c r="I106" s="7" t="inlineStr"/>
     </row>
     <row r="107">
@@ -3508,20 +3512,16 @@
       <c r="C107" s="7" t="inlineStr"/>
       <c r="D107" s="7" t="inlineStr">
         <is>
+          <t>Class 6 (ENG)</t>
+        </is>
+      </c>
+      <c r="E107" s="7" t="inlineStr"/>
+      <c r="F107" s="7" t="inlineStr">
+        <is>
           <t>Class 7 (ENG)</t>
         </is>
       </c>
-      <c r="E107" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (ENG)</t>
-        </is>
-      </c>
-      <c r="F107" s="7" t="inlineStr"/>
-      <c r="G107" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (GRAM)</t>
-        </is>
-      </c>
+      <c r="G107" s="7" t="inlineStr"/>
       <c r="H107" s="7" t="inlineStr"/>
       <c r="I107" s="7" t="inlineStr"/>
     </row>
@@ -3533,23 +3533,23 @@
       </c>
       <c r="B108" s="7" t="inlineStr"/>
       <c r="C108" s="7" t="inlineStr"/>
-      <c r="D108" s="7" t="inlineStr"/>
+      <c r="D108" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (GRAM)</t>
+        </is>
+      </c>
       <c r="E108" s="7" t="inlineStr">
         <is>
+          <t>Class 7 (ENG)</t>
+        </is>
+      </c>
+      <c r="F108" s="7" t="inlineStr"/>
+      <c r="G108" s="7" t="inlineStr"/>
+      <c r="H108" s="7" t="inlineStr">
+        <is>
           <t>Class 6 (ENG)</t>
         </is>
       </c>
-      <c r="F108" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (GRAM)</t>
-        </is>
-      </c>
-      <c r="G108" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (ENG)</t>
-        </is>
-      </c>
-      <c r="H108" s="7" t="inlineStr"/>
       <c r="I108" s="7" t="inlineStr"/>
     </row>
     <row r="109">
@@ -3563,12 +3563,12 @@
       <c r="D109" s="7" t="inlineStr"/>
       <c r="E109" s="7" t="inlineStr">
         <is>
+          <t>Class 6 (ENG)</t>
+        </is>
+      </c>
+      <c r="F109" s="7" t="inlineStr">
+        <is>
           <t>Class 7 (ENG)</t>
-        </is>
-      </c>
-      <c r="F109" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (ENG)</t>
         </is>
       </c>
       <c r="G109" s="7" t="inlineStr"/>
@@ -3644,24 +3644,20 @@
         </is>
       </c>
       <c r="B113" s="7" t="inlineStr"/>
-      <c r="C113" s="7" t="inlineStr"/>
+      <c r="C113" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (HIN)</t>
+        </is>
+      </c>
       <c r="D113" s="7" t="inlineStr"/>
-      <c r="E113" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (HIN)</t>
-        </is>
-      </c>
-      <c r="F113" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (HIN)</t>
-        </is>
-      </c>
-      <c r="G113" s="7" t="inlineStr">
+      <c r="E113" s="7" t="inlineStr"/>
+      <c r="F113" s="7" t="inlineStr"/>
+      <c r="G113" s="7" t="inlineStr"/>
+      <c r="H113" s="7" t="inlineStr">
         <is>
           <t>Class 9 (HIN)</t>
         </is>
       </c>
-      <c r="H113" s="7" t="inlineStr"/>
       <c r="I113" s="7" t="inlineStr"/>
     </row>
     <row r="114">
@@ -3673,17 +3669,21 @@
       <c r="B114" s="7" t="inlineStr"/>
       <c r="C114" s="7" t="inlineStr">
         <is>
-          <t>Class 3 (HIN)</t>
+          <t>Class 10 (HIN)</t>
         </is>
       </c>
       <c r="D114" s="7" t="inlineStr"/>
       <c r="E114" s="7" t="inlineStr">
         <is>
-          <t>Class 10 (HIN)</t>
+          <t>Class 3 (HIN)</t>
         </is>
       </c>
       <c r="F114" s="7" t="inlineStr"/>
-      <c r="G114" s="7" t="inlineStr"/>
+      <c r="G114" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (HIN)</t>
+        </is>
+      </c>
       <c r="H114" s="7" t="inlineStr"/>
       <c r="I114" s="7" t="inlineStr"/>
     </row>
@@ -3696,17 +3696,17 @@
       <c r="B115" s="7" t="inlineStr"/>
       <c r="C115" s="7" t="inlineStr">
         <is>
-          <t>Class 10 (HIN)</t>
+          <t>Class 3 (HIN)</t>
         </is>
       </c>
       <c r="D115" s="7" t="inlineStr"/>
-      <c r="E115" s="7" t="inlineStr">
+      <c r="E115" s="7" t="inlineStr"/>
+      <c r="F115" s="7" t="inlineStr"/>
+      <c r="G115" s="7" t="inlineStr">
         <is>
           <t>Class 9 (HIN)</t>
         </is>
       </c>
-      <c r="F115" s="7" t="inlineStr"/>
-      <c r="G115" s="7" t="inlineStr"/>
       <c r="H115" s="7" t="inlineStr"/>
       <c r="I115" s="7" t="inlineStr"/>
     </row>
@@ -3728,12 +3728,12 @@
           <t>Class 10 (HIN)</t>
         </is>
       </c>
-      <c r="F116" s="7" t="inlineStr">
+      <c r="F116" s="7" t="inlineStr"/>
+      <c r="G116" s="7" t="inlineStr">
         <is>
           <t>Class 9 (HIN)</t>
         </is>
       </c>
-      <c r="G116" s="7" t="inlineStr"/>
       <c r="H116" s="7" t="inlineStr"/>
       <c r="I116" s="7" t="inlineStr"/>
     </row>
@@ -3756,7 +3756,11 @@
         </is>
       </c>
       <c r="F117" s="7" t="inlineStr"/>
-      <c r="G117" s="7" t="inlineStr"/>
+      <c r="G117" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (HIN)</t>
+        </is>
+      </c>
       <c r="H117" s="7" t="inlineStr"/>
       <c r="I117" s="7" t="inlineStr"/>
     </row>
@@ -3767,24 +3771,20 @@
         </is>
       </c>
       <c r="B118" s="7" t="inlineStr"/>
-      <c r="C118" s="7" t="inlineStr"/>
+      <c r="C118" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (HIN)</t>
+        </is>
+      </c>
       <c r="D118" s="7" t="inlineStr"/>
       <c r="E118" s="7" t="inlineStr">
         <is>
-          <t>Class 9 (HIN)</t>
+          <t>Class 10 (HIN)</t>
         </is>
       </c>
       <c r="F118" s="7" t="inlineStr"/>
-      <c r="G118" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (HIN)</t>
-        </is>
-      </c>
-      <c r="H118" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (HIN)</t>
-        </is>
-      </c>
+      <c r="G118" s="7" t="inlineStr"/>
+      <c r="H118" s="7" t="inlineStr"/>
       <c r="I118" s="7" t="inlineStr"/>
     </row>
     <row r="120">
@@ -3862,30 +3862,30 @@
       </c>
       <c r="C122" s="7" t="inlineStr">
         <is>
+          <t>Class 3 (G.K)</t>
+        </is>
+      </c>
+      <c r="D122" s="7" t="inlineStr">
+        <is>
+          <t>Class 1 (EVS)</t>
+        </is>
+      </c>
+      <c r="E122" s="7" t="inlineStr">
+        <is>
+          <t>Class 1 (HIN)</t>
+        </is>
+      </c>
+      <c r="F122" s="7" t="inlineStr">
+        <is>
           <t>U.K.G (ENG)</t>
         </is>
       </c>
-      <c r="D122" s="7" t="inlineStr">
+      <c r="G122" s="7" t="inlineStr">
         <is>
           <t>Class 2 (HIN)</t>
         </is>
       </c>
-      <c r="E122" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (EVS)</t>
-        </is>
-      </c>
-      <c r="F122" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (ENG)</t>
-        </is>
-      </c>
-      <c r="G122" s="7" t="inlineStr"/>
-      <c r="H122" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (HIN)</t>
-        </is>
-      </c>
+      <c r="H122" s="7" t="inlineStr"/>
       <c r="I122" s="8" t="inlineStr">
         <is>
           <t>Class 2</t>
@@ -3900,33 +3900,33 @@
       </c>
       <c r="B123" s="7" t="inlineStr">
         <is>
+          <t>Class 2 (HIN)</t>
+        </is>
+      </c>
+      <c r="C123" s="7" t="inlineStr">
+        <is>
+          <t>U.K.G (ENG)</t>
+        </is>
+      </c>
+      <c r="D123" s="7" t="inlineStr">
+        <is>
+          <t>Class 1 (EVS)</t>
+        </is>
+      </c>
+      <c r="E123" s="7" t="inlineStr">
+        <is>
+          <t>U.K.G (ENG)</t>
+        </is>
+      </c>
+      <c r="F123" s="7" t="inlineStr">
+        <is>
           <t>Class 2 (EVS)</t>
-        </is>
-      </c>
-      <c r="C123" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (ENG)</t>
-        </is>
-      </c>
-      <c r="D123" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (ENG)</t>
-        </is>
-      </c>
-      <c r="E123" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (EVS)</t>
-        </is>
-      </c>
-      <c r="F123" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (HIN)</t>
         </is>
       </c>
       <c r="G123" s="7" t="inlineStr"/>
       <c r="H123" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (HIN)</t>
+          <t>Class 1 (HIN)</t>
         </is>
       </c>
       <c r="I123" s="8" t="inlineStr">
@@ -3948,28 +3948,32 @@
       </c>
       <c r="C124" s="7" t="inlineStr">
         <is>
+          <t>U.K.G (ENG)</t>
+        </is>
+      </c>
+      <c r="D124" s="7" t="inlineStr">
+        <is>
+          <t>Class 1 (HIN)</t>
+        </is>
+      </c>
+      <c r="E124" s="7" t="inlineStr">
+        <is>
+          <t>Class 1 (EVS)</t>
+        </is>
+      </c>
+      <c r="F124" s="7" t="inlineStr">
+        <is>
           <t>Class 2 (EVS)</t>
         </is>
       </c>
-      <c r="D124" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (G.K)</t>
-        </is>
-      </c>
-      <c r="E124" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (HIN)</t>
-        </is>
-      </c>
-      <c r="F124" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (ENG)</t>
-        </is>
-      </c>
-      <c r="G124" s="7" t="inlineStr"/>
+      <c r="G124" s="7" t="inlineStr">
+        <is>
+          <t>Class 1 (EVS)</t>
+        </is>
+      </c>
       <c r="H124" s="7" t="inlineStr">
         <is>
-          <t>Class 1 (EVS)</t>
+          <t>Class 2 (EVS)</t>
         </is>
       </c>
       <c r="I124" s="8" t="inlineStr">
@@ -3986,7 +3990,7 @@
       </c>
       <c r="B125" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (EVS)</t>
+          <t>Class 2 (HIN)</t>
         </is>
       </c>
       <c r="C125" s="7" t="inlineStr">
@@ -3996,25 +4000,21 @@
       </c>
       <c r="D125" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (HIN)</t>
-        </is>
-      </c>
-      <c r="E125" s="7" t="inlineStr">
-        <is>
           <t>U.K.G (ENG)</t>
         </is>
       </c>
+      <c r="E125" s="7" t="inlineStr"/>
       <c r="F125" s="7" t="inlineStr">
         <is>
           <t>Class 1 (EVS)</t>
         </is>
       </c>
-      <c r="G125" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (HIN)</t>
-        </is>
-      </c>
-      <c r="H125" s="7" t="inlineStr"/>
+      <c r="G125" s="7" t="inlineStr"/>
+      <c r="H125" s="7" t="inlineStr">
+        <is>
+          <t>U.K.G (ENG)</t>
+        </is>
+      </c>
       <c r="I125" s="8" t="inlineStr">
         <is>
           <t>Class 2</t>
@@ -4029,31 +4029,35 @@
       </c>
       <c r="B126" s="7" t="inlineStr">
         <is>
+          <t>Class 2 (EVS)</t>
+        </is>
+      </c>
+      <c r="C126" s="7" t="inlineStr">
+        <is>
+          <t>U.K.G (ENG)</t>
+        </is>
+      </c>
+      <c r="D126" s="7" t="inlineStr">
+        <is>
+          <t>Class 1 (HIN)</t>
+        </is>
+      </c>
+      <c r="E126" s="7" t="inlineStr">
+        <is>
           <t>Class 2 (HIN)</t>
         </is>
       </c>
-      <c r="C126" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (EVS)</t>
-        </is>
-      </c>
-      <c r="D126" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (EVS)</t>
-        </is>
-      </c>
-      <c r="E126" s="7" t="inlineStr"/>
-      <c r="F126" s="7" t="inlineStr"/>
+      <c r="F126" s="7" t="inlineStr">
+        <is>
+          <t>U.K.G (ENG)</t>
+        </is>
+      </c>
       <c r="G126" s="7" t="inlineStr">
         <is>
-          <t>Class 1 (HIN)</t>
-        </is>
-      </c>
-      <c r="H126" s="7" t="inlineStr">
-        <is>
           <t>U.K.G (ENG)</t>
         </is>
       </c>
+      <c r="H126" s="7" t="inlineStr"/>
       <c r="I126" s="8" t="inlineStr">
         <is>
           <t>Class 2</t>
@@ -4073,30 +4077,26 @@
       </c>
       <c r="C127" s="7" t="inlineStr">
         <is>
+          <t>Class 2 (HIN)</t>
+        </is>
+      </c>
+      <c r="D127" s="7" t="inlineStr">
+        <is>
+          <t>Class 1 (HIN)</t>
+        </is>
+      </c>
+      <c r="E127" s="7" t="inlineStr"/>
+      <c r="F127" s="7" t="inlineStr">
+        <is>
           <t>U.K.G (ENG)</t>
         </is>
       </c>
-      <c r="D127" s="7" t="inlineStr">
+      <c r="G127" s="7" t="inlineStr">
         <is>
           <t>Class 1 (EVS)</t>
         </is>
       </c>
-      <c r="E127" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (HIN)</t>
-        </is>
-      </c>
-      <c r="F127" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (ENG)</t>
-        </is>
-      </c>
-      <c r="G127" s="7" t="inlineStr"/>
-      <c r="H127" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (ENG)</t>
-        </is>
-      </c>
+      <c r="H127" s="7" t="inlineStr"/>
       <c r="I127" s="8" t="inlineStr">
         <is>
           <t>Class 2</t>
@@ -4181,19 +4181,15 @@
           <t>Class 8 (MATH)</t>
         </is>
       </c>
-      <c r="D131" s="7" t="inlineStr"/>
-      <c r="E131" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (COMP)</t>
-        </is>
-      </c>
+      <c r="D131" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (MATH)</t>
+        </is>
+      </c>
+      <c r="E131" s="7" t="inlineStr"/>
       <c r="F131" s="7" t="inlineStr"/>
       <c r="G131" s="7" t="inlineStr"/>
-      <c r="H131" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (MATH)</t>
-        </is>
-      </c>
+      <c r="H131" s="7" t="inlineStr"/>
       <c r="I131" s="8" t="inlineStr">
         <is>
           <t>Class 6</t>
@@ -4211,24 +4207,24 @@
           <t>Class 6 (MATH)</t>
         </is>
       </c>
-      <c r="C132" s="7" t="inlineStr"/>
+      <c r="C132" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (MATH)</t>
+        </is>
+      </c>
       <c r="D132" s="7" t="inlineStr">
         <is>
           <t>Class 8 (MATH)</t>
         </is>
       </c>
-      <c r="E132" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (G.K)</t>
-        </is>
-      </c>
+      <c r="E132" s="7" t="inlineStr"/>
       <c r="F132" s="7" t="inlineStr"/>
-      <c r="G132" s="7" t="inlineStr"/>
-      <c r="H132" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (MATH)</t>
-        </is>
-      </c>
+      <c r="G132" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (MATH)</t>
+        </is>
+      </c>
+      <c r="H132" s="7" t="inlineStr"/>
       <c r="I132" s="8" t="inlineStr">
         <is>
           <t>Class 6</t>
@@ -4246,24 +4242,28 @@
           <t>Class 6 (MATH)</t>
         </is>
       </c>
-      <c r="C133" s="7" t="inlineStr">
+      <c r="C133" s="7" t="inlineStr"/>
+      <c r="D133" s="7" t="inlineStr">
         <is>
           <t>Class 7 (MATH)</t>
         </is>
       </c>
-      <c r="D133" s="7" t="inlineStr"/>
       <c r="E133" s="7" t="inlineStr">
         <is>
+          <t>Class 7 (MATH)</t>
+        </is>
+      </c>
+      <c r="F133" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (G.K)</t>
+        </is>
+      </c>
+      <c r="G133" s="7" t="inlineStr"/>
+      <c r="H133" s="7" t="inlineStr">
+        <is>
           <t>Class 8 (MATH)</t>
         </is>
       </c>
-      <c r="F133" s="7" t="inlineStr"/>
-      <c r="G133" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (MATH)</t>
-        </is>
-      </c>
-      <c r="H133" s="7" t="inlineStr"/>
       <c r="I133" s="8" t="inlineStr">
         <is>
           <t>Class 6</t>
@@ -4278,24 +4278,28 @@
       </c>
       <c r="B134" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (MATH)</t>
+          <t>Class 6 (G.K)</t>
         </is>
       </c>
       <c r="C134" s="7" t="inlineStr"/>
       <c r="D134" s="7" t="inlineStr">
         <is>
+          <t>Class 7 (COMP)</t>
+        </is>
+      </c>
+      <c r="E134" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (MATH)</t>
+        </is>
+      </c>
+      <c r="F134" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (MATH)</t>
+        </is>
+      </c>
+      <c r="G134" s="7" t="inlineStr">
+        <is>
           <t>Class 8 (COMP)</t>
-        </is>
-      </c>
-      <c r="E134" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (MATH)</t>
-        </is>
-      </c>
-      <c r="F134" s="7" t="inlineStr"/>
-      <c r="G134" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (MATH)</t>
         </is>
       </c>
       <c r="H134" s="7" t="inlineStr"/>
@@ -4316,26 +4320,26 @@
           <t>Class 6 (MATH)</t>
         </is>
       </c>
-      <c r="C135" s="7" t="inlineStr">
+      <c r="C135" s="7" t="inlineStr"/>
+      <c r="D135" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (G.K)</t>
+        </is>
+      </c>
+      <c r="E135" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (MATH)</t>
+        </is>
+      </c>
+      <c r="F135" s="7" t="inlineStr"/>
+      <c r="G135" s="7" t="inlineStr">
         <is>
           <t>Class 7 (MATH)</t>
         </is>
       </c>
-      <c r="D135" s="7" t="inlineStr"/>
-      <c r="E135" s="7" t="inlineStr">
+      <c r="H135" s="7" t="inlineStr">
         <is>
           <t>Class 7 (MATH)</t>
-        </is>
-      </c>
-      <c r="F135" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (MATH)</t>
-        </is>
-      </c>
-      <c r="G135" s="7" t="inlineStr"/>
-      <c r="H135" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (G.K)</t>
         </is>
       </c>
       <c r="I135" s="8" t="inlineStr">
@@ -4355,28 +4359,24 @@
           <t>Class 6 (MATH)</t>
         </is>
       </c>
-      <c r="C136" s="7" t="inlineStr"/>
+      <c r="C136" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (MATH)</t>
+        </is>
+      </c>
       <c r="D136" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (MATH)</t>
-        </is>
-      </c>
-      <c r="E136" s="7" t="inlineStr">
-        <is>
           <t>Class 8 (MATH)</t>
         </is>
       </c>
+      <c r="E136" s="7" t="inlineStr"/>
       <c r="F136" s="7" t="inlineStr"/>
       <c r="G136" s="7" t="inlineStr">
         <is>
           <t>Class 7 (MATH)</t>
         </is>
       </c>
-      <c r="H136" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (G.K)</t>
-        </is>
-      </c>
+      <c r="H136" s="7" t="inlineStr"/>
       <c r="I136" s="8" t="inlineStr">
         <is>
           <t>Class 6</t>
@@ -4453,31 +4453,35 @@
       </c>
       <c r="B140" s="7" t="inlineStr">
         <is>
+          <t>L.K.G (EVS)</t>
+        </is>
+      </c>
+      <c r="C140" s="7" t="inlineStr">
+        <is>
+          <t>L.K.G (ORAL)</t>
+        </is>
+      </c>
+      <c r="D140" s="7" t="inlineStr">
+        <is>
           <t>L.K.G (MATH)</t>
         </is>
       </c>
-      <c r="C140" s="7" t="inlineStr">
+      <c r="E140" s="7" t="inlineStr">
         <is>
           <t>L.K.G (MATH)</t>
         </is>
       </c>
-      <c r="D140" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (EVS)</t>
-        </is>
-      </c>
-      <c r="E140" s="7" t="inlineStr"/>
       <c r="F140" s="7" t="inlineStr">
         <is>
-          <t>L.K.G (ORAL)</t>
-        </is>
-      </c>
-      <c r="G140" s="7" t="inlineStr"/>
-      <c r="H140" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (EVS)</t>
-        </is>
-      </c>
+          <t>L.K.G (ENG)</t>
+        </is>
+      </c>
+      <c r="G140" s="7" t="inlineStr">
+        <is>
+          <t>L.K.G (ENG)</t>
+        </is>
+      </c>
+      <c r="H140" s="7" t="inlineStr"/>
       <c r="I140" s="8" t="inlineStr">
         <is>
           <t>L.K.G</t>
@@ -4492,31 +4496,35 @@
       </c>
       <c r="B141" s="7" t="inlineStr">
         <is>
+          <t>L.K.G (MATH)</t>
+        </is>
+      </c>
+      <c r="C141" s="7" t="inlineStr">
+        <is>
           <t>L.K.G (ORAL)</t>
         </is>
       </c>
-      <c r="C141" s="7" t="inlineStr">
+      <c r="D141" s="7" t="inlineStr">
+        <is>
+          <t>L.K.G (EVS)</t>
+        </is>
+      </c>
+      <c r="E141" s="7" t="inlineStr">
+        <is>
+          <t>L.K.G (EVS)</t>
+        </is>
+      </c>
+      <c r="F141" s="7" t="inlineStr">
         <is>
           <t>L.K.G (MATH)</t>
         </is>
       </c>
-      <c r="D141" s="7" t="inlineStr"/>
-      <c r="E141" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (MATH)</t>
-        </is>
-      </c>
-      <c r="F141" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (MATH)</t>
-        </is>
-      </c>
-      <c r="G141" s="7" t="inlineStr"/>
-      <c r="H141" s="7" t="inlineStr">
+      <c r="G141" s="7" t="inlineStr">
         <is>
           <t>L.K.G (ENG)</t>
         </is>
       </c>
+      <c r="H141" s="7" t="inlineStr"/>
       <c r="I141" s="8" t="inlineStr">
         <is>
           <t>L.K.G</t>
@@ -4531,29 +4539,33 @@
       </c>
       <c r="B142" s="7" t="inlineStr">
         <is>
-          <t>L.K.G (ORAL)</t>
-        </is>
-      </c>
-      <c r="C142" s="7" t="inlineStr"/>
+          <t>L.K.G (ENG)</t>
+        </is>
+      </c>
+      <c r="C142" s="7" t="inlineStr">
+        <is>
+          <t>L.K.G (MATH)</t>
+        </is>
+      </c>
       <c r="D142" s="7" t="inlineStr">
         <is>
+          <t>L.K.G (MATH)</t>
+        </is>
+      </c>
+      <c r="E142" s="7" t="inlineStr">
+        <is>
+          <t>L.K.G (ENG)</t>
+        </is>
+      </c>
+      <c r="F142" s="7" t="inlineStr">
+        <is>
           <t>L.K.G (EVS)</t>
-        </is>
-      </c>
-      <c r="E142" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (EVS)</t>
-        </is>
-      </c>
-      <c r="F142" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (ENG)</t>
         </is>
       </c>
       <c r="G142" s="7" t="inlineStr"/>
       <c r="H142" s="7" t="inlineStr">
         <is>
-          <t>L.K.G (EVS)</t>
+          <t>L.K.G (MATH)</t>
         </is>
       </c>
       <c r="I142" s="8" t="inlineStr">
@@ -4570,34 +4582,26 @@
       </c>
       <c r="B143" s="7" t="inlineStr">
         <is>
+          <t>L.K.G (ORAL)</t>
+        </is>
+      </c>
+      <c r="C143" s="7" t="inlineStr">
+        <is>
+          <t>L.K.G (EVS)</t>
+        </is>
+      </c>
+      <c r="D143" s="7" t="inlineStr">
+        <is>
           <t>L.K.G (ENG)</t>
         </is>
       </c>
-      <c r="C143" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (ENG)</t>
-        </is>
-      </c>
-      <c r="D143" s="7" t="inlineStr">
+      <c r="E143" s="7" t="inlineStr"/>
+      <c r="F143" s="7" t="inlineStr">
         <is>
           <t>L.K.G (EVS)</t>
         </is>
       </c>
-      <c r="E143" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (ENG)</t>
-        </is>
-      </c>
-      <c r="F143" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (ENG)</t>
-        </is>
-      </c>
-      <c r="G143" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (ENG)</t>
-        </is>
-      </c>
+      <c r="G143" s="7" t="inlineStr"/>
       <c r="H143" s="7" t="inlineStr">
         <is>
           <t>L.K.G (MATH)</t>
@@ -4622,28 +4626,24 @@
       </c>
       <c r="C144" s="7" t="inlineStr">
         <is>
+          <t>L.K.G (EVS)</t>
+        </is>
+      </c>
+      <c r="D144" s="7" t="inlineStr">
+        <is>
+          <t>L.K.G (EVS)</t>
+        </is>
+      </c>
+      <c r="E144" s="7" t="inlineStr"/>
+      <c r="F144" s="7" t="inlineStr">
+        <is>
           <t>L.K.G (ENG)</t>
         </is>
       </c>
-      <c r="D144" s="7" t="inlineStr">
+      <c r="G144" s="7" t="inlineStr"/>
+      <c r="H144" s="7" t="inlineStr">
         <is>
           <t>L.K.G (MATH)</t>
-        </is>
-      </c>
-      <c r="E144" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (MATH)</t>
-        </is>
-      </c>
-      <c r="F144" s="7" t="inlineStr"/>
-      <c r="G144" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (EVS)</t>
-        </is>
-      </c>
-      <c r="H144" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (ENG)</t>
         </is>
       </c>
       <c r="I144" s="8" t="inlineStr">
@@ -4665,30 +4665,30 @@
       </c>
       <c r="C145" s="7" t="inlineStr">
         <is>
+          <t>L.K.G (MATH)</t>
+        </is>
+      </c>
+      <c r="D145" s="7" t="inlineStr">
+        <is>
+          <t>L.K.G (EVS)</t>
+        </is>
+      </c>
+      <c r="E145" s="7" t="inlineStr">
+        <is>
           <t>L.K.G (ENG)</t>
         </is>
       </c>
-      <c r="D145" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (EVS)</t>
-        </is>
-      </c>
-      <c r="E145" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (EVS)</t>
-        </is>
-      </c>
-      <c r="F145" s="7" t="inlineStr"/>
+      <c r="F145" s="7" t="inlineStr">
+        <is>
+          <t>L.K.G (ENG)</t>
+        </is>
+      </c>
       <c r="G145" s="7" t="inlineStr">
         <is>
-          <t>L.K.G (MATH)</t>
-        </is>
-      </c>
-      <c r="H145" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (MATH)</t>
-        </is>
-      </c>
+          <t>L.K.G (ENG)</t>
+        </is>
+      </c>
+      <c r="H145" s="7" t="inlineStr"/>
       <c r="I145" s="8" t="inlineStr">
         <is>
           <t>L.K.G</t>
@@ -4774,12 +4774,12 @@
       </c>
       <c r="G149" s="7" t="inlineStr">
         <is>
+          <t>Class 9 (ENG)</t>
+        </is>
+      </c>
+      <c r="H149" s="7" t="inlineStr">
+        <is>
           <t>Class 10 (ENG)</t>
-        </is>
-      </c>
-      <c r="H149" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (ENG)</t>
         </is>
       </c>
       <c r="I149" s="7" t="inlineStr"/>
@@ -4823,17 +4823,17 @@
       <c r="E151" s="7" t="inlineStr"/>
       <c r="F151" s="7" t="inlineStr">
         <is>
+          <t>Class 10 (ENG)</t>
+        </is>
+      </c>
+      <c r="G151" s="7" t="inlineStr">
+        <is>
           <t>Class 8 (ENG)</t>
         </is>
       </c>
-      <c r="G151" s="7" t="inlineStr">
+      <c r="H151" s="7" t="inlineStr">
         <is>
           <t>Class 9 (ENG)</t>
-        </is>
-      </c>
-      <c r="H151" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (ENG)</t>
         </is>
       </c>
       <c r="I151" s="7" t="inlineStr"/>
@@ -4850,20 +4850,20 @@
       <c r="E152" s="7" t="inlineStr"/>
       <c r="F152" s="7" t="inlineStr">
         <is>
+          <t>Class 9 (ENG)</t>
+        </is>
+      </c>
+      <c r="G152" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (ENG)</t>
+        </is>
+      </c>
+      <c r="H152" s="7" t="inlineStr">
+        <is>
           <t>Class 8 (ENG)</t>
         </is>
       </c>
-      <c r="G152" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (ENG)</t>
-        </is>
-      </c>
-      <c r="H152" s="7" t="inlineStr"/>
-      <c r="I152" s="8" t="inlineStr">
-        <is>
-          <t>Class 10 (ENG)</t>
-        </is>
-      </c>
+      <c r="I152" s="7" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="6" t="inlineStr">
@@ -4877,17 +4877,17 @@
       <c r="E153" s="7" t="inlineStr"/>
       <c r="F153" s="7" t="inlineStr">
         <is>
+          <t>Class 10 (ENG)</t>
+        </is>
+      </c>
+      <c r="G153" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (ENG)</t>
+        </is>
+      </c>
+      <c r="H153" s="7" t="inlineStr">
+        <is>
           <t>Class 9 (ENG)</t>
-        </is>
-      </c>
-      <c r="G153" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (ENG)</t>
-        </is>
-      </c>
-      <c r="H153" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (ENG)</t>
         </is>
       </c>
       <c r="I153" s="7" t="inlineStr"/>
@@ -4904,20 +4904,20 @@
       <c r="E154" s="7" t="inlineStr"/>
       <c r="F154" s="7" t="inlineStr">
         <is>
+          <t>Class 9 (ENG)</t>
+        </is>
+      </c>
+      <c r="G154" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (ENG)</t>
+        </is>
+      </c>
+      <c r="H154" s="7" t="inlineStr"/>
+      <c r="I154" s="8" t="inlineStr">
+        <is>
           <t>Class 10 (ENG)</t>
         </is>
       </c>
-      <c r="G154" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (ENG)</t>
-        </is>
-      </c>
-      <c r="H154" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (ENG)</t>
-        </is>
-      </c>
-      <c r="I154" s="7" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="4" t="inlineStr">
@@ -4992,20 +4992,20 @@
       <c r="D158" s="7" t="inlineStr"/>
       <c r="E158" s="7" t="inlineStr">
         <is>
+          <t>Class 9 (SOC)</t>
+        </is>
+      </c>
+      <c r="F158" s="7" t="inlineStr">
+        <is>
           <t>Class 10 (SOC)</t>
         </is>
       </c>
-      <c r="F158" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (SOC)</t>
-        </is>
-      </c>
-      <c r="G158" s="7" t="inlineStr"/>
-      <c r="H158" s="7" t="inlineStr">
+      <c r="G158" s="7" t="inlineStr">
         <is>
           <t>Class 8 (SOC)</t>
         </is>
       </c>
+      <c r="H158" s="7" t="inlineStr"/>
       <c r="I158" s="7" t="inlineStr"/>
     </row>
     <row r="159">
@@ -5023,15 +5023,15 @@
       <c r="D159" s="7" t="inlineStr"/>
       <c r="E159" s="7" t="inlineStr">
         <is>
+          <t>Class 10 (SOC)</t>
+        </is>
+      </c>
+      <c r="F159" s="7" t="inlineStr">
+        <is>
           <t>Class 9 (SOC)</t>
         </is>
       </c>
-      <c r="F159" s="7" t="inlineStr"/>
-      <c r="G159" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (SOC)</t>
-        </is>
-      </c>
+      <c r="G159" s="7" t="inlineStr"/>
       <c r="H159" s="7" t="inlineStr"/>
       <c r="I159" s="7" t="inlineStr"/>
     </row>
@@ -5042,11 +5042,15 @@
         </is>
       </c>
       <c r="B160" s="7" t="inlineStr"/>
-      <c r="C160" s="7" t="inlineStr"/>
+      <c r="C160" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (SOC)</t>
+        </is>
+      </c>
       <c r="D160" s="7" t="inlineStr"/>
       <c r="E160" s="7" t="inlineStr">
         <is>
-          <t>Class 10 (SOC)</t>
+          <t>Class 8 (SOC)</t>
         </is>
       </c>
       <c r="F160" s="7" t="inlineStr">
@@ -5055,11 +5059,7 @@
         </is>
       </c>
       <c r="G160" s="7" t="inlineStr"/>
-      <c r="H160" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (SOC)</t>
-        </is>
-      </c>
+      <c r="H160" s="7" t="inlineStr"/>
       <c r="I160" s="7" t="inlineStr"/>
     </row>
     <row r="161">
@@ -5080,13 +5080,13 @@
           <t>Class 9 (SOC)</t>
         </is>
       </c>
-      <c r="F161" s="7" t="inlineStr">
+      <c r="F161" s="7" t="inlineStr"/>
+      <c r="G161" s="7" t="inlineStr"/>
+      <c r="H161" s="7" t="inlineStr">
         <is>
           <t>Class 10 (SOC)</t>
         </is>
       </c>
-      <c r="G161" s="7" t="inlineStr"/>
-      <c r="H161" s="7" t="inlineStr"/>
       <c r="I161" s="7" t="inlineStr"/>
     </row>
     <row r="162">
@@ -5100,18 +5100,18 @@
       <c r="D162" s="7" t="inlineStr"/>
       <c r="E162" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (SOC)</t>
+          <t>Class 10 (SOC)</t>
         </is>
       </c>
       <c r="F162" s="7" t="inlineStr">
         <is>
-          <t>Class 10 (SOC)</t>
+          <t>Class 9 (SOC)</t>
         </is>
       </c>
       <c r="G162" s="7" t="inlineStr"/>
       <c r="H162" s="7" t="inlineStr">
         <is>
-          <t>Class 9 (SOC)</t>
+          <t>Class 8 (SOC)</t>
         </is>
       </c>
       <c r="I162" s="7" t="inlineStr"/>
@@ -5125,13 +5125,13 @@
       <c r="B163" s="7" t="inlineStr"/>
       <c r="C163" s="7" t="inlineStr">
         <is>
-          <t>Class 9 (SOC)</t>
+          <t>Class 10 (SOC)</t>
         </is>
       </c>
       <c r="D163" s="7" t="inlineStr"/>
       <c r="E163" s="7" t="inlineStr">
         <is>
-          <t>Class 10 (SOC)</t>
+          <t>Class 9 (SOC)</t>
         </is>
       </c>
       <c r="F163" s="7" t="inlineStr">
@@ -5216,28 +5216,28 @@
           <t>Class 3 (TEL)</t>
         </is>
       </c>
-      <c r="C167" s="7" t="inlineStr"/>
-      <c r="D167" s="7" t="inlineStr">
+      <c r="C167" s="7" t="inlineStr">
         <is>
           <t>U.K.G (HIN)</t>
         </is>
       </c>
+      <c r="D167" s="7" t="inlineStr"/>
       <c r="E167" s="7" t="inlineStr">
         <is>
+          <t>Class 4 (TEL)</t>
+        </is>
+      </c>
+      <c r="F167" s="7" t="inlineStr">
+        <is>
           <t>Class 5 (TEL)</t>
         </is>
       </c>
-      <c r="F167" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (TEL)</t>
-        </is>
-      </c>
-      <c r="G167" s="7" t="inlineStr">
+      <c r="G167" s="7" t="inlineStr"/>
+      <c r="H167" s="7" t="inlineStr">
         <is>
           <t>Class 6 (TEL)</t>
         </is>
       </c>
-      <c r="H167" s="7" t="inlineStr"/>
       <c r="I167" s="8" t="inlineStr">
         <is>
           <t>Class 3</t>
@@ -5257,22 +5257,26 @@
       </c>
       <c r="C168" s="7" t="inlineStr">
         <is>
+          <t>Class 4 (TEL)</t>
+        </is>
+      </c>
+      <c r="D168" s="7" t="inlineStr">
+        <is>
           <t>Class 5 (TEL)</t>
         </is>
       </c>
-      <c r="D168" s="7" t="inlineStr"/>
       <c r="E168" s="7" t="inlineStr"/>
-      <c r="F168" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (TEL)</t>
-        </is>
-      </c>
+      <c r="F168" s="7" t="inlineStr"/>
       <c r="G168" s="7" t="inlineStr">
         <is>
           <t>Class 6 (TEL)</t>
         </is>
       </c>
-      <c r="H168" s="7" t="inlineStr"/>
+      <c r="H168" s="7" t="inlineStr">
+        <is>
+          <t>U.K.G (HIN)</t>
+        </is>
+      </c>
       <c r="I168" s="8" t="inlineStr">
         <is>
           <t>Class 3</t>
@@ -5290,26 +5294,26 @@
           <t>Class 3 (TEL)</t>
         </is>
       </c>
-      <c r="C169" s="7" t="inlineStr"/>
+      <c r="C169" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (TEL)</t>
+        </is>
+      </c>
       <c r="D169" s="7" t="inlineStr">
         <is>
+          <t>Class 4 (TEL)</t>
+        </is>
+      </c>
+      <c r="E169" s="7" t="inlineStr"/>
+      <c r="F169" s="7" t="inlineStr"/>
+      <c r="G169" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (TEL)</t>
+        </is>
+      </c>
+      <c r="H169" s="7" t="inlineStr">
+        <is>
           <t>U.K.G (HIN)</t>
-        </is>
-      </c>
-      <c r="E169" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (TEL)</t>
-        </is>
-      </c>
-      <c r="F169" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (TEL)</t>
-        </is>
-      </c>
-      <c r="G169" s="7" t="inlineStr"/>
-      <c r="H169" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (TEL)</t>
         </is>
       </c>
       <c r="I169" s="8" t="inlineStr">
@@ -5329,28 +5333,28 @@
           <t>Class 3 (TEL)</t>
         </is>
       </c>
-      <c r="C170" s="7" t="inlineStr">
+      <c r="C170" s="7" t="inlineStr"/>
+      <c r="D170" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (TEL)</t>
+        </is>
+      </c>
+      <c r="E170" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (TEL)</t>
+        </is>
+      </c>
+      <c r="F170" s="7" t="inlineStr">
         <is>
           <t>U.K.G (HIN)</t>
         </is>
       </c>
-      <c r="D170" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (TEL)</t>
-        </is>
-      </c>
-      <c r="E170" s="7" t="inlineStr"/>
-      <c r="F170" s="7" t="inlineStr">
+      <c r="G170" s="7" t="inlineStr"/>
+      <c r="H170" s="7" t="inlineStr">
         <is>
           <t>Class 6 (TEL)</t>
         </is>
       </c>
-      <c r="G170" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (TEL)</t>
-        </is>
-      </c>
-      <c r="H170" s="7" t="inlineStr"/>
       <c r="I170" s="8" t="inlineStr">
         <is>
           <t>Class 3</t>
@@ -5370,25 +5374,21 @@
       </c>
       <c r="C171" s="7" t="inlineStr">
         <is>
+          <t>Class 4 (TEL)</t>
+        </is>
+      </c>
+      <c r="D171" s="7" t="inlineStr"/>
+      <c r="E171" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (TEL)</t>
+        </is>
+      </c>
+      <c r="F171" s="7" t="inlineStr">
+        <is>
           <t>Class 5 (TEL)</t>
         </is>
       </c>
-      <c r="D171" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (TEL)</t>
-        </is>
-      </c>
-      <c r="E171" s="7" t="inlineStr"/>
-      <c r="F171" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (TEL)</t>
-        </is>
-      </c>
-      <c r="G171" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (HIN)</t>
-        </is>
-      </c>
+      <c r="G171" s="7" t="inlineStr"/>
       <c r="H171" s="7" t="inlineStr"/>
       <c r="I171" s="8" t="inlineStr">
         <is>
@@ -5414,21 +5414,21 @@
       </c>
       <c r="D172" s="7" t="inlineStr">
         <is>
-          <t>U.K.G (HIN)</t>
+          <t>Class 5 (TEL)</t>
         </is>
       </c>
       <c r="E172" s="7" t="inlineStr"/>
       <c r="F172" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (TEL)</t>
-        </is>
-      </c>
-      <c r="G172" s="7" t="inlineStr">
-        <is>
           <t>Class 6 (TEL)</t>
         </is>
       </c>
-      <c r="H172" s="7" t="inlineStr"/>
+      <c r="G172" s="7" t="inlineStr"/>
+      <c r="H172" s="7" t="inlineStr">
+        <is>
+          <t>U.K.G (HIN)</t>
+        </is>
+      </c>
       <c r="I172" s="8" t="inlineStr">
         <is>
           <t>Class 3</t>
@@ -5511,25 +5511,21 @@
       <c r="C176" s="7" t="inlineStr"/>
       <c r="D176" s="7" t="inlineStr">
         <is>
+          <t>Class 4 (MATH)</t>
+        </is>
+      </c>
+      <c r="E176" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (MATH)</t>
+        </is>
+      </c>
+      <c r="F176" s="7" t="inlineStr">
+        <is>
           <t>Class 3 (MATH)</t>
         </is>
       </c>
-      <c r="E176" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (MATH)</t>
-        </is>
-      </c>
-      <c r="F176" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (MATH)</t>
-        </is>
-      </c>
       <c r="G176" s="7" t="inlineStr"/>
-      <c r="H176" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (MATH)</t>
-        </is>
-      </c>
+      <c r="H176" s="7" t="inlineStr"/>
       <c r="I176" s="8" t="inlineStr">
         <is>
           <t>Class 4</t>
@@ -5547,26 +5543,26 @@
           <t>Class 4 (MATH)</t>
         </is>
       </c>
-      <c r="C177" s="7" t="inlineStr"/>
+      <c r="C177" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (MATH)</t>
+        </is>
+      </c>
       <c r="D177" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (MATH)</t>
-        </is>
-      </c>
-      <c r="E177" s="7" t="inlineStr">
-        <is>
           <t>Class 3 (MATH)</t>
         </is>
       </c>
-      <c r="F177" s="7" t="inlineStr">
+      <c r="E177" s="7" t="inlineStr"/>
+      <c r="F177" s="7" t="inlineStr"/>
+      <c r="G177" s="7" t="inlineStr">
         <is>
           <t>Class 3 (MATH)</t>
         </is>
       </c>
-      <c r="G177" s="7" t="inlineStr"/>
       <c r="H177" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (MATH)</t>
+          <t>Class 5 (MATH)</t>
         </is>
       </c>
       <c r="I177" s="8" t="inlineStr">
@@ -5586,28 +5582,24 @@
           <t>Class 4 (MATH)</t>
         </is>
       </c>
-      <c r="C178" s="7" t="inlineStr">
+      <c r="C178" s="7" t="inlineStr"/>
+      <c r="D178" s="7" t="inlineStr"/>
+      <c r="E178" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (MATH)</t>
+        </is>
+      </c>
+      <c r="F178" s="7" t="inlineStr">
         <is>
           <t>Class 3 (MATH)</t>
         </is>
       </c>
-      <c r="D178" s="7" t="inlineStr">
+      <c r="G178" s="7" t="inlineStr">
         <is>
           <t>Class 5 (MATH)</t>
         </is>
       </c>
-      <c r="E178" s="7" t="inlineStr"/>
-      <c r="F178" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (MATH)</t>
-        </is>
-      </c>
-      <c r="G178" s="7" t="inlineStr"/>
-      <c r="H178" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (MATH)</t>
-        </is>
-      </c>
+      <c r="H178" s="7" t="inlineStr"/>
       <c r="I178" s="8" t="inlineStr">
         <is>
           <t>Class 4</t>
@@ -5627,22 +5619,26 @@
       </c>
       <c r="C179" s="7" t="inlineStr">
         <is>
+          <t>Class 2 (MATH)</t>
+        </is>
+      </c>
+      <c r="D179" s="7" t="inlineStr"/>
+      <c r="E179" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (MATH)</t>
+        </is>
+      </c>
+      <c r="F179" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (MATH)</t>
+        </is>
+      </c>
+      <c r="G179" s="7" t="inlineStr"/>
+      <c r="H179" s="7" t="inlineStr">
+        <is>
           <t>Class 5 (MATH)</t>
         </is>
       </c>
-      <c r="D179" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (MATH)</t>
-        </is>
-      </c>
-      <c r="E179" s="7" t="inlineStr"/>
-      <c r="F179" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (MATH)</t>
-        </is>
-      </c>
-      <c r="G179" s="7" t="inlineStr"/>
-      <c r="H179" s="7" t="inlineStr"/>
       <c r="I179" s="8" t="inlineStr">
         <is>
           <t>Class 4</t>
@@ -5660,15 +5656,15 @@
           <t>Class 4 (MATH)</t>
         </is>
       </c>
-      <c r="C180" s="7" t="inlineStr"/>
-      <c r="D180" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (MATH)</t>
-        </is>
-      </c>
+      <c r="C180" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (MATH)</t>
+        </is>
+      </c>
+      <c r="D180" s="7" t="inlineStr"/>
       <c r="E180" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (MATH)</t>
+          <t>Class 3 (MATH)</t>
         </is>
       </c>
       <c r="F180" s="7" t="inlineStr">
@@ -5679,7 +5675,7 @@
       <c r="G180" s="7" t="inlineStr"/>
       <c r="H180" s="7" t="inlineStr">
         <is>
-          <t>Class 3 (MATH)</t>
+          <t>Class 5 (MATH)</t>
         </is>
       </c>
       <c r="I180" s="8" t="inlineStr">
@@ -5710,13 +5706,17 @@
           <t>Class 5 (MATH)</t>
         </is>
       </c>
-      <c r="F181" s="7" t="inlineStr"/>
-      <c r="G181" s="7" t="inlineStr">
+      <c r="F181" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (MATH)</t>
+        </is>
+      </c>
+      <c r="G181" s="7" t="inlineStr"/>
+      <c r="H181" s="7" t="inlineStr">
         <is>
           <t>Class 2 (MATH)</t>
         </is>
       </c>
-      <c r="H181" s="7" t="inlineStr"/>
       <c r="I181" s="8" t="inlineStr">
         <is>
           <t>Class 4</t>
@@ -5785,7 +5785,7 @@
         </is>
       </c>
     </row>
-    <row r="185" ht="26" customHeight="1">
+    <row r="185">
       <c r="A185" s="6" t="inlineStr">
         <is>
           <t>MON</t>
@@ -5794,18 +5794,13 @@
       <c r="B185" s="7" t="inlineStr"/>
       <c r="C185" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (KAR)</t>
-        </is>
-      </c>
-      <c r="D185" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (KAR)
-Class 10 (KAR)</t>
-        </is>
-      </c>
+          <t>Class 5 (KAR)</t>
+        </is>
+      </c>
+      <c r="D185" s="7" t="inlineStr"/>
       <c r="E185" s="7" t="inlineStr">
         <is>
-          <t>Class 9 (KAR)</t>
+          <t>Class 6 (KAR)</t>
         </is>
       </c>
       <c r="F185" s="7" t="inlineStr"/>
@@ -5820,19 +5815,23 @@
         </is>
       </c>
       <c r="B186" s="7" t="inlineStr"/>
-      <c r="C186" s="7" t="inlineStr"/>
+      <c r="C186" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (KAR)</t>
+        </is>
+      </c>
       <c r="D186" s="7" t="inlineStr"/>
       <c r="E186" s="7" t="inlineStr"/>
-      <c r="F186" s="7" t="inlineStr">
+      <c r="F186" s="7" t="inlineStr"/>
+      <c r="G186" s="7" t="inlineStr"/>
+      <c r="H186" s="7" t="inlineStr">
         <is>
           <t>Class 8 (KAR)</t>
         </is>
       </c>
-      <c r="G186" s="7" t="inlineStr"/>
-      <c r="H186" s="7" t="inlineStr"/>
       <c r="I186" s="7" t="inlineStr"/>
     </row>
-    <row r="187">
+    <row r="187" ht="26" customHeight="1">
       <c r="A187" s="6" t="inlineStr">
         <is>
           <t>WED</t>
@@ -5840,12 +5839,13 @@
       </c>
       <c r="B187" s="7" t="inlineStr"/>
       <c r="C187" s="7" t="inlineStr"/>
-      <c r="D187" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (KAR)</t>
-        </is>
-      </c>
-      <c r="E187" s="7" t="inlineStr"/>
+      <c r="D187" s="7" t="inlineStr"/>
+      <c r="E187" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (KAR)
+Class 9 (KAR)</t>
+        </is>
+      </c>
       <c r="F187" s="7" t="inlineStr"/>
       <c r="G187" s="7" t="inlineStr"/>
       <c r="H187" s="7" t="inlineStr"/>
@@ -5859,7 +5859,11 @@
       </c>
       <c r="B188" s="7" t="inlineStr"/>
       <c r="C188" s="7" t="inlineStr"/>
-      <c r="D188" s="7" t="inlineStr"/>
+      <c r="D188" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (KAR)</t>
+        </is>
+      </c>
       <c r="E188" s="7" t="inlineStr"/>
       <c r="F188" s="7" t="inlineStr"/>
       <c r="G188" s="7" t="inlineStr"/>
@@ -5876,20 +5880,12 @@
       <c r="C189" s="7" t="inlineStr"/>
       <c r="D189" s="7" t="inlineStr"/>
       <c r="E189" s="7" t="inlineStr"/>
-      <c r="F189" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (KAR)</t>
-        </is>
-      </c>
-      <c r="G189" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (KAR)</t>
-        </is>
-      </c>
+      <c r="F189" s="7" t="inlineStr"/>
+      <c r="G189" s="7" t="inlineStr"/>
       <c r="H189" s="7" t="inlineStr"/>
       <c r="I189" s="7" t="inlineStr"/>
     </row>
-    <row r="190" ht="26" customHeight="1">
+    <row r="190">
       <c r="A190" s="6" t="inlineStr">
         <is>
           <t>SAT</t>
@@ -5898,14 +5894,21 @@
       <c r="B190" s="7" t="inlineStr"/>
       <c r="C190" s="7" t="inlineStr">
         <is>
-          <t>Class 3 (KAR)
-Class 5 (KAR)</t>
+          <t>Class 1 (KAR)</t>
         </is>
       </c>
       <c r="D190" s="7" t="inlineStr"/>
       <c r="E190" s="7" t="inlineStr"/>
-      <c r="F190" s="7" t="inlineStr"/>
-      <c r="G190" s="7" t="inlineStr"/>
+      <c r="F190" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (KAR)</t>
+        </is>
+      </c>
+      <c r="G190" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (KAR)</t>
+        </is>
+      </c>
       <c r="H190" s="7" t="inlineStr"/>
       <c r="I190" s="7" t="inlineStr"/>
     </row>
@@ -5971,7 +5974,7 @@
         </is>
       </c>
     </row>
-    <row r="194" ht="52" customHeight="1">
+    <row r="194" ht="65" customHeight="1">
       <c r="A194" s="6" t="inlineStr">
         <is>
           <t>MON</t>
@@ -5982,18 +5985,19 @@
       <c r="D194" s="7" t="inlineStr"/>
       <c r="E194" s="7" t="inlineStr"/>
       <c r="F194" s="7" t="inlineStr"/>
-      <c r="G194" s="7" t="inlineStr">
+      <c r="G194" s="7" t="inlineStr"/>
+      <c r="H194" s="7" t="inlineStr">
         <is>
           <t>L.K.G (P.E.T)
+U.K.G (P.E.T)
 Class 1 (P.E.T)
 Class 2 (P.E.T)
 Class 3 (P.E.T)</t>
         </is>
       </c>
-      <c r="H194" s="7" t="inlineStr"/>
       <c r="I194" s="7" t="inlineStr"/>
     </row>
-    <row r="195" ht="65" customHeight="1">
+    <row r="195" ht="52" customHeight="1">
       <c r="A195" s="6" t="inlineStr">
         <is>
           <t>TUE</t>
@@ -6006,17 +6010,16 @@
       <c r="F195" s="7" t="inlineStr"/>
       <c r="G195" s="7" t="inlineStr">
         <is>
-          <t>L.K.G (P.E.T)
-U.K.G (P.E.T)
+          <t>U.K.G (P.E.T)
 Class 1 (P.E.T)
 Class 2 (P.E.T)
-Class 5 (P.E.T)</t>
+Class 4 (P.E.T)</t>
         </is>
       </c>
       <c r="H195" s="7" t="inlineStr"/>
       <c r="I195" s="7" t="inlineStr"/>
     </row>
-    <row r="196" ht="78" customHeight="1">
+    <row r="196">
       <c r="A196" s="6" t="inlineStr">
         <is>
           <t>WED</t>
@@ -6027,20 +6030,11 @@
       <c r="D196" s="7" t="inlineStr"/>
       <c r="E196" s="7" t="inlineStr"/>
       <c r="F196" s="7" t="inlineStr"/>
-      <c r="G196" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (P.E.T)
-U.K.G (P.E.T)
-Class 1 (P.E.T)
-Class 2 (P.E.T)
-Class 3 (P.E.T)
-Class 4 (P.E.T)</t>
-        </is>
-      </c>
+      <c r="G196" s="7" t="inlineStr"/>
       <c r="H196" s="7" t="inlineStr"/>
       <c r="I196" s="7" t="inlineStr"/>
     </row>
-    <row r="197" ht="130" customHeight="1">
+    <row r="197" ht="78" customHeight="1">
       <c r="A197" s="6" t="inlineStr">
         <is>
           <t>THU</t>
@@ -6051,24 +6045,20 @@
       <c r="D197" s="7" t="inlineStr"/>
       <c r="E197" s="7" t="inlineStr"/>
       <c r="F197" s="7" t="inlineStr"/>
-      <c r="G197" s="7" t="inlineStr"/>
-      <c r="H197" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (P.E.T)
+      <c r="G197" s="7" t="inlineStr">
+        <is>
+          <t>L.K.G (P.E.T)
+U.K.G (P.E.T)
 Class 1 (P.E.T)
 Class 2 (P.E.T)
 Class 4 (P.E.T)
-Class 5 (P.E.T)
-Class 6 (P.E.T)
-Class 7 (P.E.T)
-Class 8 (P.E.T)
-Class 9 (P.E.T)
-Class 10 (P.E.T)</t>
-        </is>
-      </c>
+Class 5 (P.E.T)</t>
+        </is>
+      </c>
+      <c r="H197" s="7" t="inlineStr"/>
       <c r="I197" s="7" t="inlineStr"/>
     </row>
-    <row r="198">
+    <row r="198" ht="65" customHeight="1">
       <c r="A198" s="6" t="inlineStr">
         <is>
           <t>FRI</t>
@@ -6079,11 +6069,19 @@
       <c r="D198" s="7" t="inlineStr"/>
       <c r="E198" s="7" t="inlineStr"/>
       <c r="F198" s="7" t="inlineStr"/>
-      <c r="G198" s="7" t="inlineStr"/>
+      <c r="G198" s="7" t="inlineStr">
+        <is>
+          <t>L.K.G (P.E.T)
+Class 1 (P.E.T)
+Class 2 (P.E.T)
+Class 3 (P.E.T)
+Class 5 (P.E.T)</t>
+        </is>
+      </c>
       <c r="H198" s="7" t="inlineStr"/>
       <c r="I198" s="7" t="inlineStr"/>
     </row>
-    <row r="199">
+    <row r="199" ht="65" customHeight="1">
       <c r="A199" s="6" t="inlineStr">
         <is>
           <t>SAT</t>
@@ -6095,7 +6093,15 @@
       <c r="E199" s="7" t="inlineStr"/>
       <c r="F199" s="7" t="inlineStr"/>
       <c r="G199" s="7" t="inlineStr"/>
-      <c r="H199" s="7" t="inlineStr"/>
+      <c r="H199" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (P.E.T)
+Class 7 (P.E.T)
+Class 8 (P.E.T)
+Class 9 (P.E.T)
+Class 10 (P.E.T)</t>
+        </is>
+      </c>
       <c r="I199" s="7" t="inlineStr"/>
     </row>
   </sheetData>
@@ -6237,7 +6243,7 @@
       <c r="C2" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(MATH)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="D2" s="7" t="inlineStr">
@@ -6273,7 +6279,7 @@
       <c r="I2" s="7" t="inlineStr">
         <is>
           <t>MAHA
-(ENG)</t>
+(GRAM)</t>
         </is>
       </c>
       <c r="J2" s="7" t="inlineStr">
@@ -6302,8 +6308,8 @@
       </c>
       <c r="N2" s="7" t="inlineStr">
         <is>
-          <t>GOWTHAM
-(MATH)</t>
+          <t>RAVI
+(GRAM)</t>
         </is>
       </c>
     </row>
@@ -6315,55 +6321,55 @@
       <c r="C3" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(MATH)</t>
+(ORAL)</t>
         </is>
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
+          <t>SWATHI
+(HIN)</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>MAHESWARI
+(COMP)</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>NAGAMANI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
           <t>SAI LAKSHMI
-(ENG)</t>
-        </is>
-      </c>
-      <c r="E3" s="7" t="inlineStr">
-        <is>
-          <t>NAGAMANI
 (G.K)</t>
         </is>
       </c>
-      <c r="F3" s="7" t="inlineStr">
-        <is>
-          <t>MAHA
-(ENG)</t>
-        </is>
-      </c>
-      <c r="G3" s="7" t="inlineStr">
+      <c r="H3" s="7" t="inlineStr">
         <is>
           <t>PALLAVI
 (SOC)</t>
         </is>
       </c>
-      <c r="H3" s="7" t="inlineStr">
+      <c r="I3" s="7" t="inlineStr">
         <is>
           <t>MARTIAL ARTS
 (KAR)</t>
         </is>
       </c>
-      <c r="I3" s="7" t="inlineStr">
-        <is>
-          <t>FATHIMA
-(HIN)</t>
-        </is>
-      </c>
       <c r="J3" s="7" t="inlineStr">
         <is>
-          <t>MAHESWARI
-(COMP)</t>
+          <t>RAVI
+(ENG)</t>
         </is>
       </c>
       <c r="K3" s="7" t="inlineStr">
         <is>
-          <t>D.V.RAO
-(TEL)</t>
+          <t>LALITHA
+(BIO)</t>
         </is>
       </c>
       <c r="L3" s="7" t="inlineStr">
@@ -6380,8 +6386,8 @@
       </c>
       <c r="N3" s="7" t="inlineStr">
         <is>
-          <t>BHEEMA
-(PHY)</t>
+          <t>RIYA
+(HIN)</t>
         </is>
       </c>
     </row>
@@ -6393,73 +6399,73 @@
       <c r="C4" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(EVS)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>SWATHI
-(HIN)</t>
-        </is>
-      </c>
-      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>BHAVANI
 (MATH)</t>
         </is>
       </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>SAI LAKSHMI
+(EVS)</t>
+        </is>
+      </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>SAI LAKSHMI
-(HIN)</t>
+          <t>MAHA
+(ENG)</t>
         </is>
       </c>
       <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>LALITHA
+(EVS)</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>TULASI
 (MATH)</t>
         </is>
       </c>
-      <c r="H4" s="7" t="inlineStr">
-        <is>
-          <t>MAHA
-(ENG)</t>
-        </is>
-      </c>
       <c r="I4" s="7" t="inlineStr">
         <is>
-          <t>PALLAVI
-(SOC)</t>
+          <t>MAHESWARI
+(COMP)</t>
         </is>
       </c>
       <c r="J4" s="7" t="inlineStr">
         <is>
-          <t>RAVI
-(GRAM)</t>
+          <t>SANGEETHA
+(MATH)</t>
         </is>
       </c>
       <c r="K4" s="7" t="inlineStr">
         <is>
-          <t>MARTIAL ARTS
-(KAR)</t>
+          <t>FATHIMA
+(G.K)</t>
         </is>
       </c>
       <c r="L4" s="7" t="inlineStr">
+        <is>
+          <t>D.V.RAO
+(TEL)</t>
+        </is>
+      </c>
+      <c r="M4" s="7" t="inlineStr">
         <is>
           <t>BHEEMA
 (CHEM)</t>
         </is>
       </c>
-      <c r="M4" s="7" t="inlineStr">
+      <c r="N4" s="7" t="inlineStr">
         <is>
           <t>GOWTHAM
 (MATH)</t>
-        </is>
-      </c>
-      <c r="N4" s="7" t="inlineStr">
-        <is>
-          <t>MARTIAL ARTS
-(KAR)</t>
         </is>
       </c>
     </row>
@@ -6470,20 +6476,20 @@
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>NAGAMANI
-(TEL)</t>
+          <t>SITHA
+(MATH)</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
           <t>BHAVANI
-(EVS)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
           <t>SAI LAKSHMI
-(EVS)</t>
+(HIN)</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
@@ -6494,50 +6500,50 @@
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>RIYA
-(HIN)</t>
+          <t>MAHA
+(ENG)</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
-        <is>
-          <t>FATHIMA
-(HIN)</t>
-        </is>
-      </c>
-      <c r="I5" s="7" t="inlineStr">
         <is>
           <t>SWATHI
 (TEL)</t>
         </is>
       </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>PALLAVI
+(SOC)</t>
+        </is>
+      </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
+          <t>MARTIAL ARTS
+(KAR)</t>
+        </is>
+      </c>
+      <c r="K5" s="7" t="inlineStr">
+        <is>
+          <t>LALITHA
+(PHY)</t>
+        </is>
+      </c>
+      <c r="L5" s="7" t="inlineStr">
+        <is>
           <t>RAVI
-(ENG)</t>
-        </is>
-      </c>
-      <c r="K5" s="7" t="inlineStr">
-        <is>
-          <t>SANGEETHA
-(COMP)</t>
-        </is>
-      </c>
-      <c r="L5" s="7" t="inlineStr">
+(GRAM)</t>
+        </is>
+      </c>
+      <c r="M5" s="7" t="inlineStr">
+        <is>
+          <t>SUNITHA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="N5" s="7" t="inlineStr">
         <is>
           <t>D.V.RAO
 (TEL)</t>
-        </is>
-      </c>
-      <c r="M5" s="7" t="inlineStr">
-        <is>
-          <t>MARTIAL ARTS
-(KAR)</t>
-        </is>
-      </c>
-      <c r="N5" s="7" t="inlineStr">
-        <is>
-          <t>SUNITHA
-(SOC)</t>
         </is>
       </c>
     </row>
@@ -6549,7 +6555,7 @@
       <c r="C6" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(ORAL)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
@@ -6566,28 +6572,28 @@
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>NAGAMANI
-(TEL)</t>
+          <t>BHAVANI
+(G.K)</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>TULASI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>LALITHA
 (EVS)</t>
         </is>
       </c>
-      <c r="H6" s="7" t="inlineStr">
+      <c r="I6" s="7" t="inlineStr">
         <is>
           <t>SWATHI
 (TEL)</t>
         </is>
       </c>
-      <c r="I6" s="7" t="inlineStr">
-        <is>
-          <t>TULASI
-(MATH)</t>
-        </is>
-      </c>
       <c r="J6" s="7" t="inlineStr">
         <is>
           <t>PALLAVI
@@ -6596,8 +6602,8 @@
       </c>
       <c r="K6" s="7" t="inlineStr">
         <is>
-          <t>FATHIMA
-(HIN)</t>
+          <t>RAVI
+(ENG)</t>
         </is>
       </c>
       <c r="L6" s="7" t="inlineStr">
@@ -6608,14 +6614,14 @@
       </c>
       <c r="M6" s="7" t="inlineStr">
         <is>
+          <t>CHALAPATHI
+(BIO)</t>
+        </is>
+      </c>
+      <c r="N6" s="7" t="inlineStr">
+        <is>
           <t>SUNITHA
 (SOC)</t>
-        </is>
-      </c>
-      <c r="N6" s="7" t="inlineStr">
-        <is>
-          <t>RIYA
-(HIN)</t>
         </is>
       </c>
     </row>
@@ -6626,74 +6632,74 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
+          <t>SITHA
+(ENG)</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
+          <t>NAGAMANI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
           <t>BHAVANI
-(EVS)</t>
-        </is>
-      </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>P.E
-(P.E.T)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
+          <t>SAI LAKSHMI
+(HIN)</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
+          <t>PALLAVI
+(SOC)</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
+          <t>FATHIMA
+(HIN)</t>
+        </is>
+      </c>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>MAHA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
           <t>LALITHA
-(EVS)</t>
-        </is>
-      </c>
-      <c r="I7" s="7" t="inlineStr">
-        <is>
-          <t>MAHA
-(GRAM)</t>
-        </is>
-      </c>
-      <c r="J7" s="7" t="inlineStr">
-        <is>
-          <t>SWATHI
+(CHEM)</t>
+        </is>
+      </c>
+      <c r="K7" s="7" t="inlineStr">
+        <is>
+          <t>D.V.RAO
 (TEL)</t>
         </is>
       </c>
-      <c r="K7" s="7" t="inlineStr">
-        <is>
-          <t>RAVI
+      <c r="L7" s="7" t="inlineStr">
+        <is>
+          <t>SUNITHA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="M7" s="7" t="inlineStr">
+        <is>
+          <t>SONU
 (ENG)</t>
         </is>
       </c>
-      <c r="L7" s="7" t="inlineStr">
+      <c r="N7" s="7" t="inlineStr">
         <is>
           <t>CHALAPATHI
 (BIO)</t>
-        </is>
-      </c>
-      <c r="M7" s="7" t="inlineStr">
-        <is>
-          <t>RIYA
-(HIN)</t>
-        </is>
-      </c>
-      <c r="N7" s="7" t="inlineStr">
-        <is>
-          <t>SONU
-(ENG)</t>
         </is>
       </c>
     </row>
@@ -6704,40 +6710,40 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>SITHA
-(EVS)</t>
+          <t>P.E
+(P.E.T)</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>NAGAMANI
-(TEL)</t>
+          <t>P.E
+(P.E.T)</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>SAI LAKSHMI
-(HIN)</t>
+          <t>P.E
+(P.E.T)</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>TULASI
-(MATH)</t>
+          <t>P.E
+(P.E.T)</t>
         </is>
       </c>
       <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>P.E
+(P.E.T)</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>MAHA
 (ENG)</t>
         </is>
       </c>
-      <c r="H8" s="7" t="inlineStr">
-        <is>
-          <t>PALLAVI
-(SOC)</t>
-        </is>
-      </c>
       <c r="I8" s="7" t="inlineStr">
         <is>
           <t>LALITHA
@@ -6746,32 +6752,32 @@
       </c>
       <c r="J8" s="7" t="inlineStr">
         <is>
-          <t>FATHIMA
+          <t>SWATHI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="K8" s="7" t="inlineStr">
+        <is>
+          <t>RAVI
+(GRAM)</t>
+        </is>
+      </c>
+      <c r="L8" s="7" t="inlineStr">
+        <is>
+          <t>CHALAPATHI
+(BIO)</t>
+        </is>
+      </c>
+      <c r="M8" s="7" t="inlineStr">
+        <is>
+          <t>RIYA
 (HIN)</t>
         </is>
       </c>
-      <c r="K8" s="7" t="inlineStr">
-        <is>
-          <t>SANGEETHA
-(MATH)</t>
-        </is>
-      </c>
-      <c r="L8" s="7" t="inlineStr">
-        <is>
-          <t>SUNITHA
-(SOC)</t>
-        </is>
-      </c>
-      <c r="M8" s="7" t="inlineStr">
+      <c r="N8" s="7" t="inlineStr">
         <is>
           <t>SONU
 (ENG)</t>
-        </is>
-      </c>
-      <c r="N8" s="7" t="inlineStr">
-        <is>
-          <t>D.V.RAO
-(TEL)</t>
         </is>
       </c>
     </row>
@@ -6865,25 +6871,25 @@
       <c r="C10" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(ORAL)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
           <t>BHAVANI
-(EVS)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
           <t>NAGAMANI
-(TEL)</t>
+(G.K)</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
           <t>SAI LAKSHMI
-(EVS)</t>
+(HIN)</t>
         </is>
       </c>
       <c r="G10" s="7" t="inlineStr">
@@ -6919,7 +6925,7 @@
       <c r="L10" s="7" t="inlineStr">
         <is>
           <t>FATHIMA
-(HIN)</t>
+(G.K)</t>
         </is>
       </c>
       <c r="M10" s="7" t="inlineStr">
@@ -6943,7 +6949,7 @@
       <c r="C11" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(MATH)</t>
+(ORAL)</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
@@ -6960,56 +6966,56 @@
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>NAGAMANI
+          <t>MAHA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>PALLAVI
+(SOC)</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>SWATHI
 (TEL)</t>
         </is>
       </c>
-      <c r="G11" s="7" t="inlineStr">
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>TULASI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>SANGEETHA
+(MATH)</t>
+        </is>
+      </c>
+      <c r="K11" s="7" t="inlineStr">
+        <is>
+          <t>MARTIAL ARTS
+(KAR)</t>
+        </is>
+      </c>
+      <c r="L11" s="7" t="inlineStr">
+        <is>
+          <t>SUNITHA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="M11" s="7" t="inlineStr">
+        <is>
+          <t>BHEEMA
+(PHY)</t>
+        </is>
+      </c>
+      <c r="N11" s="7" t="inlineStr">
         <is>
           <t>RIYA
 (HIN)</t>
-        </is>
-      </c>
-      <c r="H11" s="7" t="inlineStr">
-        <is>
-          <t>MAHA
-(GRAM)</t>
-        </is>
-      </c>
-      <c r="I11" s="7" t="inlineStr">
-        <is>
-          <t>SWATHI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="J11" s="7" t="inlineStr">
-        <is>
-          <t>FATHIMA
-(HIN)</t>
-        </is>
-      </c>
-      <c r="K11" s="7" t="inlineStr">
-        <is>
-          <t>LALITHA
-(CHEM)</t>
-        </is>
-      </c>
-      <c r="L11" s="7" t="inlineStr">
-        <is>
-          <t>SUNITHA
-(SOC)</t>
-        </is>
-      </c>
-      <c r="M11" s="7" t="inlineStr">
-        <is>
-          <t>BHEEMA
-(PHY)</t>
-        </is>
-      </c>
-      <c r="N11" s="7" t="inlineStr">
-        <is>
-          <t>RAVI
-(GRAM)</t>
         </is>
       </c>
     </row>
@@ -7020,56 +7026,56 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
+          <t>SITHA
+(EVS)</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
           <t>NAGAMANI
 (TEL)</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>SAI LAKSHMI
-(ENG)</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>MAHA
-(ENG)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>BHAVANI
+(G.K)</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
         <is>
           <t>TULASI
 (MATH)</t>
         </is>
       </c>
-      <c r="G12" s="7" t="inlineStr">
-        <is>
-          <t>PALLAVI
-(SOC)</t>
-        </is>
-      </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
+          <t>FATHIMA
+(HIN)</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>SWATHI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="J12" s="7" t="inlineStr">
+        <is>
+          <t>RAVI
+(GRAM)</t>
+        </is>
+      </c>
+      <c r="K12" s="7" t="inlineStr">
+        <is>
           <t>LALITHA
-(EVS)</t>
-        </is>
-      </c>
-      <c r="I12" s="7" t="inlineStr">
-        <is>
-          <t>MAHESWARI
-(COMP)</t>
-        </is>
-      </c>
-      <c r="J12" s="7" t="inlineStr">
-        <is>
-          <t>RAVI
-(ENG)</t>
-        </is>
-      </c>
-      <c r="K12" s="7" t="inlineStr">
-        <is>
-          <t>D.V.RAO
-(TEL)</t>
+(CHEM)</t>
         </is>
       </c>
       <c r="L12" s="7" t="inlineStr">
@@ -7087,7 +7093,7 @@
       <c r="N12" s="7" t="inlineStr">
         <is>
           <t>BHEEMA
-(PHY)</t>
+(CHEM)</t>
         </is>
       </c>
     </row>
@@ -7099,31 +7105,31 @@
       <c r="C13" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(MATH)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>BHAVANI
-(MATH)</t>
+          <t>SAI LAKSHMI
+(ENG)</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>MAHESWARI
-(COMP)</t>
+          <t>MAHA
+(ENG)</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>SAI LAKSHMI
-(EVS)</t>
+          <t>NAGAMANI
+(TEL)</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>TULASI
-(MATH)</t>
+          <t>RIYA
+(HIN)</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr">
@@ -7140,8 +7146,8 @@
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
-          <t>SANGEETHA
-(G.K)</t>
+          <t>RAVI
+(ENG)</t>
         </is>
       </c>
       <c r="K13" s="7" t="inlineStr">
@@ -7156,16 +7162,15 @@
 (TEL)</t>
         </is>
       </c>
-      <c r="M13" s="7" t="inlineStr">
+      <c r="M13" s="12" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+      <c r="N13" s="7" t="inlineStr">
         <is>
           <t>SUNITHA
 (SOC)</t>
-        </is>
-      </c>
-      <c r="N13" s="7" t="inlineStr">
-        <is>
-          <t>RIYA
-(HIN)</t>
         </is>
       </c>
     </row>
@@ -7188,26 +7193,26 @@
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
+          <t>NAGAMANI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
           <t>SAI LAKSHMI
-(HIN)</t>
-        </is>
-      </c>
-      <c r="F14" s="7" t="inlineStr">
+(EVS)</t>
+        </is>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
         <is>
           <t>MAHA
 (ENG)</t>
         </is>
       </c>
-      <c r="G14" s="7" t="inlineStr">
-        <is>
-          <t>TULASI
-(MATH)</t>
-        </is>
-      </c>
       <c r="H14" s="7" t="inlineStr">
         <is>
-          <t>SWATHI
-(TEL)</t>
+          <t>LALITHA
+(EVS)</t>
         </is>
       </c>
       <c r="I14" s="7" t="inlineStr">
@@ -7224,20 +7229,20 @@
       </c>
       <c r="K14" s="7" t="inlineStr">
         <is>
-          <t>LALITHA
+          <t>RAVI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="L14" s="7" t="inlineStr">
+        <is>
+          <t>CHALAPATHI
 (BIO)</t>
         </is>
       </c>
-      <c r="L14" s="7" t="inlineStr">
-        <is>
-          <t>MARTIAL ARTS
-(KAR)</t>
-        </is>
-      </c>
       <c r="M14" s="7" t="inlineStr">
         <is>
-          <t>RAVI
-(GRAM)</t>
+          <t>SUNITHA
+(SOC)</t>
         </is>
       </c>
       <c r="N14" s="7" t="inlineStr">
@@ -7254,44 +7259,44 @@
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
+          <t>SITHA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
           <t>P.E
 (P.E.T)</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr">
+      <c r="E15" s="7" t="inlineStr">
         <is>
           <t>P.E
 (P.E.T)</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
+      <c r="F15" s="7" t="inlineStr">
         <is>
           <t>P.E
 (P.E.T)</t>
         </is>
       </c>
-      <c r="F15" s="7" t="inlineStr">
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>TULASI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
         <is>
           <t>P.E
 (P.E.T)</t>
         </is>
       </c>
-      <c r="G15" s="7" t="inlineStr">
-        <is>
-          <t>LALITHA
-(EVS)</t>
-        </is>
-      </c>
-      <c r="H15" s="7" t="inlineStr">
-        <is>
-          <t>MAHA
-(ENG)</t>
-        </is>
-      </c>
       <c r="I15" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
+          <t>PALLAVI
+(SOC)</t>
         </is>
       </c>
       <c r="J15" s="7" t="inlineStr">
@@ -7302,8 +7307,8 @@
       </c>
       <c r="K15" s="7" t="inlineStr">
         <is>
-          <t>FATHIMA
-(G.K)</t>
+          <t>SANGEETHA
+(MATH)</t>
         </is>
       </c>
       <c r="L15" s="7" t="inlineStr">
@@ -7314,14 +7319,14 @@
       </c>
       <c r="M15" s="7" t="inlineStr">
         <is>
-          <t>CHALAPATHI
-(BIO)</t>
+          <t>RIYA
+(HIN)</t>
         </is>
       </c>
       <c r="N15" s="7" t="inlineStr">
         <is>
-          <t>SUNITHA
-(SOC)</t>
+          <t>D.V.RAO
+(TEL)</t>
         </is>
       </c>
     </row>
@@ -7332,62 +7337,62 @@
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>SITHA
-(ENG)</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
           <t>NAGAMANI
 (TEL)</t>
         </is>
       </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>SWATHI
+(HIN)</t>
+        </is>
+      </c>
       <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>BHAVANI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="F16" s="7" t="inlineStr">
         <is>
           <t>SAI LAKSHMI
 (HIN)</t>
         </is>
       </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>MAHESWARI
+(COMP)</t>
+        </is>
+      </c>
       <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>LALITHA
+(EVS)</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="inlineStr">
         <is>
           <t>MAHA
 (ENG)</t>
         </is>
       </c>
-      <c r="H16" s="7" t="inlineStr">
+      <c r="I16" s="7" t="inlineStr">
         <is>
           <t>TULASI
 (MATH)</t>
         </is>
       </c>
-      <c r="I16" s="7" t="inlineStr">
-        <is>
-          <t>PALLAVI
-(SOC)</t>
-        </is>
-      </c>
       <c r="J16" s="7" t="inlineStr">
         <is>
-          <t>LALITHA
-(BIO)</t>
+          <t>FATHIMA
+(HIN)</t>
         </is>
       </c>
       <c r="K16" s="7" t="inlineStr">
         <is>
-          <t>RAVI
-(ENG)</t>
+          <t>D.V.RAO
+(TEL)</t>
         </is>
       </c>
       <c r="L16" s="7" t="inlineStr">
         <is>
-          <t>SANGEETHA
-(MATH)</t>
+          <t>MARTIAL ARTS
+(KAR)</t>
         </is>
       </c>
       <c r="M16" s="7" t="inlineStr">
@@ -7398,8 +7403,8 @@
       </c>
       <c r="N16" s="7" t="inlineStr">
         <is>
-          <t>D.V.RAO
-(TEL)</t>
+          <t>CHALAPATHI
+(BIO)</t>
         </is>
       </c>
     </row>
@@ -7493,13 +7498,13 @@
       <c r="C18" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(ORAL)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
           <t>BHAVANI
-(MATH)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
@@ -7559,7 +7564,7 @@
       <c r="N18" s="7" t="inlineStr">
         <is>
           <t>BHEEMA
-(CHEM)</t>
+(PHY)</t>
         </is>
       </c>
     </row>
@@ -7570,32 +7575,32 @@
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
+          <t>SITHA
+(MATH)</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>SAI LAKSHMI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>BHAVANI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
           <t>NAGAMANI
 (TEL)</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>BHAVANI
-(EVS)</t>
-        </is>
-      </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>MAHA
-(ENG)</t>
-        </is>
-      </c>
-      <c r="F19" s="7" t="inlineStr">
-        <is>
-          <t>SAI LAKSHMI
-(EVS)</t>
-        </is>
-      </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>TULASI
-(MATH)</t>
+          <t>RIYA
+(HIN)</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr">
@@ -7606,26 +7611,26 @@
       </c>
       <c r="I19" s="7" t="inlineStr">
         <is>
+          <t>SWATHI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="J19" s="7" t="inlineStr">
+        <is>
+          <t>RAVI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="K19" s="7" t="inlineStr">
+        <is>
           <t>LALITHA
-(EVS)</t>
-        </is>
-      </c>
-      <c r="J19" s="7" t="inlineStr">
-        <is>
-          <t>PALLAVI
-(SOC)</t>
-        </is>
-      </c>
-      <c r="K19" s="7" t="inlineStr">
-        <is>
-          <t>SANGEETHA
-(MATH)</t>
+(PHY)</t>
         </is>
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
           <t>BHEEMA
-(CHEM)</t>
+(PHY)</t>
         </is>
       </c>
       <c r="M19" s="7" t="inlineStr">
@@ -7636,8 +7641,8 @@
       </c>
       <c r="N19" s="7" t="inlineStr">
         <is>
-          <t>RIYA
-(HIN)</t>
+          <t>SUNITHA
+(SOC)</t>
         </is>
       </c>
     </row>
@@ -7649,55 +7654,55 @@
       <c r="C20" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(EVS)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>SWATHI
-(HIN)</t>
-        </is>
-      </c>
-      <c r="E20" s="7" t="inlineStr">
         <is>
           <t>BHAVANI
 (MATH)</t>
         </is>
       </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>SAI LAKSHMI
+(HIN)</t>
+        </is>
+      </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>MAHESWARI
-(COMP)</t>
+          <t>MAHA
+(ENG)</t>
         </is>
       </c>
       <c r="G20" s="7" t="inlineStr">
-        <is>
-          <t>SAI LAKSHMI
-(G.K)</t>
-        </is>
-      </c>
-      <c r="H20" s="7" t="inlineStr">
         <is>
           <t>LALITHA
 (EVS)</t>
         </is>
       </c>
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>SWATHI
+(TEL)</t>
+        </is>
+      </c>
       <c r="I20" s="7" t="inlineStr">
         <is>
-          <t>TULASI
+          <t>PALLAVI
+(SOC)</t>
+        </is>
+      </c>
+      <c r="J20" s="7" t="inlineStr">
+        <is>
+          <t>FATHIMA
+(HIN)</t>
+        </is>
+      </c>
+      <c r="K20" s="7" t="inlineStr">
+        <is>
+          <t>SANGEETHA
 (MATH)</t>
-        </is>
-      </c>
-      <c r="J20" s="7" t="inlineStr">
-        <is>
-          <t>MARTIAL ARTS
-(KAR)</t>
-        </is>
-      </c>
-      <c r="K20" s="7" t="inlineStr">
-        <is>
-          <t>RAVI
-(ENG)</t>
         </is>
       </c>
       <c r="L20" s="7" t="inlineStr">
@@ -7709,7 +7714,7 @@
       <c r="M20" s="7" t="inlineStr">
         <is>
           <t>BHEEMA
-(CHEM)</t>
+(PHY)</t>
         </is>
       </c>
       <c r="N20" s="7" t="inlineStr">
@@ -7727,7 +7732,7 @@
       <c r="C21" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(EVS)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
@@ -7739,61 +7744,60 @@
       <c r="E21" s="7" t="inlineStr">
         <is>
           <t>SAI LAKSHMI
-(HIN)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>TULASI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
         <is>
           <t>MAHA
 (ENG)</t>
         </is>
       </c>
-      <c r="G21" s="7" t="inlineStr">
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>MARTIAL ARTS
+(KAR)</t>
+        </is>
+      </c>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>LALITHA
+(EVS)</t>
+        </is>
+      </c>
+      <c r="J21" s="7" t="inlineStr">
         <is>
           <t>PALLAVI
 (SOC)</t>
         </is>
       </c>
-      <c r="H21" s="7" t="inlineStr">
-        <is>
-          <t>SWATHI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="I21" s="7" t="inlineStr">
-        <is>
-          <t>FATHIMA
-(HIN)</t>
-        </is>
-      </c>
-      <c r="J21" s="7" t="inlineStr">
-        <is>
-          <t>RAVI
-(ENG)</t>
-        </is>
-      </c>
       <c r="K21" s="7" t="inlineStr">
-        <is>
-          <t>LALITHA
-(CHEM)</t>
-        </is>
-      </c>
-      <c r="L21" s="7" t="inlineStr">
         <is>
           <t>SANGEETHA
 (MATH)</t>
         </is>
       </c>
-      <c r="M21" s="7" t="inlineStr">
-        <is>
-          <t>RIYA
-(HIN)</t>
-        </is>
-      </c>
-      <c r="N21" s="7" t="inlineStr">
+      <c r="L21" s="7" t="inlineStr">
         <is>
           <t>SUNITHA
 (SOC)</t>
+        </is>
+      </c>
+      <c r="M21" s="7" t="inlineStr">
+        <is>
+          <t>MARTIAL ARTS
+(KAR)</t>
+        </is>
+      </c>
+      <c r="N21" s="12" t="inlineStr">
+        <is>
+          <t>Recreation</t>
         </is>
       </c>
     </row>
@@ -7805,33 +7809,33 @@
       <c r="C22" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(ENG)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>SAI LAKSHMI
-(ENG)</t>
-        </is>
-      </c>
-      <c r="E22" s="7" t="inlineStr">
         <is>
           <t>BHAVANI
 (MATH)</t>
         </is>
       </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>MAHA
+(ENG)</t>
+        </is>
+      </c>
       <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>SAI LAKSHMI
+(EVS)</t>
+        </is>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
         <is>
           <t>TULASI
 (MATH)</t>
         </is>
       </c>
-      <c r="G22" s="7" t="inlineStr">
-        <is>
-          <t>MAHA
-(ENG)</t>
-        </is>
-      </c>
       <c r="H22" s="7" t="inlineStr">
         <is>
           <t>PALLAVI
@@ -7840,8 +7844,8 @@
       </c>
       <c r="I22" s="7" t="inlineStr">
         <is>
-          <t>SWATHI
-(TEL)</t>
+          <t>SANGEETHA
+(G.K)</t>
         </is>
       </c>
       <c r="J22" s="7" t="inlineStr">
@@ -7858,20 +7862,20 @@
       </c>
       <c r="L22" s="7" t="inlineStr">
         <is>
+          <t>CHALAPATHI
+(BIO)</t>
+        </is>
+      </c>
+      <c r="M22" s="7" t="inlineStr">
+        <is>
+          <t>SUNITHA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="N22" s="7" t="inlineStr">
+        <is>
           <t>SONU
 (ENG)</t>
-        </is>
-      </c>
-      <c r="M22" s="7" t="inlineStr">
-        <is>
-          <t>SUNITHA
-(SOC)</t>
-        </is>
-      </c>
-      <c r="N22" s="7" t="inlineStr">
-        <is>
-          <t>CHALAPATHI
-(BIO)</t>
         </is>
       </c>
     </row>
@@ -7882,68 +7886,68 @@
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
+          <t>NAGAMANI
+(TEL)</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
+          <t>BHAVANI
+(MATH)</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
+          <t>SAI LAKSHMI
+(EVS)</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
+          <t>MAHA
+(GRAM)</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
+          <t>MAHESWARI
+(COMP)</t>
         </is>
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
+          <t>LALITHA
+(EVS)</t>
         </is>
       </c>
       <c r="I23" s="7" t="inlineStr">
         <is>
-          <t>PALLAVI
-(SOC)</t>
+          <t>TULASI
+(MATH)</t>
         </is>
       </c>
       <c r="J23" s="7" t="inlineStr">
+        <is>
+          <t>SWATHI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="K23" s="7" t="inlineStr">
         <is>
           <t>FATHIMA
 (HIN)</t>
         </is>
       </c>
-      <c r="K23" s="7" t="inlineStr">
-        <is>
-          <t>LALITHA
-(BIO)</t>
-        </is>
-      </c>
       <c r="L23" s="7" t="inlineStr">
-        <is>
-          <t>SANGEETHA
-(MATH)</t>
-        </is>
-      </c>
-      <c r="M23" s="7" t="inlineStr">
         <is>
           <t>SONU
 (ENG)</t>
+        </is>
+      </c>
+      <c r="M23" s="7" t="inlineStr">
+        <is>
+          <t>RIYA
+(HIN)</t>
         </is>
       </c>
       <c r="N23" s="7" t="inlineStr">
@@ -7961,31 +7965,31 @@
       <c r="C24" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(EVS)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>BHAVANI
-(EVS)</t>
+          <t>SWATHI
+(HIN)</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>NAGAMANI
+(G.K)</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
         <is>
           <t>SAI LAKSHMI
 (EVS)</t>
         </is>
       </c>
-      <c r="F24" s="7" t="inlineStr">
-        <is>
-          <t>NAGAMANI
-(TEL)</t>
-        </is>
-      </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>LALITHA
-(EVS)</t>
+          <t>PALLAVI
+(SOC)</t>
         </is>
       </c>
       <c r="H24" s="7" t="inlineStr">
@@ -7996,38 +8000,37 @@
       </c>
       <c r="I24" s="7" t="inlineStr">
         <is>
-          <t>TULASI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="J24" s="7" t="inlineStr">
-        <is>
-          <t>SWATHI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="K24" s="7" t="inlineStr">
-        <is>
           <t>FATHIMA
 (HIN)</t>
         </is>
       </c>
+      <c r="J24" s="7" t="inlineStr">
+        <is>
+          <t>LALITHA
+(BIO)</t>
+        </is>
+      </c>
+      <c r="K24" s="7" t="inlineStr">
+        <is>
+          <t>RAVI
+(ENG)</t>
+        </is>
+      </c>
       <c r="L24" s="7" t="inlineStr">
         <is>
-          <t>SUNITHA
-(SOC)</t>
+          <t>SANGEETHA
+(MATH)</t>
         </is>
       </c>
       <c r="M24" s="7" t="inlineStr">
-        <is>
-          <t>CHALAPATHI
-(BIO)</t>
-        </is>
-      </c>
-      <c r="N24" s="7" t="inlineStr">
         <is>
           <t>SONU
 (ENG)</t>
+        </is>
+      </c>
+      <c r="N24" s="12" t="inlineStr">
+        <is>
+          <t>Recreation</t>
         </is>
       </c>
     </row>
@@ -8121,13 +8124,13 @@
       <c r="C26" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(ENG)</t>
+(ORAL)</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
           <t>BHAVANI
-(MATH)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
@@ -8139,7 +8142,7 @@
       <c r="F26" s="7" t="inlineStr">
         <is>
           <t>SAI LAKSHMI
-(EVS)</t>
+(HIN)</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">
@@ -8163,7 +8166,7 @@
       <c r="J26" s="7" t="inlineStr">
         <is>
           <t>SANGEETHA
-(MATH)</t>
+(G.K)</t>
         </is>
       </c>
       <c r="K26" s="7" t="inlineStr">
@@ -8184,9 +8187,10 @@
 (TEL)</t>
         </is>
       </c>
-      <c r="N26" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
+      <c r="N26" s="7" t="inlineStr">
+        <is>
+          <t>GOWTHAM
+(MATH)</t>
         </is>
       </c>
     </row>
@@ -8198,13 +8202,13 @@
       <c r="C27" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(ENG)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>SWATHI
-(HIN)</t>
+          <t>NAGAMANI
+(TEL)</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
@@ -8215,8 +8219,8 @@
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>NAGAMANI
-(TEL)</t>
+          <t>TULASI
+(MATH)</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr">
@@ -8227,26 +8231,26 @@
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
+          <t>MAHA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>FATHIMA
+(HIN)</t>
+        </is>
+      </c>
+      <c r="J27" s="7" t="inlineStr">
+        <is>
           <t>PALLAVI
 (SOC)</t>
         </is>
       </c>
-      <c r="I27" s="7" t="inlineStr">
-        <is>
-          <t>TULASI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="J27" s="7" t="inlineStr">
+      <c r="K27" s="7" t="inlineStr">
         <is>
           <t>LALITHA
-(BIO)</t>
-        </is>
-      </c>
-      <c r="K27" s="7" t="inlineStr">
-        <is>
-          <t>FATHIMA
-(HIN)</t>
+(CHEM)</t>
         </is>
       </c>
       <c r="L27" s="7" t="inlineStr">
@@ -8263,8 +8267,8 @@
       </c>
       <c r="N27" s="7" t="inlineStr">
         <is>
-          <t>GOWTHAM
-(MATH)</t>
+          <t>D.V.RAO
+(TEL)</t>
         </is>
       </c>
     </row>
@@ -8276,63 +8280,63 @@
       <c r="C28" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(EVS)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>SAI LAKSHMI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
         <is>
           <t>BHAVANI
 (MATH)</t>
         </is>
       </c>
-      <c r="E28" s="7" t="inlineStr">
-        <is>
-          <t>MAHA
-(ENG)</t>
-        </is>
-      </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>SAI LAKSHMI
-(HIN)</t>
+          <t>MAHESWARI
+(COMP)</t>
         </is>
       </c>
       <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>PALLAVI
+(SOC)</t>
+        </is>
+      </c>
+      <c r="H28" s="7" t="inlineStr">
+        <is>
+          <t>SWATHI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="I28" s="7" t="inlineStr">
         <is>
           <t>LALITHA
 (EVS)</t>
         </is>
       </c>
-      <c r="H28" s="7" t="inlineStr">
-        <is>
-          <t>SWATHI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="I28" s="7" t="inlineStr">
-        <is>
-          <t>TULASI
-(MATH)</t>
-        </is>
-      </c>
       <c r="J28" s="7" t="inlineStr">
-        <is>
-          <t>PALLAVI
-(SOC)</t>
-        </is>
-      </c>
-      <c r="K28" s="7" t="inlineStr">
         <is>
           <t>RAVI
 (ENG)</t>
         </is>
       </c>
-      <c r="L28" s="7" t="inlineStr">
+      <c r="K28" s="7" t="inlineStr">
         <is>
           <t>SANGEETHA
 (COMP)</t>
         </is>
       </c>
+      <c r="L28" s="7" t="inlineStr">
+        <is>
+          <t>BHEEMA
+(CHEM)</t>
+        </is>
+      </c>
       <c r="M28" s="7" t="inlineStr">
         <is>
           <t>GOWTHAM
@@ -8341,8 +8345,8 @@
       </c>
       <c r="N28" s="7" t="inlineStr">
         <is>
-          <t>D.V.RAO
-(TEL)</t>
+          <t>MARTIAL ARTS
+(KAR)</t>
         </is>
       </c>
     </row>
@@ -8353,50 +8357,50 @@
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>SITHA
-(ENG)</t>
+          <t>NAGAMANI
+(TEL)</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>SAI LAKSHMI
-(ENG)</t>
+          <t>BHAVANI
+(EVS)</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
-        <is>
-          <t>NAGAMANI
-(G.K)</t>
-        </is>
-      </c>
-      <c r="F29" s="7" t="inlineStr">
-        <is>
-          <t>BHAVANI
-(G.K)</t>
-        </is>
-      </c>
-      <c r="G29" s="7" t="inlineStr">
         <is>
           <t>MAHESWARI
 (COMP)</t>
         </is>
       </c>
-      <c r="H29" s="7" t="inlineStr">
+      <c r="F29" s="7" t="inlineStr">
         <is>
           <t>MAHA
 (ENG)</t>
         </is>
       </c>
-      <c r="I29" s="7" t="inlineStr">
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>TULASI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="H29" s="7" t="inlineStr">
         <is>
           <t>LALITHA
 (EVS)</t>
         </is>
       </c>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>SWATHI
+(TEL)</t>
+        </is>
+      </c>
       <c r="J29" s="7" t="inlineStr">
         <is>
-          <t>RAVI
-(ENG)</t>
+          <t>FATHIMA
+(HIN)</t>
         </is>
       </c>
       <c r="K29" s="7" t="inlineStr">
@@ -8432,13 +8436,13 @@
       <c r="C30" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(ENG)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>BHAVANI
-(EVS)</t>
+          <t>SWATHI
+(HIN)</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
@@ -8449,20 +8453,20 @@
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>MAHA
-(GRAM)</t>
-        </is>
-      </c>
-      <c r="G30" s="7" t="inlineStr">
-        <is>
           <t>TULASI
 (MATH)</t>
         </is>
       </c>
+      <c r="G30" s="7" t="inlineStr">
+        <is>
+          <t>MAHA
+(ENG)</t>
+        </is>
+      </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
-          <t>LALITHA
-(EVS)</t>
+          <t>FATHIMA
+(HIN)</t>
         </is>
       </c>
       <c r="I30" s="7" t="inlineStr">
@@ -8473,32 +8477,32 @@
       </c>
       <c r="J30" s="7" t="inlineStr">
         <is>
-          <t>SWATHI
-(TEL)</t>
+          <t>LALITHA
+(BIO)</t>
         </is>
       </c>
       <c r="K30" s="7" t="inlineStr">
         <is>
-          <t>D.V.RAO
-(TEL)</t>
+          <t>RAVI
+(ENG)</t>
         </is>
       </c>
       <c r="L30" s="7" t="inlineStr">
+        <is>
+          <t>SANGEETHA
+(MATH)</t>
+        </is>
+      </c>
+      <c r="M30" s="7" t="inlineStr">
         <is>
           <t>SONU
 (ENG)</t>
         </is>
       </c>
-      <c r="M30" s="7" t="inlineStr">
-        <is>
-          <t>RIYA
-(HIN)</t>
-        </is>
-      </c>
       <c r="N30" s="7" t="inlineStr">
         <is>
-          <t>SUNITHA
-(SOC)</t>
+          <t>CHALAPATHI
+(BIO)</t>
         </is>
       </c>
     </row>
@@ -8509,74 +8513,74 @@
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>SITHA
-(ENG)</t>
+          <t>P.E
+(P.E.T)</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>NAGAMANI
+          <t>P.E
+(P.E.T)</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>P.E
+(P.E.T)</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>P.E
+(P.E.T)</t>
+        </is>
+      </c>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>MAHA
+(GRAM)</t>
+        </is>
+      </c>
+      <c r="H31" s="7" t="inlineStr">
+        <is>
+          <t>P.E
+(P.E.T)</t>
+        </is>
+      </c>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t>P.E
+(P.E.T)</t>
+        </is>
+      </c>
+      <c r="J31" s="7" t="inlineStr">
+        <is>
+          <t>LALITHA
+(PHY)</t>
+        </is>
+      </c>
+      <c r="K31" s="7" t="inlineStr">
+        <is>
+          <t>D.V.RAO
 (TEL)</t>
         </is>
       </c>
-      <c r="E31" s="7" t="inlineStr">
-        <is>
-          <t>SAI LAKSHMI
+      <c r="L31" s="7" t="inlineStr">
+        <is>
+          <t>SANGEETHA
+(COMP)</t>
+        </is>
+      </c>
+      <c r="M31" s="7" t="inlineStr">
+        <is>
+          <t>RIYA
 (HIN)</t>
         </is>
       </c>
-      <c r="F31" s="7" t="inlineStr">
-        <is>
-          <t>MAHA
-(ENG)</t>
-        </is>
-      </c>
-      <c r="G31" s="7" t="inlineStr">
-        <is>
-          <t>PALLAVI
-(SOC)</t>
-        </is>
-      </c>
-      <c r="H31" s="7" t="inlineStr">
-        <is>
-          <t>FATHIMA
-(HIN)</t>
-        </is>
-      </c>
-      <c r="I31" s="7" t="inlineStr">
-        <is>
-          <t>SWATHI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="J31" s="7" t="inlineStr">
-        <is>
-          <t>LALITHA
-(CHEM)</t>
-        </is>
-      </c>
-      <c r="K31" s="7" t="inlineStr">
-        <is>
-          <t>SANGEETHA
-(MATH)</t>
-        </is>
-      </c>
-      <c r="L31" s="7" t="inlineStr">
-        <is>
-          <t>RAVI
-(GRAM)</t>
-        </is>
-      </c>
-      <c r="M31" s="7" t="inlineStr">
+      <c r="N31" s="7" t="inlineStr">
         <is>
           <t>SONU
 (ENG)</t>
-        </is>
-      </c>
-      <c r="N31" s="7" t="inlineStr">
-        <is>
-          <t>CHALAPATHI
-(BIO)</t>
         </is>
       </c>
     </row>
@@ -8593,68 +8597,68 @@
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
+          <t>SAI LAKSHMI
+(ENG)</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
-        <is>
-          <t>P.E
-(P.E.T)</t>
-        </is>
-      </c>
-      <c r="F32" s="7" t="inlineStr">
-        <is>
-          <t>P.E
-(P.E.T)</t>
-        </is>
-      </c>
-      <c r="G32" s="7" t="inlineStr">
         <is>
           <t>MAHA
 (ENG)</t>
         </is>
       </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>NAGAMANI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="G32" s="7" t="inlineStr">
+        <is>
+          <t>LALITHA
+(EVS)</t>
+        </is>
+      </c>
       <c r="H32" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
+          <t>PALLAVI
+(SOC)</t>
         </is>
       </c>
       <c r="I32" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
+          <t>TULASI
+(MATH)</t>
         </is>
       </c>
       <c r="J32" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
+          <t>SWATHI
+(TEL)</t>
         </is>
       </c>
       <c r="K32" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
+          <t>FATHIMA
+(HIN)</t>
         </is>
       </c>
       <c r="L32" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
+          <t>SONU
+(ENG)</t>
         </is>
       </c>
       <c r="M32" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
+          <t>CHALAPATHI
+(BIO)</t>
         </is>
       </c>
       <c r="N32" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
+          <t>SUNITHA
+(SOC)</t>
         </is>
       </c>
     </row>
@@ -8730,10 +8734,9 @@
 (CLASS)</t>
         </is>
       </c>
-      <c r="N33" s="8" t="inlineStr">
-        <is>
-          <t>SONU
-(ENG)</t>
+      <c r="N33" s="12" t="inlineStr">
+        <is>
+          <t>Recreation</t>
         </is>
       </c>
     </row>
@@ -8755,7 +8758,7 @@
       <c r="D34" s="7" t="inlineStr">
         <is>
           <t>BHAVANI
-(MATH)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
@@ -8767,7 +8770,7 @@
       <c r="F34" s="7" t="inlineStr">
         <is>
           <t>SAI LAKSHMI
-(HIN)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
@@ -8814,8 +8817,8 @@
       </c>
       <c r="N34" s="7" t="inlineStr">
         <is>
-          <t>GOWTHAM
-(MATH)</t>
+          <t>BHEEMA
+(PHY)</t>
         </is>
       </c>
     </row>
@@ -8827,25 +8830,25 @@
       <c r="C35" s="7" t="inlineStr">
         <is>
           <t>SITHA
+(EVS)</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>SAI LAKSHMI
 (ENG)</t>
         </is>
       </c>
-      <c r="D35" s="7" t="inlineStr">
+      <c r="E35" s="7" t="inlineStr">
         <is>
           <t>BHAVANI
 (MATH)</t>
         </is>
       </c>
-      <c r="E35" s="7" t="inlineStr">
-        <is>
-          <t>SAI LAKSHMI
-(EVS)</t>
-        </is>
-      </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>MAHESWARI
-(COMP)</t>
+          <t>TULASI
+(MATH)</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
@@ -8856,16 +8859,16 @@
       </c>
       <c r="H35" s="7" t="inlineStr">
         <is>
+          <t>SWATHI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="I35" s="7" t="inlineStr">
+        <is>
           <t>LALITHA
 (EVS)</t>
         </is>
       </c>
-      <c r="I35" s="7" t="inlineStr">
-        <is>
-          <t>SWATHI
-(TEL)</t>
-        </is>
-      </c>
       <c r="J35" s="7" t="inlineStr">
         <is>
           <t>PALLAVI
@@ -8874,14 +8877,14 @@
       </c>
       <c r="K35" s="7" t="inlineStr">
         <is>
-          <t>SANGEETHA
-(MATH)</t>
+          <t>FATHIMA
+(HIN)</t>
         </is>
       </c>
       <c r="L35" s="7" t="inlineStr">
         <is>
           <t>BHEEMA
-(PHY)</t>
+(CHEM)</t>
         </is>
       </c>
       <c r="M35" s="7" t="inlineStr">
@@ -8905,73 +8908,73 @@
       <c r="C36" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(MATH)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
-        <is>
-          <t>BHAVANI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="E36" s="7" t="inlineStr">
-        <is>
-          <t>SAI LAKSHMI
-(EVS)</t>
-        </is>
-      </c>
-      <c r="F36" s="7" t="inlineStr">
         <is>
           <t>NAGAMANI
 (TEL)</t>
         </is>
       </c>
-      <c r="G36" s="7" t="inlineStr">
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>SAI LAKSHMI
+(HIN)</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
         <is>
           <t>MAHA
 (ENG)</t>
         </is>
       </c>
+      <c r="G36" s="7" t="inlineStr">
+        <is>
+          <t>LALITHA
+(EVS)</t>
+        </is>
+      </c>
       <c r="H36" s="7" t="inlineStr">
         <is>
-          <t>SWATHI
-(TEL)</t>
+          <t>SANGEETHA
+(G.K)</t>
         </is>
       </c>
       <c r="I36" s="7" t="inlineStr">
-        <is>
-          <t>TULASI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="J36" s="7" t="inlineStr">
         <is>
           <t>FATHIMA
 (HIN)</t>
         </is>
       </c>
+      <c r="J36" s="7" t="inlineStr">
+        <is>
+          <t>MAHESWARI
+(COMP)</t>
+        </is>
+      </c>
       <c r="K36" s="7" t="inlineStr">
-        <is>
-          <t>LALITHA
-(PHY)</t>
-        </is>
-      </c>
-      <c r="L36" s="7" t="inlineStr">
         <is>
           <t>D.V.RAO
 (TEL)</t>
         </is>
       </c>
+      <c r="L36" s="7" t="inlineStr">
+        <is>
+          <t>BHEEMA
+(PHY)</t>
+        </is>
+      </c>
       <c r="M36" s="7" t="inlineStr">
+        <is>
+          <t>RAVI
+(GRAM)</t>
+        </is>
+      </c>
+      <c r="N36" s="7" t="inlineStr">
         <is>
           <t>GOWTHAM
 (MATH)</t>
-        </is>
-      </c>
-      <c r="N36" s="7" t="inlineStr">
-        <is>
-          <t>BHEEMA
-(CHEM)</t>
         </is>
       </c>
     </row>
@@ -8982,73 +8985,74 @@
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>SITHA
-(MATH)</t>
-        </is>
-      </c>
-      <c r="D37" s="7" t="inlineStr">
-        <is>
           <t>NAGAMANI
 (TEL)</t>
         </is>
       </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>BHAVANI
+(EVS)</t>
+        </is>
+      </c>
       <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>MAHESWARI
+(COMP)</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>SAI LAKSHMI
+(HIN)</t>
+        </is>
+      </c>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>TULASI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="H37" s="7" t="inlineStr">
         <is>
           <t>MAHA
 (ENG)</t>
         </is>
       </c>
-      <c r="F37" s="7" t="inlineStr">
-        <is>
-          <t>TULASI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="G37" s="7" t="inlineStr">
-        <is>
-          <t>LALITHA
-(EVS)</t>
-        </is>
-      </c>
-      <c r="H37" s="7" t="inlineStr">
+      <c r="I37" s="7" t="inlineStr">
         <is>
           <t>PALLAVI
 (SOC)</t>
         </is>
       </c>
-      <c r="I37" s="7" t="inlineStr">
-        <is>
-          <t>FATHIMA
-(HIN)</t>
-        </is>
-      </c>
       <c r="J37" s="7" t="inlineStr">
+        <is>
+          <t>SWATHI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="K37" s="7" t="inlineStr">
         <is>
           <t>RAVI
 (ENG)</t>
         </is>
       </c>
-      <c r="K37" s="7" t="inlineStr">
+      <c r="L37" s="7" t="inlineStr">
         <is>
           <t>SANGEETHA
 (MATH)</t>
         </is>
       </c>
-      <c r="L37" s="7" t="inlineStr">
+      <c r="M37" s="7" t="inlineStr">
+        <is>
+          <t>RIYA
+(HIN)</t>
+        </is>
+      </c>
+      <c r="N37" s="7" t="inlineStr">
         <is>
           <t>SUNITHA
 (SOC)</t>
-        </is>
-      </c>
-      <c r="M37" s="7" t="inlineStr">
-        <is>
-          <t>RIYA
-(HIN)</t>
-        </is>
-      </c>
-      <c r="N37" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
         </is>
       </c>
     </row>
@@ -9059,22 +9063,22 @@
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>NAGAMANI
-(TEL)</t>
+          <t>SITHA
+(ENG)</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>SAI LAKSHMI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
         <is>
           <t>BHAVANI
 (MATH)</t>
         </is>
       </c>
-      <c r="E38" s="7" t="inlineStr">
-        <is>
-          <t>MARTIAL ARTS
-(KAR)</t>
-        </is>
-      </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
           <t>TULASI
@@ -9083,50 +9087,50 @@
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
+          <t>MAHA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="H38" s="7" t="inlineStr">
+        <is>
           <t>PALLAVI
 (SOC)</t>
         </is>
       </c>
-      <c r="H38" s="7" t="inlineStr">
-        <is>
-          <t>MAHA
-(ENG)</t>
-        </is>
-      </c>
       <c r="I38" s="7" t="inlineStr">
-        <is>
-          <t>LALITHA
-(EVS)</t>
-        </is>
-      </c>
-      <c r="J38" s="7" t="inlineStr">
         <is>
           <t>SWATHI
 (TEL)</t>
         </is>
       </c>
+      <c r="J38" s="7" t="inlineStr">
+        <is>
+          <t>FATHIMA
+(HIN)</t>
+        </is>
+      </c>
       <c r="K38" s="7" t="inlineStr">
         <is>
-          <t>RAVI
-(GRAM)</t>
+          <t>LALITHA
+(BIO)</t>
         </is>
       </c>
       <c r="L38" s="7" t="inlineStr">
         <is>
-          <t>SANGEETHA
-(MATH)</t>
+          <t>D.V.RAO
+(TEL)</t>
         </is>
       </c>
       <c r="M38" s="7" t="inlineStr">
+        <is>
+          <t>SUNITHA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="N38" s="7" t="inlineStr">
         <is>
           <t>SONU
 (ENG)</t>
-        </is>
-      </c>
-      <c r="N38" s="7" t="inlineStr">
-        <is>
-          <t>SUNITHA
-(SOC)</t>
         </is>
       </c>
     </row>
@@ -9137,44 +9141,44 @@
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>SITHA
-(EVS)</t>
+          <t>P.E
+(P.E.T)</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>SWATHI
-(HIN)</t>
+          <t>SAI LAKSHMI
+(ENG)</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>SAI LAKSHMI
-(HIN)</t>
+          <t>P.E
+(P.E.T)</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>MARTIAL ARTS
-(KAR)</t>
+          <t>P.E
+(P.E.T)</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t>P.E
+(P.E.T)</t>
+        </is>
+      </c>
+      <c r="H39" s="7" t="inlineStr">
         <is>
           <t>MAHA
 (GRAM)</t>
         </is>
       </c>
-      <c r="H39" s="7" t="inlineStr">
-        <is>
-          <t>MAHESWARI
-(COMP)</t>
-        </is>
-      </c>
       <c r="I39" s="7" t="inlineStr">
         <is>
-          <t>PALLAVI
-(SOC)</t>
+          <t>P.E
+(P.E.T)</t>
         </is>
       </c>
       <c r="J39" s="7" t="inlineStr">
@@ -9185,8 +9189,8 @@
       </c>
       <c r="K39" s="7" t="inlineStr">
         <is>
-          <t>RAVI
-(ENG)</t>
+          <t>SANGEETHA
+(MATH)</t>
         </is>
       </c>
       <c r="L39" s="7" t="inlineStr">
@@ -9202,8 +9206,8 @@
       </c>
       <c r="N39" s="7" t="inlineStr">
         <is>
-          <t>CHALAPATHI
-(BIO)</t>
+          <t>RIYA
+(HIN)</t>
         </is>
       </c>
     </row>
@@ -9215,73 +9219,73 @@
       <c r="C40" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(ENG)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>SAI LAKSHMI
-(ENG)</t>
+          <t>BHAVANI
+(EVS)</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
-        <is>
-          <t>MAHESWARI
-(COMP)</t>
-        </is>
-      </c>
-      <c r="F40" s="7" t="inlineStr">
         <is>
           <t>MAHA
 (ENG)</t>
         </is>
       </c>
+      <c r="F40" s="7" t="inlineStr">
+        <is>
+          <t>NAGAMANI
+(TEL)</t>
+        </is>
+      </c>
       <c r="G40" s="7" t="inlineStr">
+        <is>
+          <t>PALLAVI
+(SOC)</t>
+        </is>
+      </c>
+      <c r="H40" s="7" t="inlineStr">
+        <is>
+          <t>LALITHA
+(EVS)</t>
+        </is>
+      </c>
+      <c r="I40" s="7" t="inlineStr">
         <is>
           <t>TULASI
 (MATH)</t>
         </is>
       </c>
-      <c r="H40" s="7" t="inlineStr">
-        <is>
-          <t>FATHIMA
-(HIN)</t>
-        </is>
-      </c>
-      <c r="I40" s="7" t="inlineStr">
+      <c r="J40" s="7" t="inlineStr">
+        <is>
+          <t>RAVI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="K40" s="7" t="inlineStr">
         <is>
           <t>SANGEETHA
-(G.K)</t>
-        </is>
-      </c>
-      <c r="J40" s="7" t="inlineStr">
-        <is>
-          <t>LALITHA
-(CHEM)</t>
-        </is>
-      </c>
-      <c r="K40" s="7" t="inlineStr">
-        <is>
-          <t>D.V.RAO
-(TEL)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="L40" s="7" t="inlineStr">
+        <is>
+          <t>SUNITHA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="M40" s="7" t="inlineStr">
+        <is>
+          <t>SONU
+(ENG)</t>
+        </is>
+      </c>
+      <c r="N40" s="7" t="inlineStr">
         <is>
           <t>CHALAPATHI
 (BIO)</t>
-        </is>
-      </c>
-      <c r="M40" s="7" t="inlineStr">
-        <is>
-          <t>SUNITHA
-(SOC)</t>
-        </is>
-      </c>
-      <c r="N40" s="7" t="inlineStr">
-        <is>
-          <t>SONU
-(ENG)</t>
         </is>
       </c>
     </row>
@@ -9381,7 +9385,7 @@
       <c r="D42" s="7" t="inlineStr">
         <is>
           <t>BHAVANI
-(MATH)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
@@ -9429,7 +9433,7 @@
       <c r="L42" s="7" t="inlineStr">
         <is>
           <t>FATHIMA
-(G.K)</t>
+(HIN)</t>
         </is>
       </c>
       <c r="M42" s="7" t="inlineStr">
@@ -9453,33 +9457,33 @@
       <c r="C43" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(ENG)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>SAI LAKSHMI
-(ENG)</t>
+          <t>NAGAMANI
+(TEL)</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr">
-        <is>
-          <t>MAHA
-(GRAM)</t>
-        </is>
-      </c>
-      <c r="F43" s="7" t="inlineStr">
-        <is>
-          <t>BHAVANI
-(G.K)</t>
-        </is>
-      </c>
-      <c r="G43" s="7" t="inlineStr">
         <is>
           <t>MARTIAL ARTS
 (KAR)</t>
         </is>
       </c>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>SAI LAKSHMI
+(HIN)</t>
+        </is>
+      </c>
+      <c r="G43" s="7" t="inlineStr">
+        <is>
+          <t>RIYA
+(HIN)</t>
+        </is>
+      </c>
       <c r="H43" s="7" t="inlineStr">
         <is>
           <t>SWATHI
@@ -9488,38 +9492,38 @@
       </c>
       <c r="I43" s="7" t="inlineStr">
         <is>
-          <t>MARTIAL ARTS
-(KAR)</t>
-        </is>
-      </c>
-      <c r="J43" s="7" t="inlineStr">
-        <is>
           <t>PALLAVI
 (SOC)</t>
         </is>
       </c>
+      <c r="J43" s="7" t="inlineStr">
+        <is>
+          <t>LALITHA
+(CHEM)</t>
+        </is>
+      </c>
       <c r="K43" s="7" t="inlineStr">
         <is>
-          <t>LALITHA
-(BIO)</t>
+          <t>D.V.RAO
+(TEL)</t>
         </is>
       </c>
       <c r="L43" s="7" t="inlineStr">
         <is>
-          <t>BHEEMA
-(PHY)</t>
+          <t>SANGEETHA
+(MATH)</t>
         </is>
       </c>
       <c r="M43" s="7" t="inlineStr">
+        <is>
+          <t>GOWTHAM
+(MATH)</t>
+        </is>
+      </c>
+      <c r="N43" s="7" t="inlineStr">
         <is>
           <t>SUNITHA
 (SOC)</t>
-        </is>
-      </c>
-      <c r="N43" s="7" t="inlineStr">
-        <is>
-          <t>D.V.RAO
-(TEL)</t>
         </is>
       </c>
     </row>
@@ -9536,14 +9540,14 @@
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>SWATHI
+          <t>BHAVANI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>SAI LAKSHMI
 (HIN)</t>
-        </is>
-      </c>
-      <c r="E44" s="7" t="inlineStr">
-        <is>
-          <t>SAI LAKSHMI
-(EVS)</t>
         </is>
       </c>
       <c r="F44" s="7" t="inlineStr">
@@ -9560,43 +9564,44 @@
       </c>
       <c r="H44" s="7" t="inlineStr">
         <is>
-          <t>PALLAVI
-(SOC)</t>
+          <t>MAHA
+(ENG)</t>
         </is>
       </c>
       <c r="I44" s="7" t="inlineStr">
         <is>
+          <t>SWATHI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="J44" s="7" t="inlineStr">
+        <is>
+          <t>FATHIMA
+(HIN)</t>
+        </is>
+      </c>
+      <c r="K44" s="7" t="inlineStr">
+        <is>
           <t>LALITHA
-(EVS)</t>
-        </is>
-      </c>
-      <c r="J44" s="7" t="inlineStr">
+(BIO)</t>
+        </is>
+      </c>
+      <c r="L44" s="7" t="inlineStr">
         <is>
           <t>SANGEETHA
 (MATH)</t>
         </is>
       </c>
-      <c r="K44" s="7" t="inlineStr">
-        <is>
-          <t>FATHIMA
-(HIN)</t>
-        </is>
-      </c>
-      <c r="L44" s="7" t="inlineStr">
-        <is>
-          <t>D.V.RAO
-(TEL)</t>
-        </is>
-      </c>
       <c r="M44" s="7" t="inlineStr">
         <is>
+          <t>GOWTHAM
+(MATH)</t>
+        </is>
+      </c>
+      <c r="N44" s="7" t="inlineStr">
+        <is>
           <t>BHEEMA
-(PHY)</t>
-        </is>
-      </c>
-      <c r="N44" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
+(CHEM)</t>
         </is>
       </c>
     </row>
@@ -9608,27 +9613,27 @@
       <c r="C45" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(EVS)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
           <t>BHAVANI
-(EVS)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>MAHA
+(GRAM)</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="inlineStr">
         <is>
           <t>MAHESWARI
 (COMP)</t>
         </is>
       </c>
-      <c r="F45" s="7" t="inlineStr">
-        <is>
-          <t>SAI LAKSHMI
-(HIN)</t>
-        </is>
-      </c>
       <c r="G45" s="7" t="inlineStr">
         <is>
           <t>LALITHA
@@ -9637,8 +9642,8 @@
       </c>
       <c r="H45" s="7" t="inlineStr">
         <is>
-          <t>MAHA
-(ENG)</t>
+          <t>PALLAVI
+(SOC)</t>
         </is>
       </c>
       <c r="I45" s="7" t="inlineStr">
@@ -9649,32 +9654,32 @@
       </c>
       <c r="J45" s="7" t="inlineStr">
         <is>
+          <t>RAVI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="K45" s="7" t="inlineStr">
+        <is>
           <t>FATHIMA
 (HIN)</t>
         </is>
       </c>
-      <c r="K45" s="7" t="inlineStr">
-        <is>
-          <t>RAVI
-(ENG)</t>
-        </is>
-      </c>
       <c r="L45" s="7" t="inlineStr">
         <is>
-          <t>SANGEETHA
-(MATH)</t>
+          <t>D.V.RAO
+(TEL)</t>
         </is>
       </c>
       <c r="M45" s="7" t="inlineStr">
+        <is>
+          <t>SUNITHA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="N45" s="7" t="inlineStr">
         <is>
           <t>RIYA
 (HIN)</t>
-        </is>
-      </c>
-      <c r="N45" s="7" t="inlineStr">
-        <is>
-          <t>SUNITHA
-(SOC)</t>
         </is>
       </c>
     </row>
@@ -9685,8 +9690,8 @@
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>NAGAMANI
-(TEL)</t>
+          <t>SITHA
+(ENG)</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
@@ -9703,40 +9708,40 @@
       </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
+          <t>MARTIAL ARTS
+(KAR)</t>
+        </is>
+      </c>
+      <c r="G46" s="7" t="inlineStr">
+        <is>
+          <t>MAHA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="H46" s="7" t="inlineStr">
+        <is>
           <t>MAHESWARI
 (COMP)</t>
         </is>
       </c>
-      <c r="G46" s="7" t="inlineStr">
-        <is>
-          <t>MAHA
-(ENG)</t>
-        </is>
-      </c>
-      <c r="H46" s="7" t="inlineStr">
-        <is>
-          <t>FATHIMA
-(HIN)</t>
-        </is>
-      </c>
       <c r="I46" s="7" t="inlineStr">
+        <is>
+          <t>TULASI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="J46" s="7" t="inlineStr">
         <is>
           <t>SWATHI
 (TEL)</t>
         </is>
       </c>
-      <c r="J46" s="7" t="inlineStr">
+      <c r="K46" s="7" t="inlineStr">
         <is>
           <t>RAVI
 (ENG)</t>
         </is>
       </c>
-      <c r="K46" s="7" t="inlineStr">
-        <is>
-          <t>LALITHA
-(PHY)</t>
-        </is>
-      </c>
       <c r="L46" s="7" t="inlineStr">
         <is>
           <t>SUNITHA
@@ -9745,14 +9750,14 @@
       </c>
       <c r="M46" s="7" t="inlineStr">
         <is>
-          <t>CHALAPATHI
-(BIO)</t>
-        </is>
-      </c>
-      <c r="N46" s="7" t="inlineStr">
-        <is>
           <t>SONU
 (ENG)</t>
+        </is>
+      </c>
+      <c r="N46" s="7" t="inlineStr">
+        <is>
+          <t>D.V.RAO
+(TEL)</t>
         </is>
       </c>
     </row>
@@ -9764,31 +9769,31 @@
       <c r="C47" s="7" t="inlineStr">
         <is>
           <t>SITHA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>BHAVANI
 (MATH)</t>
         </is>
       </c>
-      <c r="D47" s="7" t="inlineStr">
-        <is>
-          <t>NAGAMANI
-(TEL)</t>
-        </is>
-      </c>
       <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>SAI LAKSHMI
+(EVS)</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="inlineStr">
         <is>
           <t>MAHA
 (ENG)</t>
         </is>
       </c>
-      <c r="F47" s="7" t="inlineStr">
-        <is>
-          <t>TULASI
-(MATH)</t>
-        </is>
-      </c>
       <c r="G47" s="7" t="inlineStr">
         <is>
-          <t>RIYA
-(HIN)</t>
+          <t>MARTIAL ARTS
+(KAR)</t>
         </is>
       </c>
       <c r="H47" s="7" t="inlineStr">
@@ -9799,16 +9804,16 @@
       </c>
       <c r="I47" s="7" t="inlineStr">
         <is>
+          <t>FATHIMA
+(HIN)</t>
+        </is>
+      </c>
+      <c r="J47" s="7" t="inlineStr">
+        <is>
           <t>PALLAVI
 (SOC)</t>
         </is>
       </c>
-      <c r="J47" s="7" t="inlineStr">
-        <is>
-          <t>SWATHI
-(TEL)</t>
-        </is>
-      </c>
       <c r="K47" s="7" t="inlineStr">
         <is>
           <t>SANGEETHA
@@ -9821,15 +9826,15 @@
 (ENG)</t>
         </is>
       </c>
-      <c r="M47" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
-        </is>
-      </c>
-      <c r="N47" s="7" t="inlineStr">
+      <c r="M47" s="7" t="inlineStr">
         <is>
           <t>CHALAPATHI
 (BIO)</t>
+        </is>
+      </c>
+      <c r="N47" s="12" t="inlineStr">
+        <is>
+          <t>Recreation</t>
         </is>
       </c>
     </row>
@@ -9840,28 +9845,28 @@
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>SITHA
-(MATH)</t>
+          <t>NAGAMANI
+(TEL)</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>SAI LAKSHMI
-(ENG)</t>
+          <t>SWATHI
+(HIN)</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
-        <is>
-          <t>BHAVANI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="F48" s="7" t="inlineStr">
         <is>
           <t>MAHA
 (ENG)</t>
         </is>
       </c>
+      <c r="F48" s="7" t="inlineStr">
+        <is>
+          <t>TULASI
+(MATH)</t>
+        </is>
+      </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
           <t>PALLAVI
@@ -9870,44 +9875,44 @@
       </c>
       <c r="H48" s="7" t="inlineStr">
         <is>
-          <t>SANGEETHA
-(G.K)</t>
-        </is>
-      </c>
-      <c r="I48" s="7" t="inlineStr">
-        <is>
           <t>FATHIMA
 (HIN)</t>
         </is>
       </c>
+      <c r="I48" s="7" t="inlineStr">
+        <is>
+          <t>LALITHA
+(EVS)</t>
+        </is>
+      </c>
       <c r="J48" s="7" t="inlineStr">
         <is>
-          <t>LALITHA
-(PHY)</t>
+          <t>P.E
+(P.E.T)</t>
         </is>
       </c>
       <c r="K48" s="7" t="inlineStr">
         <is>
-          <t>D.V.RAO
-(TEL)</t>
+          <t>P.E
+(P.E.T)</t>
         </is>
       </c>
       <c r="L48" s="7" t="inlineStr">
         <is>
-          <t>CHALAPATHI
-(BIO)</t>
+          <t>P.E
+(P.E.T)</t>
         </is>
       </c>
       <c r="M48" s="7" t="inlineStr">
         <is>
-          <t>SONU
-(ENG)</t>
+          <t>P.E
+(P.E.T)</t>
         </is>
       </c>
       <c r="N48" s="7" t="inlineStr">
         <is>
-          <t>RIYA
-(HIN)</t>
+          <t>P.E
+(P.E.T)</t>
         </is>
       </c>
     </row>
@@ -9983,9 +9988,10 @@
 (CLASS)</t>
         </is>
       </c>
-      <c r="N49" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
+      <c r="N49" s="8" t="inlineStr">
+        <is>
+          <t>SONU
+(ENG)</t>
         </is>
       </c>
     </row>

--- a/NRCS/Output/NRCS_Timetable_Final.xlsx
+++ b/NRCS/Output/NRCS_Timetable_Final.xlsx
@@ -656,28 +656,24 @@
           <t>U.K.G (EVS)</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr"/>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>U.K.G (EVS)</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr"/>
+      <c r="E5" s="7" t="inlineStr">
         <is>
           <t>U.K.G (MATH)</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (MATH)</t>
-        </is>
-      </c>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="F5" s="7" t="inlineStr"/>
+      <c r="G5" s="7" t="inlineStr"/>
+      <c r="H5" s="7" t="inlineStr">
         <is>
           <t>Class 2 (G.K)</t>
         </is>
       </c>
-      <c r="G5" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (MATH)</t>
-        </is>
-      </c>
-      <c r="H5" s="7" t="inlineStr"/>
       <c r="I5" s="8" t="inlineStr">
         <is>
           <t>U.K.G</t>
@@ -692,27 +688,31 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>U.K.G (MATH)</t>
+          <t>U.K.G (EVS)</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
+          <t>U.K.G (EVS)</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr"/>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
           <t>Class 1 (MATH)</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr"/>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>Class 1 (MATH)</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>Class 2 (G.K)</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr"/>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (MATH)</t>
-        </is>
-      </c>
-      <c r="G6" s="7" t="inlineStr"/>
-      <c r="H6" s="7" t="inlineStr"/>
       <c r="I6" s="8" t="inlineStr">
         <is>
           <t>U.K.G</t>
@@ -727,31 +727,27 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
+          <t>U.K.G (MATH)</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr"/>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
           <t>U.K.G (EVS)</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="E7" s="7" t="inlineStr">
         <is>
           <t>Class 1 (MATH)</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (MATH)</t>
-        </is>
-      </c>
-      <c r="E7" s="7" t="inlineStr"/>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (MATH)</t>
-        </is>
-      </c>
-      <c r="G7" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (MATH)</t>
-        </is>
-      </c>
-      <c r="H7" s="7" t="inlineStr"/>
+      <c r="F7" s="7" t="inlineStr"/>
+      <c r="G7" s="7" t="inlineStr"/>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>U.K.G (EVS)</t>
+        </is>
+      </c>
       <c r="I7" s="8" t="inlineStr">
         <is>
           <t>U.K.G</t>
@@ -769,20 +765,24 @@
           <t>U.K.G (EVS)</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr"/>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (MATH)</t>
-        </is>
-      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>U.K.G (EVS)</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr"/>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>U.K.G (EVS)</t>
+          <t>U.K.G (MATH)</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr"/>
       <c r="G8" s="7" t="inlineStr"/>
-      <c r="H8" s="7" t="inlineStr"/>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>Class 1 (MATH)</t>
+        </is>
+      </c>
       <c r="I8" s="8" t="inlineStr">
         <is>
           <t>U.K.G</t>
@@ -797,31 +797,31 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>U.K.G (EVS)</t>
+          <t>U.K.G (MATH)</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>Class 1 (MATH)</t>
+          <t>U.K.G (MATH)</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr"/>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>U.K.G (EVS)</t>
+          <t>Class 1 (MATH)</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
+          <t>U.K.G (MATH)</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
           <t>Class 1 (MATH)</t>
         </is>
       </c>
-      <c r="G9" s="7" t="inlineStr"/>
-      <c r="H9" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (EVS)</t>
-        </is>
-      </c>
+      <c r="H9" s="7" t="inlineStr"/>
       <c r="I9" s="8" t="inlineStr">
         <is>
           <t>U.K.G</t>
@@ -836,23 +836,23 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>U.K.G (EVS)</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr"/>
+          <t>U.K.G (MATH)</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>U.K.G (MATH)</t>
+        </is>
+      </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>Class 1 (MATH)</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr"/>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
           <t>U.K.G (MATH)</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (MATH)</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (MATH)</t>
         </is>
       </c>
       <c r="G10" s="7" t="inlineStr">
@@ -935,11 +935,19 @@
           <t>MON</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr"/>
-      <c r="C14" s="7" t="inlineStr"/>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (PHY)</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (PHY)</t>
+        </is>
+      </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>Class 9 (CHEM)</t>
+          <t>Class 9 (PHY)</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr"/>
@@ -957,12 +965,12 @@
       <c r="B15" s="7" t="inlineStr"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>Class 9 (PHY)</t>
+          <t>Class 8 (CHEM)</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Class 10 (CHEM)</t>
+          <t>Class 9 (CHEM)</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr"/>
@@ -984,12 +992,12 @@
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
+          <t>Class 9 (PHY)</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
           <t>Class 8 (PHY)</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (PHY)</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr"/>
@@ -1007,12 +1015,12 @@
       <c r="B17" s="7" t="inlineStr"/>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>Class 9 (CHEM)</t>
+          <t>Class 8 (CHEM)</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (CHEM)</t>
+          <t>Class 10 (CHEM)</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr"/>
@@ -1029,17 +1037,13 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Class 10 (PHY)</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (CHEM)</t>
-        </is>
-      </c>
+          <t>Class 10 (CHEM)</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr"/>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (PHY)</t>
+          <t>Class 9 (CHEM)</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr"/>
@@ -1056,11 +1060,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr"/>
       <c r="C19" s="7" t="inlineStr"/>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (CHEM)</t>
-        </is>
-      </c>
+      <c r="D19" s="7" t="inlineStr"/>
       <c r="E19" s="7" t="inlineStr"/>
       <c r="F19" s="7" t="inlineStr"/>
       <c r="G19" s="7" t="inlineStr"/>
@@ -1139,21 +1139,13 @@
       <c r="C23" s="7" t="inlineStr"/>
       <c r="D23" s="7" t="inlineStr"/>
       <c r="E23" s="7" t="inlineStr"/>
-      <c r="F23" s="7" t="inlineStr">
+      <c r="F23" s="7" t="inlineStr"/>
+      <c r="G23" s="7" t="inlineStr">
         <is>
           <t>Class 9 (BIO)</t>
         </is>
       </c>
-      <c r="G23" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (BIO)</t>
-        </is>
-      </c>
-      <c r="H23" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (BIO)</t>
-        </is>
-      </c>
+      <c r="H23" s="7" t="inlineStr"/>
       <c r="I23" s="7" t="inlineStr"/>
     </row>
     <row r="24">
@@ -1166,15 +1158,15 @@
       <c r="C24" s="7" t="inlineStr"/>
       <c r="D24" s="7" t="inlineStr"/>
       <c r="E24" s="7" t="inlineStr"/>
-      <c r="F24" s="7" t="inlineStr">
+      <c r="F24" s="7" t="inlineStr"/>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (BIO)</t>
+        </is>
+      </c>
+      <c r="H24" s="7" t="inlineStr">
         <is>
           <t>Class 8 (BIO)</t>
-        </is>
-      </c>
-      <c r="G24" s="7" t="inlineStr"/>
-      <c r="H24" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (BIO)</t>
         </is>
       </c>
       <c r="I24" s="7" t="inlineStr"/>
@@ -1191,11 +1183,15 @@
       <c r="E25" s="7" t="inlineStr"/>
       <c r="F25" s="7" t="inlineStr">
         <is>
+          <t>Class 10 (BIO)</t>
+        </is>
+      </c>
+      <c r="G25" s="7" t="inlineStr"/>
+      <c r="H25" s="7" t="inlineStr">
+        <is>
           <t>Class 8 (BIO)</t>
         </is>
       </c>
-      <c r="G25" s="7" t="inlineStr"/>
-      <c r="H25" s="7" t="inlineStr"/>
       <c r="I25" s="7" t="inlineStr"/>
     </row>
     <row r="26">
@@ -1208,15 +1204,11 @@
       <c r="C26" s="7" t="inlineStr"/>
       <c r="D26" s="7" t="inlineStr"/>
       <c r="E26" s="7" t="inlineStr"/>
-      <c r="F26" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (BIO)</t>
-        </is>
-      </c>
+      <c r="F26" s="7" t="inlineStr"/>
       <c r="G26" s="7" t="inlineStr"/>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>Class 9 (BIO)</t>
+          <t>Class 10 (BIO)</t>
         </is>
       </c>
       <c r="I26" s="7" t="inlineStr"/>
@@ -1231,13 +1223,13 @@
       <c r="C27" s="7" t="inlineStr"/>
       <c r="D27" s="7" t="inlineStr"/>
       <c r="E27" s="7" t="inlineStr"/>
-      <c r="F27" s="7" t="inlineStr"/>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (BIO)</t>
+        </is>
+      </c>
       <c r="G27" s="7" t="inlineStr"/>
-      <c r="H27" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (BIO)</t>
-        </is>
-      </c>
+      <c r="H27" s="7" t="inlineStr"/>
       <c r="I27" s="7" t="inlineStr"/>
     </row>
     <row r="28">
@@ -1250,13 +1242,21 @@
       <c r="C28" s="7" t="inlineStr"/>
       <c r="D28" s="7" t="inlineStr"/>
       <c r="E28" s="7" t="inlineStr"/>
-      <c r="F28" s="7" t="inlineStr"/>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (BIO)</t>
+        </is>
+      </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
           <t>Class 9 (BIO)</t>
         </is>
       </c>
-      <c r="H28" s="7" t="inlineStr"/>
+      <c r="H28" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (BIO)</t>
+        </is>
+      </c>
       <c r="I28" s="7" t="inlineStr"/>
     </row>
     <row r="30">
@@ -1332,24 +1332,24 @@
           <t>Class 9 (TEL)</t>
         </is>
       </c>
-      <c r="C32" s="7" t="inlineStr"/>
-      <c r="D32" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (TEL)</t>
-        </is>
-      </c>
-      <c r="E32" s="7" t="inlineStr">
+      <c r="C32" s="7" t="inlineStr">
         <is>
           <t>Class 10 (TEL)</t>
         </is>
       </c>
+      <c r="D32" s="7" t="inlineStr"/>
+      <c r="E32" s="7" t="inlineStr"/>
       <c r="F32" s="7" t="inlineStr"/>
       <c r="G32" s="7" t="inlineStr">
         <is>
           <t>Class 7 (TEL)</t>
         </is>
       </c>
-      <c r="H32" s="7" t="inlineStr"/>
+      <c r="H32" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (TEL)</t>
+        </is>
+      </c>
       <c r="I32" s="8" t="inlineStr">
         <is>
           <t>Class 9</t>
@@ -1368,21 +1368,21 @@
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr"/>
-      <c r="D33" s="7" t="inlineStr"/>
-      <c r="E33" s="7" t="inlineStr">
+      <c r="D33" s="7" t="inlineStr">
         <is>
           <t>Class 8 (TEL)</t>
         </is>
       </c>
-      <c r="F33" s="7" t="inlineStr"/>
-      <c r="G33" s="7" t="inlineStr">
+      <c r="E33" s="7" t="inlineStr"/>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (TEL)</t>
+        </is>
+      </c>
+      <c r="G33" s="7" t="inlineStr"/>
+      <c r="H33" s="7" t="inlineStr">
         <is>
           <t>Class 10 (TEL)</t>
-        </is>
-      </c>
-      <c r="H33" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (TEL)</t>
         </is>
       </c>
       <c r="I33" s="8" t="inlineStr">
@@ -1402,18 +1402,18 @@
           <t>Class 9 (TEL)</t>
         </is>
       </c>
-      <c r="C34" s="7" t="inlineStr"/>
-      <c r="D34" s="7" t="inlineStr">
+      <c r="C34" s="7" t="inlineStr">
         <is>
           <t>Class 8 (TEL)</t>
         </is>
       </c>
-      <c r="E34" s="7" t="inlineStr"/>
-      <c r="F34" s="7" t="inlineStr">
+      <c r="D34" s="7" t="inlineStr"/>
+      <c r="E34" s="7" t="inlineStr">
         <is>
           <t>Class 7 (TEL)</t>
         </is>
       </c>
+      <c r="F34" s="7" t="inlineStr"/>
       <c r="G34" s="7" t="inlineStr">
         <is>
           <t>Class 10 (TEL)</t>
@@ -1437,24 +1437,24 @@
           <t>Class 9 (TEL)</t>
         </is>
       </c>
-      <c r="C35" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (TEL)</t>
-        </is>
-      </c>
+      <c r="C35" s="7" t="inlineStr"/>
       <c r="D35" s="7" t="inlineStr"/>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (TEL)</t>
+          <t>Class 10 (TEL)</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr"/>
       <c r="G35" s="7" t="inlineStr">
         <is>
+          <t>Class 8 (TEL)</t>
+        </is>
+      </c>
+      <c r="H35" s="7" t="inlineStr">
+        <is>
           <t>Class 7 (TEL)</t>
         </is>
       </c>
-      <c r="H35" s="7" t="inlineStr"/>
       <c r="I35" s="8" t="inlineStr">
         <is>
           <t>Class 9</t>
@@ -1474,18 +1474,18 @@
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>Class 10 (TEL)</t>
+          <t>Class 7 (TEL)</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (TEL)</t>
+          <t>Class 8 (TEL)</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr"/>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (TEL)</t>
+          <t>Class 10 (TEL)</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr"/>
@@ -1509,22 +1509,22 @@
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
+          <t>Class 8 (TEL)</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (TEL)</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr"/>
+      <c r="F37" s="7" t="inlineStr"/>
+      <c r="G37" s="7" t="inlineStr"/>
+      <c r="H37" s="7" t="inlineStr">
+        <is>
           <t>Class 7 (TEL)</t>
         </is>
       </c>
-      <c r="D37" s="7" t="inlineStr"/>
-      <c r="E37" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (TEL)</t>
-        </is>
-      </c>
-      <c r="F37" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (TEL)</t>
-        </is>
-      </c>
-      <c r="G37" s="7" t="inlineStr"/>
-      <c r="H37" s="7" t="inlineStr"/>
       <c r="I37" s="8" t="inlineStr">
         <is>
           <t>Class 9</t>
@@ -1607,17 +1607,25 @@
       <c r="C41" s="7" t="inlineStr"/>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (G.K)</t>
-        </is>
-      </c>
-      <c r="E41" s="7" t="inlineStr"/>
-      <c r="F41" s="7" t="inlineStr"/>
-      <c r="G41" s="7" t="inlineStr">
+          <t>Class 5 (HIN)</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
         <is>
           <t>Class 4 (HIN)</t>
         </is>
       </c>
-      <c r="H41" s="7" t="inlineStr"/>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (HIN)</t>
+        </is>
+      </c>
+      <c r="G41" s="7" t="inlineStr"/>
+      <c r="H41" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (HIN)</t>
+        </is>
+      </c>
       <c r="I41" s="8" t="inlineStr">
         <is>
           <t>Class 8</t>
@@ -1632,31 +1640,27 @@
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (G.K)</t>
+          <t>Class 8 (HIN)</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr"/>
       <c r="D42" s="7" t="inlineStr">
         <is>
+          <t>Class 7 (HIN)</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
           <t>Class 4 (HIN)</t>
         </is>
       </c>
-      <c r="E42" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (HIN)</t>
-        </is>
-      </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (HIN)</t>
+          <t>Class 6 (HIN)</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr"/>
-      <c r="H42" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (HIN)</t>
-        </is>
-      </c>
+      <c r="H42" s="7" t="inlineStr"/>
       <c r="I42" s="8" t="inlineStr">
         <is>
           <t>Class 8</t>
@@ -1674,28 +1678,28 @@
           <t>Class 8 (HIN)</t>
         </is>
       </c>
-      <c r="C43" s="7" t="inlineStr">
+      <c r="C43" s="7" t="inlineStr"/>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (HIN)</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (HIN)</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
         <is>
           <t>Class 4 (HIN)</t>
         </is>
       </c>
-      <c r="D43" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (HIN)</t>
-        </is>
-      </c>
-      <c r="E43" s="7" t="inlineStr"/>
-      <c r="F43" s="7" t="inlineStr"/>
       <c r="G43" s="7" t="inlineStr">
         <is>
           <t>Class 7 (HIN)</t>
         </is>
       </c>
-      <c r="H43" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (HIN)</t>
-        </is>
-      </c>
+      <c r="H43" s="7" t="inlineStr"/>
       <c r="I43" s="8" t="inlineStr">
         <is>
           <t>Class 8</t>
@@ -1715,7 +1719,7 @@
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (HIN)</t>
+          <t>Class 4 (HIN)</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr"/>
@@ -1726,13 +1730,13 @@
       </c>
       <c r="F44" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (HIN)</t>
+          <t>Class 7 (HIN)</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr"/>
       <c r="H44" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (HIN)</t>
+          <t>Class 5 (HIN)</t>
         </is>
       </c>
       <c r="I44" s="8" t="inlineStr">
@@ -1752,23 +1756,23 @@
           <t>Class 8 (HIN)</t>
         </is>
       </c>
-      <c r="C45" s="7" t="inlineStr">
+      <c r="C45" s="7" t="inlineStr"/>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (G.K)</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
         <is>
           <t>Class 7 (HIN)</t>
         </is>
       </c>
-      <c r="D45" s="7" t="inlineStr">
+      <c r="F45" s="7" t="inlineStr"/>
+      <c r="G45" s="7" t="inlineStr">
         <is>
           <t>Class 5 (HIN)</t>
         </is>
       </c>
-      <c r="E45" s="7" t="inlineStr"/>
-      <c r="F45" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (HIN)</t>
-        </is>
-      </c>
-      <c r="G45" s="7" t="inlineStr"/>
       <c r="H45" s="7" t="inlineStr"/>
       <c r="I45" s="8" t="inlineStr">
         <is>
@@ -1784,31 +1788,27 @@
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (HIN)</t>
-        </is>
-      </c>
-      <c r="C46" s="7" t="inlineStr"/>
-      <c r="D46" s="7" t="inlineStr">
+          <t>Class 8 (G.K)</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (HIN)</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="inlineStr"/>
+      <c r="E46" s="7" t="inlineStr">
         <is>
           <t>Class 6 (HIN)</t>
         </is>
       </c>
-      <c r="E46" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (HIN)</t>
-        </is>
-      </c>
-      <c r="F46" s="7" t="inlineStr"/>
-      <c r="G46" s="7" t="inlineStr">
+      <c r="F46" s="7" t="inlineStr">
         <is>
           <t>Class 5 (HIN)</t>
         </is>
       </c>
-      <c r="H46" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (HIN)</t>
-        </is>
-      </c>
+      <c r="G46" s="7" t="inlineStr"/>
+      <c r="H46" s="7" t="inlineStr"/>
       <c r="I46" s="8" t="inlineStr">
         <is>
           <t>Class 8</t>
@@ -1906,15 +1906,15 @@
           <t>TUE</t>
         </is>
       </c>
-      <c r="B51" s="7" t="inlineStr">
+      <c r="B51" s="7" t="inlineStr"/>
+      <c r="C51" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (MATH)</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="inlineStr">
         <is>
           <t>Class 10 (MATH)</t>
-        </is>
-      </c>
-      <c r="C51" s="7" t="inlineStr"/>
-      <c r="D51" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (MATH)</t>
         </is>
       </c>
       <c r="E51" s="7" t="inlineStr"/>
@@ -1932,12 +1932,12 @@
       <c r="B52" s="7" t="inlineStr"/>
       <c r="C52" s="7" t="inlineStr">
         <is>
+          <t>Class 10 (MATH)</t>
+        </is>
+      </c>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
           <t>Class 9 (MATH)</t>
-        </is>
-      </c>
-      <c r="D52" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (MATH)</t>
         </is>
       </c>
       <c r="E52" s="7" t="inlineStr"/>
@@ -1957,7 +1957,11 @@
           <t>Class 10 (MATH)</t>
         </is>
       </c>
-      <c r="C53" s="7" t="inlineStr"/>
+      <c r="C53" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (MATH)</t>
+        </is>
+      </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
           <t>Class 9 (MATH)</t>
@@ -1978,14 +1982,10 @@
       <c r="B54" s="7" t="inlineStr"/>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>Class 9 (MATH)</t>
-        </is>
-      </c>
-      <c r="D54" s="7" t="inlineStr">
-        <is>
           <t>Class 10 (MATH)</t>
         </is>
       </c>
+      <c r="D54" s="7" t="inlineStr"/>
       <c r="E54" s="7" t="inlineStr"/>
       <c r="F54" s="7" t="inlineStr"/>
       <c r="G54" s="7" t="inlineStr"/>
@@ -2090,32 +2090,28 @@
       <c r="B59" s="7" t="inlineStr"/>
       <c r="C59" s="7" t="inlineStr">
         <is>
+          <t>Class 3 (EVS)</t>
+        </is>
+      </c>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
           <t>Class 7 (BIO)</t>
         </is>
       </c>
-      <c r="D59" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (EVS)</t>
-        </is>
-      </c>
       <c r="E59" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (PHY)</t>
+          <t>Class 6 (CHEM)</t>
         </is>
       </c>
       <c r="F59" s="7" t="inlineStr">
         <is>
+          <t>Class 5 (EVS)</t>
+        </is>
+      </c>
+      <c r="G59" s="7" t="inlineStr"/>
+      <c r="H59" s="7" t="inlineStr">
+        <is>
           <t>Class 4 (EVS)</t>
-        </is>
-      </c>
-      <c r="G59" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (CHEM)</t>
-        </is>
-      </c>
-      <c r="H59" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (EVS)</t>
         </is>
       </c>
       <c r="I59" s="7" t="inlineStr"/>
@@ -2127,23 +2123,31 @@
         </is>
       </c>
       <c r="B60" s="7" t="inlineStr"/>
-      <c r="C60" s="7" t="inlineStr"/>
+      <c r="C60" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (EVS)</t>
+        </is>
+      </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
+          <t>Class 6 (PHY)</t>
+        </is>
+      </c>
+      <c r="E60" s="7" t="inlineStr">
+        <is>
           <t>Class 7 (CHEM)</t>
         </is>
       </c>
-      <c r="E60" s="7" t="inlineStr">
+      <c r="F60" s="7" t="inlineStr">
         <is>
           <t>Class 5 (EVS)</t>
         </is>
       </c>
-      <c r="F60" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (EVS)</t>
-        </is>
-      </c>
-      <c r="G60" s="7" t="inlineStr"/>
+      <c r="G60" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (CHEM)</t>
+        </is>
+      </c>
       <c r="H60" s="7" t="inlineStr">
         <is>
           <t>Class 3 (EVS)</t>
@@ -2160,7 +2164,7 @@
       <c r="B61" s="7" t="inlineStr"/>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (PHY)</t>
+          <t>Class 6 (PHY)</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
@@ -2170,19 +2174,15 @@
       </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
+          <t>Class 4 (EVS)</t>
+        </is>
+      </c>
+      <c r="F61" s="7" t="inlineStr">
+        <is>
           <t>Class 5 (EVS)</t>
         </is>
       </c>
-      <c r="F61" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (PHY)</t>
-        </is>
-      </c>
-      <c r="G61" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (EVS)</t>
-        </is>
-      </c>
+      <c r="G61" s="7" t="inlineStr"/>
       <c r="H61" s="7" t="inlineStr">
         <is>
           <t>Class 6 (BIO)</t>
@@ -2199,27 +2199,23 @@
       <c r="B62" s="7" t="inlineStr"/>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (CHEM)</t>
+          <t>Class 7 (BIO)</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
+          <t>Class 7 (PHY)</t>
+        </is>
+      </c>
+      <c r="E62" s="7" t="inlineStr"/>
+      <c r="F62" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (EVS)</t>
+        </is>
+      </c>
+      <c r="G62" s="7" t="inlineStr">
+        <is>
           <t>Class 5 (EVS)</t>
-        </is>
-      </c>
-      <c r="E62" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (EVS)</t>
-        </is>
-      </c>
-      <c r="F62" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (BIO)</t>
-        </is>
-      </c>
-      <c r="G62" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (PHY)</t>
         </is>
       </c>
       <c r="H62" s="7" t="inlineStr">
@@ -2238,28 +2234,28 @@
       <c r="B63" s="7" t="inlineStr"/>
       <c r="C63" s="7" t="inlineStr">
         <is>
+          <t>Class 6 (BIO)</t>
+        </is>
+      </c>
+      <c r="D63" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (EVS)</t>
+        </is>
+      </c>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
           <t>Class 5 (EVS)</t>
         </is>
       </c>
-      <c r="D63" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (EVS)</t>
-        </is>
-      </c>
-      <c r="E63" s="7" t="inlineStr"/>
       <c r="F63" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (BIO)</t>
-        </is>
-      </c>
-      <c r="G63" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (BIO)</t>
-        </is>
-      </c>
+          <t>Class 4 (EVS)</t>
+        </is>
+      </c>
+      <c r="G63" s="7" t="inlineStr"/>
       <c r="H63" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (EVS)</t>
+          <t>Class 7 (CHEM)</t>
         </is>
       </c>
       <c r="I63" s="7" t="inlineStr"/>
@@ -2273,28 +2269,32 @@
       <c r="B64" s="7" t="inlineStr"/>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (CHEM)</t>
+          <t>Class 3 (EVS)</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
+          <t>Class 5 (EVS)</t>
+        </is>
+      </c>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
           <t>Class 7 (BIO)</t>
         </is>
       </c>
-      <c r="E64" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (EVS)</t>
-        </is>
-      </c>
-      <c r="F64" s="7" t="inlineStr"/>
+      <c r="F64" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (EVS)</t>
+        </is>
+      </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (EVS)</t>
+          <t>Class 7 (PHY)</t>
         </is>
       </c>
       <c r="H64" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (EVS)</t>
+          <t>Class 6 (BIO)</t>
         </is>
       </c>
       <c r="I64" s="7" t="inlineStr"/>
@@ -2372,30 +2372,30 @@
           <t>Class 5 (GRAM)</t>
         </is>
       </c>
-      <c r="C68" s="7" t="inlineStr"/>
-      <c r="D68" s="7" t="inlineStr">
+      <c r="C68" s="7" t="inlineStr">
         <is>
           <t>Class 2 (ENG)</t>
         </is>
       </c>
+      <c r="D68" s="7" t="inlineStr"/>
       <c r="E68" s="7" t="inlineStr">
         <is>
+          <t>Class 5 (ENG)</t>
+        </is>
+      </c>
+      <c r="F68" s="7" t="inlineStr">
+        <is>
+          <t>Class 1 (ENG)</t>
+        </is>
+      </c>
+      <c r="G68" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (ENG)</t>
+        </is>
+      </c>
+      <c r="H68" s="7" t="inlineStr">
+        <is>
           <t>Class 3 (ENG)</t>
-        </is>
-      </c>
-      <c r="F68" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (ENG)</t>
-        </is>
-      </c>
-      <c r="G68" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (ENG)</t>
-        </is>
-      </c>
-      <c r="H68" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (ENG)</t>
         </is>
       </c>
       <c r="I68" s="7" t="inlineStr"/>
@@ -2411,26 +2411,30 @@
           <t>Class 5 (ENG)</t>
         </is>
       </c>
-      <c r="C69" s="7" t="inlineStr">
+      <c r="C69" s="7" t="inlineStr"/>
+      <c r="D69" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (GRAM)</t>
+        </is>
+      </c>
+      <c r="E69" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (ENG)</t>
+        </is>
+      </c>
+      <c r="F69" s="7" t="inlineStr">
         <is>
           <t>Class 2 (ENG)</t>
         </is>
       </c>
-      <c r="D69" s="7" t="inlineStr"/>
-      <c r="E69" s="7" t="inlineStr">
+      <c r="G69" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (ENG)</t>
+        </is>
+      </c>
+      <c r="H69" s="7" t="inlineStr">
         <is>
           <t>Class 1 (ENG)</t>
-        </is>
-      </c>
-      <c r="F69" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (ENG)</t>
-        </is>
-      </c>
-      <c r="G69" s="7" t="inlineStr"/>
-      <c r="H69" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (ENG)</t>
         </is>
       </c>
       <c r="I69" s="7" t="inlineStr"/>
@@ -2446,30 +2450,30 @@
           <t>Class 5 (ENG)</t>
         </is>
       </c>
-      <c r="C70" s="7" t="inlineStr"/>
+      <c r="C70" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (ENG)</t>
+        </is>
+      </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
+          <t>Class 1 (ENG)</t>
+        </is>
+      </c>
+      <c r="E70" s="7" t="inlineStr"/>
+      <c r="F70" s="7" t="inlineStr">
+        <is>
+          <t>Class 1 (GRAM)</t>
+        </is>
+      </c>
+      <c r="G70" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (ENG)</t>
+        </is>
+      </c>
+      <c r="H70" s="7" t="inlineStr">
+        <is>
           <t>Class 2 (ENG)</t>
-        </is>
-      </c>
-      <c r="E70" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (ENG)</t>
-        </is>
-      </c>
-      <c r="F70" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (ENG)</t>
-        </is>
-      </c>
-      <c r="G70" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (GRAM)</t>
-        </is>
-      </c>
-      <c r="H70" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (ENG)</t>
         </is>
       </c>
       <c r="I70" s="7" t="inlineStr"/>
@@ -2485,30 +2489,30 @@
           <t>Class 5 (ENG)</t>
         </is>
       </c>
-      <c r="C71" s="7" t="inlineStr">
+      <c r="C71" s="7" t="inlineStr"/>
+      <c r="D71" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (ENG)</t>
+        </is>
+      </c>
+      <c r="E71" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (ENG)</t>
+        </is>
+      </c>
+      <c r="F71" s="7" t="inlineStr">
+        <is>
+          <t>Class 1 (ENG)</t>
+        </is>
+      </c>
+      <c r="G71" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (GRAM)</t>
+        </is>
+      </c>
+      <c r="H71" s="7" t="inlineStr">
         <is>
           <t>Class 4 (ENG)</t>
-        </is>
-      </c>
-      <c r="D71" s="7" t="inlineStr"/>
-      <c r="E71" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (ENG)</t>
-        </is>
-      </c>
-      <c r="F71" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (ENG)</t>
-        </is>
-      </c>
-      <c r="G71" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (GRAM)</t>
-        </is>
-      </c>
-      <c r="H71" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (ENG)</t>
         </is>
       </c>
       <c r="I71" s="7" t="inlineStr"/>
@@ -2524,32 +2528,28 @@
           <t>Class 5 (ENG)</t>
         </is>
       </c>
-      <c r="C72" s="7" t="inlineStr"/>
-      <c r="D72" s="7" t="inlineStr">
+      <c r="C72" s="7" t="inlineStr">
+        <is>
+          <t>Class 1 (ENG)</t>
+        </is>
+      </c>
+      <c r="D72" s="7" t="inlineStr"/>
+      <c r="E72" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (ENG)</t>
+        </is>
+      </c>
+      <c r="F72" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (ENG)</t>
+        </is>
+      </c>
+      <c r="G72" s="7" t="inlineStr">
         <is>
           <t>Class 2 (ENG)</t>
         </is>
       </c>
-      <c r="E72" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (ENG)</t>
-        </is>
-      </c>
-      <c r="F72" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (ENG)</t>
-        </is>
-      </c>
-      <c r="G72" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (GRAM)</t>
-        </is>
-      </c>
-      <c r="H72" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (ENG)</t>
-        </is>
-      </c>
+      <c r="H72" s="7" t="inlineStr"/>
       <c r="I72" s="7" t="inlineStr"/>
     </row>
     <row r="73">
@@ -2566,27 +2566,27 @@
       <c r="C73" s="7" t="inlineStr"/>
       <c r="D73" s="7" t="inlineStr">
         <is>
+          <t>Class 4 (GRAM)</t>
+        </is>
+      </c>
+      <c r="E73" s="7" t="inlineStr">
+        <is>
+          <t>Class 1 (ENG)</t>
+        </is>
+      </c>
+      <c r="F73" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (ENG)</t>
+        </is>
+      </c>
+      <c r="G73" s="7" t="inlineStr">
+        <is>
           <t>Class 4 (ENG)</t>
         </is>
       </c>
-      <c r="E73" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (GRAM)</t>
-        </is>
-      </c>
-      <c r="F73" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (ENG)</t>
-        </is>
-      </c>
-      <c r="G73" s="7" t="inlineStr">
+      <c r="H73" s="7" t="inlineStr">
         <is>
           <t>Class 2 (ENG)</t>
-        </is>
-      </c>
-      <c r="H73" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (ENG)</t>
         </is>
       </c>
       <c r="I73" s="7" t="inlineStr"/>
@@ -2662,16 +2662,16 @@
       <c r="B77" s="7" t="inlineStr"/>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>Class 1 (COMP)</t>
-        </is>
-      </c>
-      <c r="D77" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (COMP)</t>
-        </is>
-      </c>
+          <t>Class 6 (COMP)</t>
+        </is>
+      </c>
+      <c r="D77" s="7" t="inlineStr"/>
       <c r="E77" s="7" t="inlineStr"/>
-      <c r="F77" s="7" t="inlineStr"/>
+      <c r="F77" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (COMP)</t>
+        </is>
+      </c>
       <c r="G77" s="7" t="inlineStr"/>
       <c r="H77" s="7" t="inlineStr"/>
       <c r="I77" s="7" t="inlineStr"/>
@@ -2685,14 +2685,18 @@
       <c r="B78" s="7" t="inlineStr"/>
       <c r="C78" s="7" t="inlineStr"/>
       <c r="D78" s="7" t="inlineStr"/>
-      <c r="E78" s="7" t="inlineStr"/>
+      <c r="E78" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (COMP)</t>
+        </is>
+      </c>
       <c r="F78" s="7" t="inlineStr"/>
-      <c r="G78" s="7" t="inlineStr"/>
-      <c r="H78" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (COMP)</t>
-        </is>
-      </c>
+      <c r="G78" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (COMP)</t>
+        </is>
+      </c>
+      <c r="H78" s="7" t="inlineStr"/>
       <c r="I78" s="7" t="inlineStr"/>
     </row>
     <row r="79">
@@ -2702,15 +2706,15 @@
         </is>
       </c>
       <c r="B79" s="7" t="inlineStr"/>
-      <c r="C79" s="7" t="inlineStr"/>
+      <c r="C79" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (COMP)</t>
+        </is>
+      </c>
       <c r="D79" s="7" t="inlineStr"/>
       <c r="E79" s="7" t="inlineStr"/>
       <c r="F79" s="7" t="inlineStr"/>
-      <c r="G79" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (COMP)</t>
-        </is>
-      </c>
+      <c r="G79" s="7" t="inlineStr"/>
       <c r="H79" s="7" t="inlineStr"/>
       <c r="I79" s="7" t="inlineStr"/>
     </row>
@@ -2724,14 +2728,10 @@
       <c r="C80" s="7" t="inlineStr"/>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (COMP)</t>
-        </is>
-      </c>
-      <c r="E80" s="7" t="inlineStr">
-        <is>
           <t>Class 1 (COMP)</t>
         </is>
       </c>
+      <c r="E80" s="7" t="inlineStr"/>
       <c r="F80" s="7" t="inlineStr"/>
       <c r="G80" s="7" t="inlineStr"/>
       <c r="H80" s="7" t="inlineStr"/>
@@ -2747,14 +2747,10 @@
       <c r="C81" s="7" t="inlineStr"/>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (COMP)</t>
-        </is>
-      </c>
-      <c r="E81" s="7" t="inlineStr">
-        <is>
           <t>Class 1 (COMP)</t>
         </is>
       </c>
+      <c r="E81" s="7" t="inlineStr"/>
       <c r="F81" s="7" t="inlineStr"/>
       <c r="G81" s="7" t="inlineStr"/>
       <c r="H81" s="7" t="inlineStr"/>
@@ -2776,11 +2772,15 @@
       </c>
       <c r="F82" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (COMP)</t>
+          <t>Class 1 (COMP)</t>
         </is>
       </c>
       <c r="G82" s="7" t="inlineStr"/>
-      <c r="H82" s="7" t="inlineStr"/>
+      <c r="H82" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (COMP)</t>
+        </is>
+      </c>
       <c r="I82" s="7" t="inlineStr"/>
     </row>
     <row r="84">
@@ -2853,23 +2853,31 @@
       </c>
       <c r="B86" s="7" t="inlineStr">
         <is>
+          <t>Class 1 (G.K)</t>
+        </is>
+      </c>
+      <c r="C86" s="7" t="inlineStr"/>
+      <c r="D86" s="7" t="inlineStr">
+        <is>
           <t>Class 1 (TEL)</t>
         </is>
       </c>
-      <c r="C86" s="7" t="inlineStr">
+      <c r="E86" s="7" t="inlineStr">
         <is>
           <t>Class 2 (TEL)</t>
         </is>
       </c>
-      <c r="D86" s="7" t="inlineStr"/>
-      <c r="E86" s="7" t="inlineStr"/>
-      <c r="F86" s="7" t="inlineStr"/>
-      <c r="G86" s="7" t="inlineStr">
+      <c r="F86" s="7" t="inlineStr">
+        <is>
+          <t>L.K.G (TEL)</t>
+        </is>
+      </c>
+      <c r="G86" s="7" t="inlineStr"/>
+      <c r="H86" s="7" t="inlineStr">
         <is>
           <t>U.K.G (TEL)</t>
         </is>
       </c>
-      <c r="H86" s="7" t="inlineStr"/>
       <c r="I86" s="8" t="inlineStr">
         <is>
           <t>Class 1</t>
@@ -2884,25 +2892,21 @@
       </c>
       <c r="B87" s="7" t="inlineStr">
         <is>
-          <t>Class 1 (G.K)</t>
-        </is>
-      </c>
-      <c r="C87" s="7" t="inlineStr"/>
+          <t>Class 1 (TEL)</t>
+        </is>
+      </c>
+      <c r="C87" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (TEL)</t>
+        </is>
+      </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
           <t>U.K.G (TEL)</t>
         </is>
       </c>
-      <c r="E87" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (TEL)</t>
-        </is>
-      </c>
-      <c r="F87" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (TEL)</t>
-        </is>
-      </c>
+      <c r="E87" s="7" t="inlineStr"/>
+      <c r="F87" s="7" t="inlineStr"/>
       <c r="G87" s="7" t="inlineStr"/>
       <c r="H87" s="7" t="inlineStr">
         <is>
@@ -2938,16 +2942,8 @@
         </is>
       </c>
       <c r="F88" s="7" t="inlineStr"/>
-      <c r="G88" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (TEL)</t>
-        </is>
-      </c>
-      <c r="H88" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (G.K)</t>
-        </is>
-      </c>
+      <c r="G88" s="7" t="inlineStr"/>
+      <c r="H88" s="7" t="inlineStr"/>
       <c r="I88" s="8" t="inlineStr">
         <is>
           <t>Class 1</t>
@@ -2967,7 +2963,7 @@
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>U.K.G (TEL)</t>
+          <t>Class 2 (TEL)</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr"/>
@@ -2976,13 +2972,13 @@
           <t>L.K.G (TEL)</t>
         </is>
       </c>
-      <c r="F89" s="7" t="inlineStr"/>
+      <c r="F89" s="7" t="inlineStr">
+        <is>
+          <t>U.K.G (TEL)</t>
+        </is>
+      </c>
       <c r="G89" s="7" t="inlineStr"/>
-      <c r="H89" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (TEL)</t>
-        </is>
-      </c>
+      <c r="H89" s="7" t="inlineStr"/>
       <c r="I89" s="8" t="inlineStr">
         <is>
           <t>Class 1</t>
@@ -3000,24 +2996,24 @@
           <t>Class 1 (TEL)</t>
         </is>
       </c>
-      <c r="C90" s="7" t="inlineStr"/>
-      <c r="D90" s="7" t="inlineStr">
+      <c r="C90" s="7" t="inlineStr">
+        <is>
+          <t>L.K.G (TEL)</t>
+        </is>
+      </c>
+      <c r="D90" s="7" t="inlineStr"/>
+      <c r="E90" s="7" t="inlineStr">
         <is>
           <t>U.K.G (TEL)</t>
         </is>
       </c>
-      <c r="E90" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (TEL)</t>
-        </is>
-      </c>
-      <c r="F90" s="7" t="inlineStr"/>
+      <c r="F90" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (TEL)</t>
+        </is>
+      </c>
       <c r="G90" s="7" t="inlineStr"/>
-      <c r="H90" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (TEL)</t>
-        </is>
-      </c>
+      <c r="H90" s="7" t="inlineStr"/>
       <c r="I90" s="8" t="inlineStr">
         <is>
           <t>Class 1</t>
@@ -3037,20 +3033,24 @@
       </c>
       <c r="C91" s="7" t="inlineStr">
         <is>
+          <t>Class 2 (TEL)</t>
+        </is>
+      </c>
+      <c r="D91" s="7" t="inlineStr"/>
+      <c r="E91" s="7" t="inlineStr">
+        <is>
+          <t>L.K.G (TEL)</t>
+        </is>
+      </c>
+      <c r="F91" s="7" t="inlineStr"/>
+      <c r="G91" s="7" t="inlineStr">
+        <is>
+          <t>Class 1 (G.K)</t>
+        </is>
+      </c>
+      <c r="H91" s="7" t="inlineStr">
+        <is>
           <t>U.K.G (TEL)</t>
-        </is>
-      </c>
-      <c r="D91" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (TEL)</t>
-        </is>
-      </c>
-      <c r="E91" s="7" t="inlineStr"/>
-      <c r="F91" s="7" t="inlineStr"/>
-      <c r="G91" s="7" t="inlineStr"/>
-      <c r="H91" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (TEL)</t>
         </is>
       </c>
       <c r="I91" s="8" t="inlineStr">
@@ -3134,26 +3134,26 @@
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (SOC)</t>
+          <t>Class 5 (SOC)</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr"/>
       <c r="E95" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (SOC)</t>
+          <t>Class 3 (SOC)</t>
         </is>
       </c>
       <c r="F95" s="7" t="inlineStr">
         <is>
+          <t>Class 4 (SOC)</t>
+        </is>
+      </c>
+      <c r="G95" s="7" t="inlineStr"/>
+      <c r="H95" s="7" t="inlineStr">
+        <is>
           <t>Class 6 (SOC)</t>
         </is>
       </c>
-      <c r="G95" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (SOC)</t>
-        </is>
-      </c>
-      <c r="H95" s="7" t="inlineStr"/>
       <c r="I95" s="8" t="inlineStr">
         <is>
           <t>Class 7</t>
@@ -3173,26 +3173,26 @@
       </c>
       <c r="C96" s="7" t="inlineStr">
         <is>
+          <t>Class 5 (SOC)</t>
+        </is>
+      </c>
+      <c r="D96" s="7" t="inlineStr">
+        <is>
           <t>Class 3 (SOC)</t>
         </is>
       </c>
-      <c r="D96" s="7" t="inlineStr"/>
-      <c r="E96" s="7" t="inlineStr">
+      <c r="E96" s="7" t="inlineStr"/>
+      <c r="F96" s="7" t="inlineStr">
         <is>
           <t>Class 4 (SOC)</t>
         </is>
       </c>
-      <c r="F96" s="7" t="inlineStr">
+      <c r="G96" s="7" t="inlineStr"/>
+      <c r="H96" s="7" t="inlineStr">
         <is>
           <t>Class 6 (SOC)</t>
         </is>
       </c>
-      <c r="G96" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (SOC)</t>
-        </is>
-      </c>
-      <c r="H96" s="7" t="inlineStr"/>
       <c r="I96" s="8" t="inlineStr">
         <is>
           <t>Class 7</t>
@@ -3223,13 +3223,13 @@
       </c>
       <c r="F97" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (SOC)</t>
+          <t>Class 3 (SOC)</t>
         </is>
       </c>
       <c r="G97" s="7" t="inlineStr"/>
       <c r="H97" s="7" t="inlineStr">
         <is>
-          <t>Class 3 (SOC)</t>
+          <t>Class 4 (SOC)</t>
         </is>
       </c>
       <c r="I97" s="8" t="inlineStr">
@@ -3249,26 +3249,26 @@
           <t>Class 7 (SOC)</t>
         </is>
       </c>
-      <c r="C98" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (SOC)</t>
-        </is>
-      </c>
+      <c r="C98" s="7" t="inlineStr"/>
       <c r="D98" s="7" t="inlineStr">
         <is>
+          <t>Class 4 (SOC)</t>
+        </is>
+      </c>
+      <c r="E98" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (SOC)</t>
+        </is>
+      </c>
+      <c r="F98" s="7" t="inlineStr">
+        <is>
           <t>Class 3 (SOC)</t>
-        </is>
-      </c>
-      <c r="E98" s="7" t="inlineStr"/>
-      <c r="F98" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (SOC)</t>
         </is>
       </c>
       <c r="G98" s="7" t="inlineStr"/>
       <c r="H98" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (SOC)</t>
+          <t>Class 6 (SOC)</t>
         </is>
       </c>
       <c r="I98" s="8" t="inlineStr">
@@ -3290,24 +3290,24 @@
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (SOC)</t>
+          <t>Class 5 (SOC)</t>
         </is>
       </c>
       <c r="D99" s="7" t="inlineStr"/>
       <c r="E99" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (SOC)</t>
-        </is>
-      </c>
-      <c r="F99" s="7" t="inlineStr">
+          <t>Class 3 (SOC)</t>
+        </is>
+      </c>
+      <c r="F99" s="7" t="inlineStr"/>
+      <c r="G99" s="7" t="inlineStr">
         <is>
           <t>Class 4 (SOC)</t>
         </is>
       </c>
-      <c r="G99" s="7" t="inlineStr"/>
       <c r="H99" s="7" t="inlineStr">
         <is>
-          <t>Class 3 (SOC)</t>
+          <t>Class 6 (SOC)</t>
         </is>
       </c>
       <c r="I99" s="8" t="inlineStr">
@@ -3327,12 +3327,12 @@
           <t>Class 7 (SOC)</t>
         </is>
       </c>
-      <c r="C100" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (SOC)</t>
-        </is>
-      </c>
-      <c r="D100" s="7" t="inlineStr"/>
+      <c r="C100" s="7" t="inlineStr"/>
+      <c r="D100" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (SOC)</t>
+        </is>
+      </c>
       <c r="E100" s="7" t="inlineStr">
         <is>
           <t>Class 4 (SOC)</t>
@@ -3346,7 +3346,7 @@
       </c>
       <c r="H100" s="7" t="inlineStr">
         <is>
-          <t>Class 3 (SOC)</t>
+          <t>Class 5 (SOC)</t>
         </is>
       </c>
       <c r="I100" s="8" t="inlineStr">
@@ -3423,31 +3423,27 @@
           <t>MON</t>
         </is>
       </c>
-      <c r="B104" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (GRAM)</t>
-        </is>
-      </c>
+      <c r="B104" s="7" t="inlineStr"/>
       <c r="C104" s="7" t="inlineStr">
         <is>
+          <t>Class 7 (ENG)</t>
+        </is>
+      </c>
+      <c r="D104" s="7" t="inlineStr">
+        <is>
           <t>Class 6 (ENG)</t>
         </is>
       </c>
-      <c r="D104" s="7" t="inlineStr"/>
       <c r="E104" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (GRAM)</t>
-        </is>
-      </c>
-      <c r="F104" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (ENG)</t>
-        </is>
-      </c>
+          <t>Class 7 (GRAM)</t>
+        </is>
+      </c>
+      <c r="F104" s="7" t="inlineStr"/>
       <c r="G104" s="7" t="inlineStr"/>
       <c r="H104" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (GRAM)</t>
+          <t>Class 10 (GRAM)</t>
         </is>
       </c>
       <c r="I104" s="7" t="inlineStr"/>
@@ -3459,23 +3455,19 @@
         </is>
       </c>
       <c r="B105" s="7" t="inlineStr"/>
-      <c r="C105" s="7" t="inlineStr"/>
-      <c r="D105" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (GRAM)</t>
-        </is>
-      </c>
-      <c r="E105" s="7" t="inlineStr">
+      <c r="C105" s="7" t="inlineStr">
         <is>
           <t>Class 6 (ENG)</t>
         </is>
       </c>
-      <c r="F105" s="7" t="inlineStr">
+      <c r="D105" s="7" t="inlineStr"/>
+      <c r="E105" s="7" t="inlineStr"/>
+      <c r="F105" s="7" t="inlineStr"/>
+      <c r="G105" s="7" t="inlineStr">
         <is>
           <t>Class 7 (ENG)</t>
         </is>
       </c>
-      <c r="G105" s="7" t="inlineStr"/>
       <c r="H105" s="7" t="inlineStr"/>
       <c r="I105" s="7" t="inlineStr"/>
     </row>
@@ -3488,18 +3480,22 @@
       <c r="B106" s="7" t="inlineStr"/>
       <c r="C106" s="7" t="inlineStr">
         <is>
+          <t>Class 7 (ENG)</t>
+        </is>
+      </c>
+      <c r="D106" s="7" t="inlineStr"/>
+      <c r="E106" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (GRAM)</t>
+        </is>
+      </c>
+      <c r="F106" s="7" t="inlineStr"/>
+      <c r="G106" s="7" t="inlineStr">
+        <is>
           <t>Class 6 (ENG)</t>
         </is>
       </c>
-      <c r="D106" s="7" t="inlineStr"/>
-      <c r="E106" s="7" t="inlineStr"/>
-      <c r="F106" s="7" t="inlineStr"/>
-      <c r="G106" s="7" t="inlineStr"/>
-      <c r="H106" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (ENG)</t>
-        </is>
-      </c>
+      <c r="H106" s="7" t="inlineStr"/>
       <c r="I106" s="7" t="inlineStr"/>
     </row>
     <row r="107">
@@ -3509,18 +3505,18 @@
         </is>
       </c>
       <c r="B107" s="7" t="inlineStr"/>
-      <c r="C107" s="7" t="inlineStr"/>
-      <c r="D107" s="7" t="inlineStr">
+      <c r="C107" s="7" t="inlineStr">
         <is>
           <t>Class 6 (ENG)</t>
         </is>
       </c>
-      <c r="E107" s="7" t="inlineStr"/>
-      <c r="F107" s="7" t="inlineStr">
+      <c r="D107" s="7" t="inlineStr"/>
+      <c r="E107" s="7" t="inlineStr">
         <is>
           <t>Class 7 (ENG)</t>
         </is>
       </c>
+      <c r="F107" s="7" t="inlineStr"/>
       <c r="G107" s="7" t="inlineStr"/>
       <c r="H107" s="7" t="inlineStr"/>
       <c r="I107" s="7" t="inlineStr"/>
@@ -3535,21 +3531,21 @@
       <c r="C108" s="7" t="inlineStr"/>
       <c r="D108" s="7" t="inlineStr">
         <is>
-          <t>Class 9 (GRAM)</t>
+          <t>Class 6 (GRAM)</t>
         </is>
       </c>
       <c r="E108" s="7" t="inlineStr">
         <is>
+          <t>Class 6 (ENG)</t>
+        </is>
+      </c>
+      <c r="F108" s="7" t="inlineStr">
+        <is>
           <t>Class 7 (ENG)</t>
         </is>
       </c>
-      <c r="F108" s="7" t="inlineStr"/>
       <c r="G108" s="7" t="inlineStr"/>
-      <c r="H108" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (ENG)</t>
-        </is>
-      </c>
+      <c r="H108" s="7" t="inlineStr"/>
       <c r="I108" s="7" t="inlineStr"/>
     </row>
     <row r="109">
@@ -3559,13 +3555,17 @@
         </is>
       </c>
       <c r="B109" s="7" t="inlineStr"/>
-      <c r="C109" s="7" t="inlineStr"/>
-      <c r="D109" s="7" t="inlineStr"/>
-      <c r="E109" s="7" t="inlineStr">
+      <c r="C109" s="7" t="inlineStr">
         <is>
           <t>Class 6 (ENG)</t>
         </is>
       </c>
+      <c r="D109" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (GRAM)</t>
+        </is>
+      </c>
+      <c r="E109" s="7" t="inlineStr"/>
       <c r="F109" s="7" t="inlineStr">
         <is>
           <t>Class 7 (ENG)</t>
@@ -3644,20 +3644,20 @@
         </is>
       </c>
       <c r="B113" s="7" t="inlineStr"/>
-      <c r="C113" s="7" t="inlineStr">
+      <c r="C113" s="7" t="inlineStr"/>
+      <c r="D113" s="7" t="inlineStr"/>
+      <c r="E113" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (HIN)</t>
+        </is>
+      </c>
+      <c r="F113" s="7" t="inlineStr">
         <is>
           <t>Class 10 (HIN)</t>
         </is>
       </c>
-      <c r="D113" s="7" t="inlineStr"/>
-      <c r="E113" s="7" t="inlineStr"/>
-      <c r="F113" s="7" t="inlineStr"/>
       <c r="G113" s="7" t="inlineStr"/>
-      <c r="H113" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (HIN)</t>
-        </is>
-      </c>
+      <c r="H113" s="7" t="inlineStr"/>
       <c r="I113" s="7" t="inlineStr"/>
     </row>
     <row r="114">
@@ -3673,12 +3673,12 @@
         </is>
       </c>
       <c r="D114" s="7" t="inlineStr"/>
-      <c r="E114" s="7" t="inlineStr">
+      <c r="E114" s="7" t="inlineStr"/>
+      <c r="F114" s="7" t="inlineStr">
         <is>
           <t>Class 3 (HIN)</t>
         </is>
       </c>
-      <c r="F114" s="7" t="inlineStr"/>
       <c r="G114" s="7" t="inlineStr">
         <is>
           <t>Class 9 (HIN)</t>
@@ -3694,13 +3694,13 @@
         </is>
       </c>
       <c r="B115" s="7" t="inlineStr"/>
-      <c r="C115" s="7" t="inlineStr">
+      <c r="C115" s="7" t="inlineStr"/>
+      <c r="D115" s="7" t="inlineStr"/>
+      <c r="E115" s="7" t="inlineStr">
         <is>
           <t>Class 3 (HIN)</t>
         </is>
       </c>
-      <c r="D115" s="7" t="inlineStr"/>
-      <c r="E115" s="7" t="inlineStr"/>
       <c r="F115" s="7" t="inlineStr"/>
       <c r="G115" s="7" t="inlineStr">
         <is>
@@ -3723,12 +3723,12 @@
         </is>
       </c>
       <c r="D116" s="7" t="inlineStr"/>
-      <c r="E116" s="7" t="inlineStr">
+      <c r="E116" s="7" t="inlineStr"/>
+      <c r="F116" s="7" t="inlineStr">
         <is>
           <t>Class 10 (HIN)</t>
         </is>
       </c>
-      <c r="F116" s="7" t="inlineStr"/>
       <c r="G116" s="7" t="inlineStr">
         <is>
           <t>Class 9 (HIN)</t>
@@ -3752,15 +3752,11 @@
       <c r="D117" s="7" t="inlineStr"/>
       <c r="E117" s="7" t="inlineStr">
         <is>
-          <t>Class 9 (HIN)</t>
+          <t>Class 10 (HIN)</t>
         </is>
       </c>
       <c r="F117" s="7" t="inlineStr"/>
-      <c r="G117" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (HIN)</t>
-        </is>
-      </c>
+      <c r="G117" s="7" t="inlineStr"/>
       <c r="H117" s="7" t="inlineStr"/>
       <c r="I117" s="7" t="inlineStr"/>
     </row>
@@ -3773,17 +3769,21 @@
       <c r="B118" s="7" t="inlineStr"/>
       <c r="C118" s="7" t="inlineStr">
         <is>
-          <t>Class 3 (HIN)</t>
+          <t>Class 10 (HIN)</t>
         </is>
       </c>
       <c r="D118" s="7" t="inlineStr"/>
       <c r="E118" s="7" t="inlineStr">
         <is>
-          <t>Class 10 (HIN)</t>
+          <t>Class 9 (HIN)</t>
         </is>
       </c>
       <c r="F118" s="7" t="inlineStr"/>
-      <c r="G118" s="7" t="inlineStr"/>
+      <c r="G118" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (HIN)</t>
+        </is>
+      </c>
       <c r="H118" s="7" t="inlineStr"/>
       <c r="I118" s="7" t="inlineStr"/>
     </row>
@@ -3862,19 +3862,19 @@
       </c>
       <c r="C122" s="7" t="inlineStr">
         <is>
-          <t>Class 3 (G.K)</t>
+          <t>Class 1 (HIN)</t>
         </is>
       </c>
       <c r="D122" s="7" t="inlineStr">
         <is>
+          <t>Class 2 (HIN)</t>
+        </is>
+      </c>
+      <c r="E122" s="7" t="inlineStr">
+        <is>
           <t>Class 1 (EVS)</t>
         </is>
       </c>
-      <c r="E122" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (HIN)</t>
-        </is>
-      </c>
       <c r="F122" s="7" t="inlineStr">
         <is>
           <t>U.K.G (ENG)</t>
@@ -3882,10 +3882,14 @@
       </c>
       <c r="G122" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (HIN)</t>
-        </is>
-      </c>
-      <c r="H122" s="7" t="inlineStr"/>
+          <t>U.K.G (ENG)</t>
+        </is>
+      </c>
+      <c r="H122" s="7" t="inlineStr">
+        <is>
+          <t>Class 1 (EVS)</t>
+        </is>
+      </c>
       <c r="I122" s="8" t="inlineStr">
         <is>
           <t>Class 2</t>
@@ -3900,33 +3904,33 @@
       </c>
       <c r="B123" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (HIN)</t>
-        </is>
-      </c>
-      <c r="C123" s="7" t="inlineStr">
+          <t>Class 2 (EVS)</t>
+        </is>
+      </c>
+      <c r="C123" s="7" t="inlineStr"/>
+      <c r="D123" s="7" t="inlineStr">
+        <is>
+          <t>Class 1 (EVS)</t>
+        </is>
+      </c>
+      <c r="E123" s="7" t="inlineStr">
         <is>
           <t>U.K.G (ENG)</t>
         </is>
       </c>
-      <c r="D123" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (EVS)</t>
-        </is>
-      </c>
-      <c r="E123" s="7" t="inlineStr">
+      <c r="F123" s="7" t="inlineStr">
+        <is>
+          <t>Class 1 (HIN)</t>
+        </is>
+      </c>
+      <c r="G123" s="7" t="inlineStr">
         <is>
           <t>U.K.G (ENG)</t>
         </is>
       </c>
-      <c r="F123" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (EVS)</t>
-        </is>
-      </c>
-      <c r="G123" s="7" t="inlineStr"/>
       <c r="H123" s="7" t="inlineStr">
         <is>
-          <t>Class 1 (HIN)</t>
+          <t>U.K.G (ENG)</t>
         </is>
       </c>
       <c r="I123" s="8" t="inlineStr">
@@ -3948,32 +3952,24 @@
       </c>
       <c r="C124" s="7" t="inlineStr">
         <is>
+          <t>Class 1 (HIN)</t>
+        </is>
+      </c>
+      <c r="D124" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (HIN)</t>
+        </is>
+      </c>
+      <c r="E124" s="7" t="inlineStr"/>
+      <c r="F124" s="7" t="inlineStr">
+        <is>
           <t>U.K.G (ENG)</t>
         </is>
       </c>
-      <c r="D124" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (HIN)</t>
-        </is>
-      </c>
-      <c r="E124" s="7" t="inlineStr">
+      <c r="G124" s="7" t="inlineStr"/>
+      <c r="H124" s="7" t="inlineStr">
         <is>
           <t>Class 1 (EVS)</t>
-        </is>
-      </c>
-      <c r="F124" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (EVS)</t>
-        </is>
-      </c>
-      <c r="G124" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (EVS)</t>
-        </is>
-      </c>
-      <c r="H124" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (EVS)</t>
         </is>
       </c>
       <c r="I124" s="8" t="inlineStr">
@@ -4003,10 +3999,14 @@
           <t>U.K.G (ENG)</t>
         </is>
       </c>
-      <c r="E125" s="7" t="inlineStr"/>
+      <c r="E125" s="7" t="inlineStr">
+        <is>
+          <t>Class 1 (HIN)</t>
+        </is>
+      </c>
       <c r="F125" s="7" t="inlineStr">
         <is>
-          <t>Class 1 (EVS)</t>
+          <t>Class 2 (EVS)</t>
         </is>
       </c>
       <c r="G125" s="7" t="inlineStr"/>
@@ -4034,30 +4034,30 @@
       </c>
       <c r="C126" s="7" t="inlineStr">
         <is>
+          <t>Class 2 (EVS)</t>
+        </is>
+      </c>
+      <c r="D126" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (HIN)</t>
+        </is>
+      </c>
+      <c r="E126" s="7" t="inlineStr"/>
+      <c r="F126" s="7" t="inlineStr">
+        <is>
+          <t>Class 1 (EVS)</t>
+        </is>
+      </c>
+      <c r="G126" s="7" t="inlineStr">
+        <is>
           <t>U.K.G (ENG)</t>
         </is>
       </c>
-      <c r="D126" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (HIN)</t>
-        </is>
-      </c>
-      <c r="E126" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (HIN)</t>
-        </is>
-      </c>
-      <c r="F126" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (ENG)</t>
-        </is>
-      </c>
-      <c r="G126" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (ENG)</t>
-        </is>
-      </c>
-      <c r="H126" s="7" t="inlineStr"/>
+      <c r="H126" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (G.K)</t>
+        </is>
+      </c>
       <c r="I126" s="8" t="inlineStr">
         <is>
           <t>Class 2</t>
@@ -4072,31 +4072,31 @@
       </c>
       <c r="B127" s="7" t="inlineStr">
         <is>
+          <t>Class 2 (HIN)</t>
+        </is>
+      </c>
+      <c r="C127" s="7" t="inlineStr">
+        <is>
+          <t>Class 1 (HIN)</t>
+        </is>
+      </c>
+      <c r="D127" s="7" t="inlineStr">
+        <is>
+          <t>U.K.G (ENG)</t>
+        </is>
+      </c>
+      <c r="E127" s="7" t="inlineStr"/>
+      <c r="F127" s="7" t="inlineStr"/>
+      <c r="G127" s="7" t="inlineStr">
+        <is>
           <t>Class 2 (EVS)</t>
         </is>
       </c>
-      <c r="C127" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (HIN)</t>
-        </is>
-      </c>
-      <c r="D127" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (HIN)</t>
-        </is>
-      </c>
-      <c r="E127" s="7" t="inlineStr"/>
-      <c r="F127" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (ENG)</t>
-        </is>
-      </c>
-      <c r="G127" s="7" t="inlineStr">
+      <c r="H127" s="7" t="inlineStr">
         <is>
           <t>Class 1 (EVS)</t>
         </is>
       </c>
-      <c r="H127" s="7" t="inlineStr"/>
       <c r="I127" s="8" t="inlineStr">
         <is>
           <t>Class 2</t>
@@ -4176,18 +4176,22 @@
           <t>Class 6 (MATH)</t>
         </is>
       </c>
-      <c r="C131" s="7" t="inlineStr">
+      <c r="C131" s="7" t="inlineStr"/>
+      <c r="D131" s="7" t="inlineStr">
         <is>
           <t>Class 8 (MATH)</t>
         </is>
       </c>
-      <c r="D131" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (MATH)</t>
-        </is>
-      </c>
-      <c r="E131" s="7" t="inlineStr"/>
-      <c r="F131" s="7" t="inlineStr"/>
+      <c r="E131" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (MATH)</t>
+        </is>
+      </c>
+      <c r="F131" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (MATH)</t>
+        </is>
+      </c>
       <c r="G131" s="7" t="inlineStr"/>
       <c r="H131" s="7" t="inlineStr"/>
       <c r="I131" s="8" t="inlineStr">
@@ -4209,22 +4213,26 @@
       </c>
       <c r="C132" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (MATH)</t>
-        </is>
-      </c>
-      <c r="D132" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (MATH)</t>
-        </is>
-      </c>
-      <c r="E132" s="7" t="inlineStr"/>
-      <c r="F132" s="7" t="inlineStr"/>
-      <c r="G132" s="7" t="inlineStr">
-        <is>
           <t>Class 7 (MATH)</t>
         </is>
       </c>
-      <c r="H132" s="7" t="inlineStr"/>
+      <c r="D132" s="7" t="inlineStr"/>
+      <c r="E132" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (G.K)</t>
+        </is>
+      </c>
+      <c r="F132" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (COMP)</t>
+        </is>
+      </c>
+      <c r="G132" s="7" t="inlineStr"/>
+      <c r="H132" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (MATH)</t>
+        </is>
+      </c>
       <c r="I132" s="8" t="inlineStr">
         <is>
           <t>Class 6</t>
@@ -4250,18 +4258,18 @@
       </c>
       <c r="E133" s="7" t="inlineStr">
         <is>
+          <t>Class 8 (MATH)</t>
+        </is>
+      </c>
+      <c r="F133" s="7" t="inlineStr">
+        <is>
           <t>Class 7 (MATH)</t>
-        </is>
-      </c>
-      <c r="F133" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (G.K)</t>
         </is>
       </c>
       <c r="G133" s="7" t="inlineStr"/>
       <c r="H133" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (MATH)</t>
+          <t>Class 7 (MATH)</t>
         </is>
       </c>
       <c r="I133" s="8" t="inlineStr">
@@ -4278,28 +4286,24 @@
       </c>
       <c r="B134" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (G.K)</t>
+          <t>Class 6 (MATH)</t>
         </is>
       </c>
       <c r="C134" s="7" t="inlineStr"/>
       <c r="D134" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (COMP)</t>
+          <t>Class 6 (MATH)</t>
         </is>
       </c>
       <c r="E134" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (MATH)</t>
-        </is>
-      </c>
-      <c r="F134" s="7" t="inlineStr">
-        <is>
           <t>Class 8 (MATH)</t>
         </is>
       </c>
+      <c r="F134" s="7" t="inlineStr"/>
       <c r="G134" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (COMP)</t>
+          <t>Class 6 (MATH)</t>
         </is>
       </c>
       <c r="H134" s="7" t="inlineStr"/>
@@ -4317,29 +4321,25 @@
       </c>
       <c r="B135" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (MATH)</t>
-        </is>
-      </c>
-      <c r="C135" s="7" t="inlineStr"/>
+          <t>Class 6 (G.K)</t>
+        </is>
+      </c>
+      <c r="C135" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (MATH)</t>
+        </is>
+      </c>
       <c r="D135" s="7" t="inlineStr">
         <is>
           <t>Class 4 (G.K)</t>
         </is>
       </c>
-      <c r="E135" s="7" t="inlineStr">
+      <c r="E135" s="7" t="inlineStr"/>
+      <c r="F135" s="7" t="inlineStr"/>
+      <c r="G135" s="7" t="inlineStr"/>
+      <c r="H135" s="7" t="inlineStr">
         <is>
           <t>Class 8 (MATH)</t>
-        </is>
-      </c>
-      <c r="F135" s="7" t="inlineStr"/>
-      <c r="G135" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (MATH)</t>
-        </is>
-      </c>
-      <c r="H135" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (MATH)</t>
         </is>
       </c>
       <c r="I135" s="8" t="inlineStr">
@@ -4361,19 +4361,19 @@
       </c>
       <c r="C136" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (MATH)</t>
+          <t>Class 7 (MATH)</t>
         </is>
       </c>
       <c r="D136" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (MATH)</t>
+          <t>Class 7 (COMP)</t>
         </is>
       </c>
       <c r="E136" s="7" t="inlineStr"/>
       <c r="F136" s="7" t="inlineStr"/>
       <c r="G136" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (MATH)</t>
+          <t>Class 8 (MATH)</t>
         </is>
       </c>
       <c r="H136" s="7" t="inlineStr"/>
@@ -4453,35 +4453,35 @@
       </c>
       <c r="B140" s="7" t="inlineStr">
         <is>
+          <t>L.K.G (MATH)</t>
+        </is>
+      </c>
+      <c r="C140" s="7" t="inlineStr">
+        <is>
           <t>L.K.G (EVS)</t>
         </is>
       </c>
-      <c r="C140" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (ORAL)</t>
-        </is>
-      </c>
       <c r="D140" s="7" t="inlineStr">
         <is>
-          <t>L.K.G (MATH)</t>
+          <t>L.K.G (EVS)</t>
         </is>
       </c>
       <c r="E140" s="7" t="inlineStr">
         <is>
-          <t>L.K.G (MATH)</t>
-        </is>
-      </c>
-      <c r="F140" s="7" t="inlineStr">
-        <is>
           <t>L.K.G (ENG)</t>
         </is>
       </c>
+      <c r="F140" s="7" t="inlineStr"/>
       <c r="G140" s="7" t="inlineStr">
         <is>
+          <t>L.K.G (EVS)</t>
+        </is>
+      </c>
+      <c r="H140" s="7" t="inlineStr">
+        <is>
           <t>L.K.G (ENG)</t>
         </is>
       </c>
-      <c r="H140" s="7" t="inlineStr"/>
       <c r="I140" s="8" t="inlineStr">
         <is>
           <t>L.K.G</t>
@@ -4501,17 +4501,17 @@
       </c>
       <c r="C141" s="7" t="inlineStr">
         <is>
-          <t>L.K.G (ORAL)</t>
+          <t>L.K.G (ENG)</t>
         </is>
       </c>
       <c r="D141" s="7" t="inlineStr">
         <is>
-          <t>L.K.G (EVS)</t>
+          <t>L.K.G (ENG)</t>
         </is>
       </c>
       <c r="E141" s="7" t="inlineStr">
         <is>
-          <t>L.K.G (EVS)</t>
+          <t>L.K.G (MATH)</t>
         </is>
       </c>
       <c r="F141" s="7" t="inlineStr">
@@ -4539,27 +4539,27 @@
       </c>
       <c r="B142" s="7" t="inlineStr">
         <is>
-          <t>L.K.G (ENG)</t>
+          <t>L.K.G (EVS)</t>
         </is>
       </c>
       <c r="C142" s="7" t="inlineStr">
         <is>
+          <t>L.K.G (ORAL)</t>
+        </is>
+      </c>
+      <c r="D142" s="7" t="inlineStr">
+        <is>
           <t>L.K.G (MATH)</t>
         </is>
       </c>
-      <c r="D142" s="7" t="inlineStr">
+      <c r="E142" s="7" t="inlineStr">
         <is>
           <t>L.K.G (MATH)</t>
         </is>
       </c>
-      <c r="E142" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (ENG)</t>
-        </is>
-      </c>
       <c r="F142" s="7" t="inlineStr">
         <is>
-          <t>L.K.G (EVS)</t>
+          <t>L.K.G (MATH)</t>
         </is>
       </c>
       <c r="G142" s="7" t="inlineStr"/>
@@ -4582,7 +4582,7 @@
       </c>
       <c r="B143" s="7" t="inlineStr">
         <is>
-          <t>L.K.G (ORAL)</t>
+          <t>L.K.G (EVS)</t>
         </is>
       </c>
       <c r="C143" s="7" t="inlineStr">
@@ -4592,19 +4592,19 @@
       </c>
       <c r="D143" s="7" t="inlineStr">
         <is>
-          <t>L.K.G (ENG)</t>
+          <t>L.K.G (MATH)</t>
         </is>
       </c>
       <c r="E143" s="7" t="inlineStr"/>
       <c r="F143" s="7" t="inlineStr">
         <is>
-          <t>L.K.G (EVS)</t>
+          <t>L.K.G (ENG)</t>
         </is>
       </c>
       <c r="G143" s="7" t="inlineStr"/>
       <c r="H143" s="7" t="inlineStr">
         <is>
-          <t>L.K.G (MATH)</t>
+          <t>L.K.G (ORAL)</t>
         </is>
       </c>
       <c r="I143" s="8" t="inlineStr">
@@ -4624,28 +4624,28 @@
           <t>L.K.G (EVS)</t>
         </is>
       </c>
-      <c r="C144" s="7" t="inlineStr">
+      <c r="C144" s="7" t="inlineStr"/>
+      <c r="D144" s="7" t="inlineStr">
         <is>
           <t>L.K.G (EVS)</t>
         </is>
       </c>
-      <c r="D144" s="7" t="inlineStr">
+      <c r="E144" s="7" t="inlineStr">
+        <is>
+          <t>L.K.G (ENG)</t>
+        </is>
+      </c>
+      <c r="F144" s="7" t="inlineStr">
+        <is>
+          <t>L.K.G (ORAL)</t>
+        </is>
+      </c>
+      <c r="G144" s="7" t="inlineStr">
         <is>
           <t>L.K.G (EVS)</t>
         </is>
       </c>
-      <c r="E144" s="7" t="inlineStr"/>
-      <c r="F144" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (ENG)</t>
-        </is>
-      </c>
-      <c r="G144" s="7" t="inlineStr"/>
-      <c r="H144" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (MATH)</t>
-        </is>
-      </c>
+      <c r="H144" s="7" t="inlineStr"/>
       <c r="I144" s="8" t="inlineStr">
         <is>
           <t>L.K.G</t>
@@ -4665,30 +4665,30 @@
       </c>
       <c r="C145" s="7" t="inlineStr">
         <is>
+          <t>L.K.G (ENG)</t>
+        </is>
+      </c>
+      <c r="D145" s="7" t="inlineStr">
+        <is>
+          <t>L.K.G (ENG)</t>
+        </is>
+      </c>
+      <c r="E145" s="7" t="inlineStr"/>
+      <c r="F145" s="7" t="inlineStr">
+        <is>
+          <t>L.K.G (EVS)</t>
+        </is>
+      </c>
+      <c r="G145" s="7" t="inlineStr">
+        <is>
           <t>L.K.G (MATH)</t>
         </is>
       </c>
-      <c r="D145" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (EVS)</t>
-        </is>
-      </c>
-      <c r="E145" s="7" t="inlineStr">
+      <c r="H145" s="7" t="inlineStr">
         <is>
           <t>L.K.G (ENG)</t>
         </is>
       </c>
-      <c r="F145" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (ENG)</t>
-        </is>
-      </c>
-      <c r="G145" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (ENG)</t>
-        </is>
-      </c>
-      <c r="H145" s="7" t="inlineStr"/>
       <c r="I145" s="8" t="inlineStr">
         <is>
           <t>L.K.G</t>
@@ -4774,12 +4774,12 @@
       </c>
       <c r="G149" s="7" t="inlineStr">
         <is>
+          <t>Class 10 (ENG)</t>
+        </is>
+      </c>
+      <c r="H149" s="7" t="inlineStr">
+        <is>
           <t>Class 9 (ENG)</t>
-        </is>
-      </c>
-      <c r="H149" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (ENG)</t>
         </is>
       </c>
       <c r="I149" s="7" t="inlineStr"/>
@@ -4823,17 +4823,17 @@
       <c r="E151" s="7" t="inlineStr"/>
       <c r="F151" s="7" t="inlineStr">
         <is>
+          <t>Class 9 (ENG)</t>
+        </is>
+      </c>
+      <c r="G151" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (ENG)</t>
+        </is>
+      </c>
+      <c r="H151" s="7" t="inlineStr">
+        <is>
           <t>Class 10 (ENG)</t>
-        </is>
-      </c>
-      <c r="G151" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (ENG)</t>
-        </is>
-      </c>
-      <c r="H151" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (ENG)</t>
         </is>
       </c>
       <c r="I151" s="7" t="inlineStr"/>
@@ -4850,17 +4850,17 @@
       <c r="E152" s="7" t="inlineStr"/>
       <c r="F152" s="7" t="inlineStr">
         <is>
+          <t>Class 8 (ENG)</t>
+        </is>
+      </c>
+      <c r="G152" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (ENG)</t>
+        </is>
+      </c>
+      <c r="H152" s="7" t="inlineStr">
+        <is>
           <t>Class 9 (ENG)</t>
-        </is>
-      </c>
-      <c r="G152" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (ENG)</t>
-        </is>
-      </c>
-      <c r="H152" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (ENG)</t>
         </is>
       </c>
       <c r="I152" s="7" t="inlineStr"/>
@@ -4877,20 +4877,20 @@
       <c r="E153" s="7" t="inlineStr"/>
       <c r="F153" s="7" t="inlineStr">
         <is>
+          <t>Class 8 (ENG)</t>
+        </is>
+      </c>
+      <c r="G153" s="7" t="inlineStr"/>
+      <c r="H153" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (ENG)</t>
+        </is>
+      </c>
+      <c r="I153" s="8" t="inlineStr">
+        <is>
           <t>Class 10 (ENG)</t>
         </is>
       </c>
-      <c r="G153" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (ENG)</t>
-        </is>
-      </c>
-      <c r="H153" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (ENG)</t>
-        </is>
-      </c>
-      <c r="I153" s="7" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="6" t="inlineStr">
@@ -4904,20 +4904,20 @@
       <c r="E154" s="7" t="inlineStr"/>
       <c r="F154" s="7" t="inlineStr">
         <is>
+          <t>Class 8 (ENG)</t>
+        </is>
+      </c>
+      <c r="G154" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (ENG)</t>
+        </is>
+      </c>
+      <c r="H154" s="7" t="inlineStr">
+        <is>
           <t>Class 9 (ENG)</t>
         </is>
       </c>
-      <c r="G154" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (ENG)</t>
-        </is>
-      </c>
-      <c r="H154" s="7" t="inlineStr"/>
-      <c r="I154" s="8" t="inlineStr">
-        <is>
-          <t>Class 10 (ENG)</t>
-        </is>
-      </c>
+      <c r="I154" s="7" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="4" t="inlineStr">
@@ -4992,12 +4992,12 @@
       <c r="D158" s="7" t="inlineStr"/>
       <c r="E158" s="7" t="inlineStr">
         <is>
+          <t>Class 10 (SOC)</t>
+        </is>
+      </c>
+      <c r="F158" s="7" t="inlineStr">
+        <is>
           <t>Class 9 (SOC)</t>
-        </is>
-      </c>
-      <c r="F158" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (SOC)</t>
         </is>
       </c>
       <c r="G158" s="7" t="inlineStr">
@@ -5014,16 +5014,16 @@
           <t>TUE</t>
         </is>
       </c>
-      <c r="B159" s="7" t="inlineStr"/>
-      <c r="C159" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (SOC)</t>
-        </is>
-      </c>
+      <c r="B159" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (SOC)</t>
+        </is>
+      </c>
+      <c r="C159" s="7" t="inlineStr"/>
       <c r="D159" s="7" t="inlineStr"/>
       <c r="E159" s="7" t="inlineStr">
         <is>
-          <t>Class 10 (SOC)</t>
+          <t>Class 8 (SOC)</t>
         </is>
       </c>
       <c r="F159" s="7" t="inlineStr">
@@ -5042,24 +5042,24 @@
         </is>
       </c>
       <c r="B160" s="7" t="inlineStr"/>
-      <c r="C160" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (SOC)</t>
-        </is>
-      </c>
+      <c r="C160" s="7" t="inlineStr"/>
       <c r="D160" s="7" t="inlineStr"/>
       <c r="E160" s="7" t="inlineStr">
         <is>
+          <t>Class 10 (SOC)</t>
+        </is>
+      </c>
+      <c r="F160" s="7" t="inlineStr">
+        <is>
           <t>Class 8 (SOC)</t>
         </is>
       </c>
-      <c r="F160" s="7" t="inlineStr">
+      <c r="G160" s="7" t="inlineStr"/>
+      <c r="H160" s="7" t="inlineStr">
         <is>
           <t>Class 9 (SOC)</t>
         </is>
       </c>
-      <c r="G160" s="7" t="inlineStr"/>
-      <c r="H160" s="7" t="inlineStr"/>
       <c r="I160" s="7" t="inlineStr"/>
     </row>
     <row r="161">
@@ -5071,7 +5071,7 @@
       <c r="B161" s="7" t="inlineStr"/>
       <c r="C161" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (SOC)</t>
+          <t>Class 10 (SOC)</t>
         </is>
       </c>
       <c r="D161" s="7" t="inlineStr"/>
@@ -5084,7 +5084,7 @@
       <c r="G161" s="7" t="inlineStr"/>
       <c r="H161" s="7" t="inlineStr">
         <is>
-          <t>Class 10 (SOC)</t>
+          <t>Class 8 (SOC)</t>
         </is>
       </c>
       <c r="I161" s="7" t="inlineStr"/>
@@ -5096,22 +5096,22 @@
         </is>
       </c>
       <c r="B162" s="7" t="inlineStr"/>
-      <c r="C162" s="7" t="inlineStr"/>
+      <c r="C162" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (SOC)</t>
+        </is>
+      </c>
       <c r="D162" s="7" t="inlineStr"/>
       <c r="E162" s="7" t="inlineStr">
         <is>
-          <t>Class 10 (SOC)</t>
-        </is>
-      </c>
-      <c r="F162" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (SOC)</t>
-        </is>
-      </c>
+          <t>Class 8 (SOC)</t>
+        </is>
+      </c>
+      <c r="F162" s="7" t="inlineStr"/>
       <c r="G162" s="7" t="inlineStr"/>
       <c r="H162" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (SOC)</t>
+          <t>Class 10 (SOC)</t>
         </is>
       </c>
       <c r="I162" s="7" t="inlineStr"/>
@@ -5123,24 +5123,24 @@
         </is>
       </c>
       <c r="B163" s="7" t="inlineStr"/>
-      <c r="C163" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (SOC)</t>
-        </is>
-      </c>
+      <c r="C163" s="7" t="inlineStr"/>
       <c r="D163" s="7" t="inlineStr"/>
       <c r="E163" s="7" t="inlineStr">
         <is>
+          <t>Class 8 (SOC)</t>
+        </is>
+      </c>
+      <c r="F163" s="7" t="inlineStr">
+        <is>
           <t>Class 9 (SOC)</t>
         </is>
       </c>
-      <c r="F163" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (SOC)</t>
-        </is>
-      </c>
       <c r="G163" s="7" t="inlineStr"/>
-      <c r="H163" s="7" t="inlineStr"/>
+      <c r="H163" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (SOC)</t>
+        </is>
+      </c>
       <c r="I163" s="7" t="inlineStr"/>
     </row>
     <row r="165">
@@ -5218,24 +5218,24 @@
       </c>
       <c r="C167" s="7" t="inlineStr">
         <is>
+          <t>Class 4 (TEL)</t>
+        </is>
+      </c>
+      <c r="D167" s="7" t="inlineStr">
+        <is>
           <t>U.K.G (HIN)</t>
         </is>
       </c>
-      <c r="D167" s="7" t="inlineStr"/>
-      <c r="E167" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (TEL)</t>
-        </is>
-      </c>
-      <c r="F167" s="7" t="inlineStr">
+      <c r="E167" s="7" t="inlineStr"/>
+      <c r="F167" s="7" t="inlineStr"/>
+      <c r="G167" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (TEL)</t>
+        </is>
+      </c>
+      <c r="H167" s="7" t="inlineStr">
         <is>
           <t>Class 5 (TEL)</t>
-        </is>
-      </c>
-      <c r="G167" s="7" t="inlineStr"/>
-      <c r="H167" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (TEL)</t>
         </is>
       </c>
       <c r="I167" s="8" t="inlineStr">
@@ -5255,26 +5255,26 @@
           <t>Class 3 (TEL)</t>
         </is>
       </c>
-      <c r="C168" s="7" t="inlineStr">
+      <c r="C168" s="7" t="inlineStr"/>
+      <c r="D168" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (TEL)</t>
+        </is>
+      </c>
+      <c r="E168" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (TEL)</t>
+        </is>
+      </c>
+      <c r="F168" s="7" t="inlineStr">
+        <is>
+          <t>U.K.G (HIN)</t>
+        </is>
+      </c>
+      <c r="G168" s="7" t="inlineStr"/>
+      <c r="H168" s="7" t="inlineStr">
         <is>
           <t>Class 4 (TEL)</t>
-        </is>
-      </c>
-      <c r="D168" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (TEL)</t>
-        </is>
-      </c>
-      <c r="E168" s="7" t="inlineStr"/>
-      <c r="F168" s="7" t="inlineStr"/>
-      <c r="G168" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (TEL)</t>
-        </is>
-      </c>
-      <c r="H168" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (HIN)</t>
         </is>
       </c>
       <c r="I168" s="8" t="inlineStr">
@@ -5296,24 +5296,24 @@
       </c>
       <c r="C169" s="7" t="inlineStr">
         <is>
+          <t>U.K.G (HIN)</t>
+        </is>
+      </c>
+      <c r="D169" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (TEL)</t>
+        </is>
+      </c>
+      <c r="E169" s="7" t="inlineStr"/>
+      <c r="F169" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (TEL)</t>
+        </is>
+      </c>
+      <c r="G169" s="7" t="inlineStr"/>
+      <c r="H169" s="7" t="inlineStr">
+        <is>
           <t>Class 5 (TEL)</t>
-        </is>
-      </c>
-      <c r="D169" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (TEL)</t>
-        </is>
-      </c>
-      <c r="E169" s="7" t="inlineStr"/>
-      <c r="F169" s="7" t="inlineStr"/>
-      <c r="G169" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (TEL)</t>
-        </is>
-      </c>
-      <c r="H169" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (HIN)</t>
         </is>
       </c>
       <c r="I169" s="8" t="inlineStr">
@@ -5336,25 +5336,21 @@
       <c r="C170" s="7" t="inlineStr"/>
       <c r="D170" s="7" t="inlineStr">
         <is>
+          <t>Class 5 (TEL)</t>
+        </is>
+      </c>
+      <c r="E170" s="7" t="inlineStr">
+        <is>
           <t>Class 4 (TEL)</t>
         </is>
       </c>
-      <c r="E170" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (TEL)</t>
-        </is>
-      </c>
       <c r="F170" s="7" t="inlineStr">
         <is>
-          <t>U.K.G (HIN)</t>
+          <t>Class 6 (TEL)</t>
         </is>
       </c>
       <c r="G170" s="7" t="inlineStr"/>
-      <c r="H170" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (TEL)</t>
-        </is>
-      </c>
+      <c r="H170" s="7" t="inlineStr"/>
       <c r="I170" s="8" t="inlineStr">
         <is>
           <t>Class 3</t>
@@ -5377,19 +5373,23 @@
           <t>Class 4 (TEL)</t>
         </is>
       </c>
-      <c r="D171" s="7" t="inlineStr"/>
-      <c r="E171" s="7" t="inlineStr">
+      <c r="D171" s="7" t="inlineStr">
+        <is>
+          <t>U.K.G (HIN)</t>
+        </is>
+      </c>
+      <c r="E171" s="7" t="inlineStr"/>
+      <c r="F171" s="7" t="inlineStr">
         <is>
           <t>Class 6 (TEL)</t>
         </is>
       </c>
-      <c r="F171" s="7" t="inlineStr">
+      <c r="G171" s="7" t="inlineStr"/>
+      <c r="H171" s="7" t="inlineStr">
         <is>
           <t>Class 5 (TEL)</t>
         </is>
       </c>
-      <c r="G171" s="7" t="inlineStr"/>
-      <c r="H171" s="7" t="inlineStr"/>
       <c r="I171" s="8" t="inlineStr">
         <is>
           <t>Class 3</t>
@@ -5409,15 +5409,15 @@
       </c>
       <c r="C172" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (TEL)</t>
-        </is>
-      </c>
-      <c r="D172" s="7" t="inlineStr">
-        <is>
           <t>Class 5 (TEL)</t>
         </is>
       </c>
-      <c r="E172" s="7" t="inlineStr"/>
+      <c r="D172" s="7" t="inlineStr"/>
+      <c r="E172" s="7" t="inlineStr">
+        <is>
+          <t>U.K.G (HIN)</t>
+        </is>
+      </c>
       <c r="F172" s="7" t="inlineStr">
         <is>
           <t>Class 6 (TEL)</t>
@@ -5426,7 +5426,7 @@
       <c r="G172" s="7" t="inlineStr"/>
       <c r="H172" s="7" t="inlineStr">
         <is>
-          <t>U.K.G (HIN)</t>
+          <t>Class 4 (TEL)</t>
         </is>
       </c>
       <c r="I172" s="8" t="inlineStr">
@@ -5511,14 +5511,10 @@
       <c r="C176" s="7" t="inlineStr"/>
       <c r="D176" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (MATH)</t>
-        </is>
-      </c>
-      <c r="E176" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (MATH)</t>
-        </is>
-      </c>
+          <t>Class 3 (MATH)</t>
+        </is>
+      </c>
+      <c r="E176" s="7" t="inlineStr"/>
       <c r="F176" s="7" t="inlineStr">
         <is>
           <t>Class 3 (MATH)</t>
@@ -5545,19 +5541,19 @@
       </c>
       <c r="C177" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (MATH)</t>
+          <t>Class 3 (MATH)</t>
         </is>
       </c>
       <c r="D177" s="7" t="inlineStr">
         <is>
-          <t>Class 3 (MATH)</t>
+          <t>Class 4 (MATH)</t>
         </is>
       </c>
       <c r="E177" s="7" t="inlineStr"/>
       <c r="F177" s="7" t="inlineStr"/>
       <c r="G177" s="7" t="inlineStr">
         <is>
-          <t>Class 3 (MATH)</t>
+          <t>Class 2 (MATH)</t>
         </is>
       </c>
       <c r="H177" s="7" t="inlineStr">
@@ -5582,7 +5578,11 @@
           <t>Class 4 (MATH)</t>
         </is>
       </c>
-      <c r="C178" s="7" t="inlineStr"/>
+      <c r="C178" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (MATH)</t>
+        </is>
+      </c>
       <c r="D178" s="7" t="inlineStr"/>
       <c r="E178" s="7" t="inlineStr">
         <is>
@@ -5591,15 +5591,15 @@
       </c>
       <c r="F178" s="7" t="inlineStr">
         <is>
+          <t>Class 2 (MATH)</t>
+        </is>
+      </c>
+      <c r="G178" s="7" t="inlineStr"/>
+      <c r="H178" s="7" t="inlineStr">
+        <is>
           <t>Class 3 (MATH)</t>
         </is>
       </c>
-      <c r="G178" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (MATH)</t>
-        </is>
-      </c>
-      <c r="H178" s="7" t="inlineStr"/>
       <c r="I178" s="8" t="inlineStr">
         <is>
           <t>Class 4</t>
@@ -5619,7 +5619,7 @@
       </c>
       <c r="C179" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (MATH)</t>
+          <t>Class 5 (MATH)</t>
         </is>
       </c>
       <c r="D179" s="7" t="inlineStr"/>
@@ -5630,13 +5630,13 @@
       </c>
       <c r="F179" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (MATH)</t>
+          <t>Class 5 (MATH)</t>
         </is>
       </c>
       <c r="G179" s="7" t="inlineStr"/>
       <c r="H179" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (MATH)</t>
+          <t>Class 2 (MATH)</t>
         </is>
       </c>
       <c r="I179" s="8" t="inlineStr">
@@ -5656,28 +5656,28 @@
           <t>Class 4 (MATH)</t>
         </is>
       </c>
-      <c r="C180" s="7" t="inlineStr">
+      <c r="C180" s="7" t="inlineStr"/>
+      <c r="D180" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (MATH)</t>
+        </is>
+      </c>
+      <c r="E180" s="7" t="inlineStr">
         <is>
           <t>Class 2 (MATH)</t>
         </is>
       </c>
-      <c r="D180" s="7" t="inlineStr"/>
-      <c r="E180" s="7" t="inlineStr">
+      <c r="F180" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (MATH)</t>
+        </is>
+      </c>
+      <c r="G180" s="7" t="inlineStr">
         <is>
           <t>Class 3 (MATH)</t>
         </is>
       </c>
-      <c r="F180" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (MATH)</t>
-        </is>
-      </c>
-      <c r="G180" s="7" t="inlineStr"/>
-      <c r="H180" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (MATH)</t>
-        </is>
-      </c>
+      <c r="H180" s="7" t="inlineStr"/>
       <c r="I180" s="8" t="inlineStr">
         <is>
           <t>Class 4</t>
@@ -5698,25 +5698,25 @@
       <c r="C181" s="7" t="inlineStr"/>
       <c r="D181" s="7" t="inlineStr">
         <is>
+          <t>Class 2 (MATH)</t>
+        </is>
+      </c>
+      <c r="E181" s="7" t="inlineStr">
+        <is>
           <t>Class 3 (MATH)</t>
         </is>
       </c>
-      <c r="E181" s="7" t="inlineStr">
+      <c r="F181" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (MATH)</t>
+        </is>
+      </c>
+      <c r="G181" s="7" t="inlineStr">
         <is>
           <t>Class 5 (MATH)</t>
         </is>
       </c>
-      <c r="F181" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (MATH)</t>
-        </is>
-      </c>
-      <c r="G181" s="7" t="inlineStr"/>
-      <c r="H181" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (MATH)</t>
-        </is>
-      </c>
+      <c r="H181" s="7" t="inlineStr"/>
       <c r="I181" s="8" t="inlineStr">
         <is>
           <t>Class 4</t>
@@ -5792,17 +5792,13 @@
         </is>
       </c>
       <c r="B185" s="7" t="inlineStr"/>
-      <c r="C185" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (KAR)</t>
-        </is>
-      </c>
-      <c r="D185" s="7" t="inlineStr"/>
-      <c r="E185" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (KAR)</t>
-        </is>
-      </c>
+      <c r="C185" s="7" t="inlineStr"/>
+      <c r="D185" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (KAR)</t>
+        </is>
+      </c>
+      <c r="E185" s="7" t="inlineStr"/>
       <c r="F185" s="7" t="inlineStr"/>
       <c r="G185" s="7" t="inlineStr"/>
       <c r="H185" s="7" t="inlineStr"/>
@@ -5817,21 +5813,21 @@
       <c r="B186" s="7" t="inlineStr"/>
       <c r="C186" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (KAR)</t>
+          <t>Class 1 (KAR)</t>
         </is>
       </c>
       <c r="D186" s="7" t="inlineStr"/>
       <c r="E186" s="7" t="inlineStr"/>
       <c r="F186" s="7" t="inlineStr"/>
-      <c r="G186" s="7" t="inlineStr"/>
-      <c r="H186" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (KAR)</t>
-        </is>
-      </c>
+      <c r="G186" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (KAR)</t>
+        </is>
+      </c>
+      <c r="H186" s="7" t="inlineStr"/>
       <c r="I186" s="7" t="inlineStr"/>
     </row>
-    <row r="187" ht="26" customHeight="1">
+    <row r="187">
       <c r="A187" s="6" t="inlineStr">
         <is>
           <t>WED</t>
@@ -5840,18 +5836,13 @@
       <c r="B187" s="7" t="inlineStr"/>
       <c r="C187" s="7" t="inlineStr"/>
       <c r="D187" s="7" t="inlineStr"/>
-      <c r="E187" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (KAR)
-Class 9 (KAR)</t>
-        </is>
-      </c>
+      <c r="E187" s="7" t="inlineStr"/>
       <c r="F187" s="7" t="inlineStr"/>
       <c r="G187" s="7" t="inlineStr"/>
       <c r="H187" s="7" t="inlineStr"/>
       <c r="I187" s="7" t="inlineStr"/>
     </row>
-    <row r="188">
+    <row r="188" ht="26" customHeight="1">
       <c r="A188" s="6" t="inlineStr">
         <is>
           <t>THU</t>
@@ -5861,12 +5852,21 @@
       <c r="C188" s="7" t="inlineStr"/>
       <c r="D188" s="7" t="inlineStr">
         <is>
-          <t>Class 10 (KAR)</t>
+          <t>Class 2 (KAR)
+Class 8 (KAR)</t>
         </is>
       </c>
       <c r="E188" s="7" t="inlineStr"/>
-      <c r="F188" s="7" t="inlineStr"/>
-      <c r="G188" s="7" t="inlineStr"/>
+      <c r="F188" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (KAR)</t>
+        </is>
+      </c>
+      <c r="G188" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (KAR)</t>
+        </is>
+      </c>
       <c r="H188" s="7" t="inlineStr"/>
       <c r="I188" s="7" t="inlineStr"/>
     </row>
@@ -5878,7 +5878,11 @@
       </c>
       <c r="B189" s="7" t="inlineStr"/>
       <c r="C189" s="7" t="inlineStr"/>
-      <c r="D189" s="7" t="inlineStr"/>
+      <c r="D189" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (KAR)</t>
+        </is>
+      </c>
       <c r="E189" s="7" t="inlineStr"/>
       <c r="F189" s="7" t="inlineStr"/>
       <c r="G189" s="7" t="inlineStr"/>
@@ -5892,23 +5896,19 @@
         </is>
       </c>
       <c r="B190" s="7" t="inlineStr"/>
-      <c r="C190" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (KAR)</t>
-        </is>
-      </c>
-      <c r="D190" s="7" t="inlineStr"/>
-      <c r="E190" s="7" t="inlineStr"/>
-      <c r="F190" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (KAR)</t>
-        </is>
-      </c>
-      <c r="G190" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (KAR)</t>
-        </is>
-      </c>
+      <c r="C190" s="7" t="inlineStr"/>
+      <c r="D190" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (KAR)</t>
+        </is>
+      </c>
+      <c r="E190" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (KAR)</t>
+        </is>
+      </c>
+      <c r="F190" s="7" t="inlineStr"/>
+      <c r="G190" s="7" t="inlineStr"/>
       <c r="H190" s="7" t="inlineStr"/>
       <c r="I190" s="7" t="inlineStr"/>
     </row>
@@ -5974,7 +5974,7 @@
         </is>
       </c>
     </row>
-    <row r="194" ht="65" customHeight="1">
+    <row r="194" ht="52" customHeight="1">
       <c r="A194" s="6" t="inlineStr">
         <is>
           <t>MON</t>
@@ -5985,19 +5985,18 @@
       <c r="D194" s="7" t="inlineStr"/>
       <c r="E194" s="7" t="inlineStr"/>
       <c r="F194" s="7" t="inlineStr"/>
-      <c r="G194" s="7" t="inlineStr"/>
-      <c r="H194" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (P.E.T)
-U.K.G (P.E.T)
-Class 1 (P.E.T)
+      <c r="G194" s="7" t="inlineStr">
+        <is>
+          <t>Class 1 (P.E.T)
 Class 2 (P.E.T)
-Class 3 (P.E.T)</t>
-        </is>
-      </c>
+Class 3 (P.E.T)
+Class 5 (P.E.T)</t>
+        </is>
+      </c>
+      <c r="H194" s="7" t="inlineStr"/>
       <c r="I194" s="7" t="inlineStr"/>
     </row>
-    <row r="195" ht="52" customHeight="1">
+    <row r="195">
       <c r="A195" s="6" t="inlineStr">
         <is>
           <t>TUE</t>
@@ -6008,18 +6007,11 @@
       <c r="D195" s="7" t="inlineStr"/>
       <c r="E195" s="7" t="inlineStr"/>
       <c r="F195" s="7" t="inlineStr"/>
-      <c r="G195" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (P.E.T)
-Class 1 (P.E.T)
-Class 2 (P.E.T)
-Class 4 (P.E.T)</t>
-        </is>
-      </c>
+      <c r="G195" s="7" t="inlineStr"/>
       <c r="H195" s="7" t="inlineStr"/>
       <c r="I195" s="7" t="inlineStr"/>
     </row>
-    <row r="196">
+    <row r="196" ht="78" customHeight="1">
       <c r="A196" s="6" t="inlineStr">
         <is>
           <t>WED</t>
@@ -6030,11 +6022,20 @@
       <c r="D196" s="7" t="inlineStr"/>
       <c r="E196" s="7" t="inlineStr"/>
       <c r="F196" s="7" t="inlineStr"/>
-      <c r="G196" s="7" t="inlineStr"/>
+      <c r="G196" s="7" t="inlineStr">
+        <is>
+          <t>L.K.G (P.E.T)
+U.K.G (P.E.T)
+Class 1 (P.E.T)
+Class 2 (P.E.T)
+Class 3 (P.E.T)
+Class 5 (P.E.T)</t>
+        </is>
+      </c>
       <c r="H196" s="7" t="inlineStr"/>
       <c r="I196" s="7" t="inlineStr"/>
     </row>
-    <row r="197" ht="78" customHeight="1">
+    <row r="197" ht="65" customHeight="1">
       <c r="A197" s="6" t="inlineStr">
         <is>
           <t>THU</t>
@@ -6051,8 +6052,7 @@
 U.K.G (P.E.T)
 Class 1 (P.E.T)
 Class 2 (P.E.T)
-Class 4 (P.E.T)
-Class 5 (P.E.T)</t>
+Class 4 (P.E.T)</t>
         </is>
       </c>
       <c r="H197" s="7" t="inlineStr"/>
@@ -6071,17 +6071,25 @@
       <c r="F198" s="7" t="inlineStr"/>
       <c r="G198" s="7" t="inlineStr">
         <is>
+          <t>Class 6 (P.E.T)
+Class 7 (P.E.T)
+Class 8 (P.E.T)
+Class 9 (P.E.T)
+Class 10 (P.E.T)</t>
+        </is>
+      </c>
+      <c r="H198" s="7" t="inlineStr">
+        <is>
           <t>L.K.G (P.E.T)
+U.K.G (P.E.T)
 Class 1 (P.E.T)
 Class 2 (P.E.T)
-Class 3 (P.E.T)
-Class 5 (P.E.T)</t>
-        </is>
-      </c>
-      <c r="H198" s="7" t="inlineStr"/>
+Class 4 (P.E.T)</t>
+        </is>
+      </c>
       <c r="I198" s="7" t="inlineStr"/>
     </row>
-    <row r="199" ht="65" customHeight="1">
+    <row r="199">
       <c r="A199" s="6" t="inlineStr">
         <is>
           <t>SAT</t>
@@ -6093,15 +6101,7 @@
       <c r="E199" s="7" t="inlineStr"/>
       <c r="F199" s="7" t="inlineStr"/>
       <c r="G199" s="7" t="inlineStr"/>
-      <c r="H199" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (P.E.T)
-Class 7 (P.E.T)
-Class 8 (P.E.T)
-Class 9 (P.E.T)
-Class 10 (P.E.T)</t>
-        </is>
-      </c>
+      <c r="H199" s="7" t="inlineStr"/>
       <c r="I199" s="7" t="inlineStr"/>
     </row>
   </sheetData>
@@ -6243,7 +6243,7 @@
       <c r="C2" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(EVS)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="D2" s="7" t="inlineStr">
@@ -6255,7 +6255,7 @@
       <c r="E2" s="7" t="inlineStr">
         <is>
           <t>NAGAMANI
-(TEL)</t>
+(G.K)</t>
         </is>
       </c>
       <c r="F2" s="7" t="inlineStr">
@@ -6308,8 +6308,8 @@
       </c>
       <c r="N2" s="7" t="inlineStr">
         <is>
-          <t>RAVI
-(GRAM)</t>
+          <t>BHEEMA
+(PHY)</t>
         </is>
       </c>
     </row>
@@ -6321,61 +6321,61 @@
       <c r="C3" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(ORAL)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
+          <t>BHAVANI
+(EVS)</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>SAI LAKSHMI
+(HIN)</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>MAHA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>LALITHA
+(EVS)</t>
+        </is>
+      </c>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
           <t>SWATHI
-(HIN)</t>
-        </is>
-      </c>
-      <c r="E3" s="7" t="inlineStr">
+(TEL)</t>
+        </is>
+      </c>
+      <c r="I3" s="7" t="inlineStr">
+        <is>
+          <t>PALLAVI
+(SOC)</t>
+        </is>
+      </c>
+      <c r="J3" s="7" t="inlineStr">
         <is>
           <t>MAHESWARI
 (COMP)</t>
         </is>
       </c>
-      <c r="F3" s="7" t="inlineStr">
-        <is>
-          <t>NAGAMANI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="G3" s="7" t="inlineStr">
-        <is>
-          <t>SAI LAKSHMI
-(G.K)</t>
-        </is>
-      </c>
-      <c r="H3" s="7" t="inlineStr">
-        <is>
-          <t>PALLAVI
-(SOC)</t>
-        </is>
-      </c>
-      <c r="I3" s="7" t="inlineStr">
-        <is>
-          <t>MARTIAL ARTS
-(KAR)</t>
-        </is>
-      </c>
-      <c r="J3" s="7" t="inlineStr">
+      <c r="K3" s="7" t="inlineStr">
         <is>
           <t>RAVI
 (ENG)</t>
         </is>
       </c>
-      <c r="K3" s="7" t="inlineStr">
-        <is>
-          <t>LALITHA
-(BIO)</t>
-        </is>
-      </c>
       <c r="L3" s="7" t="inlineStr">
         <is>
-          <t>SANGEETHA
-(MATH)</t>
+          <t>BHEEMA
+(PHY)</t>
         </is>
       </c>
       <c r="M3" s="7" t="inlineStr">
@@ -6386,8 +6386,8 @@
       </c>
       <c r="N3" s="7" t="inlineStr">
         <is>
-          <t>RIYA
-(HIN)</t>
+          <t>D.V.RAO
+(TEL)</t>
         </is>
       </c>
     </row>
@@ -6399,67 +6399,67 @@
       <c r="C4" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(MATH)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>BHAVANI
-(MATH)</t>
+          <t>SWATHI
+(HIN)</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
+          <t>NAGAMANI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
           <t>SAI LAKSHMI
-(EVS)</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>MAHA
-(ENG)</t>
+(HIN)</t>
         </is>
       </c>
       <c r="G4" s="7" t="inlineStr">
-        <is>
-          <t>LALITHA
-(EVS)</t>
-        </is>
-      </c>
-      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>TULASI
 (MATH)</t>
         </is>
       </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>MARTIAL ARTS
+(KAR)</t>
+        </is>
+      </c>
       <c r="I4" s="7" t="inlineStr">
         <is>
-          <t>MAHESWARI
-(COMP)</t>
+          <t>FATHIMA
+(HIN)</t>
         </is>
       </c>
       <c r="J4" s="7" t="inlineStr">
+        <is>
+          <t>RAVI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="K4" s="7" t="inlineStr">
+        <is>
+          <t>LALITHA
+(BIO)</t>
+        </is>
+      </c>
+      <c r="L4" s="7" t="inlineStr">
         <is>
           <t>SANGEETHA
 (MATH)</t>
         </is>
       </c>
-      <c r="K4" s="7" t="inlineStr">
-        <is>
-          <t>FATHIMA
-(G.K)</t>
-        </is>
-      </c>
-      <c r="L4" s="7" t="inlineStr">
-        <is>
-          <t>D.V.RAO
-(TEL)</t>
-        </is>
-      </c>
       <c r="M4" s="7" t="inlineStr">
         <is>
           <t>BHEEMA
-(CHEM)</t>
+(PHY)</t>
         </is>
       </c>
       <c r="N4" s="7" t="inlineStr">
@@ -6477,7 +6477,7 @@
       <c r="C5" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(MATH)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
@@ -6489,61 +6489,61 @@
       <c r="E5" s="7" t="inlineStr">
         <is>
           <t>SAI LAKSHMI
+(EVS)</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>NAGAMANI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>PALLAVI
+(SOC)</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>FATHIMA
 (HIN)</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
-        <is>
-          <t>TULASI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="I5" s="7" t="inlineStr">
         <is>
           <t>MAHA
 (ENG)</t>
         </is>
       </c>
-      <c r="H5" s="7" t="inlineStr">
-        <is>
-          <t>SWATHI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="I5" s="7" t="inlineStr">
-        <is>
-          <t>PALLAVI
-(SOC)</t>
-        </is>
-      </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
-          <t>MARTIAL ARTS
-(KAR)</t>
+          <t>LALITHA
+(CHEM)</t>
         </is>
       </c>
       <c r="K5" s="7" t="inlineStr">
-        <is>
-          <t>LALITHA
-(PHY)</t>
-        </is>
-      </c>
-      <c r="L5" s="7" t="inlineStr">
         <is>
           <t>RAVI
 (GRAM)</t>
         </is>
       </c>
+      <c r="L5" s="7" t="inlineStr">
+        <is>
+          <t>SANGEETHA
+(MATH)</t>
+        </is>
+      </c>
       <c r="M5" s="7" t="inlineStr">
+        <is>
+          <t>RIYA
+(HIN)</t>
+        </is>
+      </c>
+      <c r="N5" s="7" t="inlineStr">
         <is>
           <t>SUNITHA
 (SOC)</t>
-        </is>
-      </c>
-      <c r="N5" s="7" t="inlineStr">
-        <is>
-          <t>D.V.RAO
-(TEL)</t>
         </is>
       </c>
     </row>
@@ -6554,8 +6554,8 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>SITHA
-(ENG)</t>
+          <t>NAGAMANI
+(TEL)</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
@@ -6572,8 +6572,8 @@
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>BHAVANI
-(G.K)</t>
+          <t>MAHESWARI
+(COMP)</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
@@ -6584,26 +6584,26 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
+          <t>PALLAVI
+(SOC)</t>
+        </is>
+      </c>
+      <c r="I6" s="7" t="inlineStr">
+        <is>
           <t>LALITHA
 (EVS)</t>
         </is>
       </c>
-      <c r="I6" s="7" t="inlineStr">
-        <is>
-          <t>SWATHI
-(TEL)</t>
-        </is>
-      </c>
       <c r="J6" s="7" t="inlineStr">
         <is>
-          <t>PALLAVI
-(SOC)</t>
+          <t>FATHIMA
+(HIN)</t>
         </is>
       </c>
       <c r="K6" s="7" t="inlineStr">
         <is>
-          <t>RAVI
-(ENG)</t>
+          <t>SANGEETHA
+(MATH)</t>
         </is>
       </c>
       <c r="L6" s="7" t="inlineStr">
@@ -6614,14 +6614,14 @@
       </c>
       <c r="M6" s="7" t="inlineStr">
         <is>
-          <t>CHALAPATHI
-(BIO)</t>
-        </is>
-      </c>
-      <c r="N6" s="7" t="inlineStr">
-        <is>
           <t>SUNITHA
 (SOC)</t>
+        </is>
+      </c>
+      <c r="N6" s="7" t="inlineStr">
+        <is>
+          <t>RIYA
+(HIN)</t>
         </is>
       </c>
     </row>
@@ -6633,49 +6633,49 @@
       <c r="C7" s="7" t="inlineStr">
         <is>
           <t>SITHA
+(EVS)</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>SAI LAKSHMI
 (ENG)</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>NAGAMANI
-(TEL)</t>
-        </is>
-      </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>BHAVANI
-(MATH)</t>
+          <t>P.E
+(P.E.T)</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>SAI LAKSHMI
-(HIN)</t>
+          <t>P.E
+(P.E.T)</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>PALLAVI
-(SOC)</t>
+          <t>P.E
+(P.E.T)</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
-        <is>
-          <t>FATHIMA
-(HIN)</t>
-        </is>
-      </c>
-      <c r="I7" s="7" t="inlineStr">
         <is>
           <t>MAHA
 (ENG)</t>
         </is>
       </c>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>P.E
+(P.E.T)</t>
+        </is>
+      </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>LALITHA
-(CHEM)</t>
+          <t>SWATHI
+(TEL)</t>
         </is>
       </c>
       <c r="K7" s="7" t="inlineStr">
@@ -6692,14 +6692,14 @@
       </c>
       <c r="M7" s="7" t="inlineStr">
         <is>
+          <t>CHALAPATHI
+(BIO)</t>
+        </is>
+      </c>
+      <c r="N7" s="7" t="inlineStr">
+        <is>
           <t>SONU
 (ENG)</t>
-        </is>
-      </c>
-      <c r="N7" s="7" t="inlineStr">
-        <is>
-          <t>CHALAPATHI
-(BIO)</t>
         </is>
       </c>
     </row>
@@ -6710,74 +6710,74 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
+          <t>SITHA
+(ENG)</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
+          <t>NAGAMANI
+(TEL)</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
+          <t>SAI LAKSHMI
+(EVS)</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
+          <t>BHAVANI
+(G.K)</t>
         </is>
       </c>
       <c r="G8" s="7" t="inlineStr">
-        <is>
-          <t>P.E
-(P.E.T)</t>
-        </is>
-      </c>
-      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>MAHA
 (ENG)</t>
         </is>
       </c>
-      <c r="I8" s="7" t="inlineStr">
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>LALITHA
 (EVS)</t>
         </is>
       </c>
-      <c r="J8" s="7" t="inlineStr">
+      <c r="I8" s="7" t="inlineStr">
         <is>
           <t>SWATHI
 (TEL)</t>
         </is>
       </c>
+      <c r="J8" s="7" t="inlineStr">
+        <is>
+          <t>PALLAVI
+(SOC)</t>
+        </is>
+      </c>
       <c r="K8" s="7" t="inlineStr">
+        <is>
+          <t>FATHIMA
+(HIN)</t>
+        </is>
+      </c>
+      <c r="L8" s="7" t="inlineStr">
+        <is>
+          <t>D.V.RAO
+(TEL)</t>
+        </is>
+      </c>
+      <c r="M8" s="7" t="inlineStr">
+        <is>
+          <t>SONU
+(ENG)</t>
+        </is>
+      </c>
+      <c r="N8" s="7" t="inlineStr">
         <is>
           <t>RAVI
 (GRAM)</t>
-        </is>
-      </c>
-      <c r="L8" s="7" t="inlineStr">
-        <is>
-          <t>CHALAPATHI
-(BIO)</t>
-        </is>
-      </c>
-      <c r="M8" s="7" t="inlineStr">
-        <is>
-          <t>RIYA
-(HIN)</t>
-        </is>
-      </c>
-      <c r="N8" s="7" t="inlineStr">
-        <is>
-          <t>SONU
-(ENG)</t>
         </is>
       </c>
     </row>
@@ -6877,19 +6877,19 @@
       <c r="D10" s="7" t="inlineStr">
         <is>
           <t>BHAVANI
-(MATH)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
           <t>NAGAMANI
-(G.K)</t>
+(TEL)</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
           <t>SAI LAKSHMI
-(HIN)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="G10" s="7" t="inlineStr">
@@ -6925,7 +6925,7 @@
       <c r="L10" s="7" t="inlineStr">
         <is>
           <t>FATHIMA
-(G.K)</t>
+(HIN)</t>
         </is>
       </c>
       <c r="M10" s="7" t="inlineStr">
@@ -6936,8 +6936,8 @@
       </c>
       <c r="N10" s="7" t="inlineStr">
         <is>
-          <t>GOWTHAM
-(MATH)</t>
+          <t>SUNITHA
+(SOC)</t>
         </is>
       </c>
     </row>
@@ -6949,67 +6949,67 @@
       <c r="C11" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(ORAL)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>SAI LAKSHMI
-(ENG)</t>
+          <t>BHAVANI
+(EVS)</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>BHAVANI
+          <t>MARTIAL ARTS
+(KAR)</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>NAGAMANI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>TULASI
 (MATH)</t>
         </is>
       </c>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>MAHA
-(ENG)</t>
-        </is>
-      </c>
-      <c r="G11" s="7" t="inlineStr">
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>LALITHA
+(EVS)</t>
+        </is>
+      </c>
+      <c r="I11" s="7" t="inlineStr">
         <is>
           <t>PALLAVI
 (SOC)</t>
         </is>
       </c>
-      <c r="H11" s="7" t="inlineStr">
-        <is>
-          <t>SWATHI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="I11" s="7" t="inlineStr">
-        <is>
-          <t>TULASI
-(MATH)</t>
-        </is>
-      </c>
       <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>RAVI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="K11" s="7" t="inlineStr">
         <is>
           <t>SANGEETHA
 (MATH)</t>
         </is>
       </c>
-      <c r="K11" s="7" t="inlineStr">
-        <is>
-          <t>MARTIAL ARTS
-(KAR)</t>
-        </is>
-      </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
-          <t>SUNITHA
-(SOC)</t>
+          <t>BHEEMA
+(CHEM)</t>
         </is>
       </c>
       <c r="M11" s="7" t="inlineStr">
         <is>
-          <t>BHEEMA
-(PHY)</t>
+          <t>GOWTHAM
+(MATH)</t>
         </is>
       </c>
       <c r="N11" s="7" t="inlineStr">
@@ -7027,7 +7027,7 @@
       <c r="C12" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(EVS)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
@@ -7044,56 +7044,56 @@
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>BHAVANI
-(G.K)</t>
+          <t>MAHA
+(GRAM)</t>
         </is>
       </c>
       <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>PALLAVI
+(SOC)</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>TULASI
 (MATH)</t>
         </is>
       </c>
-      <c r="H12" s="7" t="inlineStr">
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>SWATHI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="J12" s="7" t="inlineStr">
+        <is>
+          <t>LALITHA
+(PHY)</t>
+        </is>
+      </c>
+      <c r="K12" s="7" t="inlineStr">
         <is>
           <t>FATHIMA
 (HIN)</t>
         </is>
       </c>
-      <c r="I12" s="7" t="inlineStr">
-        <is>
-          <t>SWATHI
+      <c r="L12" s="7" t="inlineStr">
+        <is>
+          <t>D.V.RAO
 (TEL)</t>
         </is>
       </c>
-      <c r="J12" s="7" t="inlineStr">
-        <is>
-          <t>RAVI
-(GRAM)</t>
-        </is>
-      </c>
-      <c r="K12" s="7" t="inlineStr">
-        <is>
-          <t>LALITHA
+      <c r="M12" s="7" t="inlineStr">
+        <is>
+          <t>BHEEMA
 (CHEM)</t>
         </is>
       </c>
-      <c r="L12" s="7" t="inlineStr">
-        <is>
-          <t>SANGEETHA
-(MATH)</t>
-        </is>
-      </c>
-      <c r="M12" s="7" t="inlineStr">
+      <c r="N12" s="7" t="inlineStr">
         <is>
           <t>GOWTHAM
 (MATH)</t>
-        </is>
-      </c>
-      <c r="N12" s="7" t="inlineStr">
-        <is>
-          <t>BHEEMA
-(CHEM)</t>
         </is>
       </c>
     </row>
@@ -7105,7 +7105,7 @@
       <c r="C13" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(EVS)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
@@ -7116,61 +7116,60 @@
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
+          <t>BHAVANI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>MAHESWARI
+(COMP)</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
           <t>MAHA
 (ENG)</t>
         </is>
       </c>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t>NAGAMANI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="G13" s="7" t="inlineStr">
-        <is>
-          <t>RIYA
-(HIN)</t>
-        </is>
-      </c>
       <c r="H13" s="7" t="inlineStr">
-        <is>
-          <t>PALLAVI
-(SOC)</t>
-        </is>
-      </c>
-      <c r="I13" s="7" t="inlineStr">
-        <is>
-          <t>LALITHA
-(EVS)</t>
-        </is>
-      </c>
-      <c r="J13" s="7" t="inlineStr">
-        <is>
-          <t>RAVI
-(ENG)</t>
-        </is>
-      </c>
-      <c r="K13" s="7" t="inlineStr">
         <is>
           <t>FATHIMA
 (HIN)</t>
         </is>
       </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>SANGEETHA
+(G.K)</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>SWATHI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="K13" s="7" t="inlineStr">
+        <is>
+          <t>LALITHA
+(CHEM)</t>
+        </is>
+      </c>
       <c r="L13" s="7" t="inlineStr">
-        <is>
-          <t>D.V.RAO
-(TEL)</t>
-        </is>
-      </c>
-      <c r="M13" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
-        </is>
-      </c>
-      <c r="N13" s="7" t="inlineStr">
         <is>
           <t>SUNITHA
 (SOC)</t>
+        </is>
+      </c>
+      <c r="M13" s="12" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+      <c r="N13" s="12" t="inlineStr">
+        <is>
+          <t>Recreation</t>
         </is>
       </c>
     </row>
@@ -7187,56 +7186,56 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>BHAVANI
-(MATH)</t>
+          <t>SWATHI
+(HIN)</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>NAGAMANI
-(TEL)</t>
+          <t>SAI LAKSHMI
+(HIN)</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
-        <is>
-          <t>SAI LAKSHMI
-(EVS)</t>
-        </is>
-      </c>
-      <c r="G14" s="7" t="inlineStr">
         <is>
           <t>MAHA
 (ENG)</t>
         </is>
       </c>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>RIYA
+(HIN)</t>
+        </is>
+      </c>
       <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>PALLAVI
+(SOC)</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="inlineStr">
         <is>
           <t>LALITHA
 (EVS)</t>
         </is>
       </c>
-      <c r="I14" s="7" t="inlineStr">
+      <c r="J14" s="7" t="inlineStr">
         <is>
           <t>FATHIMA
 (HIN)</t>
         </is>
       </c>
-      <c r="J14" s="7" t="inlineStr">
-        <is>
-          <t>PALLAVI
-(SOC)</t>
-        </is>
-      </c>
       <c r="K14" s="7" t="inlineStr">
         <is>
-          <t>RAVI
-(ENG)</t>
+          <t>D.V.RAO
+(TEL)</t>
         </is>
       </c>
       <c r="L14" s="7" t="inlineStr">
         <is>
-          <t>CHALAPATHI
-(BIO)</t>
+          <t>SANGEETHA
+(COMP)</t>
         </is>
       </c>
       <c r="M14" s="7" t="inlineStr">
@@ -7265,50 +7264,50 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
+          <t>SAI LAKSHMI
+(ENG)</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
+          <t>BHAVANI
+(MATH)</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
-        <is>
-          <t>P.E
-(P.E.T)</t>
-        </is>
-      </c>
-      <c r="G15" s="7" t="inlineStr">
         <is>
           <t>TULASI
 (MATH)</t>
         </is>
       </c>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>MARTIAL ARTS
+(KAR)</t>
+        </is>
+      </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
+          <t>MAHA
+(ENG)</t>
         </is>
       </c>
       <c r="I15" s="7" t="inlineStr">
         <is>
-          <t>PALLAVI
-(SOC)</t>
+          <t>MAHESWARI
+(COMP)</t>
         </is>
       </c>
       <c r="J15" s="7" t="inlineStr">
         <is>
-          <t>SWATHI
-(TEL)</t>
+          <t>LALITHA
+(CHEM)</t>
         </is>
       </c>
       <c r="K15" s="7" t="inlineStr">
         <is>
-          <t>SANGEETHA
-(MATH)</t>
+          <t>RAVI
+(ENG)</t>
         </is>
       </c>
       <c r="L15" s="7" t="inlineStr">
@@ -7325,8 +7324,8 @@
       </c>
       <c r="N15" s="7" t="inlineStr">
         <is>
-          <t>D.V.RAO
-(TEL)</t>
+          <t>CHALAPATHI
+(BIO)</t>
         </is>
       </c>
     </row>
@@ -7343,20 +7342,20 @@
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>SWATHI
-(HIN)</t>
+          <t>SAI LAKSHMI
+(ENG)</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>SAI LAKSHMI
-(HIN)</t>
+          <t>MAHA
+(ENG)</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>MAHESWARI
-(COMP)</t>
+          <t>BHAVANI
+(G.K)</t>
         </is>
       </c>
       <c r="G16" s="7" t="inlineStr">
@@ -7367,8 +7366,8 @@
       </c>
       <c r="H16" s="7" t="inlineStr">
         <is>
-          <t>MAHA
-(ENG)</t>
+          <t>SWATHI
+(TEL)</t>
         </is>
       </c>
       <c r="I16" s="7" t="inlineStr">
@@ -7379,32 +7378,32 @@
       </c>
       <c r="J16" s="7" t="inlineStr">
         <is>
-          <t>FATHIMA
-(HIN)</t>
+          <t>PALLAVI
+(SOC)</t>
         </is>
       </c>
       <c r="K16" s="7" t="inlineStr">
+        <is>
+          <t>SANGEETHA
+(MATH)</t>
+        </is>
+      </c>
+      <c r="L16" s="7" t="inlineStr">
+        <is>
+          <t>CHALAPATHI
+(BIO)</t>
+        </is>
+      </c>
+      <c r="M16" s="7" t="inlineStr">
+        <is>
+          <t>SONU
+(ENG)</t>
+        </is>
+      </c>
+      <c r="N16" s="7" t="inlineStr">
         <is>
           <t>D.V.RAO
 (TEL)</t>
-        </is>
-      </c>
-      <c r="L16" s="7" t="inlineStr">
-        <is>
-          <t>MARTIAL ARTS
-(KAR)</t>
-        </is>
-      </c>
-      <c r="M16" s="7" t="inlineStr">
-        <is>
-          <t>SONU
-(ENG)</t>
-        </is>
-      </c>
-      <c r="N16" s="7" t="inlineStr">
-        <is>
-          <t>CHALAPATHI
-(BIO)</t>
         </is>
       </c>
     </row>
@@ -7498,13 +7497,13 @@
       <c r="C18" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(ENG)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
           <t>BHAVANI
-(EVS)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
@@ -7576,19 +7575,19 @@
       <c r="C19" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(MATH)</t>
+(ORAL)</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
+          <t>SWATHI
+(HIN)</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
           <t>SAI LAKSHMI
-(ENG)</t>
-        </is>
-      </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>BHAVANI
-(MATH)</t>
+(HIN)</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
@@ -7599,50 +7598,50 @@
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>RIYA
-(HIN)</t>
+          <t>MAHA
+(ENG)</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>FATHIMA
-(HIN)</t>
+          <t>MAHESWARI
+(COMP)</t>
         </is>
       </c>
       <c r="I19" s="7" t="inlineStr">
         <is>
-          <t>SWATHI
-(TEL)</t>
+          <t>TULASI
+(MATH)</t>
         </is>
       </c>
       <c r="J19" s="7" t="inlineStr">
+        <is>
+          <t>LALITHA
+(PHY)</t>
+        </is>
+      </c>
+      <c r="K19" s="7" t="inlineStr">
         <is>
           <t>RAVI
 (ENG)</t>
         </is>
       </c>
-      <c r="K19" s="7" t="inlineStr">
-        <is>
-          <t>LALITHA
-(PHY)</t>
-        </is>
-      </c>
       <c r="L19" s="7" t="inlineStr">
+        <is>
+          <t>D.V.RAO
+(TEL)</t>
+        </is>
+      </c>
+      <c r="M19" s="7" t="inlineStr">
         <is>
           <t>BHEEMA
 (PHY)</t>
         </is>
       </c>
-      <c r="M19" s="7" t="inlineStr">
+      <c r="N19" s="7" t="inlineStr">
         <is>
           <t>GOWTHAM
 (MATH)</t>
-        </is>
-      </c>
-      <c r="N19" s="7" t="inlineStr">
-        <is>
-          <t>SUNITHA
-(SOC)</t>
         </is>
       </c>
     </row>
@@ -7660,21 +7659,21 @@
       <c r="D20" s="7" t="inlineStr">
         <is>
           <t>BHAVANI
-(MATH)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>MAHA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
         <is>
           <t>SAI LAKSHMI
 (HIN)</t>
         </is>
       </c>
-      <c r="F20" s="7" t="inlineStr">
-        <is>
-          <t>MAHA
-(ENG)</t>
-        </is>
-      </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
           <t>LALITHA
@@ -7707,20 +7706,19 @@
       </c>
       <c r="L20" s="7" t="inlineStr">
         <is>
-          <t>D.V.RAO
-(TEL)</t>
-        </is>
-      </c>
-      <c r="M20" s="7" t="inlineStr">
-        <is>
           <t>BHEEMA
 (PHY)</t>
         </is>
       </c>
-      <c r="N20" s="7" t="inlineStr">
+      <c r="M20" s="7" t="inlineStr">
         <is>
           <t>GOWTHAM
 (MATH)</t>
+        </is>
+      </c>
+      <c r="N20" s="12" t="inlineStr">
+        <is>
+          <t>Recreation</t>
         </is>
       </c>
     </row>
@@ -7732,7 +7730,7 @@
       <c r="C21" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(ENG)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
@@ -7743,8 +7741,8 @@
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>SAI LAKSHMI
-(EVS)</t>
+          <t>BHAVANI
+(MATH)</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
@@ -7755,22 +7753,22 @@
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>MAHA
-(ENG)</t>
+          <t>RIYA
+(HIN)</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
-        <is>
-          <t>MARTIAL ARTS
-(KAR)</t>
-        </is>
-      </c>
-      <c r="I21" s="7" t="inlineStr">
         <is>
           <t>LALITHA
 (EVS)</t>
         </is>
       </c>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>FATHIMA
+(HIN)</t>
+        </is>
+      </c>
       <c r="J21" s="7" t="inlineStr">
         <is>
           <t>PALLAVI
@@ -7779,25 +7777,26 @@
       </c>
       <c r="K21" s="7" t="inlineStr">
         <is>
+          <t>D.V.RAO
+(TEL)</t>
+        </is>
+      </c>
+      <c r="L21" s="7" t="inlineStr">
+        <is>
           <t>SANGEETHA
 (MATH)</t>
         </is>
       </c>
-      <c r="L21" s="7" t="inlineStr">
+      <c r="M21" s="7" t="inlineStr">
+        <is>
+          <t>RAVI
+(GRAM)</t>
+        </is>
+      </c>
+      <c r="N21" s="7" t="inlineStr">
         <is>
           <t>SUNITHA
 (SOC)</t>
-        </is>
-      </c>
-      <c r="M21" s="7" t="inlineStr">
-        <is>
-          <t>MARTIAL ARTS
-(KAR)</t>
-        </is>
-      </c>
-      <c r="N21" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
         </is>
       </c>
     </row>
@@ -7809,73 +7808,73 @@
       <c r="C22" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(EVS)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>BHAVANI
-(MATH)</t>
+          <t>SAI LAKSHMI
+(ENG)</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
           <t>MAHA
-(ENG)</t>
+(GRAM)</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
-        <is>
-          <t>SAI LAKSHMI
-(EVS)</t>
-        </is>
-      </c>
-      <c r="G22" s="7" t="inlineStr">
         <is>
           <t>TULASI
 (MATH)</t>
         </is>
       </c>
-      <c r="H22" s="7" t="inlineStr">
+      <c r="G22" s="7" t="inlineStr">
         <is>
           <t>PALLAVI
 (SOC)</t>
         </is>
       </c>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>FATHIMA
+(HIN)</t>
+        </is>
+      </c>
       <c r="I22" s="7" t="inlineStr">
         <is>
+          <t>LALITHA
+(EVS)</t>
+        </is>
+      </c>
+      <c r="J22" s="7" t="inlineStr">
+        <is>
+          <t>SWATHI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="K22" s="7" t="inlineStr">
+        <is>
           <t>SANGEETHA
-(G.K)</t>
-        </is>
-      </c>
-      <c r="J22" s="7" t="inlineStr">
-        <is>
-          <t>LALITHA
-(PHY)</t>
-        </is>
-      </c>
-      <c r="K22" s="7" t="inlineStr">
-        <is>
-          <t>D.V.RAO
-(TEL)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="L22" s="7" t="inlineStr">
+        <is>
+          <t>SUNITHA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="M22" s="7" t="inlineStr">
+        <is>
+          <t>SONU
+(ENG)</t>
+        </is>
+      </c>
+      <c r="N22" s="7" t="inlineStr">
         <is>
           <t>CHALAPATHI
 (BIO)</t>
-        </is>
-      </c>
-      <c r="M22" s="7" t="inlineStr">
-        <is>
-          <t>SUNITHA
-(SOC)</t>
-        </is>
-      </c>
-      <c r="N22" s="7" t="inlineStr">
-        <is>
-          <t>SONU
-(ENG)</t>
         </is>
       </c>
     </row>
@@ -7886,50 +7885,50 @@
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>NAGAMANI
-(TEL)</t>
+          <t>P.E
+(P.E.T)</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>BHAVANI
-(MATH)</t>
+          <t>P.E
+(P.E.T)</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>SAI LAKSHMI
-(EVS)</t>
+          <t>P.E
+(P.E.T)</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
+          <t>P.E
+(P.E.T)</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>P.E
+(P.E.T)</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
           <t>MAHA
-(GRAM)</t>
-        </is>
-      </c>
-      <c r="G23" s="7" t="inlineStr">
-        <is>
-          <t>MAHESWARI
-(COMP)</t>
-        </is>
-      </c>
-      <c r="H23" s="7" t="inlineStr">
-        <is>
-          <t>LALITHA
-(EVS)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="I23" s="7" t="inlineStr">
         <is>
-          <t>TULASI
-(MATH)</t>
+          <t>P.E
+(P.E.T)</t>
         </is>
       </c>
       <c r="J23" s="7" t="inlineStr">
         <is>
-          <t>SWATHI
-(TEL)</t>
+          <t>RAVI
+(ENG)</t>
         </is>
       </c>
       <c r="K23" s="7" t="inlineStr">
@@ -7970,38 +7969,38 @@
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>SWATHI
-(HIN)</t>
+          <t>BHAVANI
+(EVS)</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
-        <is>
-          <t>NAGAMANI
-(G.K)</t>
-        </is>
-      </c>
-      <c r="F24" s="7" t="inlineStr">
         <is>
           <t>SAI LAKSHMI
 (EVS)</t>
         </is>
       </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>MAHA
+(ENG)</t>
+        </is>
+      </c>
       <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>TULASI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="H24" s="7" t="inlineStr">
         <is>
           <t>PALLAVI
 (SOC)</t>
         </is>
       </c>
-      <c r="H24" s="7" t="inlineStr">
-        <is>
-          <t>MAHA
-(ENG)</t>
-        </is>
-      </c>
       <c r="I24" s="7" t="inlineStr">
         <is>
-          <t>FATHIMA
-(HIN)</t>
+          <t>SWATHI
+(TEL)</t>
         </is>
       </c>
       <c r="J24" s="7" t="inlineStr">
@@ -8012,25 +8011,26 @@
       </c>
       <c r="K24" s="7" t="inlineStr">
         <is>
-          <t>RAVI
-(ENG)</t>
-        </is>
-      </c>
-      <c r="L24" s="7" t="inlineStr">
-        <is>
           <t>SANGEETHA
 (MATH)</t>
         </is>
       </c>
+      <c r="L24" s="7" t="inlineStr">
+        <is>
+          <t>CHALAPATHI
+(BIO)</t>
+        </is>
+      </c>
       <c r="M24" s="7" t="inlineStr">
+        <is>
+          <t>SUNITHA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="N24" s="7" t="inlineStr">
         <is>
           <t>SONU
 (ENG)</t>
-        </is>
-      </c>
-      <c r="N24" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
         </is>
       </c>
     </row>
@@ -8124,7 +8124,7 @@
       <c r="C26" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(ORAL)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
@@ -8166,7 +8166,7 @@
       <c r="J26" s="7" t="inlineStr">
         <is>
           <t>SANGEETHA
-(G.K)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="K26" s="7" t="inlineStr">
@@ -8207,68 +8207,68 @@
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
+          <t>BHAVANI
+(EVS)</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>SAI LAKSHMI
+(EVS)</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
           <t>NAGAMANI
 (TEL)</t>
         </is>
       </c>
-      <c r="E27" s="7" t="inlineStr">
-        <is>
-          <t>SAI LAKSHMI
-(EVS)</t>
-        </is>
-      </c>
-      <c r="F27" s="7" t="inlineStr">
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>RIYA
+(HIN)</t>
+        </is>
+      </c>
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>FATHIMA
+(HIN)</t>
+        </is>
+      </c>
+      <c r="I27" s="7" t="inlineStr">
         <is>
           <t>TULASI
 (MATH)</t>
         </is>
       </c>
-      <c r="G27" s="7" t="inlineStr">
-        <is>
-          <t>RIYA
-(HIN)</t>
-        </is>
-      </c>
-      <c r="H27" s="7" t="inlineStr">
-        <is>
-          <t>MAHA
+      <c r="J27" s="7" t="inlineStr">
+        <is>
+          <t>RAVI
 (ENG)</t>
         </is>
       </c>
-      <c r="I27" s="7" t="inlineStr">
-        <is>
-          <t>FATHIMA
-(HIN)</t>
-        </is>
-      </c>
-      <c r="J27" s="7" t="inlineStr">
-        <is>
-          <t>PALLAVI
-(SOC)</t>
-        </is>
-      </c>
       <c r="K27" s="7" t="inlineStr">
         <is>
           <t>LALITHA
+(BIO)</t>
+        </is>
+      </c>
+      <c r="L27" s="7" t="inlineStr">
+        <is>
+          <t>BHEEMA
 (CHEM)</t>
         </is>
       </c>
-      <c r="L27" s="7" t="inlineStr">
+      <c r="M27" s="7" t="inlineStr">
+        <is>
+          <t>GOWTHAM
+(MATH)</t>
+        </is>
+      </c>
+      <c r="N27" s="7" t="inlineStr">
         <is>
           <t>SUNITHA
 (SOC)</t>
-        </is>
-      </c>
-      <c r="M27" s="7" t="inlineStr">
-        <is>
-          <t>BHEEMA
-(CHEM)</t>
-        </is>
-      </c>
-      <c r="N27" s="7" t="inlineStr">
-        <is>
-          <t>D.V.RAO
-(TEL)</t>
         </is>
       </c>
     </row>
@@ -8280,7 +8280,7 @@
       <c r="C28" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(ENG)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
@@ -8291,62 +8291,62 @@
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>BHAVANI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="F28" s="7" t="inlineStr">
-        <is>
           <t>MAHESWARI
 (COMP)</t>
         </is>
       </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>MARTIAL ARTS
+(KAR)</t>
+        </is>
+      </c>
       <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>MAHA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="H28" s="7" t="inlineStr">
         <is>
           <t>PALLAVI
 (SOC)</t>
         </is>
       </c>
-      <c r="H28" s="7" t="inlineStr">
+      <c r="I28" s="7" t="inlineStr">
         <is>
           <t>SWATHI
 (TEL)</t>
         </is>
       </c>
-      <c r="I28" s="7" t="inlineStr">
+      <c r="J28" s="7" t="inlineStr">
+        <is>
+          <t>SANGEETHA
+(MATH)</t>
+        </is>
+      </c>
+      <c r="K28" s="7" t="inlineStr">
         <is>
           <t>LALITHA
-(EVS)</t>
-        </is>
-      </c>
-      <c r="J28" s="7" t="inlineStr">
-        <is>
-          <t>RAVI
-(ENG)</t>
-        </is>
-      </c>
-      <c r="K28" s="7" t="inlineStr">
-        <is>
-          <t>SANGEETHA
-(COMP)</t>
+(PHY)</t>
         </is>
       </c>
       <c r="L28" s="7" t="inlineStr">
+        <is>
+          <t>MARTIAL ARTS
+(KAR)</t>
+        </is>
+      </c>
+      <c r="M28" s="7" t="inlineStr">
+        <is>
+          <t>GOWTHAM
+(MATH)</t>
+        </is>
+      </c>
+      <c r="N28" s="7" t="inlineStr">
         <is>
           <t>BHEEMA
 (CHEM)</t>
-        </is>
-      </c>
-      <c r="M28" s="7" t="inlineStr">
-        <is>
-          <t>GOWTHAM
-(MATH)</t>
-        </is>
-      </c>
-      <c r="N28" s="7" t="inlineStr">
-        <is>
-          <t>MARTIAL ARTS
-(KAR)</t>
         </is>
       </c>
     </row>
@@ -8364,13 +8364,13 @@
       <c r="D29" s="7" t="inlineStr">
         <is>
           <t>BHAVANI
-(EVS)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>MAHESWARI
-(COMP)</t>
+          <t>SAI LAKSHMI
+(HIN)</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
@@ -8387,16 +8387,16 @@
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
-          <t>LALITHA
-(EVS)</t>
-        </is>
-      </c>
-      <c r="I29" s="7" t="inlineStr">
-        <is>
           <t>SWATHI
 (TEL)</t>
         </is>
       </c>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>PALLAVI
+(SOC)</t>
+        </is>
+      </c>
       <c r="J29" s="7" t="inlineStr">
         <is>
           <t>FATHIMA
@@ -8405,26 +8405,26 @@
       </c>
       <c r="K29" s="7" t="inlineStr">
         <is>
+          <t>RAVI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="L29" s="7" t="inlineStr">
+        <is>
           <t>SANGEETHA
 (MATH)</t>
         </is>
       </c>
-      <c r="L29" s="7" t="inlineStr">
+      <c r="M29" s="7" t="inlineStr">
+        <is>
+          <t>SUNITHA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="N29" s="7" t="inlineStr">
         <is>
           <t>D.V.RAO
 (TEL)</t>
-        </is>
-      </c>
-      <c r="M29" s="7" t="inlineStr">
-        <is>
-          <t>SUNITHA
-(SOC)</t>
-        </is>
-      </c>
-      <c r="N29" s="7" t="inlineStr">
-        <is>
-          <t>RIYA
-(HIN)</t>
         </is>
       </c>
     </row>
@@ -8436,73 +8436,73 @@
       <c r="C30" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(EVS)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>SWATHI
-(HIN)</t>
+          <t>NAGAMANI
+(TEL)</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>MAHA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
         <is>
           <t>SAI LAKSHMI
 (EVS)</t>
         </is>
       </c>
-      <c r="F30" s="7" t="inlineStr">
+      <c r="G30" s="7" t="inlineStr">
+        <is>
+          <t>PALLAVI
+(SOC)</t>
+        </is>
+      </c>
+      <c r="H30" s="7" t="inlineStr">
+        <is>
+          <t>LALITHA
+(EVS)</t>
+        </is>
+      </c>
+      <c r="I30" s="7" t="inlineStr">
         <is>
           <t>TULASI
 (MATH)</t>
         </is>
       </c>
-      <c r="G30" s="7" t="inlineStr">
-        <is>
-          <t>MAHA
-(ENG)</t>
-        </is>
-      </c>
-      <c r="H30" s="7" t="inlineStr">
+      <c r="J30" s="7" t="inlineStr">
+        <is>
+          <t>SWATHI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="K30" s="7" t="inlineStr">
         <is>
           <t>FATHIMA
 (HIN)</t>
         </is>
       </c>
-      <c r="I30" s="7" t="inlineStr">
-        <is>
-          <t>PALLAVI
-(SOC)</t>
-        </is>
-      </c>
-      <c r="J30" s="7" t="inlineStr">
-        <is>
-          <t>LALITHA
-(BIO)</t>
-        </is>
-      </c>
-      <c r="K30" s="7" t="inlineStr">
-        <is>
-          <t>RAVI
-(ENG)</t>
-        </is>
-      </c>
       <c r="L30" s="7" t="inlineStr">
-        <is>
-          <t>SANGEETHA
-(MATH)</t>
-        </is>
-      </c>
-      <c r="M30" s="7" t="inlineStr">
         <is>
           <t>SONU
 (ENG)</t>
         </is>
       </c>
+      <c r="M30" s="7" t="inlineStr">
+        <is>
+          <t>MARTIAL ARTS
+(KAR)</t>
+        </is>
+      </c>
       <c r="N30" s="7" t="inlineStr">
         <is>
-          <t>CHALAPATHI
-(BIO)</t>
+          <t>RIYA
+(HIN)</t>
         </is>
       </c>
     </row>
@@ -8549,26 +8549,26 @@
       </c>
       <c r="I31" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
+          <t>LALITHA
+(EVS)</t>
         </is>
       </c>
       <c r="J31" s="7" t="inlineStr">
         <is>
-          <t>LALITHA
-(PHY)</t>
+          <t>SANGEETHA
+(MATH)</t>
         </is>
       </c>
       <c r="K31" s="7" t="inlineStr">
+        <is>
+          <t>MARTIAL ARTS
+(KAR)</t>
+        </is>
+      </c>
+      <c r="L31" s="7" t="inlineStr">
         <is>
           <t>D.V.RAO
 (TEL)</t>
-        </is>
-      </c>
-      <c r="L31" s="7" t="inlineStr">
-        <is>
-          <t>SANGEETHA
-(COMP)</t>
         </is>
       </c>
       <c r="M31" s="7" t="inlineStr">
@@ -8592,7 +8592,7 @@
       <c r="C32" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(MATH)</t>
+(ORAL)</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
@@ -8603,62 +8603,62 @@
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
+          <t>BHAVANI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>TULASI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="G32" s="7" t="inlineStr">
+        <is>
+          <t>LALITHA
+(EVS)</t>
+        </is>
+      </c>
+      <c r="H32" s="7" t="inlineStr">
+        <is>
           <t>MAHA
 (ENG)</t>
         </is>
       </c>
-      <c r="F32" s="7" t="inlineStr">
-        <is>
-          <t>NAGAMANI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="G32" s="7" t="inlineStr">
-        <is>
-          <t>LALITHA
-(EVS)</t>
-        </is>
-      </c>
-      <c r="H32" s="7" t="inlineStr">
+      <c r="I32" s="7" t="inlineStr">
+        <is>
+          <t>FATHIMA
+(HIN)</t>
+        </is>
+      </c>
+      <c r="J32" s="7" t="inlineStr">
         <is>
           <t>PALLAVI
 (SOC)</t>
         </is>
       </c>
-      <c r="I32" s="7" t="inlineStr">
-        <is>
-          <t>TULASI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="J32" s="7" t="inlineStr">
-        <is>
-          <t>SWATHI
+      <c r="K32" s="7" t="inlineStr">
+        <is>
+          <t>D.V.RAO
 (TEL)</t>
         </is>
       </c>
-      <c r="K32" s="7" t="inlineStr">
-        <is>
-          <t>FATHIMA
-(HIN)</t>
-        </is>
-      </c>
       <c r="L32" s="7" t="inlineStr">
+        <is>
+          <t>SUNITHA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="M32" s="7" t="inlineStr">
         <is>
           <t>SONU
 (ENG)</t>
         </is>
       </c>
-      <c r="M32" s="7" t="inlineStr">
+      <c r="N32" s="7" t="inlineStr">
         <is>
           <t>CHALAPATHI
 (BIO)</t>
-        </is>
-      </c>
-      <c r="N32" s="7" t="inlineStr">
-        <is>
-          <t>SUNITHA
-(SOC)</t>
         </is>
       </c>
     </row>
@@ -8758,7 +8758,7 @@
       <c r="D34" s="7" t="inlineStr">
         <is>
           <t>BHAVANI
-(EVS)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
@@ -8794,7 +8794,7 @@
       <c r="J34" s="7" t="inlineStr">
         <is>
           <t>SANGEETHA
-(MATH)</t>
+(G.K)</t>
         </is>
       </c>
       <c r="K34" s="7" t="inlineStr">
@@ -8818,7 +8818,7 @@
       <c r="N34" s="7" t="inlineStr">
         <is>
           <t>BHEEMA
-(PHY)</t>
+(CHEM)</t>
         </is>
       </c>
     </row>
@@ -8829,26 +8829,26 @@
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>SITHA
-(EVS)</t>
+          <t>NAGAMANI
+(TEL)</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
-        <is>
-          <t>SAI LAKSHMI
-(ENG)</t>
-        </is>
-      </c>
-      <c r="E35" s="7" t="inlineStr">
         <is>
           <t>BHAVANI
 (MATH)</t>
         </is>
       </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>MAHA
+(ENG)</t>
+        </is>
+      </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>TULASI
-(MATH)</t>
+          <t>SAI LAKSHMI
+(EVS)</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
@@ -8865,38 +8865,38 @@
       </c>
       <c r="I35" s="7" t="inlineStr">
         <is>
-          <t>LALITHA
-(EVS)</t>
-        </is>
-      </c>
-      <c r="J35" s="7" t="inlineStr">
-        <is>
           <t>PALLAVI
 (SOC)</t>
         </is>
       </c>
+      <c r="J35" s="7" t="inlineStr">
+        <is>
+          <t>LALITHA
+(BIO)</t>
+        </is>
+      </c>
       <c r="K35" s="7" t="inlineStr">
         <is>
-          <t>FATHIMA
-(HIN)</t>
+          <t>D.V.RAO
+(TEL)</t>
         </is>
       </c>
       <c r="L35" s="7" t="inlineStr">
         <is>
-          <t>BHEEMA
-(CHEM)</t>
+          <t>SANGEETHA
+(MATH)</t>
         </is>
       </c>
       <c r="M35" s="7" t="inlineStr">
+        <is>
+          <t>SUNITHA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="N35" s="7" t="inlineStr">
         <is>
           <t>GOWTHAM
 (MATH)</t>
-        </is>
-      </c>
-      <c r="N35" s="7" t="inlineStr">
-        <is>
-          <t>D.V.RAO
-(TEL)</t>
         </is>
       </c>
     </row>
@@ -8913,22 +8913,22 @@
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>NAGAMANI
-(TEL)</t>
+          <t>SWATHI
+(HIN)</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>MAHESWARI
+(COMP)</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
         <is>
           <t>SAI LAKSHMI
 (HIN)</t>
         </is>
       </c>
-      <c r="F36" s="7" t="inlineStr">
-        <is>
-          <t>MAHA
-(ENG)</t>
-        </is>
-      </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
           <t>LALITHA
@@ -8943,38 +8943,38 @@
       </c>
       <c r="I36" s="7" t="inlineStr">
         <is>
+          <t>TULASI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="J36" s="7" t="inlineStr">
+        <is>
+          <t>RAVI
+(GRAM)</t>
+        </is>
+      </c>
+      <c r="K36" s="7" t="inlineStr">
+        <is>
           <t>FATHIMA
-(HIN)</t>
-        </is>
-      </c>
-      <c r="J36" s="7" t="inlineStr">
-        <is>
-          <t>MAHESWARI
-(COMP)</t>
-        </is>
-      </c>
-      <c r="K36" s="7" t="inlineStr">
+(G.K)</t>
+        </is>
+      </c>
+      <c r="L36" s="7" t="inlineStr">
         <is>
           <t>D.V.RAO
 (TEL)</t>
         </is>
       </c>
-      <c r="L36" s="7" t="inlineStr">
+      <c r="M36" s="7" t="inlineStr">
         <is>
           <t>BHEEMA
-(PHY)</t>
-        </is>
-      </c>
-      <c r="M36" s="7" t="inlineStr">
-        <is>
-          <t>RAVI
-(GRAM)</t>
+(CHEM)</t>
         </is>
       </c>
       <c r="N36" s="7" t="inlineStr">
         <is>
-          <t>GOWTHAM
-(MATH)</t>
+          <t>MARTIAL ARTS
+(KAR)</t>
         </is>
       </c>
     </row>
@@ -8985,34 +8985,34 @@
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
+          <t>SITHA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
           <t>NAGAMANI
 (TEL)</t>
         </is>
       </c>
-      <c r="D37" s="7" t="inlineStr">
+      <c r="E37" s="7" t="inlineStr">
         <is>
           <t>BHAVANI
-(EVS)</t>
-        </is>
-      </c>
-      <c r="E37" s="7" t="inlineStr">
-        <is>
-          <t>MAHESWARI
-(COMP)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="F37" s="7" t="inlineStr">
-        <is>
-          <t>SAI LAKSHMI
-(HIN)</t>
-        </is>
-      </c>
-      <c r="G37" s="7" t="inlineStr">
         <is>
           <t>TULASI
 (MATH)</t>
         </is>
       </c>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>PALLAVI
+(SOC)</t>
+        </is>
+      </c>
       <c r="H37" s="7" t="inlineStr">
         <is>
           <t>MAHA
@@ -9021,38 +9021,37 @@
       </c>
       <c r="I37" s="7" t="inlineStr">
         <is>
-          <t>PALLAVI
-(SOC)</t>
+          <t>LALITHA
+(EVS)</t>
         </is>
       </c>
       <c r="J37" s="7" t="inlineStr">
-        <is>
-          <t>SWATHI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="K37" s="7" t="inlineStr">
         <is>
           <t>RAVI
 (ENG)</t>
         </is>
       </c>
+      <c r="K37" s="7" t="inlineStr">
+        <is>
+          <t>FATHIMA
+(HIN)</t>
+        </is>
+      </c>
       <c r="L37" s="7" t="inlineStr">
         <is>
-          <t>SANGEETHA
-(MATH)</t>
-        </is>
-      </c>
-      <c r="M37" s="7" t="inlineStr">
+          <t>SUNITHA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="M37" s="12" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+      <c r="N37" s="7" t="inlineStr">
         <is>
           <t>RIYA
 (HIN)</t>
-        </is>
-      </c>
-      <c r="N37" s="7" t="inlineStr">
-        <is>
-          <t>SUNITHA
-(SOC)</t>
         </is>
       </c>
     </row>
@@ -9064,73 +9063,73 @@
       <c r="C38" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(ENG)</t>
+(ORAL)</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
-        <is>
-          <t>SAI LAKSHMI
-(ENG)</t>
-        </is>
-      </c>
-      <c r="E38" s="7" t="inlineStr">
         <is>
           <t>BHAVANI
 (MATH)</t>
         </is>
       </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>SAI LAKSHMI
+(EVS)</t>
+        </is>
+      </c>
       <c r="F38" s="7" t="inlineStr">
+        <is>
+          <t>NAGAMANI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="G38" s="7" t="inlineStr">
+        <is>
+          <t>MAHA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="H38" s="7" t="inlineStr">
+        <is>
+          <t>LALITHA
+(EVS)</t>
+        </is>
+      </c>
+      <c r="I38" s="7" t="inlineStr">
         <is>
           <t>TULASI
 (MATH)</t>
         </is>
       </c>
-      <c r="G38" s="7" t="inlineStr">
-        <is>
-          <t>MAHA
-(ENG)</t>
-        </is>
-      </c>
-      <c r="H38" s="7" t="inlineStr">
-        <is>
-          <t>PALLAVI
-(SOC)</t>
-        </is>
-      </c>
-      <c r="I38" s="7" t="inlineStr">
+      <c r="J38" s="7" t="inlineStr">
         <is>
           <t>SWATHI
 (TEL)</t>
         </is>
       </c>
-      <c r="J38" s="7" t="inlineStr">
-        <is>
-          <t>FATHIMA
-(HIN)</t>
-        </is>
-      </c>
       <c r="K38" s="7" t="inlineStr">
         <is>
-          <t>LALITHA
+          <t>RAVI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="L38" s="7" t="inlineStr">
+        <is>
+          <t>SONU
+(ENG)</t>
+        </is>
+      </c>
+      <c r="M38" s="7" t="inlineStr">
+        <is>
+          <t>CHALAPATHI
 (BIO)</t>
         </is>
       </c>
-      <c r="L38" s="7" t="inlineStr">
+      <c r="N38" s="7" t="inlineStr">
         <is>
           <t>D.V.RAO
 (TEL)</t>
-        </is>
-      </c>
-      <c r="M38" s="7" t="inlineStr">
-        <is>
-          <t>SUNITHA
-(SOC)</t>
-        </is>
-      </c>
-      <c r="N38" s="7" t="inlineStr">
-        <is>
-          <t>SONU
-(ENG)</t>
         </is>
       </c>
     </row>
@@ -9141,73 +9140,74 @@
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
+          <t>SITHA
+(EVS)</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>SAI LAKSHMI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>BHAVANI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>MAHA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t>TULASI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="H39" s="7" t="inlineStr">
+        <is>
+          <t>PALLAVI
+(SOC)</t>
+        </is>
+      </c>
+      <c r="I39" s="7" t="inlineStr">
+        <is>
+          <t>FATHIMA
+(HIN)</t>
+        </is>
+      </c>
+      <c r="J39" s="7" t="inlineStr">
+        <is>
           <t>P.E
 (P.E.T)</t>
         </is>
       </c>
-      <c r="D39" s="7" t="inlineStr">
-        <is>
-          <t>SAI LAKSHMI
-(ENG)</t>
-        </is>
-      </c>
-      <c r="E39" s="7" t="inlineStr">
+      <c r="K39" s="7" t="inlineStr">
         <is>
           <t>P.E
 (P.E.T)</t>
         </is>
       </c>
-      <c r="F39" s="7" t="inlineStr">
+      <c r="L39" s="7" t="inlineStr">
         <is>
           <t>P.E
 (P.E.T)</t>
         </is>
       </c>
-      <c r="G39" s="7" t="inlineStr">
+      <c r="M39" s="7" t="inlineStr">
         <is>
           <t>P.E
 (P.E.T)</t>
         </is>
       </c>
-      <c r="H39" s="7" t="inlineStr">
-        <is>
-          <t>MAHA
-(GRAM)</t>
-        </is>
-      </c>
-      <c r="I39" s="7" t="inlineStr">
+      <c r="N39" s="7" t="inlineStr">
         <is>
           <t>P.E
 (P.E.T)</t>
-        </is>
-      </c>
-      <c r="J39" s="7" t="inlineStr">
-        <is>
-          <t>LALITHA
-(BIO)</t>
-        </is>
-      </c>
-      <c r="K39" s="7" t="inlineStr">
-        <is>
-          <t>SANGEETHA
-(MATH)</t>
-        </is>
-      </c>
-      <c r="L39" s="7" t="inlineStr">
-        <is>
-          <t>SONU
-(ENG)</t>
-        </is>
-      </c>
-      <c r="M39" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
-        </is>
-      </c>
-      <c r="N39" s="7" t="inlineStr">
-        <is>
-          <t>RIYA
-(HIN)</t>
         </is>
       </c>
     </row>
@@ -9218,74 +9218,74 @@
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>SITHA
-(MATH)</t>
+          <t>P.E
+(P.E.T)</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>BHAVANI
-(EVS)</t>
+          <t>P.E
+(P.E.T)</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>MAHA
-(ENG)</t>
+          <t>P.E
+(P.E.T)</t>
         </is>
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
-          <t>NAGAMANI
+          <t>P.E
+(P.E.T)</t>
+        </is>
+      </c>
+      <c r="G40" s="7" t="inlineStr">
+        <is>
+          <t>SAI LAKSHMI
+(G.K)</t>
+        </is>
+      </c>
+      <c r="H40" s="7" t="inlineStr">
+        <is>
+          <t>P.E
+(P.E.T)</t>
+        </is>
+      </c>
+      <c r="I40" s="7" t="inlineStr">
+        <is>
+          <t>SWATHI
 (TEL)</t>
         </is>
       </c>
-      <c r="G40" s="7" t="inlineStr">
+      <c r="J40" s="7" t="inlineStr">
         <is>
           <t>PALLAVI
 (SOC)</t>
         </is>
       </c>
-      <c r="H40" s="7" t="inlineStr">
+      <c r="K40" s="7" t="inlineStr">
         <is>
           <t>LALITHA
-(EVS)</t>
-        </is>
-      </c>
-      <c r="I40" s="7" t="inlineStr">
-        <is>
-          <t>TULASI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="J40" s="7" t="inlineStr">
-        <is>
-          <t>RAVI
-(ENG)</t>
-        </is>
-      </c>
-      <c r="K40" s="7" t="inlineStr">
+(CHEM)</t>
+        </is>
+      </c>
+      <c r="L40" s="7" t="inlineStr">
         <is>
           <t>SANGEETHA
 (MATH)</t>
         </is>
       </c>
-      <c r="L40" s="7" t="inlineStr">
+      <c r="M40" s="7" t="inlineStr">
+        <is>
+          <t>SONU
+(ENG)</t>
+        </is>
+      </c>
+      <c r="N40" s="7" t="inlineStr">
         <is>
           <t>SUNITHA
 (SOC)</t>
-        </is>
-      </c>
-      <c r="M40" s="7" t="inlineStr">
-        <is>
-          <t>SONU
-(ENG)</t>
-        </is>
-      </c>
-      <c r="N40" s="7" t="inlineStr">
-        <is>
-          <t>CHALAPATHI
-(BIO)</t>
         </is>
       </c>
     </row>
@@ -9361,9 +9361,10 @@
 (CLASS)</t>
         </is>
       </c>
-      <c r="N41" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
+      <c r="N41" s="8" t="inlineStr">
+        <is>
+          <t>SONU
+(ENG)</t>
         </is>
       </c>
     </row>
@@ -9385,7 +9386,7 @@
       <c r="D42" s="7" t="inlineStr">
         <is>
           <t>BHAVANI
-(EVS)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
@@ -9397,7 +9398,7 @@
       <c r="F42" s="7" t="inlineStr">
         <is>
           <t>SAI LAKSHMI
-(EVS)</t>
+(HIN)</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
@@ -9433,7 +9434,7 @@
       <c r="L42" s="7" t="inlineStr">
         <is>
           <t>FATHIMA
-(HIN)</t>
+(G.K)</t>
         </is>
       </c>
       <c r="M42" s="7" t="inlineStr">
@@ -9457,73 +9458,73 @@
       <c r="C43" s="7" t="inlineStr">
         <is>
           <t>SITHA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>BHAVANI
 (MATH)</t>
         </is>
       </c>
-      <c r="D43" s="7" t="inlineStr">
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>SAI LAKSHMI
+(HIN)</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
         <is>
           <t>NAGAMANI
 (TEL)</t>
         </is>
       </c>
-      <c r="E43" s="7" t="inlineStr">
-        <is>
-          <t>MARTIAL ARTS
-(KAR)</t>
-        </is>
-      </c>
-      <c r="F43" s="7" t="inlineStr">
-        <is>
-          <t>SAI LAKSHMI
+      <c r="G43" s="7" t="inlineStr">
+        <is>
+          <t>LALITHA
+(EVS)</t>
+        </is>
+      </c>
+      <c r="H43" s="7" t="inlineStr">
+        <is>
+          <t>FATHIMA
 (HIN)</t>
         </is>
       </c>
-      <c r="G43" s="7" t="inlineStr">
+      <c r="I43" s="7" t="inlineStr">
+        <is>
+          <t>SWATHI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="J43" s="7" t="inlineStr">
+        <is>
+          <t>RAVI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="K43" s="7" t="inlineStr">
+        <is>
+          <t>SANGEETHA
+(MATH)</t>
+        </is>
+      </c>
+      <c r="L43" s="7" t="inlineStr">
+        <is>
+          <t>D.V.RAO
+(TEL)</t>
+        </is>
+      </c>
+      <c r="M43" s="7" t="inlineStr">
+        <is>
+          <t>GOWTHAM
+(MATH)</t>
+        </is>
+      </c>
+      <c r="N43" s="7" t="inlineStr">
         <is>
           <t>RIYA
 (HIN)</t>
-        </is>
-      </c>
-      <c r="H43" s="7" t="inlineStr">
-        <is>
-          <t>SWATHI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="I43" s="7" t="inlineStr">
-        <is>
-          <t>PALLAVI
-(SOC)</t>
-        </is>
-      </c>
-      <c r="J43" s="7" t="inlineStr">
-        <is>
-          <t>LALITHA
-(CHEM)</t>
-        </is>
-      </c>
-      <c r="K43" s="7" t="inlineStr">
-        <is>
-          <t>D.V.RAO
-(TEL)</t>
-        </is>
-      </c>
-      <c r="L43" s="7" t="inlineStr">
-        <is>
-          <t>SANGEETHA
-(MATH)</t>
-        </is>
-      </c>
-      <c r="M43" s="7" t="inlineStr">
-        <is>
-          <t>GOWTHAM
-(MATH)</t>
-        </is>
-      </c>
-      <c r="N43" s="7" t="inlineStr">
-        <is>
-          <t>SUNITHA
-(SOC)</t>
         </is>
       </c>
     </row>
@@ -9535,61 +9536,61 @@
       <c r="C44" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(EVS)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>SAI LAKSHMI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
         <is>
           <t>BHAVANI
 (MATH)</t>
         </is>
       </c>
-      <c r="E44" s="7" t="inlineStr">
-        <is>
-          <t>SAI LAKSHMI
-(HIN)</t>
-        </is>
-      </c>
       <c r="F44" s="7" t="inlineStr">
-        <is>
-          <t>NAGAMANI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="G44" s="7" t="inlineStr">
         <is>
           <t>TULASI
 (MATH)</t>
         </is>
       </c>
+      <c r="G44" s="7" t="inlineStr">
+        <is>
+          <t>PALLAVI
+(SOC)</t>
+        </is>
+      </c>
       <c r="H44" s="7" t="inlineStr">
         <is>
           <t>MAHA
-(ENG)</t>
+(GRAM)</t>
         </is>
       </c>
       <c r="I44" s="7" t="inlineStr">
         <is>
-          <t>SWATHI
-(TEL)</t>
+          <t>LALITHA
+(EVS)</t>
         </is>
       </c>
       <c r="J44" s="7" t="inlineStr">
         <is>
-          <t>FATHIMA
-(HIN)</t>
+          <t>MARTIAL ARTS
+(KAR)</t>
         </is>
       </c>
       <c r="K44" s="7" t="inlineStr">
         <is>
-          <t>LALITHA
-(BIO)</t>
+          <t>SANGEETHA
+(COMP)</t>
         </is>
       </c>
       <c r="L44" s="7" t="inlineStr">
         <is>
-          <t>SANGEETHA
-(MATH)</t>
+          <t>RAVI
+(GRAM)</t>
         </is>
       </c>
       <c r="M44" s="7" t="inlineStr">
@@ -9600,8 +9601,8 @@
       </c>
       <c r="N44" s="7" t="inlineStr">
         <is>
-          <t>BHEEMA
-(CHEM)</t>
+          <t>D.V.RAO
+(TEL)</t>
         </is>
       </c>
     </row>
@@ -9612,20 +9613,20 @@
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>SITHA
+          <t>NAGAMANI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>SWATHI
+(HIN)</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>MAHA
 (ENG)</t>
-        </is>
-      </c>
-      <c r="D45" s="7" t="inlineStr">
-        <is>
-          <t>BHAVANI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="E45" s="7" t="inlineStr">
-        <is>
-          <t>MAHA
-(GRAM)</t>
         </is>
       </c>
       <c r="F45" s="7" t="inlineStr">
@@ -9636,8 +9637,8 @@
       </c>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>LALITHA
-(EVS)</t>
+          <t>TULASI
+(MATH)</t>
         </is>
       </c>
       <c r="H45" s="7" t="inlineStr">
@@ -9648,38 +9649,37 @@
       </c>
       <c r="I45" s="7" t="inlineStr">
         <is>
-          <t>TULASI
-(MATH)</t>
+          <t>MARTIAL ARTS
+(KAR)</t>
         </is>
       </c>
       <c r="J45" s="7" t="inlineStr">
-        <is>
-          <t>RAVI
-(ENG)</t>
-        </is>
-      </c>
-      <c r="K45" s="7" t="inlineStr">
         <is>
           <t>FATHIMA
 (HIN)</t>
         </is>
       </c>
+      <c r="K45" s="7" t="inlineStr">
+        <is>
+          <t>LALITHA
+(BIO)</t>
+        </is>
+      </c>
       <c r="L45" s="7" t="inlineStr">
-        <is>
-          <t>D.V.RAO
-(TEL)</t>
-        </is>
-      </c>
-      <c r="M45" s="7" t="inlineStr">
         <is>
           <t>SUNITHA
 (SOC)</t>
         </is>
       </c>
-      <c r="N45" s="7" t="inlineStr">
+      <c r="M45" s="7" t="inlineStr">
         <is>
           <t>RIYA
 (HIN)</t>
+        </is>
+      </c>
+      <c r="N45" s="12" t="inlineStr">
+        <is>
+          <t>Recreation</t>
         </is>
       </c>
     </row>
@@ -9691,25 +9691,25 @@
       <c r="C46" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(ENG)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
-        <is>
-          <t>SAI LAKSHMI
-(ENG)</t>
-        </is>
-      </c>
-      <c r="E46" s="7" t="inlineStr">
         <is>
           <t>BHAVANI
 (MATH)</t>
         </is>
       </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>MAHESWARI
+(COMP)</t>
+        </is>
+      </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
-          <t>MARTIAL ARTS
-(KAR)</t>
+          <t>TULASI
+(MATH)</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
@@ -9720,14 +9720,14 @@
       </c>
       <c r="H46" s="7" t="inlineStr">
         <is>
-          <t>MAHESWARI
-(COMP)</t>
+          <t>LALITHA
+(EVS)</t>
         </is>
       </c>
       <c r="I46" s="7" t="inlineStr">
         <is>
-          <t>TULASI
-(MATH)</t>
+          <t>FATHIMA
+(HIN)</t>
         </is>
       </c>
       <c r="J46" s="7" t="inlineStr">
@@ -9744,20 +9744,20 @@
       </c>
       <c r="L46" s="7" t="inlineStr">
         <is>
+          <t>SONU
+(ENG)</t>
+        </is>
+      </c>
+      <c r="M46" s="7" t="inlineStr">
+        <is>
           <t>SUNITHA
 (SOC)</t>
         </is>
       </c>
-      <c r="M46" s="7" t="inlineStr">
-        <is>
-          <t>SONU
-(ENG)</t>
-        </is>
-      </c>
       <c r="N46" s="7" t="inlineStr">
         <is>
-          <t>D.V.RAO
-(TEL)</t>
+          <t>CHALAPATHI
+(BIO)</t>
         </is>
       </c>
     </row>
@@ -9769,7 +9769,7 @@
       <c r="C47" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(ENG)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
@@ -9780,32 +9780,32 @@
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
+          <t>NAGAMANI
+(G.K)</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="inlineStr">
+        <is>
           <t>SAI LAKSHMI
 (EVS)</t>
         </is>
       </c>
-      <c r="F47" s="7" t="inlineStr">
+      <c r="G47" s="7" t="inlineStr">
+        <is>
+          <t>RIYA
+(HIN)</t>
+        </is>
+      </c>
+      <c r="H47" s="7" t="inlineStr">
         <is>
           <t>MAHA
 (ENG)</t>
         </is>
       </c>
-      <c r="G47" s="7" t="inlineStr">
-        <is>
-          <t>MARTIAL ARTS
-(KAR)</t>
-        </is>
-      </c>
-      <c r="H47" s="7" t="inlineStr">
-        <is>
-          <t>LALITHA
-(EVS)</t>
-        </is>
-      </c>
       <c r="I47" s="7" t="inlineStr">
         <is>
-          <t>FATHIMA
-(HIN)</t>
+          <t>TULASI
+(MATH)</t>
         </is>
       </c>
       <c r="J47" s="7" t="inlineStr">
@@ -9816,25 +9816,26 @@
       </c>
       <c r="K47" s="7" t="inlineStr">
         <is>
+          <t>LALITHA
+(PHY)</t>
+        </is>
+      </c>
+      <c r="L47" s="7" t="inlineStr">
+        <is>
           <t>SANGEETHA
 (MATH)</t>
         </is>
       </c>
-      <c r="L47" s="7" t="inlineStr">
+      <c r="M47" s="7" t="inlineStr">
+        <is>
+          <t>CHALAPATHI
+(BIO)</t>
+        </is>
+      </c>
+      <c r="N47" s="7" t="inlineStr">
         <is>
           <t>SONU
 (ENG)</t>
-        </is>
-      </c>
-      <c r="M47" s="7" t="inlineStr">
-        <is>
-          <t>CHALAPATHI
-(BIO)</t>
-        </is>
-      </c>
-      <c r="N47" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
         </is>
       </c>
     </row>
@@ -9845,74 +9846,74 @@
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
+          <t>SITHA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
           <t>NAGAMANI
 (TEL)</t>
         </is>
       </c>
-      <c r="D48" s="7" t="inlineStr">
-        <is>
-          <t>SWATHI
-(HIN)</t>
-        </is>
-      </c>
       <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>SAI LAKSHMI
+(EVS)</t>
+        </is>
+      </c>
+      <c r="F48" s="7" t="inlineStr">
         <is>
           <t>MAHA
 (ENG)</t>
         </is>
       </c>
-      <c r="F48" s="7" t="inlineStr">
-        <is>
-          <t>TULASI
-(MATH)</t>
-        </is>
-      </c>
       <c r="G48" s="7" t="inlineStr">
+        <is>
+          <t>MAHESWARI
+(COMP)</t>
+        </is>
+      </c>
+      <c r="H48" s="7" t="inlineStr">
+        <is>
+          <t>SWATHI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="I48" s="7" t="inlineStr">
         <is>
           <t>PALLAVI
 (SOC)</t>
         </is>
       </c>
-      <c r="H48" s="7" t="inlineStr">
-        <is>
-          <t>FATHIMA
-(HIN)</t>
-        </is>
-      </c>
-      <c r="I48" s="7" t="inlineStr">
+      <c r="J48" s="7" t="inlineStr">
         <is>
           <t>LALITHA
-(EVS)</t>
-        </is>
-      </c>
-      <c r="J48" s="7" t="inlineStr">
-        <is>
-          <t>P.E
-(P.E.T)</t>
+(BIO)</t>
         </is>
       </c>
       <c r="K48" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
+          <t>D.V.RAO
+(TEL)</t>
         </is>
       </c>
       <c r="L48" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
+          <t>CHALAPATHI
+(BIO)</t>
         </is>
       </c>
       <c r="M48" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
+          <t>SONU
+(ENG)</t>
         </is>
       </c>
       <c r="N48" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
+          <t>SUNITHA
+(SOC)</t>
         </is>
       </c>
     </row>
@@ -9988,10 +9989,9 @@
 (CLASS)</t>
         </is>
       </c>
-      <c r="N49" s="8" t="inlineStr">
-        <is>
-          <t>SONU
-(ENG)</t>
+      <c r="N49" s="12" t="inlineStr">
+        <is>
+          <t>Recreation</t>
         </is>
       </c>
     </row>
